--- a/Result/checksun_type/塔架.xlsx
+++ b/Result/checksun_type/塔架.xlsx
@@ -878,12 +878,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>-8.16</t>
+          <t>-2.96</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>5388.546</t>
+          <t>4003.393</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -893,7 +893,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>137.5</t>
+          <t>133.5</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -908,12 +908,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-1.0</t>
+          <t>-1.8</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>18.56</t>
+          <t>36.89</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -923,7 +923,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>-65.0</t>
+          <t>-90.0</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -978,7 +978,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-41.98</t>
+          <t>-43.67</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -988,17 +988,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>22.28</t>
+          <t>16.56</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>-5.06</t>
+          <t>-5.24</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1009,12 +1009,12 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>130</t>
+          <t>40</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>5389</t>
+          <t>4003</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
@@ -1029,57 +1029,57 @@
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>-6.59</t>
+          <t>-7.23</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>-4.57</t>
+          <t>-5.73</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>-6.11</t>
+          <t>-6.6</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>-5.70</t>
+          <t>-5.82</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>147.2</t>
+          <t>143.9</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>154.25</t>
+          <t>152.65</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>164.29</t>
+          <t>163.44</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>174.21</t>
+          <t>173.54</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>-13.45</t>
+          <t>-22.90</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>-6.00</t>
+          <t>-6.89</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>-5.29</t>
+          <t>-5.61</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -1089,7 +1089,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-121.24</t>
+          <t>-122.53</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1099,41 +1099,41 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>1704071593.966715</t>
+          <t>1702786797.786849</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>753939618.0</t>
+          <t>543328425.0</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>239835367.0</t>
+          <t>317370279.0</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>202283159.5</t>
+          <t>231842549.9</t>
         </is>
       </c>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>250790390.86</t>
+          <t>254515985.98</t>
         </is>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>37552207</t>
+          <t>85527729</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>-12161789.58854426</t>
+          <t>-3818988.443072045</t>
         </is>
       </c>
       <c r="BC2" t="n">
-        <v>23946656.01</v>
+        <v>42066417.86</v>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
@@ -1152,7 +1152,7 @@
       </c>
       <c r="BG2" t="inlineStr">
         <is>
-          <t>-23.61</t>
+          <t>-25.83</t>
         </is>
       </c>
       <c r="BH2" t="inlineStr">
@@ -1182,37 +1182,37 @@
       </c>
       <c r="BM2" t="inlineStr">
         <is>
-          <t>-6.515514567392438</t>
+          <t>7.556077963084796</t>
         </is>
       </c>
       <c r="BN2" t="inlineStr">
         <is>
-          <t>2.378389744623612</t>
+          <t>10.88205073781603</t>
         </is>
       </c>
       <c r="BO2" t="inlineStr">
         <is>
-          <t>22.58355091692932</t>
+          <t>19.50943262662372</t>
         </is>
       </c>
       <c r="BP2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;衝高回落,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>價跌量增</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
         <is>
-          <t>3.17</t>
+          <t>3.08</t>
         </is>
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>3.03</t>
+          <t>3.12</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
@@ -1222,7 +1222,7 @@
       </c>
       <c r="BU2" t="inlineStr">
         <is>
-          <t>25.85</t>
+          <t>25.09</t>
         </is>
       </c>
       <c r="BV2" t="inlineStr">
@@ -1237,12 +1237,12 @@
       </c>
       <c r="BX2" t="inlineStr">
         <is>
-          <t>29.59</t>
+          <t>28.92</t>
         </is>
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>33948</t>
+          <t>32961</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
@@ -1262,22 +1262,22 @@
       </c>
       <c r="CC2" t="inlineStr">
         <is>
-          <t>147.0</t>
+          <t>135.0</t>
         </is>
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>147.0</t>
+          <t>141.5</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>135.0</t>
+          <t>132.5</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>137.5</t>
+          <t>133.5</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
@@ -1309,12 +1309,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-8.16</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>617.888</t>
+          <t>5388.546</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1324,7 +1324,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>149.5</t>
+          <t>137.5</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1334,17 +1334,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-8.73</t>
+          <t>-3.0</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-1.0</t>
+          <t>-1.8</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>-14.19</t>
+          <t>18.56</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1354,7 +1354,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>-65.0</t>
+          <t>-90.0</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -1409,7 +1409,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-36.92</t>
+          <t>-41.98</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1419,17 +1419,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>2.56</t>
+          <t>22.28</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>-1.34</t>
+          <t>-5.06</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1440,12 +1440,12 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>130</t>
+          <t>40</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>5389</t>
+          <t>4003</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
@@ -1460,57 +1460,57 @@
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>-0.07</t>
+          <t>-6.59</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>-3.96</t>
+          <t>-4.57</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-5.65</t>
+          <t>-6.11</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>-5.63</t>
+          <t>-5.70</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>149.6</t>
+          <t>147.2</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>155.78</t>
+          <t>154.25</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>165.1</t>
+          <t>164.29</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>174.95</t>
+          <t>174.21</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>-1.33</t>
+          <t>-13.45</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>-5.18</t>
+          <t>-6.00</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>-5.11</t>
+          <t>-5.29</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1520,7 +1520,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-120.53</t>
+          <t>-121.24</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1530,41 +1530,41 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>1704071593.966715</t>
+          <t>1702786797.786849</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>92809478.0</t>
+          <t>753939618.0</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>127850905.8</t>
+          <t>239835367.0</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>148995940.1</t>
+          <t>202283159.5</t>
         </is>
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>248204610.78</t>
+          <t>250790390.86</t>
         </is>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>-21145034</t>
+          <t>37552207</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>-18726961.5147791</t>
+          <t>-12161789.58854426</t>
         </is>
       </c>
       <c r="BC3" t="n">
-        <v>-25359440.75</v>
+        <v>23946656.01</v>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
@@ -1583,7 +1583,7 @@
       </c>
       <c r="BG3" t="inlineStr">
         <is>
-          <t>-16.94</t>
+          <t>-23.61</t>
         </is>
       </c>
       <c r="BH3" t="inlineStr">
@@ -1613,17 +1613,17 @@
       </c>
       <c r="BM3" t="inlineStr">
         <is>
-          <t>-6.515514567392438</t>
+          <t>7.556077963084796</t>
         </is>
       </c>
       <c r="BN3" t="inlineStr">
         <is>
-          <t>2.378389744623612</t>
+          <t>10.88205073781603</t>
         </is>
       </c>
       <c r="BO3" t="inlineStr">
         <is>
-          <t>22.58355091692932</t>
+          <t>19.50943262662372</t>
         </is>
       </c>
       <c r="BP3" t="inlineStr">
@@ -1633,17 +1633,17 @@
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價跌量增</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
         <is>
-          <t>3.44</t>
+          <t>3.17</t>
         </is>
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>3.03</t>
+          <t>3.12</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
@@ -1653,7 +1653,7 @@
       </c>
       <c r="BU3" t="inlineStr">
         <is>
-          <t>25.85</t>
+          <t>25.09</t>
         </is>
       </c>
       <c r="BV3" t="inlineStr">
@@ -1668,12 +1668,12 @@
       </c>
       <c r="BX3" t="inlineStr">
         <is>
-          <t>29.59</t>
+          <t>28.92</t>
         </is>
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>33948</t>
+          <t>32961</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
@@ -1693,22 +1693,22 @@
       </c>
       <c r="CC3" t="inlineStr">
         <is>
-          <t>150.0</t>
+          <t>147.0</t>
         </is>
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>151.5</t>
+          <t>147.0</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>149.5</t>
+          <t>135.0</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>149.5</t>
+          <t>137.5</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
@@ -1745,7 +1745,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>723.545</t>
+          <t>617.888</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1765,17 +1765,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-8.73</t>
+          <t>-11.99</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-1.0</t>
+          <t>-1.8</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>-23.11</t>
+          <t>-14.19</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1785,7 +1785,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>-65.0</t>
+          <t>-90.0</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -1850,17 +1850,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>2.99</t>
+          <t>2.56</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>-1.67</t>
+          <t>-1.34</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1871,12 +1871,12 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>130</t>
+          <t>40</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>5389</t>
+          <t>4003</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
@@ -1886,62 +1886,62 @@
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>2.22</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>-0.47</t>
+          <t>-0.07</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>-4.07</t>
+          <t>-3.96</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>-5.55</t>
+          <t>-5.65</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>-5.58</t>
+          <t>-5.63</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>150.2</t>
+          <t>149.6</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>156.57</t>
+          <t>155.78</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>165.78</t>
+          <t>165.1</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>175.58</t>
+          <t>174.95</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>-3.60</t>
+          <t>-1.33</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>-5.28</t>
+          <t>-5.18</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>-5.09</t>
+          <t>-5.11</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1951,7 +1951,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-120.46</t>
+          <t>-120.53</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1961,41 +1961,41 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>1704071593.966715</t>
+          <t>1702786797.786849</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>108786918.0</t>
+          <t>92809478.0</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>129166834.4</t>
+          <t>127850905.8</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>167987433.4</t>
+          <t>148995940.1</t>
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>261232164.76</t>
+          <t>248204610.78</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>-38820599</t>
+          <t>-21145034</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>-17521056.19996015</t>
+          <t>-18726961.5147791</t>
         </is>
       </c>
       <c r="BC4" t="n">
-        <v>-24055655.37</v>
+        <v>-25359440.75</v>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
@@ -2044,22 +2044,22 @@
       </c>
       <c r="BM4" t="inlineStr">
         <is>
-          <t>-6.515514567392438</t>
+          <t>7.556077963084796</t>
         </is>
       </c>
       <c r="BN4" t="inlineStr">
         <is>
-          <t>2.378389744623612</t>
+          <t>10.88205073781603</t>
         </is>
       </c>
       <c r="BO4" t="inlineStr">
         <is>
-          <t>22.58355091692932</t>
+          <t>19.50943262662372</t>
         </is>
       </c>
       <c r="BP4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ4" t="inlineStr">
@@ -2074,7 +2074,7 @@
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>3.03</t>
+          <t>3.12</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
@@ -2084,7 +2084,7 @@
       </c>
       <c r="BU4" t="inlineStr">
         <is>
-          <t>25.85</t>
+          <t>25.09</t>
         </is>
       </c>
       <c r="BV4" t="inlineStr">
@@ -2099,12 +2099,12 @@
       </c>
       <c r="BX4" t="inlineStr">
         <is>
-          <t>29.59</t>
+          <t>28.92</t>
         </is>
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>33948</t>
+          <t>32961</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
@@ -2124,17 +2124,17 @@
       </c>
       <c r="CC4" t="inlineStr">
         <is>
+          <t>150.0</t>
+        </is>
+      </c>
+      <c r="CD4" t="inlineStr">
+        <is>
           <t>151.5</t>
         </is>
       </c>
-      <c r="CD4" t="inlineStr">
-        <is>
-          <t>152.5</t>
-        </is>
-      </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>149.0</t>
+          <t>149.5</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
@@ -2171,12 +2171,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>-0.33</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>586.018</t>
+          <t>723.545</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2196,17 +2196,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-8.73</t>
+          <t>-11.99</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-1.0</t>
+          <t>-1.8</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>-28.30</t>
+          <t>-23.11</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2216,7 +2216,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>-65.0</t>
+          <t>-90.0</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -2281,17 +2281,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>2.42</t>
+          <t>2.99</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>-1.34</t>
+          <t>-1.67</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2302,12 +2302,12 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>130</t>
+          <t>40</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>5389</t>
+          <t>4003</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
@@ -2322,57 +2322,57 @@
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>-0.86</t>
+          <t>-0.47</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>-4.25</t>
+          <t>-4.07</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>-5.43</t>
+          <t>-5.55</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>-5.49</t>
+          <t>-5.58</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>150.8</t>
+          <t>150.2</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>157.5</t>
+          <t>156.57</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>166.55</t>
+          <t>165.78</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>176.23</t>
+          <t>175.58</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>-5.51</t>
+          <t>-3.60</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>-5.32</t>
+          <t>-5.28</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>-5.05</t>
+          <t>-5.09</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-120.28</t>
+          <t>-120.46</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2392,41 +2392,41 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>1704071593.966715</t>
+          <t>1702786797.786849</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>87986956.0</t>
+          <t>108786918.0</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>130706959.2</t>
+          <t>129166834.4</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>182292868.5</t>
+          <t>167987433.4</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>265109106.98</t>
+          <t>261232164.76</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>-51585909</t>
+          <t>-38820599</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>-16332947.26079137</t>
+          <t>-17521056.19996015</t>
         </is>
       </c>
       <c r="BC5" t="n">
-        <v>-23045842.84</v>
+        <v>-24055655.37</v>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
@@ -2475,22 +2475,22 @@
       </c>
       <c r="BM5" t="inlineStr">
         <is>
-          <t>-6.515514567392438</t>
+          <t>7.556077963084796</t>
         </is>
       </c>
       <c r="BN5" t="inlineStr">
         <is>
-          <t>2.378389744623612</t>
+          <t>10.88205073781603</t>
         </is>
       </c>
       <c r="BO5" t="inlineStr">
         <is>
-          <t>22.58355091692932</t>
+          <t>19.50943262662372</t>
         </is>
       </c>
       <c r="BP5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ5" t="inlineStr">
@@ -2505,7 +2505,7 @@
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>3.03</t>
+          <t>3.12</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
@@ -2515,7 +2515,7 @@
       </c>
       <c r="BU5" t="inlineStr">
         <is>
-          <t>25.85</t>
+          <t>25.09</t>
         </is>
       </c>
       <c r="BV5" t="inlineStr">
@@ -2530,12 +2530,12 @@
       </c>
       <c r="BX5" t="inlineStr">
         <is>
-          <t>29.59</t>
+          <t>28.92</t>
         </is>
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>33948</t>
+          <t>32961</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
@@ -2560,12 +2560,12 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>151.5</t>
+          <t>152.5</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>149.5</t>
+          <t>149.0</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
@@ -2602,12 +2602,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>0.33</t>
+          <t>-0.33</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>1040.36</t>
+          <t>586.018</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2617,7 +2617,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>150.0</t>
+          <t>149.5</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2627,17 +2627,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-9.09</t>
+          <t>-11.99</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-1.0</t>
+          <t>-1.8</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>-24.53</t>
+          <t>-28.30</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2647,7 +2647,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>-65.0</t>
+          <t>-90.0</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -2702,7 +2702,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-36.71</t>
+          <t>-36.92</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2712,17 +2712,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>4.30</t>
+          <t>2.42</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>1.39</t>
+          <t>-1.34</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2733,17 +2733,17 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>130</t>
+          <t>40</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>5389</t>
+          <t>4003</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>6.67</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
@@ -2753,57 +2753,57 @@
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>-1.12</t>
+          <t>-0.86</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>-4.31</t>
+          <t>-4.25</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>-5.31</t>
+          <t>-5.43</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>-5.34</t>
+          <t>-5.49</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>151.7</t>
+          <t>150.8</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>158.52</t>
+          <t>157.5</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>167.41</t>
+          <t>166.55</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>176.86</t>
+          <t>176.23</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>-6.68</t>
+          <t>-5.51</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>-5.31</t>
+          <t>-5.32</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>-4.98</t>
+          <t>-5.05</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -2813,7 +2813,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-120.00</t>
+          <t>-120.28</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2823,41 +2823,41 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>1704071593.966715</t>
+          <t>1702786797.786849</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>155653865.0</t>
+          <t>87986956.0</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>146314820.8</t>
+          <t>130706959.2</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>193869307.6</t>
+          <t>182292868.5</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>274342437.92</t>
+          <t>265109106.98</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>-47554486</t>
+          <t>-51585909</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>-15112420.79113203</t>
+          <t>-16332947.26079137</t>
         </is>
       </c>
       <c r="BC6" t="n">
-        <v>-18551620.35</v>
+        <v>-23045842.84</v>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
@@ -2876,7 +2876,7 @@
       </c>
       <c r="BG6" t="inlineStr">
         <is>
-          <t>-16.67</t>
+          <t>-16.94</t>
         </is>
       </c>
       <c r="BH6" t="inlineStr">
@@ -2906,22 +2906,22 @@
       </c>
       <c r="BM6" t="inlineStr">
         <is>
-          <t>-6.515514567392438</t>
+          <t>7.556077963084796</t>
         </is>
       </c>
       <c r="BN6" t="inlineStr">
         <is>
-          <t>2.378389744623612</t>
+          <t>10.88205073781603</t>
         </is>
       </c>
       <c r="BO6" t="inlineStr">
         <is>
-          <t>22.58355091692932</t>
+          <t>19.50943262662372</t>
         </is>
       </c>
       <c r="BP6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;可能出現反轉訊號&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;3&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ6" t="inlineStr">
@@ -2931,12 +2931,12 @@
       </c>
       <c r="BR6" t="inlineStr">
         <is>
-          <t>3.46</t>
+          <t>3.44</t>
         </is>
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>3.03</t>
+          <t>3.12</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="BU6" t="inlineStr">
         <is>
-          <t>25.85</t>
+          <t>25.09</t>
         </is>
       </c>
       <c r="BV6" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="BX6" t="inlineStr">
         <is>
-          <t>29.59</t>
+          <t>28.92</t>
         </is>
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>33948</t>
+          <t>32961</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
@@ -2986,7 +2986,7 @@
       </c>
       <c r="CC6" t="inlineStr">
         <is>
-          <t>150.5</t>
+          <t>151.5</t>
         </is>
       </c>
       <c r="CD6" t="inlineStr">
@@ -2996,12 +2996,12 @@
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>146.5</t>
+          <t>149.5</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>150.0</t>
+          <t>149.5</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
@@ -3033,12 +3033,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>-1.97</t>
+          <t>0.33</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1294.619</t>
+          <t>1040.36</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3048,7 +3048,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>149.5</t>
+          <t>150.0</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3058,17 +3058,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-8.73</t>
+          <t>-12.36</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-1.0</t>
+          <t>-1.8</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>-16.90</t>
+          <t>-24.53</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3078,7 +3078,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>-65.0</t>
+          <t>-90.0</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -3133,7 +3133,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-36.92</t>
+          <t>-36.71</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3143,17 +3143,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>5.35</t>
+          <t>4.30</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>-1.00</t>
+          <t>1.39</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3164,77 +3164,77 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>130</t>
+          <t>40</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>5389</t>
+          <t>4003</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>6.67</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>2.22</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>-2.35</t>
+          <t>-1.12</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>-3.97</t>
+          <t>-4.31</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>-5.19</t>
+          <t>-5.31</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>-5.28</t>
+          <t>-5.34</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>153.1</t>
+          <t>151.7</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>159.43</t>
+          <t>158.52</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>168.15</t>
+          <t>167.41</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>177.52</t>
+          <t>176.86</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>-7.56</t>
+          <t>-6.68</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>-5.26</t>
+          <t>-5.31</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>-4.89</t>
+          <t>-4.98</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -3244,7 +3244,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-119.66</t>
+          <t>-120.00</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3254,41 +3254,41 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>1704071593.966715</t>
+          <t>1702786797.786849</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>194017312.0</t>
+          <t>155653865.0</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>164730952.0</t>
+          <t>146314820.8</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>198237890.5</t>
+          <t>193869307.6</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>287305576.32</t>
+          <t>274342437.92</t>
         </is>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>-33506938</t>
+          <t>-47554486</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>-14487111.77960444</t>
+          <t>-15112420.79113203</t>
         </is>
       </c>
       <c r="BC7" t="n">
-        <v>-18718770.61</v>
+        <v>-18551620.35</v>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
@@ -3307,7 +3307,7 @@
       </c>
       <c r="BG7" t="inlineStr">
         <is>
-          <t>-16.94</t>
+          <t>-16.67</t>
         </is>
       </c>
       <c r="BH7" t="inlineStr">
@@ -3337,22 +3337,22 @@
       </c>
       <c r="BM7" t="inlineStr">
         <is>
-          <t>-6.515514567392438</t>
+          <t>7.556077963084796</t>
         </is>
       </c>
       <c r="BN7" t="inlineStr">
         <is>
-          <t>2.378389744623612</t>
+          <t>10.88205073781603</t>
         </is>
       </c>
       <c r="BO7" t="inlineStr">
         <is>
-          <t>22.58355091692932</t>
+          <t>19.50943262662372</t>
         </is>
       </c>
       <c r="BP7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;可能出現反轉訊號&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;3&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ7" t="inlineStr">
@@ -3362,12 +3362,12 @@
       </c>
       <c r="BR7" t="inlineStr">
         <is>
-          <t>3.44</t>
+          <t>3.46</t>
         </is>
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>3.03</t>
+          <t>3.12</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
@@ -3377,7 +3377,7 @@
       </c>
       <c r="BU7" t="inlineStr">
         <is>
-          <t>25.85</t>
+          <t>25.09</t>
         </is>
       </c>
       <c r="BV7" t="inlineStr">
@@ -3392,12 +3392,12 @@
       </c>
       <c r="BX7" t="inlineStr">
         <is>
-          <t>29.59</t>
+          <t>28.92</t>
         </is>
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>33948</t>
+          <t>32961</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
@@ -3417,22 +3417,22 @@
       </c>
       <c r="CC7" t="inlineStr">
         <is>
-          <t>152.0</t>
+          <t>150.5</t>
         </is>
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>152.0</t>
+          <t>151.5</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>148.5</t>
+          <t>146.5</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>149.5</t>
+          <t>150.0</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
@@ -3464,12 +3464,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-1.97</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>653.151</t>
+          <t>1294.619</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3479,7 +3479,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>152.5</t>
+          <t>149.5</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3489,17 +3489,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-10.91</t>
+          <t>-11.99</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-1.0</t>
+          <t>-1.8</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>-18.28</t>
+          <t>-16.90</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3509,7 +3509,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>-65.0</t>
+          <t>-90.0</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -3564,7 +3564,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-35.65</t>
+          <t>-36.92</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3574,17 +3574,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-06</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>2.70</t>
+          <t>5.35</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>-0.32</t>
+          <t>-1.00</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3595,12 +3595,12 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>130</t>
+          <t>40</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>5389</t>
+          <t>4003</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
@@ -3610,62 +3610,62 @@
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>2.38</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>-0.91</t>
+          <t>-2.35</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>-4.07</t>
+          <t>-3.97</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>-5.07</t>
+          <t>-5.19</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>-5.19</t>
+          <t>-5.28</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>153.9</t>
+          <t>153.1</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>160.43</t>
+          <t>159.43</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>169.0</t>
+          <t>168.15</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>178.25</t>
+          <t>177.52</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>-5.77</t>
+          <t>-7.56</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>-5.08</t>
+          <t>-5.26</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>-4.80</t>
+          <t>-4.89</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -3675,7 +3675,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-119.29</t>
+          <t>-119.66</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3685,41 +3685,41 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>1704071593.966715</t>
+          <t>1702786797.786849</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>99389121.0</t>
+          <t>194017312.0</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>170140974.4</t>
+          <t>164730952.0</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>208211819.2</t>
+          <t>198237890.5</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>301691507.7</t>
+          <t>287305576.32</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>-38070844</t>
+          <t>-33506938</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>-13717719.26552568</t>
+          <t>-14487111.77960444</t>
         </is>
       </c>
       <c r="BC8" t="n">
-        <v>-22399398.48</v>
+        <v>-18718770.61</v>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
@@ -3738,7 +3738,7 @@
       </c>
       <c r="BG8" t="inlineStr">
         <is>
-          <t>-15.28</t>
+          <t>-16.94</t>
         </is>
       </c>
       <c r="BH8" t="inlineStr">
@@ -3768,22 +3768,22 @@
       </c>
       <c r="BM8" t="inlineStr">
         <is>
-          <t>-6.515514567392438</t>
+          <t>7.556077963084796</t>
         </is>
       </c>
       <c r="BN8" t="inlineStr">
         <is>
-          <t>2.378389744623612</t>
+          <t>10.88205073781603</t>
         </is>
       </c>
       <c r="BO8" t="inlineStr">
         <is>
-          <t>22.58355091692932</t>
+          <t>19.50943262662372</t>
         </is>
       </c>
       <c r="BP8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ8" t="inlineStr">
@@ -3793,12 +3793,12 @@
       </c>
       <c r="BR8" t="inlineStr">
         <is>
-          <t>3.51</t>
+          <t>3.44</t>
         </is>
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>3.03</t>
+          <t>3.12</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
@@ -3808,7 +3808,7 @@
       </c>
       <c r="BU8" t="inlineStr">
         <is>
-          <t>25.85</t>
+          <t>25.09</t>
         </is>
       </c>
       <c r="BV8" t="inlineStr">
@@ -3823,12 +3823,12 @@
       </c>
       <c r="BX8" t="inlineStr">
         <is>
-          <t>29.59</t>
+          <t>28.92</t>
         </is>
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>33948</t>
+          <t>32961</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
@@ -3848,22 +3848,22 @@
       </c>
       <c r="CC8" t="inlineStr">
         <is>
-          <t>154.0</t>
+          <t>152.0</t>
         </is>
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>154.5</t>
+          <t>152.0</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>151.0</t>
+          <t>148.5</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>152.5</t>
+          <t>149.5</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
@@ -3895,12 +3895,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>-0.98</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>767.34</t>
+          <t>653.151</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3920,17 +3920,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-10.91</t>
+          <t>-14.23</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-1.0</t>
+          <t>-1.8</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>-2.01</t>
+          <t>-18.28</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3940,7 +3940,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>-65.0</t>
+          <t>-90.0</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -4005,17 +4005,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-05</t>
+          <t>2025-11-06</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>3.17</t>
+          <t>2.70</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>0.35</t>
+          <t>-0.32</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4026,12 +4026,12 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>130</t>
+          <t>40</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>5389</t>
+          <t>4003</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
@@ -4041,62 +4041,62 @@
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>17.94</t>
+          <t>2.38</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>-1.17</t>
+          <t>-0.91</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>-4.49</t>
+          <t>-4.07</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>-4.9</t>
+          <t>-5.07</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>-5.05</t>
+          <t>-5.19</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>154.3</t>
+          <t>153.9</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>161.55</t>
+          <t>160.43</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>169.88</t>
+          <t>169.0</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>178.91</t>
+          <t>178.25</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>-7.21</t>
+          <t>-5.77</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>-5.07</t>
+          <t>-5.08</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>-4.73</t>
+          <t>-4.80</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -4106,7 +4106,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-119.01</t>
+          <t>-119.29</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4116,41 +4116,41 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>1704071593.966715</t>
+          <t>1702786797.786849</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>116487542.0</t>
+          <t>99389121.0</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>206808032.4</t>
+          <t>170140974.4</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>211045311.6</t>
+          <t>208211819.2</t>
         </is>
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>314221303.24</t>
+          <t>301691507.7</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>-4237279</t>
+          <t>-38070844</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>-12139232.13529545</t>
+          <t>-13717719.26552568</t>
         </is>
       </c>
       <c r="BC9" t="n">
-        <v>-16718725.04</v>
+        <v>-22399398.48</v>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
@@ -4199,22 +4199,22 @@
       </c>
       <c r="BM9" t="inlineStr">
         <is>
-          <t>-6.515514567392438</t>
+          <t>7.556077963084796</t>
         </is>
       </c>
       <c r="BN9" t="inlineStr">
         <is>
-          <t>2.378389744623612</t>
+          <t>10.88205073781603</t>
         </is>
       </c>
       <c r="BO9" t="inlineStr">
         <is>
-          <t>22.58355091692932</t>
+          <t>19.50943262662372</t>
         </is>
       </c>
       <c r="BP9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ9" t="inlineStr">
@@ -4229,7 +4229,7 @@
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>3.03</t>
+          <t>3.12</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
@@ -4239,7 +4239,7 @@
       </c>
       <c r="BU9" t="inlineStr">
         <is>
-          <t>25.85</t>
+          <t>25.09</t>
         </is>
       </c>
       <c r="BV9" t="inlineStr">
@@ -4254,12 +4254,12 @@
       </c>
       <c r="BX9" t="inlineStr">
         <is>
-          <t>29.59</t>
+          <t>28.92</t>
         </is>
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>33948</t>
+          <t>32961</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
@@ -4279,17 +4279,17 @@
       </c>
       <c r="CC9" t="inlineStr">
         <is>
-          <t>153.0</t>
+          <t>154.0</t>
         </is>
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>154.0</t>
+          <t>154.5</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>150.5</t>
+          <t>151.0</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
@@ -4326,12 +4326,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>-1.9</t>
+          <t>-0.98</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>1062.556</t>
+          <t>767.34</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4341,7 +4341,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>154.0</t>
+          <t>152.5</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4351,17 +4351,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-12.0</t>
+          <t>-14.23</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-1.0</t>
+          <t>-1.8</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>8.13</t>
+          <t>-2.01</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4371,7 +4371,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>-65.0</t>
+          <t>-90.0</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -4426,7 +4426,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-35.02</t>
+          <t>-35.65</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4436,17 +4436,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-04</t>
+          <t>2025-11-05</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>4.39</t>
+          <t>3.17</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>-2.92</t>
+          <t>0.35</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4457,17 +4457,17 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>130</t>
+          <t>40</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>5389</t>
+          <t>4003</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>7.14</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
@@ -4477,57 +4477,57 @@
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>-0.58</t>
+          <t>-1.17</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>-4.59</t>
+          <t>-4.49</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>-4.89</t>
+          <t>-4.9</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>-4.93</t>
+          <t>-5.05</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>154.9</t>
+          <t>154.3</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>162.35</t>
+          <t>161.55</t>
         </is>
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>170.7</t>
+          <t>169.88</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>179.54</t>
+          <t>178.91</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>-7.45</t>
+          <t>-7.21</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>-4.99</t>
+          <t>-5.07</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>-4.65</t>
+          <t>-4.73</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -4537,7 +4537,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-118.67</t>
+          <t>-119.01</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4547,41 +4547,41 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>1704071593.966715</t>
+          <t>1702786797.786849</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>166026264.0</t>
+          <t>116487542.0</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>233878777.8</t>
+          <t>206808032.4</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>216301717.4</t>
+          <t>211045311.6</t>
         </is>
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>327913288.88</t>
+          <t>314221303.24</t>
         </is>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>17577060</t>
+          <t>-4237279</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>-11306597.06250142</t>
+          <t>-12139232.13529545</t>
         </is>
       </c>
       <c r="BC10" t="n">
-        <v>-9838353.609999999</v>
+        <v>-16718725.04</v>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
@@ -4600,7 +4600,7 @@
       </c>
       <c r="BG10" t="inlineStr">
         <is>
-          <t>-14.44</t>
+          <t>-15.28</t>
         </is>
       </c>
       <c r="BH10" t="inlineStr">
@@ -4630,22 +4630,22 @@
       </c>
       <c r="BM10" t="inlineStr">
         <is>
-          <t>-6.515514567392438</t>
+          <t>7.556077963084796</t>
         </is>
       </c>
       <c r="BN10" t="inlineStr">
         <is>
-          <t>2.378389744623612</t>
+          <t>10.88205073781603</t>
         </is>
       </c>
       <c r="BO10" t="inlineStr">
         <is>
-          <t>22.58355091692932</t>
+          <t>19.50943262662372</t>
         </is>
       </c>
       <c r="BP10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ10" t="inlineStr">
@@ -4655,12 +4655,12 @@
       </c>
       <c r="BR10" t="inlineStr">
         <is>
-          <t>3.55</t>
+          <t>3.51</t>
         </is>
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>3.03</t>
+          <t>3.12</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
@@ -4670,7 +4670,7 @@
       </c>
       <c r="BU10" t="inlineStr">
         <is>
-          <t>25.85</t>
+          <t>25.09</t>
         </is>
       </c>
       <c r="BV10" t="inlineStr">
@@ -4685,12 +4685,12 @@
       </c>
       <c r="BX10" t="inlineStr">
         <is>
-          <t>29.59</t>
+          <t>28.92</t>
         </is>
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>33948</t>
+          <t>32961</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
@@ -4710,22 +4710,22 @@
       </c>
       <c r="CC10" t="inlineStr">
         <is>
-          <t>157.5</t>
+          <t>153.0</t>
         </is>
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>158.5</t>
+          <t>154.0</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>154.0</t>
+          <t>150.5</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>154.0</t>
+          <t>152.5</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
@@ -4757,12 +4757,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>2.28</t>
+          <t>-1.9</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>1583.205</t>
+          <t>1062.556</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4772,7 +4772,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>157.0</t>
+          <t>154.0</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4782,17 +4782,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-14.18</t>
+          <t>-15.36</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-1.0</t>
+          <t>-1.8</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>2.53</t>
+          <t>8.13</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4802,7 +4802,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>-65.0</t>
+          <t>-90.0</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -4857,7 +4857,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-33.76</t>
+          <t>-35.02</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4867,17 +4867,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-03</t>
+          <t>2025-11-04</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>6.55</t>
+          <t>4.39</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>1.01</t>
+          <t>-2.92</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4888,77 +4888,77 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>130</t>
+          <t>40</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>5389</t>
+          <t>4003</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>46.67</t>
+          <t>7.14</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>15.56</t>
+          <t>17.94</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>0.90</t>
+          <t>-0.58</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>-4.61</t>
+          <t>-4.59</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>-4.84</t>
+          <t>-4.89</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>-4.85</t>
+          <t>-4.93</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>155.6</t>
+          <t>154.9</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>163.12</t>
+          <t>162.35</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>171.42</t>
+          <t>170.7</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>180.16</t>
+          <t>179.54</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>-9.00</t>
+          <t>-7.45</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>-4.97</t>
+          <t>-4.99</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>-4.56</t>
+          <t>-4.65</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -4968,7 +4968,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-118.32</t>
+          <t>-118.67</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -4978,41 +4978,41 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>1704071593.966715</t>
+          <t>1702786797.786849</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>247734521.0</t>
+          <t>166026264.0</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>241423794.4</t>
+          <t>233878777.8</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>235467468.4</t>
+          <t>216301717.4</t>
         </is>
       </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>338636186.98</t>
+          <t>327913288.88</t>
         </is>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>5956326</t>
+          <t>17577060</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>-11573550.41725676</t>
+          <t>-11306597.06250142</t>
         </is>
       </c>
       <c r="BC11" t="n">
-        <v>-4965602.02</v>
+        <v>-9838353.609999999</v>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
@@ -5031,7 +5031,7 @@
       </c>
       <c r="BG11" t="inlineStr">
         <is>
-          <t>-12.78</t>
+          <t>-14.44</t>
         </is>
       </c>
       <c r="BH11" t="inlineStr">
@@ -5061,22 +5061,22 @@
       </c>
       <c r="BM11" t="inlineStr">
         <is>
-          <t>-6.515514567392438</t>
+          <t>7.556077963084796</t>
         </is>
       </c>
       <c r="BN11" t="inlineStr">
         <is>
-          <t>2.378389744623612</t>
+          <t>10.88205073781603</t>
         </is>
       </c>
       <c r="BO11" t="inlineStr">
         <is>
-          <t>22.58355091692932</t>
+          <t>19.50943262662372</t>
         </is>
       </c>
       <c r="BP11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ11" t="inlineStr">
@@ -5086,12 +5086,12 @@
       </c>
       <c r="BR11" t="inlineStr">
         <is>
-          <t>3.62</t>
+          <t>3.55</t>
         </is>
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>3.03</t>
+          <t>3.12</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
@@ -5101,7 +5101,7 @@
       </c>
       <c r="BU11" t="inlineStr">
         <is>
-          <t>25.85</t>
+          <t>25.09</t>
         </is>
       </c>
       <c r="BV11" t="inlineStr">
@@ -5116,12 +5116,12 @@
       </c>
       <c r="BX11" t="inlineStr">
         <is>
-          <t>29.59</t>
+          <t>28.92</t>
         </is>
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>33948</t>
+          <t>32961</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
@@ -5141,22 +5141,22 @@
       </c>
       <c r="CC11" t="inlineStr">
         <is>
-          <t>153.5</t>
+          <t>157.5</t>
         </is>
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>159.0</t>
+          <t>158.5</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>153.5</t>
+          <t>154.0</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>157.0</t>
+          <t>154.0</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
@@ -5188,12 +5188,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>-0.65</t>
+          <t>2.28</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>1432.343</t>
+          <t>1583.205</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5203,7 +5203,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>153.5</t>
+          <t>157.0</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5213,17 +5213,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-11.64</t>
+          <t>-17.6</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-1.0</t>
+          <t>-1.8</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>-1.40</t>
+          <t>2.53</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5233,7 +5233,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>-65.0</t>
+          <t>-90.0</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -5288,7 +5288,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-35.23</t>
+          <t>-33.76</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5298,17 +5298,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-10-31</t>
+          <t>2025-11-03</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>5.92</t>
+          <t>6.55</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>-1.63</t>
+          <t>1.01</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5319,77 +5319,77 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>130</t>
+          <t>40</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>5389</t>
+          <t>4003</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>46.67</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>15.56</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>-1.54</t>
+          <t>0.90</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>-4.81</t>
+          <t>-4.61</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
+          <t>-4.84</t>
+        </is>
+      </c>
+      <c r="AK12" t="inlineStr">
+        <is>
           <t>-4.85</t>
         </is>
       </c>
-      <c r="AK12" t="inlineStr">
-        <is>
-          <t>-4.81</t>
-        </is>
-      </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>155.9</t>
+          <t>155.6</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>163.78</t>
+          <t>163.12</t>
         </is>
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>172.12</t>
+          <t>171.42</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>180.82</t>
+          <t>180.16</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>-16.10</t>
+          <t>-9.00</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>-5.18</t>
+          <t>-4.97</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>-4.46</t>
+          <t>-4.56</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
@@ -5399,7 +5399,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-117.91</t>
+          <t>-118.32</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5409,41 +5409,41 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>1704071593.966715</t>
+          <t>1702786797.786849</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>221067424.0</t>
+          <t>247734521.0</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>231744829.0</t>
+          <t>241423794.4</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>235023973.1</t>
+          <t>235467468.4</t>
         </is>
       </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>344452883.32</t>
+          <t>338636186.98</t>
         </is>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>-3279144</t>
+          <t>5956326</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>-12774995.58056483</t>
+          <t>-11573550.41725676</t>
         </is>
       </c>
       <c r="BC12" t="n">
-        <v>-6581641.49</v>
+        <v>-4965602.02</v>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
@@ -5462,7 +5462,7 @@
       </c>
       <c r="BG12" t="inlineStr">
         <is>
-          <t>-14.72</t>
+          <t>-12.78</t>
         </is>
       </c>
       <c r="BH12" t="inlineStr">
@@ -5492,22 +5492,22 @@
       </c>
       <c r="BM12" t="inlineStr">
         <is>
-          <t>-6.515514567392438</t>
+          <t>7.556077963084796</t>
         </is>
       </c>
       <c r="BN12" t="inlineStr">
         <is>
-          <t>2.378389744623612</t>
+          <t>10.88205073781603</t>
         </is>
       </c>
       <c r="BO12" t="inlineStr">
         <is>
-          <t>22.58355091692932</t>
+          <t>19.50943262662372</t>
         </is>
       </c>
       <c r="BP12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ12" t="inlineStr">
@@ -5517,12 +5517,12 @@
       </c>
       <c r="BR12" t="inlineStr">
         <is>
-          <t>3.54</t>
+          <t>3.62</t>
         </is>
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>3.03</t>
+          <t>3.12</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
@@ -5532,7 +5532,7 @@
       </c>
       <c r="BU12" t="inlineStr">
         <is>
-          <t>25.85</t>
+          <t>25.09</t>
         </is>
       </c>
       <c r="BV12" t="inlineStr">
@@ -5547,12 +5547,12 @@
       </c>
       <c r="BX12" t="inlineStr">
         <is>
-          <t>29.59</t>
+          <t>28.92</t>
         </is>
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>33948</t>
+          <t>32961</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
@@ -5572,22 +5572,22 @@
       </c>
       <c r="CC12" t="inlineStr">
         <is>
-          <t>154.5</t>
+          <t>153.5</t>
         </is>
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>156.5</t>
+          <t>159.0</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>153.0</t>
+          <t>153.5</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>153.5</t>
+          <t>157.0</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
@@ -5619,12 +5619,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>-1.71</t>
+          <t>-1.34</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>1408.733</t>
+          <t>1065.248</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -5634,7 +5634,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>37.45</t>
+          <t>36.95</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -5649,12 +5649,12 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>-1.11</t>
+          <t>-1.02</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>22.93</t>
+          <t>28.28</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -5719,7 +5719,7 @@
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>-13.21</t>
+          <t>-14.37</t>
         </is>
       </c>
       <c r="X13" t="inlineStr">
@@ -5729,17 +5729,17 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>15.01</t>
+          <t>11.35</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>-2.94</t>
+          <t>-0.81</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
@@ -5755,7 +5755,7 @@
       </c>
       <c r="AE13" t="inlineStr">
         <is>
-          <t>1409</t>
+          <t>1065</t>
         </is>
       </c>
       <c r="AF13" t="inlineStr">
@@ -5765,62 +5765,62 @@
       </c>
       <c r="AG13" t="inlineStr">
         <is>
-          <t>16.69</t>
+          <t>9.38</t>
         </is>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>-1.42</t>
+          <t>-1.86</t>
         </is>
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>-3.63</t>
+          <t>-4.02</t>
         </is>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>-3.96</t>
+          <t>-4.09</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>-1.34</t>
+          <t>-1.60</t>
         </is>
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>37.99</t>
+          <t>37.65000000000001</t>
         </is>
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>39.42</t>
+          <t>39.23</t>
         </is>
       </c>
       <c r="AN13" t="inlineStr">
         <is>
-          <t>41.05</t>
+          <t>40.9</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>41.6</t>
+          <t>41.57</t>
         </is>
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>-15.49</t>
+          <t>-18.37</t>
         </is>
       </c>
       <c r="AQ13" t="inlineStr">
         <is>
-          <t>-0.91</t>
+          <t>-0.97</t>
         </is>
       </c>
       <c r="AR13" t="inlineStr">
         <is>
-          <t>-0.78</t>
+          <t>-0.82</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr">
@@ -5830,7 +5830,7 @@
       </c>
       <c r="AT13" t="inlineStr">
         <is>
-          <t>-129.19</t>
+          <t>-130.59</t>
         </is>
       </c>
       <c r="AU13" t="inlineStr">
@@ -5840,41 +5840,41 @@
       </c>
       <c r="AV13" t="inlineStr">
         <is>
-          <t>151111618.248191</t>
+          <t>150978598.7687861</t>
         </is>
       </c>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>53218422.0</t>
+          <t>39374759.0</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>36341855.6</t>
+          <t>40349216.0</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>29562657.9</t>
+          <t>31454761.9</t>
         </is>
       </c>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>28846965.04</t>
+          <t>29061426.18</t>
         </is>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
-          <t>6779197</t>
+          <t>8894454</t>
         </is>
       </c>
       <c r="BB13" t="inlineStr">
         <is>
-          <t>149309.3019995387</t>
+          <t>507671.8217403347</t>
         </is>
       </c>
       <c r="BC13" t="n">
-        <v>2288252.23</v>
+        <v>2478665.68</v>
       </c>
       <c r="BD13" t="inlineStr">
         <is>
@@ -5893,7 +5893,7 @@
       </c>
       <c r="BG13" t="inlineStr">
         <is>
-          <t>-9.76</t>
+          <t>-10.96</t>
         </is>
       </c>
       <c r="BH13" t="inlineStr">
@@ -5923,37 +5923,37 @@
       </c>
       <c r="BM13" t="inlineStr">
         <is>
-          <t>-4.834008229657466</t>
+          <t>-13.67996844119094</t>
         </is>
       </c>
       <c r="BN13" t="inlineStr">
         <is>
-          <t>-0.138178351458681</t>
+          <t>-10.11024290164889</t>
         </is>
       </c>
       <c r="BO13" t="inlineStr">
         <is>
-          <t>28.83362772156236</t>
+          <t>24.12947661306339</t>
         </is>
       </c>
       <c r="BP13" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BQ13" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BR13" t="inlineStr">
         <is>
-          <t>1.03</t>
+          <t>1.02</t>
         </is>
       </c>
       <c r="BS13" t="inlineStr">
         <is>
-          <t>6.68</t>
+          <t>6.77</t>
         </is>
       </c>
       <c r="BT13" t="inlineStr">
@@ -5963,7 +5963,7 @@
       </c>
       <c r="BU13" t="inlineStr">
         <is>
-          <t>15.48</t>
+          <t>15.27</t>
         </is>
       </c>
       <c r="BV13" t="inlineStr">
@@ -5978,12 +5978,12 @@
       </c>
       <c r="BX13" t="inlineStr">
         <is>
-          <t>29.59</t>
+          <t>28.92</t>
         </is>
       </c>
       <c r="BY13" t="inlineStr">
         <is>
-          <t>12027</t>
+          <t>11866</t>
         </is>
       </c>
       <c r="BZ13" t="inlineStr">
@@ -6003,22 +6003,22 @@
       </c>
       <c r="CC13" t="inlineStr">
         <is>
-          <t>38.1</t>
+          <t>37.3</t>
         </is>
       </c>
       <c r="CD13" t="inlineStr">
         <is>
-          <t>38.7</t>
+          <t>37.5</t>
         </is>
       </c>
       <c r="CE13" t="inlineStr">
         <is>
-          <t>37.3</t>
+          <t>36.7</t>
         </is>
       </c>
       <c r="CF13" t="inlineStr">
         <is>
-          <t>37.45</t>
+          <t>36.95</t>
         </is>
       </c>
       <c r="CG13" t="inlineStr">
@@ -6050,12 +6050,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-1.71</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>504.317</t>
+          <t>1408.733</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -6065,7 +6065,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>38.1</t>
+          <t>37.45</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -6075,17 +6075,17 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>-1.74</t>
+          <t>-1.35</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>-1.11</t>
+          <t>-1.02</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>20.39</t>
+          <t>22.93</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -6150,7 +6150,7 @@
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>-11.70</t>
+          <t>-13.21</t>
         </is>
       </c>
       <c r="X14" t="inlineStr">
@@ -6160,17 +6160,17 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>5.37</t>
+          <t>15.01</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>-0.39</t>
+          <t>-2.94</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
@@ -6186,12 +6186,12 @@
       </c>
       <c r="AE14" t="inlineStr">
         <is>
-          <t>1409</t>
+          <t>1065</t>
         </is>
       </c>
       <c r="AF14" t="inlineStr">
         <is>
-          <t>28.13</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG14" t="inlineStr">
@@ -6201,57 +6201,57 @@
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>-0.55</t>
+          <t>-1.42</t>
         </is>
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>-3.22</t>
+          <t>-3.63</t>
         </is>
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>-3.86</t>
+          <t>-3.96</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>-1.12</t>
+          <t>-1.34</t>
         </is>
       </c>
       <c r="AL14" t="inlineStr">
         <is>
-          <t>38.31</t>
+          <t>37.99</t>
         </is>
       </c>
       <c r="AM14" t="inlineStr">
         <is>
-          <t>39.58</t>
+          <t>39.42</t>
         </is>
       </c>
       <c r="AN14" t="inlineStr">
         <is>
-          <t>41.17</t>
+          <t>41.05</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>41.64</t>
+          <t>41.6</t>
         </is>
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>-13.76</t>
+          <t>-15.49</t>
         </is>
       </c>
       <c r="AQ14" t="inlineStr">
         <is>
-          <t>-0.86</t>
+          <t>-0.91</t>
         </is>
       </c>
       <c r="AR14" t="inlineStr">
         <is>
-          <t>-0.75</t>
+          <t>-0.78</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr">
@@ -6261,7 +6261,7 @@
       </c>
       <c r="AT14" t="inlineStr">
         <is>
-          <t>-128.06</t>
+          <t>-129.19</t>
         </is>
       </c>
       <c r="AU14" t="inlineStr">
@@ -6271,41 +6271,41 @@
       </c>
       <c r="AV14" t="inlineStr">
         <is>
-          <t>151111618.248191</t>
+          <t>150978598.7687861</t>
         </is>
       </c>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>19248593.0</t>
+          <t>53218422.0</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>31147112.0</t>
+          <t>36341855.6</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
-          <t>25871081.1</t>
+          <t>29562657.9</t>
         </is>
       </c>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>28091032.78</t>
+          <t>28846965.04</t>
         </is>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
-          <t>5276030</t>
+          <t>6779197</t>
         </is>
       </c>
       <c r="BB14" t="inlineStr">
         <is>
-          <t>-239589.4123123131</t>
+          <t>149309.3019995387</t>
         </is>
       </c>
       <c r="BC14" t="n">
-        <v>451260.12</v>
+        <v>2288252.23</v>
       </c>
       <c r="BD14" t="inlineStr">
         <is>
@@ -6324,7 +6324,7 @@
       </c>
       <c r="BG14" t="inlineStr">
         <is>
-          <t>-8.19</t>
+          <t>-9.76</t>
         </is>
       </c>
       <c r="BH14" t="inlineStr">
@@ -6354,22 +6354,22 @@
       </c>
       <c r="BM14" t="inlineStr">
         <is>
-          <t>-4.834008229657466</t>
+          <t>-13.67996844119094</t>
         </is>
       </c>
       <c r="BN14" t="inlineStr">
         <is>
-          <t>-0.138178351458681</t>
+          <t>-10.11024290164889</t>
         </is>
       </c>
       <c r="BO14" t="inlineStr">
         <is>
-          <t>28.83362772156236</t>
+          <t>24.12947661306339</t>
         </is>
       </c>
       <c r="BP14" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ14" t="inlineStr">
@@ -6379,12 +6379,12 @@
       </c>
       <c r="BR14" t="inlineStr">
         <is>
-          <t>1.05</t>
+          <t>1.03</t>
         </is>
       </c>
       <c r="BS14" t="inlineStr">
         <is>
-          <t>6.68</t>
+          <t>6.77</t>
         </is>
       </c>
       <c r="BT14" t="inlineStr">
@@ -6394,7 +6394,7 @@
       </c>
       <c r="BU14" t="inlineStr">
         <is>
-          <t>15.48</t>
+          <t>15.27</t>
         </is>
       </c>
       <c r="BV14" t="inlineStr">
@@ -6409,12 +6409,12 @@
       </c>
       <c r="BX14" t="inlineStr">
         <is>
-          <t>29.59</t>
+          <t>28.92</t>
         </is>
       </c>
       <c r="BY14" t="inlineStr">
         <is>
-          <t>12027</t>
+          <t>11866</t>
         </is>
       </c>
       <c r="BZ14" t="inlineStr">
@@ -6434,22 +6434,22 @@
       </c>
       <c r="CC14" t="inlineStr">
         <is>
-          <t>38.2</t>
+          <t>38.1</t>
         </is>
       </c>
       <c r="CD14" t="inlineStr">
         <is>
-          <t>38.4</t>
+          <t>38.7</t>
         </is>
       </c>
       <c r="CE14" t="inlineStr">
         <is>
-          <t>37.95</t>
+          <t>37.3</t>
         </is>
       </c>
       <c r="CF14" t="inlineStr">
         <is>
-          <t>38.1</t>
+          <t>37.45</t>
         </is>
       </c>
       <c r="CG14" t="inlineStr">
@@ -6481,12 +6481,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>1.18</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>605.721</t>
+          <t>504.317</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -6506,17 +6506,17 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>-1.74</t>
+          <t>-3.11</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>-1.11</t>
+          <t>-1.02</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>29.75</t>
+          <t>20.39</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -6591,17 +6591,17 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>6.45</t>
+          <t>5.37</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>0.40</t>
+          <t>-0.39</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
@@ -6617,72 +6617,72 @@
       </c>
       <c r="AE15" t="inlineStr">
         <is>
-          <t>1409</t>
+          <t>1065</t>
         </is>
       </c>
       <c r="AF15" t="inlineStr">
         <is>
-          <t>21.95</t>
+          <t>28.13</t>
         </is>
       </c>
       <c r="AG15" t="inlineStr">
         <is>
-          <t>7.32</t>
+          <t>16.69</t>
         </is>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>-0.94</t>
+          <t>-0.55</t>
         </is>
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>-3.10</t>
+          <t>-3.22</t>
         </is>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>-3.87</t>
+          <t>-3.86</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>-0.91</t>
+          <t>-1.12</t>
         </is>
       </c>
       <c r="AL15" t="inlineStr">
         <is>
-          <t>38.46</t>
+          <t>38.31</t>
         </is>
       </c>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>39.69</t>
+          <t>39.58</t>
         </is>
       </c>
       <c r="AN15" t="inlineStr">
         <is>
-          <t>41.29</t>
+          <t>41.17</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>41.67</t>
+          <t>41.64</t>
         </is>
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>-16.76</t>
+          <t>-13.76</t>
         </is>
       </c>
       <c r="AQ15" t="inlineStr">
         <is>
-          <t>-0.85</t>
+          <t>-0.86</t>
         </is>
       </c>
       <c r="AR15" t="inlineStr">
         <is>
-          <t>-0.73</t>
+          <t>-0.75</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr">
@@ -6692,7 +6692,7 @@
       </c>
       <c r="AT15" t="inlineStr">
         <is>
-          <t>-127.09</t>
+          <t>-128.06</t>
         </is>
       </c>
       <c r="AU15" t="inlineStr">
@@ -6702,41 +6702,41 @@
       </c>
       <c r="AV15" t="inlineStr">
         <is>
-          <t>151111618.248191</t>
+          <t>150978598.7687861</t>
         </is>
       </c>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>23042470.0</t>
+          <t>19248593.0</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>33965584.0</t>
+          <t>31147112.0</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>26178217.9</t>
+          <t>25871081.1</t>
         </is>
       </c>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>28206383.42</t>
+          <t>28091032.78</t>
         </is>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
-          <t>7787366</t>
+          <t>5276030</t>
         </is>
       </c>
       <c r="BB15" t="inlineStr">
         <is>
-          <t>-365198.417442461</t>
+          <t>-239589.4123123131</t>
         </is>
       </c>
       <c r="BC15" t="n">
-        <v>1450493.77</v>
+        <v>451260.12</v>
       </c>
       <c r="BD15" t="inlineStr">
         <is>
@@ -6785,22 +6785,22 @@
       </c>
       <c r="BM15" t="inlineStr">
         <is>
-          <t>-4.834008229657466</t>
+          <t>-13.67996844119094</t>
         </is>
       </c>
       <c r="BN15" t="inlineStr">
         <is>
-          <t>-0.138178351458681</t>
+          <t>-10.11024290164889</t>
         </is>
       </c>
       <c r="BO15" t="inlineStr">
         <is>
-          <t>28.83362772156236</t>
+          <t>24.12947661306339</t>
         </is>
       </c>
       <c r="BP15" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;可能出現反轉訊號&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;3&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ15" t="inlineStr">
@@ -6815,7 +6815,7 @@
       </c>
       <c r="BS15" t="inlineStr">
         <is>
-          <t>6.68</t>
+          <t>6.77</t>
         </is>
       </c>
       <c r="BT15" t="inlineStr">
@@ -6825,7 +6825,7 @@
       </c>
       <c r="BU15" t="inlineStr">
         <is>
-          <t>15.48</t>
+          <t>15.27</t>
         </is>
       </c>
       <c r="BV15" t="inlineStr">
@@ -6840,12 +6840,12 @@
       </c>
       <c r="BX15" t="inlineStr">
         <is>
-          <t>29.59</t>
+          <t>28.92</t>
         </is>
       </c>
       <c r="BY15" t="inlineStr">
         <is>
-          <t>12027</t>
+          <t>11866</t>
         </is>
       </c>
       <c r="BZ15" t="inlineStr">
@@ -6865,17 +6865,17 @@
       </c>
       <c r="CC15" t="inlineStr">
         <is>
-          <t>38.0</t>
+          <t>38.2</t>
         </is>
       </c>
       <c r="CD15" t="inlineStr">
         <is>
-          <t>38.3</t>
+          <t>38.4</t>
         </is>
       </c>
       <c r="CE15" t="inlineStr">
         <is>
-          <t>37.75</t>
+          <t>37.95</t>
         </is>
       </c>
       <c r="CF15" t="inlineStr">
@@ -6912,12 +6912,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>-2.6</t>
+          <t>1.18</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>1764.112</t>
+          <t>605.721</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -6927,7 +6927,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>37.65</t>
+          <t>38.1</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -6937,17 +6937,17 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>-0.53</t>
+          <t>-3.11</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>-1.11</t>
+          <t>-1.02</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>21.53</t>
+          <t>29.75</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -7012,7 +7012,7 @@
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>-12.75</t>
+          <t>-11.70</t>
         </is>
       </c>
       <c r="X16" t="inlineStr">
@@ -7022,17 +7022,17 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>18.80</t>
+          <t>6.45</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>-2.12</t>
+          <t>0.40</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
@@ -7048,72 +7048,72 @@
       </c>
       <c r="AE16" t="inlineStr">
         <is>
-          <t>1409</t>
+          <t>1065</t>
         </is>
       </c>
       <c r="AF16" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>21.95</t>
         </is>
       </c>
       <c r="AG16" t="inlineStr">
         <is>
-          <t>6.67</t>
+          <t>7.32</t>
         </is>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>-2.44</t>
+          <t>-0.94</t>
         </is>
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>-3.03</t>
+          <t>-3.10</t>
         </is>
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>-3.91</t>
+          <t>-3.87</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>-0.66</t>
+          <t>-0.91</t>
         </is>
       </c>
       <c r="AL16" t="inlineStr">
         <is>
-          <t>38.59</t>
+          <t>38.46</t>
         </is>
       </c>
       <c r="AM16" t="inlineStr">
         <is>
-          <t>39.8</t>
+          <t>39.69</t>
         </is>
       </c>
       <c r="AN16" t="inlineStr">
         <is>
-          <t>41.42</t>
+          <t>41.29</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>41.69</t>
+          <t>41.67</t>
         </is>
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>-18.69</t>
+          <t>-16.76</t>
         </is>
       </c>
       <c r="AQ16" t="inlineStr">
         <is>
-          <t>-0.83</t>
+          <t>-0.85</t>
         </is>
       </c>
       <c r="AR16" t="inlineStr">
         <is>
-          <t>-0.70</t>
+          <t>-0.73</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr">
@@ -7123,7 +7123,7 @@
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>-125.95</t>
+          <t>-127.09</t>
         </is>
       </c>
       <c r="AU16" t="inlineStr">
@@ -7133,41 +7133,41 @@
       </c>
       <c r="AV16" t="inlineStr">
         <is>
-          <t>151111618.248191</t>
+          <t>150978598.7687861</t>
         </is>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>66861836.0</t>
+          <t>23042470.0</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>33260992.8</t>
+          <t>33965584.0</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>27368625.9</t>
+          <t>26178217.9</t>
         </is>
       </c>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>28716017.48</t>
+          <t>28206383.42</t>
         </is>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
-          <t>5892366</t>
+          <t>7787366</t>
         </is>
       </c>
       <c r="BB16" t="inlineStr">
         <is>
-          <t>-695324.269555022</t>
+          <t>-365198.417442461</t>
         </is>
       </c>
       <c r="BC16" t="n">
-        <v>2419680.25</v>
+        <v>1450493.77</v>
       </c>
       <c r="BD16" t="inlineStr">
         <is>
@@ -7186,7 +7186,7 @@
       </c>
       <c r="BG16" t="inlineStr">
         <is>
-          <t>-9.28</t>
+          <t>-8.19</t>
         </is>
       </c>
       <c r="BH16" t="inlineStr">
@@ -7216,37 +7216,37 @@
       </c>
       <c r="BM16" t="inlineStr">
         <is>
-          <t>-4.834008229657466</t>
+          <t>-13.67996844119094</t>
         </is>
       </c>
       <c r="BN16" t="inlineStr">
         <is>
-          <t>-0.138178351458681</t>
+          <t>-10.11024290164889</t>
         </is>
       </c>
       <c r="BO16" t="inlineStr">
         <is>
-          <t>28.83362772156236</t>
+          <t>24.12947661306339</t>
         </is>
       </c>
       <c r="BP16" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;可能出現反轉訊號&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;3&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ16" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BR16" t="inlineStr">
         <is>
-          <t>1.04</t>
+          <t>1.05</t>
         </is>
       </c>
       <c r="BS16" t="inlineStr">
         <is>
-          <t>6.68</t>
+          <t>6.77</t>
         </is>
       </c>
       <c r="BT16" t="inlineStr">
@@ -7256,7 +7256,7 @@
       </c>
       <c r="BU16" t="inlineStr">
         <is>
-          <t>15.48</t>
+          <t>15.27</t>
         </is>
       </c>
       <c r="BV16" t="inlineStr">
@@ -7271,12 +7271,12 @@
       </c>
       <c r="BX16" t="inlineStr">
         <is>
-          <t>29.59</t>
+          <t>28.92</t>
         </is>
       </c>
       <c r="BY16" t="inlineStr">
         <is>
-          <t>12027</t>
+          <t>11866</t>
         </is>
       </c>
       <c r="BZ16" t="inlineStr">
@@ -7296,22 +7296,22 @@
       </c>
       <c r="CC16" t="inlineStr">
         <is>
-          <t>38.45</t>
+          <t>38.0</t>
         </is>
       </c>
       <c r="CD16" t="inlineStr">
         <is>
-          <t>38.75</t>
+          <t>38.3</t>
         </is>
       </c>
       <c r="CE16" t="inlineStr">
         <is>
-          <t>37.35</t>
+          <t>37.75</t>
         </is>
       </c>
       <c r="CF16" t="inlineStr">
         <is>
-          <t>37.65</t>
+          <t>38.1</t>
         </is>
       </c>
       <c r="CG16" t="inlineStr">
@@ -7343,12 +7343,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>-1.03</t>
+          <t>-2.6</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>499.552</t>
+          <t>1764.112</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -7358,7 +7358,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>38.65</t>
+          <t>37.65</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -7368,17 +7368,17 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>-3.2</t>
+          <t>-1.89</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>-1.11</t>
+          <t>-1.02</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>0.16</t>
+          <t>21.53</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -7443,7 +7443,7 @@
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>-10.43</t>
+          <t>-12.75</t>
         </is>
       </c>
       <c r="X17" t="inlineStr">
@@ -7453,17 +7453,17 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>5.32</t>
+          <t>18.80</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>-1.42</t>
+          <t>-2.12</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
@@ -7479,7 +7479,7 @@
       </c>
       <c r="AE17" t="inlineStr">
         <is>
-          <t>1409</t>
+          <t>1065</t>
         </is>
       </c>
       <c r="AF17" t="inlineStr">
@@ -7489,17 +7489,17 @@
       </c>
       <c r="AG17" t="inlineStr">
         <is>
-          <t>8.47</t>
+          <t>6.67</t>
         </is>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>-0.57</t>
+          <t>-2.44</t>
         </is>
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>-2.61</t>
+          <t>-3.03</t>
         </is>
       </c>
       <c r="AJ17" t="inlineStr">
@@ -7509,42 +7509,42 @@
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>-0.43</t>
+          <t>-0.66</t>
         </is>
       </c>
       <c r="AL17" t="inlineStr">
         <is>
-          <t>38.87</t>
+          <t>38.59</t>
         </is>
       </c>
       <c r="AM17" t="inlineStr">
         <is>
-          <t>39.91</t>
+          <t>39.8</t>
         </is>
       </c>
       <c r="AN17" t="inlineStr">
         <is>
-          <t>41.54</t>
+          <t>41.42</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>41.72</t>
+          <t>41.69</t>
         </is>
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>-11.54</t>
+          <t>-18.69</t>
         </is>
       </c>
       <c r="AQ17" t="inlineStr">
         <is>
-          <t>-0.74</t>
+          <t>-0.83</t>
         </is>
       </c>
       <c r="AR17" t="inlineStr">
         <is>
-          <t>-0.66</t>
+          <t>-0.70</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr">
@@ -7554,7 +7554,7 @@
       </c>
       <c r="AT17" t="inlineStr">
         <is>
-          <t>-124.74</t>
+          <t>-125.95</t>
         </is>
       </c>
       <c r="AU17" t="inlineStr">
@@ -7564,41 +7564,41 @@
       </c>
       <c r="AV17" t="inlineStr">
         <is>
-          <t>151111618.248191</t>
+          <t>150978598.7687861</t>
         </is>
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>19337957.0</t>
+          <t>66861836.0</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>22560307.8</t>
+          <t>33260992.8</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>22524902.5</t>
+          <t>27368625.9</t>
         </is>
       </c>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>28140249.02</t>
+          <t>28716017.48</t>
         </is>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
-          <t>35405</t>
+          <t>5892366</t>
         </is>
       </c>
       <c r="BB17" t="inlineStr">
         <is>
-          <t>-1261688.726998104</t>
+          <t>-695324.269555022</t>
         </is>
       </c>
       <c r="BC17" t="n">
-        <v>-977116.87</v>
+        <v>2419680.25</v>
       </c>
       <c r="BD17" t="inlineStr">
         <is>
@@ -7617,7 +7617,7 @@
       </c>
       <c r="BG17" t="inlineStr">
         <is>
-          <t>-6.87</t>
+          <t>-9.28</t>
         </is>
       </c>
       <c r="BH17" t="inlineStr">
@@ -7647,37 +7647,37 @@
       </c>
       <c r="BM17" t="inlineStr">
         <is>
-          <t>-4.834008229657466</t>
+          <t>-13.67996844119094</t>
         </is>
       </c>
       <c r="BN17" t="inlineStr">
         <is>
-          <t>-0.138178351458681</t>
+          <t>-10.11024290164889</t>
         </is>
       </c>
       <c r="BO17" t="inlineStr">
         <is>
-          <t>28.83362772156236</t>
+          <t>24.12947661306339</t>
         </is>
       </c>
       <c r="BP17" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ17" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BR17" t="inlineStr">
         <is>
-          <t>1.06</t>
+          <t>1.04</t>
         </is>
       </c>
       <c r="BS17" t="inlineStr">
         <is>
-          <t>6.68</t>
+          <t>6.77</t>
         </is>
       </c>
       <c r="BT17" t="inlineStr">
@@ -7687,7 +7687,7 @@
       </c>
       <c r="BU17" t="inlineStr">
         <is>
-          <t>15.48</t>
+          <t>15.27</t>
         </is>
       </c>
       <c r="BV17" t="inlineStr">
@@ -7702,12 +7702,12 @@
       </c>
       <c r="BX17" t="inlineStr">
         <is>
-          <t>29.59</t>
+          <t>28.92</t>
         </is>
       </c>
       <c r="BY17" t="inlineStr">
         <is>
-          <t>12027</t>
+          <t>11866</t>
         </is>
       </c>
       <c r="BZ17" t="inlineStr">
@@ -7727,22 +7727,22 @@
       </c>
       <c r="CC17" t="inlineStr">
         <is>
-          <t>38.95</t>
+          <t>38.45</t>
         </is>
       </c>
       <c r="CD17" t="inlineStr">
         <is>
-          <t>39.3</t>
+          <t>38.75</t>
         </is>
       </c>
       <c r="CE17" t="inlineStr">
         <is>
-          <t>38.55</t>
+          <t>37.35</t>
         </is>
       </c>
       <c r="CF17" t="inlineStr">
         <is>
-          <t>38.65</t>
+          <t>37.65</t>
         </is>
       </c>
       <c r="CG17" t="inlineStr">
@@ -7774,12 +7774,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>0.51</t>
+          <t>-1.03</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>700.928</t>
+          <t>499.552</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -7789,7 +7789,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>39.05</t>
+          <t>38.65</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -7799,17 +7799,17 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>-4.27</t>
+          <t>-4.6</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>-1.11</t>
+          <t>-1.02</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>0.15</t>
+          <t>0.16</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -7874,7 +7874,7 @@
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>-9.50</t>
+          <t>-10.43</t>
         </is>
       </c>
       <c r="X18" t="inlineStr">
@@ -7884,17 +7884,17 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>7.47</t>
+          <t>5.32</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>1.17</t>
+          <t>-1.42</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
@@ -7910,12 +7910,12 @@
       </c>
       <c r="AE18" t="inlineStr">
         <is>
-          <t>1409</t>
+          <t>1065</t>
         </is>
       </c>
       <c r="AF18" t="inlineStr">
         <is>
-          <t>20.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG18" t="inlineStr">
@@ -7925,57 +7925,57 @@
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>0.15</t>
+          <t>-0.57</t>
         </is>
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>-2.53</t>
+          <t>-2.61</t>
         </is>
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>-3.9</t>
+          <t>-3.91</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>-0.25</t>
+          <t>-0.43</t>
         </is>
       </c>
       <c r="AL18" t="inlineStr">
         <is>
-          <t>38.99</t>
+          <t>38.87</t>
         </is>
       </c>
       <c r="AM18" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>39.91</t>
         </is>
       </c>
       <c r="AN18" t="inlineStr">
         <is>
-          <t>41.63</t>
+          <t>41.54</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>41.73</t>
+          <t>41.72</t>
         </is>
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>-11.93</t>
+          <t>-11.54</t>
         </is>
       </c>
       <c r="AQ18" t="inlineStr">
         <is>
-          <t>-0.72</t>
+          <t>-0.74</t>
         </is>
       </c>
       <c r="AR18" t="inlineStr">
         <is>
-          <t>-0.65</t>
+          <t>-0.66</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr">
@@ -7985,7 +7985,7 @@
       </c>
       <c r="AT18" t="inlineStr">
         <is>
-          <t>-124.03</t>
+          <t>-124.74</t>
         </is>
       </c>
       <c r="AU18" t="inlineStr">
@@ -7995,41 +7995,41 @@
       </c>
       <c r="AV18" t="inlineStr">
         <is>
-          <t>151111618.248191</t>
+          <t>150978598.7687861</t>
         </is>
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>27244704.0</t>
+          <t>19337957.0</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>22783460.2</t>
+          <t>22560307.8</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>22749645.3</t>
+          <t>22524902.5</t>
         </is>
       </c>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>28438883.58</t>
+          <t>28140249.02</t>
         </is>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
-          <t>33814</t>
+          <t>35405</t>
         </is>
       </c>
       <c r="BB18" t="inlineStr">
         <is>
-          <t>-1313429.065286876</t>
+          <t>-1261688.726998104</t>
         </is>
       </c>
       <c r="BC18" t="n">
-        <v>-702942.96</v>
+        <v>-977116.87</v>
       </c>
       <c r="BD18" t="inlineStr">
         <is>
@@ -8048,7 +8048,7 @@
       </c>
       <c r="BG18" t="inlineStr">
         <is>
-          <t>-5.90</t>
+          <t>-6.87</t>
         </is>
       </c>
       <c r="BH18" t="inlineStr">
@@ -8078,37 +8078,37 @@
       </c>
       <c r="BM18" t="inlineStr">
         <is>
-          <t>-4.834008229657466</t>
+          <t>-13.67996844119094</t>
         </is>
       </c>
       <c r="BN18" t="inlineStr">
         <is>
-          <t>-0.138178351458681</t>
+          <t>-10.11024290164889</t>
         </is>
       </c>
       <c r="BO18" t="inlineStr">
         <is>
-          <t>28.83362772156236</t>
+          <t>24.12947661306339</t>
         </is>
       </c>
       <c r="BP18" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ18" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BR18" t="inlineStr">
         <is>
-          <t>1.07</t>
+          <t>1.06</t>
         </is>
       </c>
       <c r="BS18" t="inlineStr">
         <is>
-          <t>6.68</t>
+          <t>6.77</t>
         </is>
       </c>
       <c r="BT18" t="inlineStr">
@@ -8118,7 +8118,7 @@
       </c>
       <c r="BU18" t="inlineStr">
         <is>
-          <t>15.48</t>
+          <t>15.27</t>
         </is>
       </c>
       <c r="BV18" t="inlineStr">
@@ -8133,12 +8133,12 @@
       </c>
       <c r="BX18" t="inlineStr">
         <is>
-          <t>29.59</t>
+          <t>28.92</t>
         </is>
       </c>
       <c r="BY18" t="inlineStr">
         <is>
-          <t>12027</t>
+          <t>11866</t>
         </is>
       </c>
       <c r="BZ18" t="inlineStr">
@@ -8158,22 +8158,22 @@
       </c>
       <c r="CC18" t="inlineStr">
         <is>
-          <t>38.85</t>
+          <t>38.95</t>
         </is>
       </c>
       <c r="CD18" t="inlineStr">
         <is>
-          <t>39.05</t>
+          <t>39.3</t>
         </is>
       </c>
       <c r="CE18" t="inlineStr">
         <is>
-          <t>38.6</t>
+          <t>38.55</t>
         </is>
       </c>
       <c r="CF18" t="inlineStr">
         <is>
-          <t>39.05</t>
+          <t>38.65</t>
         </is>
       </c>
       <c r="CG18" t="inlineStr">
@@ -8205,12 +8205,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>0.26</t>
+          <t>0.51</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>857.171</t>
+          <t>700.928</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -8220,7 +8220,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>38.85</t>
+          <t>39.05</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -8230,17 +8230,17 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>-3.74</t>
+          <t>-5.68</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>-1.11</t>
+          <t>-1.02</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>-6.52</t>
+          <t>0.15</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -8305,7 +8305,7 @@
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>-9.97</t>
+          <t>-9.50</t>
         </is>
       </c>
       <c r="X19" t="inlineStr">
@@ -8315,17 +8315,17 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-11-06</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>9.13</t>
+          <t>7.47</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>-0.13</t>
+          <t>1.17</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
@@ -8341,52 +8341,52 @@
       </c>
       <c r="AE19" t="inlineStr">
         <is>
-          <t>1409</t>
+          <t>1065</t>
         </is>
       </c>
       <c r="AF19" t="inlineStr">
         <is>
-          <t>5.41</t>
+          <t>20.0</t>
         </is>
       </c>
       <c r="AG19" t="inlineStr">
         <is>
-          <t>1.8</t>
+          <t>8.47</t>
         </is>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
-          <t>-0.69</t>
+          <t>0.15</t>
         </is>
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>-2.41</t>
+          <t>-2.53</t>
         </is>
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>-3.92</t>
+          <t>-3.9</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>-0.03</t>
+          <t>-0.25</t>
         </is>
       </c>
       <c r="AL19" t="inlineStr">
         <is>
-          <t>39.12</t>
+          <t>38.99</t>
         </is>
       </c>
       <c r="AM19" t="inlineStr">
         <is>
-          <t>40.08</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="AN19" t="inlineStr">
         <is>
-          <t>41.72</t>
+          <t>41.63</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
@@ -8396,17 +8396,17 @@
       </c>
       <c r="AP19" t="inlineStr">
         <is>
-          <t>-16.36</t>
+          <t>-11.93</t>
         </is>
       </c>
       <c r="AQ19" t="inlineStr">
         <is>
-          <t>-0.73</t>
+          <t>-0.72</t>
         </is>
       </c>
       <c r="AR19" t="inlineStr">
         <is>
-          <t>-0.63</t>
+          <t>-0.65</t>
         </is>
       </c>
       <c r="AS19" t="inlineStr">
@@ -8416,7 +8416,7 @@
       </c>
       <c r="AT19" t="inlineStr">
         <is>
-          <t>-123.31</t>
+          <t>-124.03</t>
         </is>
       </c>
       <c r="AU19" t="inlineStr">
@@ -8426,41 +8426,41 @@
       </c>
       <c r="AV19" t="inlineStr">
         <is>
-          <t>151111618.248191</t>
+          <t>150978598.7687861</t>
         </is>
       </c>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>33340953.0</t>
+          <t>27244704.0</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>20595050.2</t>
+          <t>22783460.2</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
-          <t>22030516.7</t>
+          <t>22749645.3</t>
         </is>
       </c>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>28317533.86</t>
+          <t>28438883.58</t>
         </is>
       </c>
       <c r="BA19" t="inlineStr">
         <is>
-          <t>-1435466</t>
+          <t>33814</t>
         </is>
       </c>
       <c r="BB19" t="inlineStr">
         <is>
-          <t>-1424426.538814767</t>
+          <t>-1313429.065286876</t>
         </is>
       </c>
       <c r="BC19" t="n">
-        <v>-1133312.31</v>
+        <v>-702942.96</v>
       </c>
       <c r="BD19" t="inlineStr">
         <is>
@@ -8479,7 +8479,7 @@
       </c>
       <c r="BG19" t="inlineStr">
         <is>
-          <t>-6.39</t>
+          <t>-5.90</t>
         </is>
       </c>
       <c r="BH19" t="inlineStr">
@@ -8509,22 +8509,22 @@
       </c>
       <c r="BM19" t="inlineStr">
         <is>
-          <t>-4.834008229657466</t>
+          <t>-13.67996844119094</t>
         </is>
       </c>
       <c r="BN19" t="inlineStr">
         <is>
-          <t>-0.138178351458681</t>
+          <t>-10.11024290164889</t>
         </is>
       </c>
       <c r="BO19" t="inlineStr">
         <is>
-          <t>28.83362772156236</t>
+          <t>24.12947661306339</t>
         </is>
       </c>
       <c r="BP19" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ19" t="inlineStr">
@@ -8539,7 +8539,7 @@
       </c>
       <c r="BS19" t="inlineStr">
         <is>
-          <t>6.68</t>
+          <t>6.77</t>
         </is>
       </c>
       <c r="BT19" t="inlineStr">
@@ -8549,7 +8549,7 @@
       </c>
       <c r="BU19" t="inlineStr">
         <is>
-          <t>15.48</t>
+          <t>15.27</t>
         </is>
       </c>
       <c r="BV19" t="inlineStr">
@@ -8564,12 +8564,12 @@
       </c>
       <c r="BX19" t="inlineStr">
         <is>
-          <t>29.59</t>
+          <t>28.92</t>
         </is>
       </c>
       <c r="BY19" t="inlineStr">
         <is>
-          <t>12027</t>
+          <t>11866</t>
         </is>
       </c>
       <c r="BZ19" t="inlineStr">
@@ -8589,22 +8589,22 @@
       </c>
       <c r="CC19" t="inlineStr">
         <is>
-          <t>38.95</t>
+          <t>38.85</t>
         </is>
       </c>
       <c r="CD19" t="inlineStr">
         <is>
-          <t>39.1</t>
+          <t>39.05</t>
         </is>
       </c>
       <c r="CE19" t="inlineStr">
         <is>
-          <t>38.65</t>
+          <t>38.6</t>
         </is>
       </c>
       <c r="CF19" t="inlineStr">
         <is>
-          <t>38.85</t>
+          <t>39.05</t>
         </is>
       </c>
       <c r="CG19" t="inlineStr">
@@ -8636,12 +8636,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>-0.77</t>
+          <t>0.26</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>504.24</t>
+          <t>857.171</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -8651,7 +8651,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>38.75</t>
+          <t>38.85</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -8661,17 +8661,17 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>-3.47</t>
+          <t>-5.14</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>-1.11</t>
+          <t>-1.02</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>-9.08</t>
+          <t>-6.52</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -8736,7 +8736,7 @@
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>-10.20</t>
+          <t>-9.97</t>
         </is>
       </c>
       <c r="X20" t="inlineStr">
@@ -8746,17 +8746,17 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-11-05</t>
+          <t>2025-11-06</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>5.37</t>
+          <t>9.13</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>-0.13</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
@@ -8772,72 +8772,72 @@
       </c>
       <c r="AE20" t="inlineStr">
         <is>
-          <t>1409</t>
+          <t>1065</t>
         </is>
       </c>
       <c r="AF20" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>5.41</t>
         </is>
       </c>
       <c r="AG20" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.8</t>
         </is>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
-          <t>-1.40</t>
+          <t>-0.69</t>
         </is>
       </c>
       <c r="AI20" t="inlineStr">
         <is>
-          <t>-2.22</t>
+          <t>-2.41</t>
         </is>
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>-3.89</t>
+          <t>-3.92</t>
         </is>
       </c>
       <c r="AK20" t="inlineStr">
         <is>
-          <t>0.23</t>
+          <t>-0.03</t>
         </is>
       </c>
       <c r="AL20" t="inlineStr">
         <is>
-          <t>39.3</t>
+          <t>39.12</t>
         </is>
       </c>
       <c r="AM20" t="inlineStr">
         <is>
-          <t>40.19</t>
+          <t>40.08</t>
         </is>
       </c>
       <c r="AN20" t="inlineStr">
         <is>
-          <t>41.82</t>
+          <t>41.72</t>
         </is>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>41.72</t>
+          <t>41.73</t>
         </is>
       </c>
       <c r="AP20" t="inlineStr">
         <is>
-          <t>-17.47</t>
+          <t>-16.36</t>
         </is>
       </c>
       <c r="AQ20" t="inlineStr">
         <is>
-          <t>-0.71</t>
+          <t>-0.73</t>
         </is>
       </c>
       <c r="AR20" t="inlineStr">
         <is>
-          <t>-0.60</t>
+          <t>-0.63</t>
         </is>
       </c>
       <c r="AS20" t="inlineStr">
@@ -8847,7 +8847,7 @@
       </c>
       <c r="AT20" t="inlineStr">
         <is>
-          <t>-122.36</t>
+          <t>-123.31</t>
         </is>
       </c>
       <c r="AU20" t="inlineStr">
@@ -8857,41 +8857,41 @@
       </c>
       <c r="AV20" t="inlineStr">
         <is>
-          <t>151111618.248191</t>
+          <t>150978598.7687861</t>
         </is>
       </c>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>19519514.0</t>
+          <t>33340953.0</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>18390851.8</t>
+          <t>20595050.2</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
-          <t>20228126.1</t>
+          <t>22030516.7</t>
         </is>
       </c>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>28082029.5</t>
+          <t>28317533.86</t>
         </is>
       </c>
       <c r="BA20" t="inlineStr">
         <is>
-          <t>-1837274</t>
+          <t>-1435466</t>
         </is>
       </c>
       <c r="BB20" t="inlineStr">
         <is>
-          <t>-1477356.398321357</t>
+          <t>-1424426.538814767</t>
         </is>
       </c>
       <c r="BC20" t="n">
-        <v>-2360819.77</v>
+        <v>-1133312.31</v>
       </c>
       <c r="BD20" t="inlineStr">
         <is>
@@ -8910,7 +8910,7 @@
       </c>
       <c r="BG20" t="inlineStr">
         <is>
-          <t>-6.63</t>
+          <t>-6.39</t>
         </is>
       </c>
       <c r="BH20" t="inlineStr">
@@ -8940,27 +8940,27 @@
       </c>
       <c r="BM20" t="inlineStr">
         <is>
-          <t>-4.834008229657466</t>
+          <t>-13.67996844119094</t>
         </is>
       </c>
       <c r="BN20" t="inlineStr">
         <is>
-          <t>-0.138178351458681</t>
+          <t>-10.11024290164889</t>
         </is>
       </c>
       <c r="BO20" t="inlineStr">
         <is>
-          <t>28.83362772156236</t>
+          <t>24.12947661306339</t>
         </is>
       </c>
       <c r="BP20" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ20" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BR20" t="inlineStr">
@@ -8970,7 +8970,7 @@
       </c>
       <c r="BS20" t="inlineStr">
         <is>
-          <t>6.68</t>
+          <t>6.77</t>
         </is>
       </c>
       <c r="BT20" t="inlineStr">
@@ -8980,7 +8980,7 @@
       </c>
       <c r="BU20" t="inlineStr">
         <is>
-          <t>15.48</t>
+          <t>15.27</t>
         </is>
       </c>
       <c r="BV20" t="inlineStr">
@@ -8995,12 +8995,12 @@
       </c>
       <c r="BX20" t="inlineStr">
         <is>
-          <t>29.59</t>
+          <t>28.92</t>
         </is>
       </c>
       <c r="BY20" t="inlineStr">
         <is>
-          <t>12027</t>
+          <t>11866</t>
         </is>
       </c>
       <c r="BZ20" t="inlineStr">
@@ -9020,22 +9020,22 @@
       </c>
       <c r="CC20" t="inlineStr">
         <is>
-          <t>39.15</t>
+          <t>38.95</t>
         </is>
       </c>
       <c r="CD20" t="inlineStr">
         <is>
-          <t>39.15</t>
+          <t>39.1</t>
         </is>
       </c>
       <c r="CE20" t="inlineStr">
         <is>
-          <t>38.35</t>
+          <t>38.65</t>
         </is>
       </c>
       <c r="CF20" t="inlineStr">
         <is>
-          <t>38.75</t>
+          <t>38.85</t>
         </is>
       </c>
       <c r="CG20" t="inlineStr">
@@ -9067,12 +9067,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>-0.51</t>
+          <t>-0.77</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>340.21</t>
+          <t>504.24</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -9082,7 +9082,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>39.05</t>
+          <t>38.75</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -9092,17 +9092,17 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>-4.27</t>
+          <t>-4.87</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>-1.11</t>
+          <t>-1.02</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>2.77</t>
+          <t>-9.08</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -9167,7 +9167,7 @@
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>-9.50</t>
+          <t>-10.20</t>
         </is>
       </c>
       <c r="X21" t="inlineStr">
@@ -9177,17 +9177,17 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-11-04</t>
+          <t>2025-11-05</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>3.63</t>
+          <t>5.37</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>-1.41</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
@@ -9203,7 +9203,7 @@
       </c>
       <c r="AE21" t="inlineStr">
         <is>
-          <t>1409</t>
+          <t>1065</t>
         </is>
       </c>
       <c r="AF21" t="inlineStr">
@@ -9218,57 +9218,57 @@
       </c>
       <c r="AH21" t="inlineStr">
         <is>
-          <t>-1.21</t>
+          <t>-1.40</t>
         </is>
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>-1.92</t>
+          <t>-2.22</t>
         </is>
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>-3.88</t>
+          <t>-3.89</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
         <is>
-          <t>0.53</t>
+          <t>0.23</t>
         </is>
       </c>
       <c r="AL21" t="inlineStr">
         <is>
-          <t>39.53</t>
+          <t>39.3</t>
         </is>
       </c>
       <c r="AM21" t="inlineStr">
         <is>
-          <t>40.3</t>
+          <t>40.19</t>
         </is>
       </c>
       <c r="AN21" t="inlineStr">
         <is>
-          <t>41.93</t>
+          <t>41.82</t>
         </is>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>41.71</t>
+          <t>41.72</t>
         </is>
       </c>
       <c r="AP21" t="inlineStr">
         <is>
-          <t>-14.13</t>
+          <t>-17.47</t>
         </is>
       </c>
       <c r="AQ21" t="inlineStr">
         <is>
-          <t>-0.66</t>
+          <t>-0.71</t>
         </is>
       </c>
       <c r="AR21" t="inlineStr">
         <is>
-          <t>-0.57</t>
+          <t>-0.60</t>
         </is>
       </c>
       <c r="AS21" t="inlineStr">
@@ -9278,7 +9278,7 @@
       </c>
       <c r="AT21" t="inlineStr">
         <is>
-          <t>-121.38</t>
+          <t>-122.36</t>
         </is>
       </c>
       <c r="AU21" t="inlineStr">
@@ -9288,41 +9288,41 @@
       </c>
       <c r="AV21" t="inlineStr">
         <is>
-          <t>151111618.248191</t>
+          <t>150978598.7687861</t>
         </is>
       </c>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>13358411.0</t>
+          <t>19519514.0</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>21476259.0</t>
+          <t>18390851.8</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
-          <t>20896470.1</t>
+          <t>20228126.1</t>
         </is>
       </c>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>28018183.18</t>
+          <t>28082029.5</t>
         </is>
       </c>
       <c r="BA21" t="inlineStr">
         <is>
-          <t>579788</t>
+          <t>-1837274</t>
         </is>
       </c>
       <c r="BB21" t="inlineStr">
         <is>
-          <t>-1316726.695178018</t>
+          <t>-1477356.398321357</t>
         </is>
       </c>
       <c r="BC21" t="n">
-        <v>-2549218.39</v>
+        <v>-2360819.77</v>
       </c>
       <c r="BD21" t="inlineStr">
         <is>
@@ -9341,7 +9341,7 @@
       </c>
       <c r="BG21" t="inlineStr">
         <is>
-          <t>-5.90</t>
+          <t>-6.63</t>
         </is>
       </c>
       <c r="BH21" t="inlineStr">
@@ -9371,22 +9371,22 @@
       </c>
       <c r="BM21" t="inlineStr">
         <is>
-          <t>-4.834008229657466</t>
+          <t>-13.67996844119094</t>
         </is>
       </c>
       <c r="BN21" t="inlineStr">
         <is>
-          <t>-0.138178351458681</t>
+          <t>-10.11024290164889</t>
         </is>
       </c>
       <c r="BO21" t="inlineStr">
         <is>
-          <t>28.83362772156236</t>
+          <t>24.12947661306339</t>
         </is>
       </c>
       <c r="BP21" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BQ21" t="inlineStr">
@@ -9401,7 +9401,7 @@
       </c>
       <c r="BS21" t="inlineStr">
         <is>
-          <t>6.68</t>
+          <t>6.77</t>
         </is>
       </c>
       <c r="BT21" t="inlineStr">
@@ -9411,7 +9411,7 @@
       </c>
       <c r="BU21" t="inlineStr">
         <is>
-          <t>15.48</t>
+          <t>15.27</t>
         </is>
       </c>
       <c r="BV21" t="inlineStr">
@@ -9426,12 +9426,12 @@
       </c>
       <c r="BX21" t="inlineStr">
         <is>
-          <t>29.59</t>
+          <t>28.92</t>
         </is>
       </c>
       <c r="BY21" t="inlineStr">
         <is>
-          <t>12027</t>
+          <t>11866</t>
         </is>
       </c>
       <c r="BZ21" t="inlineStr">
@@ -9451,22 +9451,22 @@
       </c>
       <c r="CC21" t="inlineStr">
         <is>
-          <t>39.2</t>
+          <t>39.15</t>
         </is>
       </c>
       <c r="CD21" t="inlineStr">
         <is>
-          <t>39.6</t>
+          <t>39.15</t>
         </is>
       </c>
       <c r="CE21" t="inlineStr">
         <is>
-          <t>39.05</t>
+          <t>38.35</t>
         </is>
       </c>
       <c r="CF21" t="inlineStr">
         <is>
-          <t>39.05</t>
+          <t>38.75</t>
         </is>
       </c>
       <c r="CG21" t="inlineStr">
@@ -9498,12 +9498,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>-1.13</t>
+          <t>-0.51</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>519.475</t>
+          <t>340.21</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -9513,7 +9513,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>39.25</t>
+          <t>39.05</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -9523,17 +9523,17 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>-4.81</t>
+          <t>-5.68</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>-1.11</t>
+          <t>-1.02</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>3.53</t>
+          <t>2.77</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -9598,7 +9598,7 @@
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>-9.04</t>
+          <t>-9.50</t>
         </is>
       </c>
       <c r="X22" t="inlineStr">
@@ -9608,17 +9608,17 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-11-03</t>
+          <t>2025-11-04</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>5.54</t>
+          <t>3.63</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>-1.15</t>
+          <t>-1.41</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
@@ -9634,7 +9634,7 @@
       </c>
       <c r="AE22" t="inlineStr">
         <is>
-          <t>1409</t>
+          <t>1065</t>
         </is>
       </c>
       <c r="AF22" t="inlineStr">
@@ -9649,57 +9649,57 @@
       </c>
       <c r="AH22" t="inlineStr">
         <is>
-          <t>-1.31</t>
+          <t>-1.21</t>
         </is>
       </c>
       <c r="AI22" t="inlineStr">
         <is>
-          <t>-1.66</t>
+          <t>-1.92</t>
         </is>
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>-3.77</t>
+          <t>-3.88</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
         <is>
-          <t>0.79</t>
+          <t>0.53</t>
         </is>
       </c>
       <c r="AL22" t="inlineStr">
         <is>
-          <t>39.77</t>
+          <t>39.53</t>
         </is>
       </c>
       <c r="AM22" t="inlineStr">
         <is>
-          <t>40.44</t>
+          <t>40.3</t>
         </is>
       </c>
       <c r="AN22" t="inlineStr">
         <is>
-          <t>42.03</t>
+          <t>41.93</t>
         </is>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>41.7</t>
+          <t>41.71</t>
         </is>
       </c>
       <c r="AP22" t="inlineStr">
         <is>
-          <t>-10.59</t>
+          <t>-14.13</t>
         </is>
       </c>
       <c r="AQ22" t="inlineStr">
         <is>
-          <t>-0.61</t>
+          <t>-0.66</t>
         </is>
       </c>
       <c r="AR22" t="inlineStr">
         <is>
-          <t>-0.55</t>
+          <t>-0.57</t>
         </is>
       </c>
       <c r="AS22" t="inlineStr">
@@ -9709,7 +9709,7 @@
       </c>
       <c r="AT22" t="inlineStr">
         <is>
-          <t>-120.63</t>
+          <t>-121.38</t>
         </is>
       </c>
       <c r="AU22" t="inlineStr">
@@ -9719,41 +9719,41 @@
       </c>
       <c r="AV22" t="inlineStr">
         <is>
-          <t>151111618.248191</t>
+          <t>150978598.7687861</t>
         </is>
       </c>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>20453719.0</t>
+          <t>13358411.0</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>22489497.2</t>
+          <t>21476259.0</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr">
         <is>
-          <t>21722221.3</t>
+          <t>20896470.1</t>
         </is>
       </c>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>28384455.58</t>
+          <t>28018183.18</t>
         </is>
       </c>
       <c r="BA22" t="inlineStr">
         <is>
-          <t>767275</t>
+          <t>579788</t>
         </is>
       </c>
       <c r="BB22" t="inlineStr">
         <is>
-          <t>-1092637.296673307</t>
+          <t>-1316726.695178018</t>
         </is>
       </c>
       <c r="BC22" t="n">
-        <v>-2067197.58</v>
+        <v>-2549218.39</v>
       </c>
       <c r="BD22" t="inlineStr">
         <is>
@@ -9772,7 +9772,7 @@
       </c>
       <c r="BG22" t="inlineStr">
         <is>
-          <t>-5.42</t>
+          <t>-5.90</t>
         </is>
       </c>
       <c r="BH22" t="inlineStr">
@@ -9802,17 +9802,17 @@
       </c>
       <c r="BM22" t="inlineStr">
         <is>
-          <t>-4.834008229657466</t>
+          <t>-13.67996844119094</t>
         </is>
       </c>
       <c r="BN22" t="inlineStr">
         <is>
-          <t>-0.138178351458681</t>
+          <t>-10.11024290164889</t>
         </is>
       </c>
       <c r="BO22" t="inlineStr">
         <is>
-          <t>28.83362772156236</t>
+          <t>24.12947661306339</t>
         </is>
       </c>
       <c r="BP22" t="inlineStr">
@@ -9827,12 +9827,12 @@
       </c>
       <c r="BR22" t="inlineStr">
         <is>
-          <t>1.08</t>
+          <t>1.07</t>
         </is>
       </c>
       <c r="BS22" t="inlineStr">
         <is>
-          <t>6.68</t>
+          <t>6.77</t>
         </is>
       </c>
       <c r="BT22" t="inlineStr">
@@ -9842,7 +9842,7 @@
       </c>
       <c r="BU22" t="inlineStr">
         <is>
-          <t>15.48</t>
+          <t>15.27</t>
         </is>
       </c>
       <c r="BV22" t="inlineStr">
@@ -9857,12 +9857,12 @@
       </c>
       <c r="BX22" t="inlineStr">
         <is>
-          <t>29.59</t>
+          <t>28.92</t>
         </is>
       </c>
       <c r="BY22" t="inlineStr">
         <is>
-          <t>12027</t>
+          <t>11866</t>
         </is>
       </c>
       <c r="BZ22" t="inlineStr">
@@ -9882,22 +9882,22 @@
       </c>
       <c r="CC22" t="inlineStr">
         <is>
-          <t>39.7</t>
+          <t>39.2</t>
         </is>
       </c>
       <c r="CD22" t="inlineStr">
         <is>
-          <t>39.7</t>
+          <t>39.6</t>
         </is>
       </c>
       <c r="CE22" t="inlineStr">
         <is>
-          <t>39.25</t>
+          <t>39.05</t>
         </is>
       </c>
       <c r="CF22" t="inlineStr">
         <is>
-          <t>39.25</t>
+          <t>39.05</t>
         </is>
       </c>
       <c r="CG22" t="inlineStr">
@@ -9929,12 +9929,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>-0.12</t>
+          <t>-1.13</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>409.169</t>
+          <t>519.475</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -9944,7 +9944,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>39.7</t>
+          <t>39.25</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -9954,17 +9954,17 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>-6.01</t>
+          <t>-6.22</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>-1.11</t>
+          <t>-1.02</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>5.80</t>
+          <t>3.53</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -10029,7 +10029,7 @@
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>-8.00</t>
+          <t>-9.04</t>
         </is>
       </c>
       <c r="X23" t="inlineStr">
@@ -10039,17 +10039,17 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-10-31</t>
+          <t>2025-11-03</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>4.36</t>
+          <t>5.54</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>-1.01</t>
+          <t>-1.15</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
@@ -10065,7 +10065,7 @@
       </c>
       <c r="AE23" t="inlineStr">
         <is>
-          <t>1409</t>
+          <t>1065</t>
         </is>
       </c>
       <c r="AF23" t="inlineStr">
@@ -10080,57 +10080,57 @@
       </c>
       <c r="AH23" t="inlineStr">
         <is>
-          <t>-0.85</t>
+          <t>-1.31</t>
         </is>
       </c>
       <c r="AI23" t="inlineStr">
         <is>
-          <t>-1.32</t>
+          <t>-1.66</t>
         </is>
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>-3.7</t>
+          <t>-3.77</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
         <is>
-          <t>1.07</t>
+          <t>0.79</t>
         </is>
       </c>
       <c r="AL23" t="inlineStr">
         <is>
-          <t>40.04</t>
+          <t>39.77</t>
         </is>
       </c>
       <c r="AM23" t="inlineStr">
         <is>
-          <t>40.58</t>
+          <t>40.44</t>
         </is>
       </c>
       <c r="AN23" t="inlineStr">
         <is>
-          <t>42.13</t>
+          <t>42.03</t>
         </is>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>41.68</t>
+          <t>41.7</t>
         </is>
       </c>
       <c r="AP23" t="inlineStr">
         <is>
-          <t>-5.61</t>
+          <t>-10.59</t>
         </is>
       </c>
       <c r="AQ23" t="inlineStr">
         <is>
-          <t>-0.57</t>
+          <t>-0.61</t>
         </is>
       </c>
       <c r="AR23" t="inlineStr">
         <is>
-          <t>-0.54</t>
+          <t>-0.55</t>
         </is>
       </c>
       <c r="AS23" t="inlineStr">
@@ -10140,7 +10140,7 @@
       </c>
       <c r="AT23" t="inlineStr">
         <is>
-          <t>-120.08</t>
+          <t>-120.63</t>
         </is>
       </c>
       <c r="AU23" t="inlineStr">
@@ -10150,41 +10150,41 @@
       </c>
       <c r="AV23" t="inlineStr">
         <is>
-          <t>151111618.248191</t>
+          <t>150978598.7687861</t>
         </is>
       </c>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>16302654.0</t>
+          <t>20453719.0</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>22715830.4</t>
+          <t>22489497.2</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr">
         <is>
-          <t>21471350.7</t>
+          <t>21722221.3</t>
         </is>
       </c>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>28713792.94</t>
+          <t>28384455.58</t>
         </is>
       </c>
       <c r="BA23" t="inlineStr">
         <is>
-          <t>1244479</t>
+          <t>767275</t>
         </is>
       </c>
       <c r="BB23" t="inlineStr">
         <is>
-          <t>-915444.5174871245</t>
+          <t>-1092637.296673307</t>
         </is>
       </c>
       <c r="BC23" t="n">
-        <v>-2064979.52</v>
+        <v>-2067197.58</v>
       </c>
       <c r="BD23" t="inlineStr">
         <is>
@@ -10203,7 +10203,7 @@
       </c>
       <c r="BG23" t="inlineStr">
         <is>
-          <t>-4.34</t>
+          <t>-5.42</t>
         </is>
       </c>
       <c r="BH23" t="inlineStr">
@@ -10233,17 +10233,17 @@
       </c>
       <c r="BM23" t="inlineStr">
         <is>
-          <t>-4.834008229657466</t>
+          <t>-13.67996844119094</t>
         </is>
       </c>
       <c r="BN23" t="inlineStr">
         <is>
-          <t>-0.138178351458681</t>
+          <t>-10.11024290164889</t>
         </is>
       </c>
       <c r="BO23" t="inlineStr">
         <is>
-          <t>28.83362772156236</t>
+          <t>24.12947661306339</t>
         </is>
       </c>
       <c r="BP23" t="inlineStr">
@@ -10258,12 +10258,12 @@
       </c>
       <c r="BR23" t="inlineStr">
         <is>
-          <t>1.09</t>
+          <t>1.08</t>
         </is>
       </c>
       <c r="BS23" t="inlineStr">
         <is>
-          <t>6.68</t>
+          <t>6.77</t>
         </is>
       </c>
       <c r="BT23" t="inlineStr">
@@ -10273,7 +10273,7 @@
       </c>
       <c r="BU23" t="inlineStr">
         <is>
-          <t>15.48</t>
+          <t>15.27</t>
         </is>
       </c>
       <c r="BV23" t="inlineStr">
@@ -10288,12 +10288,12 @@
       </c>
       <c r="BX23" t="inlineStr">
         <is>
-          <t>29.59</t>
+          <t>28.92</t>
         </is>
       </c>
       <c r="BY23" t="inlineStr">
         <is>
-          <t>12027</t>
+          <t>11866</t>
         </is>
       </c>
       <c r="BZ23" t="inlineStr">
@@ -10313,22 +10313,22 @@
       </c>
       <c r="CC23" t="inlineStr">
         <is>
-          <t>40.1</t>
+          <t>39.7</t>
         </is>
       </c>
       <c r="CD23" t="inlineStr">
         <is>
-          <t>40.1</t>
+          <t>39.7</t>
         </is>
       </c>
       <c r="CE23" t="inlineStr">
         <is>
-          <t>39.7</t>
+          <t>39.25</t>
         </is>
       </c>
       <c r="CF23" t="inlineStr">
         <is>
-          <t>39.7</t>
+          <t>39.25</t>
         </is>
       </c>
       <c r="CG23" t="inlineStr">

--- a/Result/checksun_type/塔架.xlsx
+++ b/Result/checksun_type/塔架.xlsx
@@ -878,12 +878,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>-2.96</t>
+          <t>-2.26</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>4003.393</t>
+          <t>2844.986</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -893,7 +893,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>133.5</t>
+          <t>130.5</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -908,12 +908,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-1.8</t>
+          <t>-2.63</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>36.89</t>
+          <t>48.25</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -978,7 +978,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-43.67</t>
+          <t>-44.94</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -988,17 +988,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>16.56</t>
+          <t>11.77</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>-5.24</t>
+          <t>-2.29</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1009,12 +1009,12 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>33</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>4003</t>
+          <t>2845</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
@@ -1029,57 +1029,57 @@
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>-7.23</t>
+          <t>-6.85</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>-5.73</t>
+          <t>-7.30</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>-6.6</t>
+          <t>-7.05</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>-5.82</t>
+          <t>-5.89</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>143.9</t>
+          <t>140.1</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>152.65</t>
+          <t>151.12</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>163.44</t>
+          <t>162.59</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>173.54</t>
+          <t>172.77</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>-22.90</t>
+          <t>-28.43</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>-6.89</t>
+          <t>-7.75</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>-5.61</t>
+          <t>-6.04</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -1089,7 +1089,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-122.53</t>
+          <t>-124.26</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1099,41 +1099,41 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>1702786797.786849</t>
+          <t>1701137811.822511</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>543328425.0</t>
+          <t>373359683.0</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>317370279.0</t>
+          <t>374444824.4</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>231842549.9</t>
+          <t>252575891.8</t>
         </is>
       </c>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>254515985.98</t>
+          <t>255257682.72</t>
         </is>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>85527729</t>
+          <t>121868932</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>-3818988.443072045</t>
+          <t>3068692.09532273</t>
         </is>
       </c>
       <c r="BC2" t="n">
-        <v>42066417.86</v>
+        <v>40950935.06</v>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
@@ -1152,7 +1152,7 @@
       </c>
       <c r="BG2" t="inlineStr">
         <is>
-          <t>-25.83</t>
+          <t>-27.50</t>
         </is>
       </c>
       <c r="BH2" t="inlineStr">
@@ -1177,7 +1177,7 @@
       </c>
       <c r="BL2" t="inlineStr">
         <is>
-          <t>0.99</t>
+          <t>0.98</t>
         </is>
       </c>
       <c r="BM2" t="inlineStr">
@@ -1197,7 +1197,7 @@
       </c>
       <c r="BP2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;衝高回落,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BQ2" t="inlineStr">
@@ -1207,12 +1207,12 @@
       </c>
       <c r="BR2" t="inlineStr">
         <is>
-          <t>3.08</t>
+          <t>3.01</t>
         </is>
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>3.12</t>
+          <t>3.19</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
@@ -1222,7 +1222,7 @@
       </c>
       <c r="BU2" t="inlineStr">
         <is>
-          <t>25.09</t>
+          <t>24.53</t>
         </is>
       </c>
       <c r="BV2" t="inlineStr">
@@ -1237,12 +1237,12 @@
       </c>
       <c r="BX2" t="inlineStr">
         <is>
-          <t>28.92</t>
+          <t>28.65</t>
         </is>
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>32961</t>
+          <t>32220</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
@@ -1262,22 +1262,22 @@
       </c>
       <c r="CC2" t="inlineStr">
         <is>
-          <t>135.0</t>
+          <t>133.0</t>
         </is>
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>141.5</t>
+          <t>134.5</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>132.5</t>
+          <t>129.5</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>133.5</t>
+          <t>130.5</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
@@ -1309,12 +1309,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>-8.16</t>
+          <t>-2.96</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>5388.546</t>
+          <t>4003.393</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1324,7 +1324,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>137.5</t>
+          <t>133.5</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1334,17 +1334,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-3.0</t>
+          <t>-2.3</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-1.8</t>
+          <t>-2.63</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>18.56</t>
+          <t>36.89</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1409,7 +1409,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-41.98</t>
+          <t>-43.67</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1419,17 +1419,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>22.28</t>
+          <t>16.56</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>-5.06</t>
+          <t>-5.24</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1440,12 +1440,12 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>33</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>4003</t>
+          <t>2845</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
@@ -1460,57 +1460,57 @@
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>-6.59</t>
+          <t>-7.23</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>-4.57</t>
+          <t>-5.73</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-6.11</t>
+          <t>-6.6</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>-5.70</t>
+          <t>-5.82</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>147.2</t>
+          <t>143.9</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>154.25</t>
+          <t>152.65</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>164.29</t>
+          <t>163.44</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>174.21</t>
+          <t>173.54</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>-13.45</t>
+          <t>-22.90</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>-6.00</t>
+          <t>-6.89</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>-5.29</t>
+          <t>-5.61</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1520,7 +1520,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-121.24</t>
+          <t>-122.53</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1530,41 +1530,41 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>1702786797.786849</t>
+          <t>1701137811.822511</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>753939618.0</t>
+          <t>543328425.0</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>239835367.0</t>
+          <t>317370279.0</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>202283159.5</t>
+          <t>231842549.9</t>
         </is>
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>250790390.86</t>
+          <t>254515985.98</t>
         </is>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>37552207</t>
+          <t>85527729</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>-12161789.58854426</t>
+          <t>-3818988.443072045</t>
         </is>
       </c>
       <c r="BC3" t="n">
-        <v>23946656.01</v>
+        <v>42066417.86</v>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
@@ -1583,7 +1583,7 @@
       </c>
       <c r="BG3" t="inlineStr">
         <is>
-          <t>-23.61</t>
+          <t>-25.83</t>
         </is>
       </c>
       <c r="BH3" t="inlineStr">
@@ -1608,7 +1608,7 @@
       </c>
       <c r="BL3" t="inlineStr">
         <is>
-          <t>0.99</t>
+          <t>0.98</t>
         </is>
       </c>
       <c r="BM3" t="inlineStr">
@@ -1628,22 +1628,22 @@
       </c>
       <c r="BP3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;衝高回落,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>價跌量增</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
         <is>
-          <t>3.17</t>
+          <t>3.08</t>
         </is>
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>3.12</t>
+          <t>3.19</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
@@ -1653,7 +1653,7 @@
       </c>
       <c r="BU3" t="inlineStr">
         <is>
-          <t>25.09</t>
+          <t>24.53</t>
         </is>
       </c>
       <c r="BV3" t="inlineStr">
@@ -1668,12 +1668,12 @@
       </c>
       <c r="BX3" t="inlineStr">
         <is>
-          <t>28.92</t>
+          <t>28.65</t>
         </is>
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>32961</t>
+          <t>32220</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
@@ -1693,22 +1693,22 @@
       </c>
       <c r="CC3" t="inlineStr">
         <is>
-          <t>147.0</t>
+          <t>135.0</t>
         </is>
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>147.0</t>
+          <t>141.5</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>135.0</t>
+          <t>132.5</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>137.5</t>
+          <t>133.5</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
@@ -1740,12 +1740,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-8.16</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>617.888</t>
+          <t>5388.546</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1755,7 +1755,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>149.5</t>
+          <t>137.5</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1765,17 +1765,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-11.99</t>
+          <t>-5.36</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-1.8</t>
+          <t>-2.63</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>-14.19</t>
+          <t>18.56</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1840,7 +1840,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-36.92</t>
+          <t>-41.98</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1850,17 +1850,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>2.56</t>
+          <t>22.28</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>-1.34</t>
+          <t>-5.06</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1871,12 +1871,12 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>33</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>4003</t>
+          <t>2845</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
@@ -1891,57 +1891,57 @@
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>-0.07</t>
+          <t>-6.59</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>-3.96</t>
+          <t>-4.57</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>-5.65</t>
+          <t>-6.11</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>-5.63</t>
+          <t>-5.70</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>149.6</t>
+          <t>147.2</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>155.78</t>
+          <t>154.25</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>165.1</t>
+          <t>164.29</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>174.95</t>
+          <t>174.21</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>-1.33</t>
+          <t>-13.45</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>-5.18</t>
+          <t>-6.00</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>-5.11</t>
+          <t>-5.29</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1951,7 +1951,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-120.53</t>
+          <t>-121.24</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1961,41 +1961,41 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>1702786797.786849</t>
+          <t>1701137811.822511</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>92809478.0</t>
+          <t>753939618.0</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>127850905.8</t>
+          <t>239835367.0</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>148995940.1</t>
+          <t>202283159.5</t>
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>248204610.78</t>
+          <t>250790390.86</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>-21145034</t>
+          <t>37552207</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>-18726961.5147791</t>
+          <t>-12161789.58854426</t>
         </is>
       </c>
       <c r="BC4" t="n">
-        <v>-25359440.75</v>
+        <v>23946656.01</v>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
@@ -2014,7 +2014,7 @@
       </c>
       <c r="BG4" t="inlineStr">
         <is>
-          <t>-16.94</t>
+          <t>-23.61</t>
         </is>
       </c>
       <c r="BH4" t="inlineStr">
@@ -2039,7 +2039,7 @@
       </c>
       <c r="BL4" t="inlineStr">
         <is>
-          <t>0.99</t>
+          <t>0.98</t>
         </is>
       </c>
       <c r="BM4" t="inlineStr">
@@ -2064,17 +2064,17 @@
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價跌量增</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
         <is>
-          <t>3.44</t>
+          <t>3.17</t>
         </is>
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>3.12</t>
+          <t>3.19</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
@@ -2084,7 +2084,7 @@
       </c>
       <c r="BU4" t="inlineStr">
         <is>
-          <t>25.09</t>
+          <t>24.53</t>
         </is>
       </c>
       <c r="BV4" t="inlineStr">
@@ -2099,12 +2099,12 @@
       </c>
       <c r="BX4" t="inlineStr">
         <is>
-          <t>28.92</t>
+          <t>28.65</t>
         </is>
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>32961</t>
+          <t>32220</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
@@ -2124,22 +2124,22 @@
       </c>
       <c r="CC4" t="inlineStr">
         <is>
-          <t>150.0</t>
+          <t>147.0</t>
         </is>
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>151.5</t>
+          <t>147.0</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>149.5</t>
+          <t>135.0</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>149.5</t>
+          <t>137.5</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>723.545</t>
+          <t>617.888</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2196,17 +2196,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-11.99</t>
+          <t>-14.56</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-1.8</t>
+          <t>-2.63</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>-23.11</t>
+          <t>-14.19</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2281,17 +2281,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>2.99</t>
+          <t>2.56</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>-1.67</t>
+          <t>-1.34</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2302,12 +2302,12 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>33</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>4003</t>
+          <t>2845</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
@@ -2317,62 +2317,62 @@
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>2.22</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>-0.47</t>
+          <t>-0.07</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>-4.07</t>
+          <t>-3.96</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>-5.55</t>
+          <t>-5.65</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>-5.58</t>
+          <t>-5.63</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>150.2</t>
+          <t>149.6</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>156.57</t>
+          <t>155.78</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>165.78</t>
+          <t>165.1</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>175.58</t>
+          <t>174.95</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>-3.60</t>
+          <t>-1.33</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>-5.28</t>
+          <t>-5.18</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>-5.09</t>
+          <t>-5.11</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-120.46</t>
+          <t>-120.53</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2392,41 +2392,41 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>1702786797.786849</t>
+          <t>1701137811.822511</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>108786918.0</t>
+          <t>92809478.0</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>129166834.4</t>
+          <t>127850905.8</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>167987433.4</t>
+          <t>148995940.1</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>261232164.76</t>
+          <t>248204610.78</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>-38820599</t>
+          <t>-21145034</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>-17521056.19996015</t>
+          <t>-18726961.5147791</t>
         </is>
       </c>
       <c r="BC5" t="n">
-        <v>-24055655.37</v>
+        <v>-25359440.75</v>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
@@ -2470,7 +2470,7 @@
       </c>
       <c r="BL5" t="inlineStr">
         <is>
-          <t>0.99</t>
+          <t>0.98</t>
         </is>
       </c>
       <c r="BM5" t="inlineStr">
@@ -2490,7 +2490,7 @@
       </c>
       <c r="BP5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ5" t="inlineStr">
@@ -2505,7 +2505,7 @@
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>3.12</t>
+          <t>3.19</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
@@ -2515,7 +2515,7 @@
       </c>
       <c r="BU5" t="inlineStr">
         <is>
-          <t>25.09</t>
+          <t>24.53</t>
         </is>
       </c>
       <c r="BV5" t="inlineStr">
@@ -2530,12 +2530,12 @@
       </c>
       <c r="BX5" t="inlineStr">
         <is>
-          <t>28.92</t>
+          <t>28.65</t>
         </is>
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>32961</t>
+          <t>32220</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
@@ -2555,17 +2555,17 @@
       </c>
       <c r="CC5" t="inlineStr">
         <is>
+          <t>150.0</t>
+        </is>
+      </c>
+      <c r="CD5" t="inlineStr">
+        <is>
           <t>151.5</t>
         </is>
       </c>
-      <c r="CD5" t="inlineStr">
-        <is>
-          <t>152.5</t>
-        </is>
-      </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>149.0</t>
+          <t>149.5</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
@@ -2602,12 +2602,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>-0.33</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>586.018</t>
+          <t>723.545</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2627,17 +2627,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-11.99</t>
+          <t>-14.56</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-1.8</t>
+          <t>-2.63</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>-28.30</t>
+          <t>-23.11</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2712,17 +2712,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>2.42</t>
+          <t>2.99</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>-1.34</t>
+          <t>-1.67</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2733,12 +2733,12 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>33</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>4003</t>
+          <t>2845</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
@@ -2753,57 +2753,57 @@
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>-0.86</t>
+          <t>-0.47</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>-4.25</t>
+          <t>-4.07</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>-5.43</t>
+          <t>-5.55</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>-5.49</t>
+          <t>-5.58</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>150.8</t>
+          <t>150.2</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>157.5</t>
+          <t>156.57</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>166.55</t>
+          <t>165.78</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>176.23</t>
+          <t>175.58</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>-5.51</t>
+          <t>-3.60</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>-5.32</t>
+          <t>-5.28</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>-5.05</t>
+          <t>-5.09</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -2813,7 +2813,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-120.28</t>
+          <t>-120.46</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2823,41 +2823,41 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>1702786797.786849</t>
+          <t>1701137811.822511</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>87986956.0</t>
+          <t>108786918.0</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>130706959.2</t>
+          <t>129166834.4</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>182292868.5</t>
+          <t>167987433.4</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>265109106.98</t>
+          <t>261232164.76</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>-51585909</t>
+          <t>-38820599</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>-16332947.26079137</t>
+          <t>-17521056.19996015</t>
         </is>
       </c>
       <c r="BC6" t="n">
-        <v>-23045842.84</v>
+        <v>-24055655.37</v>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
@@ -2901,7 +2901,7 @@
       </c>
       <c r="BL6" t="inlineStr">
         <is>
-          <t>0.99</t>
+          <t>0.98</t>
         </is>
       </c>
       <c r="BM6" t="inlineStr">
@@ -2921,7 +2921,7 @@
       </c>
       <c r="BP6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ6" t="inlineStr">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>3.12</t>
+          <t>3.19</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="BU6" t="inlineStr">
         <is>
-          <t>25.09</t>
+          <t>24.53</t>
         </is>
       </c>
       <c r="BV6" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="BX6" t="inlineStr">
         <is>
-          <t>28.92</t>
+          <t>28.65</t>
         </is>
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>32961</t>
+          <t>32220</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
@@ -2991,12 +2991,12 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>151.5</t>
+          <t>152.5</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>149.5</t>
+          <t>149.0</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
@@ -3033,12 +3033,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>0.33</t>
+          <t>-0.33</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1040.36</t>
+          <t>586.018</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3048,7 +3048,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>150.0</t>
+          <t>149.5</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3058,17 +3058,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-12.36</t>
+          <t>-14.56</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-1.8</t>
+          <t>-2.63</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>-24.53</t>
+          <t>-28.30</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3133,7 +3133,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-36.71</t>
+          <t>-36.92</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3143,17 +3143,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>4.30</t>
+          <t>2.42</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>1.39</t>
+          <t>-1.34</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3164,17 +3164,17 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>33</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>4003</t>
+          <t>2845</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>6.67</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
@@ -3184,57 +3184,57 @@
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>-1.12</t>
+          <t>-0.86</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>-4.31</t>
+          <t>-4.25</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>-5.31</t>
+          <t>-5.43</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>-5.34</t>
+          <t>-5.49</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>151.7</t>
+          <t>150.8</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>158.52</t>
+          <t>157.5</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>167.41</t>
+          <t>166.55</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>176.86</t>
+          <t>176.23</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>-6.68</t>
+          <t>-5.51</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>-5.31</t>
+          <t>-5.32</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>-4.98</t>
+          <t>-5.05</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -3244,7 +3244,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-120.00</t>
+          <t>-120.28</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3254,41 +3254,41 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>1702786797.786849</t>
+          <t>1701137811.822511</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>155653865.0</t>
+          <t>87986956.0</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>146314820.8</t>
+          <t>130706959.2</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>193869307.6</t>
+          <t>182292868.5</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>274342437.92</t>
+          <t>265109106.98</t>
         </is>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>-47554486</t>
+          <t>-51585909</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>-15112420.79113203</t>
+          <t>-16332947.26079137</t>
         </is>
       </c>
       <c r="BC7" t="n">
-        <v>-18551620.35</v>
+        <v>-23045842.84</v>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
@@ -3307,7 +3307,7 @@
       </c>
       <c r="BG7" t="inlineStr">
         <is>
-          <t>-16.67</t>
+          <t>-16.94</t>
         </is>
       </c>
       <c r="BH7" t="inlineStr">
@@ -3332,7 +3332,7 @@
       </c>
       <c r="BL7" t="inlineStr">
         <is>
-          <t>0.99</t>
+          <t>0.98</t>
         </is>
       </c>
       <c r="BM7" t="inlineStr">
@@ -3352,7 +3352,7 @@
       </c>
       <c r="BP7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;可能出現反轉訊號&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;3&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ7" t="inlineStr">
@@ -3362,12 +3362,12 @@
       </c>
       <c r="BR7" t="inlineStr">
         <is>
-          <t>3.46</t>
+          <t>3.44</t>
         </is>
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>3.12</t>
+          <t>3.19</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
@@ -3377,7 +3377,7 @@
       </c>
       <c r="BU7" t="inlineStr">
         <is>
-          <t>25.09</t>
+          <t>24.53</t>
         </is>
       </c>
       <c r="BV7" t="inlineStr">
@@ -3392,12 +3392,12 @@
       </c>
       <c r="BX7" t="inlineStr">
         <is>
-          <t>28.92</t>
+          <t>28.65</t>
         </is>
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>32961</t>
+          <t>32220</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
@@ -3417,7 +3417,7 @@
       </c>
       <c r="CC7" t="inlineStr">
         <is>
-          <t>150.5</t>
+          <t>151.5</t>
         </is>
       </c>
       <c r="CD7" t="inlineStr">
@@ -3427,12 +3427,12 @@
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>146.5</t>
+          <t>149.5</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>150.0</t>
+          <t>149.5</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
@@ -3464,12 +3464,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>-1.97</t>
+          <t>0.33</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>1294.619</t>
+          <t>1040.36</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3479,7 +3479,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>149.5</t>
+          <t>150.0</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3489,17 +3489,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-11.99</t>
+          <t>-14.94</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-1.8</t>
+          <t>-2.63</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>-16.90</t>
+          <t>-24.53</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3564,7 +3564,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-36.92</t>
+          <t>-36.71</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3574,17 +3574,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>5.35</t>
+          <t>4.30</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>-1.00</t>
+          <t>1.39</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3595,77 +3595,77 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>33</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>4003</t>
+          <t>2845</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>6.67</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>2.22</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>-2.35</t>
+          <t>-1.12</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>-3.97</t>
+          <t>-4.31</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>-5.19</t>
+          <t>-5.31</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>-5.28</t>
+          <t>-5.34</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>153.1</t>
+          <t>151.7</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>159.43</t>
+          <t>158.52</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>168.15</t>
+          <t>167.41</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>177.52</t>
+          <t>176.86</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>-7.56</t>
+          <t>-6.68</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>-5.26</t>
+          <t>-5.31</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>-4.89</t>
+          <t>-4.98</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -3675,7 +3675,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-119.66</t>
+          <t>-120.00</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3685,41 +3685,41 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>1702786797.786849</t>
+          <t>1701137811.822511</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>194017312.0</t>
+          <t>155653865.0</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>164730952.0</t>
+          <t>146314820.8</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>198237890.5</t>
+          <t>193869307.6</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>287305576.32</t>
+          <t>274342437.92</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>-33506938</t>
+          <t>-47554486</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>-14487111.77960444</t>
+          <t>-15112420.79113203</t>
         </is>
       </c>
       <c r="BC8" t="n">
-        <v>-18718770.61</v>
+        <v>-18551620.35</v>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
@@ -3738,7 +3738,7 @@
       </c>
       <c r="BG8" t="inlineStr">
         <is>
-          <t>-16.94</t>
+          <t>-16.67</t>
         </is>
       </c>
       <c r="BH8" t="inlineStr">
@@ -3763,7 +3763,7 @@
       </c>
       <c r="BL8" t="inlineStr">
         <is>
-          <t>0.99</t>
+          <t>0.98</t>
         </is>
       </c>
       <c r="BM8" t="inlineStr">
@@ -3783,7 +3783,7 @@
       </c>
       <c r="BP8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;可能出現反轉訊號&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;3&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ8" t="inlineStr">
@@ -3793,12 +3793,12 @@
       </c>
       <c r="BR8" t="inlineStr">
         <is>
-          <t>3.44</t>
+          <t>3.46</t>
         </is>
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>3.12</t>
+          <t>3.19</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
@@ -3808,7 +3808,7 @@
       </c>
       <c r="BU8" t="inlineStr">
         <is>
-          <t>25.09</t>
+          <t>24.53</t>
         </is>
       </c>
       <c r="BV8" t="inlineStr">
@@ -3823,12 +3823,12 @@
       </c>
       <c r="BX8" t="inlineStr">
         <is>
-          <t>28.92</t>
+          <t>28.65</t>
         </is>
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>32961</t>
+          <t>32220</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
@@ -3848,22 +3848,22 @@
       </c>
       <c r="CC8" t="inlineStr">
         <is>
-          <t>152.0</t>
+          <t>150.5</t>
         </is>
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>152.0</t>
+          <t>151.5</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>148.5</t>
+          <t>146.5</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>149.5</t>
+          <t>150.0</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
@@ -3895,12 +3895,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-1.97</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>653.151</t>
+          <t>1294.619</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3910,7 +3910,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>152.5</t>
+          <t>149.5</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3920,17 +3920,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-14.23</t>
+          <t>-14.56</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-1.8</t>
+          <t>-2.63</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>-18.28</t>
+          <t>-16.90</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3995,7 +3995,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-35.65</t>
+          <t>-36.92</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4005,17 +4005,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-06</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>2.70</t>
+          <t>5.35</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>-0.32</t>
+          <t>-1.00</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4026,12 +4026,12 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>33</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>4003</t>
+          <t>2845</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
@@ -4041,62 +4041,62 @@
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>2.38</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>-0.91</t>
+          <t>-2.35</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>-4.07</t>
+          <t>-3.97</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>-5.07</t>
+          <t>-5.19</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>-5.19</t>
+          <t>-5.28</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>153.9</t>
+          <t>153.1</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>160.43</t>
+          <t>159.43</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>169.0</t>
+          <t>168.15</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>178.25</t>
+          <t>177.52</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>-5.77</t>
+          <t>-7.56</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>-5.08</t>
+          <t>-5.26</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>-4.80</t>
+          <t>-4.89</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -4106,7 +4106,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-119.29</t>
+          <t>-119.66</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4116,41 +4116,41 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>1702786797.786849</t>
+          <t>1701137811.822511</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>99389121.0</t>
+          <t>194017312.0</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>170140974.4</t>
+          <t>164730952.0</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>208211819.2</t>
+          <t>198237890.5</t>
         </is>
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>301691507.7</t>
+          <t>287305576.32</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>-38070844</t>
+          <t>-33506938</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>-13717719.26552568</t>
+          <t>-14487111.77960444</t>
         </is>
       </c>
       <c r="BC9" t="n">
-        <v>-22399398.48</v>
+        <v>-18718770.61</v>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
@@ -4169,7 +4169,7 @@
       </c>
       <c r="BG9" t="inlineStr">
         <is>
-          <t>-15.28</t>
+          <t>-16.94</t>
         </is>
       </c>
       <c r="BH9" t="inlineStr">
@@ -4194,7 +4194,7 @@
       </c>
       <c r="BL9" t="inlineStr">
         <is>
-          <t>0.99</t>
+          <t>0.98</t>
         </is>
       </c>
       <c r="BM9" t="inlineStr">
@@ -4214,7 +4214,7 @@
       </c>
       <c r="BP9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ9" t="inlineStr">
@@ -4224,12 +4224,12 @@
       </c>
       <c r="BR9" t="inlineStr">
         <is>
-          <t>3.51</t>
+          <t>3.44</t>
         </is>
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>3.12</t>
+          <t>3.19</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
@@ -4239,7 +4239,7 @@
       </c>
       <c r="BU9" t="inlineStr">
         <is>
-          <t>25.09</t>
+          <t>24.53</t>
         </is>
       </c>
       <c r="BV9" t="inlineStr">
@@ -4254,12 +4254,12 @@
       </c>
       <c r="BX9" t="inlineStr">
         <is>
-          <t>28.92</t>
+          <t>28.65</t>
         </is>
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>32961</t>
+          <t>32220</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
@@ -4279,22 +4279,22 @@
       </c>
       <c r="CC9" t="inlineStr">
         <is>
-          <t>154.0</t>
+          <t>152.0</t>
         </is>
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>154.5</t>
+          <t>152.0</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>151.0</t>
+          <t>148.5</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>152.5</t>
+          <t>149.5</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
@@ -4326,12 +4326,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>-0.98</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>767.34</t>
+          <t>653.151</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4351,17 +4351,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-14.23</t>
+          <t>-16.86</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-1.8</t>
+          <t>-2.63</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>-2.01</t>
+          <t>-18.28</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4436,17 +4436,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-05</t>
+          <t>2025-11-06</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>3.17</t>
+          <t>2.70</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>0.35</t>
+          <t>-0.32</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4457,12 +4457,12 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>33</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>4003</t>
+          <t>2845</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
@@ -4472,62 +4472,62 @@
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>17.94</t>
+          <t>2.38</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>-1.17</t>
+          <t>-0.91</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>-4.49</t>
+          <t>-4.07</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>-4.9</t>
+          <t>-5.07</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>-5.05</t>
+          <t>-5.19</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>154.3</t>
+          <t>153.9</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>161.55</t>
+          <t>160.43</t>
         </is>
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>169.88</t>
+          <t>169.0</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>178.91</t>
+          <t>178.25</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>-7.21</t>
+          <t>-5.77</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>-5.07</t>
+          <t>-5.08</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>-4.73</t>
+          <t>-4.80</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -4537,7 +4537,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-119.01</t>
+          <t>-119.29</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4547,41 +4547,41 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>1702786797.786849</t>
+          <t>1701137811.822511</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>116487542.0</t>
+          <t>99389121.0</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>206808032.4</t>
+          <t>170140974.4</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>211045311.6</t>
+          <t>208211819.2</t>
         </is>
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>314221303.24</t>
+          <t>301691507.7</t>
         </is>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>-4237279</t>
+          <t>-38070844</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>-12139232.13529545</t>
+          <t>-13717719.26552568</t>
         </is>
       </c>
       <c r="BC10" t="n">
-        <v>-16718725.04</v>
+        <v>-22399398.48</v>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
@@ -4625,7 +4625,7 @@
       </c>
       <c r="BL10" t="inlineStr">
         <is>
-          <t>0.99</t>
+          <t>0.98</t>
         </is>
       </c>
       <c r="BM10" t="inlineStr">
@@ -4645,7 +4645,7 @@
       </c>
       <c r="BP10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ10" t="inlineStr">
@@ -4660,7 +4660,7 @@
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>3.12</t>
+          <t>3.19</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
@@ -4670,7 +4670,7 @@
       </c>
       <c r="BU10" t="inlineStr">
         <is>
-          <t>25.09</t>
+          <t>24.53</t>
         </is>
       </c>
       <c r="BV10" t="inlineStr">
@@ -4685,12 +4685,12 @@
       </c>
       <c r="BX10" t="inlineStr">
         <is>
-          <t>28.92</t>
+          <t>28.65</t>
         </is>
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>32961</t>
+          <t>32220</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
@@ -4710,17 +4710,17 @@
       </c>
       <c r="CC10" t="inlineStr">
         <is>
-          <t>153.0</t>
+          <t>154.0</t>
         </is>
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>154.0</t>
+          <t>154.5</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>150.5</t>
+          <t>151.0</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
@@ -4757,12 +4757,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>-1.9</t>
+          <t>-0.98</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>1062.556</t>
+          <t>767.34</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4772,7 +4772,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>154.0</t>
+          <t>152.5</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4782,17 +4782,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-15.36</t>
+          <t>-16.86</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-1.8</t>
+          <t>-2.63</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>8.13</t>
+          <t>-2.01</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4857,7 +4857,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-35.02</t>
+          <t>-35.65</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4867,17 +4867,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-04</t>
+          <t>2025-11-05</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>4.39</t>
+          <t>3.17</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>-2.92</t>
+          <t>0.35</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4888,17 +4888,17 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>33</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>4003</t>
+          <t>2845</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>7.14</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
@@ -4908,57 +4908,57 @@
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>-0.58</t>
+          <t>-1.17</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>-4.59</t>
+          <t>-4.49</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>-4.89</t>
+          <t>-4.9</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>-4.93</t>
+          <t>-5.05</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>154.9</t>
+          <t>154.3</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>162.35</t>
+          <t>161.55</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>170.7</t>
+          <t>169.88</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>179.54</t>
+          <t>178.91</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>-7.45</t>
+          <t>-7.21</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>-4.99</t>
+          <t>-5.07</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>-4.65</t>
+          <t>-4.73</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -4968,7 +4968,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-118.67</t>
+          <t>-119.01</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -4978,41 +4978,41 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>1702786797.786849</t>
+          <t>1701137811.822511</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>166026264.0</t>
+          <t>116487542.0</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>233878777.8</t>
+          <t>206808032.4</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>216301717.4</t>
+          <t>211045311.6</t>
         </is>
       </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>327913288.88</t>
+          <t>314221303.24</t>
         </is>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>17577060</t>
+          <t>-4237279</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>-11306597.06250142</t>
+          <t>-12139232.13529545</t>
         </is>
       </c>
       <c r="BC11" t="n">
-        <v>-9838353.609999999</v>
+        <v>-16718725.04</v>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
@@ -5031,7 +5031,7 @@
       </c>
       <c r="BG11" t="inlineStr">
         <is>
-          <t>-14.44</t>
+          <t>-15.28</t>
         </is>
       </c>
       <c r="BH11" t="inlineStr">
@@ -5056,7 +5056,7 @@
       </c>
       <c r="BL11" t="inlineStr">
         <is>
-          <t>0.99</t>
+          <t>0.98</t>
         </is>
       </c>
       <c r="BM11" t="inlineStr">
@@ -5076,7 +5076,7 @@
       </c>
       <c r="BP11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ11" t="inlineStr">
@@ -5086,12 +5086,12 @@
       </c>
       <c r="BR11" t="inlineStr">
         <is>
-          <t>3.55</t>
+          <t>3.51</t>
         </is>
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>3.12</t>
+          <t>3.19</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
@@ -5101,7 +5101,7 @@
       </c>
       <c r="BU11" t="inlineStr">
         <is>
-          <t>25.09</t>
+          <t>24.53</t>
         </is>
       </c>
       <c r="BV11" t="inlineStr">
@@ -5116,12 +5116,12 @@
       </c>
       <c r="BX11" t="inlineStr">
         <is>
-          <t>28.92</t>
+          <t>28.65</t>
         </is>
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>32961</t>
+          <t>32220</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
@@ -5141,22 +5141,22 @@
       </c>
       <c r="CC11" t="inlineStr">
         <is>
-          <t>157.5</t>
+          <t>153.0</t>
         </is>
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>158.5</t>
+          <t>154.0</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>154.0</t>
+          <t>150.5</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>154.0</t>
+          <t>152.5</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
@@ -5188,12 +5188,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>2.28</t>
+          <t>-1.9</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>1583.205</t>
+          <t>1062.556</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5203,7 +5203,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>157.0</t>
+          <t>154.0</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5213,17 +5213,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-17.6</t>
+          <t>-18.01</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-1.8</t>
+          <t>-2.63</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>2.53</t>
+          <t>8.13</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5288,7 +5288,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-33.76</t>
+          <t>-35.02</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5298,17 +5298,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-03</t>
+          <t>2025-11-04</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>6.55</t>
+          <t>4.39</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>1.01</t>
+          <t>-2.92</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5319,77 +5319,77 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>33</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>4003</t>
+          <t>2845</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>46.67</t>
+          <t>7.14</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>15.56</t>
+          <t>17.94</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>0.90</t>
+          <t>-0.58</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>-4.61</t>
+          <t>-4.59</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>-4.84</t>
+          <t>-4.89</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>-4.85</t>
+          <t>-4.93</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>155.6</t>
+          <t>154.9</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>163.12</t>
+          <t>162.35</t>
         </is>
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>171.42</t>
+          <t>170.7</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>180.16</t>
+          <t>179.54</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>-9.00</t>
+          <t>-7.45</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>-4.97</t>
+          <t>-4.99</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>-4.56</t>
+          <t>-4.65</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
@@ -5399,7 +5399,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-118.32</t>
+          <t>-118.67</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5409,41 +5409,41 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>1702786797.786849</t>
+          <t>1701137811.822511</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>247734521.0</t>
+          <t>166026264.0</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>241423794.4</t>
+          <t>233878777.8</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>235467468.4</t>
+          <t>216301717.4</t>
         </is>
       </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>338636186.98</t>
+          <t>327913288.88</t>
         </is>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>5956326</t>
+          <t>17577060</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>-11573550.41725676</t>
+          <t>-11306597.06250142</t>
         </is>
       </c>
       <c r="BC12" t="n">
-        <v>-4965602.02</v>
+        <v>-9838353.609999999</v>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
@@ -5462,7 +5462,7 @@
       </c>
       <c r="BG12" t="inlineStr">
         <is>
-          <t>-12.78</t>
+          <t>-14.44</t>
         </is>
       </c>
       <c r="BH12" t="inlineStr">
@@ -5487,7 +5487,7 @@
       </c>
       <c r="BL12" t="inlineStr">
         <is>
-          <t>0.99</t>
+          <t>0.98</t>
         </is>
       </c>
       <c r="BM12" t="inlineStr">
@@ -5507,7 +5507,7 @@
       </c>
       <c r="BP12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ12" t="inlineStr">
@@ -5517,12 +5517,12 @@
       </c>
       <c r="BR12" t="inlineStr">
         <is>
-          <t>3.62</t>
+          <t>3.55</t>
         </is>
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>3.12</t>
+          <t>3.19</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
@@ -5532,7 +5532,7 @@
       </c>
       <c r="BU12" t="inlineStr">
         <is>
-          <t>25.09</t>
+          <t>24.53</t>
         </is>
       </c>
       <c r="BV12" t="inlineStr">
@@ -5547,12 +5547,12 @@
       </c>
       <c r="BX12" t="inlineStr">
         <is>
-          <t>28.92</t>
+          <t>28.65</t>
         </is>
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>32961</t>
+          <t>32220</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
@@ -5572,22 +5572,22 @@
       </c>
       <c r="CC12" t="inlineStr">
         <is>
-          <t>153.5</t>
+          <t>157.5</t>
         </is>
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>159.0</t>
+          <t>158.5</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>153.5</t>
+          <t>154.0</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>157.0</t>
+          <t>154.0</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
@@ -5619,12 +5619,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>-1.34</t>
+          <t>-0.54</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>1065.248</t>
+          <t>672.504</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -5634,7 +5634,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>36.95</t>
+          <t>36.75</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -5649,12 +5649,12 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>-1.02</t>
+          <t>-1.79</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>28.28</t>
+          <t>-2.04</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -5719,7 +5719,7 @@
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>-14.37</t>
+          <t>-14.83</t>
         </is>
       </c>
       <c r="X13" t="inlineStr">
@@ -5729,17 +5729,17 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>11.35</t>
+          <t>7.17</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>-0.81</t>
+          <t>-1.09</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
@@ -5750,12 +5750,12 @@
       <c r="AC13" t="inlineStr"/>
       <c r="AD13" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
-          <t>1065</t>
+          <t>673</t>
         </is>
       </c>
       <c r="AF13" t="inlineStr">
@@ -5765,62 +5765,62 @@
       </c>
       <c r="AG13" t="inlineStr">
         <is>
-          <t>9.38</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>-1.86</t>
+          <t>-1.92</t>
         </is>
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>-4.02</t>
+          <t>-3.97</t>
         </is>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>-4.09</t>
+          <t>-4.25</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>-1.60</t>
+          <t>-1.83</t>
         </is>
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>37.65000000000001</t>
+          <t>37.47000000000001</t>
         </is>
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>39.23</t>
+          <t>39.02</t>
         </is>
       </c>
       <c r="AN13" t="inlineStr">
         <is>
-          <t>40.9</t>
+          <t>40.75</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>41.57</t>
+          <t>41.51</t>
         </is>
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>-18.37</t>
+          <t>-19.33</t>
         </is>
       </c>
       <c r="AQ13" t="inlineStr">
         <is>
-          <t>-0.97</t>
+          <t>-1.03</t>
         </is>
       </c>
       <c r="AR13" t="inlineStr">
         <is>
-          <t>-0.82</t>
+          <t>-0.86</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr">
@@ -5830,7 +5830,7 @@
       </c>
       <c r="AT13" t="inlineStr">
         <is>
-          <t>-130.59</t>
+          <t>-132.14</t>
         </is>
       </c>
       <c r="AU13" t="inlineStr">
@@ -5840,41 +5840,41 @@
       </c>
       <c r="AV13" t="inlineStr">
         <is>
-          <t>150978598.7687861</t>
+          <t>150814334.482684</t>
         </is>
       </c>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>39374759.0</t>
+          <t>24762299.0</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>40349216.0</t>
+          <t>31929308.6</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>31454761.9</t>
+          <t>32595150.7</t>
         </is>
       </c>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>29061426.18</t>
+          <t>29130934.74</t>
         </is>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
-          <t>8894454</t>
+          <t>-665842</t>
         </is>
       </c>
       <c r="BB13" t="inlineStr">
         <is>
-          <t>507671.8217403347</t>
+          <t>653269.0727074891</t>
         </is>
       </c>
       <c r="BC13" t="n">
-        <v>2478665.68</v>
+        <v>1454053.95</v>
       </c>
       <c r="BD13" t="inlineStr">
         <is>
@@ -5893,7 +5893,7 @@
       </c>
       <c r="BG13" t="inlineStr">
         <is>
-          <t>-10.96</t>
+          <t>-11.45</t>
         </is>
       </c>
       <c r="BH13" t="inlineStr">
@@ -5938,22 +5938,22 @@
       </c>
       <c r="BP13" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BQ13" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BR13" t="inlineStr">
         <is>
-          <t>1.02</t>
+          <t>1.01</t>
         </is>
       </c>
       <c r="BS13" t="inlineStr">
         <is>
-          <t>6.77</t>
+          <t>6.8</t>
         </is>
       </c>
       <c r="BT13" t="inlineStr">
@@ -5963,7 +5963,7 @@
       </c>
       <c r="BU13" t="inlineStr">
         <is>
-          <t>15.27</t>
+          <t>15.19</t>
         </is>
       </c>
       <c r="BV13" t="inlineStr">
@@ -5978,12 +5978,12 @@
       </c>
       <c r="BX13" t="inlineStr">
         <is>
-          <t>28.92</t>
+          <t>28.65</t>
         </is>
       </c>
       <c r="BY13" t="inlineStr">
         <is>
-          <t>11866</t>
+          <t>11802</t>
         </is>
       </c>
       <c r="BZ13" t="inlineStr">
@@ -6003,22 +6003,22 @@
       </c>
       <c r="CC13" t="inlineStr">
         <is>
+          <t>36.95</t>
+        </is>
+      </c>
+      <c r="CD13" t="inlineStr">
+        <is>
           <t>37.3</t>
         </is>
       </c>
-      <c r="CD13" t="inlineStr">
-        <is>
-          <t>37.5</t>
-        </is>
-      </c>
       <c r="CE13" t="inlineStr">
         <is>
-          <t>36.7</t>
+          <t>36.6</t>
         </is>
       </c>
       <c r="CF13" t="inlineStr">
         <is>
-          <t>36.95</t>
+          <t>36.75</t>
         </is>
       </c>
       <c r="CG13" t="inlineStr">
@@ -6050,12 +6050,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>-1.71</t>
+          <t>-1.34</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>1408.733</t>
+          <t>1065.248</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -6065,7 +6065,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>37.45</t>
+          <t>36.95</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -6075,17 +6075,17 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>-1.35</t>
+          <t>-0.54</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>-1.02</t>
+          <t>-1.79</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>22.93</t>
+          <t>28.28</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -6150,7 +6150,7 @@
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>-13.21</t>
+          <t>-14.37</t>
         </is>
       </c>
       <c r="X14" t="inlineStr">
@@ -6160,17 +6160,17 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>15.01</t>
+          <t>11.35</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>-2.94</t>
+          <t>-0.81</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
@@ -6181,12 +6181,12 @@
       <c r="AC14" t="inlineStr"/>
       <c r="AD14" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
-          <t>1065</t>
+          <t>673</t>
         </is>
       </c>
       <c r="AF14" t="inlineStr">
@@ -6196,62 +6196,62 @@
       </c>
       <c r="AG14" t="inlineStr">
         <is>
-          <t>16.69</t>
+          <t>9.38</t>
         </is>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>-1.42</t>
+          <t>-1.86</t>
         </is>
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>-3.63</t>
+          <t>-4.02</t>
         </is>
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>-3.96</t>
+          <t>-4.09</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>-1.34</t>
+          <t>-1.60</t>
         </is>
       </c>
       <c r="AL14" t="inlineStr">
         <is>
-          <t>37.99</t>
+          <t>37.65000000000001</t>
         </is>
       </c>
       <c r="AM14" t="inlineStr">
         <is>
-          <t>39.42</t>
+          <t>39.23</t>
         </is>
       </c>
       <c r="AN14" t="inlineStr">
         <is>
-          <t>41.05</t>
+          <t>40.9</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>41.6</t>
+          <t>41.57</t>
         </is>
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>-15.49</t>
+          <t>-18.37</t>
         </is>
       </c>
       <c r="AQ14" t="inlineStr">
         <is>
-          <t>-0.91</t>
+          <t>-0.97</t>
         </is>
       </c>
       <c r="AR14" t="inlineStr">
         <is>
-          <t>-0.78</t>
+          <t>-0.82</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr">
@@ -6261,7 +6261,7 @@
       </c>
       <c r="AT14" t="inlineStr">
         <is>
-          <t>-129.19</t>
+          <t>-130.59</t>
         </is>
       </c>
       <c r="AU14" t="inlineStr">
@@ -6271,41 +6271,41 @@
       </c>
       <c r="AV14" t="inlineStr">
         <is>
-          <t>150978598.7687861</t>
+          <t>150814334.482684</t>
         </is>
       </c>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>53218422.0</t>
+          <t>39374759.0</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>36341855.6</t>
+          <t>40349216.0</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
-          <t>29562657.9</t>
+          <t>31454761.9</t>
         </is>
       </c>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>28846965.04</t>
+          <t>29061426.18</t>
         </is>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
-          <t>6779197</t>
+          <t>8894454</t>
         </is>
       </c>
       <c r="BB14" t="inlineStr">
         <is>
-          <t>149309.3019995387</t>
+          <t>507671.8217403347</t>
         </is>
       </c>
       <c r="BC14" t="n">
-        <v>2288252.23</v>
+        <v>2478665.68</v>
       </c>
       <c r="BD14" t="inlineStr">
         <is>
@@ -6324,7 +6324,7 @@
       </c>
       <c r="BG14" t="inlineStr">
         <is>
-          <t>-9.76</t>
+          <t>-10.96</t>
         </is>
       </c>
       <c r="BH14" t="inlineStr">
@@ -6369,22 +6369,22 @@
       </c>
       <c r="BP14" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BQ14" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BR14" t="inlineStr">
         <is>
-          <t>1.03</t>
+          <t>1.02</t>
         </is>
       </c>
       <c r="BS14" t="inlineStr">
         <is>
-          <t>6.77</t>
+          <t>6.8</t>
         </is>
       </c>
       <c r="BT14" t="inlineStr">
@@ -6394,7 +6394,7 @@
       </c>
       <c r="BU14" t="inlineStr">
         <is>
-          <t>15.27</t>
+          <t>15.19</t>
         </is>
       </c>
       <c r="BV14" t="inlineStr">
@@ -6409,12 +6409,12 @@
       </c>
       <c r="BX14" t="inlineStr">
         <is>
-          <t>28.92</t>
+          <t>28.65</t>
         </is>
       </c>
       <c r="BY14" t="inlineStr">
         <is>
-          <t>11866</t>
+          <t>11802</t>
         </is>
       </c>
       <c r="BZ14" t="inlineStr">
@@ -6434,22 +6434,22 @@
       </c>
       <c r="CC14" t="inlineStr">
         <is>
-          <t>38.1</t>
+          <t>37.3</t>
         </is>
       </c>
       <c r="CD14" t="inlineStr">
         <is>
-          <t>38.7</t>
+          <t>37.5</t>
         </is>
       </c>
       <c r="CE14" t="inlineStr">
         <is>
-          <t>37.3</t>
+          <t>36.7</t>
         </is>
       </c>
       <c r="CF14" t="inlineStr">
         <is>
-          <t>37.45</t>
+          <t>36.95</t>
         </is>
       </c>
       <c r="CG14" t="inlineStr">
@@ -6481,12 +6481,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-1.71</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>504.317</t>
+          <t>1408.733</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -6496,7 +6496,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>38.1</t>
+          <t>37.45</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -6506,17 +6506,17 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>-3.11</t>
+          <t>-1.9</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>-1.02</t>
+          <t>-1.79</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>20.39</t>
+          <t>22.93</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -6581,7 +6581,7 @@
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>-11.70</t>
+          <t>-13.21</t>
         </is>
       </c>
       <c r="X15" t="inlineStr">
@@ -6591,17 +6591,17 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>5.37</t>
+          <t>15.01</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>-0.39</t>
+          <t>-2.94</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
@@ -6612,17 +6612,17 @@
       <c r="AC15" t="inlineStr"/>
       <c r="AD15" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
-          <t>1065</t>
+          <t>673</t>
         </is>
       </c>
       <c r="AF15" t="inlineStr">
         <is>
-          <t>28.13</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG15" t="inlineStr">
@@ -6632,57 +6632,57 @@
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>-0.55</t>
+          <t>-1.42</t>
         </is>
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>-3.22</t>
+          <t>-3.63</t>
         </is>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>-3.86</t>
+          <t>-3.96</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>-1.12</t>
+          <t>-1.34</t>
         </is>
       </c>
       <c r="AL15" t="inlineStr">
         <is>
-          <t>38.31</t>
+          <t>37.99</t>
         </is>
       </c>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>39.58</t>
+          <t>39.42</t>
         </is>
       </c>
       <c r="AN15" t="inlineStr">
         <is>
-          <t>41.17</t>
+          <t>41.05</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>41.64</t>
+          <t>41.6</t>
         </is>
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>-13.76</t>
+          <t>-15.49</t>
         </is>
       </c>
       <c r="AQ15" t="inlineStr">
         <is>
-          <t>-0.86</t>
+          <t>-0.91</t>
         </is>
       </c>
       <c r="AR15" t="inlineStr">
         <is>
-          <t>-0.75</t>
+          <t>-0.78</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr">
@@ -6692,7 +6692,7 @@
       </c>
       <c r="AT15" t="inlineStr">
         <is>
-          <t>-128.06</t>
+          <t>-129.19</t>
         </is>
       </c>
       <c r="AU15" t="inlineStr">
@@ -6702,41 +6702,41 @@
       </c>
       <c r="AV15" t="inlineStr">
         <is>
-          <t>150978598.7687861</t>
+          <t>150814334.482684</t>
         </is>
       </c>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>19248593.0</t>
+          <t>53218422.0</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>31147112.0</t>
+          <t>36341855.6</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>25871081.1</t>
+          <t>29562657.9</t>
         </is>
       </c>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>28091032.78</t>
+          <t>28846965.04</t>
         </is>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
-          <t>5276030</t>
+          <t>6779197</t>
         </is>
       </c>
       <c r="BB15" t="inlineStr">
         <is>
-          <t>-239589.4123123131</t>
+          <t>149309.3019995387</t>
         </is>
       </c>
       <c r="BC15" t="n">
-        <v>451260.12</v>
+        <v>2288252.23</v>
       </c>
       <c r="BD15" t="inlineStr">
         <is>
@@ -6755,7 +6755,7 @@
       </c>
       <c r="BG15" t="inlineStr">
         <is>
-          <t>-8.19</t>
+          <t>-9.76</t>
         </is>
       </c>
       <c r="BH15" t="inlineStr">
@@ -6800,7 +6800,7 @@
       </c>
       <c r="BP15" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ15" t="inlineStr">
@@ -6810,12 +6810,12 @@
       </c>
       <c r="BR15" t="inlineStr">
         <is>
-          <t>1.05</t>
+          <t>1.03</t>
         </is>
       </c>
       <c r="BS15" t="inlineStr">
         <is>
-          <t>6.77</t>
+          <t>6.8</t>
         </is>
       </c>
       <c r="BT15" t="inlineStr">
@@ -6825,7 +6825,7 @@
       </c>
       <c r="BU15" t="inlineStr">
         <is>
-          <t>15.27</t>
+          <t>15.19</t>
         </is>
       </c>
       <c r="BV15" t="inlineStr">
@@ -6840,12 +6840,12 @@
       </c>
       <c r="BX15" t="inlineStr">
         <is>
-          <t>28.92</t>
+          <t>28.65</t>
         </is>
       </c>
       <c r="BY15" t="inlineStr">
         <is>
-          <t>11866</t>
+          <t>11802</t>
         </is>
       </c>
       <c r="BZ15" t="inlineStr">
@@ -6865,22 +6865,22 @@
       </c>
       <c r="CC15" t="inlineStr">
         <is>
-          <t>38.2</t>
+          <t>38.1</t>
         </is>
       </c>
       <c r="CD15" t="inlineStr">
         <is>
-          <t>38.4</t>
+          <t>38.7</t>
         </is>
       </c>
       <c r="CE15" t="inlineStr">
         <is>
-          <t>37.95</t>
+          <t>37.3</t>
         </is>
       </c>
       <c r="CF15" t="inlineStr">
         <is>
-          <t>38.1</t>
+          <t>37.45</t>
         </is>
       </c>
       <c r="CG15" t="inlineStr">
@@ -6912,12 +6912,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>1.18</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>605.721</t>
+          <t>504.317</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -6937,17 +6937,17 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>-3.11</t>
+          <t>-3.67</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>-1.02</t>
+          <t>-1.79</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>29.75</t>
+          <t>20.39</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -7022,17 +7022,17 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>6.45</t>
+          <t>5.37</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>0.40</t>
+          <t>-0.39</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
@@ -7043,77 +7043,77 @@
       <c r="AC16" t="inlineStr"/>
       <c r="AD16" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
-          <t>1065</t>
+          <t>673</t>
         </is>
       </c>
       <c r="AF16" t="inlineStr">
         <is>
-          <t>21.95</t>
+          <t>28.13</t>
         </is>
       </c>
       <c r="AG16" t="inlineStr">
         <is>
-          <t>7.32</t>
+          <t>16.69</t>
         </is>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>-0.94</t>
+          <t>-0.55</t>
         </is>
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>-3.10</t>
+          <t>-3.22</t>
         </is>
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>-3.87</t>
+          <t>-3.86</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>-0.91</t>
+          <t>-1.12</t>
         </is>
       </c>
       <c r="AL16" t="inlineStr">
         <is>
-          <t>38.46</t>
+          <t>38.31</t>
         </is>
       </c>
       <c r="AM16" t="inlineStr">
         <is>
-          <t>39.69</t>
+          <t>39.58</t>
         </is>
       </c>
       <c r="AN16" t="inlineStr">
         <is>
-          <t>41.29</t>
+          <t>41.17</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>41.67</t>
+          <t>41.64</t>
         </is>
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>-16.76</t>
+          <t>-13.76</t>
         </is>
       </c>
       <c r="AQ16" t="inlineStr">
         <is>
-          <t>-0.85</t>
+          <t>-0.86</t>
         </is>
       </c>
       <c r="AR16" t="inlineStr">
         <is>
-          <t>-0.73</t>
+          <t>-0.75</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr">
@@ -7123,7 +7123,7 @@
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>-127.09</t>
+          <t>-128.06</t>
         </is>
       </c>
       <c r="AU16" t="inlineStr">
@@ -7133,41 +7133,41 @@
       </c>
       <c r="AV16" t="inlineStr">
         <is>
-          <t>150978598.7687861</t>
+          <t>150814334.482684</t>
         </is>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>23042470.0</t>
+          <t>19248593.0</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>33965584.0</t>
+          <t>31147112.0</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>26178217.9</t>
+          <t>25871081.1</t>
         </is>
       </c>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>28206383.42</t>
+          <t>28091032.78</t>
         </is>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
-          <t>7787366</t>
+          <t>5276030</t>
         </is>
       </c>
       <c r="BB16" t="inlineStr">
         <is>
-          <t>-365198.417442461</t>
+          <t>-239589.4123123131</t>
         </is>
       </c>
       <c r="BC16" t="n">
-        <v>1450493.77</v>
+        <v>451260.12</v>
       </c>
       <c r="BD16" t="inlineStr">
         <is>
@@ -7231,7 +7231,7 @@
       </c>
       <c r="BP16" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;可能出現反轉訊號&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;3&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ16" t="inlineStr">
@@ -7246,7 +7246,7 @@
       </c>
       <c r="BS16" t="inlineStr">
         <is>
-          <t>6.77</t>
+          <t>6.8</t>
         </is>
       </c>
       <c r="BT16" t="inlineStr">
@@ -7256,7 +7256,7 @@
       </c>
       <c r="BU16" t="inlineStr">
         <is>
-          <t>15.27</t>
+          <t>15.19</t>
         </is>
       </c>
       <c r="BV16" t="inlineStr">
@@ -7271,12 +7271,12 @@
       </c>
       <c r="BX16" t="inlineStr">
         <is>
-          <t>28.92</t>
+          <t>28.65</t>
         </is>
       </c>
       <c r="BY16" t="inlineStr">
         <is>
-          <t>11866</t>
+          <t>11802</t>
         </is>
       </c>
       <c r="BZ16" t="inlineStr">
@@ -7296,17 +7296,17 @@
       </c>
       <c r="CC16" t="inlineStr">
         <is>
-          <t>38.0</t>
+          <t>38.2</t>
         </is>
       </c>
       <c r="CD16" t="inlineStr">
         <is>
-          <t>38.3</t>
+          <t>38.4</t>
         </is>
       </c>
       <c r="CE16" t="inlineStr">
         <is>
-          <t>37.75</t>
+          <t>37.95</t>
         </is>
       </c>
       <c r="CF16" t="inlineStr">
@@ -7343,12 +7343,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>-2.6</t>
+          <t>1.18</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>1764.112</t>
+          <t>605.721</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -7358,7 +7358,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>37.65</t>
+          <t>38.1</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -7368,17 +7368,17 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>-1.89</t>
+          <t>-3.67</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>-1.02</t>
+          <t>-1.79</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>21.53</t>
+          <t>29.75</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -7443,7 +7443,7 @@
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>-12.75</t>
+          <t>-11.70</t>
         </is>
       </c>
       <c r="X17" t="inlineStr">
@@ -7453,17 +7453,17 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>18.80</t>
+          <t>6.45</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>-2.12</t>
+          <t>0.40</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
@@ -7474,77 +7474,77 @@
       <c r="AC17" t="inlineStr"/>
       <c r="AD17" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
-          <t>1065</t>
+          <t>673</t>
         </is>
       </c>
       <c r="AF17" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>21.95</t>
         </is>
       </c>
       <c r="AG17" t="inlineStr">
         <is>
-          <t>6.67</t>
+          <t>7.32</t>
         </is>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>-2.44</t>
+          <t>-0.94</t>
         </is>
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>-3.03</t>
+          <t>-3.10</t>
         </is>
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>-3.91</t>
+          <t>-3.87</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>-0.66</t>
+          <t>-0.91</t>
         </is>
       </c>
       <c r="AL17" t="inlineStr">
         <is>
-          <t>38.59</t>
+          <t>38.46</t>
         </is>
       </c>
       <c r="AM17" t="inlineStr">
         <is>
-          <t>39.8</t>
+          <t>39.69</t>
         </is>
       </c>
       <c r="AN17" t="inlineStr">
         <is>
-          <t>41.42</t>
+          <t>41.29</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>41.69</t>
+          <t>41.67</t>
         </is>
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>-18.69</t>
+          <t>-16.76</t>
         </is>
       </c>
       <c r="AQ17" t="inlineStr">
         <is>
-          <t>-0.83</t>
+          <t>-0.85</t>
         </is>
       </c>
       <c r="AR17" t="inlineStr">
         <is>
-          <t>-0.70</t>
+          <t>-0.73</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr">
@@ -7554,7 +7554,7 @@
       </c>
       <c r="AT17" t="inlineStr">
         <is>
-          <t>-125.95</t>
+          <t>-127.09</t>
         </is>
       </c>
       <c r="AU17" t="inlineStr">
@@ -7564,41 +7564,41 @@
       </c>
       <c r="AV17" t="inlineStr">
         <is>
-          <t>150978598.7687861</t>
+          <t>150814334.482684</t>
         </is>
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>66861836.0</t>
+          <t>23042470.0</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>33260992.8</t>
+          <t>33965584.0</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>27368625.9</t>
+          <t>26178217.9</t>
         </is>
       </c>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>28716017.48</t>
+          <t>28206383.42</t>
         </is>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
-          <t>5892366</t>
+          <t>7787366</t>
         </is>
       </c>
       <c r="BB17" t="inlineStr">
         <is>
-          <t>-695324.269555022</t>
+          <t>-365198.417442461</t>
         </is>
       </c>
       <c r="BC17" t="n">
-        <v>2419680.25</v>
+        <v>1450493.77</v>
       </c>
       <c r="BD17" t="inlineStr">
         <is>
@@ -7617,7 +7617,7 @@
       </c>
       <c r="BG17" t="inlineStr">
         <is>
-          <t>-9.28</t>
+          <t>-8.19</t>
         </is>
       </c>
       <c r="BH17" t="inlineStr">
@@ -7662,22 +7662,22 @@
       </c>
       <c r="BP17" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;可能出現反轉訊號&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;3&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ17" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BR17" t="inlineStr">
         <is>
-          <t>1.04</t>
+          <t>1.05</t>
         </is>
       </c>
       <c r="BS17" t="inlineStr">
         <is>
-          <t>6.77</t>
+          <t>6.8</t>
         </is>
       </c>
       <c r="BT17" t="inlineStr">
@@ -7687,7 +7687,7 @@
       </c>
       <c r="BU17" t="inlineStr">
         <is>
-          <t>15.27</t>
+          <t>15.19</t>
         </is>
       </c>
       <c r="BV17" t="inlineStr">
@@ -7702,12 +7702,12 @@
       </c>
       <c r="BX17" t="inlineStr">
         <is>
-          <t>28.92</t>
+          <t>28.65</t>
         </is>
       </c>
       <c r="BY17" t="inlineStr">
         <is>
-          <t>11866</t>
+          <t>11802</t>
         </is>
       </c>
       <c r="BZ17" t="inlineStr">
@@ -7727,22 +7727,22 @@
       </c>
       <c r="CC17" t="inlineStr">
         <is>
-          <t>38.45</t>
+          <t>38.0</t>
         </is>
       </c>
       <c r="CD17" t="inlineStr">
         <is>
-          <t>38.75</t>
+          <t>38.3</t>
         </is>
       </c>
       <c r="CE17" t="inlineStr">
         <is>
-          <t>37.35</t>
+          <t>37.75</t>
         </is>
       </c>
       <c r="CF17" t="inlineStr">
         <is>
-          <t>37.65</t>
+          <t>38.1</t>
         </is>
       </c>
       <c r="CG17" t="inlineStr">
@@ -7774,12 +7774,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>-1.03</t>
+          <t>-2.6</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>499.552</t>
+          <t>1764.112</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -7789,7 +7789,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>38.65</t>
+          <t>37.65</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -7799,17 +7799,17 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>-4.6</t>
+          <t>-2.45</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>-1.02</t>
+          <t>-1.79</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>0.16</t>
+          <t>21.53</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -7874,7 +7874,7 @@
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>-10.43</t>
+          <t>-12.75</t>
         </is>
       </c>
       <c r="X18" t="inlineStr">
@@ -7884,17 +7884,17 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>5.32</t>
+          <t>18.80</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>-1.42</t>
+          <t>-2.12</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
@@ -7905,12 +7905,12 @@
       <c r="AC18" t="inlineStr"/>
       <c r="AD18" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
-          <t>1065</t>
+          <t>673</t>
         </is>
       </c>
       <c r="AF18" t="inlineStr">
@@ -7920,17 +7920,17 @@
       </c>
       <c r="AG18" t="inlineStr">
         <is>
-          <t>8.47</t>
+          <t>6.67</t>
         </is>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>-0.57</t>
+          <t>-2.44</t>
         </is>
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>-2.61</t>
+          <t>-3.03</t>
         </is>
       </c>
       <c r="AJ18" t="inlineStr">
@@ -7940,42 +7940,42 @@
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>-0.43</t>
+          <t>-0.66</t>
         </is>
       </c>
       <c r="AL18" t="inlineStr">
         <is>
-          <t>38.87</t>
+          <t>38.59</t>
         </is>
       </c>
       <c r="AM18" t="inlineStr">
         <is>
-          <t>39.91</t>
+          <t>39.8</t>
         </is>
       </c>
       <c r="AN18" t="inlineStr">
         <is>
-          <t>41.54</t>
+          <t>41.42</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>41.72</t>
+          <t>41.69</t>
         </is>
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>-11.54</t>
+          <t>-18.69</t>
         </is>
       </c>
       <c r="AQ18" t="inlineStr">
         <is>
-          <t>-0.74</t>
+          <t>-0.83</t>
         </is>
       </c>
       <c r="AR18" t="inlineStr">
         <is>
-          <t>-0.66</t>
+          <t>-0.70</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr">
@@ -7985,7 +7985,7 @@
       </c>
       <c r="AT18" t="inlineStr">
         <is>
-          <t>-124.74</t>
+          <t>-125.95</t>
         </is>
       </c>
       <c r="AU18" t="inlineStr">
@@ -7995,41 +7995,41 @@
       </c>
       <c r="AV18" t="inlineStr">
         <is>
-          <t>150978598.7687861</t>
+          <t>150814334.482684</t>
         </is>
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>19337957.0</t>
+          <t>66861836.0</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>22560307.8</t>
+          <t>33260992.8</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>22524902.5</t>
+          <t>27368625.9</t>
         </is>
       </c>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>28140249.02</t>
+          <t>28716017.48</t>
         </is>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
-          <t>35405</t>
+          <t>5892366</t>
         </is>
       </c>
       <c r="BB18" t="inlineStr">
         <is>
-          <t>-1261688.726998104</t>
+          <t>-695324.269555022</t>
         </is>
       </c>
       <c r="BC18" t="n">
-        <v>-977116.87</v>
+        <v>2419680.25</v>
       </c>
       <c r="BD18" t="inlineStr">
         <is>
@@ -8048,7 +8048,7 @@
       </c>
       <c r="BG18" t="inlineStr">
         <is>
-          <t>-6.87</t>
+          <t>-9.28</t>
         </is>
       </c>
       <c r="BH18" t="inlineStr">
@@ -8093,22 +8093,22 @@
       </c>
       <c r="BP18" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ18" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BR18" t="inlineStr">
         <is>
-          <t>1.06</t>
+          <t>1.04</t>
         </is>
       </c>
       <c r="BS18" t="inlineStr">
         <is>
-          <t>6.77</t>
+          <t>6.8</t>
         </is>
       </c>
       <c r="BT18" t="inlineStr">
@@ -8118,7 +8118,7 @@
       </c>
       <c r="BU18" t="inlineStr">
         <is>
-          <t>15.27</t>
+          <t>15.19</t>
         </is>
       </c>
       <c r="BV18" t="inlineStr">
@@ -8133,12 +8133,12 @@
       </c>
       <c r="BX18" t="inlineStr">
         <is>
-          <t>28.92</t>
+          <t>28.65</t>
         </is>
       </c>
       <c r="BY18" t="inlineStr">
         <is>
-          <t>11866</t>
+          <t>11802</t>
         </is>
       </c>
       <c r="BZ18" t="inlineStr">
@@ -8158,22 +8158,22 @@
       </c>
       <c r="CC18" t="inlineStr">
         <is>
-          <t>38.95</t>
+          <t>38.45</t>
         </is>
       </c>
       <c r="CD18" t="inlineStr">
         <is>
-          <t>39.3</t>
+          <t>38.75</t>
         </is>
       </c>
       <c r="CE18" t="inlineStr">
         <is>
-          <t>38.55</t>
+          <t>37.35</t>
         </is>
       </c>
       <c r="CF18" t="inlineStr">
         <is>
-          <t>38.65</t>
+          <t>37.65</t>
         </is>
       </c>
       <c r="CG18" t="inlineStr">
@@ -8205,12 +8205,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>0.51</t>
+          <t>-1.03</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>700.928</t>
+          <t>499.552</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -8220,7 +8220,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>39.05</t>
+          <t>38.65</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -8230,17 +8230,17 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>-5.68</t>
+          <t>-5.17</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>-1.02</t>
+          <t>-1.79</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>0.15</t>
+          <t>0.16</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -8305,7 +8305,7 @@
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>-9.50</t>
+          <t>-10.43</t>
         </is>
       </c>
       <c r="X19" t="inlineStr">
@@ -8315,17 +8315,17 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>7.47</t>
+          <t>5.32</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>1.17</t>
+          <t>-1.42</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
@@ -8336,17 +8336,17 @@
       <c r="AC19" t="inlineStr"/>
       <c r="AD19" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
-          <t>1065</t>
+          <t>673</t>
         </is>
       </c>
       <c r="AF19" t="inlineStr">
         <is>
-          <t>20.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG19" t="inlineStr">
@@ -8356,57 +8356,57 @@
       </c>
       <c r="AH19" t="inlineStr">
         <is>
-          <t>0.15</t>
+          <t>-0.57</t>
         </is>
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>-2.53</t>
+          <t>-2.61</t>
         </is>
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>-3.9</t>
+          <t>-3.91</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>-0.25</t>
+          <t>-0.43</t>
         </is>
       </c>
       <c r="AL19" t="inlineStr">
         <is>
-          <t>38.99</t>
+          <t>38.87</t>
         </is>
       </c>
       <c r="AM19" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>39.91</t>
         </is>
       </c>
       <c r="AN19" t="inlineStr">
         <is>
-          <t>41.63</t>
+          <t>41.54</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>41.73</t>
+          <t>41.72</t>
         </is>
       </c>
       <c r="AP19" t="inlineStr">
         <is>
-          <t>-11.93</t>
+          <t>-11.54</t>
         </is>
       </c>
       <c r="AQ19" t="inlineStr">
         <is>
-          <t>-0.72</t>
+          <t>-0.74</t>
         </is>
       </c>
       <c r="AR19" t="inlineStr">
         <is>
-          <t>-0.65</t>
+          <t>-0.66</t>
         </is>
       </c>
       <c r="AS19" t="inlineStr">
@@ -8416,7 +8416,7 @@
       </c>
       <c r="AT19" t="inlineStr">
         <is>
-          <t>-124.03</t>
+          <t>-124.74</t>
         </is>
       </c>
       <c r="AU19" t="inlineStr">
@@ -8426,41 +8426,41 @@
       </c>
       <c r="AV19" t="inlineStr">
         <is>
-          <t>150978598.7687861</t>
+          <t>150814334.482684</t>
         </is>
       </c>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>27244704.0</t>
+          <t>19337957.0</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>22783460.2</t>
+          <t>22560307.8</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
-          <t>22749645.3</t>
+          <t>22524902.5</t>
         </is>
       </c>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>28438883.58</t>
+          <t>28140249.02</t>
         </is>
       </c>
       <c r="BA19" t="inlineStr">
         <is>
-          <t>33814</t>
+          <t>35405</t>
         </is>
       </c>
       <c r="BB19" t="inlineStr">
         <is>
-          <t>-1313429.065286876</t>
+          <t>-1261688.726998104</t>
         </is>
       </c>
       <c r="BC19" t="n">
-        <v>-702942.96</v>
+        <v>-977116.87</v>
       </c>
       <c r="BD19" t="inlineStr">
         <is>
@@ -8479,7 +8479,7 @@
       </c>
       <c r="BG19" t="inlineStr">
         <is>
-          <t>-5.90</t>
+          <t>-6.87</t>
         </is>
       </c>
       <c r="BH19" t="inlineStr">
@@ -8524,22 +8524,22 @@
       </c>
       <c r="BP19" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ19" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BR19" t="inlineStr">
         <is>
-          <t>1.07</t>
+          <t>1.06</t>
         </is>
       </c>
       <c r="BS19" t="inlineStr">
         <is>
-          <t>6.77</t>
+          <t>6.8</t>
         </is>
       </c>
       <c r="BT19" t="inlineStr">
@@ -8549,7 +8549,7 @@
       </c>
       <c r="BU19" t="inlineStr">
         <is>
-          <t>15.27</t>
+          <t>15.19</t>
         </is>
       </c>
       <c r="BV19" t="inlineStr">
@@ -8564,12 +8564,12 @@
       </c>
       <c r="BX19" t="inlineStr">
         <is>
-          <t>28.92</t>
+          <t>28.65</t>
         </is>
       </c>
       <c r="BY19" t="inlineStr">
         <is>
-          <t>11866</t>
+          <t>11802</t>
         </is>
       </c>
       <c r="BZ19" t="inlineStr">
@@ -8589,22 +8589,22 @@
       </c>
       <c r="CC19" t="inlineStr">
         <is>
-          <t>38.85</t>
+          <t>38.95</t>
         </is>
       </c>
       <c r="CD19" t="inlineStr">
         <is>
-          <t>39.05</t>
+          <t>39.3</t>
         </is>
       </c>
       <c r="CE19" t="inlineStr">
         <is>
-          <t>38.6</t>
+          <t>38.55</t>
         </is>
       </c>
       <c r="CF19" t="inlineStr">
         <is>
-          <t>39.05</t>
+          <t>38.65</t>
         </is>
       </c>
       <c r="CG19" t="inlineStr">
@@ -8636,12 +8636,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>0.26</t>
+          <t>0.51</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>857.171</t>
+          <t>700.928</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -8651,7 +8651,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>38.85</t>
+          <t>39.05</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -8661,17 +8661,17 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>-5.14</t>
+          <t>-6.26</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>-1.02</t>
+          <t>-1.79</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>-6.52</t>
+          <t>0.15</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -8736,7 +8736,7 @@
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>-9.97</t>
+          <t>-9.50</t>
         </is>
       </c>
       <c r="X20" t="inlineStr">
@@ -8746,17 +8746,17 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-11-06</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>9.13</t>
+          <t>7.47</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>-0.13</t>
+          <t>1.17</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
@@ -8767,57 +8767,57 @@
       <c r="AC20" t="inlineStr"/>
       <c r="AD20" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
-          <t>1065</t>
+          <t>673</t>
         </is>
       </c>
       <c r="AF20" t="inlineStr">
         <is>
-          <t>5.41</t>
+          <t>20.0</t>
         </is>
       </c>
       <c r="AG20" t="inlineStr">
         <is>
-          <t>1.8</t>
+          <t>8.47</t>
         </is>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
-          <t>-0.69</t>
+          <t>0.15</t>
         </is>
       </c>
       <c r="AI20" t="inlineStr">
         <is>
-          <t>-2.41</t>
+          <t>-2.53</t>
         </is>
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>-3.92</t>
+          <t>-3.9</t>
         </is>
       </c>
       <c r="AK20" t="inlineStr">
         <is>
-          <t>-0.03</t>
+          <t>-0.25</t>
         </is>
       </c>
       <c r="AL20" t="inlineStr">
         <is>
-          <t>39.12</t>
+          <t>38.99</t>
         </is>
       </c>
       <c r="AM20" t="inlineStr">
         <is>
-          <t>40.08</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="AN20" t="inlineStr">
         <is>
-          <t>41.72</t>
+          <t>41.63</t>
         </is>
       </c>
       <c r="AO20" t="inlineStr">
@@ -8827,17 +8827,17 @@
       </c>
       <c r="AP20" t="inlineStr">
         <is>
-          <t>-16.36</t>
+          <t>-11.93</t>
         </is>
       </c>
       <c r="AQ20" t="inlineStr">
         <is>
-          <t>-0.73</t>
+          <t>-0.72</t>
         </is>
       </c>
       <c r="AR20" t="inlineStr">
         <is>
-          <t>-0.63</t>
+          <t>-0.65</t>
         </is>
       </c>
       <c r="AS20" t="inlineStr">
@@ -8847,7 +8847,7 @@
       </c>
       <c r="AT20" t="inlineStr">
         <is>
-          <t>-123.31</t>
+          <t>-124.03</t>
         </is>
       </c>
       <c r="AU20" t="inlineStr">
@@ -8857,41 +8857,41 @@
       </c>
       <c r="AV20" t="inlineStr">
         <is>
-          <t>150978598.7687861</t>
+          <t>150814334.482684</t>
         </is>
       </c>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>33340953.0</t>
+          <t>27244704.0</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>20595050.2</t>
+          <t>22783460.2</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
-          <t>22030516.7</t>
+          <t>22749645.3</t>
         </is>
       </c>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>28317533.86</t>
+          <t>28438883.58</t>
         </is>
       </c>
       <c r="BA20" t="inlineStr">
         <is>
-          <t>-1435466</t>
+          <t>33814</t>
         </is>
       </c>
       <c r="BB20" t="inlineStr">
         <is>
-          <t>-1424426.538814767</t>
+          <t>-1313429.065286876</t>
         </is>
       </c>
       <c r="BC20" t="n">
-        <v>-1133312.31</v>
+        <v>-702942.96</v>
       </c>
       <c r="BD20" t="inlineStr">
         <is>
@@ -8910,7 +8910,7 @@
       </c>
       <c r="BG20" t="inlineStr">
         <is>
-          <t>-6.39</t>
+          <t>-5.90</t>
         </is>
       </c>
       <c r="BH20" t="inlineStr">
@@ -8955,7 +8955,7 @@
       </c>
       <c r="BP20" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ20" t="inlineStr">
@@ -8970,7 +8970,7 @@
       </c>
       <c r="BS20" t="inlineStr">
         <is>
-          <t>6.77</t>
+          <t>6.8</t>
         </is>
       </c>
       <c r="BT20" t="inlineStr">
@@ -8980,7 +8980,7 @@
       </c>
       <c r="BU20" t="inlineStr">
         <is>
-          <t>15.27</t>
+          <t>15.19</t>
         </is>
       </c>
       <c r="BV20" t="inlineStr">
@@ -8995,12 +8995,12 @@
       </c>
       <c r="BX20" t="inlineStr">
         <is>
-          <t>28.92</t>
+          <t>28.65</t>
         </is>
       </c>
       <c r="BY20" t="inlineStr">
         <is>
-          <t>11866</t>
+          <t>11802</t>
         </is>
       </c>
       <c r="BZ20" t="inlineStr">
@@ -9020,22 +9020,22 @@
       </c>
       <c r="CC20" t="inlineStr">
         <is>
-          <t>38.95</t>
+          <t>38.85</t>
         </is>
       </c>
       <c r="CD20" t="inlineStr">
         <is>
-          <t>39.1</t>
+          <t>39.05</t>
         </is>
       </c>
       <c r="CE20" t="inlineStr">
         <is>
-          <t>38.65</t>
+          <t>38.6</t>
         </is>
       </c>
       <c r="CF20" t="inlineStr">
         <is>
-          <t>38.85</t>
+          <t>39.05</t>
         </is>
       </c>
       <c r="CG20" t="inlineStr">
@@ -9067,12 +9067,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>-0.77</t>
+          <t>0.26</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>504.24</t>
+          <t>857.171</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -9082,7 +9082,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>38.75</t>
+          <t>38.85</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -9092,17 +9092,17 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>-4.87</t>
+          <t>-5.71</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>-1.02</t>
+          <t>-1.79</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>-9.08</t>
+          <t>-6.52</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -9167,7 +9167,7 @@
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>-10.20</t>
+          <t>-9.97</t>
         </is>
       </c>
       <c r="X21" t="inlineStr">
@@ -9177,17 +9177,17 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-11-05</t>
+          <t>2025-11-06</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>5.37</t>
+          <t>9.13</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>-0.13</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
@@ -9198,77 +9198,77 @@
       <c r="AC21" t="inlineStr"/>
       <c r="AD21" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
-          <t>1065</t>
+          <t>673</t>
         </is>
       </c>
       <c r="AF21" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>5.41</t>
         </is>
       </c>
       <c r="AG21" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.8</t>
         </is>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
-          <t>-1.40</t>
+          <t>-0.69</t>
         </is>
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>-2.22</t>
+          <t>-2.41</t>
         </is>
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>-3.89</t>
+          <t>-3.92</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
         <is>
-          <t>0.23</t>
+          <t>-0.03</t>
         </is>
       </c>
       <c r="AL21" t="inlineStr">
         <is>
-          <t>39.3</t>
+          <t>39.12</t>
         </is>
       </c>
       <c r="AM21" t="inlineStr">
         <is>
-          <t>40.19</t>
+          <t>40.08</t>
         </is>
       </c>
       <c r="AN21" t="inlineStr">
         <is>
-          <t>41.82</t>
+          <t>41.72</t>
         </is>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>41.72</t>
+          <t>41.73</t>
         </is>
       </c>
       <c r="AP21" t="inlineStr">
         <is>
-          <t>-17.47</t>
+          <t>-16.36</t>
         </is>
       </c>
       <c r="AQ21" t="inlineStr">
         <is>
-          <t>-0.71</t>
+          <t>-0.73</t>
         </is>
       </c>
       <c r="AR21" t="inlineStr">
         <is>
-          <t>-0.60</t>
+          <t>-0.63</t>
         </is>
       </c>
       <c r="AS21" t="inlineStr">
@@ -9278,7 +9278,7 @@
       </c>
       <c r="AT21" t="inlineStr">
         <is>
-          <t>-122.36</t>
+          <t>-123.31</t>
         </is>
       </c>
       <c r="AU21" t="inlineStr">
@@ -9288,41 +9288,41 @@
       </c>
       <c r="AV21" t="inlineStr">
         <is>
-          <t>150978598.7687861</t>
+          <t>150814334.482684</t>
         </is>
       </c>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>19519514.0</t>
+          <t>33340953.0</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>18390851.8</t>
+          <t>20595050.2</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
-          <t>20228126.1</t>
+          <t>22030516.7</t>
         </is>
       </c>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>28082029.5</t>
+          <t>28317533.86</t>
         </is>
       </c>
       <c r="BA21" t="inlineStr">
         <is>
-          <t>-1837274</t>
+          <t>-1435466</t>
         </is>
       </c>
       <c r="BB21" t="inlineStr">
         <is>
-          <t>-1477356.398321357</t>
+          <t>-1424426.538814767</t>
         </is>
       </c>
       <c r="BC21" t="n">
-        <v>-2360819.77</v>
+        <v>-1133312.31</v>
       </c>
       <c r="BD21" t="inlineStr">
         <is>
@@ -9341,7 +9341,7 @@
       </c>
       <c r="BG21" t="inlineStr">
         <is>
-          <t>-6.63</t>
+          <t>-6.39</t>
         </is>
       </c>
       <c r="BH21" t="inlineStr">
@@ -9386,7 +9386,7 @@
       </c>
       <c r="BP21" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ21" t="inlineStr">
@@ -9401,7 +9401,7 @@
       </c>
       <c r="BS21" t="inlineStr">
         <is>
-          <t>6.77</t>
+          <t>6.8</t>
         </is>
       </c>
       <c r="BT21" t="inlineStr">
@@ -9411,7 +9411,7 @@
       </c>
       <c r="BU21" t="inlineStr">
         <is>
-          <t>15.27</t>
+          <t>15.19</t>
         </is>
       </c>
       <c r="BV21" t="inlineStr">
@@ -9426,12 +9426,12 @@
       </c>
       <c r="BX21" t="inlineStr">
         <is>
-          <t>28.92</t>
+          <t>28.65</t>
         </is>
       </c>
       <c r="BY21" t="inlineStr">
         <is>
-          <t>11866</t>
+          <t>11802</t>
         </is>
       </c>
       <c r="BZ21" t="inlineStr">
@@ -9451,22 +9451,22 @@
       </c>
       <c r="CC21" t="inlineStr">
         <is>
-          <t>39.15</t>
+          <t>38.95</t>
         </is>
       </c>
       <c r="CD21" t="inlineStr">
         <is>
-          <t>39.15</t>
+          <t>39.1</t>
         </is>
       </c>
       <c r="CE21" t="inlineStr">
         <is>
-          <t>38.35</t>
+          <t>38.65</t>
         </is>
       </c>
       <c r="CF21" t="inlineStr">
         <is>
-          <t>38.75</t>
+          <t>38.85</t>
         </is>
       </c>
       <c r="CG21" t="inlineStr">
@@ -9498,12 +9498,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>-0.51</t>
+          <t>-0.77</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>340.21</t>
+          <t>504.24</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -9513,7 +9513,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>39.05</t>
+          <t>38.75</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -9523,17 +9523,17 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>-5.68</t>
+          <t>-5.44</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>-1.02</t>
+          <t>-1.79</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>2.77</t>
+          <t>-9.08</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -9598,7 +9598,7 @@
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>-9.50</t>
+          <t>-10.20</t>
         </is>
       </c>
       <c r="X22" t="inlineStr">
@@ -9608,17 +9608,17 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-11-04</t>
+          <t>2025-11-05</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>3.63</t>
+          <t>5.37</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>-1.41</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
@@ -9629,12 +9629,12 @@
       <c r="AC22" t="inlineStr"/>
       <c r="AD22" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AE22" t="inlineStr">
         <is>
-          <t>1065</t>
+          <t>673</t>
         </is>
       </c>
       <c r="AF22" t="inlineStr">
@@ -9649,57 +9649,57 @@
       </c>
       <c r="AH22" t="inlineStr">
         <is>
-          <t>-1.21</t>
+          <t>-1.40</t>
         </is>
       </c>
       <c r="AI22" t="inlineStr">
         <is>
-          <t>-1.92</t>
+          <t>-2.22</t>
         </is>
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>-3.88</t>
+          <t>-3.89</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
         <is>
-          <t>0.53</t>
+          <t>0.23</t>
         </is>
       </c>
       <c r="AL22" t="inlineStr">
         <is>
-          <t>39.53</t>
+          <t>39.3</t>
         </is>
       </c>
       <c r="AM22" t="inlineStr">
         <is>
-          <t>40.3</t>
+          <t>40.19</t>
         </is>
       </c>
       <c r="AN22" t="inlineStr">
         <is>
-          <t>41.93</t>
+          <t>41.82</t>
         </is>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>41.71</t>
+          <t>41.72</t>
         </is>
       </c>
       <c r="AP22" t="inlineStr">
         <is>
-          <t>-14.13</t>
+          <t>-17.47</t>
         </is>
       </c>
       <c r="AQ22" t="inlineStr">
         <is>
-          <t>-0.66</t>
+          <t>-0.71</t>
         </is>
       </c>
       <c r="AR22" t="inlineStr">
         <is>
-          <t>-0.57</t>
+          <t>-0.60</t>
         </is>
       </c>
       <c r="AS22" t="inlineStr">
@@ -9709,7 +9709,7 @@
       </c>
       <c r="AT22" t="inlineStr">
         <is>
-          <t>-121.38</t>
+          <t>-122.36</t>
         </is>
       </c>
       <c r="AU22" t="inlineStr">
@@ -9719,41 +9719,41 @@
       </c>
       <c r="AV22" t="inlineStr">
         <is>
-          <t>150978598.7687861</t>
+          <t>150814334.482684</t>
         </is>
       </c>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>13358411.0</t>
+          <t>19519514.0</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>21476259.0</t>
+          <t>18390851.8</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr">
         <is>
-          <t>20896470.1</t>
+          <t>20228126.1</t>
         </is>
       </c>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>28018183.18</t>
+          <t>28082029.5</t>
         </is>
       </c>
       <c r="BA22" t="inlineStr">
         <is>
-          <t>579788</t>
+          <t>-1837274</t>
         </is>
       </c>
       <c r="BB22" t="inlineStr">
         <is>
-          <t>-1316726.695178018</t>
+          <t>-1477356.398321357</t>
         </is>
       </c>
       <c r="BC22" t="n">
-        <v>-2549218.39</v>
+        <v>-2360819.77</v>
       </c>
       <c r="BD22" t="inlineStr">
         <is>
@@ -9772,7 +9772,7 @@
       </c>
       <c r="BG22" t="inlineStr">
         <is>
-          <t>-5.90</t>
+          <t>-6.63</t>
         </is>
       </c>
       <c r="BH22" t="inlineStr">
@@ -9817,7 +9817,7 @@
       </c>
       <c r="BP22" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BQ22" t="inlineStr">
@@ -9832,7 +9832,7 @@
       </c>
       <c r="BS22" t="inlineStr">
         <is>
-          <t>6.77</t>
+          <t>6.8</t>
         </is>
       </c>
       <c r="BT22" t="inlineStr">
@@ -9842,7 +9842,7 @@
       </c>
       <c r="BU22" t="inlineStr">
         <is>
-          <t>15.27</t>
+          <t>15.19</t>
         </is>
       </c>
       <c r="BV22" t="inlineStr">
@@ -9857,12 +9857,12 @@
       </c>
       <c r="BX22" t="inlineStr">
         <is>
-          <t>28.92</t>
+          <t>28.65</t>
         </is>
       </c>
       <c r="BY22" t="inlineStr">
         <is>
-          <t>11866</t>
+          <t>11802</t>
         </is>
       </c>
       <c r="BZ22" t="inlineStr">
@@ -9882,22 +9882,22 @@
       </c>
       <c r="CC22" t="inlineStr">
         <is>
-          <t>39.2</t>
+          <t>39.15</t>
         </is>
       </c>
       <c r="CD22" t="inlineStr">
         <is>
-          <t>39.6</t>
+          <t>39.15</t>
         </is>
       </c>
       <c r="CE22" t="inlineStr">
         <is>
-          <t>39.05</t>
+          <t>38.35</t>
         </is>
       </c>
       <c r="CF22" t="inlineStr">
         <is>
-          <t>39.05</t>
+          <t>38.75</t>
         </is>
       </c>
       <c r="CG22" t="inlineStr">
@@ -9929,12 +9929,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>-1.13</t>
+          <t>-0.51</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>519.475</t>
+          <t>340.21</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -9944,7 +9944,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>39.25</t>
+          <t>39.05</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -9954,17 +9954,17 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>-6.22</t>
+          <t>-6.26</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>-1.02</t>
+          <t>-1.79</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>3.53</t>
+          <t>2.77</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -10029,7 +10029,7 @@
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>-9.04</t>
+          <t>-9.50</t>
         </is>
       </c>
       <c r="X23" t="inlineStr">
@@ -10039,17 +10039,17 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-11-03</t>
+          <t>2025-11-04</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>5.54</t>
+          <t>3.63</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>-1.15</t>
+          <t>-1.41</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
@@ -10060,12 +10060,12 @@
       <c r="AC23" t="inlineStr"/>
       <c r="AD23" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AE23" t="inlineStr">
         <is>
-          <t>1065</t>
+          <t>673</t>
         </is>
       </c>
       <c r="AF23" t="inlineStr">
@@ -10080,57 +10080,57 @@
       </c>
       <c r="AH23" t="inlineStr">
         <is>
-          <t>-1.31</t>
+          <t>-1.21</t>
         </is>
       </c>
       <c r="AI23" t="inlineStr">
         <is>
-          <t>-1.66</t>
+          <t>-1.92</t>
         </is>
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>-3.77</t>
+          <t>-3.88</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
         <is>
-          <t>0.79</t>
+          <t>0.53</t>
         </is>
       </c>
       <c r="AL23" t="inlineStr">
         <is>
-          <t>39.77</t>
+          <t>39.53</t>
         </is>
       </c>
       <c r="AM23" t="inlineStr">
         <is>
-          <t>40.44</t>
+          <t>40.3</t>
         </is>
       </c>
       <c r="AN23" t="inlineStr">
         <is>
-          <t>42.03</t>
+          <t>41.93</t>
         </is>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>41.7</t>
+          <t>41.71</t>
         </is>
       </c>
       <c r="AP23" t="inlineStr">
         <is>
-          <t>-10.59</t>
+          <t>-14.13</t>
         </is>
       </c>
       <c r="AQ23" t="inlineStr">
         <is>
-          <t>-0.61</t>
+          <t>-0.66</t>
         </is>
       </c>
       <c r="AR23" t="inlineStr">
         <is>
-          <t>-0.55</t>
+          <t>-0.57</t>
         </is>
       </c>
       <c r="AS23" t="inlineStr">
@@ -10140,7 +10140,7 @@
       </c>
       <c r="AT23" t="inlineStr">
         <is>
-          <t>-120.63</t>
+          <t>-121.38</t>
         </is>
       </c>
       <c r="AU23" t="inlineStr">
@@ -10150,41 +10150,41 @@
       </c>
       <c r="AV23" t="inlineStr">
         <is>
-          <t>150978598.7687861</t>
+          <t>150814334.482684</t>
         </is>
       </c>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>20453719.0</t>
+          <t>13358411.0</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>22489497.2</t>
+          <t>21476259.0</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr">
         <is>
-          <t>21722221.3</t>
+          <t>20896470.1</t>
         </is>
       </c>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>28384455.58</t>
+          <t>28018183.18</t>
         </is>
       </c>
       <c r="BA23" t="inlineStr">
         <is>
-          <t>767275</t>
+          <t>579788</t>
         </is>
       </c>
       <c r="BB23" t="inlineStr">
         <is>
-          <t>-1092637.296673307</t>
+          <t>-1316726.695178018</t>
         </is>
       </c>
       <c r="BC23" t="n">
-        <v>-2067197.58</v>
+        <v>-2549218.39</v>
       </c>
       <c r="BD23" t="inlineStr">
         <is>
@@ -10203,7 +10203,7 @@
       </c>
       <c r="BG23" t="inlineStr">
         <is>
-          <t>-5.42</t>
+          <t>-5.90</t>
         </is>
       </c>
       <c r="BH23" t="inlineStr">
@@ -10258,12 +10258,12 @@
       </c>
       <c r="BR23" t="inlineStr">
         <is>
-          <t>1.08</t>
+          <t>1.07</t>
         </is>
       </c>
       <c r="BS23" t="inlineStr">
         <is>
-          <t>6.77</t>
+          <t>6.8</t>
         </is>
       </c>
       <c r="BT23" t="inlineStr">
@@ -10273,7 +10273,7 @@
       </c>
       <c r="BU23" t="inlineStr">
         <is>
-          <t>15.27</t>
+          <t>15.19</t>
         </is>
       </c>
       <c r="BV23" t="inlineStr">
@@ -10288,12 +10288,12 @@
       </c>
       <c r="BX23" t="inlineStr">
         <is>
-          <t>28.92</t>
+          <t>28.65</t>
         </is>
       </c>
       <c r="BY23" t="inlineStr">
         <is>
-          <t>11866</t>
+          <t>11802</t>
         </is>
       </c>
       <c r="BZ23" t="inlineStr">
@@ -10313,22 +10313,22 @@
       </c>
       <c r="CC23" t="inlineStr">
         <is>
-          <t>39.7</t>
+          <t>39.2</t>
         </is>
       </c>
       <c r="CD23" t="inlineStr">
         <is>
-          <t>39.7</t>
+          <t>39.6</t>
         </is>
       </c>
       <c r="CE23" t="inlineStr">
         <is>
-          <t>39.25</t>
+          <t>39.05</t>
         </is>
       </c>
       <c r="CF23" t="inlineStr">
         <is>
-          <t>39.25</t>
+          <t>39.05</t>
         </is>
       </c>
       <c r="CG23" t="inlineStr">

--- a/Result/checksun_type/塔架.xlsx
+++ b/Result/checksun_type/塔架.xlsx
@@ -878,12 +878,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>-2.26</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2844.986</t>
+          <t>1712.06</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -908,12 +908,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-2.63</t>
+          <t>-3.39</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>48.25</t>
+          <t>50.94</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -988,17 +988,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>11.77</t>
+          <t>7.08</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>-2.29</t>
+          <t>-1.14</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1009,12 +1009,12 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>2845</t>
+          <t>1712</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
@@ -1029,57 +1029,57 @@
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>-6.85</t>
+          <t>-4.26</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>-7.30</t>
+          <t>-8.89</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>-7.05</t>
+          <t>-7.5</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>-5.89</t>
+          <t>-5.97</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>140.1</t>
+          <t>136.3</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>151.12</t>
+          <t>149.6</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>162.59</t>
+          <t>161.73</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>172.77</t>
+          <t>171.99</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>-28.43</t>
+          <t>-28.35</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>-7.75</t>
+          <t>-8.34</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>-6.04</t>
+          <t>-6.50</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -1089,7 +1089,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-124.26</t>
+          <t>-126.11</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1099,41 +1099,41 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>1701137811.822511</t>
+          <t>1699170206.954611</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>373359683.0</t>
+          <t>223746689.0</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>374444824.4</t>
+          <t>397436778.6</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>252575891.8</t>
+          <t>263301806.5</t>
         </is>
       </c>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>255257682.72</t>
+          <t>254911229.58</t>
         </is>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>121868932</t>
+          <t>134134972</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>3068692.09532273</t>
+          <t>6892793.183689982</t>
         </is>
       </c>
       <c r="BC2" t="n">
-        <v>40950935.06</v>
+        <v>27925349.17</v>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
@@ -1177,7 +1177,7 @@
       </c>
       <c r="BL2" t="inlineStr">
         <is>
-          <t>0.98</t>
+          <t>0.99</t>
         </is>
       </c>
       <c r="BM2" t="inlineStr">
@@ -1197,12 +1197,12 @@
       </c>
       <c r="BP2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價漲量縮</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
@@ -1237,7 +1237,7 @@
       </c>
       <c r="BX2" t="inlineStr">
         <is>
-          <t>28.65</t>
+          <t>28.46</t>
         </is>
       </c>
       <c r="BY2" t="inlineStr">
@@ -1262,17 +1262,17 @@
       </c>
       <c r="CC2" t="inlineStr">
         <is>
-          <t>133.0</t>
+          <t>131.0</t>
         </is>
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>134.5</t>
+          <t>133.5</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>129.5</t>
+          <t>129.0</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
@@ -1309,12 +1309,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>-2.96</t>
+          <t>-2.26</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>4003.393</t>
+          <t>2844.986</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1324,7 +1324,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>133.5</t>
+          <t>130.5</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1334,17 +1334,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-2.3</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-2.63</t>
+          <t>-3.39</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>36.89</t>
+          <t>48.25</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1409,7 +1409,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-43.67</t>
+          <t>-44.94</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1419,17 +1419,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>16.56</t>
+          <t>11.77</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>-5.24</t>
+          <t>-2.29</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1440,12 +1440,12 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>2845</t>
+          <t>1712</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
@@ -1460,57 +1460,57 @@
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>-7.23</t>
+          <t>-6.85</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>-5.73</t>
+          <t>-7.30</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-6.6</t>
+          <t>-7.05</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>-5.82</t>
+          <t>-5.89</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>143.9</t>
+          <t>140.1</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>152.65</t>
+          <t>151.12</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>163.44</t>
+          <t>162.59</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>173.54</t>
+          <t>172.77</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>-22.90</t>
+          <t>-28.43</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>-6.89</t>
+          <t>-7.75</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>-5.61</t>
+          <t>-6.04</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1520,7 +1520,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-122.53</t>
+          <t>-124.26</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1530,41 +1530,41 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>1701137811.822511</t>
+          <t>1699170206.954611</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>543328425.0</t>
+          <t>373359683.0</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>317370279.0</t>
+          <t>374444824.4</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>231842549.9</t>
+          <t>252575891.8</t>
         </is>
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>254515985.98</t>
+          <t>255257682.72</t>
         </is>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>85527729</t>
+          <t>121868932</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>-3818988.443072045</t>
+          <t>3068692.09532273</t>
         </is>
       </c>
       <c r="BC3" t="n">
-        <v>42066417.86</v>
+        <v>40950935.06</v>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
@@ -1583,7 +1583,7 @@
       </c>
       <c r="BG3" t="inlineStr">
         <is>
-          <t>-25.83</t>
+          <t>-27.50</t>
         </is>
       </c>
       <c r="BH3" t="inlineStr">
@@ -1608,7 +1608,7 @@
       </c>
       <c r="BL3" t="inlineStr">
         <is>
-          <t>0.98</t>
+          <t>0.99</t>
         </is>
       </c>
       <c r="BM3" t="inlineStr">
@@ -1628,7 +1628,7 @@
       </c>
       <c r="BP3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;衝高回落,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BQ3" t="inlineStr">
@@ -1638,7 +1638,7 @@
       </c>
       <c r="BR3" t="inlineStr">
         <is>
-          <t>3.08</t>
+          <t>3.01</t>
         </is>
       </c>
       <c r="BS3" t="inlineStr">
@@ -1668,7 +1668,7 @@
       </c>
       <c r="BX3" t="inlineStr">
         <is>
-          <t>28.65</t>
+          <t>28.46</t>
         </is>
       </c>
       <c r="BY3" t="inlineStr">
@@ -1693,22 +1693,22 @@
       </c>
       <c r="CC3" t="inlineStr">
         <is>
-          <t>135.0</t>
+          <t>133.0</t>
         </is>
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>141.5</t>
+          <t>134.5</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>132.5</t>
+          <t>129.5</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>133.5</t>
+          <t>130.5</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
@@ -1740,12 +1740,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>-8.16</t>
+          <t>-2.96</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>5388.546</t>
+          <t>4003.393</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1755,7 +1755,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>137.5</t>
+          <t>133.5</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1765,17 +1765,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-5.36</t>
+          <t>-2.3</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-2.63</t>
+          <t>-3.39</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>18.56</t>
+          <t>36.89</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1840,7 +1840,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-41.98</t>
+          <t>-43.67</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1850,17 +1850,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>22.28</t>
+          <t>16.56</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>-5.06</t>
+          <t>-5.24</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1871,12 +1871,12 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>2845</t>
+          <t>1712</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
@@ -1891,57 +1891,57 @@
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>-6.59</t>
+          <t>-7.23</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>-4.57</t>
+          <t>-5.73</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>-6.11</t>
+          <t>-6.6</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>-5.70</t>
+          <t>-5.82</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>147.2</t>
+          <t>143.9</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>154.25</t>
+          <t>152.65</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>164.29</t>
+          <t>163.44</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>174.21</t>
+          <t>173.54</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>-13.45</t>
+          <t>-22.90</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>-6.00</t>
+          <t>-6.89</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>-5.29</t>
+          <t>-5.61</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1951,7 +1951,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-121.24</t>
+          <t>-122.53</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1961,41 +1961,41 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>1701137811.822511</t>
+          <t>1699170206.954611</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>753939618.0</t>
+          <t>543328425.0</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>239835367.0</t>
+          <t>317370279.0</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>202283159.5</t>
+          <t>231842549.9</t>
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>250790390.86</t>
+          <t>254515985.98</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>37552207</t>
+          <t>85527729</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>-12161789.58854426</t>
+          <t>-3818988.443072045</t>
         </is>
       </c>
       <c r="BC4" t="n">
-        <v>23946656.01</v>
+        <v>42066417.86</v>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
@@ -2014,7 +2014,7 @@
       </c>
       <c r="BG4" t="inlineStr">
         <is>
-          <t>-23.61</t>
+          <t>-25.83</t>
         </is>
       </c>
       <c r="BH4" t="inlineStr">
@@ -2039,7 +2039,7 @@
       </c>
       <c r="BL4" t="inlineStr">
         <is>
-          <t>0.98</t>
+          <t>0.99</t>
         </is>
       </c>
       <c r="BM4" t="inlineStr">
@@ -2059,17 +2059,17 @@
       </c>
       <c r="BP4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;衝高回落,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>價跌量增</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
         <is>
-          <t>3.17</t>
+          <t>3.08</t>
         </is>
       </c>
       <c r="BS4" t="inlineStr">
@@ -2099,7 +2099,7 @@
       </c>
       <c r="BX4" t="inlineStr">
         <is>
-          <t>28.65</t>
+          <t>28.46</t>
         </is>
       </c>
       <c r="BY4" t="inlineStr">
@@ -2124,22 +2124,22 @@
       </c>
       <c r="CC4" t="inlineStr">
         <is>
-          <t>147.0</t>
+          <t>135.0</t>
         </is>
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>147.0</t>
+          <t>141.5</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>135.0</t>
+          <t>132.5</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>137.5</t>
+          <t>133.5</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
@@ -2171,12 +2171,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-8.16</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>617.888</t>
+          <t>5388.546</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2186,7 +2186,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>149.5</t>
+          <t>137.5</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2196,17 +2196,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-14.56</t>
+          <t>-5.36</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-2.63</t>
+          <t>-3.39</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>-14.19</t>
+          <t>18.56</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-36.92</t>
+          <t>-41.98</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2281,17 +2281,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>2.56</t>
+          <t>22.28</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>-1.34</t>
+          <t>-5.06</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2302,12 +2302,12 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>2845</t>
+          <t>1712</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
@@ -2322,57 +2322,57 @@
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>-0.07</t>
+          <t>-6.59</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>-3.96</t>
+          <t>-4.57</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>-5.65</t>
+          <t>-6.11</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>-5.63</t>
+          <t>-5.70</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>149.6</t>
+          <t>147.2</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>155.78</t>
+          <t>154.25</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>165.1</t>
+          <t>164.29</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>174.95</t>
+          <t>174.21</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>-1.33</t>
+          <t>-13.45</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>-5.18</t>
+          <t>-6.00</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>-5.11</t>
+          <t>-5.29</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-120.53</t>
+          <t>-121.24</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2392,41 +2392,41 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>1701137811.822511</t>
+          <t>1699170206.954611</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>92809478.0</t>
+          <t>753939618.0</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>127850905.8</t>
+          <t>239835367.0</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>148995940.1</t>
+          <t>202283159.5</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>248204610.78</t>
+          <t>250790390.86</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>-21145034</t>
+          <t>37552207</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>-18726961.5147791</t>
+          <t>-12161789.58854426</t>
         </is>
       </c>
       <c r="BC5" t="n">
-        <v>-25359440.75</v>
+        <v>23946656.01</v>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
@@ -2445,7 +2445,7 @@
       </c>
       <c r="BG5" t="inlineStr">
         <is>
-          <t>-16.94</t>
+          <t>-23.61</t>
         </is>
       </c>
       <c r="BH5" t="inlineStr">
@@ -2470,7 +2470,7 @@
       </c>
       <c r="BL5" t="inlineStr">
         <is>
-          <t>0.98</t>
+          <t>0.99</t>
         </is>
       </c>
       <c r="BM5" t="inlineStr">
@@ -2495,12 +2495,12 @@
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價跌量增</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
         <is>
-          <t>3.44</t>
+          <t>3.17</t>
         </is>
       </c>
       <c r="BS5" t="inlineStr">
@@ -2530,7 +2530,7 @@
       </c>
       <c r="BX5" t="inlineStr">
         <is>
-          <t>28.65</t>
+          <t>28.46</t>
         </is>
       </c>
       <c r="BY5" t="inlineStr">
@@ -2555,22 +2555,22 @@
       </c>
       <c r="CC5" t="inlineStr">
         <is>
-          <t>150.0</t>
+          <t>147.0</t>
         </is>
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>151.5</t>
+          <t>147.0</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>149.5</t>
+          <t>135.0</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>149.5</t>
+          <t>137.5</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
@@ -2607,7 +2607,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>723.545</t>
+          <t>617.888</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2632,12 +2632,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-2.63</t>
+          <t>-3.39</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>-23.11</t>
+          <t>-14.19</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2712,17 +2712,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>2.99</t>
+          <t>2.56</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>-1.67</t>
+          <t>-1.34</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2733,12 +2733,12 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>2845</t>
+          <t>1712</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
@@ -2748,62 +2748,62 @@
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>2.22</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>-0.47</t>
+          <t>-0.07</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>-4.07</t>
+          <t>-3.96</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>-5.55</t>
+          <t>-5.65</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>-5.58</t>
+          <t>-5.63</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>150.2</t>
+          <t>149.6</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>156.57</t>
+          <t>155.78</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>165.78</t>
+          <t>165.1</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>175.58</t>
+          <t>174.95</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>-3.60</t>
+          <t>-1.33</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>-5.28</t>
+          <t>-5.18</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>-5.09</t>
+          <t>-5.11</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -2813,7 +2813,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-120.46</t>
+          <t>-120.53</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2823,41 +2823,41 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>1701137811.822511</t>
+          <t>1699170206.954611</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>108786918.0</t>
+          <t>92809478.0</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>129166834.4</t>
+          <t>127850905.8</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>167987433.4</t>
+          <t>148995940.1</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>261232164.76</t>
+          <t>248204610.78</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>-38820599</t>
+          <t>-21145034</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>-17521056.19996015</t>
+          <t>-18726961.5147791</t>
         </is>
       </c>
       <c r="BC6" t="n">
-        <v>-24055655.37</v>
+        <v>-25359440.75</v>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
@@ -2901,7 +2901,7 @@
       </c>
       <c r="BL6" t="inlineStr">
         <is>
-          <t>0.98</t>
+          <t>0.99</t>
         </is>
       </c>
       <c r="BM6" t="inlineStr">
@@ -2921,7 +2921,7 @@
       </c>
       <c r="BP6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ6" t="inlineStr">
@@ -2961,7 +2961,7 @@
       </c>
       <c r="BX6" t="inlineStr">
         <is>
-          <t>28.65</t>
+          <t>28.46</t>
         </is>
       </c>
       <c r="BY6" t="inlineStr">
@@ -2986,17 +2986,17 @@
       </c>
       <c r="CC6" t="inlineStr">
         <is>
+          <t>150.0</t>
+        </is>
+      </c>
+      <c r="CD6" t="inlineStr">
+        <is>
           <t>151.5</t>
         </is>
       </c>
-      <c r="CD6" t="inlineStr">
-        <is>
-          <t>152.5</t>
-        </is>
-      </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>149.0</t>
+          <t>149.5</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
@@ -3033,12 +3033,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>-0.33</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>586.018</t>
+          <t>723.545</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3063,12 +3063,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-2.63</t>
+          <t>-3.39</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>-28.30</t>
+          <t>-23.11</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3143,17 +3143,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>2.42</t>
+          <t>2.99</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>-1.34</t>
+          <t>-1.67</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3164,12 +3164,12 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>2845</t>
+          <t>1712</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
@@ -3184,57 +3184,57 @@
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>-0.86</t>
+          <t>-0.47</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>-4.25</t>
+          <t>-4.07</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>-5.43</t>
+          <t>-5.55</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>-5.49</t>
+          <t>-5.58</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>150.8</t>
+          <t>150.2</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>157.5</t>
+          <t>156.57</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>166.55</t>
+          <t>165.78</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>176.23</t>
+          <t>175.58</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>-5.51</t>
+          <t>-3.60</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>-5.32</t>
+          <t>-5.28</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>-5.05</t>
+          <t>-5.09</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -3244,7 +3244,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-120.28</t>
+          <t>-120.46</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3254,41 +3254,41 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>1701137811.822511</t>
+          <t>1699170206.954611</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>87986956.0</t>
+          <t>108786918.0</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>130706959.2</t>
+          <t>129166834.4</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>182292868.5</t>
+          <t>167987433.4</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>265109106.98</t>
+          <t>261232164.76</t>
         </is>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>-51585909</t>
+          <t>-38820599</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>-16332947.26079137</t>
+          <t>-17521056.19996015</t>
         </is>
       </c>
       <c r="BC7" t="n">
-        <v>-23045842.84</v>
+        <v>-24055655.37</v>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
@@ -3332,7 +3332,7 @@
       </c>
       <c r="BL7" t="inlineStr">
         <is>
-          <t>0.98</t>
+          <t>0.99</t>
         </is>
       </c>
       <c r="BM7" t="inlineStr">
@@ -3352,7 +3352,7 @@
       </c>
       <c r="BP7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ7" t="inlineStr">
@@ -3392,7 +3392,7 @@
       </c>
       <c r="BX7" t="inlineStr">
         <is>
-          <t>28.65</t>
+          <t>28.46</t>
         </is>
       </c>
       <c r="BY7" t="inlineStr">
@@ -3422,12 +3422,12 @@
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>151.5</t>
+          <t>152.5</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>149.5</t>
+          <t>149.0</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
@@ -3464,12 +3464,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>0.33</t>
+          <t>-0.33</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>1040.36</t>
+          <t>586.018</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3479,7 +3479,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>150.0</t>
+          <t>149.5</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3489,17 +3489,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-14.94</t>
+          <t>-14.56</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-2.63</t>
+          <t>-3.39</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>-24.53</t>
+          <t>-28.30</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3564,7 +3564,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-36.71</t>
+          <t>-36.92</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3574,17 +3574,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>4.30</t>
+          <t>2.42</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>1.39</t>
+          <t>-1.34</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3595,17 +3595,17 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>2845</t>
+          <t>1712</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>6.67</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
@@ -3615,57 +3615,57 @@
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>-1.12</t>
+          <t>-0.86</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>-4.31</t>
+          <t>-4.25</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>-5.31</t>
+          <t>-5.43</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>-5.34</t>
+          <t>-5.49</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>151.7</t>
+          <t>150.8</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>158.52</t>
+          <t>157.5</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>167.41</t>
+          <t>166.55</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>176.86</t>
+          <t>176.23</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>-6.68</t>
+          <t>-5.51</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>-5.31</t>
+          <t>-5.32</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>-4.98</t>
+          <t>-5.05</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -3675,7 +3675,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-120.00</t>
+          <t>-120.28</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3685,41 +3685,41 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>1701137811.822511</t>
+          <t>1699170206.954611</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>155653865.0</t>
+          <t>87986956.0</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>146314820.8</t>
+          <t>130706959.2</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>193869307.6</t>
+          <t>182292868.5</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>274342437.92</t>
+          <t>265109106.98</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>-47554486</t>
+          <t>-51585909</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>-15112420.79113203</t>
+          <t>-16332947.26079137</t>
         </is>
       </c>
       <c r="BC8" t="n">
-        <v>-18551620.35</v>
+        <v>-23045842.84</v>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
@@ -3738,7 +3738,7 @@
       </c>
       <c r="BG8" t="inlineStr">
         <is>
-          <t>-16.67</t>
+          <t>-16.94</t>
         </is>
       </c>
       <c r="BH8" t="inlineStr">
@@ -3763,7 +3763,7 @@
       </c>
       <c r="BL8" t="inlineStr">
         <is>
-          <t>0.98</t>
+          <t>0.99</t>
         </is>
       </c>
       <c r="BM8" t="inlineStr">
@@ -3783,7 +3783,7 @@
       </c>
       <c r="BP8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;可能出現反轉訊號&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;3&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ8" t="inlineStr">
@@ -3793,7 +3793,7 @@
       </c>
       <c r="BR8" t="inlineStr">
         <is>
-          <t>3.46</t>
+          <t>3.44</t>
         </is>
       </c>
       <c r="BS8" t="inlineStr">
@@ -3823,7 +3823,7 @@
       </c>
       <c r="BX8" t="inlineStr">
         <is>
-          <t>28.65</t>
+          <t>28.46</t>
         </is>
       </c>
       <c r="BY8" t="inlineStr">
@@ -3848,7 +3848,7 @@
       </c>
       <c r="CC8" t="inlineStr">
         <is>
-          <t>150.5</t>
+          <t>151.5</t>
         </is>
       </c>
       <c r="CD8" t="inlineStr">
@@ -3858,12 +3858,12 @@
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>146.5</t>
+          <t>149.5</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>150.0</t>
+          <t>149.5</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
@@ -3895,12 +3895,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>-1.97</t>
+          <t>0.33</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>1294.619</t>
+          <t>1040.36</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3910,7 +3910,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>149.5</t>
+          <t>150.0</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3920,17 +3920,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-14.56</t>
+          <t>-14.94</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-2.63</t>
+          <t>-3.39</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>-16.90</t>
+          <t>-24.53</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3995,7 +3995,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-36.92</t>
+          <t>-36.71</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4005,17 +4005,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>5.35</t>
+          <t>4.30</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>-1.00</t>
+          <t>1.39</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4026,77 +4026,77 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>2845</t>
+          <t>1712</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>6.67</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>2.22</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>-2.35</t>
+          <t>-1.12</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>-3.97</t>
+          <t>-4.31</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>-5.19</t>
+          <t>-5.31</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>-5.28</t>
+          <t>-5.34</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>153.1</t>
+          <t>151.7</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>159.43</t>
+          <t>158.52</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>168.15</t>
+          <t>167.41</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>177.52</t>
+          <t>176.86</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>-7.56</t>
+          <t>-6.68</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>-5.26</t>
+          <t>-5.31</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>-4.89</t>
+          <t>-4.98</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -4106,7 +4106,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-119.66</t>
+          <t>-120.00</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4116,41 +4116,41 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>1701137811.822511</t>
+          <t>1699170206.954611</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>194017312.0</t>
+          <t>155653865.0</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>164730952.0</t>
+          <t>146314820.8</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>198237890.5</t>
+          <t>193869307.6</t>
         </is>
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>287305576.32</t>
+          <t>274342437.92</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>-33506938</t>
+          <t>-47554486</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>-14487111.77960444</t>
+          <t>-15112420.79113203</t>
         </is>
       </c>
       <c r="BC9" t="n">
-        <v>-18718770.61</v>
+        <v>-18551620.35</v>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
@@ -4169,7 +4169,7 @@
       </c>
       <c r="BG9" t="inlineStr">
         <is>
-          <t>-16.94</t>
+          <t>-16.67</t>
         </is>
       </c>
       <c r="BH9" t="inlineStr">
@@ -4194,7 +4194,7 @@
       </c>
       <c r="BL9" t="inlineStr">
         <is>
-          <t>0.98</t>
+          <t>0.99</t>
         </is>
       </c>
       <c r="BM9" t="inlineStr">
@@ -4214,7 +4214,7 @@
       </c>
       <c r="BP9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;可能出現反轉訊號&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;3&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ9" t="inlineStr">
@@ -4224,7 +4224,7 @@
       </c>
       <c r="BR9" t="inlineStr">
         <is>
-          <t>3.44</t>
+          <t>3.46</t>
         </is>
       </c>
       <c r="BS9" t="inlineStr">
@@ -4254,7 +4254,7 @@
       </c>
       <c r="BX9" t="inlineStr">
         <is>
-          <t>28.65</t>
+          <t>28.46</t>
         </is>
       </c>
       <c r="BY9" t="inlineStr">
@@ -4279,22 +4279,22 @@
       </c>
       <c r="CC9" t="inlineStr">
         <is>
-          <t>152.0</t>
+          <t>150.5</t>
         </is>
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>152.0</t>
+          <t>151.5</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>148.5</t>
+          <t>146.5</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>149.5</t>
+          <t>150.0</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
@@ -4326,12 +4326,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-1.97</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>653.151</t>
+          <t>1294.619</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4341,7 +4341,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>152.5</t>
+          <t>149.5</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4351,17 +4351,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-16.86</t>
+          <t>-14.56</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-2.63</t>
+          <t>-3.39</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>-18.28</t>
+          <t>-16.90</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4426,7 +4426,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-35.65</t>
+          <t>-36.92</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4436,17 +4436,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-06</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>2.70</t>
+          <t>5.35</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>-0.32</t>
+          <t>-1.00</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4457,12 +4457,12 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>2845</t>
+          <t>1712</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
@@ -4472,62 +4472,62 @@
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>2.38</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>-0.91</t>
+          <t>-2.35</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>-4.07</t>
+          <t>-3.97</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>-5.07</t>
+          <t>-5.19</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>-5.19</t>
+          <t>-5.28</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>153.9</t>
+          <t>153.1</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>160.43</t>
+          <t>159.43</t>
         </is>
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>169.0</t>
+          <t>168.15</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>178.25</t>
+          <t>177.52</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>-5.77</t>
+          <t>-7.56</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>-5.08</t>
+          <t>-5.26</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>-4.80</t>
+          <t>-4.89</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -4537,7 +4537,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-119.29</t>
+          <t>-119.66</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4547,41 +4547,41 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>1701137811.822511</t>
+          <t>1699170206.954611</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>99389121.0</t>
+          <t>194017312.0</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>170140974.4</t>
+          <t>164730952.0</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>208211819.2</t>
+          <t>198237890.5</t>
         </is>
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>301691507.7</t>
+          <t>287305576.32</t>
         </is>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>-38070844</t>
+          <t>-33506938</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>-13717719.26552568</t>
+          <t>-14487111.77960444</t>
         </is>
       </c>
       <c r="BC10" t="n">
-        <v>-22399398.48</v>
+        <v>-18718770.61</v>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
@@ -4600,7 +4600,7 @@
       </c>
       <c r="BG10" t="inlineStr">
         <is>
-          <t>-15.28</t>
+          <t>-16.94</t>
         </is>
       </c>
       <c r="BH10" t="inlineStr">
@@ -4625,7 +4625,7 @@
       </c>
       <c r="BL10" t="inlineStr">
         <is>
-          <t>0.98</t>
+          <t>0.99</t>
         </is>
       </c>
       <c r="BM10" t="inlineStr">
@@ -4645,7 +4645,7 @@
       </c>
       <c r="BP10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ10" t="inlineStr">
@@ -4655,7 +4655,7 @@
       </c>
       <c r="BR10" t="inlineStr">
         <is>
-          <t>3.51</t>
+          <t>3.44</t>
         </is>
       </c>
       <c r="BS10" t="inlineStr">
@@ -4685,7 +4685,7 @@
       </c>
       <c r="BX10" t="inlineStr">
         <is>
-          <t>28.65</t>
+          <t>28.46</t>
         </is>
       </c>
       <c r="BY10" t="inlineStr">
@@ -4710,22 +4710,22 @@
       </c>
       <c r="CC10" t="inlineStr">
         <is>
-          <t>154.0</t>
+          <t>152.0</t>
         </is>
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>154.5</t>
+          <t>152.0</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>151.0</t>
+          <t>148.5</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>152.5</t>
+          <t>149.5</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
@@ -4757,12 +4757,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>-0.98</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>767.34</t>
+          <t>653.151</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4787,12 +4787,12 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-2.63</t>
+          <t>-3.39</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>-2.01</t>
+          <t>-18.28</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4867,17 +4867,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-05</t>
+          <t>2025-11-06</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>3.17</t>
+          <t>2.70</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>0.35</t>
+          <t>-0.32</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4888,12 +4888,12 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>2845</t>
+          <t>1712</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
@@ -4903,62 +4903,62 @@
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>17.94</t>
+          <t>2.38</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>-1.17</t>
+          <t>-0.91</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>-4.49</t>
+          <t>-4.07</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>-4.9</t>
+          <t>-5.07</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>-5.05</t>
+          <t>-5.19</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>154.3</t>
+          <t>153.9</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>161.55</t>
+          <t>160.43</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>169.88</t>
+          <t>169.0</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>178.91</t>
+          <t>178.25</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>-7.21</t>
+          <t>-5.77</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>-5.07</t>
+          <t>-5.08</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>-4.73</t>
+          <t>-4.80</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -4968,7 +4968,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-119.01</t>
+          <t>-119.29</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -4978,41 +4978,41 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>1701137811.822511</t>
+          <t>1699170206.954611</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>116487542.0</t>
+          <t>99389121.0</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>206808032.4</t>
+          <t>170140974.4</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>211045311.6</t>
+          <t>208211819.2</t>
         </is>
       </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>314221303.24</t>
+          <t>301691507.7</t>
         </is>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>-4237279</t>
+          <t>-38070844</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>-12139232.13529545</t>
+          <t>-13717719.26552568</t>
         </is>
       </c>
       <c r="BC11" t="n">
-        <v>-16718725.04</v>
+        <v>-22399398.48</v>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
@@ -5056,7 +5056,7 @@
       </c>
       <c r="BL11" t="inlineStr">
         <is>
-          <t>0.98</t>
+          <t>0.99</t>
         </is>
       </c>
       <c r="BM11" t="inlineStr">
@@ -5076,7 +5076,7 @@
       </c>
       <c r="BP11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ11" t="inlineStr">
@@ -5116,7 +5116,7 @@
       </c>
       <c r="BX11" t="inlineStr">
         <is>
-          <t>28.65</t>
+          <t>28.46</t>
         </is>
       </c>
       <c r="BY11" t="inlineStr">
@@ -5141,17 +5141,17 @@
       </c>
       <c r="CC11" t="inlineStr">
         <is>
-          <t>153.0</t>
+          <t>154.0</t>
         </is>
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>154.0</t>
+          <t>154.5</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>150.5</t>
+          <t>151.0</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
@@ -5188,12 +5188,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>-1.9</t>
+          <t>-0.98</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>1062.556</t>
+          <t>767.34</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5203,7 +5203,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>154.0</t>
+          <t>152.5</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5213,17 +5213,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-18.01</t>
+          <t>-16.86</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-2.63</t>
+          <t>-3.39</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>8.13</t>
+          <t>-2.01</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5288,7 +5288,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-35.02</t>
+          <t>-35.65</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5298,17 +5298,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-04</t>
+          <t>2025-11-05</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>4.39</t>
+          <t>3.17</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>-2.92</t>
+          <t>0.35</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5319,17 +5319,17 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>2845</t>
+          <t>1712</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>7.14</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
@@ -5339,57 +5339,57 @@
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>-0.58</t>
+          <t>-1.17</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>-4.59</t>
+          <t>-4.49</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>-4.89</t>
+          <t>-4.9</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>-4.93</t>
+          <t>-5.05</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>154.9</t>
+          <t>154.3</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>162.35</t>
+          <t>161.55</t>
         </is>
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>170.7</t>
+          <t>169.88</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>179.54</t>
+          <t>178.91</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>-7.45</t>
+          <t>-7.21</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>-4.99</t>
+          <t>-5.07</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>-4.65</t>
+          <t>-4.73</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
@@ -5399,7 +5399,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-118.67</t>
+          <t>-119.01</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5409,41 +5409,41 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>1701137811.822511</t>
+          <t>1699170206.954611</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>166026264.0</t>
+          <t>116487542.0</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>233878777.8</t>
+          <t>206808032.4</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>216301717.4</t>
+          <t>211045311.6</t>
         </is>
       </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>327913288.88</t>
+          <t>314221303.24</t>
         </is>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>17577060</t>
+          <t>-4237279</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>-11306597.06250142</t>
+          <t>-12139232.13529545</t>
         </is>
       </c>
       <c r="BC12" t="n">
-        <v>-9838353.609999999</v>
+        <v>-16718725.04</v>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
@@ -5462,7 +5462,7 @@
       </c>
       <c r="BG12" t="inlineStr">
         <is>
-          <t>-14.44</t>
+          <t>-15.28</t>
         </is>
       </c>
       <c r="BH12" t="inlineStr">
@@ -5487,7 +5487,7 @@
       </c>
       <c r="BL12" t="inlineStr">
         <is>
-          <t>0.98</t>
+          <t>0.99</t>
         </is>
       </c>
       <c r="BM12" t="inlineStr">
@@ -5507,7 +5507,7 @@
       </c>
       <c r="BP12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ12" t="inlineStr">
@@ -5517,7 +5517,7 @@
       </c>
       <c r="BR12" t="inlineStr">
         <is>
-          <t>3.55</t>
+          <t>3.51</t>
         </is>
       </c>
       <c r="BS12" t="inlineStr">
@@ -5547,7 +5547,7 @@
       </c>
       <c r="BX12" t="inlineStr">
         <is>
-          <t>28.65</t>
+          <t>28.46</t>
         </is>
       </c>
       <c r="BY12" t="inlineStr">
@@ -5572,22 +5572,22 @@
       </c>
       <c r="CC12" t="inlineStr">
         <is>
-          <t>157.5</t>
+          <t>153.0</t>
         </is>
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>158.5</t>
+          <t>154.0</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>154.0</t>
+          <t>150.5</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>154.0</t>
+          <t>152.5</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
@@ -5619,12 +5619,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>-0.54</t>
+          <t>-1.76</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>672.504</t>
+          <t>1212.053</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -5634,7 +5634,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>36.75</t>
+          <t>36.1</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -5649,12 +5649,12 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>-1.79</t>
+          <t>-0.53</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>-2.04</t>
+          <t>3.03</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -5719,7 +5719,7 @@
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>-14.83</t>
+          <t>-16.34</t>
         </is>
       </c>
       <c r="X13" t="inlineStr">
@@ -5729,17 +5729,17 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>7.17</t>
+          <t>12.91</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>-1.09</t>
+          <t>-1.38</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
@@ -5750,12 +5750,12 @@
       <c r="AC13" t="inlineStr"/>
       <c r="AD13" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>11</t>
         </is>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
-          <t>673</t>
+          <t>1212</t>
         </is>
       </c>
       <c r="AF13" t="inlineStr">
@@ -5770,57 +5770,57 @@
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>-1.92</t>
+          <t>-2.62</t>
         </is>
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>-3.97</t>
+          <t>-4.47</t>
         </is>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>-4.25</t>
+          <t>-4.38</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>-1.83</t>
+          <t>-2.09</t>
         </is>
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>37.47000000000001</t>
+          <t>37.07000000000001</t>
         </is>
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>39.02</t>
+          <t>38.8</t>
         </is>
       </c>
       <c r="AN13" t="inlineStr">
         <is>
-          <t>40.75</t>
+          <t>40.58</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>41.51</t>
+          <t>41.45</t>
         </is>
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>-19.33</t>
+          <t>-22.07</t>
         </is>
       </c>
       <c r="AQ13" t="inlineStr">
         <is>
-          <t>-1.03</t>
+          <t>-1.12</t>
         </is>
       </c>
       <c r="AR13" t="inlineStr">
         <is>
-          <t>-0.86</t>
+          <t>-0.91</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr">
@@ -5830,7 +5830,7 @@
       </c>
       <c r="AT13" t="inlineStr">
         <is>
-          <t>-132.14</t>
+          <t>-134.02</t>
         </is>
       </c>
       <c r="AU13" t="inlineStr">
@@ -5840,41 +5840,41 @@
       </c>
       <c r="AV13" t="inlineStr">
         <is>
-          <t>150814334.482684</t>
+          <t>150691742.176513</t>
         </is>
       </c>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>24762299.0</t>
+          <t>43823516.0</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>31929308.6</t>
+          <t>36085517.8</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>32595150.7</t>
+          <t>35025550.9</t>
         </is>
       </c>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>29130934.74</t>
+          <t>29409986.0</t>
         </is>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
-          <t>-665842</t>
+          <t>1059966</t>
         </is>
       </c>
       <c r="BB13" t="inlineStr">
         <is>
-          <t>653269.0727074891</t>
+          <t>880468.5492293607</t>
         </is>
       </c>
       <c r="BC13" t="n">
-        <v>1454053.95</v>
+        <v>2130065.67</v>
       </c>
       <c r="BD13" t="inlineStr">
         <is>
@@ -5893,7 +5893,7 @@
       </c>
       <c r="BG13" t="inlineStr">
         <is>
-          <t>-11.45</t>
+          <t>-13.01</t>
         </is>
       </c>
       <c r="BH13" t="inlineStr">
@@ -5948,12 +5948,12 @@
       </c>
       <c r="BR13" t="inlineStr">
         <is>
-          <t>1.01</t>
+          <t>0.99</t>
         </is>
       </c>
       <c r="BS13" t="inlineStr">
         <is>
-          <t>6.8</t>
+          <t>6.93</t>
         </is>
       </c>
       <c r="BT13" t="inlineStr">
@@ -5963,7 +5963,7 @@
       </c>
       <c r="BU13" t="inlineStr">
         <is>
-          <t>15.19</t>
+          <t>14.92</t>
         </is>
       </c>
       <c r="BV13" t="inlineStr">
@@ -5978,12 +5978,12 @@
       </c>
       <c r="BX13" t="inlineStr">
         <is>
-          <t>28.65</t>
+          <t>28.46</t>
         </is>
       </c>
       <c r="BY13" t="inlineStr">
         <is>
-          <t>11802</t>
+          <t>11593</t>
         </is>
       </c>
       <c r="BZ13" t="inlineStr">
@@ -6003,22 +6003,22 @@
       </c>
       <c r="CC13" t="inlineStr">
         <is>
-          <t>36.95</t>
+          <t>36.85</t>
         </is>
       </c>
       <c r="CD13" t="inlineStr">
         <is>
-          <t>37.3</t>
+          <t>36.85</t>
         </is>
       </c>
       <c r="CE13" t="inlineStr">
         <is>
-          <t>36.6</t>
+          <t>35.85</t>
         </is>
       </c>
       <c r="CF13" t="inlineStr">
         <is>
-          <t>36.75</t>
+          <t>36.1</t>
         </is>
       </c>
       <c r="CG13" t="inlineStr">
@@ -6050,12 +6050,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>-1.34</t>
+          <t>-0.54</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>1065.248</t>
+          <t>672.504</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -6065,7 +6065,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>36.95</t>
+          <t>36.75</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -6075,17 +6075,17 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>-0.54</t>
+          <t>-1.8</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>-1.79</t>
+          <t>-0.53</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>28.28</t>
+          <t>-2.04</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -6150,7 +6150,7 @@
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>-14.37</t>
+          <t>-14.83</t>
         </is>
       </c>
       <c r="X14" t="inlineStr">
@@ -6160,17 +6160,17 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>11.35</t>
+          <t>7.17</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>-0.81</t>
+          <t>-1.09</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
@@ -6181,12 +6181,12 @@
       <c r="AC14" t="inlineStr"/>
       <c r="AD14" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>11</t>
         </is>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
-          <t>673</t>
+          <t>1212</t>
         </is>
       </c>
       <c r="AF14" t="inlineStr">
@@ -6196,62 +6196,62 @@
       </c>
       <c r="AG14" t="inlineStr">
         <is>
-          <t>9.38</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>-1.86</t>
+          <t>-1.92</t>
         </is>
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>-4.02</t>
+          <t>-3.97</t>
         </is>
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>-4.09</t>
+          <t>-4.25</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>-1.60</t>
+          <t>-1.83</t>
         </is>
       </c>
       <c r="AL14" t="inlineStr">
         <is>
-          <t>37.65000000000001</t>
+          <t>37.47000000000001</t>
         </is>
       </c>
       <c r="AM14" t="inlineStr">
         <is>
-          <t>39.23</t>
+          <t>39.02</t>
         </is>
       </c>
       <c r="AN14" t="inlineStr">
         <is>
-          <t>40.9</t>
+          <t>40.75</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>41.57</t>
+          <t>41.51</t>
         </is>
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>-18.37</t>
+          <t>-19.33</t>
         </is>
       </c>
       <c r="AQ14" t="inlineStr">
         <is>
-          <t>-0.97</t>
+          <t>-1.03</t>
         </is>
       </c>
       <c r="AR14" t="inlineStr">
         <is>
-          <t>-0.82</t>
+          <t>-0.86</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr">
@@ -6261,7 +6261,7 @@
       </c>
       <c r="AT14" t="inlineStr">
         <is>
-          <t>-130.59</t>
+          <t>-132.14</t>
         </is>
       </c>
       <c r="AU14" t="inlineStr">
@@ -6271,41 +6271,41 @@
       </c>
       <c r="AV14" t="inlineStr">
         <is>
-          <t>150814334.482684</t>
+          <t>150691742.176513</t>
         </is>
       </c>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>39374759.0</t>
+          <t>24762299.0</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>40349216.0</t>
+          <t>31929308.6</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
-          <t>31454761.9</t>
+          <t>32595150.7</t>
         </is>
       </c>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>29061426.18</t>
+          <t>29130934.74</t>
         </is>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
-          <t>8894454</t>
+          <t>-665842</t>
         </is>
       </c>
       <c r="BB14" t="inlineStr">
         <is>
-          <t>507671.8217403347</t>
+          <t>653269.0727074891</t>
         </is>
       </c>
       <c r="BC14" t="n">
-        <v>2478665.68</v>
+        <v>1454053.95</v>
       </c>
       <c r="BD14" t="inlineStr">
         <is>
@@ -6324,7 +6324,7 @@
       </c>
       <c r="BG14" t="inlineStr">
         <is>
-          <t>-10.96</t>
+          <t>-11.45</t>
         </is>
       </c>
       <c r="BH14" t="inlineStr">
@@ -6369,22 +6369,22 @@
       </c>
       <c r="BP14" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BQ14" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BR14" t="inlineStr">
         <is>
-          <t>1.02</t>
+          <t>1.01</t>
         </is>
       </c>
       <c r="BS14" t="inlineStr">
         <is>
-          <t>6.8</t>
+          <t>6.93</t>
         </is>
       </c>
       <c r="BT14" t="inlineStr">
@@ -6394,7 +6394,7 @@
       </c>
       <c r="BU14" t="inlineStr">
         <is>
-          <t>15.19</t>
+          <t>14.92</t>
         </is>
       </c>
       <c r="BV14" t="inlineStr">
@@ -6409,12 +6409,12 @@
       </c>
       <c r="BX14" t="inlineStr">
         <is>
-          <t>28.65</t>
+          <t>28.46</t>
         </is>
       </c>
       <c r="BY14" t="inlineStr">
         <is>
-          <t>11802</t>
+          <t>11593</t>
         </is>
       </c>
       <c r="BZ14" t="inlineStr">
@@ -6434,22 +6434,22 @@
       </c>
       <c r="CC14" t="inlineStr">
         <is>
+          <t>36.95</t>
+        </is>
+      </c>
+      <c r="CD14" t="inlineStr">
+        <is>
           <t>37.3</t>
         </is>
       </c>
-      <c r="CD14" t="inlineStr">
-        <is>
-          <t>37.5</t>
-        </is>
-      </c>
       <c r="CE14" t="inlineStr">
         <is>
-          <t>36.7</t>
+          <t>36.6</t>
         </is>
       </c>
       <c r="CF14" t="inlineStr">
         <is>
-          <t>36.95</t>
+          <t>36.75</t>
         </is>
       </c>
       <c r="CG14" t="inlineStr">
@@ -6481,12 +6481,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>-1.71</t>
+          <t>-1.34</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>1408.733</t>
+          <t>1065.248</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -6496,7 +6496,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>37.45</t>
+          <t>36.95</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -6506,17 +6506,17 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>-1.9</t>
+          <t>-2.35</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>-1.79</t>
+          <t>-0.53</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>22.93</t>
+          <t>28.28</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -6581,7 +6581,7 @@
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>-13.21</t>
+          <t>-14.37</t>
         </is>
       </c>
       <c r="X15" t="inlineStr">
@@ -6591,17 +6591,17 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>15.01</t>
+          <t>11.35</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>-2.94</t>
+          <t>-0.81</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
@@ -6612,12 +6612,12 @@
       <c r="AC15" t="inlineStr"/>
       <c r="AD15" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>11</t>
         </is>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
-          <t>673</t>
+          <t>1212</t>
         </is>
       </c>
       <c r="AF15" t="inlineStr">
@@ -6627,62 +6627,62 @@
       </c>
       <c r="AG15" t="inlineStr">
         <is>
-          <t>16.69</t>
+          <t>9.38</t>
         </is>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>-1.42</t>
+          <t>-1.86</t>
         </is>
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>-3.63</t>
+          <t>-4.02</t>
         </is>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>-3.96</t>
+          <t>-4.09</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>-1.34</t>
+          <t>-1.60</t>
         </is>
       </c>
       <c r="AL15" t="inlineStr">
         <is>
-          <t>37.99</t>
+          <t>37.65000000000001</t>
         </is>
       </c>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>39.42</t>
+          <t>39.23</t>
         </is>
       </c>
       <c r="AN15" t="inlineStr">
         <is>
-          <t>41.05</t>
+          <t>40.9</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>41.6</t>
+          <t>41.57</t>
         </is>
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>-15.49</t>
+          <t>-18.37</t>
         </is>
       </c>
       <c r="AQ15" t="inlineStr">
         <is>
-          <t>-0.91</t>
+          <t>-0.97</t>
         </is>
       </c>
       <c r="AR15" t="inlineStr">
         <is>
-          <t>-0.78</t>
+          <t>-0.82</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr">
@@ -6692,7 +6692,7 @@
       </c>
       <c r="AT15" t="inlineStr">
         <is>
-          <t>-129.19</t>
+          <t>-130.59</t>
         </is>
       </c>
       <c r="AU15" t="inlineStr">
@@ -6702,41 +6702,41 @@
       </c>
       <c r="AV15" t="inlineStr">
         <is>
-          <t>150814334.482684</t>
+          <t>150691742.176513</t>
         </is>
       </c>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>53218422.0</t>
+          <t>39374759.0</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>36341855.6</t>
+          <t>40349216.0</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>29562657.9</t>
+          <t>31454761.9</t>
         </is>
       </c>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>28846965.04</t>
+          <t>29061426.18</t>
         </is>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
-          <t>6779197</t>
+          <t>8894454</t>
         </is>
       </c>
       <c r="BB15" t="inlineStr">
         <is>
-          <t>149309.3019995387</t>
+          <t>507671.8217403347</t>
         </is>
       </c>
       <c r="BC15" t="n">
-        <v>2288252.23</v>
+        <v>2478665.68</v>
       </c>
       <c r="BD15" t="inlineStr">
         <is>
@@ -6755,7 +6755,7 @@
       </c>
       <c r="BG15" t="inlineStr">
         <is>
-          <t>-9.76</t>
+          <t>-10.96</t>
         </is>
       </c>
       <c r="BH15" t="inlineStr">
@@ -6800,22 +6800,22 @@
       </c>
       <c r="BP15" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BQ15" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BR15" t="inlineStr">
         <is>
-          <t>1.03</t>
+          <t>1.02</t>
         </is>
       </c>
       <c r="BS15" t="inlineStr">
         <is>
-          <t>6.8</t>
+          <t>6.93</t>
         </is>
       </c>
       <c r="BT15" t="inlineStr">
@@ -6825,7 +6825,7 @@
       </c>
       <c r="BU15" t="inlineStr">
         <is>
-          <t>15.19</t>
+          <t>14.92</t>
         </is>
       </c>
       <c r="BV15" t="inlineStr">
@@ -6840,12 +6840,12 @@
       </c>
       <c r="BX15" t="inlineStr">
         <is>
-          <t>28.65</t>
+          <t>28.46</t>
         </is>
       </c>
       <c r="BY15" t="inlineStr">
         <is>
-          <t>11802</t>
+          <t>11593</t>
         </is>
       </c>
       <c r="BZ15" t="inlineStr">
@@ -6865,22 +6865,22 @@
       </c>
       <c r="CC15" t="inlineStr">
         <is>
-          <t>38.1</t>
+          <t>37.3</t>
         </is>
       </c>
       <c r="CD15" t="inlineStr">
         <is>
-          <t>38.7</t>
+          <t>37.5</t>
         </is>
       </c>
       <c r="CE15" t="inlineStr">
         <is>
-          <t>37.3</t>
+          <t>36.7</t>
         </is>
       </c>
       <c r="CF15" t="inlineStr">
         <is>
-          <t>37.45</t>
+          <t>36.95</t>
         </is>
       </c>
       <c r="CG15" t="inlineStr">
@@ -6912,12 +6912,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-1.71</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>504.317</t>
+          <t>1408.733</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -6927,7 +6927,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>38.1</t>
+          <t>37.45</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -6937,17 +6937,17 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>-3.67</t>
+          <t>-3.74</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>-1.79</t>
+          <t>-0.53</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>20.39</t>
+          <t>22.93</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -7012,7 +7012,7 @@
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>-11.70</t>
+          <t>-13.21</t>
         </is>
       </c>
       <c r="X16" t="inlineStr">
@@ -7022,17 +7022,17 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>5.37</t>
+          <t>15.01</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>-0.39</t>
+          <t>-2.94</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
@@ -7043,17 +7043,17 @@
       <c r="AC16" t="inlineStr"/>
       <c r="AD16" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>11</t>
         </is>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
-          <t>673</t>
+          <t>1212</t>
         </is>
       </c>
       <c r="AF16" t="inlineStr">
         <is>
-          <t>28.13</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG16" t="inlineStr">
@@ -7063,57 +7063,57 @@
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>-0.55</t>
+          <t>-1.42</t>
         </is>
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>-3.22</t>
+          <t>-3.63</t>
         </is>
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>-3.86</t>
+          <t>-3.96</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>-1.12</t>
+          <t>-1.34</t>
         </is>
       </c>
       <c r="AL16" t="inlineStr">
         <is>
-          <t>38.31</t>
+          <t>37.99</t>
         </is>
       </c>
       <c r="AM16" t="inlineStr">
         <is>
-          <t>39.58</t>
+          <t>39.42</t>
         </is>
       </c>
       <c r="AN16" t="inlineStr">
         <is>
-          <t>41.17</t>
+          <t>41.05</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>41.64</t>
+          <t>41.6</t>
         </is>
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>-13.76</t>
+          <t>-15.49</t>
         </is>
       </c>
       <c r="AQ16" t="inlineStr">
         <is>
-          <t>-0.86</t>
+          <t>-0.91</t>
         </is>
       </c>
       <c r="AR16" t="inlineStr">
         <is>
-          <t>-0.75</t>
+          <t>-0.78</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr">
@@ -7123,7 +7123,7 @@
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>-128.06</t>
+          <t>-129.19</t>
         </is>
       </c>
       <c r="AU16" t="inlineStr">
@@ -7133,41 +7133,41 @@
       </c>
       <c r="AV16" t="inlineStr">
         <is>
-          <t>150814334.482684</t>
+          <t>150691742.176513</t>
         </is>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>19248593.0</t>
+          <t>53218422.0</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>31147112.0</t>
+          <t>36341855.6</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>25871081.1</t>
+          <t>29562657.9</t>
         </is>
       </c>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>28091032.78</t>
+          <t>28846965.04</t>
         </is>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
-          <t>5276030</t>
+          <t>6779197</t>
         </is>
       </c>
       <c r="BB16" t="inlineStr">
         <is>
-          <t>-239589.4123123131</t>
+          <t>149309.3019995387</t>
         </is>
       </c>
       <c r="BC16" t="n">
-        <v>451260.12</v>
+        <v>2288252.23</v>
       </c>
       <c r="BD16" t="inlineStr">
         <is>
@@ -7186,7 +7186,7 @@
       </c>
       <c r="BG16" t="inlineStr">
         <is>
-          <t>-8.19</t>
+          <t>-9.76</t>
         </is>
       </c>
       <c r="BH16" t="inlineStr">
@@ -7231,7 +7231,7 @@
       </c>
       <c r="BP16" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ16" t="inlineStr">
@@ -7241,12 +7241,12 @@
       </c>
       <c r="BR16" t="inlineStr">
         <is>
-          <t>1.05</t>
+          <t>1.03</t>
         </is>
       </c>
       <c r="BS16" t="inlineStr">
         <is>
-          <t>6.8</t>
+          <t>6.93</t>
         </is>
       </c>
       <c r="BT16" t="inlineStr">
@@ -7256,7 +7256,7 @@
       </c>
       <c r="BU16" t="inlineStr">
         <is>
-          <t>15.19</t>
+          <t>14.92</t>
         </is>
       </c>
       <c r="BV16" t="inlineStr">
@@ -7271,12 +7271,12 @@
       </c>
       <c r="BX16" t="inlineStr">
         <is>
-          <t>28.65</t>
+          <t>28.46</t>
         </is>
       </c>
       <c r="BY16" t="inlineStr">
         <is>
-          <t>11802</t>
+          <t>11593</t>
         </is>
       </c>
       <c r="BZ16" t="inlineStr">
@@ -7296,22 +7296,22 @@
       </c>
       <c r="CC16" t="inlineStr">
         <is>
-          <t>38.2</t>
+          <t>38.1</t>
         </is>
       </c>
       <c r="CD16" t="inlineStr">
         <is>
-          <t>38.4</t>
+          <t>38.7</t>
         </is>
       </c>
       <c r="CE16" t="inlineStr">
         <is>
-          <t>37.95</t>
+          <t>37.3</t>
         </is>
       </c>
       <c r="CF16" t="inlineStr">
         <is>
-          <t>38.1</t>
+          <t>37.45</t>
         </is>
       </c>
       <c r="CG16" t="inlineStr">
@@ -7343,12 +7343,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>1.18</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>605.721</t>
+          <t>504.317</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -7368,17 +7368,17 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>-3.67</t>
+          <t>-5.54</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>-1.79</t>
+          <t>-0.53</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>29.75</t>
+          <t>20.39</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -7453,17 +7453,17 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>6.45</t>
+          <t>5.37</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>0.40</t>
+          <t>-0.39</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
@@ -7474,77 +7474,77 @@
       <c r="AC17" t="inlineStr"/>
       <c r="AD17" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>11</t>
         </is>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
-          <t>673</t>
+          <t>1212</t>
         </is>
       </c>
       <c r="AF17" t="inlineStr">
         <is>
-          <t>21.95</t>
+          <t>28.13</t>
         </is>
       </c>
       <c r="AG17" t="inlineStr">
         <is>
-          <t>7.32</t>
+          <t>16.69</t>
         </is>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>-0.94</t>
+          <t>-0.55</t>
         </is>
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>-3.10</t>
+          <t>-3.22</t>
         </is>
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>-3.87</t>
+          <t>-3.86</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>-0.91</t>
+          <t>-1.12</t>
         </is>
       </c>
       <c r="AL17" t="inlineStr">
         <is>
-          <t>38.46</t>
+          <t>38.31</t>
         </is>
       </c>
       <c r="AM17" t="inlineStr">
         <is>
-          <t>39.69</t>
+          <t>39.58</t>
         </is>
       </c>
       <c r="AN17" t="inlineStr">
         <is>
-          <t>41.29</t>
+          <t>41.17</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>41.67</t>
+          <t>41.64</t>
         </is>
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>-16.76</t>
+          <t>-13.76</t>
         </is>
       </c>
       <c r="AQ17" t="inlineStr">
         <is>
-          <t>-0.85</t>
+          <t>-0.86</t>
         </is>
       </c>
       <c r="AR17" t="inlineStr">
         <is>
-          <t>-0.73</t>
+          <t>-0.75</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr">
@@ -7554,7 +7554,7 @@
       </c>
       <c r="AT17" t="inlineStr">
         <is>
-          <t>-127.09</t>
+          <t>-128.06</t>
         </is>
       </c>
       <c r="AU17" t="inlineStr">
@@ -7564,41 +7564,41 @@
       </c>
       <c r="AV17" t="inlineStr">
         <is>
-          <t>150814334.482684</t>
+          <t>150691742.176513</t>
         </is>
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>23042470.0</t>
+          <t>19248593.0</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>33965584.0</t>
+          <t>31147112.0</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>26178217.9</t>
+          <t>25871081.1</t>
         </is>
       </c>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>28206383.42</t>
+          <t>28091032.78</t>
         </is>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
-          <t>7787366</t>
+          <t>5276030</t>
         </is>
       </c>
       <c r="BB17" t="inlineStr">
         <is>
-          <t>-365198.417442461</t>
+          <t>-239589.4123123131</t>
         </is>
       </c>
       <c r="BC17" t="n">
-        <v>1450493.77</v>
+        <v>451260.12</v>
       </c>
       <c r="BD17" t="inlineStr">
         <is>
@@ -7662,7 +7662,7 @@
       </c>
       <c r="BP17" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;可能出現反轉訊號&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;3&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ17" t="inlineStr">
@@ -7677,7 +7677,7 @@
       </c>
       <c r="BS17" t="inlineStr">
         <is>
-          <t>6.8</t>
+          <t>6.93</t>
         </is>
       </c>
       <c r="BT17" t="inlineStr">
@@ -7687,7 +7687,7 @@
       </c>
       <c r="BU17" t="inlineStr">
         <is>
-          <t>15.19</t>
+          <t>14.92</t>
         </is>
       </c>
       <c r="BV17" t="inlineStr">
@@ -7702,12 +7702,12 @@
       </c>
       <c r="BX17" t="inlineStr">
         <is>
-          <t>28.65</t>
+          <t>28.46</t>
         </is>
       </c>
       <c r="BY17" t="inlineStr">
         <is>
-          <t>11802</t>
+          <t>11593</t>
         </is>
       </c>
       <c r="BZ17" t="inlineStr">
@@ -7727,17 +7727,17 @@
       </c>
       <c r="CC17" t="inlineStr">
         <is>
-          <t>38.0</t>
+          <t>38.2</t>
         </is>
       </c>
       <c r="CD17" t="inlineStr">
         <is>
-          <t>38.3</t>
+          <t>38.4</t>
         </is>
       </c>
       <c r="CE17" t="inlineStr">
         <is>
-          <t>37.75</t>
+          <t>37.95</t>
         </is>
       </c>
       <c r="CF17" t="inlineStr">
@@ -7774,12 +7774,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>-2.6</t>
+          <t>1.18</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>1764.112</t>
+          <t>605.721</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -7789,7 +7789,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>37.65</t>
+          <t>38.1</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -7799,17 +7799,17 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>-2.45</t>
+          <t>-5.54</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>-1.79</t>
+          <t>-0.53</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>21.53</t>
+          <t>29.75</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -7874,7 +7874,7 @@
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>-12.75</t>
+          <t>-11.70</t>
         </is>
       </c>
       <c r="X18" t="inlineStr">
@@ -7884,17 +7884,17 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>18.80</t>
+          <t>6.45</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>-2.12</t>
+          <t>0.40</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
@@ -7905,77 +7905,77 @@
       <c r="AC18" t="inlineStr"/>
       <c r="AD18" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>11</t>
         </is>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
-          <t>673</t>
+          <t>1212</t>
         </is>
       </c>
       <c r="AF18" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>21.95</t>
         </is>
       </c>
       <c r="AG18" t="inlineStr">
         <is>
-          <t>6.67</t>
+          <t>7.32</t>
         </is>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>-2.44</t>
+          <t>-0.94</t>
         </is>
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>-3.03</t>
+          <t>-3.10</t>
         </is>
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>-3.91</t>
+          <t>-3.87</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>-0.66</t>
+          <t>-0.91</t>
         </is>
       </c>
       <c r="AL18" t="inlineStr">
         <is>
-          <t>38.59</t>
+          <t>38.46</t>
         </is>
       </c>
       <c r="AM18" t="inlineStr">
         <is>
-          <t>39.8</t>
+          <t>39.69</t>
         </is>
       </c>
       <c r="AN18" t="inlineStr">
         <is>
-          <t>41.42</t>
+          <t>41.29</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>41.69</t>
+          <t>41.67</t>
         </is>
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>-18.69</t>
+          <t>-16.76</t>
         </is>
       </c>
       <c r="AQ18" t="inlineStr">
         <is>
-          <t>-0.83</t>
+          <t>-0.85</t>
         </is>
       </c>
       <c r="AR18" t="inlineStr">
         <is>
-          <t>-0.70</t>
+          <t>-0.73</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr">
@@ -7985,7 +7985,7 @@
       </c>
       <c r="AT18" t="inlineStr">
         <is>
-          <t>-125.95</t>
+          <t>-127.09</t>
         </is>
       </c>
       <c r="AU18" t="inlineStr">
@@ -7995,41 +7995,41 @@
       </c>
       <c r="AV18" t="inlineStr">
         <is>
-          <t>150814334.482684</t>
+          <t>150691742.176513</t>
         </is>
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>66861836.0</t>
+          <t>23042470.0</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>33260992.8</t>
+          <t>33965584.0</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>27368625.9</t>
+          <t>26178217.9</t>
         </is>
       </c>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>28716017.48</t>
+          <t>28206383.42</t>
         </is>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
-          <t>5892366</t>
+          <t>7787366</t>
         </is>
       </c>
       <c r="BB18" t="inlineStr">
         <is>
-          <t>-695324.269555022</t>
+          <t>-365198.417442461</t>
         </is>
       </c>
       <c r="BC18" t="n">
-        <v>2419680.25</v>
+        <v>1450493.77</v>
       </c>
       <c r="BD18" t="inlineStr">
         <is>
@@ -8048,7 +8048,7 @@
       </c>
       <c r="BG18" t="inlineStr">
         <is>
-          <t>-9.28</t>
+          <t>-8.19</t>
         </is>
       </c>
       <c r="BH18" t="inlineStr">
@@ -8093,22 +8093,22 @@
       </c>
       <c r="BP18" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;可能出現反轉訊號&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;3&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ18" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BR18" t="inlineStr">
         <is>
-          <t>1.04</t>
+          <t>1.05</t>
         </is>
       </c>
       <c r="BS18" t="inlineStr">
         <is>
-          <t>6.8</t>
+          <t>6.93</t>
         </is>
       </c>
       <c r="BT18" t="inlineStr">
@@ -8118,7 +8118,7 @@
       </c>
       <c r="BU18" t="inlineStr">
         <is>
-          <t>15.19</t>
+          <t>14.92</t>
         </is>
       </c>
       <c r="BV18" t="inlineStr">
@@ -8133,12 +8133,12 @@
       </c>
       <c r="BX18" t="inlineStr">
         <is>
-          <t>28.65</t>
+          <t>28.46</t>
         </is>
       </c>
       <c r="BY18" t="inlineStr">
         <is>
-          <t>11802</t>
+          <t>11593</t>
         </is>
       </c>
       <c r="BZ18" t="inlineStr">
@@ -8158,22 +8158,22 @@
       </c>
       <c r="CC18" t="inlineStr">
         <is>
-          <t>38.45</t>
+          <t>38.0</t>
         </is>
       </c>
       <c r="CD18" t="inlineStr">
         <is>
-          <t>38.75</t>
+          <t>38.3</t>
         </is>
       </c>
       <c r="CE18" t="inlineStr">
         <is>
-          <t>37.35</t>
+          <t>37.75</t>
         </is>
       </c>
       <c r="CF18" t="inlineStr">
         <is>
-          <t>37.65</t>
+          <t>38.1</t>
         </is>
       </c>
       <c r="CG18" t="inlineStr">
@@ -8205,12 +8205,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>-1.03</t>
+          <t>-2.6</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>499.552</t>
+          <t>1764.112</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -8220,7 +8220,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>38.65</t>
+          <t>37.65</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -8230,17 +8230,17 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>-5.17</t>
+          <t>-4.29</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>-1.79</t>
+          <t>-0.53</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>0.16</t>
+          <t>21.53</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -8305,7 +8305,7 @@
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>-10.43</t>
+          <t>-12.75</t>
         </is>
       </c>
       <c r="X19" t="inlineStr">
@@ -8315,17 +8315,17 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>5.32</t>
+          <t>18.80</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>-1.42</t>
+          <t>-2.12</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
@@ -8336,12 +8336,12 @@
       <c r="AC19" t="inlineStr"/>
       <c r="AD19" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>11</t>
         </is>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
-          <t>673</t>
+          <t>1212</t>
         </is>
       </c>
       <c r="AF19" t="inlineStr">
@@ -8351,17 +8351,17 @@
       </c>
       <c r="AG19" t="inlineStr">
         <is>
-          <t>8.47</t>
+          <t>6.67</t>
         </is>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
-          <t>-0.57</t>
+          <t>-2.44</t>
         </is>
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>-2.61</t>
+          <t>-3.03</t>
         </is>
       </c>
       <c r="AJ19" t="inlineStr">
@@ -8371,42 +8371,42 @@
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>-0.43</t>
+          <t>-0.66</t>
         </is>
       </c>
       <c r="AL19" t="inlineStr">
         <is>
-          <t>38.87</t>
+          <t>38.59</t>
         </is>
       </c>
       <c r="AM19" t="inlineStr">
         <is>
-          <t>39.91</t>
+          <t>39.8</t>
         </is>
       </c>
       <c r="AN19" t="inlineStr">
         <is>
-          <t>41.54</t>
+          <t>41.42</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>41.72</t>
+          <t>41.69</t>
         </is>
       </c>
       <c r="AP19" t="inlineStr">
         <is>
-          <t>-11.54</t>
+          <t>-18.69</t>
         </is>
       </c>
       <c r="AQ19" t="inlineStr">
         <is>
-          <t>-0.74</t>
+          <t>-0.83</t>
         </is>
       </c>
       <c r="AR19" t="inlineStr">
         <is>
-          <t>-0.66</t>
+          <t>-0.70</t>
         </is>
       </c>
       <c r="AS19" t="inlineStr">
@@ -8416,7 +8416,7 @@
       </c>
       <c r="AT19" t="inlineStr">
         <is>
-          <t>-124.74</t>
+          <t>-125.95</t>
         </is>
       </c>
       <c r="AU19" t="inlineStr">
@@ -8426,41 +8426,41 @@
       </c>
       <c r="AV19" t="inlineStr">
         <is>
-          <t>150814334.482684</t>
+          <t>150691742.176513</t>
         </is>
       </c>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>19337957.0</t>
+          <t>66861836.0</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>22560307.8</t>
+          <t>33260992.8</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
-          <t>22524902.5</t>
+          <t>27368625.9</t>
         </is>
       </c>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>28140249.02</t>
+          <t>28716017.48</t>
         </is>
       </c>
       <c r="BA19" t="inlineStr">
         <is>
-          <t>35405</t>
+          <t>5892366</t>
         </is>
       </c>
       <c r="BB19" t="inlineStr">
         <is>
-          <t>-1261688.726998104</t>
+          <t>-695324.269555022</t>
         </is>
       </c>
       <c r="BC19" t="n">
-        <v>-977116.87</v>
+        <v>2419680.25</v>
       </c>
       <c r="BD19" t="inlineStr">
         <is>
@@ -8479,7 +8479,7 @@
       </c>
       <c r="BG19" t="inlineStr">
         <is>
-          <t>-6.87</t>
+          <t>-9.28</t>
         </is>
       </c>
       <c r="BH19" t="inlineStr">
@@ -8524,22 +8524,22 @@
       </c>
       <c r="BP19" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ19" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BR19" t="inlineStr">
         <is>
-          <t>1.06</t>
+          <t>1.04</t>
         </is>
       </c>
       <c r="BS19" t="inlineStr">
         <is>
-          <t>6.8</t>
+          <t>6.93</t>
         </is>
       </c>
       <c r="BT19" t="inlineStr">
@@ -8549,7 +8549,7 @@
       </c>
       <c r="BU19" t="inlineStr">
         <is>
-          <t>15.19</t>
+          <t>14.92</t>
         </is>
       </c>
       <c r="BV19" t="inlineStr">
@@ -8564,12 +8564,12 @@
       </c>
       <c r="BX19" t="inlineStr">
         <is>
-          <t>28.65</t>
+          <t>28.46</t>
         </is>
       </c>
       <c r="BY19" t="inlineStr">
         <is>
-          <t>11802</t>
+          <t>11593</t>
         </is>
       </c>
       <c r="BZ19" t="inlineStr">
@@ -8589,22 +8589,22 @@
       </c>
       <c r="CC19" t="inlineStr">
         <is>
-          <t>38.95</t>
+          <t>38.45</t>
         </is>
       </c>
       <c r="CD19" t="inlineStr">
         <is>
-          <t>39.3</t>
+          <t>38.75</t>
         </is>
       </c>
       <c r="CE19" t="inlineStr">
         <is>
-          <t>38.55</t>
+          <t>37.35</t>
         </is>
       </c>
       <c r="CF19" t="inlineStr">
         <is>
-          <t>38.65</t>
+          <t>37.65</t>
         </is>
       </c>
       <c r="CG19" t="inlineStr">
@@ -8636,12 +8636,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>0.51</t>
+          <t>-1.03</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>700.928</t>
+          <t>499.552</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -8651,7 +8651,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>39.05</t>
+          <t>38.65</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -8661,17 +8661,17 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>-6.26</t>
+          <t>-7.06</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>-1.79</t>
+          <t>-0.53</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>0.15</t>
+          <t>0.16</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -8736,7 +8736,7 @@
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>-9.50</t>
+          <t>-10.43</t>
         </is>
       </c>
       <c r="X20" t="inlineStr">
@@ -8746,17 +8746,17 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>7.47</t>
+          <t>5.32</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>1.17</t>
+          <t>-1.42</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
@@ -8767,17 +8767,17 @@
       <c r="AC20" t="inlineStr"/>
       <c r="AD20" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>11</t>
         </is>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
-          <t>673</t>
+          <t>1212</t>
         </is>
       </c>
       <c r="AF20" t="inlineStr">
         <is>
-          <t>20.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG20" t="inlineStr">
@@ -8787,57 +8787,57 @@
       </c>
       <c r="AH20" t="inlineStr">
         <is>
-          <t>0.15</t>
+          <t>-0.57</t>
         </is>
       </c>
       <c r="AI20" t="inlineStr">
         <is>
-          <t>-2.53</t>
+          <t>-2.61</t>
         </is>
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>-3.9</t>
+          <t>-3.91</t>
         </is>
       </c>
       <c r="AK20" t="inlineStr">
         <is>
-          <t>-0.25</t>
+          <t>-0.43</t>
         </is>
       </c>
       <c r="AL20" t="inlineStr">
         <is>
-          <t>38.99</t>
+          <t>38.87</t>
         </is>
       </c>
       <c r="AM20" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>39.91</t>
         </is>
       </c>
       <c r="AN20" t="inlineStr">
         <is>
-          <t>41.63</t>
+          <t>41.54</t>
         </is>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>41.73</t>
+          <t>41.72</t>
         </is>
       </c>
       <c r="AP20" t="inlineStr">
         <is>
-          <t>-11.93</t>
+          <t>-11.54</t>
         </is>
       </c>
       <c r="AQ20" t="inlineStr">
         <is>
-          <t>-0.72</t>
+          <t>-0.74</t>
         </is>
       </c>
       <c r="AR20" t="inlineStr">
         <is>
-          <t>-0.65</t>
+          <t>-0.66</t>
         </is>
       </c>
       <c r="AS20" t="inlineStr">
@@ -8847,7 +8847,7 @@
       </c>
       <c r="AT20" t="inlineStr">
         <is>
-          <t>-124.03</t>
+          <t>-124.74</t>
         </is>
       </c>
       <c r="AU20" t="inlineStr">
@@ -8857,41 +8857,41 @@
       </c>
       <c r="AV20" t="inlineStr">
         <is>
-          <t>150814334.482684</t>
+          <t>150691742.176513</t>
         </is>
       </c>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>27244704.0</t>
+          <t>19337957.0</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>22783460.2</t>
+          <t>22560307.8</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
-          <t>22749645.3</t>
+          <t>22524902.5</t>
         </is>
       </c>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>28438883.58</t>
+          <t>28140249.02</t>
         </is>
       </c>
       <c r="BA20" t="inlineStr">
         <is>
-          <t>33814</t>
+          <t>35405</t>
         </is>
       </c>
       <c r="BB20" t="inlineStr">
         <is>
-          <t>-1313429.065286876</t>
+          <t>-1261688.726998104</t>
         </is>
       </c>
       <c r="BC20" t="n">
-        <v>-702942.96</v>
+        <v>-977116.87</v>
       </c>
       <c r="BD20" t="inlineStr">
         <is>
@@ -8910,7 +8910,7 @@
       </c>
       <c r="BG20" t="inlineStr">
         <is>
-          <t>-5.90</t>
+          <t>-6.87</t>
         </is>
       </c>
       <c r="BH20" t="inlineStr">
@@ -8955,22 +8955,22 @@
       </c>
       <c r="BP20" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ20" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BR20" t="inlineStr">
         <is>
-          <t>1.07</t>
+          <t>1.06</t>
         </is>
       </c>
       <c r="BS20" t="inlineStr">
         <is>
-          <t>6.8</t>
+          <t>6.93</t>
         </is>
       </c>
       <c r="BT20" t="inlineStr">
@@ -8980,7 +8980,7 @@
       </c>
       <c r="BU20" t="inlineStr">
         <is>
-          <t>15.19</t>
+          <t>14.92</t>
         </is>
       </c>
       <c r="BV20" t="inlineStr">
@@ -8995,12 +8995,12 @@
       </c>
       <c r="BX20" t="inlineStr">
         <is>
-          <t>28.65</t>
+          <t>28.46</t>
         </is>
       </c>
       <c r="BY20" t="inlineStr">
         <is>
-          <t>11802</t>
+          <t>11593</t>
         </is>
       </c>
       <c r="BZ20" t="inlineStr">
@@ -9020,22 +9020,22 @@
       </c>
       <c r="CC20" t="inlineStr">
         <is>
-          <t>38.85</t>
+          <t>38.95</t>
         </is>
       </c>
       <c r="CD20" t="inlineStr">
         <is>
-          <t>39.05</t>
+          <t>39.3</t>
         </is>
       </c>
       <c r="CE20" t="inlineStr">
         <is>
-          <t>38.6</t>
+          <t>38.55</t>
         </is>
       </c>
       <c r="CF20" t="inlineStr">
         <is>
-          <t>39.05</t>
+          <t>38.65</t>
         </is>
       </c>
       <c r="CG20" t="inlineStr">
@@ -9067,12 +9067,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>0.26</t>
+          <t>0.51</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>857.171</t>
+          <t>700.928</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -9082,7 +9082,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>38.85</t>
+          <t>39.05</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -9092,17 +9092,17 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>-5.71</t>
+          <t>-8.17</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>-1.79</t>
+          <t>-0.53</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>-6.52</t>
+          <t>0.15</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -9167,7 +9167,7 @@
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>-9.97</t>
+          <t>-9.50</t>
         </is>
       </c>
       <c r="X21" t="inlineStr">
@@ -9177,17 +9177,17 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-11-06</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>9.13</t>
+          <t>7.47</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>-0.13</t>
+          <t>1.17</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
@@ -9198,57 +9198,57 @@
       <c r="AC21" t="inlineStr"/>
       <c r="AD21" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>11</t>
         </is>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
-          <t>673</t>
+          <t>1212</t>
         </is>
       </c>
       <c r="AF21" t="inlineStr">
         <is>
-          <t>5.41</t>
+          <t>20.0</t>
         </is>
       </c>
       <c r="AG21" t="inlineStr">
         <is>
-          <t>1.8</t>
+          <t>8.47</t>
         </is>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
-          <t>-0.69</t>
+          <t>0.15</t>
         </is>
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>-2.41</t>
+          <t>-2.53</t>
         </is>
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>-3.92</t>
+          <t>-3.9</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
         <is>
-          <t>-0.03</t>
+          <t>-0.25</t>
         </is>
       </c>
       <c r="AL21" t="inlineStr">
         <is>
-          <t>39.12</t>
+          <t>38.99</t>
         </is>
       </c>
       <c r="AM21" t="inlineStr">
         <is>
-          <t>40.08</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="AN21" t="inlineStr">
         <is>
-          <t>41.72</t>
+          <t>41.63</t>
         </is>
       </c>
       <c r="AO21" t="inlineStr">
@@ -9258,17 +9258,17 @@
       </c>
       <c r="AP21" t="inlineStr">
         <is>
-          <t>-16.36</t>
+          <t>-11.93</t>
         </is>
       </c>
       <c r="AQ21" t="inlineStr">
         <is>
-          <t>-0.73</t>
+          <t>-0.72</t>
         </is>
       </c>
       <c r="AR21" t="inlineStr">
         <is>
-          <t>-0.63</t>
+          <t>-0.65</t>
         </is>
       </c>
       <c r="AS21" t="inlineStr">
@@ -9278,7 +9278,7 @@
       </c>
       <c r="AT21" t="inlineStr">
         <is>
-          <t>-123.31</t>
+          <t>-124.03</t>
         </is>
       </c>
       <c r="AU21" t="inlineStr">
@@ -9288,41 +9288,41 @@
       </c>
       <c r="AV21" t="inlineStr">
         <is>
-          <t>150814334.482684</t>
+          <t>150691742.176513</t>
         </is>
       </c>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>33340953.0</t>
+          <t>27244704.0</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>20595050.2</t>
+          <t>22783460.2</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
-          <t>22030516.7</t>
+          <t>22749645.3</t>
         </is>
       </c>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>28317533.86</t>
+          <t>28438883.58</t>
         </is>
       </c>
       <c r="BA21" t="inlineStr">
         <is>
-          <t>-1435466</t>
+          <t>33814</t>
         </is>
       </c>
       <c r="BB21" t="inlineStr">
         <is>
-          <t>-1424426.538814767</t>
+          <t>-1313429.065286876</t>
         </is>
       </c>
       <c r="BC21" t="n">
-        <v>-1133312.31</v>
+        <v>-702942.96</v>
       </c>
       <c r="BD21" t="inlineStr">
         <is>
@@ -9341,7 +9341,7 @@
       </c>
       <c r="BG21" t="inlineStr">
         <is>
-          <t>-6.39</t>
+          <t>-5.90</t>
         </is>
       </c>
       <c r="BH21" t="inlineStr">
@@ -9386,7 +9386,7 @@
       </c>
       <c r="BP21" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ21" t="inlineStr">
@@ -9401,7 +9401,7 @@
       </c>
       <c r="BS21" t="inlineStr">
         <is>
-          <t>6.8</t>
+          <t>6.93</t>
         </is>
       </c>
       <c r="BT21" t="inlineStr">
@@ -9411,7 +9411,7 @@
       </c>
       <c r="BU21" t="inlineStr">
         <is>
-          <t>15.19</t>
+          <t>14.92</t>
         </is>
       </c>
       <c r="BV21" t="inlineStr">
@@ -9426,12 +9426,12 @@
       </c>
       <c r="BX21" t="inlineStr">
         <is>
-          <t>28.65</t>
+          <t>28.46</t>
         </is>
       </c>
       <c r="BY21" t="inlineStr">
         <is>
-          <t>11802</t>
+          <t>11593</t>
         </is>
       </c>
       <c r="BZ21" t="inlineStr">
@@ -9451,22 +9451,22 @@
       </c>
       <c r="CC21" t="inlineStr">
         <is>
-          <t>38.95</t>
+          <t>38.85</t>
         </is>
       </c>
       <c r="CD21" t="inlineStr">
         <is>
-          <t>39.1</t>
+          <t>39.05</t>
         </is>
       </c>
       <c r="CE21" t="inlineStr">
         <is>
-          <t>38.65</t>
+          <t>38.6</t>
         </is>
       </c>
       <c r="CF21" t="inlineStr">
         <is>
-          <t>38.85</t>
+          <t>39.05</t>
         </is>
       </c>
       <c r="CG21" t="inlineStr">
@@ -9498,12 +9498,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>-0.77</t>
+          <t>0.26</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>504.24</t>
+          <t>857.171</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -9513,7 +9513,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>38.75</t>
+          <t>38.85</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -9523,17 +9523,17 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>-5.44</t>
+          <t>-7.62</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>-1.79</t>
+          <t>-0.53</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>-9.08</t>
+          <t>-6.52</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -9598,7 +9598,7 @@
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>-10.20</t>
+          <t>-9.97</t>
         </is>
       </c>
       <c r="X22" t="inlineStr">
@@ -9608,17 +9608,17 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-11-05</t>
+          <t>2025-11-06</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>5.37</t>
+          <t>9.13</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>-0.13</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
@@ -9629,77 +9629,77 @@
       <c r="AC22" t="inlineStr"/>
       <c r="AD22" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>11</t>
         </is>
       </c>
       <c r="AE22" t="inlineStr">
         <is>
-          <t>673</t>
+          <t>1212</t>
         </is>
       </c>
       <c r="AF22" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>5.41</t>
         </is>
       </c>
       <c r="AG22" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.8</t>
         </is>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
-          <t>-1.40</t>
+          <t>-0.69</t>
         </is>
       </c>
       <c r="AI22" t="inlineStr">
         <is>
-          <t>-2.22</t>
+          <t>-2.41</t>
         </is>
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>-3.89</t>
+          <t>-3.92</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
         <is>
-          <t>0.23</t>
+          <t>-0.03</t>
         </is>
       </c>
       <c r="AL22" t="inlineStr">
         <is>
-          <t>39.3</t>
+          <t>39.12</t>
         </is>
       </c>
       <c r="AM22" t="inlineStr">
         <is>
-          <t>40.19</t>
+          <t>40.08</t>
         </is>
       </c>
       <c r="AN22" t="inlineStr">
         <is>
-          <t>41.82</t>
+          <t>41.72</t>
         </is>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>41.72</t>
+          <t>41.73</t>
         </is>
       </c>
       <c r="AP22" t="inlineStr">
         <is>
-          <t>-17.47</t>
+          <t>-16.36</t>
         </is>
       </c>
       <c r="AQ22" t="inlineStr">
         <is>
-          <t>-0.71</t>
+          <t>-0.73</t>
         </is>
       </c>
       <c r="AR22" t="inlineStr">
         <is>
-          <t>-0.60</t>
+          <t>-0.63</t>
         </is>
       </c>
       <c r="AS22" t="inlineStr">
@@ -9709,7 +9709,7 @@
       </c>
       <c r="AT22" t="inlineStr">
         <is>
-          <t>-122.36</t>
+          <t>-123.31</t>
         </is>
       </c>
       <c r="AU22" t="inlineStr">
@@ -9719,41 +9719,41 @@
       </c>
       <c r="AV22" t="inlineStr">
         <is>
-          <t>150814334.482684</t>
+          <t>150691742.176513</t>
         </is>
       </c>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>19519514.0</t>
+          <t>33340953.0</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>18390851.8</t>
+          <t>20595050.2</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr">
         <is>
-          <t>20228126.1</t>
+          <t>22030516.7</t>
         </is>
       </c>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>28082029.5</t>
+          <t>28317533.86</t>
         </is>
       </c>
       <c r="BA22" t="inlineStr">
         <is>
-          <t>-1837274</t>
+          <t>-1435466</t>
         </is>
       </c>
       <c r="BB22" t="inlineStr">
         <is>
-          <t>-1477356.398321357</t>
+          <t>-1424426.538814767</t>
         </is>
       </c>
       <c r="BC22" t="n">
-        <v>-2360819.77</v>
+        <v>-1133312.31</v>
       </c>
       <c r="BD22" t="inlineStr">
         <is>
@@ -9772,7 +9772,7 @@
       </c>
       <c r="BG22" t="inlineStr">
         <is>
-          <t>-6.63</t>
+          <t>-6.39</t>
         </is>
       </c>
       <c r="BH22" t="inlineStr">
@@ -9817,7 +9817,7 @@
       </c>
       <c r="BP22" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ22" t="inlineStr">
@@ -9832,7 +9832,7 @@
       </c>
       <c r="BS22" t="inlineStr">
         <is>
-          <t>6.8</t>
+          <t>6.93</t>
         </is>
       </c>
       <c r="BT22" t="inlineStr">
@@ -9842,7 +9842,7 @@
       </c>
       <c r="BU22" t="inlineStr">
         <is>
-          <t>15.19</t>
+          <t>14.92</t>
         </is>
       </c>
       <c r="BV22" t="inlineStr">
@@ -9857,12 +9857,12 @@
       </c>
       <c r="BX22" t="inlineStr">
         <is>
-          <t>28.65</t>
+          <t>28.46</t>
         </is>
       </c>
       <c r="BY22" t="inlineStr">
         <is>
-          <t>11802</t>
+          <t>11593</t>
         </is>
       </c>
       <c r="BZ22" t="inlineStr">
@@ -9882,22 +9882,22 @@
       </c>
       <c r="CC22" t="inlineStr">
         <is>
-          <t>39.15</t>
+          <t>38.95</t>
         </is>
       </c>
       <c r="CD22" t="inlineStr">
         <is>
-          <t>39.15</t>
+          <t>39.1</t>
         </is>
       </c>
       <c r="CE22" t="inlineStr">
         <is>
-          <t>38.35</t>
+          <t>38.65</t>
         </is>
       </c>
       <c r="CF22" t="inlineStr">
         <is>
-          <t>38.75</t>
+          <t>38.85</t>
         </is>
       </c>
       <c r="CG22" t="inlineStr">
@@ -9929,12 +9929,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>-0.51</t>
+          <t>-0.77</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>340.21</t>
+          <t>504.24</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -9944,7 +9944,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>39.05</t>
+          <t>38.75</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -9954,17 +9954,17 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>-6.26</t>
+          <t>-7.34</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>-1.79</t>
+          <t>-0.53</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>2.77</t>
+          <t>-9.08</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -10029,7 +10029,7 @@
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>-9.50</t>
+          <t>-10.20</t>
         </is>
       </c>
       <c r="X23" t="inlineStr">
@@ -10039,17 +10039,17 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-11-04</t>
+          <t>2025-11-05</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>3.63</t>
+          <t>5.37</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>-1.41</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
@@ -10060,12 +10060,12 @@
       <c r="AC23" t="inlineStr"/>
       <c r="AD23" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>11</t>
         </is>
       </c>
       <c r="AE23" t="inlineStr">
         <is>
-          <t>673</t>
+          <t>1212</t>
         </is>
       </c>
       <c r="AF23" t="inlineStr">
@@ -10080,57 +10080,57 @@
       </c>
       <c r="AH23" t="inlineStr">
         <is>
-          <t>-1.21</t>
+          <t>-1.40</t>
         </is>
       </c>
       <c r="AI23" t="inlineStr">
         <is>
-          <t>-1.92</t>
+          <t>-2.22</t>
         </is>
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>-3.88</t>
+          <t>-3.89</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
         <is>
-          <t>0.53</t>
+          <t>0.23</t>
         </is>
       </c>
       <c r="AL23" t="inlineStr">
         <is>
-          <t>39.53</t>
+          <t>39.3</t>
         </is>
       </c>
       <c r="AM23" t="inlineStr">
         <is>
-          <t>40.3</t>
+          <t>40.19</t>
         </is>
       </c>
       <c r="AN23" t="inlineStr">
         <is>
-          <t>41.93</t>
+          <t>41.82</t>
         </is>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>41.71</t>
+          <t>41.72</t>
         </is>
       </c>
       <c r="AP23" t="inlineStr">
         <is>
-          <t>-14.13</t>
+          <t>-17.47</t>
         </is>
       </c>
       <c r="AQ23" t="inlineStr">
         <is>
-          <t>-0.66</t>
+          <t>-0.71</t>
         </is>
       </c>
       <c r="AR23" t="inlineStr">
         <is>
-          <t>-0.57</t>
+          <t>-0.60</t>
         </is>
       </c>
       <c r="AS23" t="inlineStr">
@@ -10140,7 +10140,7 @@
       </c>
       <c r="AT23" t="inlineStr">
         <is>
-          <t>-121.38</t>
+          <t>-122.36</t>
         </is>
       </c>
       <c r="AU23" t="inlineStr">
@@ -10150,41 +10150,41 @@
       </c>
       <c r="AV23" t="inlineStr">
         <is>
-          <t>150814334.482684</t>
+          <t>150691742.176513</t>
         </is>
       </c>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>13358411.0</t>
+          <t>19519514.0</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>21476259.0</t>
+          <t>18390851.8</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr">
         <is>
-          <t>20896470.1</t>
+          <t>20228126.1</t>
         </is>
       </c>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>28018183.18</t>
+          <t>28082029.5</t>
         </is>
       </c>
       <c r="BA23" t="inlineStr">
         <is>
-          <t>579788</t>
+          <t>-1837274</t>
         </is>
       </c>
       <c r="BB23" t="inlineStr">
         <is>
-          <t>-1316726.695178018</t>
+          <t>-1477356.398321357</t>
         </is>
       </c>
       <c r="BC23" t="n">
-        <v>-2549218.39</v>
+        <v>-2360819.77</v>
       </c>
       <c r="BD23" t="inlineStr">
         <is>
@@ -10203,7 +10203,7 @@
       </c>
       <c r="BG23" t="inlineStr">
         <is>
-          <t>-5.90</t>
+          <t>-6.63</t>
         </is>
       </c>
       <c r="BH23" t="inlineStr">
@@ -10248,7 +10248,7 @@
       </c>
       <c r="BP23" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BQ23" t="inlineStr">
@@ -10263,7 +10263,7 @@
       </c>
       <c r="BS23" t="inlineStr">
         <is>
-          <t>6.8</t>
+          <t>6.93</t>
         </is>
       </c>
       <c r="BT23" t="inlineStr">
@@ -10273,7 +10273,7 @@
       </c>
       <c r="BU23" t="inlineStr">
         <is>
-          <t>15.19</t>
+          <t>14.92</t>
         </is>
       </c>
       <c r="BV23" t="inlineStr">
@@ -10288,12 +10288,12 @@
       </c>
       <c r="BX23" t="inlineStr">
         <is>
-          <t>28.65</t>
+          <t>28.46</t>
         </is>
       </c>
       <c r="BY23" t="inlineStr">
         <is>
-          <t>11802</t>
+          <t>11593</t>
         </is>
       </c>
       <c r="BZ23" t="inlineStr">
@@ -10313,22 +10313,22 @@
       </c>
       <c r="CC23" t="inlineStr">
         <is>
-          <t>39.2</t>
+          <t>39.15</t>
         </is>
       </c>
       <c r="CD23" t="inlineStr">
         <is>
-          <t>39.6</t>
+          <t>39.15</t>
         </is>
       </c>
       <c r="CE23" t="inlineStr">
         <is>
-          <t>39.05</t>
+          <t>38.35</t>
         </is>
       </c>
       <c r="CF23" t="inlineStr">
         <is>
-          <t>39.05</t>
+          <t>38.75</t>
         </is>
       </c>
       <c r="CG23" t="inlineStr">

--- a/Result/checksun_type/塔架.xlsx
+++ b/Result/checksun_type/塔架.xlsx
@@ -878,42 +878,42 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
+          <t>3.41</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>1595.31</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>135.0</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>1712.06</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>130.5</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-3.39</t>
+          <t>-1.56</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>50.94</t>
+          <t>53.45</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -923,7 +923,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>-90.0</t>
+          <t>-65.0</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -978,7 +978,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-44.94</t>
+          <t>-43.04</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -988,17 +988,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>7.08</t>
+          <t>6.60</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>-1.14</t>
+          <t>1.92</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1009,77 +1009,77 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>18</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>1712</t>
+          <t>1595</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>23.08</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>7.69</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>-4.26</t>
+          <t>1.20</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>-8.89</t>
+          <t>-10.06</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>-7.5</t>
+          <t>-7.84</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>-5.97</t>
+          <t>-6.04</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>136.3</t>
+          <t>133.4</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>149.6</t>
+          <t>148.32</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>161.73</t>
+          <t>160.95</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>171.99</t>
+          <t>171.29</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>-28.35</t>
+          <t>-21.52</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>-8.34</t>
+          <t>-8.35</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>-6.50</t>
+          <t>-6.87</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -1089,7 +1089,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-126.11</t>
+          <t>-127.59</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1099,41 +1099,41 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>1699170206.954611</t>
+          <t>1697184807.002158</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>223746689.0</t>
+          <t>212878160.0</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>397436778.6</t>
+          <t>421450515.0</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>263301806.5</t>
+          <t>274650710.4</t>
         </is>
       </c>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>254911229.58</t>
+          <t>254522728.7</t>
         </is>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>134134972</t>
+          <t>146799804</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>6892793.183689982</t>
+          <t>8493004.331540482</t>
         </is>
       </c>
       <c r="BC2" t="n">
-        <v>27925349.17</v>
+        <v>17294165.64</v>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
@@ -1152,7 +1152,7 @@
       </c>
       <c r="BG2" t="inlineStr">
         <is>
-          <t>-27.50</t>
+          <t>-25.00</t>
         </is>
       </c>
       <c r="BH2" t="inlineStr">
@@ -1177,7 +1177,7 @@
       </c>
       <c r="BL2" t="inlineStr">
         <is>
-          <t>0.99</t>
+          <t>0.98</t>
         </is>
       </c>
       <c r="BM2" t="inlineStr">
@@ -1197,22 +1197,22 @@
       </c>
       <c r="BP2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;可能出現反轉訊號&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;3&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>價漲量縮</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
         <is>
-          <t>3.01</t>
+          <t>3.11</t>
         </is>
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>3.19</t>
+          <t>3.08</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
@@ -1222,7 +1222,7 @@
       </c>
       <c r="BU2" t="inlineStr">
         <is>
-          <t>24.53</t>
+          <t>25.38</t>
         </is>
       </c>
       <c r="BV2" t="inlineStr">
@@ -1237,12 +1237,12 @@
       </c>
       <c r="BX2" t="inlineStr">
         <is>
-          <t>28.46</t>
+          <t>28.82</t>
         </is>
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>32220</t>
+          <t>33331</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
@@ -1262,22 +1262,22 @@
       </c>
       <c r="CC2" t="inlineStr">
         <is>
-          <t>131.0</t>
+          <t>132.0</t>
         </is>
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>133.5</t>
+          <t>136.0</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>129.0</t>
+          <t>131.5</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>130.5</t>
+          <t>135.0</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
@@ -1309,12 +1309,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>-2.26</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2844.986</t>
+          <t>1712.06</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1334,17 +1334,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>3.33</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-3.39</t>
+          <t>-1.56</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>48.25</t>
+          <t>50.94</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1354,7 +1354,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>-90.0</t>
+          <t>-65.0</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -1419,17 +1419,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11.77</t>
+          <t>7.08</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>-2.29</t>
+          <t>-1.14</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1440,12 +1440,12 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>18</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>1712</t>
+          <t>1595</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
@@ -1460,57 +1460,57 @@
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>-6.85</t>
+          <t>-4.26</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>-7.30</t>
+          <t>-8.89</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-7.05</t>
+          <t>-7.5</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>-5.89</t>
+          <t>-5.97</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>140.1</t>
+          <t>136.3</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>151.12</t>
+          <t>149.6</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>162.59</t>
+          <t>161.73</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>172.77</t>
+          <t>171.99</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>-28.43</t>
+          <t>-28.35</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>-7.75</t>
+          <t>-8.34</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>-6.04</t>
+          <t>-6.50</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1520,7 +1520,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-124.26</t>
+          <t>-126.11</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1530,41 +1530,41 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>1699170206.954611</t>
+          <t>1697184807.002158</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>373359683.0</t>
+          <t>223746689.0</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>374444824.4</t>
+          <t>397436778.6</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>252575891.8</t>
+          <t>263301806.5</t>
         </is>
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>255257682.72</t>
+          <t>254911229.58</t>
         </is>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>121868932</t>
+          <t>134134972</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>3068692.09532273</t>
+          <t>6892793.183689982</t>
         </is>
       </c>
       <c r="BC3" t="n">
-        <v>40950935.06</v>
+        <v>27925349.17</v>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
@@ -1608,7 +1608,7 @@
       </c>
       <c r="BL3" t="inlineStr">
         <is>
-          <t>0.99</t>
+          <t>0.98</t>
         </is>
       </c>
       <c r="BM3" t="inlineStr">
@@ -1628,12 +1628,12 @@
       </c>
       <c r="BP3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價漲量縮</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
@@ -1643,7 +1643,7 @@
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>3.19</t>
+          <t>3.08</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
@@ -1653,7 +1653,7 @@
       </c>
       <c r="BU3" t="inlineStr">
         <is>
-          <t>24.53</t>
+          <t>25.38</t>
         </is>
       </c>
       <c r="BV3" t="inlineStr">
@@ -1668,12 +1668,12 @@
       </c>
       <c r="BX3" t="inlineStr">
         <is>
-          <t>28.46</t>
+          <t>28.82</t>
         </is>
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>32220</t>
+          <t>33331</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
@@ -1693,17 +1693,17 @@
       </c>
       <c r="CC3" t="inlineStr">
         <is>
-          <t>133.0</t>
+          <t>131.0</t>
         </is>
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>134.5</t>
+          <t>133.5</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>129.5</t>
+          <t>129.0</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
@@ -1740,12 +1740,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>-2.96</t>
+          <t>-2.26</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>4003.393</t>
+          <t>2844.986</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1755,7 +1755,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>133.5</t>
+          <t>130.5</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1765,17 +1765,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-2.3</t>
+          <t>3.33</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-3.39</t>
+          <t>-1.56</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>36.89</t>
+          <t>48.25</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1785,7 +1785,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>-90.0</t>
+          <t>-65.0</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -1840,7 +1840,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-43.67</t>
+          <t>-44.94</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1850,17 +1850,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>16.56</t>
+          <t>11.77</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>-5.24</t>
+          <t>-2.29</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1871,12 +1871,12 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>18</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>1712</t>
+          <t>1595</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
@@ -1891,57 +1891,57 @@
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>-7.23</t>
+          <t>-6.85</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>-5.73</t>
+          <t>-7.30</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>-6.6</t>
+          <t>-7.05</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>-5.82</t>
+          <t>-5.89</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>143.9</t>
+          <t>140.1</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>152.65</t>
+          <t>151.12</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>163.44</t>
+          <t>162.59</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>173.54</t>
+          <t>172.77</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>-22.90</t>
+          <t>-28.43</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>-6.89</t>
+          <t>-7.75</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>-5.61</t>
+          <t>-6.04</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1951,7 +1951,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-122.53</t>
+          <t>-124.26</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1961,41 +1961,41 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>1699170206.954611</t>
+          <t>1697184807.002158</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>543328425.0</t>
+          <t>373359683.0</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>317370279.0</t>
+          <t>374444824.4</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>231842549.9</t>
+          <t>252575891.8</t>
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>254515985.98</t>
+          <t>255257682.72</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>85527729</t>
+          <t>121868932</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>-3818988.443072045</t>
+          <t>3068692.09532273</t>
         </is>
       </c>
       <c r="BC4" t="n">
-        <v>42066417.86</v>
+        <v>40950935.06</v>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
@@ -2014,7 +2014,7 @@
       </c>
       <c r="BG4" t="inlineStr">
         <is>
-          <t>-25.83</t>
+          <t>-27.50</t>
         </is>
       </c>
       <c r="BH4" t="inlineStr">
@@ -2039,7 +2039,7 @@
       </c>
       <c r="BL4" t="inlineStr">
         <is>
-          <t>0.99</t>
+          <t>0.98</t>
         </is>
       </c>
       <c r="BM4" t="inlineStr">
@@ -2059,7 +2059,7 @@
       </c>
       <c r="BP4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;衝高回落,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BQ4" t="inlineStr">
@@ -2069,14 +2069,14 @@
       </c>
       <c r="BR4" t="inlineStr">
         <is>
+          <t>3.01</t>
+        </is>
+      </c>
+      <c r="BS4" t="inlineStr">
+        <is>
           <t>3.08</t>
         </is>
       </c>
-      <c r="BS4" t="inlineStr">
-        <is>
-          <t>3.19</t>
-        </is>
-      </c>
       <c r="BT4" t="inlineStr">
         <is>
           <t>12.24</t>
@@ -2084,7 +2084,7 @@
       </c>
       <c r="BU4" t="inlineStr">
         <is>
-          <t>24.53</t>
+          <t>25.38</t>
         </is>
       </c>
       <c r="BV4" t="inlineStr">
@@ -2099,12 +2099,12 @@
       </c>
       <c r="BX4" t="inlineStr">
         <is>
-          <t>28.46</t>
+          <t>28.82</t>
         </is>
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>32220</t>
+          <t>33331</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
@@ -2124,22 +2124,22 @@
       </c>
       <c r="CC4" t="inlineStr">
         <is>
-          <t>135.0</t>
+          <t>133.0</t>
         </is>
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>141.5</t>
+          <t>134.5</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>132.5</t>
+          <t>129.5</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>133.5</t>
+          <t>130.5</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
@@ -2171,12 +2171,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>-8.16</t>
+          <t>-2.96</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>5388.546</t>
+          <t>4003.393</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2186,7 +2186,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>137.5</t>
+          <t>133.5</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2196,17 +2196,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-5.36</t>
+          <t>1.11</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-3.39</t>
+          <t>-1.56</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>18.56</t>
+          <t>36.89</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2216,7 +2216,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>-90.0</t>
+          <t>-65.0</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-41.98</t>
+          <t>-43.67</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2281,17 +2281,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>22.28</t>
+          <t>16.56</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>-5.06</t>
+          <t>-5.24</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2302,12 +2302,12 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>18</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>1712</t>
+          <t>1595</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
@@ -2322,57 +2322,57 @@
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>-6.59</t>
+          <t>-7.23</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>-4.57</t>
+          <t>-5.73</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>-6.11</t>
+          <t>-6.6</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>-5.70</t>
+          <t>-5.82</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>147.2</t>
+          <t>143.9</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>154.25</t>
+          <t>152.65</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>164.29</t>
+          <t>163.44</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>174.21</t>
+          <t>173.54</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>-13.45</t>
+          <t>-22.90</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>-6.00</t>
+          <t>-6.89</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>-5.29</t>
+          <t>-5.61</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-121.24</t>
+          <t>-122.53</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2392,41 +2392,41 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>1699170206.954611</t>
+          <t>1697184807.002158</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>753939618.0</t>
+          <t>543328425.0</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>239835367.0</t>
+          <t>317370279.0</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>202283159.5</t>
+          <t>231842549.9</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>250790390.86</t>
+          <t>254515985.98</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>37552207</t>
+          <t>85527729</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>-12161789.58854426</t>
+          <t>-3818988.443072045</t>
         </is>
       </c>
       <c r="BC5" t="n">
-        <v>23946656.01</v>
+        <v>42066417.86</v>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
@@ -2445,7 +2445,7 @@
       </c>
       <c r="BG5" t="inlineStr">
         <is>
-          <t>-23.61</t>
+          <t>-25.83</t>
         </is>
       </c>
       <c r="BH5" t="inlineStr">
@@ -2470,7 +2470,7 @@
       </c>
       <c r="BL5" t="inlineStr">
         <is>
-          <t>0.99</t>
+          <t>0.98</t>
         </is>
       </c>
       <c r="BM5" t="inlineStr">
@@ -2490,22 +2490,22 @@
       </c>
       <c r="BP5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;衝高回落,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>價跌量增</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
         <is>
-          <t>3.17</t>
+          <t>3.08</t>
         </is>
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>3.19</t>
+          <t>3.08</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
@@ -2515,7 +2515,7 @@
       </c>
       <c r="BU5" t="inlineStr">
         <is>
-          <t>24.53</t>
+          <t>25.38</t>
         </is>
       </c>
       <c r="BV5" t="inlineStr">
@@ -2530,12 +2530,12 @@
       </c>
       <c r="BX5" t="inlineStr">
         <is>
-          <t>28.46</t>
+          <t>28.82</t>
         </is>
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>32220</t>
+          <t>33331</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
@@ -2555,22 +2555,22 @@
       </c>
       <c r="CC5" t="inlineStr">
         <is>
-          <t>147.0</t>
+          <t>135.0</t>
         </is>
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>147.0</t>
+          <t>141.5</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>135.0</t>
+          <t>132.5</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>137.5</t>
+          <t>133.5</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
@@ -2602,12 +2602,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-8.16</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>617.888</t>
+          <t>5388.546</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2617,7 +2617,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>149.5</t>
+          <t>137.5</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2627,17 +2627,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-14.56</t>
+          <t>-1.85</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-3.39</t>
+          <t>-1.56</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>-14.19</t>
+          <t>18.56</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2647,7 +2647,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>-90.0</t>
+          <t>-65.0</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -2702,7 +2702,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-36.92</t>
+          <t>-41.98</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2712,17 +2712,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>2.56</t>
+          <t>22.28</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>-1.34</t>
+          <t>-5.06</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2733,12 +2733,12 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>18</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>1712</t>
+          <t>1595</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
@@ -2753,57 +2753,57 @@
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>-0.07</t>
+          <t>-6.59</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>-3.96</t>
+          <t>-4.57</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>-5.65</t>
+          <t>-6.11</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>-5.63</t>
+          <t>-5.70</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>149.6</t>
+          <t>147.2</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>155.78</t>
+          <t>154.25</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>165.1</t>
+          <t>164.29</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>174.95</t>
+          <t>174.21</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>-1.33</t>
+          <t>-13.45</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>-5.18</t>
+          <t>-6.00</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>-5.11</t>
+          <t>-5.29</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -2813,7 +2813,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-120.53</t>
+          <t>-121.24</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2823,41 +2823,41 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>1699170206.954611</t>
+          <t>1697184807.002158</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>92809478.0</t>
+          <t>753939618.0</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>127850905.8</t>
+          <t>239835367.0</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>148995940.1</t>
+          <t>202283159.5</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>248204610.78</t>
+          <t>250790390.86</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>-21145034</t>
+          <t>37552207</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>-18726961.5147791</t>
+          <t>-12161789.58854426</t>
         </is>
       </c>
       <c r="BC6" t="n">
-        <v>-25359440.75</v>
+        <v>23946656.01</v>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
@@ -2876,7 +2876,7 @@
       </c>
       <c r="BG6" t="inlineStr">
         <is>
-          <t>-16.94</t>
+          <t>-23.61</t>
         </is>
       </c>
       <c r="BH6" t="inlineStr">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="BL6" t="inlineStr">
         <is>
-          <t>0.99</t>
+          <t>0.98</t>
         </is>
       </c>
       <c r="BM6" t="inlineStr">
@@ -2926,17 +2926,17 @@
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價跌量增</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
         <is>
-          <t>3.44</t>
+          <t>3.17</t>
         </is>
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>3.19</t>
+          <t>3.08</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="BU6" t="inlineStr">
         <is>
-          <t>24.53</t>
+          <t>25.38</t>
         </is>
       </c>
       <c r="BV6" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="BX6" t="inlineStr">
         <is>
-          <t>28.46</t>
+          <t>28.82</t>
         </is>
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>32220</t>
+          <t>33331</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
@@ -2986,22 +2986,22 @@
       </c>
       <c r="CC6" t="inlineStr">
         <is>
-          <t>150.0</t>
+          <t>147.0</t>
         </is>
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>151.5</t>
+          <t>147.0</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>149.5</t>
+          <t>135.0</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>149.5</t>
+          <t>137.5</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
@@ -3038,7 +3038,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>723.545</t>
+          <t>617.888</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3058,17 +3058,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-14.56</t>
+          <t>-10.74</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-3.39</t>
+          <t>-1.56</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>-23.11</t>
+          <t>-14.19</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3078,7 +3078,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>-90.0</t>
+          <t>-65.0</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -3143,17 +3143,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>2.99</t>
+          <t>2.56</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>-1.67</t>
+          <t>-1.34</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3164,12 +3164,12 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>18</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>1712</t>
+          <t>1595</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
@@ -3179,62 +3179,62 @@
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>2.22</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>-0.47</t>
+          <t>-0.07</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>-4.07</t>
+          <t>-3.96</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>-5.55</t>
+          <t>-5.65</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>-5.58</t>
+          <t>-5.63</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>150.2</t>
+          <t>149.6</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>156.57</t>
+          <t>155.78</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>165.78</t>
+          <t>165.1</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>175.58</t>
+          <t>174.95</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>-3.60</t>
+          <t>-1.33</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>-5.28</t>
+          <t>-5.18</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>-5.09</t>
+          <t>-5.11</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -3244,7 +3244,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-120.46</t>
+          <t>-120.53</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3254,41 +3254,41 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>1699170206.954611</t>
+          <t>1697184807.002158</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>108786918.0</t>
+          <t>92809478.0</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>129166834.4</t>
+          <t>127850905.8</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>167987433.4</t>
+          <t>148995940.1</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>261232164.76</t>
+          <t>248204610.78</t>
         </is>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>-38820599</t>
+          <t>-21145034</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>-17521056.19996015</t>
+          <t>-18726961.5147791</t>
         </is>
       </c>
       <c r="BC7" t="n">
-        <v>-24055655.37</v>
+        <v>-25359440.75</v>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
@@ -3332,7 +3332,7 @@
       </c>
       <c r="BL7" t="inlineStr">
         <is>
-          <t>0.99</t>
+          <t>0.98</t>
         </is>
       </c>
       <c r="BM7" t="inlineStr">
@@ -3352,7 +3352,7 @@
       </c>
       <c r="BP7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ7" t="inlineStr">
@@ -3367,7 +3367,7 @@
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>3.19</t>
+          <t>3.08</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
@@ -3377,7 +3377,7 @@
       </c>
       <c r="BU7" t="inlineStr">
         <is>
-          <t>24.53</t>
+          <t>25.38</t>
         </is>
       </c>
       <c r="BV7" t="inlineStr">
@@ -3392,12 +3392,12 @@
       </c>
       <c r="BX7" t="inlineStr">
         <is>
-          <t>28.46</t>
+          <t>28.82</t>
         </is>
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>32220</t>
+          <t>33331</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
@@ -3417,17 +3417,17 @@
       </c>
       <c r="CC7" t="inlineStr">
         <is>
+          <t>150.0</t>
+        </is>
+      </c>
+      <c r="CD7" t="inlineStr">
+        <is>
           <t>151.5</t>
         </is>
       </c>
-      <c r="CD7" t="inlineStr">
-        <is>
-          <t>152.5</t>
-        </is>
-      </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>149.0</t>
+          <t>149.5</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
@@ -3464,12 +3464,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>-0.33</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>586.018</t>
+          <t>723.545</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3489,17 +3489,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-14.56</t>
+          <t>-10.74</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-3.39</t>
+          <t>-1.56</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>-28.30</t>
+          <t>-23.11</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3509,7 +3509,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>-90.0</t>
+          <t>-65.0</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -3574,17 +3574,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>2.42</t>
+          <t>2.99</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>-1.34</t>
+          <t>-1.67</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3595,12 +3595,12 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>18</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>1712</t>
+          <t>1595</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
@@ -3615,57 +3615,57 @@
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>-0.86</t>
+          <t>-0.47</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>-4.25</t>
+          <t>-4.07</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>-5.43</t>
+          <t>-5.55</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>-5.49</t>
+          <t>-5.58</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>150.8</t>
+          <t>150.2</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>157.5</t>
+          <t>156.57</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>166.55</t>
+          <t>165.78</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>176.23</t>
+          <t>175.58</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>-5.51</t>
+          <t>-3.60</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>-5.32</t>
+          <t>-5.28</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>-5.05</t>
+          <t>-5.09</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -3675,7 +3675,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-120.28</t>
+          <t>-120.46</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3685,41 +3685,41 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>1699170206.954611</t>
+          <t>1697184807.002158</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>87986956.0</t>
+          <t>108786918.0</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>130706959.2</t>
+          <t>129166834.4</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>182292868.5</t>
+          <t>167987433.4</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>265109106.98</t>
+          <t>261232164.76</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>-51585909</t>
+          <t>-38820599</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>-16332947.26079137</t>
+          <t>-17521056.19996015</t>
         </is>
       </c>
       <c r="BC8" t="n">
-        <v>-23045842.84</v>
+        <v>-24055655.37</v>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
@@ -3763,7 +3763,7 @@
       </c>
       <c r="BL8" t="inlineStr">
         <is>
-          <t>0.99</t>
+          <t>0.98</t>
         </is>
       </c>
       <c r="BM8" t="inlineStr">
@@ -3783,7 +3783,7 @@
       </c>
       <c r="BP8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ8" t="inlineStr">
@@ -3798,7 +3798,7 @@
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>3.19</t>
+          <t>3.08</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
@@ -3808,7 +3808,7 @@
       </c>
       <c r="BU8" t="inlineStr">
         <is>
-          <t>24.53</t>
+          <t>25.38</t>
         </is>
       </c>
       <c r="BV8" t="inlineStr">
@@ -3823,12 +3823,12 @@
       </c>
       <c r="BX8" t="inlineStr">
         <is>
-          <t>28.46</t>
+          <t>28.82</t>
         </is>
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>32220</t>
+          <t>33331</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
@@ -3853,12 +3853,12 @@
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>151.5</t>
+          <t>152.5</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>149.5</t>
+          <t>149.0</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
@@ -3895,12 +3895,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>0.33</t>
+          <t>-0.33</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>1040.36</t>
+          <t>586.018</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3910,7 +3910,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>150.0</t>
+          <t>149.5</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3920,17 +3920,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-14.94</t>
+          <t>-10.74</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-3.39</t>
+          <t>-1.56</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>-24.53</t>
+          <t>-28.30</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3940,7 +3940,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>-90.0</t>
+          <t>-65.0</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -3995,7 +3995,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-36.71</t>
+          <t>-36.92</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4005,17 +4005,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>4.30</t>
+          <t>2.42</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>1.39</t>
+          <t>-1.34</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4026,17 +4026,17 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>18</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>1712</t>
+          <t>1595</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>6.67</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
@@ -4046,57 +4046,57 @@
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>-1.12</t>
+          <t>-0.86</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>-4.31</t>
+          <t>-4.25</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>-5.31</t>
+          <t>-5.43</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>-5.34</t>
+          <t>-5.49</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>151.7</t>
+          <t>150.8</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>158.52</t>
+          <t>157.5</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>167.41</t>
+          <t>166.55</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>176.86</t>
+          <t>176.23</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>-6.68</t>
+          <t>-5.51</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>-5.31</t>
+          <t>-5.32</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>-4.98</t>
+          <t>-5.05</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -4106,7 +4106,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-120.00</t>
+          <t>-120.28</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4116,41 +4116,41 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>1699170206.954611</t>
+          <t>1697184807.002158</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>155653865.0</t>
+          <t>87986956.0</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>146314820.8</t>
+          <t>130706959.2</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>193869307.6</t>
+          <t>182292868.5</t>
         </is>
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>274342437.92</t>
+          <t>265109106.98</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>-47554486</t>
+          <t>-51585909</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>-15112420.79113203</t>
+          <t>-16332947.26079137</t>
         </is>
       </c>
       <c r="BC9" t="n">
-        <v>-18551620.35</v>
+        <v>-23045842.84</v>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
@@ -4169,7 +4169,7 @@
       </c>
       <c r="BG9" t="inlineStr">
         <is>
-          <t>-16.67</t>
+          <t>-16.94</t>
         </is>
       </c>
       <c r="BH9" t="inlineStr">
@@ -4194,7 +4194,7 @@
       </c>
       <c r="BL9" t="inlineStr">
         <is>
-          <t>0.99</t>
+          <t>0.98</t>
         </is>
       </c>
       <c r="BM9" t="inlineStr">
@@ -4214,7 +4214,7 @@
       </c>
       <c r="BP9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;可能出現反轉訊號&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;3&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ9" t="inlineStr">
@@ -4224,12 +4224,12 @@
       </c>
       <c r="BR9" t="inlineStr">
         <is>
-          <t>3.46</t>
+          <t>3.44</t>
         </is>
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>3.19</t>
+          <t>3.08</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
@@ -4239,7 +4239,7 @@
       </c>
       <c r="BU9" t="inlineStr">
         <is>
-          <t>24.53</t>
+          <t>25.38</t>
         </is>
       </c>
       <c r="BV9" t="inlineStr">
@@ -4254,12 +4254,12 @@
       </c>
       <c r="BX9" t="inlineStr">
         <is>
-          <t>28.46</t>
+          <t>28.82</t>
         </is>
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>32220</t>
+          <t>33331</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
@@ -4279,7 +4279,7 @@
       </c>
       <c r="CC9" t="inlineStr">
         <is>
-          <t>150.5</t>
+          <t>151.5</t>
         </is>
       </c>
       <c r="CD9" t="inlineStr">
@@ -4289,12 +4289,12 @@
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>146.5</t>
+          <t>149.5</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>150.0</t>
+          <t>149.5</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
@@ -4326,12 +4326,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>-1.97</t>
+          <t>0.33</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>1294.619</t>
+          <t>1040.36</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4341,7 +4341,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>149.5</t>
+          <t>150.0</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4351,17 +4351,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-14.56</t>
+          <t>-11.11</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-3.39</t>
+          <t>-1.56</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>-16.90</t>
+          <t>-24.53</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4371,7 +4371,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>-90.0</t>
+          <t>-65.0</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -4426,7 +4426,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-36.92</t>
+          <t>-36.71</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4436,17 +4436,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>5.35</t>
+          <t>4.30</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>-1.00</t>
+          <t>1.39</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4457,77 +4457,77 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>18</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>1712</t>
+          <t>1595</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>6.67</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>2.22</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>-2.35</t>
+          <t>-1.12</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>-3.97</t>
+          <t>-4.31</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>-5.19</t>
+          <t>-5.31</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>-5.28</t>
+          <t>-5.34</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>153.1</t>
+          <t>151.7</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>159.43</t>
+          <t>158.52</t>
         </is>
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>168.15</t>
+          <t>167.41</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>177.52</t>
+          <t>176.86</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>-7.56</t>
+          <t>-6.68</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>-5.26</t>
+          <t>-5.31</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>-4.89</t>
+          <t>-4.98</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -4537,7 +4537,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-119.66</t>
+          <t>-120.00</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4547,41 +4547,41 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>1699170206.954611</t>
+          <t>1697184807.002158</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>194017312.0</t>
+          <t>155653865.0</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>164730952.0</t>
+          <t>146314820.8</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>198237890.5</t>
+          <t>193869307.6</t>
         </is>
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>287305576.32</t>
+          <t>274342437.92</t>
         </is>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>-33506938</t>
+          <t>-47554486</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>-14487111.77960444</t>
+          <t>-15112420.79113203</t>
         </is>
       </c>
       <c r="BC10" t="n">
-        <v>-18718770.61</v>
+        <v>-18551620.35</v>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
@@ -4600,7 +4600,7 @@
       </c>
       <c r="BG10" t="inlineStr">
         <is>
-          <t>-16.94</t>
+          <t>-16.67</t>
         </is>
       </c>
       <c r="BH10" t="inlineStr">
@@ -4625,7 +4625,7 @@
       </c>
       <c r="BL10" t="inlineStr">
         <is>
-          <t>0.99</t>
+          <t>0.98</t>
         </is>
       </c>
       <c r="BM10" t="inlineStr">
@@ -4645,7 +4645,7 @@
       </c>
       <c r="BP10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;可能出現反轉訊號&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;3&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ10" t="inlineStr">
@@ -4655,12 +4655,12 @@
       </c>
       <c r="BR10" t="inlineStr">
         <is>
-          <t>3.44</t>
+          <t>3.46</t>
         </is>
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>3.19</t>
+          <t>3.08</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
@@ -4670,7 +4670,7 @@
       </c>
       <c r="BU10" t="inlineStr">
         <is>
-          <t>24.53</t>
+          <t>25.38</t>
         </is>
       </c>
       <c r="BV10" t="inlineStr">
@@ -4685,12 +4685,12 @@
       </c>
       <c r="BX10" t="inlineStr">
         <is>
-          <t>28.46</t>
+          <t>28.82</t>
         </is>
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>32220</t>
+          <t>33331</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
@@ -4710,22 +4710,22 @@
       </c>
       <c r="CC10" t="inlineStr">
         <is>
-          <t>152.0</t>
+          <t>150.5</t>
         </is>
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>152.0</t>
+          <t>151.5</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>148.5</t>
+          <t>146.5</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>149.5</t>
+          <t>150.0</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
@@ -4757,12 +4757,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-1.97</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>653.151</t>
+          <t>1294.619</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4772,7 +4772,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>152.5</t>
+          <t>149.5</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4782,17 +4782,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-16.86</t>
+          <t>-10.74</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-3.39</t>
+          <t>-1.56</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>-18.28</t>
+          <t>-16.90</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4802,7 +4802,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>-90.0</t>
+          <t>-65.0</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -4857,7 +4857,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-35.65</t>
+          <t>-36.92</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4867,17 +4867,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-06</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>2.70</t>
+          <t>5.35</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>-0.32</t>
+          <t>-1.00</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4888,12 +4888,12 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>18</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>1712</t>
+          <t>1595</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
@@ -4903,62 +4903,62 @@
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>2.38</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>-0.91</t>
+          <t>-2.35</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>-4.07</t>
+          <t>-3.97</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>-5.07</t>
+          <t>-5.19</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>-5.19</t>
+          <t>-5.28</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>153.9</t>
+          <t>153.1</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>160.43</t>
+          <t>159.43</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>169.0</t>
+          <t>168.15</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>178.25</t>
+          <t>177.52</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>-5.77</t>
+          <t>-7.56</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>-5.08</t>
+          <t>-5.26</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>-4.80</t>
+          <t>-4.89</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -4968,7 +4968,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-119.29</t>
+          <t>-119.66</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -4978,41 +4978,41 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>1699170206.954611</t>
+          <t>1697184807.002158</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>99389121.0</t>
+          <t>194017312.0</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>170140974.4</t>
+          <t>164730952.0</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>208211819.2</t>
+          <t>198237890.5</t>
         </is>
       </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>301691507.7</t>
+          <t>287305576.32</t>
         </is>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>-38070844</t>
+          <t>-33506938</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>-13717719.26552568</t>
+          <t>-14487111.77960444</t>
         </is>
       </c>
       <c r="BC11" t="n">
-        <v>-22399398.48</v>
+        <v>-18718770.61</v>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
@@ -5031,7 +5031,7 @@
       </c>
       <c r="BG11" t="inlineStr">
         <is>
-          <t>-15.28</t>
+          <t>-16.94</t>
         </is>
       </c>
       <c r="BH11" t="inlineStr">
@@ -5056,7 +5056,7 @@
       </c>
       <c r="BL11" t="inlineStr">
         <is>
-          <t>0.99</t>
+          <t>0.98</t>
         </is>
       </c>
       <c r="BM11" t="inlineStr">
@@ -5076,7 +5076,7 @@
       </c>
       <c r="BP11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ11" t="inlineStr">
@@ -5086,12 +5086,12 @@
       </c>
       <c r="BR11" t="inlineStr">
         <is>
-          <t>3.51</t>
+          <t>3.44</t>
         </is>
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>3.19</t>
+          <t>3.08</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
@@ -5101,7 +5101,7 @@
       </c>
       <c r="BU11" t="inlineStr">
         <is>
-          <t>24.53</t>
+          <t>25.38</t>
         </is>
       </c>
       <c r="BV11" t="inlineStr">
@@ -5116,12 +5116,12 @@
       </c>
       <c r="BX11" t="inlineStr">
         <is>
-          <t>28.46</t>
+          <t>28.82</t>
         </is>
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>32220</t>
+          <t>33331</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
@@ -5141,22 +5141,22 @@
       </c>
       <c r="CC11" t="inlineStr">
         <is>
-          <t>154.0</t>
+          <t>152.0</t>
         </is>
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>154.5</t>
+          <t>152.0</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>151.0</t>
+          <t>148.5</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>152.5</t>
+          <t>149.5</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
@@ -5188,12 +5188,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>-0.98</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>767.34</t>
+          <t>653.151</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5213,17 +5213,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-16.86</t>
+          <t>-12.96</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-3.39</t>
+          <t>-1.56</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>-2.01</t>
+          <t>-18.28</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5233,7 +5233,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>-90.0</t>
+          <t>-65.0</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -5298,17 +5298,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-05</t>
+          <t>2025-11-06</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>3.17</t>
+          <t>2.70</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>0.35</t>
+          <t>-0.32</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5319,12 +5319,12 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>18</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>1712</t>
+          <t>1595</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
@@ -5334,62 +5334,62 @@
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>17.94</t>
+          <t>2.38</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>-1.17</t>
+          <t>-0.91</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>-4.49</t>
+          <t>-4.07</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>-4.9</t>
+          <t>-5.07</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>-5.05</t>
+          <t>-5.19</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>154.3</t>
+          <t>153.9</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>161.55</t>
+          <t>160.43</t>
         </is>
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>169.88</t>
+          <t>169.0</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>178.91</t>
+          <t>178.25</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>-7.21</t>
+          <t>-5.77</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>-5.07</t>
+          <t>-5.08</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>-4.73</t>
+          <t>-4.80</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
@@ -5399,7 +5399,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-119.01</t>
+          <t>-119.29</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5409,41 +5409,41 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>1699170206.954611</t>
+          <t>1697184807.002158</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>116487542.0</t>
+          <t>99389121.0</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>206808032.4</t>
+          <t>170140974.4</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>211045311.6</t>
+          <t>208211819.2</t>
         </is>
       </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>314221303.24</t>
+          <t>301691507.7</t>
         </is>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>-4237279</t>
+          <t>-38070844</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>-12139232.13529545</t>
+          <t>-13717719.26552568</t>
         </is>
       </c>
       <c r="BC12" t="n">
-        <v>-16718725.04</v>
+        <v>-22399398.48</v>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
@@ -5487,7 +5487,7 @@
       </c>
       <c r="BL12" t="inlineStr">
         <is>
-          <t>0.99</t>
+          <t>0.98</t>
         </is>
       </c>
       <c r="BM12" t="inlineStr">
@@ -5507,7 +5507,7 @@
       </c>
       <c r="BP12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ12" t="inlineStr">
@@ -5522,7 +5522,7 @@
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>3.19</t>
+          <t>3.08</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
@@ -5532,7 +5532,7 @@
       </c>
       <c r="BU12" t="inlineStr">
         <is>
-          <t>24.53</t>
+          <t>25.38</t>
         </is>
       </c>
       <c r="BV12" t="inlineStr">
@@ -5547,12 +5547,12 @@
       </c>
       <c r="BX12" t="inlineStr">
         <is>
-          <t>28.46</t>
+          <t>28.82</t>
         </is>
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>32220</t>
+          <t>33331</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
@@ -5572,17 +5572,17 @@
       </c>
       <c r="CC12" t="inlineStr">
         <is>
-          <t>153.0</t>
+          <t>154.0</t>
         </is>
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>154.0</t>
+          <t>154.5</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>150.5</t>
+          <t>151.0</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
@@ -5619,12 +5619,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>-1.76</t>
+          <t>0.83</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>1212.053</t>
+          <t>776.396</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -5634,7 +5634,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>36.1</t>
+          <t>36.4</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -5649,12 +5649,12 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>-0.53</t>
+          <t>-1.07</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>3.03</t>
+          <t>9.74</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -5719,7 +5719,7 @@
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>-16.34</t>
+          <t>-15.64</t>
         </is>
       </c>
       <c r="X13" t="inlineStr">
@@ -5729,17 +5729,17 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>12.91</t>
+          <t>8.27</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>-1.38</t>
+          <t>0.70</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
@@ -5750,77 +5750,77 @@
       <c r="AC13" t="inlineStr"/>
       <c r="AD13" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
-          <t>1212</t>
+          <t>776</t>
         </is>
       </c>
       <c r="AF13" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>11.76</t>
         </is>
       </c>
       <c r="AG13" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>3.92</t>
         </is>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>-2.62</t>
+          <t>-0.90</t>
         </is>
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>-4.47</t>
+          <t>-4.83</t>
         </is>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>-4.38</t>
+          <t>-4.54</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>-2.09</t>
+          <t>-2.31</t>
         </is>
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>37.07000000000001</t>
+          <t>36.73</t>
         </is>
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>38.8</t>
+          <t>38.6</t>
         </is>
       </c>
       <c r="AN13" t="inlineStr">
         <is>
-          <t>40.58</t>
+          <t>40.43</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>41.45</t>
+          <t>41.39</t>
         </is>
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>-22.07</t>
+          <t>-19.31</t>
         </is>
       </c>
       <c r="AQ13" t="inlineStr">
         <is>
-          <t>-1.12</t>
+          <t>-1.15</t>
         </is>
       </c>
       <c r="AR13" t="inlineStr">
         <is>
-          <t>-0.91</t>
+          <t>-0.96</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr">
@@ -5830,7 +5830,7 @@
       </c>
       <c r="AT13" t="inlineStr">
         <is>
-          <t>-134.02</t>
+          <t>-135.75</t>
         </is>
       </c>
       <c r="AU13" t="inlineStr">
@@ -5840,41 +5840,41 @@
       </c>
       <c r="AV13" t="inlineStr">
         <is>
-          <t>150691742.176513</t>
+          <t>150535732.3834532</t>
         </is>
       </c>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>43823516.0</t>
+          <t>28176624.0</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>36085517.8</t>
+          <t>37871124.0</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>35025550.9</t>
+          <t>34509118.0</t>
         </is>
       </c>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>29409986.0</t>
+          <t>29545425.32</t>
         </is>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
-          <t>1059966</t>
+          <t>3362006</t>
         </is>
       </c>
       <c r="BB13" t="inlineStr">
         <is>
-          <t>880468.5492293607</t>
+          <t>956781.9001630185</t>
         </is>
       </c>
       <c r="BC13" t="n">
-        <v>2130065.67</v>
+        <v>1376505.33</v>
       </c>
       <c r="BD13" t="inlineStr">
         <is>
@@ -5893,7 +5893,7 @@
       </c>
       <c r="BG13" t="inlineStr">
         <is>
-          <t>-13.01</t>
+          <t>-12.29</t>
         </is>
       </c>
       <c r="BH13" t="inlineStr">
@@ -5918,7 +5918,7 @@
       </c>
       <c r="BL13" t="inlineStr">
         <is>
-          <t>0.64</t>
+          <t>0.63</t>
         </is>
       </c>
       <c r="BM13" t="inlineStr">
@@ -5938,7 +5938,7 @@
       </c>
       <c r="BP13" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ13" t="inlineStr">
@@ -5948,12 +5948,12 @@
       </c>
       <c r="BR13" t="inlineStr">
         <is>
-          <t>0.99</t>
+          <t>1.00</t>
         </is>
       </c>
       <c r="BS13" t="inlineStr">
         <is>
-          <t>6.93</t>
+          <t>6.87</t>
         </is>
       </c>
       <c r="BT13" t="inlineStr">
@@ -5963,7 +5963,7 @@
       </c>
       <c r="BU13" t="inlineStr">
         <is>
-          <t>14.92</t>
+          <t>15.04</t>
         </is>
       </c>
       <c r="BV13" t="inlineStr">
@@ -5978,12 +5978,12 @@
       </c>
       <c r="BX13" t="inlineStr">
         <is>
-          <t>28.46</t>
+          <t>28.82</t>
         </is>
       </c>
       <c r="BY13" t="inlineStr">
         <is>
-          <t>11593</t>
+          <t>11690</t>
         </is>
       </c>
       <c r="BZ13" t="inlineStr">
@@ -6003,22 +6003,22 @@
       </c>
       <c r="CC13" t="inlineStr">
         <is>
-          <t>36.85</t>
+          <t>36.3</t>
         </is>
       </c>
       <c r="CD13" t="inlineStr">
         <is>
-          <t>36.85</t>
+          <t>36.55</t>
         </is>
       </c>
       <c r="CE13" t="inlineStr">
         <is>
-          <t>35.85</t>
+          <t>36.0</t>
         </is>
       </c>
       <c r="CF13" t="inlineStr">
         <is>
-          <t>36.1</t>
+          <t>36.4</t>
         </is>
       </c>
       <c r="CG13" t="inlineStr">
@@ -6050,12 +6050,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>-0.54</t>
+          <t>-1.76</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>672.504</t>
+          <t>1212.053</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -6065,7 +6065,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>36.75</t>
+          <t>36.1</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -6075,17 +6075,17 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>-1.8</t>
+          <t>0.82</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>-0.53</t>
+          <t>-1.07</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>-2.04</t>
+          <t>3.03</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -6150,7 +6150,7 @@
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>-14.83</t>
+          <t>-16.34</t>
         </is>
       </c>
       <c r="X14" t="inlineStr">
@@ -6160,17 +6160,17 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>7.17</t>
+          <t>12.91</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>-1.09</t>
+          <t>-1.38</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
@@ -6181,12 +6181,12 @@
       <c r="AC14" t="inlineStr"/>
       <c r="AD14" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
-          <t>1212</t>
+          <t>776</t>
         </is>
       </c>
       <c r="AF14" t="inlineStr">
@@ -6201,57 +6201,57 @@
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>-1.92</t>
+          <t>-2.62</t>
         </is>
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>-3.97</t>
+          <t>-4.47</t>
         </is>
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>-4.25</t>
+          <t>-4.38</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>-1.83</t>
+          <t>-2.09</t>
         </is>
       </c>
       <c r="AL14" t="inlineStr">
         <is>
-          <t>37.47000000000001</t>
+          <t>37.07000000000001</t>
         </is>
       </c>
       <c r="AM14" t="inlineStr">
         <is>
-          <t>39.02</t>
+          <t>38.8</t>
         </is>
       </c>
       <c r="AN14" t="inlineStr">
         <is>
-          <t>40.75</t>
+          <t>40.58</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>41.51</t>
+          <t>41.45</t>
         </is>
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>-19.33</t>
+          <t>-22.07</t>
         </is>
       </c>
       <c r="AQ14" t="inlineStr">
         <is>
-          <t>-1.03</t>
+          <t>-1.12</t>
         </is>
       </c>
       <c r="AR14" t="inlineStr">
         <is>
-          <t>-0.86</t>
+          <t>-0.91</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr">
@@ -6261,7 +6261,7 @@
       </c>
       <c r="AT14" t="inlineStr">
         <is>
-          <t>-132.14</t>
+          <t>-134.02</t>
         </is>
       </c>
       <c r="AU14" t="inlineStr">
@@ -6271,41 +6271,41 @@
       </c>
       <c r="AV14" t="inlineStr">
         <is>
-          <t>150691742.176513</t>
+          <t>150535732.3834532</t>
         </is>
       </c>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>24762299.0</t>
+          <t>43823516.0</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>31929308.6</t>
+          <t>36085517.8</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
-          <t>32595150.7</t>
+          <t>35025550.9</t>
         </is>
       </c>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>29130934.74</t>
+          <t>29409986.0</t>
         </is>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
-          <t>-665842</t>
+          <t>1059966</t>
         </is>
       </c>
       <c r="BB14" t="inlineStr">
         <is>
-          <t>653269.0727074891</t>
+          <t>880468.5492293607</t>
         </is>
       </c>
       <c r="BC14" t="n">
-        <v>1454053.95</v>
+        <v>2130065.67</v>
       </c>
       <c r="BD14" t="inlineStr">
         <is>
@@ -6324,7 +6324,7 @@
       </c>
       <c r="BG14" t="inlineStr">
         <is>
-          <t>-11.45</t>
+          <t>-13.01</t>
         </is>
       </c>
       <c r="BH14" t="inlineStr">
@@ -6349,7 +6349,7 @@
       </c>
       <c r="BL14" t="inlineStr">
         <is>
-          <t>0.64</t>
+          <t>0.63</t>
         </is>
       </c>
       <c r="BM14" t="inlineStr">
@@ -6379,12 +6379,12 @@
       </c>
       <c r="BR14" t="inlineStr">
         <is>
-          <t>1.01</t>
+          <t>0.99</t>
         </is>
       </c>
       <c r="BS14" t="inlineStr">
         <is>
-          <t>6.93</t>
+          <t>6.87</t>
         </is>
       </c>
       <c r="BT14" t="inlineStr">
@@ -6394,7 +6394,7 @@
       </c>
       <c r="BU14" t="inlineStr">
         <is>
-          <t>14.92</t>
+          <t>15.04</t>
         </is>
       </c>
       <c r="BV14" t="inlineStr">
@@ -6409,12 +6409,12 @@
       </c>
       <c r="BX14" t="inlineStr">
         <is>
-          <t>28.46</t>
+          <t>28.82</t>
         </is>
       </c>
       <c r="BY14" t="inlineStr">
         <is>
-          <t>11593</t>
+          <t>11690</t>
         </is>
       </c>
       <c r="BZ14" t="inlineStr">
@@ -6434,22 +6434,22 @@
       </c>
       <c r="CC14" t="inlineStr">
         <is>
-          <t>36.95</t>
+          <t>36.85</t>
         </is>
       </c>
       <c r="CD14" t="inlineStr">
         <is>
-          <t>37.3</t>
+          <t>36.85</t>
         </is>
       </c>
       <c r="CE14" t="inlineStr">
         <is>
-          <t>36.6</t>
+          <t>35.85</t>
         </is>
       </c>
       <c r="CF14" t="inlineStr">
         <is>
-          <t>36.75</t>
+          <t>36.1</t>
         </is>
       </c>
       <c r="CG14" t="inlineStr">
@@ -6481,12 +6481,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>-1.34</t>
+          <t>-0.54</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>1065.248</t>
+          <t>672.504</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -6496,7 +6496,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>36.95</t>
+          <t>36.75</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -6506,17 +6506,17 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>-2.35</t>
+          <t>-0.96</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>-0.53</t>
+          <t>-1.07</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>28.28</t>
+          <t>-2.04</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -6581,7 +6581,7 @@
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>-14.37</t>
+          <t>-14.83</t>
         </is>
       </c>
       <c r="X15" t="inlineStr">
@@ -6591,17 +6591,17 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>11.35</t>
+          <t>7.17</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>-0.81</t>
+          <t>-1.09</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
@@ -6612,12 +6612,12 @@
       <c r="AC15" t="inlineStr"/>
       <c r="AD15" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
-          <t>1212</t>
+          <t>776</t>
         </is>
       </c>
       <c r="AF15" t="inlineStr">
@@ -6627,62 +6627,62 @@
       </c>
       <c r="AG15" t="inlineStr">
         <is>
-          <t>9.38</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>-1.86</t>
+          <t>-1.92</t>
         </is>
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>-4.02</t>
+          <t>-3.97</t>
         </is>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>-4.09</t>
+          <t>-4.25</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>-1.60</t>
+          <t>-1.83</t>
         </is>
       </c>
       <c r="AL15" t="inlineStr">
         <is>
-          <t>37.65000000000001</t>
+          <t>37.47000000000001</t>
         </is>
       </c>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>39.23</t>
+          <t>39.02</t>
         </is>
       </c>
       <c r="AN15" t="inlineStr">
         <is>
-          <t>40.9</t>
+          <t>40.75</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>41.57</t>
+          <t>41.51</t>
         </is>
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>-18.37</t>
+          <t>-19.33</t>
         </is>
       </c>
       <c r="AQ15" t="inlineStr">
         <is>
-          <t>-0.97</t>
+          <t>-1.03</t>
         </is>
       </c>
       <c r="AR15" t="inlineStr">
         <is>
-          <t>-0.82</t>
+          <t>-0.86</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr">
@@ -6692,7 +6692,7 @@
       </c>
       <c r="AT15" t="inlineStr">
         <is>
-          <t>-130.59</t>
+          <t>-132.14</t>
         </is>
       </c>
       <c r="AU15" t="inlineStr">
@@ -6702,41 +6702,41 @@
       </c>
       <c r="AV15" t="inlineStr">
         <is>
-          <t>150691742.176513</t>
+          <t>150535732.3834532</t>
         </is>
       </c>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>39374759.0</t>
+          <t>24762299.0</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>40349216.0</t>
+          <t>31929308.6</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>31454761.9</t>
+          <t>32595150.7</t>
         </is>
       </c>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>29061426.18</t>
+          <t>29130934.74</t>
         </is>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
-          <t>8894454</t>
+          <t>-665842</t>
         </is>
       </c>
       <c r="BB15" t="inlineStr">
         <is>
-          <t>507671.8217403347</t>
+          <t>653269.0727074891</t>
         </is>
       </c>
       <c r="BC15" t="n">
-        <v>2478665.68</v>
+        <v>1454053.95</v>
       </c>
       <c r="BD15" t="inlineStr">
         <is>
@@ -6755,7 +6755,7 @@
       </c>
       <c r="BG15" t="inlineStr">
         <is>
-          <t>-10.96</t>
+          <t>-11.45</t>
         </is>
       </c>
       <c r="BH15" t="inlineStr">
@@ -6780,7 +6780,7 @@
       </c>
       <c r="BL15" t="inlineStr">
         <is>
-          <t>0.64</t>
+          <t>0.63</t>
         </is>
       </c>
       <c r="BM15" t="inlineStr">
@@ -6800,22 +6800,22 @@
       </c>
       <c r="BP15" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BQ15" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BR15" t="inlineStr">
         <is>
-          <t>1.02</t>
+          <t>1.01</t>
         </is>
       </c>
       <c r="BS15" t="inlineStr">
         <is>
-          <t>6.93</t>
+          <t>6.87</t>
         </is>
       </c>
       <c r="BT15" t="inlineStr">
@@ -6825,7 +6825,7 @@
       </c>
       <c r="BU15" t="inlineStr">
         <is>
-          <t>14.92</t>
+          <t>15.04</t>
         </is>
       </c>
       <c r="BV15" t="inlineStr">
@@ -6840,12 +6840,12 @@
       </c>
       <c r="BX15" t="inlineStr">
         <is>
-          <t>28.46</t>
+          <t>28.82</t>
         </is>
       </c>
       <c r="BY15" t="inlineStr">
         <is>
-          <t>11593</t>
+          <t>11690</t>
         </is>
       </c>
       <c r="BZ15" t="inlineStr">
@@ -6865,22 +6865,22 @@
       </c>
       <c r="CC15" t="inlineStr">
         <is>
+          <t>36.95</t>
+        </is>
+      </c>
+      <c r="CD15" t="inlineStr">
+        <is>
           <t>37.3</t>
         </is>
       </c>
-      <c r="CD15" t="inlineStr">
-        <is>
-          <t>37.5</t>
-        </is>
-      </c>
       <c r="CE15" t="inlineStr">
         <is>
-          <t>36.7</t>
+          <t>36.6</t>
         </is>
       </c>
       <c r="CF15" t="inlineStr">
         <is>
-          <t>36.95</t>
+          <t>36.75</t>
         </is>
       </c>
       <c r="CG15" t="inlineStr">
@@ -6912,12 +6912,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>-1.71</t>
+          <t>-1.34</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>1408.733</t>
+          <t>1065.248</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -6927,7 +6927,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>37.45</t>
+          <t>36.95</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -6937,17 +6937,17 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>-3.74</t>
+          <t>-1.51</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>-0.53</t>
+          <t>-1.07</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>22.93</t>
+          <t>28.28</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -7012,7 +7012,7 @@
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>-13.21</t>
+          <t>-14.37</t>
         </is>
       </c>
       <c r="X16" t="inlineStr">
@@ -7022,17 +7022,17 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>15.01</t>
+          <t>11.35</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>-2.94</t>
+          <t>-0.81</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
@@ -7043,12 +7043,12 @@
       <c r="AC16" t="inlineStr"/>
       <c r="AD16" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
-          <t>1212</t>
+          <t>776</t>
         </is>
       </c>
       <c r="AF16" t="inlineStr">
@@ -7058,62 +7058,62 @@
       </c>
       <c r="AG16" t="inlineStr">
         <is>
-          <t>16.69</t>
+          <t>9.38</t>
         </is>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>-1.42</t>
+          <t>-1.86</t>
         </is>
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>-3.63</t>
+          <t>-4.02</t>
         </is>
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>-3.96</t>
+          <t>-4.09</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>-1.34</t>
+          <t>-1.60</t>
         </is>
       </c>
       <c r="AL16" t="inlineStr">
         <is>
-          <t>37.99</t>
+          <t>37.65000000000001</t>
         </is>
       </c>
       <c r="AM16" t="inlineStr">
         <is>
-          <t>39.42</t>
+          <t>39.23</t>
         </is>
       </c>
       <c r="AN16" t="inlineStr">
         <is>
-          <t>41.05</t>
+          <t>40.9</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>41.6</t>
+          <t>41.57</t>
         </is>
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>-15.49</t>
+          <t>-18.37</t>
         </is>
       </c>
       <c r="AQ16" t="inlineStr">
         <is>
-          <t>-0.91</t>
+          <t>-0.97</t>
         </is>
       </c>
       <c r="AR16" t="inlineStr">
         <is>
-          <t>-0.78</t>
+          <t>-0.82</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr">
@@ -7123,7 +7123,7 @@
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>-129.19</t>
+          <t>-130.59</t>
         </is>
       </c>
       <c r="AU16" t="inlineStr">
@@ -7133,41 +7133,41 @@
       </c>
       <c r="AV16" t="inlineStr">
         <is>
-          <t>150691742.176513</t>
+          <t>150535732.3834532</t>
         </is>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>53218422.0</t>
+          <t>39374759.0</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>36341855.6</t>
+          <t>40349216.0</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>29562657.9</t>
+          <t>31454761.9</t>
         </is>
       </c>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>28846965.04</t>
+          <t>29061426.18</t>
         </is>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
-          <t>6779197</t>
+          <t>8894454</t>
         </is>
       </c>
       <c r="BB16" t="inlineStr">
         <is>
-          <t>149309.3019995387</t>
+          <t>507671.8217403347</t>
         </is>
       </c>
       <c r="BC16" t="n">
-        <v>2288252.23</v>
+        <v>2478665.68</v>
       </c>
       <c r="BD16" t="inlineStr">
         <is>
@@ -7186,7 +7186,7 @@
       </c>
       <c r="BG16" t="inlineStr">
         <is>
-          <t>-9.76</t>
+          <t>-10.96</t>
         </is>
       </c>
       <c r="BH16" t="inlineStr">
@@ -7211,7 +7211,7 @@
       </c>
       <c r="BL16" t="inlineStr">
         <is>
-          <t>0.64</t>
+          <t>0.63</t>
         </is>
       </c>
       <c r="BM16" t="inlineStr">
@@ -7231,22 +7231,22 @@
       </c>
       <c r="BP16" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BQ16" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BR16" t="inlineStr">
         <is>
-          <t>1.03</t>
+          <t>1.02</t>
         </is>
       </c>
       <c r="BS16" t="inlineStr">
         <is>
-          <t>6.93</t>
+          <t>6.87</t>
         </is>
       </c>
       <c r="BT16" t="inlineStr">
@@ -7256,7 +7256,7 @@
       </c>
       <c r="BU16" t="inlineStr">
         <is>
-          <t>14.92</t>
+          <t>15.04</t>
         </is>
       </c>
       <c r="BV16" t="inlineStr">
@@ -7271,12 +7271,12 @@
       </c>
       <c r="BX16" t="inlineStr">
         <is>
-          <t>28.46</t>
+          <t>28.82</t>
         </is>
       </c>
       <c r="BY16" t="inlineStr">
         <is>
-          <t>11593</t>
+          <t>11690</t>
         </is>
       </c>
       <c r="BZ16" t="inlineStr">
@@ -7296,22 +7296,22 @@
       </c>
       <c r="CC16" t="inlineStr">
         <is>
-          <t>38.1</t>
+          <t>37.3</t>
         </is>
       </c>
       <c r="CD16" t="inlineStr">
         <is>
-          <t>38.7</t>
+          <t>37.5</t>
         </is>
       </c>
       <c r="CE16" t="inlineStr">
         <is>
-          <t>37.3</t>
+          <t>36.7</t>
         </is>
       </c>
       <c r="CF16" t="inlineStr">
         <is>
-          <t>37.45</t>
+          <t>36.95</t>
         </is>
       </c>
       <c r="CG16" t="inlineStr">
@@ -7343,12 +7343,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-1.71</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>504.317</t>
+          <t>1408.733</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -7358,7 +7358,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>38.1</t>
+          <t>37.45</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -7368,17 +7368,17 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>-5.54</t>
+          <t>-2.88</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>-0.53</t>
+          <t>-1.07</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>20.39</t>
+          <t>22.93</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -7443,7 +7443,7 @@
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>-11.70</t>
+          <t>-13.21</t>
         </is>
       </c>
       <c r="X17" t="inlineStr">
@@ -7453,17 +7453,17 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>5.37</t>
+          <t>15.01</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>-0.39</t>
+          <t>-2.94</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
@@ -7474,17 +7474,17 @@
       <c r="AC17" t="inlineStr"/>
       <c r="AD17" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
-          <t>1212</t>
+          <t>776</t>
         </is>
       </c>
       <c r="AF17" t="inlineStr">
         <is>
-          <t>28.13</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG17" t="inlineStr">
@@ -7494,57 +7494,57 @@
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>-0.55</t>
+          <t>-1.42</t>
         </is>
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>-3.22</t>
+          <t>-3.63</t>
         </is>
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>-3.86</t>
+          <t>-3.96</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>-1.12</t>
+          <t>-1.34</t>
         </is>
       </c>
       <c r="AL17" t="inlineStr">
         <is>
-          <t>38.31</t>
+          <t>37.99</t>
         </is>
       </c>
       <c r="AM17" t="inlineStr">
         <is>
-          <t>39.58</t>
+          <t>39.42</t>
         </is>
       </c>
       <c r="AN17" t="inlineStr">
         <is>
-          <t>41.17</t>
+          <t>41.05</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>41.64</t>
+          <t>41.6</t>
         </is>
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>-13.76</t>
+          <t>-15.49</t>
         </is>
       </c>
       <c r="AQ17" t="inlineStr">
         <is>
-          <t>-0.86</t>
+          <t>-0.91</t>
         </is>
       </c>
       <c r="AR17" t="inlineStr">
         <is>
-          <t>-0.75</t>
+          <t>-0.78</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr">
@@ -7554,7 +7554,7 @@
       </c>
       <c r="AT17" t="inlineStr">
         <is>
-          <t>-128.06</t>
+          <t>-129.19</t>
         </is>
       </c>
       <c r="AU17" t="inlineStr">
@@ -7564,41 +7564,41 @@
       </c>
       <c r="AV17" t="inlineStr">
         <is>
-          <t>150691742.176513</t>
+          <t>150535732.3834532</t>
         </is>
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>19248593.0</t>
+          <t>53218422.0</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>31147112.0</t>
+          <t>36341855.6</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>25871081.1</t>
+          <t>29562657.9</t>
         </is>
       </c>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>28091032.78</t>
+          <t>28846965.04</t>
         </is>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
-          <t>5276030</t>
+          <t>6779197</t>
         </is>
       </c>
       <c r="BB17" t="inlineStr">
         <is>
-          <t>-239589.4123123131</t>
+          <t>149309.3019995387</t>
         </is>
       </c>
       <c r="BC17" t="n">
-        <v>451260.12</v>
+        <v>2288252.23</v>
       </c>
       <c r="BD17" t="inlineStr">
         <is>
@@ -7617,7 +7617,7 @@
       </c>
       <c r="BG17" t="inlineStr">
         <is>
-          <t>-8.19</t>
+          <t>-9.76</t>
         </is>
       </c>
       <c r="BH17" t="inlineStr">
@@ -7642,7 +7642,7 @@
       </c>
       <c r="BL17" t="inlineStr">
         <is>
-          <t>0.64</t>
+          <t>0.63</t>
         </is>
       </c>
       <c r="BM17" t="inlineStr">
@@ -7662,7 +7662,7 @@
       </c>
       <c r="BP17" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ17" t="inlineStr">
@@ -7672,12 +7672,12 @@
       </c>
       <c r="BR17" t="inlineStr">
         <is>
-          <t>1.05</t>
+          <t>1.03</t>
         </is>
       </c>
       <c r="BS17" t="inlineStr">
         <is>
-          <t>6.93</t>
+          <t>6.87</t>
         </is>
       </c>
       <c r="BT17" t="inlineStr">
@@ -7687,7 +7687,7 @@
       </c>
       <c r="BU17" t="inlineStr">
         <is>
-          <t>14.92</t>
+          <t>15.04</t>
         </is>
       </c>
       <c r="BV17" t="inlineStr">
@@ -7702,12 +7702,12 @@
       </c>
       <c r="BX17" t="inlineStr">
         <is>
-          <t>28.46</t>
+          <t>28.82</t>
         </is>
       </c>
       <c r="BY17" t="inlineStr">
         <is>
-          <t>11593</t>
+          <t>11690</t>
         </is>
       </c>
       <c r="BZ17" t="inlineStr">
@@ -7727,22 +7727,22 @@
       </c>
       <c r="CC17" t="inlineStr">
         <is>
-          <t>38.2</t>
+          <t>38.1</t>
         </is>
       </c>
       <c r="CD17" t="inlineStr">
         <is>
-          <t>38.4</t>
+          <t>38.7</t>
         </is>
       </c>
       <c r="CE17" t="inlineStr">
         <is>
-          <t>37.95</t>
+          <t>37.3</t>
         </is>
       </c>
       <c r="CF17" t="inlineStr">
         <is>
-          <t>38.1</t>
+          <t>37.45</t>
         </is>
       </c>
       <c r="CG17" t="inlineStr">
@@ -7774,12 +7774,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>1.18</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>605.721</t>
+          <t>504.317</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -7799,17 +7799,17 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>-5.54</t>
+          <t>-4.67</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>-0.53</t>
+          <t>-1.07</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>29.75</t>
+          <t>20.39</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -7884,17 +7884,17 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>6.45</t>
+          <t>5.37</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>0.40</t>
+          <t>-0.39</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
@@ -7905,77 +7905,77 @@
       <c r="AC18" t="inlineStr"/>
       <c r="AD18" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
-          <t>1212</t>
+          <t>776</t>
         </is>
       </c>
       <c r="AF18" t="inlineStr">
         <is>
-          <t>21.95</t>
+          <t>28.13</t>
         </is>
       </c>
       <c r="AG18" t="inlineStr">
         <is>
-          <t>7.32</t>
+          <t>16.69</t>
         </is>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>-0.94</t>
+          <t>-0.55</t>
         </is>
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>-3.10</t>
+          <t>-3.22</t>
         </is>
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>-3.87</t>
+          <t>-3.86</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>-0.91</t>
+          <t>-1.12</t>
         </is>
       </c>
       <c r="AL18" t="inlineStr">
         <is>
-          <t>38.46</t>
+          <t>38.31</t>
         </is>
       </c>
       <c r="AM18" t="inlineStr">
         <is>
-          <t>39.69</t>
+          <t>39.58</t>
         </is>
       </c>
       <c r="AN18" t="inlineStr">
         <is>
-          <t>41.29</t>
+          <t>41.17</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>41.67</t>
+          <t>41.64</t>
         </is>
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>-16.76</t>
+          <t>-13.76</t>
         </is>
       </c>
       <c r="AQ18" t="inlineStr">
         <is>
-          <t>-0.85</t>
+          <t>-0.86</t>
         </is>
       </c>
       <c r="AR18" t="inlineStr">
         <is>
-          <t>-0.73</t>
+          <t>-0.75</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr">
@@ -7985,7 +7985,7 @@
       </c>
       <c r="AT18" t="inlineStr">
         <is>
-          <t>-127.09</t>
+          <t>-128.06</t>
         </is>
       </c>
       <c r="AU18" t="inlineStr">
@@ -7995,41 +7995,41 @@
       </c>
       <c r="AV18" t="inlineStr">
         <is>
-          <t>150691742.176513</t>
+          <t>150535732.3834532</t>
         </is>
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>23042470.0</t>
+          <t>19248593.0</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>33965584.0</t>
+          <t>31147112.0</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>26178217.9</t>
+          <t>25871081.1</t>
         </is>
       </c>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>28206383.42</t>
+          <t>28091032.78</t>
         </is>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
-          <t>7787366</t>
+          <t>5276030</t>
         </is>
       </c>
       <c r="BB18" t="inlineStr">
         <is>
-          <t>-365198.417442461</t>
+          <t>-239589.4123123131</t>
         </is>
       </c>
       <c r="BC18" t="n">
-        <v>1450493.77</v>
+        <v>451260.12</v>
       </c>
       <c r="BD18" t="inlineStr">
         <is>
@@ -8073,7 +8073,7 @@
       </c>
       <c r="BL18" t="inlineStr">
         <is>
-          <t>0.64</t>
+          <t>0.63</t>
         </is>
       </c>
       <c r="BM18" t="inlineStr">
@@ -8093,7 +8093,7 @@
       </c>
       <c r="BP18" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;可能出現反轉訊號&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;3&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ18" t="inlineStr">
@@ -8108,7 +8108,7 @@
       </c>
       <c r="BS18" t="inlineStr">
         <is>
-          <t>6.93</t>
+          <t>6.87</t>
         </is>
       </c>
       <c r="BT18" t="inlineStr">
@@ -8118,7 +8118,7 @@
       </c>
       <c r="BU18" t="inlineStr">
         <is>
-          <t>14.92</t>
+          <t>15.04</t>
         </is>
       </c>
       <c r="BV18" t="inlineStr">
@@ -8133,12 +8133,12 @@
       </c>
       <c r="BX18" t="inlineStr">
         <is>
-          <t>28.46</t>
+          <t>28.82</t>
         </is>
       </c>
       <c r="BY18" t="inlineStr">
         <is>
-          <t>11593</t>
+          <t>11690</t>
         </is>
       </c>
       <c r="BZ18" t="inlineStr">
@@ -8158,17 +8158,17 @@
       </c>
       <c r="CC18" t="inlineStr">
         <is>
-          <t>38.0</t>
+          <t>38.2</t>
         </is>
       </c>
       <c r="CD18" t="inlineStr">
         <is>
-          <t>38.3</t>
+          <t>38.4</t>
         </is>
       </c>
       <c r="CE18" t="inlineStr">
         <is>
-          <t>37.75</t>
+          <t>37.95</t>
         </is>
       </c>
       <c r="CF18" t="inlineStr">
@@ -8205,12 +8205,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>-2.6</t>
+          <t>1.18</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>1764.112</t>
+          <t>605.721</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -8220,7 +8220,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>37.65</t>
+          <t>38.1</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -8230,17 +8230,17 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>-4.29</t>
+          <t>-4.67</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>-0.53</t>
+          <t>-1.07</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>21.53</t>
+          <t>29.75</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -8305,7 +8305,7 @@
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>-12.75</t>
+          <t>-11.70</t>
         </is>
       </c>
       <c r="X19" t="inlineStr">
@@ -8315,17 +8315,17 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>18.80</t>
+          <t>6.45</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>-2.12</t>
+          <t>0.40</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
@@ -8336,77 +8336,77 @@
       <c r="AC19" t="inlineStr"/>
       <c r="AD19" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
-          <t>1212</t>
+          <t>776</t>
         </is>
       </c>
       <c r="AF19" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>21.95</t>
         </is>
       </c>
       <c r="AG19" t="inlineStr">
         <is>
-          <t>6.67</t>
+          <t>7.32</t>
         </is>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
-          <t>-2.44</t>
+          <t>-0.94</t>
         </is>
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>-3.03</t>
+          <t>-3.10</t>
         </is>
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>-3.91</t>
+          <t>-3.87</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>-0.66</t>
+          <t>-0.91</t>
         </is>
       </c>
       <c r="AL19" t="inlineStr">
         <is>
-          <t>38.59</t>
+          <t>38.46</t>
         </is>
       </c>
       <c r="AM19" t="inlineStr">
         <is>
-          <t>39.8</t>
+          <t>39.69</t>
         </is>
       </c>
       <c r="AN19" t="inlineStr">
         <is>
-          <t>41.42</t>
+          <t>41.29</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>41.69</t>
+          <t>41.67</t>
         </is>
       </c>
       <c r="AP19" t="inlineStr">
         <is>
-          <t>-18.69</t>
+          <t>-16.76</t>
         </is>
       </c>
       <c r="AQ19" t="inlineStr">
         <is>
-          <t>-0.83</t>
+          <t>-0.85</t>
         </is>
       </c>
       <c r="AR19" t="inlineStr">
         <is>
-          <t>-0.70</t>
+          <t>-0.73</t>
         </is>
       </c>
       <c r="AS19" t="inlineStr">
@@ -8416,7 +8416,7 @@
       </c>
       <c r="AT19" t="inlineStr">
         <is>
-          <t>-125.95</t>
+          <t>-127.09</t>
         </is>
       </c>
       <c r="AU19" t="inlineStr">
@@ -8426,41 +8426,41 @@
       </c>
       <c r="AV19" t="inlineStr">
         <is>
-          <t>150691742.176513</t>
+          <t>150535732.3834532</t>
         </is>
       </c>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>66861836.0</t>
+          <t>23042470.0</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>33260992.8</t>
+          <t>33965584.0</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
-          <t>27368625.9</t>
+          <t>26178217.9</t>
         </is>
       </c>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>28716017.48</t>
+          <t>28206383.42</t>
         </is>
       </c>
       <c r="BA19" t="inlineStr">
         <is>
-          <t>5892366</t>
+          <t>7787366</t>
         </is>
       </c>
       <c r="BB19" t="inlineStr">
         <is>
-          <t>-695324.269555022</t>
+          <t>-365198.417442461</t>
         </is>
       </c>
       <c r="BC19" t="n">
-        <v>2419680.25</v>
+        <v>1450493.77</v>
       </c>
       <c r="BD19" t="inlineStr">
         <is>
@@ -8479,7 +8479,7 @@
       </c>
       <c r="BG19" t="inlineStr">
         <is>
-          <t>-9.28</t>
+          <t>-8.19</t>
         </is>
       </c>
       <c r="BH19" t="inlineStr">
@@ -8504,7 +8504,7 @@
       </c>
       <c r="BL19" t="inlineStr">
         <is>
-          <t>0.64</t>
+          <t>0.63</t>
         </is>
       </c>
       <c r="BM19" t="inlineStr">
@@ -8524,22 +8524,22 @@
       </c>
       <c r="BP19" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;可能出現反轉訊號&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;3&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ19" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BR19" t="inlineStr">
         <is>
-          <t>1.04</t>
+          <t>1.05</t>
         </is>
       </c>
       <c r="BS19" t="inlineStr">
         <is>
-          <t>6.93</t>
+          <t>6.87</t>
         </is>
       </c>
       <c r="BT19" t="inlineStr">
@@ -8549,7 +8549,7 @@
       </c>
       <c r="BU19" t="inlineStr">
         <is>
-          <t>14.92</t>
+          <t>15.04</t>
         </is>
       </c>
       <c r="BV19" t="inlineStr">
@@ -8564,12 +8564,12 @@
       </c>
       <c r="BX19" t="inlineStr">
         <is>
-          <t>28.46</t>
+          <t>28.82</t>
         </is>
       </c>
       <c r="BY19" t="inlineStr">
         <is>
-          <t>11593</t>
+          <t>11690</t>
         </is>
       </c>
       <c r="BZ19" t="inlineStr">
@@ -8589,22 +8589,22 @@
       </c>
       <c r="CC19" t="inlineStr">
         <is>
-          <t>38.45</t>
+          <t>38.0</t>
         </is>
       </c>
       <c r="CD19" t="inlineStr">
         <is>
-          <t>38.75</t>
+          <t>38.3</t>
         </is>
       </c>
       <c r="CE19" t="inlineStr">
         <is>
-          <t>37.35</t>
+          <t>37.75</t>
         </is>
       </c>
       <c r="CF19" t="inlineStr">
         <is>
-          <t>37.65</t>
+          <t>38.1</t>
         </is>
       </c>
       <c r="CG19" t="inlineStr">
@@ -8636,12 +8636,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>-1.03</t>
+          <t>-2.6</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>499.552</t>
+          <t>1764.112</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -8651,7 +8651,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>38.65</t>
+          <t>37.65</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -8661,17 +8661,17 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>-7.06</t>
+          <t>-3.43</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>-0.53</t>
+          <t>-1.07</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>0.16</t>
+          <t>21.53</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -8736,7 +8736,7 @@
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>-10.43</t>
+          <t>-12.75</t>
         </is>
       </c>
       <c r="X20" t="inlineStr">
@@ -8746,17 +8746,17 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>5.32</t>
+          <t>18.80</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>-1.42</t>
+          <t>-2.12</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
@@ -8767,12 +8767,12 @@
       <c r="AC20" t="inlineStr"/>
       <c r="AD20" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
-          <t>1212</t>
+          <t>776</t>
         </is>
       </c>
       <c r="AF20" t="inlineStr">
@@ -8782,17 +8782,17 @@
       </c>
       <c r="AG20" t="inlineStr">
         <is>
-          <t>8.47</t>
+          <t>6.67</t>
         </is>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
-          <t>-0.57</t>
+          <t>-2.44</t>
         </is>
       </c>
       <c r="AI20" t="inlineStr">
         <is>
-          <t>-2.61</t>
+          <t>-3.03</t>
         </is>
       </c>
       <c r="AJ20" t="inlineStr">
@@ -8802,42 +8802,42 @@
       </c>
       <c r="AK20" t="inlineStr">
         <is>
-          <t>-0.43</t>
+          <t>-0.66</t>
         </is>
       </c>
       <c r="AL20" t="inlineStr">
         <is>
-          <t>38.87</t>
+          <t>38.59</t>
         </is>
       </c>
       <c r="AM20" t="inlineStr">
         <is>
-          <t>39.91</t>
+          <t>39.8</t>
         </is>
       </c>
       <c r="AN20" t="inlineStr">
         <is>
-          <t>41.54</t>
+          <t>41.42</t>
         </is>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>41.72</t>
+          <t>41.69</t>
         </is>
       </c>
       <c r="AP20" t="inlineStr">
         <is>
-          <t>-11.54</t>
+          <t>-18.69</t>
         </is>
       </c>
       <c r="AQ20" t="inlineStr">
         <is>
-          <t>-0.74</t>
+          <t>-0.83</t>
         </is>
       </c>
       <c r="AR20" t="inlineStr">
         <is>
-          <t>-0.66</t>
+          <t>-0.70</t>
         </is>
       </c>
       <c r="AS20" t="inlineStr">
@@ -8847,7 +8847,7 @@
       </c>
       <c r="AT20" t="inlineStr">
         <is>
-          <t>-124.74</t>
+          <t>-125.95</t>
         </is>
       </c>
       <c r="AU20" t="inlineStr">
@@ -8857,41 +8857,41 @@
       </c>
       <c r="AV20" t="inlineStr">
         <is>
-          <t>150691742.176513</t>
+          <t>150535732.3834532</t>
         </is>
       </c>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>19337957.0</t>
+          <t>66861836.0</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>22560307.8</t>
+          <t>33260992.8</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
-          <t>22524902.5</t>
+          <t>27368625.9</t>
         </is>
       </c>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>28140249.02</t>
+          <t>28716017.48</t>
         </is>
       </c>
       <c r="BA20" t="inlineStr">
         <is>
-          <t>35405</t>
+          <t>5892366</t>
         </is>
       </c>
       <c r="BB20" t="inlineStr">
         <is>
-          <t>-1261688.726998104</t>
+          <t>-695324.269555022</t>
         </is>
       </c>
       <c r="BC20" t="n">
-        <v>-977116.87</v>
+        <v>2419680.25</v>
       </c>
       <c r="BD20" t="inlineStr">
         <is>
@@ -8910,7 +8910,7 @@
       </c>
       <c r="BG20" t="inlineStr">
         <is>
-          <t>-6.87</t>
+          <t>-9.28</t>
         </is>
       </c>
       <c r="BH20" t="inlineStr">
@@ -8935,7 +8935,7 @@
       </c>
       <c r="BL20" t="inlineStr">
         <is>
-          <t>0.64</t>
+          <t>0.63</t>
         </is>
       </c>
       <c r="BM20" t="inlineStr">
@@ -8955,22 +8955,22 @@
       </c>
       <c r="BP20" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ20" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BR20" t="inlineStr">
         <is>
-          <t>1.06</t>
+          <t>1.04</t>
         </is>
       </c>
       <c r="BS20" t="inlineStr">
         <is>
-          <t>6.93</t>
+          <t>6.87</t>
         </is>
       </c>
       <c r="BT20" t="inlineStr">
@@ -8980,7 +8980,7 @@
       </c>
       <c r="BU20" t="inlineStr">
         <is>
-          <t>14.92</t>
+          <t>15.04</t>
         </is>
       </c>
       <c r="BV20" t="inlineStr">
@@ -8995,12 +8995,12 @@
       </c>
       <c r="BX20" t="inlineStr">
         <is>
-          <t>28.46</t>
+          <t>28.82</t>
         </is>
       </c>
       <c r="BY20" t="inlineStr">
         <is>
-          <t>11593</t>
+          <t>11690</t>
         </is>
       </c>
       <c r="BZ20" t="inlineStr">
@@ -9020,22 +9020,22 @@
       </c>
       <c r="CC20" t="inlineStr">
         <is>
-          <t>38.95</t>
+          <t>38.45</t>
         </is>
       </c>
       <c r="CD20" t="inlineStr">
         <is>
-          <t>39.3</t>
+          <t>38.75</t>
         </is>
       </c>
       <c r="CE20" t="inlineStr">
         <is>
-          <t>38.55</t>
+          <t>37.35</t>
         </is>
       </c>
       <c r="CF20" t="inlineStr">
         <is>
-          <t>38.65</t>
+          <t>37.65</t>
         </is>
       </c>
       <c r="CG20" t="inlineStr">
@@ -9067,12 +9067,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>0.51</t>
+          <t>-1.03</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>700.928</t>
+          <t>499.552</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -9082,7 +9082,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>39.05</t>
+          <t>38.65</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -9092,17 +9092,17 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>-8.17</t>
+          <t>-6.18</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>-0.53</t>
+          <t>-1.07</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>0.15</t>
+          <t>0.16</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -9167,7 +9167,7 @@
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>-9.50</t>
+          <t>-10.43</t>
         </is>
       </c>
       <c r="X21" t="inlineStr">
@@ -9177,17 +9177,17 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>7.47</t>
+          <t>5.32</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>1.17</t>
+          <t>-1.42</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
@@ -9198,17 +9198,17 @@
       <c r="AC21" t="inlineStr"/>
       <c r="AD21" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
-          <t>1212</t>
+          <t>776</t>
         </is>
       </c>
       <c r="AF21" t="inlineStr">
         <is>
-          <t>20.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG21" t="inlineStr">
@@ -9218,57 +9218,57 @@
       </c>
       <c r="AH21" t="inlineStr">
         <is>
-          <t>0.15</t>
+          <t>-0.57</t>
         </is>
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>-2.53</t>
+          <t>-2.61</t>
         </is>
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>-3.9</t>
+          <t>-3.91</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
         <is>
-          <t>-0.25</t>
+          <t>-0.43</t>
         </is>
       </c>
       <c r="AL21" t="inlineStr">
         <is>
-          <t>38.99</t>
+          <t>38.87</t>
         </is>
       </c>
       <c r="AM21" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>39.91</t>
         </is>
       </c>
       <c r="AN21" t="inlineStr">
         <is>
-          <t>41.63</t>
+          <t>41.54</t>
         </is>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>41.73</t>
+          <t>41.72</t>
         </is>
       </c>
       <c r="AP21" t="inlineStr">
         <is>
-          <t>-11.93</t>
+          <t>-11.54</t>
         </is>
       </c>
       <c r="AQ21" t="inlineStr">
         <is>
-          <t>-0.72</t>
+          <t>-0.74</t>
         </is>
       </c>
       <c r="AR21" t="inlineStr">
         <is>
-          <t>-0.65</t>
+          <t>-0.66</t>
         </is>
       </c>
       <c r="AS21" t="inlineStr">
@@ -9278,7 +9278,7 @@
       </c>
       <c r="AT21" t="inlineStr">
         <is>
-          <t>-124.03</t>
+          <t>-124.74</t>
         </is>
       </c>
       <c r="AU21" t="inlineStr">
@@ -9288,41 +9288,41 @@
       </c>
       <c r="AV21" t="inlineStr">
         <is>
-          <t>150691742.176513</t>
+          <t>150535732.3834532</t>
         </is>
       </c>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>27244704.0</t>
+          <t>19337957.0</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>22783460.2</t>
+          <t>22560307.8</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
-          <t>22749645.3</t>
+          <t>22524902.5</t>
         </is>
       </c>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>28438883.58</t>
+          <t>28140249.02</t>
         </is>
       </c>
       <c r="BA21" t="inlineStr">
         <is>
-          <t>33814</t>
+          <t>35405</t>
         </is>
       </c>
       <c r="BB21" t="inlineStr">
         <is>
-          <t>-1313429.065286876</t>
+          <t>-1261688.726998104</t>
         </is>
       </c>
       <c r="BC21" t="n">
-        <v>-702942.96</v>
+        <v>-977116.87</v>
       </c>
       <c r="BD21" t="inlineStr">
         <is>
@@ -9341,7 +9341,7 @@
       </c>
       <c r="BG21" t="inlineStr">
         <is>
-          <t>-5.90</t>
+          <t>-6.87</t>
         </is>
       </c>
       <c r="BH21" t="inlineStr">
@@ -9366,7 +9366,7 @@
       </c>
       <c r="BL21" t="inlineStr">
         <is>
-          <t>0.64</t>
+          <t>0.63</t>
         </is>
       </c>
       <c r="BM21" t="inlineStr">
@@ -9386,7 +9386,7 @@
       </c>
       <c r="BP21" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ21" t="inlineStr">
@@ -9396,12 +9396,12 @@
       </c>
       <c r="BR21" t="inlineStr">
         <is>
-          <t>1.07</t>
+          <t>1.06</t>
         </is>
       </c>
       <c r="BS21" t="inlineStr">
         <is>
-          <t>6.93</t>
+          <t>6.87</t>
         </is>
       </c>
       <c r="BT21" t="inlineStr">
@@ -9411,7 +9411,7 @@
       </c>
       <c r="BU21" t="inlineStr">
         <is>
-          <t>14.92</t>
+          <t>15.04</t>
         </is>
       </c>
       <c r="BV21" t="inlineStr">
@@ -9426,12 +9426,12 @@
       </c>
       <c r="BX21" t="inlineStr">
         <is>
-          <t>28.46</t>
+          <t>28.82</t>
         </is>
       </c>
       <c r="BY21" t="inlineStr">
         <is>
-          <t>11593</t>
+          <t>11690</t>
         </is>
       </c>
       <c r="BZ21" t="inlineStr">
@@ -9451,22 +9451,22 @@
       </c>
       <c r="CC21" t="inlineStr">
         <is>
-          <t>38.85</t>
+          <t>38.95</t>
         </is>
       </c>
       <c r="CD21" t="inlineStr">
         <is>
-          <t>39.05</t>
+          <t>39.3</t>
         </is>
       </c>
       <c r="CE21" t="inlineStr">
         <is>
-          <t>38.6</t>
+          <t>38.55</t>
         </is>
       </c>
       <c r="CF21" t="inlineStr">
         <is>
-          <t>39.05</t>
+          <t>38.65</t>
         </is>
       </c>
       <c r="CG21" t="inlineStr">
@@ -9498,12 +9498,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>0.26</t>
+          <t>0.51</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>857.171</t>
+          <t>700.928</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -9513,7 +9513,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>38.85</t>
+          <t>39.05</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -9523,17 +9523,17 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>-7.62</t>
+          <t>-7.28</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>-0.53</t>
+          <t>-1.07</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>-6.52</t>
+          <t>0.15</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -9598,7 +9598,7 @@
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>-9.97</t>
+          <t>-9.50</t>
         </is>
       </c>
       <c r="X22" t="inlineStr">
@@ -9608,17 +9608,17 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-11-06</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>9.13</t>
+          <t>7.47</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>-0.13</t>
+          <t>1.17</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
@@ -9629,57 +9629,57 @@
       <c r="AC22" t="inlineStr"/>
       <c r="AD22" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE22" t="inlineStr">
         <is>
-          <t>1212</t>
+          <t>776</t>
         </is>
       </c>
       <c r="AF22" t="inlineStr">
         <is>
-          <t>5.41</t>
+          <t>20.0</t>
         </is>
       </c>
       <c r="AG22" t="inlineStr">
         <is>
-          <t>1.8</t>
+          <t>8.47</t>
         </is>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
-          <t>-0.69</t>
+          <t>0.15</t>
         </is>
       </c>
       <c r="AI22" t="inlineStr">
         <is>
-          <t>-2.41</t>
+          <t>-2.53</t>
         </is>
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>-3.92</t>
+          <t>-3.9</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
         <is>
-          <t>-0.03</t>
+          <t>-0.25</t>
         </is>
       </c>
       <c r="AL22" t="inlineStr">
         <is>
-          <t>39.12</t>
+          <t>38.99</t>
         </is>
       </c>
       <c r="AM22" t="inlineStr">
         <is>
-          <t>40.08</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="AN22" t="inlineStr">
         <is>
-          <t>41.72</t>
+          <t>41.63</t>
         </is>
       </c>
       <c r="AO22" t="inlineStr">
@@ -9689,17 +9689,17 @@
       </c>
       <c r="AP22" t="inlineStr">
         <is>
-          <t>-16.36</t>
+          <t>-11.93</t>
         </is>
       </c>
       <c r="AQ22" t="inlineStr">
         <is>
-          <t>-0.73</t>
+          <t>-0.72</t>
         </is>
       </c>
       <c r="AR22" t="inlineStr">
         <is>
-          <t>-0.63</t>
+          <t>-0.65</t>
         </is>
       </c>
       <c r="AS22" t="inlineStr">
@@ -9709,7 +9709,7 @@
       </c>
       <c r="AT22" t="inlineStr">
         <is>
-          <t>-123.31</t>
+          <t>-124.03</t>
         </is>
       </c>
       <c r="AU22" t="inlineStr">
@@ -9719,41 +9719,41 @@
       </c>
       <c r="AV22" t="inlineStr">
         <is>
-          <t>150691742.176513</t>
+          <t>150535732.3834532</t>
         </is>
       </c>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>33340953.0</t>
+          <t>27244704.0</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>20595050.2</t>
+          <t>22783460.2</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr">
         <is>
-          <t>22030516.7</t>
+          <t>22749645.3</t>
         </is>
       </c>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>28317533.86</t>
+          <t>28438883.58</t>
         </is>
       </c>
       <c r="BA22" t="inlineStr">
         <is>
-          <t>-1435466</t>
+          <t>33814</t>
         </is>
       </c>
       <c r="BB22" t="inlineStr">
         <is>
-          <t>-1424426.538814767</t>
+          <t>-1313429.065286876</t>
         </is>
       </c>
       <c r="BC22" t="n">
-        <v>-1133312.31</v>
+        <v>-702942.96</v>
       </c>
       <c r="BD22" t="inlineStr">
         <is>
@@ -9772,7 +9772,7 @@
       </c>
       <c r="BG22" t="inlineStr">
         <is>
-          <t>-6.39</t>
+          <t>-5.90</t>
         </is>
       </c>
       <c r="BH22" t="inlineStr">
@@ -9797,7 +9797,7 @@
       </c>
       <c r="BL22" t="inlineStr">
         <is>
-          <t>0.64</t>
+          <t>0.63</t>
         </is>
       </c>
       <c r="BM22" t="inlineStr">
@@ -9817,7 +9817,7 @@
       </c>
       <c r="BP22" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ22" t="inlineStr">
@@ -9832,7 +9832,7 @@
       </c>
       <c r="BS22" t="inlineStr">
         <is>
-          <t>6.93</t>
+          <t>6.87</t>
         </is>
       </c>
       <c r="BT22" t="inlineStr">
@@ -9842,7 +9842,7 @@
       </c>
       <c r="BU22" t="inlineStr">
         <is>
-          <t>14.92</t>
+          <t>15.04</t>
         </is>
       </c>
       <c r="BV22" t="inlineStr">
@@ -9857,12 +9857,12 @@
       </c>
       <c r="BX22" t="inlineStr">
         <is>
-          <t>28.46</t>
+          <t>28.82</t>
         </is>
       </c>
       <c r="BY22" t="inlineStr">
         <is>
-          <t>11593</t>
+          <t>11690</t>
         </is>
       </c>
       <c r="BZ22" t="inlineStr">
@@ -9882,22 +9882,22 @@
       </c>
       <c r="CC22" t="inlineStr">
         <is>
-          <t>38.95</t>
+          <t>38.85</t>
         </is>
       </c>
       <c r="CD22" t="inlineStr">
         <is>
-          <t>39.1</t>
+          <t>39.05</t>
         </is>
       </c>
       <c r="CE22" t="inlineStr">
         <is>
-          <t>38.65</t>
+          <t>38.6</t>
         </is>
       </c>
       <c r="CF22" t="inlineStr">
         <is>
-          <t>38.85</t>
+          <t>39.05</t>
         </is>
       </c>
       <c r="CG22" t="inlineStr">
@@ -9929,12 +9929,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>-0.77</t>
+          <t>0.26</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>504.24</t>
+          <t>857.171</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -9944,7 +9944,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>38.75</t>
+          <t>38.85</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -9954,17 +9954,17 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>-7.34</t>
+          <t>-6.73</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>-0.53</t>
+          <t>-1.07</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>-9.08</t>
+          <t>-6.52</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -10029,7 +10029,7 @@
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>-10.20</t>
+          <t>-9.97</t>
         </is>
       </c>
       <c r="X23" t="inlineStr">
@@ -10039,17 +10039,17 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-11-05</t>
+          <t>2025-11-06</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>5.37</t>
+          <t>9.13</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>-0.13</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
@@ -10060,77 +10060,77 @@
       <c r="AC23" t="inlineStr"/>
       <c r="AD23" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE23" t="inlineStr">
         <is>
-          <t>1212</t>
+          <t>776</t>
         </is>
       </c>
       <c r="AF23" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>5.41</t>
         </is>
       </c>
       <c r="AG23" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.8</t>
         </is>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
-          <t>-1.40</t>
+          <t>-0.69</t>
         </is>
       </c>
       <c r="AI23" t="inlineStr">
         <is>
-          <t>-2.22</t>
+          <t>-2.41</t>
         </is>
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>-3.89</t>
+          <t>-3.92</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
         <is>
-          <t>0.23</t>
+          <t>-0.03</t>
         </is>
       </c>
       <c r="AL23" t="inlineStr">
         <is>
-          <t>39.3</t>
+          <t>39.12</t>
         </is>
       </c>
       <c r="AM23" t="inlineStr">
         <is>
-          <t>40.19</t>
+          <t>40.08</t>
         </is>
       </c>
       <c r="AN23" t="inlineStr">
         <is>
-          <t>41.82</t>
+          <t>41.72</t>
         </is>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>41.72</t>
+          <t>41.73</t>
         </is>
       </c>
       <c r="AP23" t="inlineStr">
         <is>
-          <t>-17.47</t>
+          <t>-16.36</t>
         </is>
       </c>
       <c r="AQ23" t="inlineStr">
         <is>
-          <t>-0.71</t>
+          <t>-0.73</t>
         </is>
       </c>
       <c r="AR23" t="inlineStr">
         <is>
-          <t>-0.60</t>
+          <t>-0.63</t>
         </is>
       </c>
       <c r="AS23" t="inlineStr">
@@ -10140,7 +10140,7 @@
       </c>
       <c r="AT23" t="inlineStr">
         <is>
-          <t>-122.36</t>
+          <t>-123.31</t>
         </is>
       </c>
       <c r="AU23" t="inlineStr">
@@ -10150,41 +10150,41 @@
       </c>
       <c r="AV23" t="inlineStr">
         <is>
-          <t>150691742.176513</t>
+          <t>150535732.3834532</t>
         </is>
       </c>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>19519514.0</t>
+          <t>33340953.0</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>18390851.8</t>
+          <t>20595050.2</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr">
         <is>
-          <t>20228126.1</t>
+          <t>22030516.7</t>
         </is>
       </c>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>28082029.5</t>
+          <t>28317533.86</t>
         </is>
       </c>
       <c r="BA23" t="inlineStr">
         <is>
-          <t>-1837274</t>
+          <t>-1435466</t>
         </is>
       </c>
       <c r="BB23" t="inlineStr">
         <is>
-          <t>-1477356.398321357</t>
+          <t>-1424426.538814767</t>
         </is>
       </c>
       <c r="BC23" t="n">
-        <v>-2360819.77</v>
+        <v>-1133312.31</v>
       </c>
       <c r="BD23" t="inlineStr">
         <is>
@@ -10203,7 +10203,7 @@
       </c>
       <c r="BG23" t="inlineStr">
         <is>
-          <t>-6.63</t>
+          <t>-6.39</t>
         </is>
       </c>
       <c r="BH23" t="inlineStr">
@@ -10228,7 +10228,7 @@
       </c>
       <c r="BL23" t="inlineStr">
         <is>
-          <t>0.64</t>
+          <t>0.63</t>
         </is>
       </c>
       <c r="BM23" t="inlineStr">
@@ -10248,7 +10248,7 @@
       </c>
       <c r="BP23" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ23" t="inlineStr">
@@ -10263,7 +10263,7 @@
       </c>
       <c r="BS23" t="inlineStr">
         <is>
-          <t>6.93</t>
+          <t>6.87</t>
         </is>
       </c>
       <c r="BT23" t="inlineStr">
@@ -10273,7 +10273,7 @@
       </c>
       <c r="BU23" t="inlineStr">
         <is>
-          <t>14.92</t>
+          <t>15.04</t>
         </is>
       </c>
       <c r="BV23" t="inlineStr">
@@ -10288,12 +10288,12 @@
       </c>
       <c r="BX23" t="inlineStr">
         <is>
-          <t>28.46</t>
+          <t>28.82</t>
         </is>
       </c>
       <c r="BY23" t="inlineStr">
         <is>
-          <t>11593</t>
+          <t>11690</t>
         </is>
       </c>
       <c r="BZ23" t="inlineStr">
@@ -10313,22 +10313,22 @@
       </c>
       <c r="CC23" t="inlineStr">
         <is>
-          <t>39.15</t>
+          <t>38.95</t>
         </is>
       </c>
       <c r="CD23" t="inlineStr">
         <is>
-          <t>39.15</t>
+          <t>39.1</t>
         </is>
       </c>
       <c r="CE23" t="inlineStr">
         <is>
-          <t>38.35</t>
+          <t>38.65</t>
         </is>
       </c>
       <c r="CF23" t="inlineStr">
         <is>
-          <t>38.75</t>
+          <t>38.85</t>
         </is>
       </c>
       <c r="CG23" t="inlineStr">

--- a/Result/checksun_type/塔架.xlsx
+++ b/Result/checksun_type/塔架.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CI23"/>
+  <dimension ref="A1:CJ23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -701,165 +701,170 @@
       </c>
       <c r="BC1" s="1" t="inlineStr">
         <is>
-          <t>Volume_Price_Change_sum</t>
+          <t>VPC_MACD</t>
         </is>
       </c>
       <c r="BD1" s="1" t="inlineStr">
         <is>
+          <t>Volume_Price_Change</t>
+        </is>
+      </c>
+      <c r="BE1" s="1" t="inlineStr">
+        <is>
           <t>highlight_enddate</t>
         </is>
       </c>
-      <c r="BE1" s="1" t="inlineStr">
+      <c r="BF1" s="1" t="inlineStr">
         <is>
           <t>MA_last_cross_date收盤價</t>
         </is>
       </c>
-      <c r="BF1" s="1" t="inlineStr">
+      <c r="BG1" s="1" t="inlineStr">
         <is>
           <t>MA_last_cross_date</t>
         </is>
       </c>
-      <c r="BG1" s="1" t="inlineStr">
+      <c r="BH1" s="1" t="inlineStr">
         <is>
           <t>MA_last_cross_%</t>
         </is>
       </c>
-      <c r="BH1" s="1" t="inlineStr">
+      <c r="BI1" s="1" t="inlineStr">
         <is>
           <t>stock_name</t>
         </is>
       </c>
-      <c r="BI1" s="1" t="inlineStr">
+      <c r="BJ1" s="1" t="inlineStr">
         <is>
           <t>Type0</t>
         </is>
       </c>
-      <c r="BJ1" s="1" t="inlineStr">
+      <c r="BK1" s="1" t="inlineStr">
         <is>
           <t>Type1</t>
         </is>
       </c>
-      <c r="BK1" s="1" t="inlineStr">
+      <c r="BL1" s="1" t="inlineStr">
         <is>
           <t>Type2</t>
         </is>
       </c>
-      <c r="BL1" s="1" t="inlineStr">
+      <c r="BM1" s="1" t="inlineStr">
         <is>
           <t>貝他值</t>
         </is>
       </c>
-      <c r="BM1" s="1" t="inlineStr">
+      <c r="BN1" s="1" t="inlineStr">
         <is>
           <t>營業收入-上月比較增減(%)</t>
         </is>
       </c>
-      <c r="BN1" s="1" t="inlineStr">
+      <c r="BO1" s="1" t="inlineStr">
         <is>
           <t>營業收入-去年同月增減(%)</t>
         </is>
       </c>
-      <c r="BO1" s="1" t="inlineStr">
+      <c r="BP1" s="1" t="inlineStr">
         <is>
           <t>累計營業收入-前期比較增減(%)</t>
         </is>
       </c>
-      <c r="BP1" s="1" t="inlineStr">
+      <c r="BQ1" s="1" t="inlineStr">
         <is>
           <t>Full_Summary</t>
         </is>
       </c>
-      <c r="BQ1" s="1" t="inlineStr">
+      <c r="BR1" s="1" t="inlineStr">
         <is>
           <t>textdesc</t>
         </is>
       </c>
-      <c r="BR1" s="1" t="inlineStr">
+      <c r="BS1" s="1" t="inlineStr">
         <is>
           <t>淨值倍率</t>
         </is>
       </c>
-      <c r="BS1" s="1" t="inlineStr">
+      <c r="BT1" s="1" t="inlineStr">
         <is>
           <t>殖利率</t>
         </is>
       </c>
-      <c r="BT1" s="1" t="inlineStr">
+      <c r="BU1" s="1" t="inlineStr">
         <is>
           <t>每股營收(元)</t>
         </is>
       </c>
-      <c r="BU1" s="1" t="inlineStr">
+      <c r="BV1" s="1" t="inlineStr">
         <is>
           <t>本益比</t>
         </is>
       </c>
-      <c r="BV1" s="1" t="inlineStr">
+      <c r="BW1" s="1" t="inlineStr">
         <is>
           <t>營業毛利率</t>
         </is>
       </c>
-      <c r="BW1" s="1" t="inlineStr">
+      <c r="BX1" s="1" t="inlineStr">
         <is>
           <t>營業利益率</t>
         </is>
       </c>
-      <c r="BX1" s="1" t="inlineStr">
+      <c r="BY1" s="1" t="inlineStr">
         <is>
           <t>同業平均本益比</t>
         </is>
       </c>
-      <c r="BY1" s="1" t="inlineStr">
+      <c r="BZ1" s="1" t="inlineStr">
         <is>
           <t>總市值</t>
         </is>
       </c>
-      <c r="BZ1" s="1" t="inlineStr">
+      <c r="CA1" s="1" t="inlineStr">
         <is>
           <t>營收比重</t>
         </is>
       </c>
-      <c r="CA1" s="1" t="inlineStr">
+      <c r="CB1" s="1" t="inlineStr">
         <is>
           <t>Type</t>
         </is>
       </c>
-      <c r="CB1" s="1" t="inlineStr">
+      <c r="CC1" s="1" t="inlineStr">
         <is>
           <t>Typelevel</t>
         </is>
       </c>
-      <c r="CC1" s="1" t="inlineStr">
+      <c r="CD1" s="1" t="inlineStr">
         <is>
           <t>開盤價</t>
         </is>
       </c>
-      <c r="CD1" s="1" t="inlineStr">
+      <c r="CE1" s="1" t="inlineStr">
         <is>
           <t>最高價</t>
         </is>
       </c>
-      <c r="CE1" s="1" t="inlineStr">
+      <c r="CF1" s="1" t="inlineStr">
         <is>
           <t>最低價</t>
         </is>
       </c>
-      <c r="CF1" s="1" t="inlineStr">
+      <c r="CG1" s="1" t="inlineStr">
         <is>
           <t>收盤價</t>
         </is>
       </c>
-      <c r="CG1" s="1" t="inlineStr">
+      <c r="CH1" s="1" t="inlineStr">
         <is>
           <t>每股淨值(元)</t>
         </is>
       </c>
-      <c r="CH1" s="1" t="inlineStr">
+      <c r="CI1" s="1" t="inlineStr">
         <is>
           <t>desc</t>
         </is>
       </c>
-      <c r="CI1" s="1" t="inlineStr">
+      <c r="CJ1" s="1" t="inlineStr">
         <is>
           <t>flag_stat</t>
         </is>
@@ -878,12 +883,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>3.41</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>1595.31</t>
+          <t>1302.953</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -908,12 +913,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-1.56</t>
+          <t>-3.39</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>53.45</t>
+          <t>12.02</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -988,17 +993,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>6.60</t>
+          <t>5.39</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>1.92</t>
+          <t>3.05</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1009,77 +1014,77 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>12</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>1595</t>
+          <t>1303</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>23.08</t>
+          <t>23.68</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>7.69</t>
+          <t>15.59</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>1.20</t>
+          <t>1.58</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>-10.06</t>
+          <t>-9.76</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>-7.84</t>
+          <t>-8.05</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>-6.04</t>
+          <t>-6.11</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>133.4</t>
+          <t>132.9</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>148.32</t>
+          <t>147.28</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>160.95</t>
+          <t>160.17</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>171.29</t>
+          <t>170.59</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>-21.52</t>
+          <t>-15.53</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>-8.35</t>
+          <t>-8.25</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>-6.87</t>
+          <t>-7.14</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -1089,7 +1094,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-127.59</t>
+          <t>-128.71</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1099,198 +1104,203 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>1697184807.002158</t>
+          <t>1695120094.609914</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>212878160.0</t>
+          <t>173429988.0</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>421450515.0</t>
+          <t>305348589.0</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>274650710.4</t>
+          <t>272591978.0</t>
         </is>
       </c>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>254522728.7</t>
+          <t>254388028.92</t>
         </is>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>146799804</t>
+          <t>32756611</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>8493004.331540482</t>
-        </is>
-      </c>
-      <c r="BC2" t="n">
-        <v>17294165.64</v>
-      </c>
-      <c r="BD2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+          <t>8180445.224550578</t>
+        </is>
+      </c>
+      <c r="BC2" t="inlineStr">
+        <is>
+          <t>6461370.136106104</t>
+        </is>
+      </c>
+      <c r="BD2" t="n">
+        <v>173429988</v>
       </c>
       <c r="BE2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF2" t="inlineStr">
+        <is>
           <t>180.0</t>
         </is>
       </c>
-      <c r="BF2" t="inlineStr">
+      <c r="BG2" t="inlineStr">
         <is>
           <t>2025/05/20</t>
         </is>
       </c>
-      <c r="BG2" t="inlineStr">
+      <c r="BH2" t="inlineStr">
         <is>
           <t>-25.00</t>
         </is>
       </c>
-      <c r="BH2" t="inlineStr">
+      <c r="BI2" t="inlineStr">
         <is>
           <t>世紀鋼</t>
         </is>
       </c>
-      <c r="BI2" t="inlineStr">
+      <c r="BJ2" t="inlineStr">
         <is>
           <t>世紀鋼</t>
         </is>
       </c>
-      <c r="BJ2" t="inlineStr">
+      <c r="BK2" t="inlineStr">
         <is>
           <t>鋼鐵工業</t>
         </is>
       </c>
-      <c r="BK2" t="inlineStr">
+      <c r="BL2" t="inlineStr">
         <is>
           <t>上市</t>
         </is>
       </c>
-      <c r="BL2" t="inlineStr">
-        <is>
-          <t>0.98</t>
-        </is>
-      </c>
       <c r="BM2" t="inlineStr">
         <is>
+          <t>0.97</t>
+        </is>
+      </c>
+      <c r="BN2" t="inlineStr">
+        <is>
           <t>7.556077963084796</t>
         </is>
       </c>
-      <c r="BN2" t="inlineStr">
+      <c r="BO2" t="inlineStr">
         <is>
           <t>10.88205073781603</t>
         </is>
       </c>
-      <c r="BO2" t="inlineStr">
+      <c r="BP2" t="inlineStr">
         <is>
           <t>19.50943262662372</t>
         </is>
       </c>
-      <c r="BP2" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;可能出現反轉訊號&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;3&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
         <is>
+          <t>價-量-</t>
+        </is>
+      </c>
+      <c r="BS2" t="inlineStr">
+        <is>
           <t>3.11</t>
         </is>
       </c>
-      <c r="BS2" t="inlineStr">
+      <c r="BT2" t="inlineStr">
         <is>
           <t>3.08</t>
         </is>
       </c>
-      <c r="BT2" t="inlineStr">
+      <c r="BU2" t="inlineStr">
         <is>
           <t>12.24</t>
         </is>
       </c>
-      <c r="BU2" t="inlineStr">
+      <c r="BV2" t="inlineStr">
         <is>
           <t>25.38</t>
         </is>
       </c>
-      <c r="BV2" t="inlineStr">
+      <c r="BW2" t="inlineStr">
         <is>
           <t>26.49%</t>
         </is>
       </c>
-      <c r="BW2" t="inlineStr">
+      <c r="BX2" t="inlineStr">
         <is>
           <t>15.03%</t>
         </is>
       </c>
-      <c r="BX2" t="inlineStr">
-        <is>
-          <t>28.82</t>
-        </is>
-      </c>
       <c r="BY2" t="inlineStr">
         <is>
+          <t>28.48</t>
+        </is>
+      </c>
+      <c r="BZ2" t="inlineStr">
+        <is>
           <t>33331</t>
         </is>
       </c>
-      <c r="BZ2" t="inlineStr">
+      <c r="CA2" t="inlineStr">
         <is>
           <t>風力發電鋼構工程88.69%、高樓建物鋼構工程10.17%、其他鋼構(含鋼品)0.82%、工業廠房鋼構工程0.16%、公共工程鋼構工程0.16% (2024年)</t>
         </is>
       </c>
-      <c r="CA2" t="inlineStr">
+      <c r="CB2" t="inlineStr">
         <is>
           <t>世紀鋼-鋼鐵工業-上市</t>
         </is>
       </c>
-      <c r="CB2" t="inlineStr">
+      <c r="CC2" t="inlineStr">
         <is>
           <t>鋼鐵工業右下上市</t>
         </is>
       </c>
-      <c r="CC2" t="inlineStr">
-        <is>
-          <t>132.0</t>
-        </is>
-      </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>136.0</t>
+          <t>132.5</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>131.5</t>
+          <t>135.0</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
+          <t>131.0</t>
+        </is>
+      </c>
+      <c r="CG2" t="inlineStr">
+        <is>
           <t>135.0</t>
         </is>
       </c>
-      <c r="CG2" t="inlineStr">
+      <c r="CH2" t="inlineStr">
         <is>
           <t>43.4</t>
         </is>
       </c>
-      <c r="CH2" t="inlineStr">
+      <c r="CI2" t="inlineStr">
         <is>
           <t>** 建材營造 - 工程承攬** 風力發電 - 塔架、電纜、其他配件</t>
         </is>
       </c>
-      <c r="CI2" t="inlineStr">
+      <c r="CJ2" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -1309,42 +1319,42 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
+          <t>3.41</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>1595.31</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>135.0</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>1712.06</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>130.5</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>3.33</t>
-        </is>
-      </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-1.56</t>
+          <t>-3.39</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>50.94</t>
+          <t>53.45</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1409,7 +1419,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-44.94</t>
+          <t>-43.04</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1419,17 +1429,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>7.08</t>
+          <t>6.60</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>-1.14</t>
+          <t>1.92</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1440,77 +1450,77 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>12</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>1595</t>
+          <t>1303</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>23.08</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>7.69</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>-4.26</t>
+          <t>1.20</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>-8.89</t>
+          <t>-10.06</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-7.5</t>
+          <t>-7.84</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>-5.97</t>
+          <t>-6.04</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>136.3</t>
+          <t>133.4</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>149.6</t>
+          <t>148.32</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>161.73</t>
+          <t>160.95</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>171.99</t>
+          <t>171.29</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>-28.35</t>
+          <t>-21.52</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>-8.34</t>
+          <t>-8.35</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>-6.50</t>
+          <t>-6.87</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1520,7 +1530,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-126.11</t>
+          <t>-127.59</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1530,198 +1540,203 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>1697184807.002158</t>
+          <t>1695120094.609914</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>223746689.0</t>
+          <t>212878160.0</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>397436778.6</t>
+          <t>421450515.0</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>263301806.5</t>
+          <t>274650710.4</t>
         </is>
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>254911229.58</t>
+          <t>254522728.7</t>
         </is>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>134134972</t>
+          <t>146799804</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>6892793.183689982</t>
-        </is>
-      </c>
-      <c r="BC3" t="n">
-        <v>27925349.17</v>
-      </c>
-      <c r="BD3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+          <t>8493004.331540482</t>
+        </is>
+      </c>
+      <c r="BC3" t="inlineStr">
+        <is>
+          <t>17294165.64471823</t>
+        </is>
+      </c>
+      <c r="BD3" t="n">
+        <v>212878160</v>
       </c>
       <c r="BE3" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF3" t="inlineStr">
+        <is>
           <t>180.0</t>
         </is>
       </c>
-      <c r="BF3" t="inlineStr">
+      <c r="BG3" t="inlineStr">
         <is>
           <t>2025/05/20</t>
         </is>
       </c>
-      <c r="BG3" t="inlineStr">
-        <is>
-          <t>-27.50</t>
-        </is>
-      </c>
       <c r="BH3" t="inlineStr">
         <is>
+          <t>-25.00</t>
+        </is>
+      </c>
+      <c r="BI3" t="inlineStr">
+        <is>
           <t>世紀鋼</t>
         </is>
       </c>
-      <c r="BI3" t="inlineStr">
+      <c r="BJ3" t="inlineStr">
         <is>
           <t>世紀鋼</t>
         </is>
       </c>
-      <c r="BJ3" t="inlineStr">
+      <c r="BK3" t="inlineStr">
         <is>
           <t>鋼鐵工業</t>
         </is>
       </c>
-      <c r="BK3" t="inlineStr">
+      <c r="BL3" t="inlineStr">
         <is>
           <t>上市</t>
         </is>
       </c>
-      <c r="BL3" t="inlineStr">
-        <is>
-          <t>0.98</t>
-        </is>
-      </c>
       <c r="BM3" t="inlineStr">
         <is>
+          <t>0.97</t>
+        </is>
+      </c>
+      <c r="BN3" t="inlineStr">
+        <is>
           <t>7.556077963084796</t>
         </is>
       </c>
-      <c r="BN3" t="inlineStr">
+      <c r="BO3" t="inlineStr">
         <is>
           <t>10.88205073781603</t>
         </is>
       </c>
-      <c r="BO3" t="inlineStr">
+      <c r="BP3" t="inlineStr">
         <is>
           <t>19.50943262662372</t>
         </is>
       </c>
-      <c r="BP3" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>價漲量縮</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;可能出現反轉訊號&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;3&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
         <is>
-          <t>3.01</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS3" t="inlineStr">
         <is>
+          <t>3.11</t>
+        </is>
+      </c>
+      <c r="BT3" t="inlineStr">
+        <is>
           <t>3.08</t>
         </is>
       </c>
-      <c r="BT3" t="inlineStr">
+      <c r="BU3" t="inlineStr">
         <is>
           <t>12.24</t>
         </is>
       </c>
-      <c r="BU3" t="inlineStr">
+      <c r="BV3" t="inlineStr">
         <is>
           <t>25.38</t>
         </is>
       </c>
-      <c r="BV3" t="inlineStr">
+      <c r="BW3" t="inlineStr">
         <is>
           <t>26.49%</t>
         </is>
       </c>
-      <c r="BW3" t="inlineStr">
+      <c r="BX3" t="inlineStr">
         <is>
           <t>15.03%</t>
         </is>
       </c>
-      <c r="BX3" t="inlineStr">
-        <is>
-          <t>28.82</t>
-        </is>
-      </c>
       <c r="BY3" t="inlineStr">
         <is>
+          <t>28.48</t>
+        </is>
+      </c>
+      <c r="BZ3" t="inlineStr">
+        <is>
           <t>33331</t>
         </is>
       </c>
-      <c r="BZ3" t="inlineStr">
+      <c r="CA3" t="inlineStr">
         <is>
           <t>風力發電鋼構工程88.69%、高樓建物鋼構工程10.17%、其他鋼構(含鋼品)0.82%、工業廠房鋼構工程0.16%、公共工程鋼構工程0.16% (2024年)</t>
         </is>
       </c>
-      <c r="CA3" t="inlineStr">
+      <c r="CB3" t="inlineStr">
         <is>
           <t>世紀鋼-鋼鐵工業-上市</t>
         </is>
       </c>
-      <c r="CB3" t="inlineStr">
+      <c r="CC3" t="inlineStr">
         <is>
           <t>鋼鐵工業右下上市</t>
         </is>
       </c>
-      <c r="CC3" t="inlineStr">
-        <is>
-          <t>131.0</t>
-        </is>
-      </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>133.5</t>
+          <t>132.0</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>129.0</t>
+          <t>136.0</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>130.5</t>
+          <t>131.5</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
         <is>
+          <t>135.0</t>
+        </is>
+      </c>
+      <c r="CH3" t="inlineStr">
+        <is>
           <t>43.4</t>
         </is>
       </c>
-      <c r="CH3" t="inlineStr">
+      <c r="CI3" t="inlineStr">
         <is>
           <t>** 建材營造 - 工程承攬** 風力發電 - 塔架、電纜、其他配件</t>
         </is>
       </c>
-      <c r="CI3" t="inlineStr">
+      <c r="CJ3" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -1740,12 +1755,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>-2.26</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2844.986</t>
+          <t>1712.06</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1770,12 +1785,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-1.56</t>
+          <t>-3.39</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>48.25</t>
+          <t>50.94</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1850,17 +1865,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11.77</t>
+          <t>7.08</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>-2.29</t>
+          <t>-1.14</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1871,12 +1886,12 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>12</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>1595</t>
+          <t>1303</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
@@ -1891,57 +1906,57 @@
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>-6.85</t>
+          <t>-4.26</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>-7.30</t>
+          <t>-8.89</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>-7.05</t>
+          <t>-7.5</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>-5.89</t>
+          <t>-5.97</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>140.1</t>
+          <t>136.3</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>151.12</t>
+          <t>149.6</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>162.59</t>
+          <t>161.73</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>172.77</t>
+          <t>171.99</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>-28.43</t>
+          <t>-28.35</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>-7.75</t>
+          <t>-8.34</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>-6.04</t>
+          <t>-6.50</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1951,7 +1966,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-124.26</t>
+          <t>-126.11</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1961,198 +1976,203 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>1697184807.002158</t>
+          <t>1695120094.609914</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>373359683.0</t>
+          <t>223746689.0</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>374444824.4</t>
+          <t>397436778.6</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>252575891.8</t>
+          <t>263301806.5</t>
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>255257682.72</t>
+          <t>254911229.58</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>121868932</t>
+          <t>134134972</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>3068692.09532273</t>
-        </is>
-      </c>
-      <c r="BC4" t="n">
-        <v>40950935.06</v>
-      </c>
-      <c r="BD4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+          <t>6892793.183689982</t>
+        </is>
+      </c>
+      <c r="BC4" t="inlineStr">
+        <is>
+          <t>27925349.16970986</t>
+        </is>
+      </c>
+      <c r="BD4" t="n">
+        <v>223746689</v>
       </c>
       <c r="BE4" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF4" t="inlineStr">
+        <is>
           <t>180.0</t>
         </is>
       </c>
-      <c r="BF4" t="inlineStr">
+      <c r="BG4" t="inlineStr">
         <is>
           <t>2025/05/20</t>
         </is>
       </c>
-      <c r="BG4" t="inlineStr">
+      <c r="BH4" t="inlineStr">
         <is>
           <t>-27.50</t>
         </is>
       </c>
-      <c r="BH4" t="inlineStr">
+      <c r="BI4" t="inlineStr">
         <is>
           <t>世紀鋼</t>
         </is>
       </c>
-      <c r="BI4" t="inlineStr">
+      <c r="BJ4" t="inlineStr">
         <is>
           <t>世紀鋼</t>
         </is>
       </c>
-      <c r="BJ4" t="inlineStr">
+      <c r="BK4" t="inlineStr">
         <is>
           <t>鋼鐵工業</t>
         </is>
       </c>
-      <c r="BK4" t="inlineStr">
+      <c r="BL4" t="inlineStr">
         <is>
           <t>上市</t>
         </is>
       </c>
-      <c r="BL4" t="inlineStr">
-        <is>
-          <t>0.98</t>
-        </is>
-      </c>
       <c r="BM4" t="inlineStr">
         <is>
+          <t>0.97</t>
+        </is>
+      </c>
+      <c r="BN4" t="inlineStr">
+        <is>
           <t>7.556077963084796</t>
         </is>
       </c>
-      <c r="BN4" t="inlineStr">
+      <c r="BO4" t="inlineStr">
         <is>
           <t>10.88205073781603</t>
         </is>
       </c>
-      <c r="BO4" t="inlineStr">
+      <c r="BP4" t="inlineStr">
         <is>
           <t>19.50943262662372</t>
         </is>
       </c>
-      <c r="BP4" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
-        </is>
-      </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
         <is>
+          <t>價漲量縮</t>
+        </is>
+      </c>
+      <c r="BS4" t="inlineStr">
+        <is>
           <t>3.01</t>
         </is>
       </c>
-      <c r="BS4" t="inlineStr">
+      <c r="BT4" t="inlineStr">
         <is>
           <t>3.08</t>
         </is>
       </c>
-      <c r="BT4" t="inlineStr">
+      <c r="BU4" t="inlineStr">
         <is>
           <t>12.24</t>
         </is>
       </c>
-      <c r="BU4" t="inlineStr">
+      <c r="BV4" t="inlineStr">
         <is>
           <t>25.38</t>
         </is>
       </c>
-      <c r="BV4" t="inlineStr">
+      <c r="BW4" t="inlineStr">
         <is>
           <t>26.49%</t>
         </is>
       </c>
-      <c r="BW4" t="inlineStr">
+      <c r="BX4" t="inlineStr">
         <is>
           <t>15.03%</t>
         </is>
       </c>
-      <c r="BX4" t="inlineStr">
-        <is>
-          <t>28.82</t>
-        </is>
-      </c>
       <c r="BY4" t="inlineStr">
         <is>
+          <t>28.48</t>
+        </is>
+      </c>
+      <c r="BZ4" t="inlineStr">
+        <is>
           <t>33331</t>
         </is>
       </c>
-      <c r="BZ4" t="inlineStr">
+      <c r="CA4" t="inlineStr">
         <is>
           <t>風力發電鋼構工程88.69%、高樓建物鋼構工程10.17%、其他鋼構(含鋼品)0.82%、工業廠房鋼構工程0.16%、公共工程鋼構工程0.16% (2024年)</t>
         </is>
       </c>
-      <c r="CA4" t="inlineStr">
+      <c r="CB4" t="inlineStr">
         <is>
           <t>世紀鋼-鋼鐵工業-上市</t>
         </is>
       </c>
-      <c r="CB4" t="inlineStr">
+      <c r="CC4" t="inlineStr">
         <is>
           <t>鋼鐵工業右下上市</t>
         </is>
       </c>
-      <c r="CC4" t="inlineStr">
-        <is>
-          <t>133.0</t>
-        </is>
-      </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>134.5</t>
+          <t>131.0</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>129.5</t>
+          <t>133.5</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
+          <t>129.0</t>
+        </is>
+      </c>
+      <c r="CG4" t="inlineStr">
+        <is>
           <t>130.5</t>
         </is>
       </c>
-      <c r="CG4" t="inlineStr">
+      <c r="CH4" t="inlineStr">
         <is>
           <t>43.4</t>
         </is>
       </c>
-      <c r="CH4" t="inlineStr">
+      <c r="CI4" t="inlineStr">
         <is>
           <t>** 建材營造 - 工程承攬** 風力發電 - 塔架、電纜、其他配件</t>
         </is>
       </c>
-      <c r="CI4" t="inlineStr">
+      <c r="CJ4" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -2171,12 +2191,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>-2.96</t>
+          <t>-2.26</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>4003.393</t>
+          <t>2844.986</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2186,7 +2206,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>133.5</t>
+          <t>130.5</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2196,17 +2216,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>1.11</t>
+          <t>3.33</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-1.56</t>
+          <t>-3.39</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>36.89</t>
+          <t>48.25</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2271,7 +2291,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-43.67</t>
+          <t>-44.94</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2281,17 +2301,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>16.56</t>
+          <t>11.77</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>-5.24</t>
+          <t>-2.29</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2302,12 +2322,12 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>12</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>1595</t>
+          <t>1303</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
@@ -2322,57 +2342,57 @@
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>-7.23</t>
+          <t>-6.85</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>-5.73</t>
+          <t>-7.30</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>-6.6</t>
+          <t>-7.05</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>-5.82</t>
+          <t>-5.89</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>143.9</t>
+          <t>140.1</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>152.65</t>
+          <t>151.12</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>163.44</t>
+          <t>162.59</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>173.54</t>
+          <t>172.77</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>-22.90</t>
+          <t>-28.43</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>-6.89</t>
+          <t>-7.75</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>-5.61</t>
+          <t>-6.04</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -2382,7 +2402,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-122.53</t>
+          <t>-124.26</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2392,198 +2412,203 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>1697184807.002158</t>
+          <t>1695120094.609914</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>543328425.0</t>
+          <t>373359683.0</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>317370279.0</t>
+          <t>374444824.4</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>231842549.9</t>
+          <t>252575891.8</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>254515985.98</t>
+          <t>255257682.72</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>85527729</t>
+          <t>121868932</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>-3818988.443072045</t>
-        </is>
-      </c>
-      <c r="BC5" t="n">
-        <v>42066417.86</v>
-      </c>
-      <c r="BD5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+          <t>3068692.09532273</t>
+        </is>
+      </c>
+      <c r="BC5" t="inlineStr">
+        <is>
+          <t>40950935.056494</t>
+        </is>
+      </c>
+      <c r="BD5" t="n">
+        <v>373359683</v>
       </c>
       <c r="BE5" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF5" t="inlineStr">
+        <is>
           <t>180.0</t>
         </is>
       </c>
-      <c r="BF5" t="inlineStr">
+      <c r="BG5" t="inlineStr">
         <is>
           <t>2025/05/20</t>
         </is>
       </c>
-      <c r="BG5" t="inlineStr">
-        <is>
-          <t>-25.83</t>
-        </is>
-      </c>
       <c r="BH5" t="inlineStr">
         <is>
+          <t>-27.50</t>
+        </is>
+      </c>
+      <c r="BI5" t="inlineStr">
+        <is>
           <t>世紀鋼</t>
         </is>
       </c>
-      <c r="BI5" t="inlineStr">
+      <c r="BJ5" t="inlineStr">
         <is>
           <t>世紀鋼</t>
         </is>
       </c>
-      <c r="BJ5" t="inlineStr">
+      <c r="BK5" t="inlineStr">
         <is>
           <t>鋼鐵工業</t>
         </is>
       </c>
-      <c r="BK5" t="inlineStr">
+      <c r="BL5" t="inlineStr">
         <is>
           <t>上市</t>
         </is>
       </c>
-      <c r="BL5" t="inlineStr">
-        <is>
-          <t>0.98</t>
-        </is>
-      </c>
       <c r="BM5" t="inlineStr">
         <is>
+          <t>0.97</t>
+        </is>
+      </c>
+      <c r="BN5" t="inlineStr">
+        <is>
           <t>7.556077963084796</t>
         </is>
       </c>
-      <c r="BN5" t="inlineStr">
+      <c r="BO5" t="inlineStr">
         <is>
           <t>10.88205073781603</t>
         </is>
       </c>
-      <c r="BO5" t="inlineStr">
+      <c r="BP5" t="inlineStr">
         <is>
           <t>19.50943262662372</t>
         </is>
       </c>
-      <c r="BP5" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;衝高回落,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
-        </is>
-      </c>
       <c r="BQ5" t="inlineStr">
         <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+        </is>
+      </c>
+      <c r="BR5" t="inlineStr">
+        <is>
           <t>價-量增</t>
         </is>
       </c>
-      <c r="BR5" t="inlineStr">
+      <c r="BS5" t="inlineStr">
+        <is>
+          <t>3.01</t>
+        </is>
+      </c>
+      <c r="BT5" t="inlineStr">
         <is>
           <t>3.08</t>
         </is>
       </c>
-      <c r="BS5" t="inlineStr">
-        <is>
-          <t>3.08</t>
-        </is>
-      </c>
-      <c r="BT5" t="inlineStr">
+      <c r="BU5" t="inlineStr">
         <is>
           <t>12.24</t>
         </is>
       </c>
-      <c r="BU5" t="inlineStr">
+      <c r="BV5" t="inlineStr">
         <is>
           <t>25.38</t>
         </is>
       </c>
-      <c r="BV5" t="inlineStr">
+      <c r="BW5" t="inlineStr">
         <is>
           <t>26.49%</t>
         </is>
       </c>
-      <c r="BW5" t="inlineStr">
+      <c r="BX5" t="inlineStr">
         <is>
           <t>15.03%</t>
         </is>
       </c>
-      <c r="BX5" t="inlineStr">
-        <is>
-          <t>28.82</t>
-        </is>
-      </c>
       <c r="BY5" t="inlineStr">
         <is>
+          <t>28.48</t>
+        </is>
+      </c>
+      <c r="BZ5" t="inlineStr">
+        <is>
           <t>33331</t>
         </is>
       </c>
-      <c r="BZ5" t="inlineStr">
+      <c r="CA5" t="inlineStr">
         <is>
           <t>風力發電鋼構工程88.69%、高樓建物鋼構工程10.17%、其他鋼構(含鋼品)0.82%、工業廠房鋼構工程0.16%、公共工程鋼構工程0.16% (2024年)</t>
         </is>
       </c>
-      <c r="CA5" t="inlineStr">
+      <c r="CB5" t="inlineStr">
         <is>
           <t>世紀鋼-鋼鐵工業-上市</t>
         </is>
       </c>
-      <c r="CB5" t="inlineStr">
+      <c r="CC5" t="inlineStr">
         <is>
           <t>鋼鐵工業右下上市</t>
         </is>
       </c>
-      <c r="CC5" t="inlineStr">
-        <is>
-          <t>135.0</t>
-        </is>
-      </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>141.5</t>
+          <t>133.0</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>132.5</t>
+          <t>134.5</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>133.5</t>
+          <t>129.5</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
         <is>
+          <t>130.5</t>
+        </is>
+      </c>
+      <c r="CH5" t="inlineStr">
+        <is>
           <t>43.4</t>
         </is>
       </c>
-      <c r="CH5" t="inlineStr">
+      <c r="CI5" t="inlineStr">
         <is>
           <t>** 建材營造 - 工程承攬** 風力發電 - 塔架、電纜、其他配件</t>
         </is>
       </c>
-      <c r="CI5" t="inlineStr">
+      <c r="CJ5" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -2602,12 +2627,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>-8.16</t>
+          <t>-2.96</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>5388.546</t>
+          <t>4003.393</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2617,7 +2642,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>137.5</t>
+          <t>133.5</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2627,17 +2652,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-1.85</t>
+          <t>1.11</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-1.56</t>
+          <t>-3.39</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>18.56</t>
+          <t>36.89</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2702,7 +2727,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-41.98</t>
+          <t>-43.67</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2712,17 +2737,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>22.28</t>
+          <t>16.56</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>-5.06</t>
+          <t>-5.24</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2733,12 +2758,12 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>12</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>1595</t>
+          <t>1303</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
@@ -2753,57 +2778,57 @@
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>-6.59</t>
+          <t>-7.23</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>-4.57</t>
+          <t>-5.73</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>-6.11</t>
+          <t>-6.6</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>-5.70</t>
+          <t>-5.82</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>147.2</t>
+          <t>143.9</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>154.25</t>
+          <t>152.65</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>164.29</t>
+          <t>163.44</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>174.21</t>
+          <t>173.54</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>-13.45</t>
+          <t>-22.90</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>-6.00</t>
+          <t>-6.89</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>-5.29</t>
+          <t>-5.61</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -2813,7 +2838,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-121.24</t>
+          <t>-122.53</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2823,115 +2848,115 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>1697184807.002158</t>
+          <t>1695120094.609914</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>753939618.0</t>
+          <t>543328425.0</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>239835367.0</t>
+          <t>317370279.0</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>202283159.5</t>
+          <t>231842549.9</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>250790390.86</t>
+          <t>254515985.98</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>37552207</t>
+          <t>85527729</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>-12161789.58854426</t>
-        </is>
-      </c>
-      <c r="BC6" t="n">
-        <v>23946656.01</v>
-      </c>
-      <c r="BD6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+          <t>-3818988.443072045</t>
+        </is>
+      </c>
+      <c r="BC6" t="inlineStr">
+        <is>
+          <t>42066417.85702515</t>
+        </is>
+      </c>
+      <c r="BD6" t="n">
+        <v>543328425</v>
       </c>
       <c r="BE6" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF6" t="inlineStr">
+        <is>
           <t>180.0</t>
         </is>
       </c>
-      <c r="BF6" t="inlineStr">
+      <c r="BG6" t="inlineStr">
         <is>
           <t>2025/05/20</t>
         </is>
       </c>
-      <c r="BG6" t="inlineStr">
-        <is>
-          <t>-23.61</t>
-        </is>
-      </c>
       <c r="BH6" t="inlineStr">
         <is>
+          <t>-25.83</t>
+        </is>
+      </c>
+      <c r="BI6" t="inlineStr">
+        <is>
           <t>世紀鋼</t>
         </is>
       </c>
-      <c r="BI6" t="inlineStr">
+      <c r="BJ6" t="inlineStr">
         <is>
           <t>世紀鋼</t>
         </is>
       </c>
-      <c r="BJ6" t="inlineStr">
+      <c r="BK6" t="inlineStr">
         <is>
           <t>鋼鐵工業</t>
         </is>
       </c>
-      <c r="BK6" t="inlineStr">
+      <c r="BL6" t="inlineStr">
         <is>
           <t>上市</t>
         </is>
       </c>
-      <c r="BL6" t="inlineStr">
-        <is>
-          <t>0.98</t>
-        </is>
-      </c>
       <c r="BM6" t="inlineStr">
         <is>
+          <t>0.97</t>
+        </is>
+      </c>
+      <c r="BN6" t="inlineStr">
+        <is>
           <t>7.556077963084796</t>
         </is>
       </c>
-      <c r="BN6" t="inlineStr">
+      <c r="BO6" t="inlineStr">
         <is>
           <t>10.88205073781603</t>
         </is>
       </c>
-      <c r="BO6" t="inlineStr">
+      <c r="BP6" t="inlineStr">
         <is>
           <t>19.50943262662372</t>
         </is>
       </c>
-      <c r="BP6" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>價跌量增</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;衝高回落,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
         <is>
-          <t>3.17</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS6" t="inlineStr">
@@ -2941,80 +2966,85 @@
       </c>
       <c r="BT6" t="inlineStr">
         <is>
+          <t>3.08</t>
+        </is>
+      </c>
+      <c r="BU6" t="inlineStr">
+        <is>
           <t>12.24</t>
         </is>
       </c>
-      <c r="BU6" t="inlineStr">
+      <c r="BV6" t="inlineStr">
         <is>
           <t>25.38</t>
         </is>
       </c>
-      <c r="BV6" t="inlineStr">
+      <c r="BW6" t="inlineStr">
         <is>
           <t>26.49%</t>
         </is>
       </c>
-      <c r="BW6" t="inlineStr">
+      <c r="BX6" t="inlineStr">
         <is>
           <t>15.03%</t>
         </is>
       </c>
-      <c r="BX6" t="inlineStr">
-        <is>
-          <t>28.82</t>
-        </is>
-      </c>
       <c r="BY6" t="inlineStr">
         <is>
+          <t>28.48</t>
+        </is>
+      </c>
+      <c r="BZ6" t="inlineStr">
+        <is>
           <t>33331</t>
         </is>
       </c>
-      <c r="BZ6" t="inlineStr">
+      <c r="CA6" t="inlineStr">
         <is>
           <t>風力發電鋼構工程88.69%、高樓建物鋼構工程10.17%、其他鋼構(含鋼品)0.82%、工業廠房鋼構工程0.16%、公共工程鋼構工程0.16% (2024年)</t>
         </is>
       </c>
-      <c r="CA6" t="inlineStr">
+      <c r="CB6" t="inlineStr">
         <is>
           <t>世紀鋼-鋼鐵工業-上市</t>
         </is>
       </c>
-      <c r="CB6" t="inlineStr">
+      <c r="CC6" t="inlineStr">
         <is>
           <t>鋼鐵工業右下上市</t>
         </is>
       </c>
-      <c r="CC6" t="inlineStr">
-        <is>
-          <t>147.0</t>
-        </is>
-      </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>147.0</t>
+          <t>135.0</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>135.0</t>
+          <t>141.5</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>137.5</t>
+          <t>132.5</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
         <is>
+          <t>133.5</t>
+        </is>
+      </c>
+      <c r="CH6" t="inlineStr">
+        <is>
           <t>43.4</t>
         </is>
       </c>
-      <c r="CH6" t="inlineStr">
+      <c r="CI6" t="inlineStr">
         <is>
           <t>** 建材營造 - 工程承攬** 風力發電 - 塔架、電纜、其他配件</t>
         </is>
       </c>
-      <c r="CI6" t="inlineStr">
+      <c r="CJ6" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -3033,12 +3063,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-8.16</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>617.888</t>
+          <t>5388.546</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3048,7 +3078,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>149.5</t>
+          <t>137.5</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3058,17 +3088,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-10.74</t>
+          <t>-1.85</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-1.56</t>
+          <t>-3.39</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>-14.19</t>
+          <t>18.56</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3133,7 +3163,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-36.92</t>
+          <t>-41.98</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3143,17 +3173,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>2.56</t>
+          <t>22.28</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>-1.34</t>
+          <t>-5.06</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3164,12 +3194,12 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>12</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>1595</t>
+          <t>1303</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
@@ -3184,57 +3214,57 @@
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>-0.07</t>
+          <t>-6.59</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>-3.96</t>
+          <t>-4.57</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>-5.65</t>
+          <t>-6.11</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>-5.63</t>
+          <t>-5.70</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>149.6</t>
+          <t>147.2</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>155.78</t>
+          <t>154.25</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>165.1</t>
+          <t>164.29</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>174.95</t>
+          <t>174.21</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>-1.33</t>
+          <t>-13.45</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>-5.18</t>
+          <t>-6.00</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>-5.11</t>
+          <t>-5.29</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -3244,7 +3274,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-120.53</t>
+          <t>-121.24</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3254,198 +3284,203 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>1697184807.002158</t>
+          <t>1695120094.609914</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>92809478.0</t>
+          <t>753939618.0</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>127850905.8</t>
+          <t>239835367.0</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>148995940.1</t>
+          <t>202283159.5</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>248204610.78</t>
+          <t>250790390.86</t>
         </is>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>-21145034</t>
+          <t>37552207</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>-18726961.5147791</t>
-        </is>
-      </c>
-      <c r="BC7" t="n">
-        <v>-25359440.75</v>
-      </c>
-      <c r="BD7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+          <t>-12161789.58854426</t>
+        </is>
+      </c>
+      <c r="BC7" t="inlineStr">
+        <is>
+          <t>23946656.00574735</t>
+        </is>
+      </c>
+      <c r="BD7" t="n">
+        <v>753939618</v>
       </c>
       <c r="BE7" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF7" t="inlineStr">
+        <is>
           <t>180.0</t>
         </is>
       </c>
-      <c r="BF7" t="inlineStr">
+      <c r="BG7" t="inlineStr">
         <is>
           <t>2025/05/20</t>
         </is>
       </c>
-      <c r="BG7" t="inlineStr">
-        <is>
-          <t>-16.94</t>
-        </is>
-      </c>
       <c r="BH7" t="inlineStr">
         <is>
+          <t>-23.61</t>
+        </is>
+      </c>
+      <c r="BI7" t="inlineStr">
+        <is>
           <t>世紀鋼</t>
         </is>
       </c>
-      <c r="BI7" t="inlineStr">
+      <c r="BJ7" t="inlineStr">
         <is>
           <t>世紀鋼</t>
         </is>
       </c>
-      <c r="BJ7" t="inlineStr">
+      <c r="BK7" t="inlineStr">
         <is>
           <t>鋼鐵工業</t>
         </is>
       </c>
-      <c r="BK7" t="inlineStr">
+      <c r="BL7" t="inlineStr">
         <is>
           <t>上市</t>
         </is>
       </c>
-      <c r="BL7" t="inlineStr">
-        <is>
-          <t>0.98</t>
-        </is>
-      </c>
       <c r="BM7" t="inlineStr">
         <is>
+          <t>0.97</t>
+        </is>
+      </c>
+      <c r="BN7" t="inlineStr">
+        <is>
           <t>7.556077963084796</t>
         </is>
       </c>
-      <c r="BN7" t="inlineStr">
+      <c r="BO7" t="inlineStr">
         <is>
           <t>10.88205073781603</t>
         </is>
       </c>
-      <c r="BO7" t="inlineStr">
+      <c r="BP7" t="inlineStr">
         <is>
           <t>19.50943262662372</t>
         </is>
       </c>
-      <c r="BP7" t="inlineStr">
+      <c r="BQ7" t="inlineStr">
         <is>
           <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
-      <c r="BQ7" t="inlineStr">
-        <is>
-          <t>價-量-</t>
-        </is>
-      </c>
       <c r="BR7" t="inlineStr">
         <is>
-          <t>3.44</t>
+          <t>價跌量增</t>
         </is>
       </c>
       <c r="BS7" t="inlineStr">
         <is>
+          <t>3.17</t>
+        </is>
+      </c>
+      <c r="BT7" t="inlineStr">
+        <is>
           <t>3.08</t>
         </is>
       </c>
-      <c r="BT7" t="inlineStr">
+      <c r="BU7" t="inlineStr">
         <is>
           <t>12.24</t>
         </is>
       </c>
-      <c r="BU7" t="inlineStr">
+      <c r="BV7" t="inlineStr">
         <is>
           <t>25.38</t>
         </is>
       </c>
-      <c r="BV7" t="inlineStr">
+      <c r="BW7" t="inlineStr">
         <is>
           <t>26.49%</t>
         </is>
       </c>
-      <c r="BW7" t="inlineStr">
+      <c r="BX7" t="inlineStr">
         <is>
           <t>15.03%</t>
         </is>
       </c>
-      <c r="BX7" t="inlineStr">
-        <is>
-          <t>28.82</t>
-        </is>
-      </c>
       <c r="BY7" t="inlineStr">
         <is>
+          <t>28.48</t>
+        </is>
+      </c>
+      <c r="BZ7" t="inlineStr">
+        <is>
           <t>33331</t>
         </is>
       </c>
-      <c r="BZ7" t="inlineStr">
+      <c r="CA7" t="inlineStr">
         <is>
           <t>風力發電鋼構工程88.69%、高樓建物鋼構工程10.17%、其他鋼構(含鋼品)0.82%、工業廠房鋼構工程0.16%、公共工程鋼構工程0.16% (2024年)</t>
         </is>
       </c>
-      <c r="CA7" t="inlineStr">
+      <c r="CB7" t="inlineStr">
         <is>
           <t>世紀鋼-鋼鐵工業-上市</t>
         </is>
       </c>
-      <c r="CB7" t="inlineStr">
+      <c r="CC7" t="inlineStr">
         <is>
           <t>鋼鐵工業右下上市</t>
         </is>
       </c>
-      <c r="CC7" t="inlineStr">
-        <is>
-          <t>150.0</t>
-        </is>
-      </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>151.5</t>
+          <t>147.0</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>149.5</t>
+          <t>147.0</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>149.5</t>
+          <t>135.0</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
         <is>
+          <t>137.5</t>
+        </is>
+      </c>
+      <c r="CH7" t="inlineStr">
+        <is>
           <t>43.4</t>
         </is>
       </c>
-      <c r="CH7" t="inlineStr">
+      <c r="CI7" t="inlineStr">
         <is>
           <t>** 建材營造 - 工程承攬** 風力發電 - 塔架、電纜、其他配件</t>
         </is>
       </c>
-      <c r="CI7" t="inlineStr">
+      <c r="CJ7" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -3469,7 +3504,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>723.545</t>
+          <t>617.888</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3494,12 +3529,12 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-1.56</t>
+          <t>-3.39</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>-23.11</t>
+          <t>-14.19</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3574,17 +3609,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>2.99</t>
+          <t>2.56</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>-1.67</t>
+          <t>-1.34</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3595,12 +3630,12 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>12</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>1595</t>
+          <t>1303</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
@@ -3610,62 +3645,62 @@
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>2.22</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>-0.47</t>
+          <t>-0.07</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>-4.07</t>
+          <t>-3.96</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>-5.55</t>
+          <t>-5.65</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>-5.58</t>
+          <t>-5.63</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>150.2</t>
+          <t>149.6</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>156.57</t>
+          <t>155.78</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>165.78</t>
+          <t>165.1</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>175.58</t>
+          <t>174.95</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>-3.60</t>
+          <t>-1.33</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>-5.28</t>
+          <t>-5.18</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>-5.09</t>
+          <t>-5.11</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -3675,7 +3710,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-120.46</t>
+          <t>-120.53</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3685,182 +3720,182 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>1697184807.002158</t>
+          <t>1695120094.609914</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>108786918.0</t>
+          <t>92809478.0</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>129166834.4</t>
+          <t>127850905.8</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>167987433.4</t>
+          <t>148995940.1</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>261232164.76</t>
+          <t>248204610.78</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>-38820599</t>
+          <t>-21145034</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>-17521056.19996015</t>
-        </is>
-      </c>
-      <c r="BC8" t="n">
-        <v>-24055655.37</v>
-      </c>
-      <c r="BD8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+          <t>-18726961.5147791</t>
+        </is>
+      </c>
+      <c r="BC8" t="inlineStr">
+        <is>
+          <t>-25359440.74628332</t>
+        </is>
+      </c>
+      <c r="BD8" t="n">
+        <v>92809478</v>
       </c>
       <c r="BE8" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF8" t="inlineStr">
+        <is>
           <t>180.0</t>
         </is>
       </c>
-      <c r="BF8" t="inlineStr">
+      <c r="BG8" t="inlineStr">
         <is>
           <t>2025/05/20</t>
         </is>
       </c>
-      <c r="BG8" t="inlineStr">
+      <c r="BH8" t="inlineStr">
         <is>
           <t>-16.94</t>
         </is>
       </c>
-      <c r="BH8" t="inlineStr">
+      <c r="BI8" t="inlineStr">
         <is>
           <t>世紀鋼</t>
         </is>
       </c>
-      <c r="BI8" t="inlineStr">
+      <c r="BJ8" t="inlineStr">
         <is>
           <t>世紀鋼</t>
         </is>
       </c>
-      <c r="BJ8" t="inlineStr">
+      <c r="BK8" t="inlineStr">
         <is>
           <t>鋼鐵工業</t>
         </is>
       </c>
-      <c r="BK8" t="inlineStr">
+      <c r="BL8" t="inlineStr">
         <is>
           <t>上市</t>
         </is>
       </c>
-      <c r="BL8" t="inlineStr">
-        <is>
-          <t>0.98</t>
-        </is>
-      </c>
       <c r="BM8" t="inlineStr">
         <is>
+          <t>0.97</t>
+        </is>
+      </c>
+      <c r="BN8" t="inlineStr">
+        <is>
           <t>7.556077963084796</t>
         </is>
       </c>
-      <c r="BN8" t="inlineStr">
+      <c r="BO8" t="inlineStr">
         <is>
           <t>10.88205073781603</t>
         </is>
       </c>
-      <c r="BO8" t="inlineStr">
+      <c r="BP8" t="inlineStr">
         <is>
           <t>19.50943262662372</t>
         </is>
       </c>
-      <c r="BP8" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
       <c r="BQ8" t="inlineStr">
         <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BR8" t="inlineStr">
+        <is>
           <t>價-量-</t>
         </is>
       </c>
-      <c r="BR8" t="inlineStr">
+      <c r="BS8" t="inlineStr">
         <is>
           <t>3.44</t>
         </is>
       </c>
-      <c r="BS8" t="inlineStr">
+      <c r="BT8" t="inlineStr">
         <is>
           <t>3.08</t>
         </is>
       </c>
-      <c r="BT8" t="inlineStr">
+      <c r="BU8" t="inlineStr">
         <is>
           <t>12.24</t>
         </is>
       </c>
-      <c r="BU8" t="inlineStr">
+      <c r="BV8" t="inlineStr">
         <is>
           <t>25.38</t>
         </is>
       </c>
-      <c r="BV8" t="inlineStr">
+      <c r="BW8" t="inlineStr">
         <is>
           <t>26.49%</t>
         </is>
       </c>
-      <c r="BW8" t="inlineStr">
+      <c r="BX8" t="inlineStr">
         <is>
           <t>15.03%</t>
         </is>
       </c>
-      <c r="BX8" t="inlineStr">
-        <is>
-          <t>28.82</t>
-        </is>
-      </c>
       <c r="BY8" t="inlineStr">
         <is>
+          <t>28.48</t>
+        </is>
+      </c>
+      <c r="BZ8" t="inlineStr">
+        <is>
           <t>33331</t>
         </is>
       </c>
-      <c r="BZ8" t="inlineStr">
+      <c r="CA8" t="inlineStr">
         <is>
           <t>風力發電鋼構工程88.69%、高樓建物鋼構工程10.17%、其他鋼構(含鋼品)0.82%、工業廠房鋼構工程0.16%、公共工程鋼構工程0.16% (2024年)</t>
         </is>
       </c>
-      <c r="CA8" t="inlineStr">
+      <c r="CB8" t="inlineStr">
         <is>
           <t>世紀鋼-鋼鐵工業-上市</t>
         </is>
       </c>
-      <c r="CB8" t="inlineStr">
+      <c r="CC8" t="inlineStr">
         <is>
           <t>鋼鐵工業右下上市</t>
         </is>
       </c>
-      <c r="CC8" t="inlineStr">
+      <c r="CD8" t="inlineStr">
+        <is>
+          <t>150.0</t>
+        </is>
+      </c>
+      <c r="CE8" t="inlineStr">
         <is>
           <t>151.5</t>
         </is>
       </c>
-      <c r="CD8" t="inlineStr">
-        <is>
-          <t>152.5</t>
-        </is>
-      </c>
-      <c r="CE8" t="inlineStr">
-        <is>
-          <t>149.0</t>
-        </is>
-      </c>
       <c r="CF8" t="inlineStr">
         <is>
           <t>149.5</t>
@@ -3868,15 +3903,20 @@
       </c>
       <c r="CG8" t="inlineStr">
         <is>
+          <t>149.5</t>
+        </is>
+      </c>
+      <c r="CH8" t="inlineStr">
+        <is>
           <t>43.4</t>
         </is>
       </c>
-      <c r="CH8" t="inlineStr">
+      <c r="CI8" t="inlineStr">
         <is>
           <t>** 建材營造 - 工程承攬** 風力發電 - 塔架、電纜、其他配件</t>
         </is>
       </c>
-      <c r="CI8" t="inlineStr">
+      <c r="CJ8" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -3895,12 +3935,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>-0.33</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>586.018</t>
+          <t>723.545</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3925,12 +3965,12 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-1.56</t>
+          <t>-3.39</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>-28.30</t>
+          <t>-23.11</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -4005,17 +4045,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>2.42</t>
+          <t>2.99</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>-1.34</t>
+          <t>-1.67</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4026,12 +4066,12 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>12</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>1595</t>
+          <t>1303</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
@@ -4046,57 +4086,57 @@
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>-0.86</t>
+          <t>-0.47</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>-4.25</t>
+          <t>-4.07</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>-5.43</t>
+          <t>-5.55</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>-5.49</t>
+          <t>-5.58</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>150.8</t>
+          <t>150.2</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>157.5</t>
+          <t>156.57</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>166.55</t>
+          <t>165.78</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>176.23</t>
+          <t>175.58</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>-5.51</t>
+          <t>-3.60</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>-5.32</t>
+          <t>-5.28</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>-5.05</t>
+          <t>-5.09</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -4106,7 +4146,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-120.28</t>
+          <t>-120.46</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4116,198 +4156,203 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>1697184807.002158</t>
+          <t>1695120094.609914</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>87986956.0</t>
+          <t>108786918.0</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>130706959.2</t>
+          <t>129166834.4</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>182292868.5</t>
+          <t>167987433.4</t>
         </is>
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>265109106.98</t>
+          <t>261232164.76</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>-51585909</t>
+          <t>-38820599</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>-16332947.26079137</t>
-        </is>
-      </c>
-      <c r="BC9" t="n">
-        <v>-23045842.84</v>
-      </c>
-      <c r="BD9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+          <t>-17521056.19996015</t>
+        </is>
+      </c>
+      <c r="BC9" t="inlineStr">
+        <is>
+          <t>-24055655.36538848</t>
+        </is>
+      </c>
+      <c r="BD9" t="n">
+        <v>108786918</v>
       </c>
       <c r="BE9" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF9" t="inlineStr">
+        <is>
           <t>180.0</t>
         </is>
       </c>
-      <c r="BF9" t="inlineStr">
+      <c r="BG9" t="inlineStr">
         <is>
           <t>2025/05/20</t>
         </is>
       </c>
-      <c r="BG9" t="inlineStr">
+      <c r="BH9" t="inlineStr">
         <is>
           <t>-16.94</t>
         </is>
       </c>
-      <c r="BH9" t="inlineStr">
+      <c r="BI9" t="inlineStr">
         <is>
           <t>世紀鋼</t>
         </is>
       </c>
-      <c r="BI9" t="inlineStr">
+      <c r="BJ9" t="inlineStr">
         <is>
           <t>世紀鋼</t>
         </is>
       </c>
-      <c r="BJ9" t="inlineStr">
+      <c r="BK9" t="inlineStr">
         <is>
           <t>鋼鐵工業</t>
         </is>
       </c>
-      <c r="BK9" t="inlineStr">
+      <c r="BL9" t="inlineStr">
         <is>
           <t>上市</t>
         </is>
       </c>
-      <c r="BL9" t="inlineStr">
-        <is>
-          <t>0.98</t>
-        </is>
-      </c>
       <c r="BM9" t="inlineStr">
         <is>
+          <t>0.97</t>
+        </is>
+      </c>
+      <c r="BN9" t="inlineStr">
+        <is>
           <t>7.556077963084796</t>
         </is>
       </c>
-      <c r="BN9" t="inlineStr">
+      <c r="BO9" t="inlineStr">
         <is>
           <t>10.88205073781603</t>
         </is>
       </c>
-      <c r="BO9" t="inlineStr">
+      <c r="BP9" t="inlineStr">
         <is>
           <t>19.50943262662372</t>
         </is>
       </c>
-      <c r="BP9" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
       <c r="BQ9" t="inlineStr">
         <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BR9" t="inlineStr">
+        <is>
           <t>價-量-</t>
         </is>
       </c>
-      <c r="BR9" t="inlineStr">
+      <c r="BS9" t="inlineStr">
         <is>
           <t>3.44</t>
         </is>
       </c>
-      <c r="BS9" t="inlineStr">
+      <c r="BT9" t="inlineStr">
         <is>
           <t>3.08</t>
         </is>
       </c>
-      <c r="BT9" t="inlineStr">
+      <c r="BU9" t="inlineStr">
         <is>
           <t>12.24</t>
         </is>
       </c>
-      <c r="BU9" t="inlineStr">
+      <c r="BV9" t="inlineStr">
         <is>
           <t>25.38</t>
         </is>
       </c>
-      <c r="BV9" t="inlineStr">
+      <c r="BW9" t="inlineStr">
         <is>
           <t>26.49%</t>
         </is>
       </c>
-      <c r="BW9" t="inlineStr">
+      <c r="BX9" t="inlineStr">
         <is>
           <t>15.03%</t>
         </is>
       </c>
-      <c r="BX9" t="inlineStr">
-        <is>
-          <t>28.82</t>
-        </is>
-      </c>
       <c r="BY9" t="inlineStr">
         <is>
+          <t>28.48</t>
+        </is>
+      </c>
+      <c r="BZ9" t="inlineStr">
+        <is>
           <t>33331</t>
         </is>
       </c>
-      <c r="BZ9" t="inlineStr">
+      <c r="CA9" t="inlineStr">
         <is>
           <t>風力發電鋼構工程88.69%、高樓建物鋼構工程10.17%、其他鋼構(含鋼品)0.82%、工業廠房鋼構工程0.16%、公共工程鋼構工程0.16% (2024年)</t>
         </is>
       </c>
-      <c r="CA9" t="inlineStr">
+      <c r="CB9" t="inlineStr">
         <is>
           <t>世紀鋼-鋼鐵工業-上市</t>
         </is>
       </c>
-      <c r="CB9" t="inlineStr">
+      <c r="CC9" t="inlineStr">
         <is>
           <t>鋼鐵工業右下上市</t>
         </is>
       </c>
-      <c r="CC9" t="inlineStr">
+      <c r="CD9" t="inlineStr">
         <is>
           <t>151.5</t>
         </is>
       </c>
-      <c r="CD9" t="inlineStr">
-        <is>
-          <t>151.5</t>
-        </is>
-      </c>
       <c r="CE9" t="inlineStr">
         <is>
+          <t>152.5</t>
+        </is>
+      </c>
+      <c r="CF9" t="inlineStr">
+        <is>
+          <t>149.0</t>
+        </is>
+      </c>
+      <c r="CG9" t="inlineStr">
+        <is>
           <t>149.5</t>
         </is>
       </c>
-      <c r="CF9" t="inlineStr">
-        <is>
-          <t>149.5</t>
-        </is>
-      </c>
-      <c r="CG9" t="inlineStr">
+      <c r="CH9" t="inlineStr">
         <is>
           <t>43.4</t>
         </is>
       </c>
-      <c r="CH9" t="inlineStr">
+      <c r="CI9" t="inlineStr">
         <is>
           <t>** 建材營造 - 工程承攬** 風力發電 - 塔架、電纜、其他配件</t>
         </is>
       </c>
-      <c r="CI9" t="inlineStr">
+      <c r="CJ9" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -4326,12 +4371,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>0.33</t>
+          <t>-0.33</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>1040.36</t>
+          <t>586.018</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4341,7 +4386,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>150.0</t>
+          <t>149.5</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4351,17 +4396,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-11.11</t>
+          <t>-10.74</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-1.56</t>
+          <t>-3.39</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>-24.53</t>
+          <t>-28.30</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4426,7 +4471,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-36.71</t>
+          <t>-36.92</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4436,17 +4481,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>4.30</t>
+          <t>2.42</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>1.39</t>
+          <t>-1.34</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4457,17 +4502,17 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>12</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>1595</t>
+          <t>1303</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>6.67</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
@@ -4477,57 +4522,57 @@
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>-1.12</t>
+          <t>-0.86</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>-4.31</t>
+          <t>-4.25</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>-5.31</t>
+          <t>-5.43</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>-5.34</t>
+          <t>-5.49</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>151.7</t>
+          <t>150.8</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>158.52</t>
+          <t>157.5</t>
         </is>
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>167.41</t>
+          <t>166.55</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>176.86</t>
+          <t>176.23</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>-6.68</t>
+          <t>-5.51</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>-5.31</t>
+          <t>-5.32</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>-4.98</t>
+          <t>-5.05</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -4537,7 +4582,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-120.00</t>
+          <t>-120.28</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4547,172 +4592,172 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>1697184807.002158</t>
+          <t>1695120094.609914</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>155653865.0</t>
+          <t>87986956.0</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>146314820.8</t>
+          <t>130706959.2</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>193869307.6</t>
+          <t>182292868.5</t>
         </is>
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>274342437.92</t>
+          <t>265109106.98</t>
         </is>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>-47554486</t>
+          <t>-51585909</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>-15112420.79113203</t>
-        </is>
-      </c>
-      <c r="BC10" t="n">
-        <v>-18551620.35</v>
-      </c>
-      <c r="BD10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+          <t>-16332947.26079137</t>
+        </is>
+      </c>
+      <c r="BC10" t="inlineStr">
+        <is>
+          <t>-23045842.8439177</t>
+        </is>
+      </c>
+      <c r="BD10" t="n">
+        <v>87986956</v>
       </c>
       <c r="BE10" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF10" t="inlineStr">
+        <is>
           <t>180.0</t>
         </is>
       </c>
-      <c r="BF10" t="inlineStr">
+      <c r="BG10" t="inlineStr">
         <is>
           <t>2025/05/20</t>
         </is>
       </c>
-      <c r="BG10" t="inlineStr">
-        <is>
-          <t>-16.67</t>
-        </is>
-      </c>
       <c r="BH10" t="inlineStr">
         <is>
+          <t>-16.94</t>
+        </is>
+      </c>
+      <c r="BI10" t="inlineStr">
+        <is>
           <t>世紀鋼</t>
         </is>
       </c>
-      <c r="BI10" t="inlineStr">
+      <c r="BJ10" t="inlineStr">
         <is>
           <t>世紀鋼</t>
         </is>
       </c>
-      <c r="BJ10" t="inlineStr">
+      <c r="BK10" t="inlineStr">
         <is>
           <t>鋼鐵工業</t>
         </is>
       </c>
-      <c r="BK10" t="inlineStr">
+      <c r="BL10" t="inlineStr">
         <is>
           <t>上市</t>
         </is>
       </c>
-      <c r="BL10" t="inlineStr">
-        <is>
-          <t>0.98</t>
-        </is>
-      </c>
       <c r="BM10" t="inlineStr">
         <is>
+          <t>0.97</t>
+        </is>
+      </c>
+      <c r="BN10" t="inlineStr">
+        <is>
           <t>7.556077963084796</t>
         </is>
       </c>
-      <c r="BN10" t="inlineStr">
+      <c r="BO10" t="inlineStr">
         <is>
           <t>10.88205073781603</t>
         </is>
       </c>
-      <c r="BO10" t="inlineStr">
+      <c r="BP10" t="inlineStr">
         <is>
           <t>19.50943262662372</t>
         </is>
       </c>
-      <c r="BP10" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;可能出現反轉訊號&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;3&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
       <c r="BQ10" t="inlineStr">
         <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BR10" t="inlineStr">
+        <is>
           <t>價-量增</t>
         </is>
       </c>
-      <c r="BR10" t="inlineStr">
-        <is>
-          <t>3.46</t>
-        </is>
-      </c>
       <c r="BS10" t="inlineStr">
         <is>
+          <t>3.44</t>
+        </is>
+      </c>
+      <c r="BT10" t="inlineStr">
+        <is>
           <t>3.08</t>
         </is>
       </c>
-      <c r="BT10" t="inlineStr">
+      <c r="BU10" t="inlineStr">
         <is>
           <t>12.24</t>
         </is>
       </c>
-      <c r="BU10" t="inlineStr">
+      <c r="BV10" t="inlineStr">
         <is>
           <t>25.38</t>
         </is>
       </c>
-      <c r="BV10" t="inlineStr">
+      <c r="BW10" t="inlineStr">
         <is>
           <t>26.49%</t>
         </is>
       </c>
-      <c r="BW10" t="inlineStr">
+      <c r="BX10" t="inlineStr">
         <is>
           <t>15.03%</t>
         </is>
       </c>
-      <c r="BX10" t="inlineStr">
-        <is>
-          <t>28.82</t>
-        </is>
-      </c>
       <c r="BY10" t="inlineStr">
         <is>
+          <t>28.48</t>
+        </is>
+      </c>
+      <c r="BZ10" t="inlineStr">
+        <is>
           <t>33331</t>
         </is>
       </c>
-      <c r="BZ10" t="inlineStr">
+      <c r="CA10" t="inlineStr">
         <is>
           <t>風力發電鋼構工程88.69%、高樓建物鋼構工程10.17%、其他鋼構(含鋼品)0.82%、工業廠房鋼構工程0.16%、公共工程鋼構工程0.16% (2024年)</t>
         </is>
       </c>
-      <c r="CA10" t="inlineStr">
+      <c r="CB10" t="inlineStr">
         <is>
           <t>世紀鋼-鋼鐵工業-上市</t>
         </is>
       </c>
-      <c r="CB10" t="inlineStr">
+      <c r="CC10" t="inlineStr">
         <is>
           <t>鋼鐵工業右下上市</t>
         </is>
       </c>
-      <c r="CC10" t="inlineStr">
-        <is>
-          <t>150.5</t>
-        </is>
-      </c>
       <c r="CD10" t="inlineStr">
         <is>
           <t>151.5</t>
@@ -4720,25 +4765,30 @@
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>146.5</t>
+          <t>151.5</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>150.0</t>
+          <t>149.5</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
         <is>
+          <t>149.5</t>
+        </is>
+      </c>
+      <c r="CH10" t="inlineStr">
+        <is>
           <t>43.4</t>
         </is>
       </c>
-      <c r="CH10" t="inlineStr">
+      <c r="CI10" t="inlineStr">
         <is>
           <t>** 建材營造 - 工程承攬** 風力發電 - 塔架、電纜、其他配件</t>
         </is>
       </c>
-      <c r="CI10" t="inlineStr">
+      <c r="CJ10" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -4757,12 +4807,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>-1.97</t>
+          <t>0.33</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>1294.619</t>
+          <t>1040.36</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4772,7 +4822,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>149.5</t>
+          <t>150.0</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4782,17 +4832,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-10.74</t>
+          <t>-11.11</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-1.56</t>
+          <t>-3.39</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>-16.90</t>
+          <t>-24.53</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4857,7 +4907,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-36.92</t>
+          <t>-36.71</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4867,17 +4917,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>5.35</t>
+          <t>4.30</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>-1.00</t>
+          <t>1.39</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4888,77 +4938,77 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>12</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>1595</t>
+          <t>1303</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>6.67</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>2.22</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>-2.35</t>
+          <t>-1.12</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>-3.97</t>
+          <t>-4.31</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>-5.19</t>
+          <t>-5.31</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>-5.28</t>
+          <t>-5.34</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>153.1</t>
+          <t>151.7</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>159.43</t>
+          <t>158.52</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>168.15</t>
+          <t>167.41</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>177.52</t>
+          <t>176.86</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>-7.56</t>
+          <t>-6.68</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>-5.26</t>
+          <t>-5.31</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>-4.89</t>
+          <t>-4.98</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -4968,7 +5018,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-119.66</t>
+          <t>-120.00</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -4978,198 +5028,203 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>1697184807.002158</t>
+          <t>1695120094.609914</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>194017312.0</t>
+          <t>155653865.0</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>164730952.0</t>
+          <t>146314820.8</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>198237890.5</t>
+          <t>193869307.6</t>
         </is>
       </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>287305576.32</t>
+          <t>274342437.92</t>
         </is>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>-33506938</t>
+          <t>-47554486</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>-14487111.77960444</t>
-        </is>
-      </c>
-      <c r="BC11" t="n">
-        <v>-18718770.61</v>
-      </c>
-      <c r="BD11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+          <t>-15112420.79113203</t>
+        </is>
+      </c>
+      <c r="BC11" t="inlineStr">
+        <is>
+          <t>-18551620.35453376</t>
+        </is>
+      </c>
+      <c r="BD11" t="n">
+        <v>155653865</v>
       </c>
       <c r="BE11" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF11" t="inlineStr">
+        <is>
           <t>180.0</t>
         </is>
       </c>
-      <c r="BF11" t="inlineStr">
+      <c r="BG11" t="inlineStr">
         <is>
           <t>2025/05/20</t>
         </is>
       </c>
-      <c r="BG11" t="inlineStr">
-        <is>
-          <t>-16.94</t>
-        </is>
-      </c>
       <c r="BH11" t="inlineStr">
         <is>
+          <t>-16.67</t>
+        </is>
+      </c>
+      <c r="BI11" t="inlineStr">
+        <is>
           <t>世紀鋼</t>
         </is>
       </c>
-      <c r="BI11" t="inlineStr">
+      <c r="BJ11" t="inlineStr">
         <is>
           <t>世紀鋼</t>
         </is>
       </c>
-      <c r="BJ11" t="inlineStr">
+      <c r="BK11" t="inlineStr">
         <is>
           <t>鋼鐵工業</t>
         </is>
       </c>
-      <c r="BK11" t="inlineStr">
+      <c r="BL11" t="inlineStr">
         <is>
           <t>上市</t>
         </is>
       </c>
-      <c r="BL11" t="inlineStr">
-        <is>
-          <t>0.98</t>
-        </is>
-      </c>
       <c r="BM11" t="inlineStr">
         <is>
+          <t>0.97</t>
+        </is>
+      </c>
+      <c r="BN11" t="inlineStr">
+        <is>
           <t>7.556077963084796</t>
         </is>
       </c>
-      <c r="BN11" t="inlineStr">
+      <c r="BO11" t="inlineStr">
         <is>
           <t>10.88205073781603</t>
         </is>
       </c>
-      <c r="BO11" t="inlineStr">
+      <c r="BP11" t="inlineStr">
         <is>
           <t>19.50943262662372</t>
         </is>
       </c>
-      <c r="BP11" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
       <c r="BQ11" t="inlineStr">
         <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;可能出現反轉訊號&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;3&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BR11" t="inlineStr">
+        <is>
           <t>價-量-</t>
         </is>
       </c>
-      <c r="BR11" t="inlineStr">
-        <is>
-          <t>3.44</t>
-        </is>
-      </c>
       <c r="BS11" t="inlineStr">
         <is>
+          <t>3.46</t>
+        </is>
+      </c>
+      <c r="BT11" t="inlineStr">
+        <is>
           <t>3.08</t>
         </is>
       </c>
-      <c r="BT11" t="inlineStr">
+      <c r="BU11" t="inlineStr">
         <is>
           <t>12.24</t>
         </is>
       </c>
-      <c r="BU11" t="inlineStr">
+      <c r="BV11" t="inlineStr">
         <is>
           <t>25.38</t>
         </is>
       </c>
-      <c r="BV11" t="inlineStr">
+      <c r="BW11" t="inlineStr">
         <is>
           <t>26.49%</t>
         </is>
       </c>
-      <c r="BW11" t="inlineStr">
+      <c r="BX11" t="inlineStr">
         <is>
           <t>15.03%</t>
         </is>
       </c>
-      <c r="BX11" t="inlineStr">
-        <is>
-          <t>28.82</t>
-        </is>
-      </c>
       <c r="BY11" t="inlineStr">
         <is>
+          <t>28.48</t>
+        </is>
+      </c>
+      <c r="BZ11" t="inlineStr">
+        <is>
           <t>33331</t>
         </is>
       </c>
-      <c r="BZ11" t="inlineStr">
+      <c r="CA11" t="inlineStr">
         <is>
           <t>風力發電鋼構工程88.69%、高樓建物鋼構工程10.17%、其他鋼構(含鋼品)0.82%、工業廠房鋼構工程0.16%、公共工程鋼構工程0.16% (2024年)</t>
         </is>
       </c>
-      <c r="CA11" t="inlineStr">
+      <c r="CB11" t="inlineStr">
         <is>
           <t>世紀鋼-鋼鐵工業-上市</t>
         </is>
       </c>
-      <c r="CB11" t="inlineStr">
+      <c r="CC11" t="inlineStr">
         <is>
           <t>鋼鐵工業右下上市</t>
         </is>
       </c>
-      <c r="CC11" t="inlineStr">
-        <is>
-          <t>152.0</t>
-        </is>
-      </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>152.0</t>
+          <t>150.5</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>148.5</t>
+          <t>151.5</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>149.5</t>
+          <t>146.5</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
         <is>
+          <t>150.0</t>
+        </is>
+      </c>
+      <c r="CH11" t="inlineStr">
+        <is>
           <t>43.4</t>
         </is>
       </c>
-      <c r="CH11" t="inlineStr">
+      <c r="CI11" t="inlineStr">
         <is>
           <t>** 建材營造 - 工程承攬** 風力發電 - 塔架、電纜、其他配件</t>
         </is>
       </c>
-      <c r="CI11" t="inlineStr">
+      <c r="CJ11" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -5188,12 +5243,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-1.97</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>653.151</t>
+          <t>1294.619</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5203,7 +5258,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>152.5</t>
+          <t>149.5</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5213,17 +5268,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-12.96</t>
+          <t>-10.74</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-1.56</t>
+          <t>-3.39</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>-18.28</t>
+          <t>-16.90</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5288,7 +5343,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-35.65</t>
+          <t>-36.92</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5298,17 +5353,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-06</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>2.70</t>
+          <t>5.35</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>-0.32</t>
+          <t>-1.00</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5319,12 +5374,12 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>12</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>1595</t>
+          <t>1303</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
@@ -5334,62 +5389,62 @@
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>2.38</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>-0.91</t>
+          <t>-2.35</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>-4.07</t>
+          <t>-3.97</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>-5.07</t>
+          <t>-5.19</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>-5.19</t>
+          <t>-5.28</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>153.9</t>
+          <t>153.1</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>160.43</t>
+          <t>159.43</t>
         </is>
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>169.0</t>
+          <t>168.15</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>178.25</t>
+          <t>177.52</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>-5.77</t>
+          <t>-7.56</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>-5.08</t>
+          <t>-5.26</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>-4.80</t>
+          <t>-4.89</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
@@ -5399,7 +5454,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-119.29</t>
+          <t>-119.66</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5409,198 +5464,203 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>1697184807.002158</t>
+          <t>1695120094.609914</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>99389121.0</t>
+          <t>194017312.0</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>170140974.4</t>
+          <t>164730952.0</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>208211819.2</t>
+          <t>198237890.5</t>
         </is>
       </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>301691507.7</t>
+          <t>287305576.32</t>
         </is>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>-38070844</t>
+          <t>-33506938</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>-13717719.26552568</t>
-        </is>
-      </c>
-      <c r="BC12" t="n">
-        <v>-22399398.48</v>
-      </c>
-      <c r="BD12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+          <t>-14487111.77960444</t>
+        </is>
+      </c>
+      <c r="BC12" t="inlineStr">
+        <is>
+          <t>-18718770.60703766</t>
+        </is>
+      </c>
+      <c r="BD12" t="n">
+        <v>194017312</v>
       </c>
       <c r="BE12" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF12" t="inlineStr">
+        <is>
           <t>180.0</t>
         </is>
       </c>
-      <c r="BF12" t="inlineStr">
+      <c r="BG12" t="inlineStr">
         <is>
           <t>2025/05/20</t>
         </is>
       </c>
-      <c r="BG12" t="inlineStr">
-        <is>
-          <t>-15.28</t>
-        </is>
-      </c>
       <c r="BH12" t="inlineStr">
         <is>
+          <t>-16.94</t>
+        </is>
+      </c>
+      <c r="BI12" t="inlineStr">
+        <is>
           <t>世紀鋼</t>
         </is>
       </c>
-      <c r="BI12" t="inlineStr">
+      <c r="BJ12" t="inlineStr">
         <is>
           <t>世紀鋼</t>
         </is>
       </c>
-      <c r="BJ12" t="inlineStr">
+      <c r="BK12" t="inlineStr">
         <is>
           <t>鋼鐵工業</t>
         </is>
       </c>
-      <c r="BK12" t="inlineStr">
+      <c r="BL12" t="inlineStr">
         <is>
           <t>上市</t>
         </is>
       </c>
-      <c r="BL12" t="inlineStr">
-        <is>
-          <t>0.98</t>
-        </is>
-      </c>
       <c r="BM12" t="inlineStr">
         <is>
+          <t>0.97</t>
+        </is>
+      </c>
+      <c r="BN12" t="inlineStr">
+        <is>
           <t>7.556077963084796</t>
         </is>
       </c>
-      <c r="BN12" t="inlineStr">
+      <c r="BO12" t="inlineStr">
         <is>
           <t>10.88205073781603</t>
         </is>
       </c>
-      <c r="BO12" t="inlineStr">
+      <c r="BP12" t="inlineStr">
         <is>
           <t>19.50943262662372</t>
         </is>
       </c>
-      <c r="BP12" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
       <c r="BQ12" t="inlineStr">
         <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BR12" t="inlineStr">
+        <is>
           <t>價-量-</t>
         </is>
       </c>
-      <c r="BR12" t="inlineStr">
-        <is>
-          <t>3.51</t>
-        </is>
-      </c>
       <c r="BS12" t="inlineStr">
         <is>
+          <t>3.44</t>
+        </is>
+      </c>
+      <c r="BT12" t="inlineStr">
+        <is>
           <t>3.08</t>
         </is>
       </c>
-      <c r="BT12" t="inlineStr">
+      <c r="BU12" t="inlineStr">
         <is>
           <t>12.24</t>
         </is>
       </c>
-      <c r="BU12" t="inlineStr">
+      <c r="BV12" t="inlineStr">
         <is>
           <t>25.38</t>
         </is>
       </c>
-      <c r="BV12" t="inlineStr">
+      <c r="BW12" t="inlineStr">
         <is>
           <t>26.49%</t>
         </is>
       </c>
-      <c r="BW12" t="inlineStr">
+      <c r="BX12" t="inlineStr">
         <is>
           <t>15.03%</t>
         </is>
       </c>
-      <c r="BX12" t="inlineStr">
-        <is>
-          <t>28.82</t>
-        </is>
-      </c>
       <c r="BY12" t="inlineStr">
         <is>
+          <t>28.48</t>
+        </is>
+      </c>
+      <c r="BZ12" t="inlineStr">
+        <is>
           <t>33331</t>
         </is>
       </c>
-      <c r="BZ12" t="inlineStr">
+      <c r="CA12" t="inlineStr">
         <is>
           <t>風力發電鋼構工程88.69%、高樓建物鋼構工程10.17%、其他鋼構(含鋼品)0.82%、工業廠房鋼構工程0.16%、公共工程鋼構工程0.16% (2024年)</t>
         </is>
       </c>
-      <c r="CA12" t="inlineStr">
+      <c r="CB12" t="inlineStr">
         <is>
           <t>世紀鋼-鋼鐵工業-上市</t>
         </is>
       </c>
-      <c r="CB12" t="inlineStr">
+      <c r="CC12" t="inlineStr">
         <is>
           <t>鋼鐵工業右下上市</t>
         </is>
       </c>
-      <c r="CC12" t="inlineStr">
-        <is>
-          <t>154.0</t>
-        </is>
-      </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>154.5</t>
+          <t>152.0</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>151.0</t>
+          <t>152.0</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>152.5</t>
+          <t>148.5</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
         <is>
+          <t>149.5</t>
+        </is>
+      </c>
+      <c r="CH12" t="inlineStr">
+        <is>
           <t>43.4</t>
         </is>
       </c>
-      <c r="CH12" t="inlineStr">
+      <c r="CI12" t="inlineStr">
         <is>
           <t>** 建材營造 - 工程承攬** 風力發電 - 塔架、電纜、其他配件</t>
         </is>
       </c>
-      <c r="CI12" t="inlineStr">
+      <c r="CJ12" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -5619,12 +5679,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>0.83</t>
+          <t>1.24</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>776.396</t>
+          <t>1128.761</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -5634,7 +5694,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>36.4</t>
+          <t>36.85</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -5649,12 +5709,12 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>-1.07</t>
+          <t>-1.23</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>9.74</t>
+          <t>-1.19</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -5719,7 +5779,7 @@
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>-15.64</t>
+          <t>-14.60</t>
         </is>
       </c>
       <c r="X13" t="inlineStr">
@@ -5729,17 +5789,17 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>8.27</t>
+          <t>12.03</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>0.70</t>
+          <t>2.09</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
@@ -5750,77 +5810,77 @@
       <c r="AC13" t="inlineStr"/>
       <c r="AD13" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
-          <t>776</t>
+          <t>1129</t>
         </is>
       </c>
       <c r="AF13" t="inlineStr">
         <is>
-          <t>11.76</t>
+          <t>37.5</t>
         </is>
       </c>
       <c r="AG13" t="inlineStr">
         <is>
-          <t>3.92</t>
+          <t>16.42</t>
         </is>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>-0.90</t>
+          <t>0.66</t>
         </is>
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>-4.83</t>
+          <t>-4.68</t>
         </is>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>-4.54</t>
+          <t>-4.69</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>-2.31</t>
+          <t>-2.48</t>
         </is>
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>36.73</t>
+          <t>36.61</t>
         </is>
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>38.6</t>
+          <t>38.41</t>
         </is>
       </c>
       <c r="AN13" t="inlineStr">
         <is>
-          <t>40.43</t>
+          <t>40.3</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>41.39</t>
+          <t>41.32</t>
         </is>
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>-19.31</t>
+          <t>-12.91</t>
         </is>
       </c>
       <c r="AQ13" t="inlineStr">
         <is>
-          <t>-1.15</t>
+          <t>-1.12</t>
         </is>
       </c>
       <c r="AR13" t="inlineStr">
         <is>
-          <t>-0.96</t>
+          <t>-0.99</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr">
@@ -5830,7 +5890,7 @@
       </c>
       <c r="AT13" t="inlineStr">
         <is>
-          <t>-135.75</t>
+          <t>-136.94</t>
         </is>
       </c>
       <c r="AU13" t="inlineStr">
@@ -5840,198 +5900,203 @@
       </c>
       <c r="AV13" t="inlineStr">
         <is>
-          <t>150535732.3834532</t>
+          <t>150408451.7952586</t>
         </is>
       </c>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>28176624.0</t>
+          <t>41298962.0</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>37871124.0</t>
+          <t>35487232.0</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>34509118.0</t>
+          <t>35914543.8</t>
         </is>
       </c>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>29545425.32</t>
+          <t>29950115.64</t>
         </is>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
-          <t>3362006</t>
+          <t>-427311</t>
         </is>
       </c>
       <c r="BB13" t="inlineStr">
         <is>
-          <t>956781.9001630185</t>
-        </is>
-      </c>
-      <c r="BC13" t="n">
-        <v>1376505.33</v>
-      </c>
-      <c r="BD13" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+          <t>1086319.424627111</t>
+        </is>
+      </c>
+      <c r="BC13" t="inlineStr">
+        <is>
+          <t>1798775.809179619</t>
+        </is>
+      </c>
+      <c r="BD13" t="n">
+        <v>41298962</v>
       </c>
       <c r="BE13" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF13" t="inlineStr">
+        <is>
           <t>41.5</t>
         </is>
       </c>
-      <c r="BF13" t="inlineStr">
+      <c r="BG13" t="inlineStr">
         <is>
           <t>2025/08/07</t>
         </is>
       </c>
-      <c r="BG13" t="inlineStr">
-        <is>
-          <t>-12.29</t>
-        </is>
-      </c>
       <c r="BH13" t="inlineStr">
         <is>
+          <t>-11.20</t>
+        </is>
+      </c>
+      <c r="BI13" t="inlineStr">
+        <is>
           <t>新光鋼</t>
         </is>
       </c>
-      <c r="BI13" t="inlineStr">
+      <c r="BJ13" t="inlineStr">
         <is>
           <t>新光鋼</t>
         </is>
       </c>
-      <c r="BJ13" t="inlineStr">
+      <c r="BK13" t="inlineStr">
         <is>
           <t>鋼鐵工業</t>
         </is>
       </c>
-      <c r="BK13" t="inlineStr">
+      <c r="BL13" t="inlineStr">
         <is>
           <t>上市</t>
         </is>
       </c>
-      <c r="BL13" t="inlineStr">
-        <is>
-          <t>0.63</t>
-        </is>
-      </c>
       <c r="BM13" t="inlineStr">
         <is>
+          <t>0.61</t>
+        </is>
+      </c>
+      <c r="BN13" t="inlineStr">
+        <is>
           <t>-13.67996844119094</t>
         </is>
       </c>
-      <c r="BN13" t="inlineStr">
+      <c r="BO13" t="inlineStr">
         <is>
           <t>-10.11024290164889</t>
         </is>
       </c>
-      <c r="BO13" t="inlineStr">
+      <c r="BP13" t="inlineStr">
         <is>
           <t>24.12947661306339</t>
         </is>
       </c>
-      <c r="BP13" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
       <c r="BQ13" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;可能出現反轉訊號&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;3&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR13" t="inlineStr">
         <is>
-          <t>1.00</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS13" t="inlineStr">
         <is>
-          <t>6.87</t>
+          <t>1.01</t>
         </is>
       </c>
       <c r="BT13" t="inlineStr">
         <is>
+          <t>6.78</t>
+        </is>
+      </c>
+      <c r="BU13" t="inlineStr">
+        <is>
           <t>11.90</t>
         </is>
       </c>
-      <c r="BU13" t="inlineStr">
-        <is>
-          <t>15.04</t>
-        </is>
-      </c>
       <c r="BV13" t="inlineStr">
         <is>
+          <t>15.23</t>
+        </is>
+      </c>
+      <c r="BW13" t="inlineStr">
+        <is>
           <t>8.69%</t>
         </is>
       </c>
-      <c r="BW13" t="inlineStr">
+      <c r="BX13" t="inlineStr">
         <is>
           <t>5.19%</t>
         </is>
       </c>
-      <c r="BX13" t="inlineStr">
-        <is>
-          <t>28.82</t>
-        </is>
-      </c>
       <c r="BY13" t="inlineStr">
         <is>
-          <t>11690</t>
+          <t>28.48</t>
         </is>
       </c>
       <c r="BZ13" t="inlineStr">
         <is>
+          <t>11834</t>
+        </is>
+      </c>
+      <c r="CA13" t="inlineStr">
+        <is>
           <t>鋼板38.80%、熱軋及鍍鋅鋼板33.80%、不�袗�板12.60%、特殊鋼板7.00%、加工及其他6.90%、型鋼0.90% (2024年)</t>
         </is>
       </c>
-      <c r="CA13" t="inlineStr">
+      <c r="CB13" t="inlineStr">
         <is>
           <t>新光鋼-鋼鐵工業-上市</t>
         </is>
       </c>
-      <c r="CB13" t="inlineStr">
+      <c r="CC13" t="inlineStr">
         <is>
           <t>鋼鐵工業右下上市</t>
         </is>
       </c>
-      <c r="CC13" t="inlineStr">
-        <is>
-          <t>36.3</t>
-        </is>
-      </c>
       <c r="CD13" t="inlineStr">
         <is>
-          <t>36.55</t>
+          <t>36.4</t>
         </is>
       </c>
       <c r="CE13" t="inlineStr">
         <is>
+          <t>36.95</t>
+        </is>
+      </c>
+      <c r="CF13" t="inlineStr">
+        <is>
           <t>36.0</t>
         </is>
       </c>
-      <c r="CF13" t="inlineStr">
-        <is>
-          <t>36.4</t>
-        </is>
-      </c>
       <c r="CG13" t="inlineStr">
         <is>
+          <t>36.85</t>
+        </is>
+      </c>
+      <c r="CH13" t="inlineStr">
+        <is>
           <t>36.35</t>
         </is>
       </c>
-      <c r="CH13" t="inlineStr">
+      <c r="CI13" t="inlineStr">
         <is>
           <t>** 鋼鐵 - 裁剪加工** 建材營造 - 基礎工程、結構工程** 太陽能產業 - 太陽能發電設備/系統及系統工程** 風力發電 - 鋼材、塔架、其他配件</t>
         </is>
       </c>
-      <c r="CI13" t="inlineStr">
+      <c r="CJ13" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -6050,12 +6115,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>-1.76</t>
+          <t>0.83</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>1212.053</t>
+          <t>776.396</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -6065,7 +6130,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>36.1</t>
+          <t>36.4</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -6075,17 +6140,17 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>0.82</t>
+          <t>1.22</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>-1.07</t>
+          <t>-1.23</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>3.03</t>
+          <t>9.74</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -6150,7 +6215,7 @@
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>-16.34</t>
+          <t>-15.64</t>
         </is>
       </c>
       <c r="X14" t="inlineStr">
@@ -6160,17 +6225,17 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>12.91</t>
+          <t>8.27</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>-1.38</t>
+          <t>0.70</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
@@ -6181,77 +6246,77 @@
       <c r="AC14" t="inlineStr"/>
       <c r="AD14" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
-          <t>776</t>
+          <t>1129</t>
         </is>
       </c>
       <c r="AF14" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>11.76</t>
         </is>
       </c>
       <c r="AG14" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>3.92</t>
         </is>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>-2.62</t>
+          <t>-0.90</t>
         </is>
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>-4.47</t>
+          <t>-4.83</t>
         </is>
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>-4.38</t>
+          <t>-4.54</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>-2.09</t>
+          <t>-2.31</t>
         </is>
       </c>
       <c r="AL14" t="inlineStr">
         <is>
-          <t>37.07000000000001</t>
+          <t>36.73</t>
         </is>
       </c>
       <c r="AM14" t="inlineStr">
         <is>
-          <t>38.8</t>
+          <t>38.6</t>
         </is>
       </c>
       <c r="AN14" t="inlineStr">
         <is>
-          <t>40.58</t>
+          <t>40.43</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>41.45</t>
+          <t>41.39</t>
         </is>
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>-22.07</t>
+          <t>-19.31</t>
         </is>
       </c>
       <c r="AQ14" t="inlineStr">
         <is>
-          <t>-1.12</t>
+          <t>-1.15</t>
         </is>
       </c>
       <c r="AR14" t="inlineStr">
         <is>
-          <t>-0.91</t>
+          <t>-0.96</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr">
@@ -6261,7 +6326,7 @@
       </c>
       <c r="AT14" t="inlineStr">
         <is>
-          <t>-134.02</t>
+          <t>-135.75</t>
         </is>
       </c>
       <c r="AU14" t="inlineStr">
@@ -6271,198 +6336,203 @@
       </c>
       <c r="AV14" t="inlineStr">
         <is>
-          <t>150535732.3834532</t>
+          <t>150408451.7952586</t>
         </is>
       </c>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>43823516.0</t>
+          <t>28176624.0</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>36085517.8</t>
+          <t>37871124.0</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
-          <t>35025550.9</t>
+          <t>34509118.0</t>
         </is>
       </c>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>29409986.0</t>
+          <t>29545425.32</t>
         </is>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
-          <t>1059966</t>
+          <t>3362006</t>
         </is>
       </c>
       <c r="BB14" t="inlineStr">
         <is>
-          <t>880468.5492293607</t>
-        </is>
-      </c>
-      <c r="BC14" t="n">
-        <v>2130065.67</v>
-      </c>
-      <c r="BD14" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+          <t>956781.9001630185</t>
+        </is>
+      </c>
+      <c r="BC14" t="inlineStr">
+        <is>
+          <t>1376505.330298137</t>
+        </is>
+      </c>
+      <c r="BD14" t="n">
+        <v>28176624</v>
       </c>
       <c r="BE14" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF14" t="inlineStr">
+        <is>
           <t>41.5</t>
         </is>
       </c>
-      <c r="BF14" t="inlineStr">
+      <c r="BG14" t="inlineStr">
         <is>
           <t>2025/08/07</t>
         </is>
       </c>
-      <c r="BG14" t="inlineStr">
-        <is>
-          <t>-13.01</t>
-        </is>
-      </c>
       <c r="BH14" t="inlineStr">
         <is>
+          <t>-12.29</t>
+        </is>
+      </c>
+      <c r="BI14" t="inlineStr">
+        <is>
           <t>新光鋼</t>
         </is>
       </c>
-      <c r="BI14" t="inlineStr">
+      <c r="BJ14" t="inlineStr">
         <is>
           <t>新光鋼</t>
         </is>
       </c>
-      <c r="BJ14" t="inlineStr">
+      <c r="BK14" t="inlineStr">
         <is>
           <t>鋼鐵工業</t>
         </is>
       </c>
-      <c r="BK14" t="inlineStr">
+      <c r="BL14" t="inlineStr">
         <is>
           <t>上市</t>
         </is>
       </c>
-      <c r="BL14" t="inlineStr">
-        <is>
-          <t>0.63</t>
-        </is>
-      </c>
       <c r="BM14" t="inlineStr">
         <is>
+          <t>0.61</t>
+        </is>
+      </c>
+      <c r="BN14" t="inlineStr">
+        <is>
           <t>-13.67996844119094</t>
         </is>
       </c>
-      <c r="BN14" t="inlineStr">
+      <c r="BO14" t="inlineStr">
         <is>
           <t>-10.11024290164889</t>
         </is>
       </c>
-      <c r="BO14" t="inlineStr">
+      <c r="BP14" t="inlineStr">
         <is>
           <t>24.12947661306339</t>
         </is>
       </c>
-      <c r="BP14" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
-        </is>
-      </c>
       <c r="BQ14" t="inlineStr">
         <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BR14" t="inlineStr">
+        <is>
           <t>價-量-</t>
         </is>
       </c>
-      <c r="BR14" t="inlineStr">
-        <is>
-          <t>0.99</t>
-        </is>
-      </c>
       <c r="BS14" t="inlineStr">
         <is>
-          <t>6.87</t>
+          <t>1.00</t>
         </is>
       </c>
       <c r="BT14" t="inlineStr">
         <is>
+          <t>6.78</t>
+        </is>
+      </c>
+      <c r="BU14" t="inlineStr">
+        <is>
           <t>11.90</t>
         </is>
       </c>
-      <c r="BU14" t="inlineStr">
-        <is>
-          <t>15.04</t>
-        </is>
-      </c>
       <c r="BV14" t="inlineStr">
         <is>
+          <t>15.23</t>
+        </is>
+      </c>
+      <c r="BW14" t="inlineStr">
+        <is>
           <t>8.69%</t>
         </is>
       </c>
-      <c r="BW14" t="inlineStr">
+      <c r="BX14" t="inlineStr">
         <is>
           <t>5.19%</t>
         </is>
       </c>
-      <c r="BX14" t="inlineStr">
-        <is>
-          <t>28.82</t>
-        </is>
-      </c>
       <c r="BY14" t="inlineStr">
         <is>
-          <t>11690</t>
+          <t>28.48</t>
         </is>
       </c>
       <c r="BZ14" t="inlineStr">
         <is>
+          <t>11834</t>
+        </is>
+      </c>
+      <c r="CA14" t="inlineStr">
+        <is>
           <t>鋼板38.80%、熱軋及鍍鋅鋼板33.80%、不�袗�板12.60%、特殊鋼板7.00%、加工及其他6.90%、型鋼0.90% (2024年)</t>
         </is>
       </c>
-      <c r="CA14" t="inlineStr">
+      <c r="CB14" t="inlineStr">
         <is>
           <t>新光鋼-鋼鐵工業-上市</t>
         </is>
       </c>
-      <c r="CB14" t="inlineStr">
+      <c r="CC14" t="inlineStr">
         <is>
           <t>鋼鐵工業右下上市</t>
         </is>
       </c>
-      <c r="CC14" t="inlineStr">
-        <is>
-          <t>36.85</t>
-        </is>
-      </c>
       <c r="CD14" t="inlineStr">
         <is>
-          <t>36.85</t>
+          <t>36.3</t>
         </is>
       </c>
       <c r="CE14" t="inlineStr">
         <is>
-          <t>35.85</t>
+          <t>36.55</t>
         </is>
       </c>
       <c r="CF14" t="inlineStr">
         <is>
-          <t>36.1</t>
+          <t>36.0</t>
         </is>
       </c>
       <c r="CG14" t="inlineStr">
         <is>
+          <t>36.4</t>
+        </is>
+      </c>
+      <c r="CH14" t="inlineStr">
+        <is>
           <t>36.35</t>
         </is>
       </c>
-      <c r="CH14" t="inlineStr">
+      <c r="CI14" t="inlineStr">
         <is>
           <t>** 鋼鐵 - 裁剪加工** 建材營造 - 基礎工程、結構工程** 太陽能產業 - 太陽能發電設備/系統及系統工程** 風力發電 - 鋼材、塔架、其他配件</t>
         </is>
       </c>
-      <c r="CI14" t="inlineStr">
+      <c r="CJ14" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -6481,12 +6551,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>-0.54</t>
+          <t>-1.76</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>672.504</t>
+          <t>1212.053</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -6496,7 +6566,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>36.75</t>
+          <t>36.1</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -6506,17 +6576,17 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>-0.96</t>
+          <t>2.04</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>-1.07</t>
+          <t>-1.23</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>-2.04</t>
+          <t>3.03</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -6581,7 +6651,7 @@
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>-14.83</t>
+          <t>-16.34</t>
         </is>
       </c>
       <c r="X15" t="inlineStr">
@@ -6591,17 +6661,17 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>7.17</t>
+          <t>12.91</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>-1.09</t>
+          <t>-1.38</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
@@ -6612,12 +6682,12 @@
       <c r="AC15" t="inlineStr"/>
       <c r="AD15" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
-          <t>776</t>
+          <t>1129</t>
         </is>
       </c>
       <c r="AF15" t="inlineStr">
@@ -6632,57 +6702,57 @@
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>-1.92</t>
+          <t>-2.62</t>
         </is>
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>-3.97</t>
+          <t>-4.47</t>
         </is>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>-4.25</t>
+          <t>-4.38</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>-1.83</t>
+          <t>-2.09</t>
         </is>
       </c>
       <c r="AL15" t="inlineStr">
         <is>
-          <t>37.47000000000001</t>
+          <t>37.07000000000001</t>
         </is>
       </c>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>39.02</t>
+          <t>38.8</t>
         </is>
       </c>
       <c r="AN15" t="inlineStr">
         <is>
-          <t>40.75</t>
+          <t>40.58</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>41.51</t>
+          <t>41.45</t>
         </is>
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>-19.33</t>
+          <t>-22.07</t>
         </is>
       </c>
       <c r="AQ15" t="inlineStr">
         <is>
-          <t>-1.03</t>
+          <t>-1.12</t>
         </is>
       </c>
       <c r="AR15" t="inlineStr">
         <is>
-          <t>-0.86</t>
+          <t>-0.91</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr">
@@ -6692,7 +6762,7 @@
       </c>
       <c r="AT15" t="inlineStr">
         <is>
-          <t>-132.14</t>
+          <t>-134.02</t>
         </is>
       </c>
       <c r="AU15" t="inlineStr">
@@ -6702,198 +6772,203 @@
       </c>
       <c r="AV15" t="inlineStr">
         <is>
-          <t>150535732.3834532</t>
+          <t>150408451.7952586</t>
         </is>
       </c>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>24762299.0</t>
+          <t>43823516.0</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>31929308.6</t>
+          <t>36085517.8</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>32595150.7</t>
+          <t>35025550.9</t>
         </is>
       </c>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>29130934.74</t>
+          <t>29409986.0</t>
         </is>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
-          <t>-665842</t>
+          <t>1059966</t>
         </is>
       </c>
       <c r="BB15" t="inlineStr">
         <is>
-          <t>653269.0727074891</t>
-        </is>
-      </c>
-      <c r="BC15" t="n">
-        <v>1454053.95</v>
-      </c>
-      <c r="BD15" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+          <t>880468.5492293607</t>
+        </is>
+      </c>
+      <c r="BC15" t="inlineStr">
+        <is>
+          <t>2130065.670099653</t>
+        </is>
+      </c>
+      <c r="BD15" t="n">
+        <v>43823516</v>
       </c>
       <c r="BE15" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF15" t="inlineStr">
+        <is>
           <t>41.5</t>
         </is>
       </c>
-      <c r="BF15" t="inlineStr">
+      <c r="BG15" t="inlineStr">
         <is>
           <t>2025/08/07</t>
         </is>
       </c>
-      <c r="BG15" t="inlineStr">
-        <is>
-          <t>-11.45</t>
-        </is>
-      </c>
       <c r="BH15" t="inlineStr">
         <is>
+          <t>-13.01</t>
+        </is>
+      </c>
+      <c r="BI15" t="inlineStr">
+        <is>
           <t>新光鋼</t>
         </is>
       </c>
-      <c r="BI15" t="inlineStr">
+      <c r="BJ15" t="inlineStr">
         <is>
           <t>新光鋼</t>
         </is>
       </c>
-      <c r="BJ15" t="inlineStr">
+      <c r="BK15" t="inlineStr">
         <is>
           <t>鋼鐵工業</t>
         </is>
       </c>
-      <c r="BK15" t="inlineStr">
+      <c r="BL15" t="inlineStr">
         <is>
           <t>上市</t>
         </is>
       </c>
-      <c r="BL15" t="inlineStr">
-        <is>
-          <t>0.63</t>
-        </is>
-      </c>
       <c r="BM15" t="inlineStr">
         <is>
+          <t>0.61</t>
+        </is>
+      </c>
+      <c r="BN15" t="inlineStr">
+        <is>
           <t>-13.67996844119094</t>
         </is>
       </c>
-      <c r="BN15" t="inlineStr">
+      <c r="BO15" t="inlineStr">
         <is>
           <t>-10.11024290164889</t>
         </is>
       </c>
-      <c r="BO15" t="inlineStr">
+      <c r="BP15" t="inlineStr">
         <is>
           <t>24.12947661306339</t>
         </is>
       </c>
-      <c r="BP15" t="inlineStr">
+      <c r="BQ15" t="inlineStr">
         <is>
           <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
-      <c r="BQ15" t="inlineStr">
+      <c r="BR15" t="inlineStr">
         <is>
           <t>價-量-</t>
         </is>
       </c>
-      <c r="BR15" t="inlineStr">
-        <is>
-          <t>1.01</t>
-        </is>
-      </c>
       <c r="BS15" t="inlineStr">
         <is>
-          <t>6.87</t>
+          <t>0.99</t>
         </is>
       </c>
       <c r="BT15" t="inlineStr">
         <is>
+          <t>6.78</t>
+        </is>
+      </c>
+      <c r="BU15" t="inlineStr">
+        <is>
           <t>11.90</t>
         </is>
       </c>
-      <c r="BU15" t="inlineStr">
-        <is>
-          <t>15.04</t>
-        </is>
-      </c>
       <c r="BV15" t="inlineStr">
         <is>
+          <t>15.23</t>
+        </is>
+      </c>
+      <c r="BW15" t="inlineStr">
+        <is>
           <t>8.69%</t>
         </is>
       </c>
-      <c r="BW15" t="inlineStr">
+      <c r="BX15" t="inlineStr">
         <is>
           <t>5.19%</t>
         </is>
       </c>
-      <c r="BX15" t="inlineStr">
-        <is>
-          <t>28.82</t>
-        </is>
-      </c>
       <c r="BY15" t="inlineStr">
         <is>
-          <t>11690</t>
+          <t>28.48</t>
         </is>
       </c>
       <c r="BZ15" t="inlineStr">
         <is>
+          <t>11834</t>
+        </is>
+      </c>
+      <c r="CA15" t="inlineStr">
+        <is>
           <t>鋼板38.80%、熱軋及鍍鋅鋼板33.80%、不�袗�板12.60%、特殊鋼板7.00%、加工及其他6.90%、型鋼0.90% (2024年)</t>
         </is>
       </c>
-      <c r="CA15" t="inlineStr">
+      <c r="CB15" t="inlineStr">
         <is>
           <t>新光鋼-鋼鐵工業-上市</t>
         </is>
       </c>
-      <c r="CB15" t="inlineStr">
+      <c r="CC15" t="inlineStr">
         <is>
           <t>鋼鐵工業右下上市</t>
         </is>
       </c>
-      <c r="CC15" t="inlineStr">
-        <is>
-          <t>36.95</t>
-        </is>
-      </c>
       <c r="CD15" t="inlineStr">
         <is>
-          <t>37.3</t>
+          <t>36.85</t>
         </is>
       </c>
       <c r="CE15" t="inlineStr">
         <is>
-          <t>36.6</t>
+          <t>36.85</t>
         </is>
       </c>
       <c r="CF15" t="inlineStr">
         <is>
-          <t>36.75</t>
+          <t>35.85</t>
         </is>
       </c>
       <c r="CG15" t="inlineStr">
         <is>
+          <t>36.1</t>
+        </is>
+      </c>
+      <c r="CH15" t="inlineStr">
+        <is>
           <t>36.35</t>
         </is>
       </c>
-      <c r="CH15" t="inlineStr">
+      <c r="CI15" t="inlineStr">
         <is>
           <t>** 鋼鐵 - 裁剪加工** 建材營造 - 基礎工程、結構工程** 太陽能產業 - 太陽能發電設備/系統及系統工程** 風力發電 - 鋼材、塔架、其他配件</t>
         </is>
       </c>
-      <c r="CI15" t="inlineStr">
+      <c r="CJ15" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -6912,12 +6987,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>-1.34</t>
+          <t>-0.54</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>1065.248</t>
+          <t>672.504</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -6927,7 +7002,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>36.95</t>
+          <t>36.75</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -6937,17 +7012,17 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>-1.51</t>
+          <t>0.27</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>-1.07</t>
+          <t>-1.23</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>28.28</t>
+          <t>-2.04</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -7012,7 +7087,7 @@
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>-14.37</t>
+          <t>-14.83</t>
         </is>
       </c>
       <c r="X16" t="inlineStr">
@@ -7022,17 +7097,17 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>11.35</t>
+          <t>7.17</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>-0.81</t>
+          <t>-1.09</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
@@ -7043,12 +7118,12 @@
       <c r="AC16" t="inlineStr"/>
       <c r="AD16" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
-          <t>776</t>
+          <t>1129</t>
         </is>
       </c>
       <c r="AF16" t="inlineStr">
@@ -7058,62 +7133,62 @@
       </c>
       <c r="AG16" t="inlineStr">
         <is>
-          <t>9.38</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>-1.86</t>
+          <t>-1.92</t>
         </is>
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>-4.02</t>
+          <t>-3.97</t>
         </is>
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>-4.09</t>
+          <t>-4.25</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>-1.60</t>
+          <t>-1.83</t>
         </is>
       </c>
       <c r="AL16" t="inlineStr">
         <is>
-          <t>37.65000000000001</t>
+          <t>37.47000000000001</t>
         </is>
       </c>
       <c r="AM16" t="inlineStr">
         <is>
-          <t>39.23</t>
+          <t>39.02</t>
         </is>
       </c>
       <c r="AN16" t="inlineStr">
         <is>
-          <t>40.9</t>
+          <t>40.75</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>41.57</t>
+          <t>41.51</t>
         </is>
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>-18.37</t>
+          <t>-19.33</t>
         </is>
       </c>
       <c r="AQ16" t="inlineStr">
         <is>
-          <t>-0.97</t>
+          <t>-1.03</t>
         </is>
       </c>
       <c r="AR16" t="inlineStr">
         <is>
-          <t>-0.82</t>
+          <t>-0.86</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr">
@@ -7123,7 +7198,7 @@
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>-130.59</t>
+          <t>-132.14</t>
         </is>
       </c>
       <c r="AU16" t="inlineStr">
@@ -7133,198 +7208,203 @@
       </c>
       <c r="AV16" t="inlineStr">
         <is>
-          <t>150535732.3834532</t>
+          <t>150408451.7952586</t>
         </is>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>39374759.0</t>
+          <t>24762299.0</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>40349216.0</t>
+          <t>31929308.6</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>31454761.9</t>
+          <t>32595150.7</t>
         </is>
       </c>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>29061426.18</t>
+          <t>29130934.74</t>
         </is>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
-          <t>8894454</t>
+          <t>-665842</t>
         </is>
       </c>
       <c r="BB16" t="inlineStr">
         <is>
-          <t>507671.8217403347</t>
-        </is>
-      </c>
-      <c r="BC16" t="n">
-        <v>2478665.68</v>
-      </c>
-      <c r="BD16" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+          <t>653269.0727074891</t>
+        </is>
+      </c>
+      <c r="BC16" t="inlineStr">
+        <is>
+          <t>1454053.953026839</t>
+        </is>
+      </c>
+      <c r="BD16" t="n">
+        <v>24762299</v>
       </c>
       <c r="BE16" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF16" t="inlineStr">
+        <is>
           <t>41.5</t>
         </is>
       </c>
-      <c r="BF16" t="inlineStr">
+      <c r="BG16" t="inlineStr">
         <is>
           <t>2025/08/07</t>
         </is>
       </c>
-      <c r="BG16" t="inlineStr">
-        <is>
-          <t>-10.96</t>
-        </is>
-      </c>
       <c r="BH16" t="inlineStr">
         <is>
+          <t>-11.45</t>
+        </is>
+      </c>
+      <c r="BI16" t="inlineStr">
+        <is>
           <t>新光鋼</t>
         </is>
       </c>
-      <c r="BI16" t="inlineStr">
+      <c r="BJ16" t="inlineStr">
         <is>
           <t>新光鋼</t>
         </is>
       </c>
-      <c r="BJ16" t="inlineStr">
+      <c r="BK16" t="inlineStr">
         <is>
           <t>鋼鐵工業</t>
         </is>
       </c>
-      <c r="BK16" t="inlineStr">
+      <c r="BL16" t="inlineStr">
         <is>
           <t>上市</t>
         </is>
       </c>
-      <c r="BL16" t="inlineStr">
-        <is>
-          <t>0.63</t>
-        </is>
-      </c>
       <c r="BM16" t="inlineStr">
         <is>
+          <t>0.61</t>
+        </is>
+      </c>
+      <c r="BN16" t="inlineStr">
+        <is>
           <t>-13.67996844119094</t>
         </is>
       </c>
-      <c r="BN16" t="inlineStr">
+      <c r="BO16" t="inlineStr">
         <is>
           <t>-10.11024290164889</t>
         </is>
       </c>
-      <c r="BO16" t="inlineStr">
+      <c r="BP16" t="inlineStr">
         <is>
           <t>24.12947661306339</t>
         </is>
       </c>
-      <c r="BP16" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
-        </is>
-      </c>
       <c r="BQ16" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR16" t="inlineStr">
         <is>
-          <t>1.02</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS16" t="inlineStr">
         <is>
-          <t>6.87</t>
+          <t>1.01</t>
         </is>
       </c>
       <c r="BT16" t="inlineStr">
         <is>
+          <t>6.78</t>
+        </is>
+      </c>
+      <c r="BU16" t="inlineStr">
+        <is>
           <t>11.90</t>
         </is>
       </c>
-      <c r="BU16" t="inlineStr">
-        <is>
-          <t>15.04</t>
-        </is>
-      </c>
       <c r="BV16" t="inlineStr">
         <is>
+          <t>15.23</t>
+        </is>
+      </c>
+      <c r="BW16" t="inlineStr">
+        <is>
           <t>8.69%</t>
         </is>
       </c>
-      <c r="BW16" t="inlineStr">
+      <c r="BX16" t="inlineStr">
         <is>
           <t>5.19%</t>
         </is>
       </c>
-      <c r="BX16" t="inlineStr">
-        <is>
-          <t>28.82</t>
-        </is>
-      </c>
       <c r="BY16" t="inlineStr">
         <is>
-          <t>11690</t>
+          <t>28.48</t>
         </is>
       </c>
       <c r="BZ16" t="inlineStr">
         <is>
+          <t>11834</t>
+        </is>
+      </c>
+      <c r="CA16" t="inlineStr">
+        <is>
           <t>鋼板38.80%、熱軋及鍍鋅鋼板33.80%、不�袗�板12.60%、特殊鋼板7.00%、加工及其他6.90%、型鋼0.90% (2024年)</t>
         </is>
       </c>
-      <c r="CA16" t="inlineStr">
+      <c r="CB16" t="inlineStr">
         <is>
           <t>新光鋼-鋼鐵工業-上市</t>
         </is>
       </c>
-      <c r="CB16" t="inlineStr">
+      <c r="CC16" t="inlineStr">
         <is>
           <t>鋼鐵工業右下上市</t>
         </is>
       </c>
-      <c r="CC16" t="inlineStr">
+      <c r="CD16" t="inlineStr">
+        <is>
+          <t>36.95</t>
+        </is>
+      </c>
+      <c r="CE16" t="inlineStr">
         <is>
           <t>37.3</t>
         </is>
       </c>
-      <c r="CD16" t="inlineStr">
-        <is>
-          <t>37.5</t>
-        </is>
-      </c>
-      <c r="CE16" t="inlineStr">
-        <is>
-          <t>36.7</t>
-        </is>
-      </c>
       <c r="CF16" t="inlineStr">
         <is>
-          <t>36.95</t>
+          <t>36.6</t>
         </is>
       </c>
       <c r="CG16" t="inlineStr">
         <is>
+          <t>36.75</t>
+        </is>
+      </c>
+      <c r="CH16" t="inlineStr">
+        <is>
           <t>36.35</t>
         </is>
       </c>
-      <c r="CH16" t="inlineStr">
+      <c r="CI16" t="inlineStr">
         <is>
           <t>** 鋼鐵 - 裁剪加工** 建材營造 - 基礎工程、結構工程** 太陽能產業 - 太陽能發電設備/系統及系統工程** 風力發電 - 鋼材、塔架、其他配件</t>
         </is>
       </c>
-      <c r="CI16" t="inlineStr">
+      <c r="CJ16" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -7343,12 +7423,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>-1.71</t>
+          <t>-1.34</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>1408.733</t>
+          <t>1065.248</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -7358,7 +7438,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>37.45</t>
+          <t>36.95</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -7368,17 +7448,17 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>-2.88</t>
+          <t>-0.27</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>-1.07</t>
+          <t>-1.23</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>22.93</t>
+          <t>28.28</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -7443,7 +7523,7 @@
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>-13.21</t>
+          <t>-14.37</t>
         </is>
       </c>
       <c r="X17" t="inlineStr">
@@ -7453,17 +7533,17 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>15.01</t>
+          <t>11.35</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>-2.94</t>
+          <t>-0.81</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
@@ -7474,12 +7554,12 @@
       <c r="AC17" t="inlineStr"/>
       <c r="AD17" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
-          <t>776</t>
+          <t>1129</t>
         </is>
       </c>
       <c r="AF17" t="inlineStr">
@@ -7489,62 +7569,62 @@
       </c>
       <c r="AG17" t="inlineStr">
         <is>
-          <t>16.69</t>
+          <t>9.38</t>
         </is>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>-1.42</t>
+          <t>-1.86</t>
         </is>
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>-3.63</t>
+          <t>-4.02</t>
         </is>
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>-3.96</t>
+          <t>-4.09</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>-1.34</t>
+          <t>-1.60</t>
         </is>
       </c>
       <c r="AL17" t="inlineStr">
         <is>
-          <t>37.99</t>
+          <t>37.65000000000001</t>
         </is>
       </c>
       <c r="AM17" t="inlineStr">
         <is>
-          <t>39.42</t>
+          <t>39.23</t>
         </is>
       </c>
       <c r="AN17" t="inlineStr">
         <is>
-          <t>41.05</t>
+          <t>40.9</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>41.6</t>
+          <t>41.57</t>
         </is>
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>-15.49</t>
+          <t>-18.37</t>
         </is>
       </c>
       <c r="AQ17" t="inlineStr">
         <is>
-          <t>-0.91</t>
+          <t>-0.97</t>
         </is>
       </c>
       <c r="AR17" t="inlineStr">
         <is>
-          <t>-0.78</t>
+          <t>-0.82</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr">
@@ -7554,7 +7634,7 @@
       </c>
       <c r="AT17" t="inlineStr">
         <is>
-          <t>-129.19</t>
+          <t>-130.59</t>
         </is>
       </c>
       <c r="AU17" t="inlineStr">
@@ -7564,198 +7644,203 @@
       </c>
       <c r="AV17" t="inlineStr">
         <is>
-          <t>150535732.3834532</t>
+          <t>150408451.7952586</t>
         </is>
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>53218422.0</t>
+          <t>39374759.0</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>36341855.6</t>
+          <t>40349216.0</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>29562657.9</t>
+          <t>31454761.9</t>
         </is>
       </c>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>28846965.04</t>
+          <t>29061426.18</t>
         </is>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
-          <t>6779197</t>
+          <t>8894454</t>
         </is>
       </c>
       <c r="BB17" t="inlineStr">
         <is>
-          <t>149309.3019995387</t>
-        </is>
-      </c>
-      <c r="BC17" t="n">
-        <v>2288252.23</v>
-      </c>
-      <c r="BD17" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+          <t>507671.8217403347</t>
+        </is>
+      </c>
+      <c r="BC17" t="inlineStr">
+        <is>
+          <t>2478665.680314712</t>
+        </is>
+      </c>
+      <c r="BD17" t="n">
+        <v>39374759</v>
       </c>
       <c r="BE17" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF17" t="inlineStr">
+        <is>
           <t>41.5</t>
         </is>
       </c>
-      <c r="BF17" t="inlineStr">
+      <c r="BG17" t="inlineStr">
         <is>
           <t>2025/08/07</t>
         </is>
       </c>
-      <c r="BG17" t="inlineStr">
-        <is>
-          <t>-9.76</t>
-        </is>
-      </c>
       <c r="BH17" t="inlineStr">
         <is>
+          <t>-10.96</t>
+        </is>
+      </c>
+      <c r="BI17" t="inlineStr">
+        <is>
           <t>新光鋼</t>
         </is>
       </c>
-      <c r="BI17" t="inlineStr">
+      <c r="BJ17" t="inlineStr">
         <is>
           <t>新光鋼</t>
         </is>
       </c>
-      <c r="BJ17" t="inlineStr">
+      <c r="BK17" t="inlineStr">
         <is>
           <t>鋼鐵工業</t>
         </is>
       </c>
-      <c r="BK17" t="inlineStr">
+      <c r="BL17" t="inlineStr">
         <is>
           <t>上市</t>
         </is>
       </c>
-      <c r="BL17" t="inlineStr">
-        <is>
-          <t>0.63</t>
-        </is>
-      </c>
       <c r="BM17" t="inlineStr">
         <is>
+          <t>0.61</t>
+        </is>
+      </c>
+      <c r="BN17" t="inlineStr">
+        <is>
           <t>-13.67996844119094</t>
         </is>
       </c>
-      <c r="BN17" t="inlineStr">
+      <c r="BO17" t="inlineStr">
         <is>
           <t>-10.11024290164889</t>
         </is>
       </c>
-      <c r="BO17" t="inlineStr">
+      <c r="BP17" t="inlineStr">
         <is>
           <t>24.12947661306339</t>
         </is>
       </c>
-      <c r="BP17" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
       <c r="BQ17" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR17" t="inlineStr">
         <is>
-          <t>1.03</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS17" t="inlineStr">
         <is>
-          <t>6.87</t>
+          <t>1.02</t>
         </is>
       </c>
       <c r="BT17" t="inlineStr">
         <is>
+          <t>6.78</t>
+        </is>
+      </c>
+      <c r="BU17" t="inlineStr">
+        <is>
           <t>11.90</t>
         </is>
       </c>
-      <c r="BU17" t="inlineStr">
-        <is>
-          <t>15.04</t>
-        </is>
-      </c>
       <c r="BV17" t="inlineStr">
         <is>
+          <t>15.23</t>
+        </is>
+      </c>
+      <c r="BW17" t="inlineStr">
+        <is>
           <t>8.69%</t>
         </is>
       </c>
-      <c r="BW17" t="inlineStr">
+      <c r="BX17" t="inlineStr">
         <is>
           <t>5.19%</t>
         </is>
       </c>
-      <c r="BX17" t="inlineStr">
-        <is>
-          <t>28.82</t>
-        </is>
-      </c>
       <c r="BY17" t="inlineStr">
         <is>
-          <t>11690</t>
+          <t>28.48</t>
         </is>
       </c>
       <c r="BZ17" t="inlineStr">
         <is>
+          <t>11834</t>
+        </is>
+      </c>
+      <c r="CA17" t="inlineStr">
+        <is>
           <t>鋼板38.80%、熱軋及鍍鋅鋼板33.80%、不�袗�板12.60%、特殊鋼板7.00%、加工及其他6.90%、型鋼0.90% (2024年)</t>
         </is>
       </c>
-      <c r="CA17" t="inlineStr">
+      <c r="CB17" t="inlineStr">
         <is>
           <t>新光鋼-鋼鐵工業-上市</t>
         </is>
       </c>
-      <c r="CB17" t="inlineStr">
+      <c r="CC17" t="inlineStr">
         <is>
           <t>鋼鐵工業右下上市</t>
         </is>
       </c>
-      <c r="CC17" t="inlineStr">
-        <is>
-          <t>38.1</t>
-        </is>
-      </c>
       <c r="CD17" t="inlineStr">
         <is>
-          <t>38.7</t>
+          <t>37.3</t>
         </is>
       </c>
       <c r="CE17" t="inlineStr">
         <is>
-          <t>37.3</t>
+          <t>37.5</t>
         </is>
       </c>
       <c r="CF17" t="inlineStr">
         <is>
-          <t>37.45</t>
+          <t>36.7</t>
         </is>
       </c>
       <c r="CG17" t="inlineStr">
         <is>
+          <t>36.95</t>
+        </is>
+      </c>
+      <c r="CH17" t="inlineStr">
+        <is>
           <t>36.35</t>
         </is>
       </c>
-      <c r="CH17" t="inlineStr">
+      <c r="CI17" t="inlineStr">
         <is>
           <t>** 鋼鐵 - 裁剪加工** 建材營造 - 基礎工程、結構工程** 太陽能產業 - 太陽能發電設備/系統及系統工程** 風力發電 - 鋼材、塔架、其他配件</t>
         </is>
       </c>
-      <c r="CI17" t="inlineStr">
+      <c r="CJ17" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -7774,12 +7859,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-1.71</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>504.317</t>
+          <t>1408.733</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -7789,7 +7874,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>38.1</t>
+          <t>37.45</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -7799,17 +7884,17 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>-4.67</t>
+          <t>-1.63</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>-1.07</t>
+          <t>-1.23</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>20.39</t>
+          <t>22.93</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -7874,7 +7959,7 @@
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>-11.70</t>
+          <t>-13.21</t>
         </is>
       </c>
       <c r="X18" t="inlineStr">
@@ -7884,17 +7969,17 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>5.37</t>
+          <t>15.01</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>-0.39</t>
+          <t>-2.94</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
@@ -7905,17 +7990,17 @@
       <c r="AC18" t="inlineStr"/>
       <c r="AD18" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
-          <t>776</t>
+          <t>1129</t>
         </is>
       </c>
       <c r="AF18" t="inlineStr">
         <is>
-          <t>28.13</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG18" t="inlineStr">
@@ -7925,57 +8010,57 @@
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>-0.55</t>
+          <t>-1.42</t>
         </is>
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>-3.22</t>
+          <t>-3.63</t>
         </is>
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>-3.86</t>
+          <t>-3.96</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>-1.12</t>
+          <t>-1.34</t>
         </is>
       </c>
       <c r="AL18" t="inlineStr">
         <is>
-          <t>38.31</t>
+          <t>37.99</t>
         </is>
       </c>
       <c r="AM18" t="inlineStr">
         <is>
-          <t>39.58</t>
+          <t>39.42</t>
         </is>
       </c>
       <c r="AN18" t="inlineStr">
         <is>
-          <t>41.17</t>
+          <t>41.05</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>41.64</t>
+          <t>41.6</t>
         </is>
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>-13.76</t>
+          <t>-15.49</t>
         </is>
       </c>
       <c r="AQ18" t="inlineStr">
         <is>
-          <t>-0.86</t>
+          <t>-0.91</t>
         </is>
       </c>
       <c r="AR18" t="inlineStr">
         <is>
-          <t>-0.75</t>
+          <t>-0.78</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr">
@@ -7985,7 +8070,7 @@
       </c>
       <c r="AT18" t="inlineStr">
         <is>
-          <t>-128.06</t>
+          <t>-129.19</t>
         </is>
       </c>
       <c r="AU18" t="inlineStr">
@@ -7995,198 +8080,203 @@
       </c>
       <c r="AV18" t="inlineStr">
         <is>
-          <t>150535732.3834532</t>
+          <t>150408451.7952586</t>
         </is>
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>19248593.0</t>
+          <t>53218422.0</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>31147112.0</t>
+          <t>36341855.6</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>25871081.1</t>
+          <t>29562657.9</t>
         </is>
       </c>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>28091032.78</t>
+          <t>28846965.04</t>
         </is>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
-          <t>5276030</t>
+          <t>6779197</t>
         </is>
       </c>
       <c r="BB18" t="inlineStr">
         <is>
-          <t>-239589.4123123131</t>
-        </is>
-      </c>
-      <c r="BC18" t="n">
-        <v>451260.12</v>
-      </c>
-      <c r="BD18" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+          <t>149309.3019995387</t>
+        </is>
+      </c>
+      <c r="BC18" t="inlineStr">
+        <is>
+          <t>2288252.230714723</t>
+        </is>
+      </c>
+      <c r="BD18" t="n">
+        <v>53218422</v>
       </c>
       <c r="BE18" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF18" t="inlineStr">
+        <is>
           <t>41.5</t>
         </is>
       </c>
-      <c r="BF18" t="inlineStr">
+      <c r="BG18" t="inlineStr">
         <is>
           <t>2025/08/07</t>
         </is>
       </c>
-      <c r="BG18" t="inlineStr">
-        <is>
-          <t>-8.19</t>
-        </is>
-      </c>
       <c r="BH18" t="inlineStr">
         <is>
+          <t>-9.76</t>
+        </is>
+      </c>
+      <c r="BI18" t="inlineStr">
+        <is>
           <t>新光鋼</t>
         </is>
       </c>
-      <c r="BI18" t="inlineStr">
+      <c r="BJ18" t="inlineStr">
         <is>
           <t>新光鋼</t>
         </is>
       </c>
-      <c r="BJ18" t="inlineStr">
+      <c r="BK18" t="inlineStr">
         <is>
           <t>鋼鐵工業</t>
         </is>
       </c>
-      <c r="BK18" t="inlineStr">
+      <c r="BL18" t="inlineStr">
         <is>
           <t>上市</t>
         </is>
       </c>
-      <c r="BL18" t="inlineStr">
-        <is>
-          <t>0.63</t>
-        </is>
-      </c>
       <c r="BM18" t="inlineStr">
         <is>
+          <t>0.61</t>
+        </is>
+      </c>
+      <c r="BN18" t="inlineStr">
+        <is>
           <t>-13.67996844119094</t>
         </is>
       </c>
-      <c r="BN18" t="inlineStr">
+      <c r="BO18" t="inlineStr">
         <is>
           <t>-10.11024290164889</t>
         </is>
       </c>
-      <c r="BO18" t="inlineStr">
+      <c r="BP18" t="inlineStr">
         <is>
           <t>24.12947661306339</t>
         </is>
       </c>
-      <c r="BP18" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
       <c r="BQ18" t="inlineStr">
         <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BR18" t="inlineStr">
+        <is>
           <t>價-量-</t>
         </is>
       </c>
-      <c r="BR18" t="inlineStr">
-        <is>
-          <t>1.05</t>
-        </is>
-      </c>
       <c r="BS18" t="inlineStr">
         <is>
-          <t>6.87</t>
+          <t>1.03</t>
         </is>
       </c>
       <c r="BT18" t="inlineStr">
         <is>
+          <t>6.78</t>
+        </is>
+      </c>
+      <c r="BU18" t="inlineStr">
+        <is>
           <t>11.90</t>
         </is>
       </c>
-      <c r="BU18" t="inlineStr">
-        <is>
-          <t>15.04</t>
-        </is>
-      </c>
       <c r="BV18" t="inlineStr">
         <is>
+          <t>15.23</t>
+        </is>
+      </c>
+      <c r="BW18" t="inlineStr">
+        <is>
           <t>8.69%</t>
         </is>
       </c>
-      <c r="BW18" t="inlineStr">
+      <c r="BX18" t="inlineStr">
         <is>
           <t>5.19%</t>
         </is>
       </c>
-      <c r="BX18" t="inlineStr">
-        <is>
-          <t>28.82</t>
-        </is>
-      </c>
       <c r="BY18" t="inlineStr">
         <is>
-          <t>11690</t>
+          <t>28.48</t>
         </is>
       </c>
       <c r="BZ18" t="inlineStr">
         <is>
+          <t>11834</t>
+        </is>
+      </c>
+      <c r="CA18" t="inlineStr">
+        <is>
           <t>鋼板38.80%、熱軋及鍍鋅鋼板33.80%、不�袗�板12.60%、特殊鋼板7.00%、加工及其他6.90%、型鋼0.90% (2024年)</t>
         </is>
       </c>
-      <c r="CA18" t="inlineStr">
+      <c r="CB18" t="inlineStr">
         <is>
           <t>新光鋼-鋼鐵工業-上市</t>
         </is>
       </c>
-      <c r="CB18" t="inlineStr">
+      <c r="CC18" t="inlineStr">
         <is>
           <t>鋼鐵工業右下上市</t>
         </is>
       </c>
-      <c r="CC18" t="inlineStr">
-        <is>
-          <t>38.2</t>
-        </is>
-      </c>
       <c r="CD18" t="inlineStr">
         <is>
-          <t>38.4</t>
+          <t>38.1</t>
         </is>
       </c>
       <c r="CE18" t="inlineStr">
         <is>
-          <t>37.95</t>
+          <t>38.7</t>
         </is>
       </c>
       <c r="CF18" t="inlineStr">
         <is>
-          <t>38.1</t>
+          <t>37.3</t>
         </is>
       </c>
       <c r="CG18" t="inlineStr">
         <is>
+          <t>37.45</t>
+        </is>
+      </c>
+      <c r="CH18" t="inlineStr">
+        <is>
           <t>36.35</t>
         </is>
       </c>
-      <c r="CH18" t="inlineStr">
+      <c r="CI18" t="inlineStr">
         <is>
           <t>** 鋼鐵 - 裁剪加工** 建材營造 - 基礎工程、結構工程** 太陽能產業 - 太陽能發電設備/系統及系統工程** 風力發電 - 鋼材、塔架、其他配件</t>
         </is>
       </c>
-      <c r="CI18" t="inlineStr">
+      <c r="CJ18" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -8205,12 +8295,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>1.18</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>605.721</t>
+          <t>504.317</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -8230,17 +8320,17 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>-4.67</t>
+          <t>-3.39</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>-1.07</t>
+          <t>-1.23</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>29.75</t>
+          <t>20.39</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -8315,17 +8405,17 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>6.45</t>
+          <t>5.37</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>0.40</t>
+          <t>-0.39</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
@@ -8336,77 +8426,77 @@
       <c r="AC19" t="inlineStr"/>
       <c r="AD19" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
-          <t>776</t>
+          <t>1129</t>
         </is>
       </c>
       <c r="AF19" t="inlineStr">
         <is>
-          <t>21.95</t>
+          <t>28.13</t>
         </is>
       </c>
       <c r="AG19" t="inlineStr">
         <is>
-          <t>7.32</t>
+          <t>16.69</t>
         </is>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
-          <t>-0.94</t>
+          <t>-0.55</t>
         </is>
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>-3.10</t>
+          <t>-3.22</t>
         </is>
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>-3.87</t>
+          <t>-3.86</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>-0.91</t>
+          <t>-1.12</t>
         </is>
       </c>
       <c r="AL19" t="inlineStr">
         <is>
-          <t>38.46</t>
+          <t>38.31</t>
         </is>
       </c>
       <c r="AM19" t="inlineStr">
         <is>
-          <t>39.69</t>
+          <t>39.58</t>
         </is>
       </c>
       <c r="AN19" t="inlineStr">
         <is>
-          <t>41.29</t>
+          <t>41.17</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>41.67</t>
+          <t>41.64</t>
         </is>
       </c>
       <c r="AP19" t="inlineStr">
         <is>
-          <t>-16.76</t>
+          <t>-13.76</t>
         </is>
       </c>
       <c r="AQ19" t="inlineStr">
         <is>
-          <t>-0.85</t>
+          <t>-0.86</t>
         </is>
       </c>
       <c r="AR19" t="inlineStr">
         <is>
-          <t>-0.73</t>
+          <t>-0.75</t>
         </is>
       </c>
       <c r="AS19" t="inlineStr">
@@ -8416,7 +8506,7 @@
       </c>
       <c r="AT19" t="inlineStr">
         <is>
-          <t>-127.09</t>
+          <t>-128.06</t>
         </is>
       </c>
       <c r="AU19" t="inlineStr">
@@ -8426,198 +8516,203 @@
       </c>
       <c r="AV19" t="inlineStr">
         <is>
-          <t>150535732.3834532</t>
+          <t>150408451.7952586</t>
         </is>
       </c>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>23042470.0</t>
+          <t>19248593.0</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>33965584.0</t>
+          <t>31147112.0</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
-          <t>26178217.9</t>
+          <t>25871081.1</t>
         </is>
       </c>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>28206383.42</t>
+          <t>28091032.78</t>
         </is>
       </c>
       <c r="BA19" t="inlineStr">
         <is>
-          <t>7787366</t>
+          <t>5276030</t>
         </is>
       </c>
       <c r="BB19" t="inlineStr">
         <is>
-          <t>-365198.417442461</t>
-        </is>
-      </c>
-      <c r="BC19" t="n">
-        <v>1450493.77</v>
-      </c>
-      <c r="BD19" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+          <t>-239589.4123123131</t>
+        </is>
+      </c>
+      <c r="BC19" t="inlineStr">
+        <is>
+          <t>451260.1159035005</t>
+        </is>
+      </c>
+      <c r="BD19" t="n">
+        <v>19248593</v>
       </c>
       <c r="BE19" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF19" t="inlineStr">
+        <is>
           <t>41.5</t>
         </is>
       </c>
-      <c r="BF19" t="inlineStr">
+      <c r="BG19" t="inlineStr">
         <is>
           <t>2025/08/07</t>
         </is>
       </c>
-      <c r="BG19" t="inlineStr">
+      <c r="BH19" t="inlineStr">
         <is>
           <t>-8.19</t>
         </is>
       </c>
-      <c r="BH19" t="inlineStr">
+      <c r="BI19" t="inlineStr">
         <is>
           <t>新光鋼</t>
         </is>
       </c>
-      <c r="BI19" t="inlineStr">
+      <c r="BJ19" t="inlineStr">
         <is>
           <t>新光鋼</t>
         </is>
       </c>
-      <c r="BJ19" t="inlineStr">
+      <c r="BK19" t="inlineStr">
         <is>
           <t>鋼鐵工業</t>
         </is>
       </c>
-      <c r="BK19" t="inlineStr">
+      <c r="BL19" t="inlineStr">
         <is>
           <t>上市</t>
         </is>
       </c>
-      <c r="BL19" t="inlineStr">
-        <is>
-          <t>0.63</t>
-        </is>
-      </c>
       <c r="BM19" t="inlineStr">
         <is>
+          <t>0.61</t>
+        </is>
+      </c>
+      <c r="BN19" t="inlineStr">
+        <is>
           <t>-13.67996844119094</t>
         </is>
       </c>
-      <c r="BN19" t="inlineStr">
+      <c r="BO19" t="inlineStr">
         <is>
           <t>-10.11024290164889</t>
         </is>
       </c>
-      <c r="BO19" t="inlineStr">
+      <c r="BP19" t="inlineStr">
         <is>
           <t>24.12947661306339</t>
         </is>
       </c>
-      <c r="BP19" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;可能出現反轉訊號&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;3&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
       <c r="BQ19" t="inlineStr">
         <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BR19" t="inlineStr">
+        <is>
           <t>價-量-</t>
         </is>
       </c>
-      <c r="BR19" t="inlineStr">
+      <c r="BS19" t="inlineStr">
         <is>
           <t>1.05</t>
         </is>
       </c>
-      <c r="BS19" t="inlineStr">
-        <is>
-          <t>6.87</t>
-        </is>
-      </c>
       <c r="BT19" t="inlineStr">
         <is>
+          <t>6.78</t>
+        </is>
+      </c>
+      <c r="BU19" t="inlineStr">
+        <is>
           <t>11.90</t>
         </is>
       </c>
-      <c r="BU19" t="inlineStr">
-        <is>
-          <t>15.04</t>
-        </is>
-      </c>
       <c r="BV19" t="inlineStr">
         <is>
+          <t>15.23</t>
+        </is>
+      </c>
+      <c r="BW19" t="inlineStr">
+        <is>
           <t>8.69%</t>
         </is>
       </c>
-      <c r="BW19" t="inlineStr">
+      <c r="BX19" t="inlineStr">
         <is>
           <t>5.19%</t>
         </is>
       </c>
-      <c r="BX19" t="inlineStr">
-        <is>
-          <t>28.82</t>
-        </is>
-      </c>
       <c r="BY19" t="inlineStr">
         <is>
-          <t>11690</t>
+          <t>28.48</t>
         </is>
       </c>
       <c r="BZ19" t="inlineStr">
         <is>
+          <t>11834</t>
+        </is>
+      </c>
+      <c r="CA19" t="inlineStr">
+        <is>
           <t>鋼板38.80%、熱軋及鍍鋅鋼板33.80%、不�袗�板12.60%、特殊鋼板7.00%、加工及其他6.90%、型鋼0.90% (2024年)</t>
         </is>
       </c>
-      <c r="CA19" t="inlineStr">
+      <c r="CB19" t="inlineStr">
         <is>
           <t>新光鋼-鋼鐵工業-上市</t>
         </is>
       </c>
-      <c r="CB19" t="inlineStr">
+      <c r="CC19" t="inlineStr">
         <is>
           <t>鋼鐵工業右下上市</t>
         </is>
       </c>
-      <c r="CC19" t="inlineStr">
-        <is>
-          <t>38.0</t>
-        </is>
-      </c>
       <c r="CD19" t="inlineStr">
         <is>
-          <t>38.3</t>
+          <t>38.2</t>
         </is>
       </c>
       <c r="CE19" t="inlineStr">
         <is>
-          <t>37.75</t>
+          <t>38.4</t>
         </is>
       </c>
       <c r="CF19" t="inlineStr">
         <is>
+          <t>37.95</t>
+        </is>
+      </c>
+      <c r="CG19" t="inlineStr">
+        <is>
           <t>38.1</t>
         </is>
       </c>
-      <c r="CG19" t="inlineStr">
+      <c r="CH19" t="inlineStr">
         <is>
           <t>36.35</t>
         </is>
       </c>
-      <c r="CH19" t="inlineStr">
+      <c r="CI19" t="inlineStr">
         <is>
           <t>** 鋼鐵 - 裁剪加工** 建材營造 - 基礎工程、結構工程** 太陽能產業 - 太陽能發電設備/系統及系統工程** 風力發電 - 鋼材、塔架、其他配件</t>
         </is>
       </c>
-      <c r="CI19" t="inlineStr">
+      <c r="CJ19" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -8636,12 +8731,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>-2.6</t>
+          <t>1.18</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>1764.112</t>
+          <t>605.721</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -8651,7 +8746,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>37.65</t>
+          <t>38.1</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -8661,17 +8756,17 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>-3.43</t>
+          <t>-3.39</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>-1.07</t>
+          <t>-1.23</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>21.53</t>
+          <t>29.75</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -8736,7 +8831,7 @@
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>-12.75</t>
+          <t>-11.70</t>
         </is>
       </c>
       <c r="X20" t="inlineStr">
@@ -8746,17 +8841,17 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>18.80</t>
+          <t>6.45</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>-2.12</t>
+          <t>0.40</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
@@ -8767,77 +8862,77 @@
       <c r="AC20" t="inlineStr"/>
       <c r="AD20" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
-          <t>776</t>
+          <t>1129</t>
         </is>
       </c>
       <c r="AF20" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>21.95</t>
         </is>
       </c>
       <c r="AG20" t="inlineStr">
         <is>
-          <t>6.67</t>
+          <t>7.32</t>
         </is>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
-          <t>-2.44</t>
+          <t>-0.94</t>
         </is>
       </c>
       <c r="AI20" t="inlineStr">
         <is>
-          <t>-3.03</t>
+          <t>-3.10</t>
         </is>
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>-3.91</t>
+          <t>-3.87</t>
         </is>
       </c>
       <c r="AK20" t="inlineStr">
         <is>
-          <t>-0.66</t>
+          <t>-0.91</t>
         </is>
       </c>
       <c r="AL20" t="inlineStr">
         <is>
-          <t>38.59</t>
+          <t>38.46</t>
         </is>
       </c>
       <c r="AM20" t="inlineStr">
         <is>
-          <t>39.8</t>
+          <t>39.69</t>
         </is>
       </c>
       <c r="AN20" t="inlineStr">
         <is>
-          <t>41.42</t>
+          <t>41.29</t>
         </is>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>41.69</t>
+          <t>41.67</t>
         </is>
       </c>
       <c r="AP20" t="inlineStr">
         <is>
-          <t>-18.69</t>
+          <t>-16.76</t>
         </is>
       </c>
       <c r="AQ20" t="inlineStr">
         <is>
-          <t>-0.83</t>
+          <t>-0.85</t>
         </is>
       </c>
       <c r="AR20" t="inlineStr">
         <is>
-          <t>-0.70</t>
+          <t>-0.73</t>
         </is>
       </c>
       <c r="AS20" t="inlineStr">
@@ -8847,7 +8942,7 @@
       </c>
       <c r="AT20" t="inlineStr">
         <is>
-          <t>-125.95</t>
+          <t>-127.09</t>
         </is>
       </c>
       <c r="AU20" t="inlineStr">
@@ -8857,198 +8952,203 @@
       </c>
       <c r="AV20" t="inlineStr">
         <is>
-          <t>150535732.3834532</t>
+          <t>150408451.7952586</t>
         </is>
       </c>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>66861836.0</t>
+          <t>23042470.0</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>33260992.8</t>
+          <t>33965584.0</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
-          <t>27368625.9</t>
+          <t>26178217.9</t>
         </is>
       </c>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>28716017.48</t>
+          <t>28206383.42</t>
         </is>
       </c>
       <c r="BA20" t="inlineStr">
         <is>
-          <t>5892366</t>
+          <t>7787366</t>
         </is>
       </c>
       <c r="BB20" t="inlineStr">
         <is>
-          <t>-695324.269555022</t>
-        </is>
-      </c>
-      <c r="BC20" t="n">
-        <v>2419680.25</v>
-      </c>
-      <c r="BD20" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+          <t>-365198.417442461</t>
+        </is>
+      </c>
+      <c r="BC20" t="inlineStr">
+        <is>
+          <t>1450493.769176625</t>
+        </is>
+      </c>
+      <c r="BD20" t="n">
+        <v>23042470</v>
       </c>
       <c r="BE20" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF20" t="inlineStr">
+        <is>
           <t>41.5</t>
         </is>
       </c>
-      <c r="BF20" t="inlineStr">
+      <c r="BG20" t="inlineStr">
         <is>
           <t>2025/08/07</t>
         </is>
       </c>
-      <c r="BG20" t="inlineStr">
-        <is>
-          <t>-9.28</t>
-        </is>
-      </c>
       <c r="BH20" t="inlineStr">
         <is>
+          <t>-8.19</t>
+        </is>
+      </c>
+      <c r="BI20" t="inlineStr">
+        <is>
           <t>新光鋼</t>
         </is>
       </c>
-      <c r="BI20" t="inlineStr">
+      <c r="BJ20" t="inlineStr">
         <is>
           <t>新光鋼</t>
         </is>
       </c>
-      <c r="BJ20" t="inlineStr">
+      <c r="BK20" t="inlineStr">
         <is>
           <t>鋼鐵工業</t>
         </is>
       </c>
-      <c r="BK20" t="inlineStr">
+      <c r="BL20" t="inlineStr">
         <is>
           <t>上市</t>
         </is>
       </c>
-      <c r="BL20" t="inlineStr">
-        <is>
-          <t>0.63</t>
-        </is>
-      </c>
       <c r="BM20" t="inlineStr">
         <is>
+          <t>0.61</t>
+        </is>
+      </c>
+      <c r="BN20" t="inlineStr">
+        <is>
           <t>-13.67996844119094</t>
         </is>
       </c>
-      <c r="BN20" t="inlineStr">
+      <c r="BO20" t="inlineStr">
         <is>
           <t>-10.11024290164889</t>
         </is>
       </c>
-      <c r="BO20" t="inlineStr">
+      <c r="BP20" t="inlineStr">
         <is>
           <t>24.12947661306339</t>
         </is>
       </c>
-      <c r="BP20" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
       <c r="BQ20" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;可能出現反轉訊號&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;3&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR20" t="inlineStr">
         <is>
-          <t>1.04</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS20" t="inlineStr">
         <is>
-          <t>6.87</t>
+          <t>1.05</t>
         </is>
       </c>
       <c r="BT20" t="inlineStr">
         <is>
+          <t>6.78</t>
+        </is>
+      </c>
+      <c r="BU20" t="inlineStr">
+        <is>
           <t>11.90</t>
         </is>
       </c>
-      <c r="BU20" t="inlineStr">
-        <is>
-          <t>15.04</t>
-        </is>
-      </c>
       <c r="BV20" t="inlineStr">
         <is>
+          <t>15.23</t>
+        </is>
+      </c>
+      <c r="BW20" t="inlineStr">
+        <is>
           <t>8.69%</t>
         </is>
       </c>
-      <c r="BW20" t="inlineStr">
+      <c r="BX20" t="inlineStr">
         <is>
           <t>5.19%</t>
         </is>
       </c>
-      <c r="BX20" t="inlineStr">
-        <is>
-          <t>28.82</t>
-        </is>
-      </c>
       <c r="BY20" t="inlineStr">
         <is>
-          <t>11690</t>
+          <t>28.48</t>
         </is>
       </c>
       <c r="BZ20" t="inlineStr">
         <is>
+          <t>11834</t>
+        </is>
+      </c>
+      <c r="CA20" t="inlineStr">
+        <is>
           <t>鋼板38.80%、熱軋及鍍鋅鋼板33.80%、不�袗�板12.60%、特殊鋼板7.00%、加工及其他6.90%、型鋼0.90% (2024年)</t>
         </is>
       </c>
-      <c r="CA20" t="inlineStr">
+      <c r="CB20" t="inlineStr">
         <is>
           <t>新光鋼-鋼鐵工業-上市</t>
         </is>
       </c>
-      <c r="CB20" t="inlineStr">
+      <c r="CC20" t="inlineStr">
         <is>
           <t>鋼鐵工業右下上市</t>
         </is>
       </c>
-      <c r="CC20" t="inlineStr">
-        <is>
-          <t>38.45</t>
-        </is>
-      </c>
       <c r="CD20" t="inlineStr">
         <is>
-          <t>38.75</t>
+          <t>38.0</t>
         </is>
       </c>
       <c r="CE20" t="inlineStr">
         <is>
-          <t>37.35</t>
+          <t>38.3</t>
         </is>
       </c>
       <c r="CF20" t="inlineStr">
         <is>
-          <t>37.65</t>
+          <t>37.75</t>
         </is>
       </c>
       <c r="CG20" t="inlineStr">
         <is>
+          <t>38.1</t>
+        </is>
+      </c>
+      <c r="CH20" t="inlineStr">
+        <is>
           <t>36.35</t>
         </is>
       </c>
-      <c r="CH20" t="inlineStr">
+      <c r="CI20" t="inlineStr">
         <is>
           <t>** 鋼鐵 - 裁剪加工** 建材營造 - 基礎工程、結構工程** 太陽能產業 - 太陽能發電設備/系統及系統工程** 風力發電 - 鋼材、塔架、其他配件</t>
         </is>
       </c>
-      <c r="CI20" t="inlineStr">
+      <c r="CJ20" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -9067,12 +9167,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>-1.03</t>
+          <t>-2.6</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>499.552</t>
+          <t>1764.112</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -9082,7 +9182,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>38.65</t>
+          <t>37.65</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -9092,17 +9192,17 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>-6.18</t>
+          <t>-2.17</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>-1.07</t>
+          <t>-1.23</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>0.16</t>
+          <t>21.53</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -9167,7 +9267,7 @@
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>-10.43</t>
+          <t>-12.75</t>
         </is>
       </c>
       <c r="X21" t="inlineStr">
@@ -9177,17 +9277,17 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>5.32</t>
+          <t>18.80</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>-1.42</t>
+          <t>-2.12</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
@@ -9198,12 +9298,12 @@
       <c r="AC21" t="inlineStr"/>
       <c r="AD21" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
-          <t>776</t>
+          <t>1129</t>
         </is>
       </c>
       <c r="AF21" t="inlineStr">
@@ -9213,17 +9313,17 @@
       </c>
       <c r="AG21" t="inlineStr">
         <is>
-          <t>8.47</t>
+          <t>6.67</t>
         </is>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
-          <t>-0.57</t>
+          <t>-2.44</t>
         </is>
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>-2.61</t>
+          <t>-3.03</t>
         </is>
       </c>
       <c r="AJ21" t="inlineStr">
@@ -9233,42 +9333,42 @@
       </c>
       <c r="AK21" t="inlineStr">
         <is>
-          <t>-0.43</t>
+          <t>-0.66</t>
         </is>
       </c>
       <c r="AL21" t="inlineStr">
         <is>
-          <t>38.87</t>
+          <t>38.59</t>
         </is>
       </c>
       <c r="AM21" t="inlineStr">
         <is>
-          <t>39.91</t>
+          <t>39.8</t>
         </is>
       </c>
       <c r="AN21" t="inlineStr">
         <is>
-          <t>41.54</t>
+          <t>41.42</t>
         </is>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>41.72</t>
+          <t>41.69</t>
         </is>
       </c>
       <c r="AP21" t="inlineStr">
         <is>
-          <t>-11.54</t>
+          <t>-18.69</t>
         </is>
       </c>
       <c r="AQ21" t="inlineStr">
         <is>
-          <t>-0.74</t>
+          <t>-0.83</t>
         </is>
       </c>
       <c r="AR21" t="inlineStr">
         <is>
-          <t>-0.66</t>
+          <t>-0.70</t>
         </is>
       </c>
       <c r="AS21" t="inlineStr">
@@ -9278,7 +9378,7 @@
       </c>
       <c r="AT21" t="inlineStr">
         <is>
-          <t>-124.74</t>
+          <t>-125.95</t>
         </is>
       </c>
       <c r="AU21" t="inlineStr">
@@ -9288,198 +9388,203 @@
       </c>
       <c r="AV21" t="inlineStr">
         <is>
-          <t>150535732.3834532</t>
+          <t>150408451.7952586</t>
         </is>
       </c>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>19337957.0</t>
+          <t>66861836.0</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>22560307.8</t>
+          <t>33260992.8</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
-          <t>22524902.5</t>
+          <t>27368625.9</t>
         </is>
       </c>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>28140249.02</t>
+          <t>28716017.48</t>
         </is>
       </c>
       <c r="BA21" t="inlineStr">
         <is>
-          <t>35405</t>
+          <t>5892366</t>
         </is>
       </c>
       <c r="BB21" t="inlineStr">
         <is>
-          <t>-1261688.726998104</t>
-        </is>
-      </c>
-      <c r="BC21" t="n">
-        <v>-977116.87</v>
-      </c>
-      <c r="BD21" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+          <t>-695324.269555022</t>
+        </is>
+      </c>
+      <c r="BC21" t="inlineStr">
+        <is>
+          <t>2419680.246381927</t>
+        </is>
+      </c>
+      <c r="BD21" t="n">
+        <v>66861836</v>
       </c>
       <c r="BE21" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF21" t="inlineStr">
+        <is>
           <t>41.5</t>
         </is>
       </c>
-      <c r="BF21" t="inlineStr">
+      <c r="BG21" t="inlineStr">
         <is>
           <t>2025/08/07</t>
         </is>
       </c>
-      <c r="BG21" t="inlineStr">
-        <is>
-          <t>-6.87</t>
-        </is>
-      </c>
       <c r="BH21" t="inlineStr">
         <is>
+          <t>-9.28</t>
+        </is>
+      </c>
+      <c r="BI21" t="inlineStr">
+        <is>
           <t>新光鋼</t>
         </is>
       </c>
-      <c r="BI21" t="inlineStr">
+      <c r="BJ21" t="inlineStr">
         <is>
           <t>新光鋼</t>
         </is>
       </c>
-      <c r="BJ21" t="inlineStr">
+      <c r="BK21" t="inlineStr">
         <is>
           <t>鋼鐵工業</t>
         </is>
       </c>
-      <c r="BK21" t="inlineStr">
+      <c r="BL21" t="inlineStr">
         <is>
           <t>上市</t>
         </is>
       </c>
-      <c r="BL21" t="inlineStr">
-        <is>
-          <t>0.63</t>
-        </is>
-      </c>
       <c r="BM21" t="inlineStr">
         <is>
+          <t>0.61</t>
+        </is>
+      </c>
+      <c r="BN21" t="inlineStr">
+        <is>
           <t>-13.67996844119094</t>
         </is>
       </c>
-      <c r="BN21" t="inlineStr">
+      <c r="BO21" t="inlineStr">
         <is>
           <t>-10.11024290164889</t>
         </is>
       </c>
-      <c r="BO21" t="inlineStr">
+      <c r="BP21" t="inlineStr">
         <is>
           <t>24.12947661306339</t>
         </is>
       </c>
-      <c r="BP21" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
       <c r="BQ21" t="inlineStr">
         <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BR21" t="inlineStr">
+        <is>
           <t>價-量增</t>
         </is>
       </c>
-      <c r="BR21" t="inlineStr">
-        <is>
-          <t>1.06</t>
-        </is>
-      </c>
       <c r="BS21" t="inlineStr">
         <is>
-          <t>6.87</t>
+          <t>1.04</t>
         </is>
       </c>
       <c r="BT21" t="inlineStr">
         <is>
+          <t>6.78</t>
+        </is>
+      </c>
+      <c r="BU21" t="inlineStr">
+        <is>
           <t>11.90</t>
         </is>
       </c>
-      <c r="BU21" t="inlineStr">
-        <is>
-          <t>15.04</t>
-        </is>
-      </c>
       <c r="BV21" t="inlineStr">
         <is>
+          <t>15.23</t>
+        </is>
+      </c>
+      <c r="BW21" t="inlineStr">
+        <is>
           <t>8.69%</t>
         </is>
       </c>
-      <c r="BW21" t="inlineStr">
+      <c r="BX21" t="inlineStr">
         <is>
           <t>5.19%</t>
         </is>
       </c>
-      <c r="BX21" t="inlineStr">
-        <is>
-          <t>28.82</t>
-        </is>
-      </c>
       <c r="BY21" t="inlineStr">
         <is>
-          <t>11690</t>
+          <t>28.48</t>
         </is>
       </c>
       <c r="BZ21" t="inlineStr">
         <is>
+          <t>11834</t>
+        </is>
+      </c>
+      <c r="CA21" t="inlineStr">
+        <is>
           <t>鋼板38.80%、熱軋及鍍鋅鋼板33.80%、不�袗�板12.60%、特殊鋼板7.00%、加工及其他6.90%、型鋼0.90% (2024年)</t>
         </is>
       </c>
-      <c r="CA21" t="inlineStr">
+      <c r="CB21" t="inlineStr">
         <is>
           <t>新光鋼-鋼鐵工業-上市</t>
         </is>
       </c>
-      <c r="CB21" t="inlineStr">
+      <c r="CC21" t="inlineStr">
         <is>
           <t>鋼鐵工業右下上市</t>
         </is>
       </c>
-      <c r="CC21" t="inlineStr">
-        <is>
-          <t>38.95</t>
-        </is>
-      </c>
       <c r="CD21" t="inlineStr">
         <is>
-          <t>39.3</t>
+          <t>38.45</t>
         </is>
       </c>
       <c r="CE21" t="inlineStr">
         <is>
-          <t>38.55</t>
+          <t>38.75</t>
         </is>
       </c>
       <c r="CF21" t="inlineStr">
         <is>
-          <t>38.65</t>
+          <t>37.35</t>
         </is>
       </c>
       <c r="CG21" t="inlineStr">
         <is>
+          <t>37.65</t>
+        </is>
+      </c>
+      <c r="CH21" t="inlineStr">
+        <is>
           <t>36.35</t>
         </is>
       </c>
-      <c r="CH21" t="inlineStr">
+      <c r="CI21" t="inlineStr">
         <is>
           <t>** 鋼鐵 - 裁剪加工** 建材營造 - 基礎工程、結構工程** 太陽能產業 - 太陽能發電設備/系統及系統工程** 風力發電 - 鋼材、塔架、其他配件</t>
         </is>
       </c>
-      <c r="CI21" t="inlineStr">
+      <c r="CJ21" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -9498,12 +9603,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>0.51</t>
+          <t>-1.03</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>700.928</t>
+          <t>499.552</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -9513,7 +9618,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>39.05</t>
+          <t>38.65</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -9523,17 +9628,17 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>-7.28</t>
+          <t>-4.88</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>-1.07</t>
+          <t>-1.23</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>0.15</t>
+          <t>0.16</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -9598,7 +9703,7 @@
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>-9.50</t>
+          <t>-10.43</t>
         </is>
       </c>
       <c r="X22" t="inlineStr">
@@ -9608,17 +9713,17 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>7.47</t>
+          <t>5.32</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>1.17</t>
+          <t>-1.42</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
@@ -9629,17 +9734,17 @@
       <c r="AC22" t="inlineStr"/>
       <c r="AD22" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AE22" t="inlineStr">
         <is>
-          <t>776</t>
+          <t>1129</t>
         </is>
       </c>
       <c r="AF22" t="inlineStr">
         <is>
-          <t>20.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG22" t="inlineStr">
@@ -9649,57 +9754,57 @@
       </c>
       <c r="AH22" t="inlineStr">
         <is>
-          <t>0.15</t>
+          <t>-0.57</t>
         </is>
       </c>
       <c r="AI22" t="inlineStr">
         <is>
-          <t>-2.53</t>
+          <t>-2.61</t>
         </is>
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>-3.9</t>
+          <t>-3.91</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
         <is>
-          <t>-0.25</t>
+          <t>-0.43</t>
         </is>
       </c>
       <c r="AL22" t="inlineStr">
         <is>
-          <t>38.99</t>
+          <t>38.87</t>
         </is>
       </c>
       <c r="AM22" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>39.91</t>
         </is>
       </c>
       <c r="AN22" t="inlineStr">
         <is>
-          <t>41.63</t>
+          <t>41.54</t>
         </is>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>41.73</t>
+          <t>41.72</t>
         </is>
       </c>
       <c r="AP22" t="inlineStr">
         <is>
-          <t>-11.93</t>
+          <t>-11.54</t>
         </is>
       </c>
       <c r="AQ22" t="inlineStr">
         <is>
-          <t>-0.72</t>
+          <t>-0.74</t>
         </is>
       </c>
       <c r="AR22" t="inlineStr">
         <is>
-          <t>-0.65</t>
+          <t>-0.66</t>
         </is>
       </c>
       <c r="AS22" t="inlineStr">
@@ -9709,7 +9814,7 @@
       </c>
       <c r="AT22" t="inlineStr">
         <is>
-          <t>-124.03</t>
+          <t>-124.74</t>
         </is>
       </c>
       <c r="AU22" t="inlineStr">
@@ -9719,198 +9824,203 @@
       </c>
       <c r="AV22" t="inlineStr">
         <is>
-          <t>150535732.3834532</t>
+          <t>150408451.7952586</t>
         </is>
       </c>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>27244704.0</t>
+          <t>19337957.0</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>22783460.2</t>
+          <t>22560307.8</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr">
         <is>
-          <t>22749645.3</t>
+          <t>22524902.5</t>
         </is>
       </c>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>28438883.58</t>
+          <t>28140249.02</t>
         </is>
       </c>
       <c r="BA22" t="inlineStr">
         <is>
-          <t>33814</t>
+          <t>35405</t>
         </is>
       </c>
       <c r="BB22" t="inlineStr">
         <is>
-          <t>-1313429.065286876</t>
-        </is>
-      </c>
-      <c r="BC22" t="n">
-        <v>-702942.96</v>
-      </c>
-      <c r="BD22" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+          <t>-1261688.726998104</t>
+        </is>
+      </c>
+      <c r="BC22" t="inlineStr">
+        <is>
+          <t>-977116.8664098568</t>
+        </is>
+      </c>
+      <c r="BD22" t="n">
+        <v>19337957</v>
       </c>
       <c r="BE22" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF22" t="inlineStr">
+        <is>
           <t>41.5</t>
         </is>
       </c>
-      <c r="BF22" t="inlineStr">
+      <c r="BG22" t="inlineStr">
         <is>
           <t>2025/08/07</t>
         </is>
       </c>
-      <c r="BG22" t="inlineStr">
-        <is>
-          <t>-5.90</t>
-        </is>
-      </c>
       <c r="BH22" t="inlineStr">
         <is>
+          <t>-6.87</t>
+        </is>
+      </c>
+      <c r="BI22" t="inlineStr">
+        <is>
           <t>新光鋼</t>
         </is>
       </c>
-      <c r="BI22" t="inlineStr">
+      <c r="BJ22" t="inlineStr">
         <is>
           <t>新光鋼</t>
         </is>
       </c>
-      <c r="BJ22" t="inlineStr">
+      <c r="BK22" t="inlineStr">
         <is>
           <t>鋼鐵工業</t>
         </is>
       </c>
-      <c r="BK22" t="inlineStr">
+      <c r="BL22" t="inlineStr">
         <is>
           <t>上市</t>
         </is>
       </c>
-      <c r="BL22" t="inlineStr">
-        <is>
-          <t>0.63</t>
-        </is>
-      </c>
       <c r="BM22" t="inlineStr">
         <is>
+          <t>0.61</t>
+        </is>
+      </c>
+      <c r="BN22" t="inlineStr">
+        <is>
           <t>-13.67996844119094</t>
         </is>
       </c>
-      <c r="BN22" t="inlineStr">
+      <c r="BO22" t="inlineStr">
         <is>
           <t>-10.11024290164889</t>
         </is>
       </c>
-      <c r="BO22" t="inlineStr">
+      <c r="BP22" t="inlineStr">
         <is>
           <t>24.12947661306339</t>
         </is>
       </c>
-      <c r="BP22" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
       <c r="BQ22" t="inlineStr">
         <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BR22" t="inlineStr">
+        <is>
           <t>價-量-</t>
         </is>
       </c>
-      <c r="BR22" t="inlineStr">
-        <is>
-          <t>1.07</t>
-        </is>
-      </c>
       <c r="BS22" t="inlineStr">
         <is>
-          <t>6.87</t>
+          <t>1.06</t>
         </is>
       </c>
       <c r="BT22" t="inlineStr">
         <is>
+          <t>6.78</t>
+        </is>
+      </c>
+      <c r="BU22" t="inlineStr">
+        <is>
           <t>11.90</t>
         </is>
       </c>
-      <c r="BU22" t="inlineStr">
-        <is>
-          <t>15.04</t>
-        </is>
-      </c>
       <c r="BV22" t="inlineStr">
         <is>
+          <t>15.23</t>
+        </is>
+      </c>
+      <c r="BW22" t="inlineStr">
+        <is>
           <t>8.69%</t>
         </is>
       </c>
-      <c r="BW22" t="inlineStr">
+      <c r="BX22" t="inlineStr">
         <is>
           <t>5.19%</t>
         </is>
       </c>
-      <c r="BX22" t="inlineStr">
-        <is>
-          <t>28.82</t>
-        </is>
-      </c>
       <c r="BY22" t="inlineStr">
         <is>
-          <t>11690</t>
+          <t>28.48</t>
         </is>
       </c>
       <c r="BZ22" t="inlineStr">
         <is>
+          <t>11834</t>
+        </is>
+      </c>
+      <c r="CA22" t="inlineStr">
+        <is>
           <t>鋼板38.80%、熱軋及鍍鋅鋼板33.80%、不�袗�板12.60%、特殊鋼板7.00%、加工及其他6.90%、型鋼0.90% (2024年)</t>
         </is>
       </c>
-      <c r="CA22" t="inlineStr">
+      <c r="CB22" t="inlineStr">
         <is>
           <t>新光鋼-鋼鐵工業-上市</t>
         </is>
       </c>
-      <c r="CB22" t="inlineStr">
+      <c r="CC22" t="inlineStr">
         <is>
           <t>鋼鐵工業右下上市</t>
         </is>
       </c>
-      <c r="CC22" t="inlineStr">
-        <is>
-          <t>38.85</t>
-        </is>
-      </c>
       <c r="CD22" t="inlineStr">
         <is>
-          <t>39.05</t>
+          <t>38.95</t>
         </is>
       </c>
       <c r="CE22" t="inlineStr">
         <is>
-          <t>38.6</t>
+          <t>39.3</t>
         </is>
       </c>
       <c r="CF22" t="inlineStr">
         <is>
-          <t>39.05</t>
+          <t>38.55</t>
         </is>
       </c>
       <c r="CG22" t="inlineStr">
         <is>
+          <t>38.65</t>
+        </is>
+      </c>
+      <c r="CH22" t="inlineStr">
+        <is>
           <t>36.35</t>
         </is>
       </c>
-      <c r="CH22" t="inlineStr">
+      <c r="CI22" t="inlineStr">
         <is>
           <t>** 鋼鐵 - 裁剪加工** 建材營造 - 基礎工程、結構工程** 太陽能產業 - 太陽能發電設備/系統及系統工程** 風力發電 - 鋼材、塔架、其他配件</t>
         </is>
       </c>
-      <c r="CI22" t="inlineStr">
+      <c r="CJ22" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -9929,12 +10039,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>0.26</t>
+          <t>0.51</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>857.171</t>
+          <t>700.928</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -9944,7 +10054,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>38.85</t>
+          <t>39.05</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -9954,17 +10064,17 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>-6.73</t>
+          <t>-5.97</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>-1.07</t>
+          <t>-1.23</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>-6.52</t>
+          <t>0.15</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -10029,7 +10139,7 @@
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>-9.97</t>
+          <t>-9.50</t>
         </is>
       </c>
       <c r="X23" t="inlineStr">
@@ -10039,17 +10149,17 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-11-06</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>9.13</t>
+          <t>7.47</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>-0.13</t>
+          <t>1.17</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
@@ -10060,57 +10170,57 @@
       <c r="AC23" t="inlineStr"/>
       <c r="AD23" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AE23" t="inlineStr">
         <is>
-          <t>776</t>
+          <t>1129</t>
         </is>
       </c>
       <c r="AF23" t="inlineStr">
         <is>
-          <t>5.41</t>
+          <t>20.0</t>
         </is>
       </c>
       <c r="AG23" t="inlineStr">
         <is>
-          <t>1.8</t>
+          <t>8.47</t>
         </is>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
-          <t>-0.69</t>
+          <t>0.15</t>
         </is>
       </c>
       <c r="AI23" t="inlineStr">
         <is>
-          <t>-2.41</t>
+          <t>-2.53</t>
         </is>
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>-3.92</t>
+          <t>-3.9</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
         <is>
-          <t>-0.03</t>
+          <t>-0.25</t>
         </is>
       </c>
       <c r="AL23" t="inlineStr">
         <is>
-          <t>39.12</t>
+          <t>38.99</t>
         </is>
       </c>
       <c r="AM23" t="inlineStr">
         <is>
-          <t>40.08</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="AN23" t="inlineStr">
         <is>
-          <t>41.72</t>
+          <t>41.63</t>
         </is>
       </c>
       <c r="AO23" t="inlineStr">
@@ -10120,17 +10230,17 @@
       </c>
       <c r="AP23" t="inlineStr">
         <is>
-          <t>-16.36</t>
+          <t>-11.93</t>
         </is>
       </c>
       <c r="AQ23" t="inlineStr">
         <is>
-          <t>-0.73</t>
+          <t>-0.72</t>
         </is>
       </c>
       <c r="AR23" t="inlineStr">
         <is>
-          <t>-0.63</t>
+          <t>-0.65</t>
         </is>
       </c>
       <c r="AS23" t="inlineStr">
@@ -10140,7 +10250,7 @@
       </c>
       <c r="AT23" t="inlineStr">
         <is>
-          <t>-123.31</t>
+          <t>-124.03</t>
         </is>
       </c>
       <c r="AU23" t="inlineStr">
@@ -10150,198 +10260,203 @@
       </c>
       <c r="AV23" t="inlineStr">
         <is>
-          <t>150535732.3834532</t>
+          <t>150408451.7952586</t>
         </is>
       </c>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>33340953.0</t>
+          <t>27244704.0</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>20595050.2</t>
+          <t>22783460.2</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr">
         <is>
-          <t>22030516.7</t>
+          <t>22749645.3</t>
         </is>
       </c>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>28317533.86</t>
+          <t>28438883.58</t>
         </is>
       </c>
       <c r="BA23" t="inlineStr">
         <is>
-          <t>-1435466</t>
+          <t>33814</t>
         </is>
       </c>
       <c r="BB23" t="inlineStr">
         <is>
-          <t>-1424426.538814767</t>
-        </is>
-      </c>
-      <c r="BC23" t="n">
-        <v>-1133312.31</v>
-      </c>
-      <c r="BD23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+          <t>-1313429.065286876</t>
+        </is>
+      </c>
+      <c r="BC23" t="inlineStr">
+        <is>
+          <t>-702942.9608834758</t>
+        </is>
+      </c>
+      <c r="BD23" t="n">
+        <v>27244704</v>
       </c>
       <c r="BE23" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF23" t="inlineStr">
+        <is>
           <t>41.5</t>
         </is>
       </c>
-      <c r="BF23" t="inlineStr">
+      <c r="BG23" t="inlineStr">
         <is>
           <t>2025/08/07</t>
         </is>
       </c>
-      <c r="BG23" t="inlineStr">
-        <is>
-          <t>-6.39</t>
-        </is>
-      </c>
       <c r="BH23" t="inlineStr">
         <is>
+          <t>-5.90</t>
+        </is>
+      </c>
+      <c r="BI23" t="inlineStr">
+        <is>
           <t>新光鋼</t>
         </is>
       </c>
-      <c r="BI23" t="inlineStr">
+      <c r="BJ23" t="inlineStr">
         <is>
           <t>新光鋼</t>
         </is>
       </c>
-      <c r="BJ23" t="inlineStr">
+      <c r="BK23" t="inlineStr">
         <is>
           <t>鋼鐵工業</t>
         </is>
       </c>
-      <c r="BK23" t="inlineStr">
+      <c r="BL23" t="inlineStr">
         <is>
           <t>上市</t>
         </is>
       </c>
-      <c r="BL23" t="inlineStr">
-        <is>
-          <t>0.63</t>
-        </is>
-      </c>
       <c r="BM23" t="inlineStr">
         <is>
+          <t>0.61</t>
+        </is>
+      </c>
+      <c r="BN23" t="inlineStr">
+        <is>
           <t>-13.67996844119094</t>
         </is>
       </c>
-      <c r="BN23" t="inlineStr">
+      <c r="BO23" t="inlineStr">
         <is>
           <t>-10.11024290164889</t>
         </is>
       </c>
-      <c r="BO23" t="inlineStr">
+      <c r="BP23" t="inlineStr">
         <is>
           <t>24.12947661306339</t>
         </is>
       </c>
-      <c r="BP23" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
       <c r="BQ23" t="inlineStr">
         <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BR23" t="inlineStr">
+        <is>
           <t>價-量-</t>
         </is>
       </c>
-      <c r="BR23" t="inlineStr">
+      <c r="BS23" t="inlineStr">
         <is>
           <t>1.07</t>
         </is>
       </c>
-      <c r="BS23" t="inlineStr">
-        <is>
-          <t>6.87</t>
-        </is>
-      </c>
       <c r="BT23" t="inlineStr">
         <is>
+          <t>6.78</t>
+        </is>
+      </c>
+      <c r="BU23" t="inlineStr">
+        <is>
           <t>11.90</t>
         </is>
       </c>
-      <c r="BU23" t="inlineStr">
-        <is>
-          <t>15.04</t>
-        </is>
-      </c>
       <c r="BV23" t="inlineStr">
         <is>
+          <t>15.23</t>
+        </is>
+      </c>
+      <c r="BW23" t="inlineStr">
+        <is>
           <t>8.69%</t>
         </is>
       </c>
-      <c r="BW23" t="inlineStr">
+      <c r="BX23" t="inlineStr">
         <is>
           <t>5.19%</t>
         </is>
       </c>
-      <c r="BX23" t="inlineStr">
-        <is>
-          <t>28.82</t>
-        </is>
-      </c>
       <c r="BY23" t="inlineStr">
         <is>
-          <t>11690</t>
+          <t>28.48</t>
         </is>
       </c>
       <c r="BZ23" t="inlineStr">
         <is>
+          <t>11834</t>
+        </is>
+      </c>
+      <c r="CA23" t="inlineStr">
+        <is>
           <t>鋼板38.80%、熱軋及鍍鋅鋼板33.80%、不�袗�板12.60%、特殊鋼板7.00%、加工及其他6.90%、型鋼0.90% (2024年)</t>
         </is>
       </c>
-      <c r="CA23" t="inlineStr">
+      <c r="CB23" t="inlineStr">
         <is>
           <t>新光鋼-鋼鐵工業-上市</t>
         </is>
       </c>
-      <c r="CB23" t="inlineStr">
+      <c r="CC23" t="inlineStr">
         <is>
           <t>鋼鐵工業右下上市</t>
         </is>
       </c>
-      <c r="CC23" t="inlineStr">
-        <is>
-          <t>38.95</t>
-        </is>
-      </c>
       <c r="CD23" t="inlineStr">
         <is>
-          <t>39.1</t>
+          <t>38.85</t>
         </is>
       </c>
       <c r="CE23" t="inlineStr">
         <is>
-          <t>38.65</t>
+          <t>39.05</t>
         </is>
       </c>
       <c r="CF23" t="inlineStr">
         <is>
-          <t>38.85</t>
+          <t>38.6</t>
         </is>
       </c>
       <c r="CG23" t="inlineStr">
         <is>
+          <t>39.05</t>
+        </is>
+      </c>
+      <c r="CH23" t="inlineStr">
+        <is>
           <t>36.35</t>
         </is>
       </c>
-      <c r="CH23" t="inlineStr">
+      <c r="CI23" t="inlineStr">
         <is>
           <t>** 鋼鐵 - 裁剪加工** 建材營造 - 基礎工程、結構工程** 太陽能產業 - 太陽能發電設備/系統及系統工程** 風力發電 - 鋼材、塔架、其他配件</t>
         </is>
       </c>
-      <c r="CI23" t="inlineStr">
+      <c r="CJ23" t="inlineStr">
         <is>
           <t>False</t>
         </is>

--- a/Result/checksun_type/塔架.xlsx
+++ b/Result/checksun_type/塔架.xlsx
@@ -883,42 +883,42 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
+          <t>2.56</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>1721.237</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>138.5</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>1302.953</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>135.0</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-3.39</t>
+          <t>-3.38</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>12.02</t>
+          <t>-13.08</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-43.04</t>
+          <t>-41.56</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -993,17 +993,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>5.39</t>
+          <t>7.12</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>3.05</t>
+          <t>1.87</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1014,77 +1014,77 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>22</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>1303</t>
+          <t>1721</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>23.68</t>
+          <t>42.11</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>15.59</t>
+          <t>29.62</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>1.58</t>
+          <t>3.44</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>-9.76</t>
+          <t>-8.46</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>-8.05</t>
+          <t>-8.28</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>-6.11</t>
+          <t>-6.17</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>132.9</t>
+          <t>133.9</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>147.28</t>
+          <t>146.28</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>160.17</t>
+          <t>159.48</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>170.59</t>
+          <t>169.96</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>-15.53</t>
+          <t>-7.31</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>-8.25</t>
+          <t>-7.81</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>-7.14</t>
+          <t>-7.28</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -1094,7 +1094,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-128.71</t>
+          <t>-129.24</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1104,46 +1104,46 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>1695120094.609914</t>
+          <t>1693196887.497848</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>173429988.0</t>
+          <t>236429825.0</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>305348589.0</t>
+          <t>243968869.0</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>272591978.0</t>
+          <t>280669574.0</t>
         </is>
       </c>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>254388028.92</t>
+          <t>255272113.08</t>
         </is>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>32756611</t>
+          <t>-36700705</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>8180445.224550578</t>
+          <t>7451433.159492791</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>6461370.136106104</t>
+          <t>3441866.801674962</t>
         </is>
       </c>
       <c r="BD2" t="n">
-        <v>173429988</v>
+        <v>236429825</v>
       </c>
       <c r="BE2" t="inlineStr">
         <is>
@@ -1162,7 +1162,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>-25.00</t>
+          <t>-23.06</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
@@ -1207,7 +1207,7 @@
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;可能出現反轉訊號&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;3&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
@@ -1217,12 +1217,12 @@
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>3.11</t>
+          <t>3.19</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
         <is>
-          <t>3.08</t>
+          <t>3.01</t>
         </is>
       </c>
       <c r="BU2" t="inlineStr">
@@ -1232,7 +1232,7 @@
       </c>
       <c r="BV2" t="inlineStr">
         <is>
-          <t>25.38</t>
+          <t>26.03</t>
         </is>
       </c>
       <c r="BW2" t="inlineStr">
@@ -1247,12 +1247,12 @@
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>28.48</t>
+          <t>28.89</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>33331</t>
+          <t>34195</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
@@ -1272,22 +1272,22 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>132.5</t>
+          <t>136.5</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
+          <t>139.5</t>
+        </is>
+      </c>
+      <c r="CF2" t="inlineStr">
+        <is>
           <t>135.0</t>
         </is>
       </c>
-      <c r="CF2" t="inlineStr">
-        <is>
-          <t>131.0</t>
-        </is>
-      </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>135.0</t>
+          <t>138.5</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
@@ -1319,12 +1319,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>3.41</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1595.31</t>
+          <t>1302.953</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1344,17 +1344,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>2.53</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-3.39</t>
+          <t>-3.38</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>53.45</t>
+          <t>12.02</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1429,17 +1429,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>6.60</t>
+          <t>5.39</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>1.92</t>
+          <t>3.05</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1450,77 +1450,77 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>22</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>1303</t>
+          <t>1721</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>23.08</t>
+          <t>23.68</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>7.69</t>
+          <t>15.59</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>1.20</t>
+          <t>1.58</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>-10.06</t>
+          <t>-9.76</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-7.84</t>
+          <t>-8.05</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>-6.04</t>
+          <t>-6.11</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>133.4</t>
+          <t>132.9</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>148.32</t>
+          <t>147.28</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>160.95</t>
+          <t>160.17</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>171.29</t>
+          <t>170.59</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>-21.52</t>
+          <t>-15.53</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>-8.35</t>
+          <t>-8.25</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>-6.87</t>
+          <t>-7.14</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1530,7 +1530,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-127.59</t>
+          <t>-128.71</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1540,46 +1540,46 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>1695120094.609914</t>
+          <t>1693196887.497848</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>212878160.0</t>
+          <t>173429988.0</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>421450515.0</t>
+          <t>305348589.0</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>274650710.4</t>
+          <t>272591978.0</t>
         </is>
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>254522728.7</t>
+          <t>254388028.92</t>
         </is>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>146799804</t>
+          <t>32756611</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>8493004.331540482</t>
+          <t>8180445.224550578</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>17294165.64471823</t>
+          <t>6461370.136106104</t>
         </is>
       </c>
       <c r="BD3" t="n">
-        <v>212878160</v>
+        <v>173429988</v>
       </c>
       <c r="BE3" t="inlineStr">
         <is>
@@ -1643,12 +1643,12 @@
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;可能出現反轉訊號&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;3&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS3" t="inlineStr">
@@ -1658,7 +1658,7 @@
       </c>
       <c r="BT3" t="inlineStr">
         <is>
-          <t>3.08</t>
+          <t>3.01</t>
         </is>
       </c>
       <c r="BU3" t="inlineStr">
@@ -1668,7 +1668,7 @@
       </c>
       <c r="BV3" t="inlineStr">
         <is>
-          <t>25.38</t>
+          <t>26.03</t>
         </is>
       </c>
       <c r="BW3" t="inlineStr">
@@ -1683,12 +1683,12 @@
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>28.48</t>
+          <t>28.89</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
-          <t>33331</t>
+          <t>34195</t>
         </is>
       </c>
       <c r="CA3" t="inlineStr">
@@ -1708,17 +1708,17 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>132.0</t>
+          <t>132.5</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>136.0</t>
+          <t>135.0</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>131.5</t>
+          <t>131.0</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
@@ -1755,12 +1755,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>3.41</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>1712.06</t>
+          <t>1595.31</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1770,7 +1770,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>130.5</t>
+          <t>135.0</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1780,17 +1780,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>3.33</t>
+          <t>2.53</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-3.39</t>
+          <t>-3.38</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>50.94</t>
+          <t>53.45</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1855,7 +1855,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-44.94</t>
+          <t>-43.04</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1865,17 +1865,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>7.08</t>
+          <t>6.60</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>-1.14</t>
+          <t>1.92</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1886,77 +1886,77 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>22</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>1303</t>
+          <t>1721</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>23.08</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>7.69</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>-4.26</t>
+          <t>1.20</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>-8.89</t>
+          <t>-10.06</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>-7.5</t>
+          <t>-7.84</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>-5.97</t>
+          <t>-6.04</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>136.3</t>
+          <t>133.4</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>149.6</t>
+          <t>148.32</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>161.73</t>
+          <t>160.95</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>171.99</t>
+          <t>171.29</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>-28.35</t>
+          <t>-21.52</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>-8.34</t>
+          <t>-8.35</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>-6.50</t>
+          <t>-6.87</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1966,7 +1966,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-126.11</t>
+          <t>-127.59</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1976,46 +1976,46 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>1695120094.609914</t>
+          <t>1693196887.497848</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>223746689.0</t>
+          <t>212878160.0</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>397436778.6</t>
+          <t>421450515.0</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>263301806.5</t>
+          <t>274650710.4</t>
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>254911229.58</t>
+          <t>254522728.7</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>134134972</t>
+          <t>146799804</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>6892793.183689982</t>
+          <t>8493004.331540482</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>27925349.16970986</t>
+          <t>17294165.64471823</t>
         </is>
       </c>
       <c r="BD4" t="n">
-        <v>223746689</v>
+        <v>212878160</v>
       </c>
       <c r="BE4" t="inlineStr">
         <is>
@@ -2034,7 +2034,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>-27.50</t>
+          <t>-25.00</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
@@ -2079,24 +2079,24 @@
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;可能出現反轉訊號&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;3&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
         <is>
-          <t>價漲量縮</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS4" t="inlineStr">
         <is>
+          <t>3.11</t>
+        </is>
+      </c>
+      <c r="BT4" t="inlineStr">
+        <is>
           <t>3.01</t>
         </is>
       </c>
-      <c r="BT4" t="inlineStr">
-        <is>
-          <t>3.08</t>
-        </is>
-      </c>
       <c r="BU4" t="inlineStr">
         <is>
           <t>12.24</t>
@@ -2104,7 +2104,7 @@
       </c>
       <c r="BV4" t="inlineStr">
         <is>
-          <t>25.38</t>
+          <t>26.03</t>
         </is>
       </c>
       <c r="BW4" t="inlineStr">
@@ -2119,12 +2119,12 @@
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>28.48</t>
+          <t>28.89</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
-          <t>33331</t>
+          <t>34195</t>
         </is>
       </c>
       <c r="CA4" t="inlineStr">
@@ -2144,22 +2144,22 @@
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>131.0</t>
+          <t>132.0</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>133.5</t>
+          <t>136.0</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>129.0</t>
+          <t>131.5</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>130.5</t>
+          <t>135.0</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>-2.26</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2844.986</t>
+          <t>1712.06</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2216,17 +2216,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>3.33</t>
+          <t>5.78</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-3.39</t>
+          <t>-3.38</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>48.25</t>
+          <t>50.94</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2301,17 +2301,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11.77</t>
+          <t>7.08</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>-2.29</t>
+          <t>-1.14</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2322,12 +2322,12 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>22</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>1303</t>
+          <t>1721</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
@@ -2342,57 +2342,57 @@
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>-6.85</t>
+          <t>-4.26</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>-7.30</t>
+          <t>-8.89</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>-7.05</t>
+          <t>-7.5</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>-5.89</t>
+          <t>-5.97</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>140.1</t>
+          <t>136.3</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>151.12</t>
+          <t>149.6</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>162.59</t>
+          <t>161.73</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>172.77</t>
+          <t>171.99</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>-28.43</t>
+          <t>-28.35</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>-7.75</t>
+          <t>-8.34</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>-6.04</t>
+          <t>-6.50</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -2402,7 +2402,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-124.26</t>
+          <t>-126.11</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2412,46 +2412,46 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>1695120094.609914</t>
+          <t>1693196887.497848</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>373359683.0</t>
+          <t>223746689.0</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>374444824.4</t>
+          <t>397436778.6</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>252575891.8</t>
+          <t>263301806.5</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>255257682.72</t>
+          <t>254911229.58</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>121868932</t>
+          <t>134134972</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>3068692.09532273</t>
+          <t>6892793.183689982</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>40950935.056494</t>
+          <t>27925349.16970986</t>
         </is>
       </c>
       <c r="BD5" t="n">
-        <v>373359683</v>
+        <v>223746689</v>
       </c>
       <c r="BE5" t="inlineStr">
         <is>
@@ -2515,12 +2515,12 @@
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價漲量縮</t>
         </is>
       </c>
       <c r="BS5" t="inlineStr">
@@ -2530,7 +2530,7 @@
       </c>
       <c r="BT5" t="inlineStr">
         <is>
-          <t>3.08</t>
+          <t>3.01</t>
         </is>
       </c>
       <c r="BU5" t="inlineStr">
@@ -2540,7 +2540,7 @@
       </c>
       <c r="BV5" t="inlineStr">
         <is>
-          <t>25.38</t>
+          <t>26.03</t>
         </is>
       </c>
       <c r="BW5" t="inlineStr">
@@ -2555,12 +2555,12 @@
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>28.48</t>
+          <t>28.89</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
-          <t>33331</t>
+          <t>34195</t>
         </is>
       </c>
       <c r="CA5" t="inlineStr">
@@ -2580,17 +2580,17 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>133.0</t>
+          <t>131.0</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>134.5</t>
+          <t>133.5</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>129.5</t>
+          <t>129.0</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
@@ -2627,12 +2627,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>-2.96</t>
+          <t>-2.26</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>4003.393</t>
+          <t>2844.986</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2642,7 +2642,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>133.5</t>
+          <t>130.5</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2652,17 +2652,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>1.11</t>
+          <t>5.78</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-3.39</t>
+          <t>-3.38</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>36.89</t>
+          <t>48.25</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2727,7 +2727,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-43.67</t>
+          <t>-44.94</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2737,17 +2737,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>16.56</t>
+          <t>11.77</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>-5.24</t>
+          <t>-2.29</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2758,12 +2758,12 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>22</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>1303</t>
+          <t>1721</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
@@ -2778,57 +2778,57 @@
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>-7.23</t>
+          <t>-6.85</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>-5.73</t>
+          <t>-7.30</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>-6.6</t>
+          <t>-7.05</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>-5.82</t>
+          <t>-5.89</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>143.9</t>
+          <t>140.1</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>152.65</t>
+          <t>151.12</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>163.44</t>
+          <t>162.59</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>173.54</t>
+          <t>172.77</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>-22.90</t>
+          <t>-28.43</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>-6.89</t>
+          <t>-7.75</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>-5.61</t>
+          <t>-6.04</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -2838,7 +2838,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-122.53</t>
+          <t>-124.26</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2848,46 +2848,46 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>1695120094.609914</t>
+          <t>1693196887.497848</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>543328425.0</t>
+          <t>373359683.0</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>317370279.0</t>
+          <t>374444824.4</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>231842549.9</t>
+          <t>252575891.8</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>254515985.98</t>
+          <t>255257682.72</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>85527729</t>
+          <t>121868932</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>-3818988.443072045</t>
+          <t>3068692.09532273</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>42066417.85702515</t>
+          <t>40950935.056494</t>
         </is>
       </c>
       <c r="BD6" t="n">
-        <v>543328425</v>
+        <v>373359683</v>
       </c>
       <c r="BE6" t="inlineStr">
         <is>
@@ -2906,7 +2906,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>-25.83</t>
+          <t>-27.50</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
@@ -2951,7 +2951,7 @@
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;衝高回落,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>3.08</t>
+          <t>3.01</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
         <is>
-          <t>3.08</t>
+          <t>3.01</t>
         </is>
       </c>
       <c r="BU6" t="inlineStr">
@@ -2976,7 +2976,7 @@
       </c>
       <c r="BV6" t="inlineStr">
         <is>
-          <t>25.38</t>
+          <t>26.03</t>
         </is>
       </c>
       <c r="BW6" t="inlineStr">
@@ -2991,12 +2991,12 @@
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>28.48</t>
+          <t>28.89</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
         <is>
-          <t>33331</t>
+          <t>34195</t>
         </is>
       </c>
       <c r="CA6" t="inlineStr">
@@ -3016,22 +3016,22 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>135.0</t>
+          <t>133.0</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>141.5</t>
+          <t>134.5</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>132.5</t>
+          <t>129.5</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>133.5</t>
+          <t>130.5</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
@@ -3063,12 +3063,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>-8.16</t>
+          <t>-2.96</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>5388.546</t>
+          <t>4003.393</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3078,7 +3078,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>137.5</t>
+          <t>133.5</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3088,17 +3088,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-1.85</t>
+          <t>3.61</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-3.39</t>
+          <t>-3.38</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>18.56</t>
+          <t>36.89</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3163,7 +3163,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-41.98</t>
+          <t>-43.67</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3173,17 +3173,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>22.28</t>
+          <t>16.56</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>-5.06</t>
+          <t>-5.24</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3194,12 +3194,12 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>22</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>1303</t>
+          <t>1721</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
@@ -3214,57 +3214,57 @@
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>-6.59</t>
+          <t>-7.23</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>-4.57</t>
+          <t>-5.73</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>-6.11</t>
+          <t>-6.6</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>-5.70</t>
+          <t>-5.82</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>147.2</t>
+          <t>143.9</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>154.25</t>
+          <t>152.65</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>164.29</t>
+          <t>163.44</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>174.21</t>
+          <t>173.54</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>-13.45</t>
+          <t>-22.90</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>-6.00</t>
+          <t>-6.89</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>-5.29</t>
+          <t>-5.61</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -3274,7 +3274,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-121.24</t>
+          <t>-122.53</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3284,46 +3284,46 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>1695120094.609914</t>
+          <t>1693196887.497848</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>753939618.0</t>
+          <t>543328425.0</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>239835367.0</t>
+          <t>317370279.0</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>202283159.5</t>
+          <t>231842549.9</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>250790390.86</t>
+          <t>254515985.98</t>
         </is>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>37552207</t>
+          <t>85527729</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>-12161789.58854426</t>
+          <t>-3818988.443072045</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>23946656.00574735</t>
+          <t>42066417.85702515</t>
         </is>
       </c>
       <c r="BD7" t="n">
-        <v>753939618</v>
+        <v>543328425</v>
       </c>
       <c r="BE7" t="inlineStr">
         <is>
@@ -3342,7 +3342,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>-23.61</t>
+          <t>-25.83</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
@@ -3387,22 +3387,22 @@
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;衝高回落,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
         <is>
-          <t>價跌量增</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>3.17</t>
+          <t>3.08</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
         <is>
-          <t>3.08</t>
+          <t>3.01</t>
         </is>
       </c>
       <c r="BU7" t="inlineStr">
@@ -3412,7 +3412,7 @@
       </c>
       <c r="BV7" t="inlineStr">
         <is>
-          <t>25.38</t>
+          <t>26.03</t>
         </is>
       </c>
       <c r="BW7" t="inlineStr">
@@ -3427,12 +3427,12 @@
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>28.48</t>
+          <t>28.89</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
         <is>
-          <t>33331</t>
+          <t>34195</t>
         </is>
       </c>
       <c r="CA7" t="inlineStr">
@@ -3452,22 +3452,22 @@
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>147.0</t>
+          <t>135.0</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>147.0</t>
+          <t>141.5</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>135.0</t>
+          <t>132.5</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>137.5</t>
+          <t>133.5</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
@@ -3499,12 +3499,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-8.16</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>617.888</t>
+          <t>5388.546</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3514,7 +3514,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>149.5</t>
+          <t>137.5</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3524,17 +3524,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-10.74</t>
+          <t>0.72</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-3.39</t>
+          <t>-3.38</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>-14.19</t>
+          <t>18.56</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3599,7 +3599,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-36.92</t>
+          <t>-41.98</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3609,17 +3609,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>2.56</t>
+          <t>22.28</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>-1.34</t>
+          <t>-5.06</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3630,12 +3630,12 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>22</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>1303</t>
+          <t>1721</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
@@ -3650,57 +3650,57 @@
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>-0.07</t>
+          <t>-6.59</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>-3.96</t>
+          <t>-4.57</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>-5.65</t>
+          <t>-6.11</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>-5.63</t>
+          <t>-5.70</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>149.6</t>
+          <t>147.2</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>155.78</t>
+          <t>154.25</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>165.1</t>
+          <t>164.29</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>174.95</t>
+          <t>174.21</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>-1.33</t>
+          <t>-13.45</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>-5.18</t>
+          <t>-6.00</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>-5.11</t>
+          <t>-5.29</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -3710,7 +3710,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-120.53</t>
+          <t>-121.24</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3720,46 +3720,46 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>1695120094.609914</t>
+          <t>1693196887.497848</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>92809478.0</t>
+          <t>753939618.0</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>127850905.8</t>
+          <t>239835367.0</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>148995940.1</t>
+          <t>202283159.5</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>248204610.78</t>
+          <t>250790390.86</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>-21145034</t>
+          <t>37552207</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>-18726961.5147791</t>
+          <t>-12161789.58854426</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>-25359440.74628332</t>
+          <t>23946656.00574735</t>
         </is>
       </c>
       <c r="BD8" t="n">
-        <v>92809478</v>
+        <v>753939618</v>
       </c>
       <c r="BE8" t="inlineStr">
         <is>
@@ -3778,7 +3778,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>-16.94</t>
+          <t>-23.61</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
@@ -3828,17 +3828,17 @@
       </c>
       <c r="BR8" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價跌量增</t>
         </is>
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>3.44</t>
+          <t>3.17</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
         <is>
-          <t>3.08</t>
+          <t>3.01</t>
         </is>
       </c>
       <c r="BU8" t="inlineStr">
@@ -3848,7 +3848,7 @@
       </c>
       <c r="BV8" t="inlineStr">
         <is>
-          <t>25.38</t>
+          <t>26.03</t>
         </is>
       </c>
       <c r="BW8" t="inlineStr">
@@ -3863,12 +3863,12 @@
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>28.48</t>
+          <t>28.89</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
         <is>
-          <t>33331</t>
+          <t>34195</t>
         </is>
       </c>
       <c r="CA8" t="inlineStr">
@@ -3888,22 +3888,22 @@
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>150.0</t>
+          <t>147.0</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>151.5</t>
+          <t>147.0</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>149.5</t>
+          <t>135.0</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>149.5</t>
+          <t>137.5</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
@@ -3940,7 +3940,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>723.545</t>
+          <t>617.888</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3960,17 +3960,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-10.74</t>
+          <t>-7.94</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-3.39</t>
+          <t>-3.38</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>-23.11</t>
+          <t>-14.19</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -4045,17 +4045,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>2.99</t>
+          <t>2.56</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>-1.67</t>
+          <t>-1.34</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4066,12 +4066,12 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>22</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>1303</t>
+          <t>1721</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
@@ -4081,62 +4081,62 @@
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>2.22</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>-0.47</t>
+          <t>-0.07</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>-4.07</t>
+          <t>-3.96</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>-5.55</t>
+          <t>-5.65</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>-5.58</t>
+          <t>-5.63</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>150.2</t>
+          <t>149.6</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>156.57</t>
+          <t>155.78</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>165.78</t>
+          <t>165.1</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>175.58</t>
+          <t>174.95</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>-3.60</t>
+          <t>-1.33</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>-5.28</t>
+          <t>-5.18</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>-5.09</t>
+          <t>-5.11</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -4146,7 +4146,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-120.46</t>
+          <t>-120.53</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4156,46 +4156,46 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>1695120094.609914</t>
+          <t>1693196887.497848</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>108786918.0</t>
+          <t>92809478.0</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>129166834.4</t>
+          <t>127850905.8</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>167987433.4</t>
+          <t>148995940.1</t>
         </is>
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>261232164.76</t>
+          <t>248204610.78</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>-38820599</t>
+          <t>-21145034</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>-17521056.19996015</t>
+          <t>-18726961.5147791</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>-24055655.36538848</t>
+          <t>-25359440.74628332</t>
         </is>
       </c>
       <c r="BD9" t="n">
-        <v>108786918</v>
+        <v>92809478</v>
       </c>
       <c r="BE9" t="inlineStr">
         <is>
@@ -4259,7 +4259,7 @@
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
@@ -4274,7 +4274,7 @@
       </c>
       <c r="BT9" t="inlineStr">
         <is>
-          <t>3.08</t>
+          <t>3.01</t>
         </is>
       </c>
       <c r="BU9" t="inlineStr">
@@ -4284,7 +4284,7 @@
       </c>
       <c r="BV9" t="inlineStr">
         <is>
-          <t>25.38</t>
+          <t>26.03</t>
         </is>
       </c>
       <c r="BW9" t="inlineStr">
@@ -4299,12 +4299,12 @@
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>28.48</t>
+          <t>28.89</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
         <is>
-          <t>33331</t>
+          <t>34195</t>
         </is>
       </c>
       <c r="CA9" t="inlineStr">
@@ -4324,17 +4324,17 @@
       </c>
       <c r="CD9" t="inlineStr">
         <is>
+          <t>150.0</t>
+        </is>
+      </c>
+      <c r="CE9" t="inlineStr">
+        <is>
           <t>151.5</t>
         </is>
       </c>
-      <c r="CE9" t="inlineStr">
-        <is>
-          <t>152.5</t>
-        </is>
-      </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>149.0</t>
+          <t>149.5</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
@@ -4371,12 +4371,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>-0.33</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>586.018</t>
+          <t>723.545</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4396,17 +4396,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-10.74</t>
+          <t>-7.94</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-3.39</t>
+          <t>-3.38</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>-28.30</t>
+          <t>-23.11</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4481,17 +4481,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>2.42</t>
+          <t>2.99</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>-1.34</t>
+          <t>-1.67</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4502,12 +4502,12 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>22</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>1303</t>
+          <t>1721</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
@@ -4522,57 +4522,57 @@
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>-0.86</t>
+          <t>-0.47</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>-4.25</t>
+          <t>-4.07</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>-5.43</t>
+          <t>-5.55</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>-5.49</t>
+          <t>-5.58</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>150.8</t>
+          <t>150.2</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>157.5</t>
+          <t>156.57</t>
         </is>
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>166.55</t>
+          <t>165.78</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>176.23</t>
+          <t>175.58</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>-5.51</t>
+          <t>-3.60</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>-5.32</t>
+          <t>-5.28</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>-5.05</t>
+          <t>-5.09</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -4582,7 +4582,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-120.28</t>
+          <t>-120.46</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4592,46 +4592,46 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>1695120094.609914</t>
+          <t>1693196887.497848</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>87986956.0</t>
+          <t>108786918.0</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>130706959.2</t>
+          <t>129166834.4</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>182292868.5</t>
+          <t>167987433.4</t>
         </is>
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>265109106.98</t>
+          <t>261232164.76</t>
         </is>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>-51585909</t>
+          <t>-38820599</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>-16332947.26079137</t>
+          <t>-17521056.19996015</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>-23045842.8439177</t>
+          <t>-24055655.36538848</t>
         </is>
       </c>
       <c r="BD10" t="n">
-        <v>87986956</v>
+        <v>108786918</v>
       </c>
       <c r="BE10" t="inlineStr">
         <is>
@@ -4695,7 +4695,7 @@
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
@@ -4710,7 +4710,7 @@
       </c>
       <c r="BT10" t="inlineStr">
         <is>
-          <t>3.08</t>
+          <t>3.01</t>
         </is>
       </c>
       <c r="BU10" t="inlineStr">
@@ -4720,7 +4720,7 @@
       </c>
       <c r="BV10" t="inlineStr">
         <is>
-          <t>25.38</t>
+          <t>26.03</t>
         </is>
       </c>
       <c r="BW10" t="inlineStr">
@@ -4735,12 +4735,12 @@
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>28.48</t>
+          <t>28.89</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
         <is>
-          <t>33331</t>
+          <t>34195</t>
         </is>
       </c>
       <c r="CA10" t="inlineStr">
@@ -4765,12 +4765,12 @@
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>151.5</t>
+          <t>152.5</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>149.5</t>
+          <t>149.0</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
@@ -4807,12 +4807,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>0.33</t>
+          <t>-0.33</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>1040.36</t>
+          <t>586.018</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4822,7 +4822,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>150.0</t>
+          <t>149.5</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4832,17 +4832,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-11.11</t>
+          <t>-7.94</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-3.39</t>
+          <t>-3.38</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>-24.53</t>
+          <t>-28.30</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4907,7 +4907,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-36.71</t>
+          <t>-36.92</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4917,17 +4917,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>4.30</t>
+          <t>2.42</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>1.39</t>
+          <t>-1.34</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4938,17 +4938,17 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>22</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>1303</t>
+          <t>1721</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>6.67</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
@@ -4958,57 +4958,57 @@
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>-1.12</t>
+          <t>-0.86</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>-4.31</t>
+          <t>-4.25</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>-5.31</t>
+          <t>-5.43</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>-5.34</t>
+          <t>-5.49</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>151.7</t>
+          <t>150.8</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>158.52</t>
+          <t>157.5</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>167.41</t>
+          <t>166.55</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>176.86</t>
+          <t>176.23</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>-6.68</t>
+          <t>-5.51</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>-5.31</t>
+          <t>-5.32</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>-4.98</t>
+          <t>-5.05</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -5018,7 +5018,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-120.00</t>
+          <t>-120.28</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -5028,46 +5028,46 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>1695120094.609914</t>
+          <t>1693196887.497848</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>155653865.0</t>
+          <t>87986956.0</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>146314820.8</t>
+          <t>130706959.2</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>193869307.6</t>
+          <t>182292868.5</t>
         </is>
       </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>274342437.92</t>
+          <t>265109106.98</t>
         </is>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>-47554486</t>
+          <t>-51585909</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>-15112420.79113203</t>
+          <t>-16332947.26079137</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>-18551620.35453376</t>
+          <t>-23045842.8439177</t>
         </is>
       </c>
       <c r="BD11" t="n">
-        <v>155653865</v>
+        <v>87986956</v>
       </c>
       <c r="BE11" t="inlineStr">
         <is>
@@ -5086,7 +5086,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>-16.67</t>
+          <t>-16.94</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
@@ -5131,7 +5131,7 @@
       </c>
       <c r="BQ11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;可能出現反轉訊號&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;3&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR11" t="inlineStr">
@@ -5141,12 +5141,12 @@
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>3.46</t>
+          <t>3.44</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
         <is>
-          <t>3.08</t>
+          <t>3.01</t>
         </is>
       </c>
       <c r="BU11" t="inlineStr">
@@ -5156,7 +5156,7 @@
       </c>
       <c r="BV11" t="inlineStr">
         <is>
-          <t>25.38</t>
+          <t>26.03</t>
         </is>
       </c>
       <c r="BW11" t="inlineStr">
@@ -5171,12 +5171,12 @@
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>28.48</t>
+          <t>28.89</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
         <is>
-          <t>33331</t>
+          <t>34195</t>
         </is>
       </c>
       <c r="CA11" t="inlineStr">
@@ -5196,7 +5196,7 @@
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>150.5</t>
+          <t>151.5</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
@@ -5206,12 +5206,12 @@
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>146.5</t>
+          <t>149.5</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>150.0</t>
+          <t>149.5</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
@@ -5243,12 +5243,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>-1.97</t>
+          <t>0.33</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>1294.619</t>
+          <t>1040.36</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5258,7 +5258,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>149.5</t>
+          <t>150.0</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5268,17 +5268,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-10.74</t>
+          <t>-8.3</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-3.39</t>
+          <t>-3.38</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>-16.90</t>
+          <t>-24.53</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5343,7 +5343,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-36.92</t>
+          <t>-36.71</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5353,17 +5353,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>5.35</t>
+          <t>4.30</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>-1.00</t>
+          <t>1.39</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5374,77 +5374,77 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>22</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>1303</t>
+          <t>1721</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>6.67</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>2.22</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>-2.35</t>
+          <t>-1.12</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>-3.97</t>
+          <t>-4.31</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>-5.19</t>
+          <t>-5.31</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>-5.28</t>
+          <t>-5.34</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>153.1</t>
+          <t>151.7</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>159.43</t>
+          <t>158.52</t>
         </is>
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>168.15</t>
+          <t>167.41</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>177.52</t>
+          <t>176.86</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>-7.56</t>
+          <t>-6.68</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>-5.26</t>
+          <t>-5.31</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>-4.89</t>
+          <t>-4.98</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
@@ -5454,7 +5454,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-119.66</t>
+          <t>-120.00</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5464,46 +5464,46 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>1695120094.609914</t>
+          <t>1693196887.497848</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>194017312.0</t>
+          <t>155653865.0</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>164730952.0</t>
+          <t>146314820.8</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>198237890.5</t>
+          <t>193869307.6</t>
         </is>
       </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>287305576.32</t>
+          <t>274342437.92</t>
         </is>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>-33506938</t>
+          <t>-47554486</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>-14487111.77960444</t>
+          <t>-15112420.79113203</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>-18718770.60703766</t>
+          <t>-18551620.35453376</t>
         </is>
       </c>
       <c r="BD12" t="n">
-        <v>194017312</v>
+        <v>155653865</v>
       </c>
       <c r="BE12" t="inlineStr">
         <is>
@@ -5522,7 +5522,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>-16.94</t>
+          <t>-16.67</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
@@ -5567,7 +5567,7 @@
       </c>
       <c r="BQ12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;可能出現反轉訊號&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;3&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR12" t="inlineStr">
@@ -5577,12 +5577,12 @@
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>3.44</t>
+          <t>3.46</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
         <is>
-          <t>3.08</t>
+          <t>3.01</t>
         </is>
       </c>
       <c r="BU12" t="inlineStr">
@@ -5592,7 +5592,7 @@
       </c>
       <c r="BV12" t="inlineStr">
         <is>
-          <t>25.38</t>
+          <t>26.03</t>
         </is>
       </c>
       <c r="BW12" t="inlineStr">
@@ -5607,12 +5607,12 @@
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>28.48</t>
+          <t>28.89</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
         <is>
-          <t>33331</t>
+          <t>34195</t>
         </is>
       </c>
       <c r="CA12" t="inlineStr">
@@ -5632,22 +5632,22 @@
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>152.0</t>
+          <t>150.5</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>152.0</t>
+          <t>151.5</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>148.5</t>
+          <t>146.5</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
         <is>
-          <t>149.5</t>
+          <t>150.0</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">
@@ -5679,12 +5679,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>1.24</t>
+          <t>0.14</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>1128.761</t>
+          <t>6301.223</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -5694,7 +5694,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>36.85</t>
+          <t>36.9</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -5709,12 +5709,12 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>-1.23</t>
+          <t>-1.09</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>-1.19</t>
+          <t>29.52</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -5779,7 +5779,7 @@
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>-14.60</t>
+          <t>-14.48</t>
         </is>
       </c>
       <c r="X13" t="inlineStr">
@@ -5789,17 +5789,17 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>12.03</t>
+          <t>67.14</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2.09</t>
+          <t>-1.63</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
@@ -5810,280 +5810,280 @@
       <c r="AC13" t="inlineStr"/>
       <c r="AD13" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
-          <t>1129</t>
+          <t>6301</t>
         </is>
       </c>
       <c r="AF13" t="inlineStr">
         <is>
+          <t>40.0</t>
+        </is>
+      </c>
+      <c r="AG13" t="inlineStr">
+        <is>
+          <t>29.75</t>
+        </is>
+      </c>
+      <c r="AH13" t="inlineStr">
+        <is>
+          <t>0.82</t>
+        </is>
+      </c>
+      <c r="AI13" t="inlineStr">
+        <is>
+          <t>-4.24</t>
+        </is>
+      </c>
+      <c r="AJ13" t="inlineStr">
+        <is>
+          <t>-4.85</t>
+        </is>
+      </c>
+      <c r="AK13" t="inlineStr">
+        <is>
+          <t>-2.68</t>
+        </is>
+      </c>
+      <c r="AL13" t="inlineStr">
+        <is>
+          <t>36.60000000000001</t>
+        </is>
+      </c>
+      <c r="AM13" t="inlineStr">
+        <is>
+          <t>38.22</t>
+        </is>
+      </c>
+      <c r="AN13" t="inlineStr">
+        <is>
+          <t>40.17</t>
+        </is>
+      </c>
+      <c r="AO13" t="inlineStr">
+        <is>
+          <t>41.28</t>
+        </is>
+      </c>
+      <c r="AP13" t="inlineStr">
+        <is>
+          <t>-7.24</t>
+        </is>
+      </c>
+      <c r="AQ13" t="inlineStr">
+        <is>
+          <t>-1.08</t>
+        </is>
+      </c>
+      <c r="AR13" t="inlineStr">
+        <is>
+          <t>-1.01</t>
+        </is>
+      </c>
+      <c r="AS13" t="inlineStr">
+        <is>
+          <t>2.69</t>
+        </is>
+      </c>
+      <c r="AT13" t="inlineStr">
+        <is>
+          <t>-137.62</t>
+        </is>
+      </c>
+      <c r="AU13" t="inlineStr">
+        <is>
+          <t>2025/10/23</t>
+        </is>
+      </c>
+      <c r="AV13" t="inlineStr">
+        <is>
+          <t>150693340.205165</t>
+        </is>
+      </c>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>232650449.0</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>74142370.0</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr">
+        <is>
+          <t>57245793.0</t>
+        </is>
+      </c>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>34130931.06</t>
+        </is>
+      </c>
+      <c r="BA13" t="inlineStr">
+        <is>
+          <t>16896577</t>
+        </is>
+      </c>
+      <c r="BB13" t="inlineStr">
+        <is>
+          <t>3442386.786094812</t>
+        </is>
+      </c>
+      <c r="BC13" t="inlineStr">
+        <is>
+          <t>16400757.27416717</t>
+        </is>
+      </c>
+      <c r="BD13" t="n">
+        <v>232650449</v>
+      </c>
+      <c r="BE13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF13" t="inlineStr">
+        <is>
+          <t>41.5</t>
+        </is>
+      </c>
+      <c r="BG13" t="inlineStr">
+        <is>
+          <t>2025/08/07</t>
+        </is>
+      </c>
+      <c r="BH13" t="inlineStr">
+        <is>
+          <t>-11.08</t>
+        </is>
+      </c>
+      <c r="BI13" t="inlineStr">
+        <is>
+          <t>新光鋼</t>
+        </is>
+      </c>
+      <c r="BJ13" t="inlineStr">
+        <is>
+          <t>新光鋼</t>
+        </is>
+      </c>
+      <c r="BK13" t="inlineStr">
+        <is>
+          <t>鋼鐵工業</t>
+        </is>
+      </c>
+      <c r="BL13" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="BM13" t="inlineStr">
+        <is>
+          <t>0.61</t>
+        </is>
+      </c>
+      <c r="BN13" t="inlineStr">
+        <is>
+          <t>-13.67996844119094</t>
+        </is>
+      </c>
+      <c r="BO13" t="inlineStr">
+        <is>
+          <t>-10.11024290164889</t>
+        </is>
+      </c>
+      <c r="BP13" t="inlineStr">
+        <is>
+          <t>24.12947661306339</t>
+        </is>
+      </c>
+      <c r="BQ13" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BR13" t="inlineStr">
+        <is>
+          <t>價-量增</t>
+        </is>
+      </c>
+      <c r="BS13" t="inlineStr">
+        <is>
+          <t>1.02</t>
+        </is>
+      </c>
+      <c r="BT13" t="inlineStr">
+        <is>
+          <t>6.78</t>
+        </is>
+      </c>
+      <c r="BU13" t="inlineStr">
+        <is>
+          <t>11.90</t>
+        </is>
+      </c>
+      <c r="BV13" t="inlineStr">
+        <is>
+          <t>15.25</t>
+        </is>
+      </c>
+      <c r="BW13" t="inlineStr">
+        <is>
+          <t>8.69%</t>
+        </is>
+      </c>
+      <c r="BX13" t="inlineStr">
+        <is>
+          <t>5.19%</t>
+        </is>
+      </c>
+      <c r="BY13" t="inlineStr">
+        <is>
+          <t>28.89</t>
+        </is>
+      </c>
+      <c r="BZ13" t="inlineStr">
+        <is>
+          <t>11850</t>
+        </is>
+      </c>
+      <c r="CA13" t="inlineStr">
+        <is>
+          <t>鋼板38.80%、熱軋及鍍鋅鋼板33.80%、不�袗�板12.60%、特殊鋼板7.00%、加工及其他6.90%、型鋼0.90% (2024年)</t>
+        </is>
+      </c>
+      <c r="CB13" t="inlineStr">
+        <is>
+          <t>新光鋼-鋼鐵工業-上市</t>
+        </is>
+      </c>
+      <c r="CC13" t="inlineStr">
+        <is>
+          <t>鋼鐵工業右下上市</t>
+        </is>
+      </c>
+      <c r="CD13" t="inlineStr">
+        <is>
+          <t>37.0</t>
+        </is>
+      </c>
+      <c r="CE13" t="inlineStr">
+        <is>
           <t>37.5</t>
         </is>
       </c>
-      <c r="AG13" t="inlineStr">
-        <is>
-          <t>16.42</t>
-        </is>
-      </c>
-      <c r="AH13" t="inlineStr">
-        <is>
-          <t>0.66</t>
-        </is>
-      </c>
-      <c r="AI13" t="inlineStr">
-        <is>
-          <t>-4.68</t>
-        </is>
-      </c>
-      <c r="AJ13" t="inlineStr">
-        <is>
-          <t>-4.69</t>
-        </is>
-      </c>
-      <c r="AK13" t="inlineStr">
-        <is>
-          <t>-2.48</t>
-        </is>
-      </c>
-      <c r="AL13" t="inlineStr">
-        <is>
-          <t>36.61</t>
-        </is>
-      </c>
-      <c r="AM13" t="inlineStr">
-        <is>
-          <t>38.41</t>
-        </is>
-      </c>
-      <c r="AN13" t="inlineStr">
-        <is>
-          <t>40.3</t>
-        </is>
-      </c>
-      <c r="AO13" t="inlineStr">
-        <is>
-          <t>41.32</t>
-        </is>
-      </c>
-      <c r="AP13" t="inlineStr">
-        <is>
-          <t>-12.91</t>
-        </is>
-      </c>
-      <c r="AQ13" t="inlineStr">
-        <is>
-          <t>-1.12</t>
-        </is>
-      </c>
-      <c r="AR13" t="inlineStr">
-        <is>
-          <t>-0.99</t>
-        </is>
-      </c>
-      <c r="AS13" t="inlineStr">
-        <is>
-          <t>2.69</t>
-        </is>
-      </c>
-      <c r="AT13" t="inlineStr">
-        <is>
-          <t>-136.94</t>
-        </is>
-      </c>
-      <c r="AU13" t="inlineStr">
-        <is>
-          <t>2025/10/23</t>
-        </is>
-      </c>
-      <c r="AV13" t="inlineStr">
-        <is>
-          <t>150408451.7952586</t>
-        </is>
-      </c>
-      <c r="AW13" t="inlineStr">
-        <is>
-          <t>41298962.0</t>
-        </is>
-      </c>
-      <c r="AX13" t="inlineStr">
-        <is>
-          <t>35487232.0</t>
-        </is>
-      </c>
-      <c r="AY13" t="inlineStr">
-        <is>
-          <t>35914543.8</t>
-        </is>
-      </c>
-      <c r="AZ13" t="inlineStr">
-        <is>
-          <t>29950115.64</t>
-        </is>
-      </c>
-      <c r="BA13" t="inlineStr">
-        <is>
-          <t>-427311</t>
-        </is>
-      </c>
-      <c r="BB13" t="inlineStr">
-        <is>
-          <t>1086319.424627111</t>
-        </is>
-      </c>
-      <c r="BC13" t="inlineStr">
-        <is>
-          <t>1798775.809179619</t>
-        </is>
-      </c>
-      <c r="BD13" t="n">
-        <v>41298962</v>
-      </c>
-      <c r="BE13" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BF13" t="inlineStr">
-        <is>
-          <t>41.5</t>
-        </is>
-      </c>
-      <c r="BG13" t="inlineStr">
-        <is>
-          <t>2025/08/07</t>
-        </is>
-      </c>
-      <c r="BH13" t="inlineStr">
-        <is>
-          <t>-11.20</t>
-        </is>
-      </c>
-      <c r="BI13" t="inlineStr">
-        <is>
-          <t>新光鋼</t>
-        </is>
-      </c>
-      <c r="BJ13" t="inlineStr">
-        <is>
-          <t>新光鋼</t>
-        </is>
-      </c>
-      <c r="BK13" t="inlineStr">
-        <is>
-          <t>鋼鐵工業</t>
-        </is>
-      </c>
-      <c r="BL13" t="inlineStr">
-        <is>
-          <t>上市</t>
-        </is>
-      </c>
-      <c r="BM13" t="inlineStr">
-        <is>
-          <t>0.61</t>
-        </is>
-      </c>
-      <c r="BN13" t="inlineStr">
-        <is>
-          <t>-13.67996844119094</t>
-        </is>
-      </c>
-      <c r="BO13" t="inlineStr">
-        <is>
-          <t>-10.11024290164889</t>
-        </is>
-      </c>
-      <c r="BP13" t="inlineStr">
-        <is>
-          <t>24.12947661306339</t>
-        </is>
-      </c>
-      <c r="BQ13" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;可能出現反轉訊號&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;3&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="BR13" t="inlineStr">
-        <is>
-          <t>價-量增</t>
-        </is>
-      </c>
-      <c r="BS13" t="inlineStr">
-        <is>
-          <t>1.01</t>
-        </is>
-      </c>
-      <c r="BT13" t="inlineStr">
-        <is>
-          <t>6.78</t>
-        </is>
-      </c>
-      <c r="BU13" t="inlineStr">
-        <is>
-          <t>11.90</t>
-        </is>
-      </c>
-      <c r="BV13" t="inlineStr">
-        <is>
-          <t>15.23</t>
-        </is>
-      </c>
-      <c r="BW13" t="inlineStr">
-        <is>
-          <t>8.69%</t>
-        </is>
-      </c>
-      <c r="BX13" t="inlineStr">
-        <is>
-          <t>5.19%</t>
-        </is>
-      </c>
-      <c r="BY13" t="inlineStr">
-        <is>
-          <t>28.48</t>
-        </is>
-      </c>
-      <c r="BZ13" t="inlineStr">
-        <is>
-          <t>11834</t>
-        </is>
-      </c>
-      <c r="CA13" t="inlineStr">
-        <is>
-          <t>鋼板38.80%、熱軋及鍍鋅鋼板33.80%、不�袗�板12.60%、特殊鋼板7.00%、加工及其他6.90%、型鋼0.90% (2024年)</t>
-        </is>
-      </c>
-      <c r="CB13" t="inlineStr">
-        <is>
-          <t>新光鋼-鋼鐵工業-上市</t>
-        </is>
-      </c>
-      <c r="CC13" t="inlineStr">
-        <is>
-          <t>鋼鐵工業右下上市</t>
-        </is>
-      </c>
-      <c r="CD13" t="inlineStr">
-        <is>
-          <t>36.4</t>
-        </is>
-      </c>
-      <c r="CE13" t="inlineStr">
-        <is>
-          <t>36.95</t>
-        </is>
-      </c>
       <c r="CF13" t="inlineStr">
         <is>
-          <t>36.0</t>
+          <t>36.9</t>
         </is>
       </c>
       <c r="CG13" t="inlineStr">
         <is>
-          <t>36.85</t>
+          <t>36.9</t>
         </is>
       </c>
       <c r="CH13" t="inlineStr">
@@ -6115,12 +6115,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>0.83</t>
+          <t>1.24</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>776.396</t>
+          <t>1128.761</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -6130,7 +6130,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>36.4</t>
+          <t>36.85</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -6140,17 +6140,17 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>1.22</t>
+          <t>0.14</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>-1.23</t>
+          <t>-1.09</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>9.74</t>
+          <t>-1.19</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -6215,7 +6215,7 @@
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>-15.64</t>
+          <t>-14.60</t>
         </is>
       </c>
       <c r="X14" t="inlineStr">
@@ -6225,17 +6225,17 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>8.27</t>
+          <t>12.03</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>0.70</t>
+          <t>2.09</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
@@ -6246,77 +6246,77 @@
       <c r="AC14" t="inlineStr"/>
       <c r="AD14" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
-          <t>1129</t>
+          <t>6301</t>
         </is>
       </c>
       <c r="AF14" t="inlineStr">
         <is>
-          <t>11.76</t>
+          <t>37.5</t>
         </is>
       </c>
       <c r="AG14" t="inlineStr">
         <is>
-          <t>3.92</t>
+          <t>16.42</t>
         </is>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>-0.90</t>
+          <t>0.66</t>
         </is>
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>-4.83</t>
+          <t>-4.68</t>
         </is>
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>-4.54</t>
+          <t>-4.69</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>-2.31</t>
+          <t>-2.48</t>
         </is>
       </c>
       <c r="AL14" t="inlineStr">
         <is>
-          <t>36.73</t>
+          <t>36.61</t>
         </is>
       </c>
       <c r="AM14" t="inlineStr">
         <is>
-          <t>38.6</t>
+          <t>38.41</t>
         </is>
       </c>
       <c r="AN14" t="inlineStr">
         <is>
-          <t>40.43</t>
+          <t>40.3</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>41.39</t>
+          <t>41.32</t>
         </is>
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>-19.31</t>
+          <t>-12.91</t>
         </is>
       </c>
       <c r="AQ14" t="inlineStr">
         <is>
-          <t>-1.15</t>
+          <t>-1.12</t>
         </is>
       </c>
       <c r="AR14" t="inlineStr">
         <is>
-          <t>-0.96</t>
+          <t>-0.99</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr">
@@ -6326,7 +6326,7 @@
       </c>
       <c r="AT14" t="inlineStr">
         <is>
-          <t>-135.75</t>
+          <t>-136.94</t>
         </is>
       </c>
       <c r="AU14" t="inlineStr">
@@ -6336,46 +6336,46 @@
       </c>
       <c r="AV14" t="inlineStr">
         <is>
-          <t>150408451.7952586</t>
+          <t>150693340.205165</t>
         </is>
       </c>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>28176624.0</t>
+          <t>41298962.0</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>37871124.0</t>
+          <t>35487232.0</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
-          <t>34509118.0</t>
+          <t>35914543.8</t>
         </is>
       </c>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>29545425.32</t>
+          <t>29950115.64</t>
         </is>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
-          <t>3362006</t>
+          <t>-427311</t>
         </is>
       </c>
       <c r="BB14" t="inlineStr">
         <is>
-          <t>956781.9001630185</t>
+          <t>1086319.424627111</t>
         </is>
       </c>
       <c r="BC14" t="inlineStr">
         <is>
-          <t>1376505.330298137</t>
+          <t>1798775.809179619</t>
         </is>
       </c>
       <c r="BD14" t="n">
-        <v>28176624</v>
+        <v>41298962</v>
       </c>
       <c r="BE14" t="inlineStr">
         <is>
@@ -6394,7 +6394,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>-12.29</t>
+          <t>-11.20</t>
         </is>
       </c>
       <c r="BI14" t="inlineStr">
@@ -6439,17 +6439,17 @@
       </c>
       <c r="BQ14" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;可能出現反轉訊號&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;3&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR14" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS14" t="inlineStr">
         <is>
-          <t>1.00</t>
+          <t>1.01</t>
         </is>
       </c>
       <c r="BT14" t="inlineStr">
@@ -6464,7 +6464,7 @@
       </c>
       <c r="BV14" t="inlineStr">
         <is>
-          <t>15.23</t>
+          <t>15.25</t>
         </is>
       </c>
       <c r="BW14" t="inlineStr">
@@ -6479,12 +6479,12 @@
       </c>
       <c r="BY14" t="inlineStr">
         <is>
-          <t>28.48</t>
+          <t>28.89</t>
         </is>
       </c>
       <c r="BZ14" t="inlineStr">
         <is>
-          <t>11834</t>
+          <t>11850</t>
         </is>
       </c>
       <c r="CA14" t="inlineStr">
@@ -6504,12 +6504,12 @@
       </c>
       <c r="CD14" t="inlineStr">
         <is>
-          <t>36.3</t>
+          <t>36.4</t>
         </is>
       </c>
       <c r="CE14" t="inlineStr">
         <is>
-          <t>36.55</t>
+          <t>36.95</t>
         </is>
       </c>
       <c r="CF14" t="inlineStr">
@@ -6519,7 +6519,7 @@
       </c>
       <c r="CG14" t="inlineStr">
         <is>
-          <t>36.4</t>
+          <t>36.85</t>
         </is>
       </c>
       <c r="CH14" t="inlineStr">
@@ -6551,12 +6551,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>-1.76</t>
+          <t>0.83</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>1212.053</t>
+          <t>776.396</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -6566,7 +6566,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>36.1</t>
+          <t>36.4</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -6576,17 +6576,17 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>2.04</t>
+          <t>1.36</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>-1.23</t>
+          <t>-1.09</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>3.03</t>
+          <t>9.74</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -6651,7 +6651,7 @@
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>-16.34</t>
+          <t>-15.64</t>
         </is>
       </c>
       <c r="X15" t="inlineStr">
@@ -6661,17 +6661,17 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>12.91</t>
+          <t>8.27</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>-1.38</t>
+          <t>0.70</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
@@ -6682,77 +6682,77 @@
       <c r="AC15" t="inlineStr"/>
       <c r="AD15" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
-          <t>1129</t>
+          <t>6301</t>
         </is>
       </c>
       <c r="AF15" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>11.76</t>
         </is>
       </c>
       <c r="AG15" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>3.92</t>
         </is>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>-2.62</t>
+          <t>-0.90</t>
         </is>
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>-4.47</t>
+          <t>-4.83</t>
         </is>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>-4.38</t>
+          <t>-4.54</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>-2.09</t>
+          <t>-2.31</t>
         </is>
       </c>
       <c r="AL15" t="inlineStr">
         <is>
-          <t>37.07000000000001</t>
+          <t>36.73</t>
         </is>
       </c>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>38.8</t>
+          <t>38.6</t>
         </is>
       </c>
       <c r="AN15" t="inlineStr">
         <is>
-          <t>40.58</t>
+          <t>40.43</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>41.45</t>
+          <t>41.39</t>
         </is>
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>-22.07</t>
+          <t>-19.31</t>
         </is>
       </c>
       <c r="AQ15" t="inlineStr">
         <is>
-          <t>-1.12</t>
+          <t>-1.15</t>
         </is>
       </c>
       <c r="AR15" t="inlineStr">
         <is>
-          <t>-0.91</t>
+          <t>-0.96</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr">
@@ -6762,7 +6762,7 @@
       </c>
       <c r="AT15" t="inlineStr">
         <is>
-          <t>-134.02</t>
+          <t>-135.75</t>
         </is>
       </c>
       <c r="AU15" t="inlineStr">
@@ -6772,46 +6772,46 @@
       </c>
       <c r="AV15" t="inlineStr">
         <is>
-          <t>150408451.7952586</t>
+          <t>150693340.205165</t>
         </is>
       </c>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>43823516.0</t>
+          <t>28176624.0</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>36085517.8</t>
+          <t>37871124.0</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>35025550.9</t>
+          <t>34509118.0</t>
         </is>
       </c>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>29409986.0</t>
+          <t>29545425.32</t>
         </is>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
-          <t>1059966</t>
+          <t>3362006</t>
         </is>
       </c>
       <c r="BB15" t="inlineStr">
         <is>
-          <t>880468.5492293607</t>
+          <t>956781.9001630185</t>
         </is>
       </c>
       <c r="BC15" t="inlineStr">
         <is>
-          <t>2130065.670099653</t>
+          <t>1376505.330298137</t>
         </is>
       </c>
       <c r="BD15" t="n">
-        <v>43823516</v>
+        <v>28176624</v>
       </c>
       <c r="BE15" t="inlineStr">
         <is>
@@ -6830,7 +6830,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>-13.01</t>
+          <t>-12.29</t>
         </is>
       </c>
       <c r="BI15" t="inlineStr">
@@ -6875,7 +6875,7 @@
       </c>
       <c r="BQ15" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR15" t="inlineStr">
@@ -6885,7 +6885,7 @@
       </c>
       <c r="BS15" t="inlineStr">
         <is>
-          <t>0.99</t>
+          <t>1.00</t>
         </is>
       </c>
       <c r="BT15" t="inlineStr">
@@ -6900,7 +6900,7 @@
       </c>
       <c r="BV15" t="inlineStr">
         <is>
-          <t>15.23</t>
+          <t>15.25</t>
         </is>
       </c>
       <c r="BW15" t="inlineStr">
@@ -6915,12 +6915,12 @@
       </c>
       <c r="BY15" t="inlineStr">
         <is>
-          <t>28.48</t>
+          <t>28.89</t>
         </is>
       </c>
       <c r="BZ15" t="inlineStr">
         <is>
-          <t>11834</t>
+          <t>11850</t>
         </is>
       </c>
       <c r="CA15" t="inlineStr">
@@ -6940,22 +6940,22 @@
       </c>
       <c r="CD15" t="inlineStr">
         <is>
-          <t>36.85</t>
+          <t>36.3</t>
         </is>
       </c>
       <c r="CE15" t="inlineStr">
         <is>
-          <t>36.85</t>
+          <t>36.55</t>
         </is>
       </c>
       <c r="CF15" t="inlineStr">
         <is>
-          <t>35.85</t>
+          <t>36.0</t>
         </is>
       </c>
       <c r="CG15" t="inlineStr">
         <is>
-          <t>36.1</t>
+          <t>36.4</t>
         </is>
       </c>
       <c r="CH15" t="inlineStr">
@@ -6987,12 +6987,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>-0.54</t>
+          <t>-1.76</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>672.504</t>
+          <t>1212.053</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -7002,7 +7002,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>36.75</t>
+          <t>36.1</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -7012,17 +7012,17 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>0.27</t>
+          <t>2.17</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>-1.23</t>
+          <t>-1.09</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>-2.04</t>
+          <t>3.03</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -7087,7 +7087,7 @@
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>-14.83</t>
+          <t>-16.34</t>
         </is>
       </c>
       <c r="X16" t="inlineStr">
@@ -7097,17 +7097,17 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>7.17</t>
+          <t>12.91</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>-1.09</t>
+          <t>-1.38</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
@@ -7118,12 +7118,12 @@
       <c r="AC16" t="inlineStr"/>
       <c r="AD16" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
-          <t>1129</t>
+          <t>6301</t>
         </is>
       </c>
       <c r="AF16" t="inlineStr">
@@ -7138,57 +7138,57 @@
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>-1.92</t>
+          <t>-2.62</t>
         </is>
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>-3.97</t>
+          <t>-4.47</t>
         </is>
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>-4.25</t>
+          <t>-4.38</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>-1.83</t>
+          <t>-2.09</t>
         </is>
       </c>
       <c r="AL16" t="inlineStr">
         <is>
-          <t>37.47000000000001</t>
+          <t>37.07000000000001</t>
         </is>
       </c>
       <c r="AM16" t="inlineStr">
         <is>
-          <t>39.02</t>
+          <t>38.8</t>
         </is>
       </c>
       <c r="AN16" t="inlineStr">
         <is>
-          <t>40.75</t>
+          <t>40.58</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>41.51</t>
+          <t>41.45</t>
         </is>
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>-19.33</t>
+          <t>-22.07</t>
         </is>
       </c>
       <c r="AQ16" t="inlineStr">
         <is>
-          <t>-1.03</t>
+          <t>-1.12</t>
         </is>
       </c>
       <c r="AR16" t="inlineStr">
         <is>
-          <t>-0.86</t>
+          <t>-0.91</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr">
@@ -7198,7 +7198,7 @@
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>-132.14</t>
+          <t>-134.02</t>
         </is>
       </c>
       <c r="AU16" t="inlineStr">
@@ -7208,46 +7208,46 @@
       </c>
       <c r="AV16" t="inlineStr">
         <is>
-          <t>150408451.7952586</t>
+          <t>150693340.205165</t>
         </is>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>24762299.0</t>
+          <t>43823516.0</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>31929308.6</t>
+          <t>36085517.8</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>32595150.7</t>
+          <t>35025550.9</t>
         </is>
       </c>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>29130934.74</t>
+          <t>29409986.0</t>
         </is>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
-          <t>-665842</t>
+          <t>1059966</t>
         </is>
       </c>
       <c r="BB16" t="inlineStr">
         <is>
-          <t>653269.0727074891</t>
+          <t>880468.5492293607</t>
         </is>
       </c>
       <c r="BC16" t="inlineStr">
         <is>
-          <t>1454053.953026839</t>
+          <t>2130065.670099653</t>
         </is>
       </c>
       <c r="BD16" t="n">
-        <v>24762299</v>
+        <v>43823516</v>
       </c>
       <c r="BE16" t="inlineStr">
         <is>
@@ -7266,7 +7266,7 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>-11.45</t>
+          <t>-13.01</t>
         </is>
       </c>
       <c r="BI16" t="inlineStr">
@@ -7321,7 +7321,7 @@
       </c>
       <c r="BS16" t="inlineStr">
         <is>
-          <t>1.01</t>
+          <t>0.99</t>
         </is>
       </c>
       <c r="BT16" t="inlineStr">
@@ -7336,7 +7336,7 @@
       </c>
       <c r="BV16" t="inlineStr">
         <is>
-          <t>15.23</t>
+          <t>15.25</t>
         </is>
       </c>
       <c r="BW16" t="inlineStr">
@@ -7351,12 +7351,12 @@
       </c>
       <c r="BY16" t="inlineStr">
         <is>
-          <t>28.48</t>
+          <t>28.89</t>
         </is>
       </c>
       <c r="BZ16" t="inlineStr">
         <is>
-          <t>11834</t>
+          <t>11850</t>
         </is>
       </c>
       <c r="CA16" t="inlineStr">
@@ -7376,22 +7376,22 @@
       </c>
       <c r="CD16" t="inlineStr">
         <is>
-          <t>36.95</t>
+          <t>36.85</t>
         </is>
       </c>
       <c r="CE16" t="inlineStr">
         <is>
-          <t>37.3</t>
+          <t>36.85</t>
         </is>
       </c>
       <c r="CF16" t="inlineStr">
         <is>
-          <t>36.6</t>
+          <t>35.85</t>
         </is>
       </c>
       <c r="CG16" t="inlineStr">
         <is>
-          <t>36.75</t>
+          <t>36.1</t>
         </is>
       </c>
       <c r="CH16" t="inlineStr">
@@ -7423,12 +7423,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>-1.34</t>
+          <t>-0.54</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>1065.248</t>
+          <t>672.504</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -7438,7 +7438,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>36.95</t>
+          <t>36.75</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -7448,17 +7448,17 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>-0.27</t>
+          <t>0.41</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>-1.23</t>
+          <t>-1.09</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>28.28</t>
+          <t>-2.04</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -7523,7 +7523,7 @@
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>-14.37</t>
+          <t>-14.83</t>
         </is>
       </c>
       <c r="X17" t="inlineStr">
@@ -7533,17 +7533,17 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>11.35</t>
+          <t>7.17</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>-0.81</t>
+          <t>-1.09</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
@@ -7554,12 +7554,12 @@
       <c r="AC17" t="inlineStr"/>
       <c r="AD17" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
-          <t>1129</t>
+          <t>6301</t>
         </is>
       </c>
       <c r="AF17" t="inlineStr">
@@ -7569,62 +7569,62 @@
       </c>
       <c r="AG17" t="inlineStr">
         <is>
-          <t>9.38</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>-1.86</t>
+          <t>-1.92</t>
         </is>
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>-4.02</t>
+          <t>-3.97</t>
         </is>
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>-4.09</t>
+          <t>-4.25</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>-1.60</t>
+          <t>-1.83</t>
         </is>
       </c>
       <c r="AL17" t="inlineStr">
         <is>
-          <t>37.65000000000001</t>
+          <t>37.47000000000001</t>
         </is>
       </c>
       <c r="AM17" t="inlineStr">
         <is>
-          <t>39.23</t>
+          <t>39.02</t>
         </is>
       </c>
       <c r="AN17" t="inlineStr">
         <is>
-          <t>40.9</t>
+          <t>40.75</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>41.57</t>
+          <t>41.51</t>
         </is>
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>-18.37</t>
+          <t>-19.33</t>
         </is>
       </c>
       <c r="AQ17" t="inlineStr">
         <is>
-          <t>-0.97</t>
+          <t>-1.03</t>
         </is>
       </c>
       <c r="AR17" t="inlineStr">
         <is>
-          <t>-0.82</t>
+          <t>-0.86</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr">
@@ -7634,7 +7634,7 @@
       </c>
       <c r="AT17" t="inlineStr">
         <is>
-          <t>-130.59</t>
+          <t>-132.14</t>
         </is>
       </c>
       <c r="AU17" t="inlineStr">
@@ -7644,46 +7644,46 @@
       </c>
       <c r="AV17" t="inlineStr">
         <is>
-          <t>150408451.7952586</t>
+          <t>150693340.205165</t>
         </is>
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>39374759.0</t>
+          <t>24762299.0</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>40349216.0</t>
+          <t>31929308.6</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>31454761.9</t>
+          <t>32595150.7</t>
         </is>
       </c>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>29061426.18</t>
+          <t>29130934.74</t>
         </is>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
-          <t>8894454</t>
+          <t>-665842</t>
         </is>
       </c>
       <c r="BB17" t="inlineStr">
         <is>
-          <t>507671.8217403347</t>
+          <t>653269.0727074891</t>
         </is>
       </c>
       <c r="BC17" t="inlineStr">
         <is>
-          <t>2478665.680314712</t>
+          <t>1454053.953026839</t>
         </is>
       </c>
       <c r="BD17" t="n">
-        <v>39374759</v>
+        <v>24762299</v>
       </c>
       <c r="BE17" t="inlineStr">
         <is>
@@ -7702,7 +7702,7 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>-10.96</t>
+          <t>-11.45</t>
         </is>
       </c>
       <c r="BI17" t="inlineStr">
@@ -7747,17 +7747,17 @@
       </c>
       <c r="BQ17" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR17" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS17" t="inlineStr">
         <is>
-          <t>1.02</t>
+          <t>1.01</t>
         </is>
       </c>
       <c r="BT17" t="inlineStr">
@@ -7772,7 +7772,7 @@
       </c>
       <c r="BV17" t="inlineStr">
         <is>
-          <t>15.23</t>
+          <t>15.25</t>
         </is>
       </c>
       <c r="BW17" t="inlineStr">
@@ -7787,12 +7787,12 @@
       </c>
       <c r="BY17" t="inlineStr">
         <is>
-          <t>28.48</t>
+          <t>28.89</t>
         </is>
       </c>
       <c r="BZ17" t="inlineStr">
         <is>
-          <t>11834</t>
+          <t>11850</t>
         </is>
       </c>
       <c r="CA17" t="inlineStr">
@@ -7812,22 +7812,22 @@
       </c>
       <c r="CD17" t="inlineStr">
         <is>
+          <t>36.95</t>
+        </is>
+      </c>
+      <c r="CE17" t="inlineStr">
+        <is>
           <t>37.3</t>
         </is>
       </c>
-      <c r="CE17" t="inlineStr">
-        <is>
-          <t>37.5</t>
-        </is>
-      </c>
       <c r="CF17" t="inlineStr">
         <is>
-          <t>36.7</t>
+          <t>36.6</t>
         </is>
       </c>
       <c r="CG17" t="inlineStr">
         <is>
-          <t>36.95</t>
+          <t>36.75</t>
         </is>
       </c>
       <c r="CH17" t="inlineStr">
@@ -7859,12 +7859,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>-1.71</t>
+          <t>-1.34</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>1408.733</t>
+          <t>1065.248</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -7874,7 +7874,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>37.45</t>
+          <t>36.95</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -7884,17 +7884,17 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>-1.63</t>
+          <t>-0.14</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>-1.23</t>
+          <t>-1.09</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>22.93</t>
+          <t>28.28</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -7959,7 +7959,7 @@
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>-13.21</t>
+          <t>-14.37</t>
         </is>
       </c>
       <c r="X18" t="inlineStr">
@@ -7969,17 +7969,17 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>15.01</t>
+          <t>11.35</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>-2.94</t>
+          <t>-0.81</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
@@ -7990,12 +7990,12 @@
       <c r="AC18" t="inlineStr"/>
       <c r="AD18" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
-          <t>1129</t>
+          <t>6301</t>
         </is>
       </c>
       <c r="AF18" t="inlineStr">
@@ -8005,62 +8005,62 @@
       </c>
       <c r="AG18" t="inlineStr">
         <is>
-          <t>16.69</t>
+          <t>9.38</t>
         </is>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>-1.42</t>
+          <t>-1.86</t>
         </is>
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>-3.63</t>
+          <t>-4.02</t>
         </is>
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>-3.96</t>
+          <t>-4.09</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>-1.34</t>
+          <t>-1.60</t>
         </is>
       </c>
       <c r="AL18" t="inlineStr">
         <is>
-          <t>37.99</t>
+          <t>37.65000000000001</t>
         </is>
       </c>
       <c r="AM18" t="inlineStr">
         <is>
-          <t>39.42</t>
+          <t>39.23</t>
         </is>
       </c>
       <c r="AN18" t="inlineStr">
         <is>
-          <t>41.05</t>
+          <t>40.9</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>41.6</t>
+          <t>41.57</t>
         </is>
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>-15.49</t>
+          <t>-18.37</t>
         </is>
       </c>
       <c r="AQ18" t="inlineStr">
         <is>
-          <t>-0.91</t>
+          <t>-0.97</t>
         </is>
       </c>
       <c r="AR18" t="inlineStr">
         <is>
-          <t>-0.78</t>
+          <t>-0.82</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr">
@@ -8070,7 +8070,7 @@
       </c>
       <c r="AT18" t="inlineStr">
         <is>
-          <t>-129.19</t>
+          <t>-130.59</t>
         </is>
       </c>
       <c r="AU18" t="inlineStr">
@@ -8080,46 +8080,46 @@
       </c>
       <c r="AV18" t="inlineStr">
         <is>
-          <t>150408451.7952586</t>
+          <t>150693340.205165</t>
         </is>
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>53218422.0</t>
+          <t>39374759.0</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>36341855.6</t>
+          <t>40349216.0</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>29562657.9</t>
+          <t>31454761.9</t>
         </is>
       </c>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>28846965.04</t>
+          <t>29061426.18</t>
         </is>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
-          <t>6779197</t>
+          <t>8894454</t>
         </is>
       </c>
       <c r="BB18" t="inlineStr">
         <is>
-          <t>149309.3019995387</t>
+          <t>507671.8217403347</t>
         </is>
       </c>
       <c r="BC18" t="inlineStr">
         <is>
-          <t>2288252.230714723</t>
+          <t>2478665.680314712</t>
         </is>
       </c>
       <c r="BD18" t="n">
-        <v>53218422</v>
+        <v>39374759</v>
       </c>
       <c r="BE18" t="inlineStr">
         <is>
@@ -8138,7 +8138,7 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>-9.76</t>
+          <t>-10.96</t>
         </is>
       </c>
       <c r="BI18" t="inlineStr">
@@ -8183,17 +8183,17 @@
       </c>
       <c r="BQ18" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR18" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS18" t="inlineStr">
         <is>
-          <t>1.03</t>
+          <t>1.02</t>
         </is>
       </c>
       <c r="BT18" t="inlineStr">
@@ -8208,7 +8208,7 @@
       </c>
       <c r="BV18" t="inlineStr">
         <is>
-          <t>15.23</t>
+          <t>15.25</t>
         </is>
       </c>
       <c r="BW18" t="inlineStr">
@@ -8223,12 +8223,12 @@
       </c>
       <c r="BY18" t="inlineStr">
         <is>
-          <t>28.48</t>
+          <t>28.89</t>
         </is>
       </c>
       <c r="BZ18" t="inlineStr">
         <is>
-          <t>11834</t>
+          <t>11850</t>
         </is>
       </c>
       <c r="CA18" t="inlineStr">
@@ -8248,22 +8248,22 @@
       </c>
       <c r="CD18" t="inlineStr">
         <is>
-          <t>38.1</t>
+          <t>37.3</t>
         </is>
       </c>
       <c r="CE18" t="inlineStr">
         <is>
-          <t>38.7</t>
+          <t>37.5</t>
         </is>
       </c>
       <c r="CF18" t="inlineStr">
         <is>
-          <t>37.3</t>
+          <t>36.7</t>
         </is>
       </c>
       <c r="CG18" t="inlineStr">
         <is>
-          <t>37.45</t>
+          <t>36.95</t>
         </is>
       </c>
       <c r="CH18" t="inlineStr">
@@ -8295,12 +8295,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-1.71</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>504.317</t>
+          <t>1408.733</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -8310,7 +8310,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>38.1</t>
+          <t>37.45</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -8320,17 +8320,17 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>-3.39</t>
+          <t>-1.49</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>-1.23</t>
+          <t>-1.09</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>20.39</t>
+          <t>22.93</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -8395,7 +8395,7 @@
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>-11.70</t>
+          <t>-13.21</t>
         </is>
       </c>
       <c r="X19" t="inlineStr">
@@ -8405,17 +8405,17 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>5.37</t>
+          <t>15.01</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>-0.39</t>
+          <t>-2.94</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
@@ -8426,17 +8426,17 @@
       <c r="AC19" t="inlineStr"/>
       <c r="AD19" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
-          <t>1129</t>
+          <t>6301</t>
         </is>
       </c>
       <c r="AF19" t="inlineStr">
         <is>
-          <t>28.13</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG19" t="inlineStr">
@@ -8446,57 +8446,57 @@
       </c>
       <c r="AH19" t="inlineStr">
         <is>
-          <t>-0.55</t>
+          <t>-1.42</t>
         </is>
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>-3.22</t>
+          <t>-3.63</t>
         </is>
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>-3.86</t>
+          <t>-3.96</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>-1.12</t>
+          <t>-1.34</t>
         </is>
       </c>
       <c r="AL19" t="inlineStr">
         <is>
-          <t>38.31</t>
+          <t>37.99</t>
         </is>
       </c>
       <c r="AM19" t="inlineStr">
         <is>
-          <t>39.58</t>
+          <t>39.42</t>
         </is>
       </c>
       <c r="AN19" t="inlineStr">
         <is>
-          <t>41.17</t>
+          <t>41.05</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>41.64</t>
+          <t>41.6</t>
         </is>
       </c>
       <c r="AP19" t="inlineStr">
         <is>
-          <t>-13.76</t>
+          <t>-15.49</t>
         </is>
       </c>
       <c r="AQ19" t="inlineStr">
         <is>
-          <t>-0.86</t>
+          <t>-0.91</t>
         </is>
       </c>
       <c r="AR19" t="inlineStr">
         <is>
-          <t>-0.75</t>
+          <t>-0.78</t>
         </is>
       </c>
       <c r="AS19" t="inlineStr">
@@ -8506,7 +8506,7 @@
       </c>
       <c r="AT19" t="inlineStr">
         <is>
-          <t>-128.06</t>
+          <t>-129.19</t>
         </is>
       </c>
       <c r="AU19" t="inlineStr">
@@ -8516,46 +8516,46 @@
       </c>
       <c r="AV19" t="inlineStr">
         <is>
-          <t>150408451.7952586</t>
+          <t>150693340.205165</t>
         </is>
       </c>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>19248593.0</t>
+          <t>53218422.0</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>31147112.0</t>
+          <t>36341855.6</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
-          <t>25871081.1</t>
+          <t>29562657.9</t>
         </is>
       </c>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>28091032.78</t>
+          <t>28846965.04</t>
         </is>
       </c>
       <c r="BA19" t="inlineStr">
         <is>
-          <t>5276030</t>
+          <t>6779197</t>
         </is>
       </c>
       <c r="BB19" t="inlineStr">
         <is>
-          <t>-239589.4123123131</t>
+          <t>149309.3019995387</t>
         </is>
       </c>
       <c r="BC19" t="inlineStr">
         <is>
-          <t>451260.1159035005</t>
+          <t>2288252.230714723</t>
         </is>
       </c>
       <c r="BD19" t="n">
-        <v>19248593</v>
+        <v>53218422</v>
       </c>
       <c r="BE19" t="inlineStr">
         <is>
@@ -8574,7 +8574,7 @@
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>-8.19</t>
+          <t>-9.76</t>
         </is>
       </c>
       <c r="BI19" t="inlineStr">
@@ -8619,7 +8619,7 @@
       </c>
       <c r="BQ19" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR19" t="inlineStr">
@@ -8629,7 +8629,7 @@
       </c>
       <c r="BS19" t="inlineStr">
         <is>
-          <t>1.05</t>
+          <t>1.03</t>
         </is>
       </c>
       <c r="BT19" t="inlineStr">
@@ -8644,7 +8644,7 @@
       </c>
       <c r="BV19" t="inlineStr">
         <is>
-          <t>15.23</t>
+          <t>15.25</t>
         </is>
       </c>
       <c r="BW19" t="inlineStr">
@@ -8659,12 +8659,12 @@
       </c>
       <c r="BY19" t="inlineStr">
         <is>
-          <t>28.48</t>
+          <t>28.89</t>
         </is>
       </c>
       <c r="BZ19" t="inlineStr">
         <is>
-          <t>11834</t>
+          <t>11850</t>
         </is>
       </c>
       <c r="CA19" t="inlineStr">
@@ -8684,22 +8684,22 @@
       </c>
       <c r="CD19" t="inlineStr">
         <is>
-          <t>38.2</t>
+          <t>38.1</t>
         </is>
       </c>
       <c r="CE19" t="inlineStr">
         <is>
-          <t>38.4</t>
+          <t>38.7</t>
         </is>
       </c>
       <c r="CF19" t="inlineStr">
         <is>
-          <t>37.95</t>
+          <t>37.3</t>
         </is>
       </c>
       <c r="CG19" t="inlineStr">
         <is>
-          <t>38.1</t>
+          <t>37.45</t>
         </is>
       </c>
       <c r="CH19" t="inlineStr">
@@ -8731,12 +8731,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>1.18</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>605.721</t>
+          <t>504.317</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -8756,17 +8756,17 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>-3.39</t>
+          <t>-3.25</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>-1.23</t>
+          <t>-1.09</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>29.75</t>
+          <t>20.39</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -8841,17 +8841,17 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>6.45</t>
+          <t>5.37</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>0.40</t>
+          <t>-0.39</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
@@ -8862,77 +8862,77 @@
       <c r="AC20" t="inlineStr"/>
       <c r="AD20" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
-          <t>1129</t>
+          <t>6301</t>
         </is>
       </c>
       <c r="AF20" t="inlineStr">
         <is>
-          <t>21.95</t>
+          <t>28.13</t>
         </is>
       </c>
       <c r="AG20" t="inlineStr">
         <is>
-          <t>7.32</t>
+          <t>16.69</t>
         </is>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
-          <t>-0.94</t>
+          <t>-0.55</t>
         </is>
       </c>
       <c r="AI20" t="inlineStr">
         <is>
-          <t>-3.10</t>
+          <t>-3.22</t>
         </is>
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>-3.87</t>
+          <t>-3.86</t>
         </is>
       </c>
       <c r="AK20" t="inlineStr">
         <is>
-          <t>-0.91</t>
+          <t>-1.12</t>
         </is>
       </c>
       <c r="AL20" t="inlineStr">
         <is>
-          <t>38.46</t>
+          <t>38.31</t>
         </is>
       </c>
       <c r="AM20" t="inlineStr">
         <is>
-          <t>39.69</t>
+          <t>39.58</t>
         </is>
       </c>
       <c r="AN20" t="inlineStr">
         <is>
-          <t>41.29</t>
+          <t>41.17</t>
         </is>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>41.67</t>
+          <t>41.64</t>
         </is>
       </c>
       <c r="AP20" t="inlineStr">
         <is>
-          <t>-16.76</t>
+          <t>-13.76</t>
         </is>
       </c>
       <c r="AQ20" t="inlineStr">
         <is>
-          <t>-0.85</t>
+          <t>-0.86</t>
         </is>
       </c>
       <c r="AR20" t="inlineStr">
         <is>
-          <t>-0.73</t>
+          <t>-0.75</t>
         </is>
       </c>
       <c r="AS20" t="inlineStr">
@@ -8942,7 +8942,7 @@
       </c>
       <c r="AT20" t="inlineStr">
         <is>
-          <t>-127.09</t>
+          <t>-128.06</t>
         </is>
       </c>
       <c r="AU20" t="inlineStr">
@@ -8952,46 +8952,46 @@
       </c>
       <c r="AV20" t="inlineStr">
         <is>
-          <t>150408451.7952586</t>
+          <t>150693340.205165</t>
         </is>
       </c>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>23042470.0</t>
+          <t>19248593.0</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>33965584.0</t>
+          <t>31147112.0</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
-          <t>26178217.9</t>
+          <t>25871081.1</t>
         </is>
       </c>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>28206383.42</t>
+          <t>28091032.78</t>
         </is>
       </c>
       <c r="BA20" t="inlineStr">
         <is>
-          <t>7787366</t>
+          <t>5276030</t>
         </is>
       </c>
       <c r="BB20" t="inlineStr">
         <is>
-          <t>-365198.417442461</t>
+          <t>-239589.4123123131</t>
         </is>
       </c>
       <c r="BC20" t="inlineStr">
         <is>
-          <t>1450493.769176625</t>
+          <t>451260.1159035005</t>
         </is>
       </c>
       <c r="BD20" t="n">
-        <v>23042470</v>
+        <v>19248593</v>
       </c>
       <c r="BE20" t="inlineStr">
         <is>
@@ -9055,7 +9055,7 @@
       </c>
       <c r="BQ20" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;可能出現反轉訊號&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;3&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR20" t="inlineStr">
@@ -9080,7 +9080,7 @@
       </c>
       <c r="BV20" t="inlineStr">
         <is>
-          <t>15.23</t>
+          <t>15.25</t>
         </is>
       </c>
       <c r="BW20" t="inlineStr">
@@ -9095,12 +9095,12 @@
       </c>
       <c r="BY20" t="inlineStr">
         <is>
-          <t>28.48</t>
+          <t>28.89</t>
         </is>
       </c>
       <c r="BZ20" t="inlineStr">
         <is>
-          <t>11834</t>
+          <t>11850</t>
         </is>
       </c>
       <c r="CA20" t="inlineStr">
@@ -9120,17 +9120,17 @@
       </c>
       <c r="CD20" t="inlineStr">
         <is>
-          <t>38.0</t>
+          <t>38.2</t>
         </is>
       </c>
       <c r="CE20" t="inlineStr">
         <is>
-          <t>38.3</t>
+          <t>38.4</t>
         </is>
       </c>
       <c r="CF20" t="inlineStr">
         <is>
-          <t>37.75</t>
+          <t>37.95</t>
         </is>
       </c>
       <c r="CG20" t="inlineStr">
@@ -9167,12 +9167,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>-2.6</t>
+          <t>1.18</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>1764.112</t>
+          <t>605.721</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -9182,7 +9182,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>37.65</t>
+          <t>38.1</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -9192,17 +9192,17 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>-2.17</t>
+          <t>-3.25</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>-1.23</t>
+          <t>-1.09</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>21.53</t>
+          <t>29.75</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -9267,7 +9267,7 @@
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>-12.75</t>
+          <t>-11.70</t>
         </is>
       </c>
       <c r="X21" t="inlineStr">
@@ -9277,17 +9277,17 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>18.80</t>
+          <t>6.45</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>-2.12</t>
+          <t>0.40</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
@@ -9298,77 +9298,77 @@
       <c r="AC21" t="inlineStr"/>
       <c r="AD21" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
-          <t>1129</t>
+          <t>6301</t>
         </is>
       </c>
       <c r="AF21" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>21.95</t>
         </is>
       </c>
       <c r="AG21" t="inlineStr">
         <is>
-          <t>6.67</t>
+          <t>7.32</t>
         </is>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
-          <t>-2.44</t>
+          <t>-0.94</t>
         </is>
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>-3.03</t>
+          <t>-3.10</t>
         </is>
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>-3.91</t>
+          <t>-3.87</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
         <is>
-          <t>-0.66</t>
+          <t>-0.91</t>
         </is>
       </c>
       <c r="AL21" t="inlineStr">
         <is>
-          <t>38.59</t>
+          <t>38.46</t>
         </is>
       </c>
       <c r="AM21" t="inlineStr">
         <is>
-          <t>39.8</t>
+          <t>39.69</t>
         </is>
       </c>
       <c r="AN21" t="inlineStr">
         <is>
-          <t>41.42</t>
+          <t>41.29</t>
         </is>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>41.69</t>
+          <t>41.67</t>
         </is>
       </c>
       <c r="AP21" t="inlineStr">
         <is>
-          <t>-18.69</t>
+          <t>-16.76</t>
         </is>
       </c>
       <c r="AQ21" t="inlineStr">
         <is>
-          <t>-0.83</t>
+          <t>-0.85</t>
         </is>
       </c>
       <c r="AR21" t="inlineStr">
         <is>
-          <t>-0.70</t>
+          <t>-0.73</t>
         </is>
       </c>
       <c r="AS21" t="inlineStr">
@@ -9378,7 +9378,7 @@
       </c>
       <c r="AT21" t="inlineStr">
         <is>
-          <t>-125.95</t>
+          <t>-127.09</t>
         </is>
       </c>
       <c r="AU21" t="inlineStr">
@@ -9388,46 +9388,46 @@
       </c>
       <c r="AV21" t="inlineStr">
         <is>
-          <t>150408451.7952586</t>
+          <t>150693340.205165</t>
         </is>
       </c>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>66861836.0</t>
+          <t>23042470.0</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>33260992.8</t>
+          <t>33965584.0</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
-          <t>27368625.9</t>
+          <t>26178217.9</t>
         </is>
       </c>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>28716017.48</t>
+          <t>28206383.42</t>
         </is>
       </c>
       <c r="BA21" t="inlineStr">
         <is>
-          <t>5892366</t>
+          <t>7787366</t>
         </is>
       </c>
       <c r="BB21" t="inlineStr">
         <is>
-          <t>-695324.269555022</t>
+          <t>-365198.417442461</t>
         </is>
       </c>
       <c r="BC21" t="inlineStr">
         <is>
-          <t>2419680.246381927</t>
+          <t>1450493.769176625</t>
         </is>
       </c>
       <c r="BD21" t="n">
-        <v>66861836</v>
+        <v>23042470</v>
       </c>
       <c r="BE21" t="inlineStr">
         <is>
@@ -9446,7 +9446,7 @@
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>-9.28</t>
+          <t>-8.19</t>
         </is>
       </c>
       <c r="BI21" t="inlineStr">
@@ -9491,7 +9491,7 @@
       </c>
       <c r="BQ21" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;可能出現反轉訊號&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;3&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR21" t="inlineStr">
@@ -9501,7 +9501,7 @@
       </c>
       <c r="BS21" t="inlineStr">
         <is>
-          <t>1.04</t>
+          <t>1.05</t>
         </is>
       </c>
       <c r="BT21" t="inlineStr">
@@ -9516,7 +9516,7 @@
       </c>
       <c r="BV21" t="inlineStr">
         <is>
-          <t>15.23</t>
+          <t>15.25</t>
         </is>
       </c>
       <c r="BW21" t="inlineStr">
@@ -9531,12 +9531,12 @@
       </c>
       <c r="BY21" t="inlineStr">
         <is>
-          <t>28.48</t>
+          <t>28.89</t>
         </is>
       </c>
       <c r="BZ21" t="inlineStr">
         <is>
-          <t>11834</t>
+          <t>11850</t>
         </is>
       </c>
       <c r="CA21" t="inlineStr">
@@ -9556,22 +9556,22 @@
       </c>
       <c r="CD21" t="inlineStr">
         <is>
-          <t>38.45</t>
+          <t>38.0</t>
         </is>
       </c>
       <c r="CE21" t="inlineStr">
         <is>
-          <t>38.75</t>
+          <t>38.3</t>
         </is>
       </c>
       <c r="CF21" t="inlineStr">
         <is>
-          <t>37.35</t>
+          <t>37.75</t>
         </is>
       </c>
       <c r="CG21" t="inlineStr">
         <is>
-          <t>37.65</t>
+          <t>38.1</t>
         </is>
       </c>
       <c r="CH21" t="inlineStr">
@@ -9603,12 +9603,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>-1.03</t>
+          <t>-2.6</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>499.552</t>
+          <t>1764.112</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -9618,7 +9618,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>38.65</t>
+          <t>37.65</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -9628,17 +9628,17 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>-4.88</t>
+          <t>-2.03</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>-1.23</t>
+          <t>-1.09</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>0.16</t>
+          <t>21.53</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -9703,7 +9703,7 @@
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>-10.43</t>
+          <t>-12.75</t>
         </is>
       </c>
       <c r="X22" t="inlineStr">
@@ -9713,17 +9713,17 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>5.32</t>
+          <t>18.80</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>-1.42</t>
+          <t>-2.12</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
@@ -9734,12 +9734,12 @@
       <c r="AC22" t="inlineStr"/>
       <c r="AD22" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE22" t="inlineStr">
         <is>
-          <t>1129</t>
+          <t>6301</t>
         </is>
       </c>
       <c r="AF22" t="inlineStr">
@@ -9749,17 +9749,17 @@
       </c>
       <c r="AG22" t="inlineStr">
         <is>
-          <t>8.47</t>
+          <t>6.67</t>
         </is>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
-          <t>-0.57</t>
+          <t>-2.44</t>
         </is>
       </c>
       <c r="AI22" t="inlineStr">
         <is>
-          <t>-2.61</t>
+          <t>-3.03</t>
         </is>
       </c>
       <c r="AJ22" t="inlineStr">
@@ -9769,42 +9769,42 @@
       </c>
       <c r="AK22" t="inlineStr">
         <is>
-          <t>-0.43</t>
+          <t>-0.66</t>
         </is>
       </c>
       <c r="AL22" t="inlineStr">
         <is>
-          <t>38.87</t>
+          <t>38.59</t>
         </is>
       </c>
       <c r="AM22" t="inlineStr">
         <is>
-          <t>39.91</t>
+          <t>39.8</t>
         </is>
       </c>
       <c r="AN22" t="inlineStr">
         <is>
-          <t>41.54</t>
+          <t>41.42</t>
         </is>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>41.72</t>
+          <t>41.69</t>
         </is>
       </c>
       <c r="AP22" t="inlineStr">
         <is>
-          <t>-11.54</t>
+          <t>-18.69</t>
         </is>
       </c>
       <c r="AQ22" t="inlineStr">
         <is>
-          <t>-0.74</t>
+          <t>-0.83</t>
         </is>
       </c>
       <c r="AR22" t="inlineStr">
         <is>
-          <t>-0.66</t>
+          <t>-0.70</t>
         </is>
       </c>
       <c r="AS22" t="inlineStr">
@@ -9814,7 +9814,7 @@
       </c>
       <c r="AT22" t="inlineStr">
         <is>
-          <t>-124.74</t>
+          <t>-125.95</t>
         </is>
       </c>
       <c r="AU22" t="inlineStr">
@@ -9824,46 +9824,46 @@
       </c>
       <c r="AV22" t="inlineStr">
         <is>
-          <t>150408451.7952586</t>
+          <t>150693340.205165</t>
         </is>
       </c>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>19337957.0</t>
+          <t>66861836.0</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>22560307.8</t>
+          <t>33260992.8</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr">
         <is>
-          <t>22524902.5</t>
+          <t>27368625.9</t>
         </is>
       </c>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>28140249.02</t>
+          <t>28716017.48</t>
         </is>
       </c>
       <c r="BA22" t="inlineStr">
         <is>
-          <t>35405</t>
+          <t>5892366</t>
         </is>
       </c>
       <c r="BB22" t="inlineStr">
         <is>
-          <t>-1261688.726998104</t>
+          <t>-695324.269555022</t>
         </is>
       </c>
       <c r="BC22" t="inlineStr">
         <is>
-          <t>-977116.8664098568</t>
+          <t>2419680.246381927</t>
         </is>
       </c>
       <c r="BD22" t="n">
-        <v>19337957</v>
+        <v>66861836</v>
       </c>
       <c r="BE22" t="inlineStr">
         <is>
@@ -9882,7 +9882,7 @@
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>-6.87</t>
+          <t>-9.28</t>
         </is>
       </c>
       <c r="BI22" t="inlineStr">
@@ -9927,7 +9927,7 @@
       </c>
       <c r="BQ22" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR22" t="inlineStr">
@@ -9937,7 +9937,7 @@
       </c>
       <c r="BS22" t="inlineStr">
         <is>
-          <t>1.06</t>
+          <t>1.04</t>
         </is>
       </c>
       <c r="BT22" t="inlineStr">
@@ -9952,7 +9952,7 @@
       </c>
       <c r="BV22" t="inlineStr">
         <is>
-          <t>15.23</t>
+          <t>15.25</t>
         </is>
       </c>
       <c r="BW22" t="inlineStr">
@@ -9967,12 +9967,12 @@
       </c>
       <c r="BY22" t="inlineStr">
         <is>
-          <t>28.48</t>
+          <t>28.89</t>
         </is>
       </c>
       <c r="BZ22" t="inlineStr">
         <is>
-          <t>11834</t>
+          <t>11850</t>
         </is>
       </c>
       <c r="CA22" t="inlineStr">
@@ -9992,22 +9992,22 @@
       </c>
       <c r="CD22" t="inlineStr">
         <is>
-          <t>38.95</t>
+          <t>38.45</t>
         </is>
       </c>
       <c r="CE22" t="inlineStr">
         <is>
-          <t>39.3</t>
+          <t>38.75</t>
         </is>
       </c>
       <c r="CF22" t="inlineStr">
         <is>
-          <t>38.55</t>
+          <t>37.35</t>
         </is>
       </c>
       <c r="CG22" t="inlineStr">
         <is>
-          <t>38.65</t>
+          <t>37.65</t>
         </is>
       </c>
       <c r="CH22" t="inlineStr">
@@ -10039,12 +10039,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>0.51</t>
+          <t>-1.03</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>700.928</t>
+          <t>499.552</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -10054,7 +10054,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>39.05</t>
+          <t>38.65</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -10064,17 +10064,17 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>-5.97</t>
+          <t>-4.74</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>-1.23</t>
+          <t>-1.09</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>0.15</t>
+          <t>0.16</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -10139,7 +10139,7 @@
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>-9.50</t>
+          <t>-10.43</t>
         </is>
       </c>
       <c r="X23" t="inlineStr">
@@ -10149,17 +10149,17 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>7.47</t>
+          <t>5.32</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>1.17</t>
+          <t>-1.42</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
@@ -10170,17 +10170,17 @@
       <c r="AC23" t="inlineStr"/>
       <c r="AD23" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE23" t="inlineStr">
         <is>
-          <t>1129</t>
+          <t>6301</t>
         </is>
       </c>
       <c r="AF23" t="inlineStr">
         <is>
-          <t>20.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG23" t="inlineStr">
@@ -10190,57 +10190,57 @@
       </c>
       <c r="AH23" t="inlineStr">
         <is>
-          <t>0.15</t>
+          <t>-0.57</t>
         </is>
       </c>
       <c r="AI23" t="inlineStr">
         <is>
-          <t>-2.53</t>
+          <t>-2.61</t>
         </is>
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>-3.9</t>
+          <t>-3.91</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
         <is>
-          <t>-0.25</t>
+          <t>-0.43</t>
         </is>
       </c>
       <c r="AL23" t="inlineStr">
         <is>
-          <t>38.99</t>
+          <t>38.87</t>
         </is>
       </c>
       <c r="AM23" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>39.91</t>
         </is>
       </c>
       <c r="AN23" t="inlineStr">
         <is>
-          <t>41.63</t>
+          <t>41.54</t>
         </is>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>41.73</t>
+          <t>41.72</t>
         </is>
       </c>
       <c r="AP23" t="inlineStr">
         <is>
-          <t>-11.93</t>
+          <t>-11.54</t>
         </is>
       </c>
       <c r="AQ23" t="inlineStr">
         <is>
-          <t>-0.72</t>
+          <t>-0.74</t>
         </is>
       </c>
       <c r="AR23" t="inlineStr">
         <is>
-          <t>-0.65</t>
+          <t>-0.66</t>
         </is>
       </c>
       <c r="AS23" t="inlineStr">
@@ -10250,7 +10250,7 @@
       </c>
       <c r="AT23" t="inlineStr">
         <is>
-          <t>-124.03</t>
+          <t>-124.74</t>
         </is>
       </c>
       <c r="AU23" t="inlineStr">
@@ -10260,46 +10260,46 @@
       </c>
       <c r="AV23" t="inlineStr">
         <is>
-          <t>150408451.7952586</t>
+          <t>150693340.205165</t>
         </is>
       </c>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>27244704.0</t>
+          <t>19337957.0</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>22783460.2</t>
+          <t>22560307.8</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr">
         <is>
-          <t>22749645.3</t>
+          <t>22524902.5</t>
         </is>
       </c>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>28438883.58</t>
+          <t>28140249.02</t>
         </is>
       </c>
       <c r="BA23" t="inlineStr">
         <is>
-          <t>33814</t>
+          <t>35405</t>
         </is>
       </c>
       <c r="BB23" t="inlineStr">
         <is>
-          <t>-1313429.065286876</t>
+          <t>-1261688.726998104</t>
         </is>
       </c>
       <c r="BC23" t="inlineStr">
         <is>
-          <t>-702942.9608834758</t>
+          <t>-977116.8664098568</t>
         </is>
       </c>
       <c r="BD23" t="n">
-        <v>27244704</v>
+        <v>19337957</v>
       </c>
       <c r="BE23" t="inlineStr">
         <is>
@@ -10318,7 +10318,7 @@
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>-5.90</t>
+          <t>-6.87</t>
         </is>
       </c>
       <c r="BI23" t="inlineStr">
@@ -10363,7 +10363,7 @@
       </c>
       <c r="BQ23" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR23" t="inlineStr">
@@ -10373,7 +10373,7 @@
       </c>
       <c r="BS23" t="inlineStr">
         <is>
-          <t>1.07</t>
+          <t>1.06</t>
         </is>
       </c>
       <c r="BT23" t="inlineStr">
@@ -10388,7 +10388,7 @@
       </c>
       <c r="BV23" t="inlineStr">
         <is>
-          <t>15.23</t>
+          <t>15.25</t>
         </is>
       </c>
       <c r="BW23" t="inlineStr">
@@ -10403,12 +10403,12 @@
       </c>
       <c r="BY23" t="inlineStr">
         <is>
-          <t>28.48</t>
+          <t>28.89</t>
         </is>
       </c>
       <c r="BZ23" t="inlineStr">
         <is>
-          <t>11834</t>
+          <t>11850</t>
         </is>
       </c>
       <c r="CA23" t="inlineStr">
@@ -10428,22 +10428,22 @@
       </c>
       <c r="CD23" t="inlineStr">
         <is>
-          <t>38.85</t>
+          <t>38.95</t>
         </is>
       </c>
       <c r="CE23" t="inlineStr">
         <is>
-          <t>39.05</t>
+          <t>39.3</t>
         </is>
       </c>
       <c r="CF23" t="inlineStr">
         <is>
-          <t>38.6</t>
+          <t>38.55</t>
         </is>
       </c>
       <c r="CG23" t="inlineStr">
         <is>
-          <t>39.05</t>
+          <t>38.65</t>
         </is>
       </c>
       <c r="CH23" t="inlineStr">

--- a/Result/checksun_type/塔架.xlsx
+++ b/Result/checksun_type/塔架.xlsx
@@ -883,12 +883,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2.56</t>
+          <t>0.36</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>1721.237</t>
+          <t>1070.548</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>138.5</t>
+          <t>139.0</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-3.38</t>
+          <t>0.32</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>-13.08</t>
+          <t>-30.56</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-41.56</t>
+          <t>-41.35</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -993,17 +993,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>7.12</t>
+          <t>4.43</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>1.87</t>
+          <t>-0.71</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1014,77 +1014,77 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>12</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>1721</t>
+          <t>1071</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>42.11</t>
+          <t>44.74</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>29.62</t>
+          <t>36.84</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>3.44</t>
+          <t>2.51</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>-8.46</t>
+          <t>-6.71</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>-8.28</t>
+          <t>-8.49</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>-6.17</t>
+          <t>-6.19</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>133.9</t>
+          <t>135.6</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>146.28</t>
+          <t>145.35</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>159.48</t>
+          <t>158.83</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>169.96</t>
+          <t>169.32</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>-7.31</t>
+          <t>-0.61</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>-7.81</t>
+          <t>-7.33</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>-7.28</t>
+          <t>-7.29</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -1094,7 +1094,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-129.24</t>
+          <t>-129.29</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1104,46 +1104,46 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>1693196887.497848</t>
+          <t>1691092068.840258</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>236429825.0</t>
+          <t>149355643.0</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>243968869.0</t>
+          <t>199168061.0</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>280669574.0</t>
+          <t>286806442.7</t>
         </is>
       </c>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>255272113.08</t>
+          <t>252995092.08</t>
         </is>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>-36700705</t>
+          <t>-87638381</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>7451433.159492791</t>
+          <t>5491459.465344865</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>3441866.801674962</t>
+          <t>-5288395.852468729</t>
         </is>
       </c>
       <c r="BD2" t="n">
-        <v>236429825</v>
+        <v>149355643</v>
       </c>
       <c r="BE2" t="inlineStr">
         <is>
@@ -1162,7 +1162,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>-23.06</t>
+          <t>-22.78</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
@@ -1207,7 +1207,7 @@
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;可能出現反轉訊號&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;3&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
@@ -1217,12 +1217,12 @@
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>3.19</t>
+          <t>3.20</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
         <is>
-          <t>3.01</t>
+          <t>2.99</t>
         </is>
       </c>
       <c r="BU2" t="inlineStr">
@@ -1232,7 +1232,7 @@
       </c>
       <c r="BV2" t="inlineStr">
         <is>
-          <t>26.03</t>
+          <t>26.13</t>
         </is>
       </c>
       <c r="BW2" t="inlineStr">
@@ -1247,12 +1247,12 @@
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>28.89</t>
+          <t>29.15</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>34195</t>
+          <t>34319</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
@@ -1272,22 +1272,22 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>136.5</t>
+          <t>139.5</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>139.5</t>
+          <t>141.0</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>135.0</t>
+          <t>138.0</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>138.5</t>
+          <t>139.0</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
@@ -1319,12 +1319,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>2.56</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1302.953</t>
+          <t>1721.237</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1334,7 +1334,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>135.0</t>
+          <t>138.5</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1344,17 +1344,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2.53</t>
+          <t>0.36</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-3.38</t>
+          <t>0.32</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>12.02</t>
+          <t>-13.08</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1419,7 +1419,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-43.04</t>
+          <t>-41.56</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1429,17 +1429,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>5.39</t>
+          <t>7.12</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>3.05</t>
+          <t>1.87</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1450,77 +1450,77 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>12</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>1721</t>
+          <t>1071</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>23.68</t>
+          <t>42.11</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>15.59</t>
+          <t>29.62</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>1.58</t>
+          <t>3.44</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>-9.76</t>
+          <t>-8.46</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-8.05</t>
+          <t>-8.28</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>-6.11</t>
+          <t>-6.17</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>132.9</t>
+          <t>133.9</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>147.28</t>
+          <t>146.28</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>160.17</t>
+          <t>159.48</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>170.59</t>
+          <t>169.96</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>-15.53</t>
+          <t>-7.31</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>-8.25</t>
+          <t>-7.81</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>-7.14</t>
+          <t>-7.28</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1530,7 +1530,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-128.71</t>
+          <t>-129.24</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1540,46 +1540,46 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>1693196887.497848</t>
+          <t>1691092068.840258</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>173429988.0</t>
+          <t>236429825.0</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>305348589.0</t>
+          <t>243968869.0</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>272591978.0</t>
+          <t>280669574.0</t>
         </is>
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>254388028.92</t>
+          <t>255272113.08</t>
         </is>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>32756611</t>
+          <t>-36700705</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>8180445.224550578</t>
+          <t>7451433.159492791</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>6461370.136106104</t>
+          <t>3441866.801674962</t>
         </is>
       </c>
       <c r="BD3" t="n">
-        <v>173429988</v>
+        <v>236429825</v>
       </c>
       <c r="BE3" t="inlineStr">
         <is>
@@ -1598,7 +1598,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>-25.00</t>
+          <t>-23.06</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
@@ -1643,7 +1643,7 @@
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;可能出現反轉訊號&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;3&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
@@ -1653,12 +1653,12 @@
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>3.11</t>
+          <t>3.19</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
         <is>
-          <t>3.01</t>
+          <t>2.99</t>
         </is>
       </c>
       <c r="BU3" t="inlineStr">
@@ -1668,7 +1668,7 @@
       </c>
       <c r="BV3" t="inlineStr">
         <is>
-          <t>26.03</t>
+          <t>26.13</t>
         </is>
       </c>
       <c r="BW3" t="inlineStr">
@@ -1683,12 +1683,12 @@
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>28.89</t>
+          <t>29.15</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
-          <t>34195</t>
+          <t>34319</t>
         </is>
       </c>
       <c r="CA3" t="inlineStr">
@@ -1708,22 +1708,22 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>132.5</t>
+          <t>136.5</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
+          <t>139.5</t>
+        </is>
+      </c>
+      <c r="CF3" t="inlineStr">
+        <is>
           <t>135.0</t>
         </is>
       </c>
-      <c r="CF3" t="inlineStr">
-        <is>
-          <t>131.0</t>
-        </is>
-      </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>135.0</t>
+          <t>138.5</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
@@ -1755,12 +1755,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>3.41</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>1595.31</t>
+          <t>1302.953</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1780,17 +1780,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2.53</t>
+          <t>2.88</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-3.38</t>
+          <t>0.32</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>53.45</t>
+          <t>12.02</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1865,17 +1865,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>6.60</t>
+          <t>5.39</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>1.92</t>
+          <t>3.05</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1886,77 +1886,77 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>12</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>1721</t>
+          <t>1071</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>23.08</t>
+          <t>23.68</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>7.69</t>
+          <t>15.59</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>1.20</t>
+          <t>1.58</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>-10.06</t>
+          <t>-9.76</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>-7.84</t>
+          <t>-8.05</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>-6.04</t>
+          <t>-6.11</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>133.4</t>
+          <t>132.9</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>148.32</t>
+          <t>147.28</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>160.95</t>
+          <t>160.17</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>171.29</t>
+          <t>170.59</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>-21.52</t>
+          <t>-15.53</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>-8.35</t>
+          <t>-8.25</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>-6.87</t>
+          <t>-7.14</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1966,7 +1966,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-127.59</t>
+          <t>-128.71</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1976,46 +1976,46 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>1693196887.497848</t>
+          <t>1691092068.840258</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>212878160.0</t>
+          <t>173429988.0</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>421450515.0</t>
+          <t>305348589.0</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>274650710.4</t>
+          <t>272591978.0</t>
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>254522728.7</t>
+          <t>254388028.92</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>146799804</t>
+          <t>32756611</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>8493004.331540482</t>
+          <t>8180445.224550578</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>17294165.64471823</t>
+          <t>6461370.136106104</t>
         </is>
       </c>
       <c r="BD4" t="n">
-        <v>212878160</v>
+        <v>173429988</v>
       </c>
       <c r="BE4" t="inlineStr">
         <is>
@@ -2079,12 +2079,12 @@
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;可能出現反轉訊號&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;3&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS4" t="inlineStr">
@@ -2094,7 +2094,7 @@
       </c>
       <c r="BT4" t="inlineStr">
         <is>
-          <t>3.01</t>
+          <t>2.99</t>
         </is>
       </c>
       <c r="BU4" t="inlineStr">
@@ -2104,7 +2104,7 @@
       </c>
       <c r="BV4" t="inlineStr">
         <is>
-          <t>26.03</t>
+          <t>26.13</t>
         </is>
       </c>
       <c r="BW4" t="inlineStr">
@@ -2119,12 +2119,12 @@
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>28.89</t>
+          <t>29.15</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
-          <t>34195</t>
+          <t>34319</t>
         </is>
       </c>
       <c r="CA4" t="inlineStr">
@@ -2144,17 +2144,17 @@
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>132.0</t>
+          <t>132.5</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>136.0</t>
+          <t>135.0</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>131.5</t>
+          <t>131.0</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>3.41</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>1712.06</t>
+          <t>1595.31</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2206,7 +2206,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>130.5</t>
+          <t>135.0</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2216,17 +2216,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>5.78</t>
+          <t>2.88</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-3.38</t>
+          <t>0.32</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>50.94</t>
+          <t>53.45</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2291,7 +2291,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-44.94</t>
+          <t>-43.04</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2301,17 +2301,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>7.08</t>
+          <t>6.60</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>-1.14</t>
+          <t>1.92</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2322,77 +2322,77 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>12</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>1721</t>
+          <t>1071</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>23.08</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>7.69</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>-4.26</t>
+          <t>1.20</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>-8.89</t>
+          <t>-10.06</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>-7.5</t>
+          <t>-7.84</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>-5.97</t>
+          <t>-6.04</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>136.3</t>
+          <t>133.4</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>149.6</t>
+          <t>148.32</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>161.73</t>
+          <t>160.95</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>171.99</t>
+          <t>171.29</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>-28.35</t>
+          <t>-21.52</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>-8.34</t>
+          <t>-8.35</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>-6.50</t>
+          <t>-6.87</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -2402,7 +2402,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-126.11</t>
+          <t>-127.59</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2412,46 +2412,46 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>1693196887.497848</t>
+          <t>1691092068.840258</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>223746689.0</t>
+          <t>212878160.0</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>397436778.6</t>
+          <t>421450515.0</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>263301806.5</t>
+          <t>274650710.4</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>254911229.58</t>
+          <t>254522728.7</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>134134972</t>
+          <t>146799804</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>6892793.183689982</t>
+          <t>8493004.331540482</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>27925349.16970986</t>
+          <t>17294165.64471823</t>
         </is>
       </c>
       <c r="BD5" t="n">
-        <v>223746689</v>
+        <v>212878160</v>
       </c>
       <c r="BE5" t="inlineStr">
         <is>
@@ -2470,7 +2470,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>-27.50</t>
+          <t>-25.00</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
@@ -2515,22 +2515,22 @@
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;可能出現反轉訊號&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;3&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
         <is>
-          <t>價漲量縮</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>3.01</t>
+          <t>3.11</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
         <is>
-          <t>3.01</t>
+          <t>2.99</t>
         </is>
       </c>
       <c r="BU5" t="inlineStr">
@@ -2540,7 +2540,7 @@
       </c>
       <c r="BV5" t="inlineStr">
         <is>
-          <t>26.03</t>
+          <t>26.13</t>
         </is>
       </c>
       <c r="BW5" t="inlineStr">
@@ -2555,12 +2555,12 @@
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>28.89</t>
+          <t>29.15</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
-          <t>34195</t>
+          <t>34319</t>
         </is>
       </c>
       <c r="CA5" t="inlineStr">
@@ -2580,22 +2580,22 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>131.0</t>
+          <t>132.0</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>133.5</t>
+          <t>136.0</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>129.0</t>
+          <t>131.5</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>130.5</t>
+          <t>135.0</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
@@ -2627,12 +2627,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>-2.26</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2844.986</t>
+          <t>1712.06</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2652,17 +2652,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>5.78</t>
+          <t>6.12</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-3.38</t>
+          <t>0.32</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>48.25</t>
+          <t>50.94</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2737,17 +2737,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>11.77</t>
+          <t>7.08</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>-2.29</t>
+          <t>-1.14</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2758,12 +2758,12 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>12</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>1721</t>
+          <t>1071</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
@@ -2778,57 +2778,57 @@
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>-6.85</t>
+          <t>-4.26</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>-7.30</t>
+          <t>-8.89</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>-7.05</t>
+          <t>-7.5</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>-5.89</t>
+          <t>-5.97</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>140.1</t>
+          <t>136.3</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>151.12</t>
+          <t>149.6</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>162.59</t>
+          <t>161.73</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>172.77</t>
+          <t>171.99</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>-28.43</t>
+          <t>-28.35</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>-7.75</t>
+          <t>-8.34</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>-6.04</t>
+          <t>-6.50</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -2838,7 +2838,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-124.26</t>
+          <t>-126.11</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2848,46 +2848,46 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>1693196887.497848</t>
+          <t>1691092068.840258</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>373359683.0</t>
+          <t>223746689.0</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>374444824.4</t>
+          <t>397436778.6</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>252575891.8</t>
+          <t>263301806.5</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>255257682.72</t>
+          <t>254911229.58</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>121868932</t>
+          <t>134134972</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>3068692.09532273</t>
+          <t>6892793.183689982</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>40950935.056494</t>
+          <t>27925349.16970986</t>
         </is>
       </c>
       <c r="BD6" t="n">
-        <v>373359683</v>
+        <v>223746689</v>
       </c>
       <c r="BE6" t="inlineStr">
         <is>
@@ -2951,12 +2951,12 @@
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價漲量縮</t>
         </is>
       </c>
       <c r="BS6" t="inlineStr">
@@ -2966,7 +2966,7 @@
       </c>
       <c r="BT6" t="inlineStr">
         <is>
-          <t>3.01</t>
+          <t>2.99</t>
         </is>
       </c>
       <c r="BU6" t="inlineStr">
@@ -2976,7 +2976,7 @@
       </c>
       <c r="BV6" t="inlineStr">
         <is>
-          <t>26.03</t>
+          <t>26.13</t>
         </is>
       </c>
       <c r="BW6" t="inlineStr">
@@ -2991,12 +2991,12 @@
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>28.89</t>
+          <t>29.15</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
         <is>
-          <t>34195</t>
+          <t>34319</t>
         </is>
       </c>
       <c r="CA6" t="inlineStr">
@@ -3016,17 +3016,17 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>133.0</t>
+          <t>131.0</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>134.5</t>
+          <t>133.5</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>129.5</t>
+          <t>129.0</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
@@ -3063,12 +3063,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>-2.96</t>
+          <t>-2.26</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>4003.393</t>
+          <t>2844.986</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3078,7 +3078,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>133.5</t>
+          <t>130.5</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3088,17 +3088,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>3.61</t>
+          <t>6.12</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-3.38</t>
+          <t>0.32</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>36.89</t>
+          <t>48.25</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3163,7 +3163,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-43.67</t>
+          <t>-44.94</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3173,17 +3173,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>16.56</t>
+          <t>11.77</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>-5.24</t>
+          <t>-2.29</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3194,12 +3194,12 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>12</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>1721</t>
+          <t>1071</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
@@ -3214,57 +3214,57 @@
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>-7.23</t>
+          <t>-6.85</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>-5.73</t>
+          <t>-7.30</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>-6.6</t>
+          <t>-7.05</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>-5.82</t>
+          <t>-5.89</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>143.9</t>
+          <t>140.1</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>152.65</t>
+          <t>151.12</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>163.44</t>
+          <t>162.59</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>173.54</t>
+          <t>172.77</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>-22.90</t>
+          <t>-28.43</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>-6.89</t>
+          <t>-7.75</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>-5.61</t>
+          <t>-6.04</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -3274,7 +3274,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-122.53</t>
+          <t>-124.26</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3284,46 +3284,46 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>1693196887.497848</t>
+          <t>1691092068.840258</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>543328425.0</t>
+          <t>373359683.0</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>317370279.0</t>
+          <t>374444824.4</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>231842549.9</t>
+          <t>252575891.8</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>254515985.98</t>
+          <t>255257682.72</t>
         </is>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>85527729</t>
+          <t>121868932</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>-3818988.443072045</t>
+          <t>3068692.09532273</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>42066417.85702515</t>
+          <t>40950935.056494</t>
         </is>
       </c>
       <c r="BD7" t="n">
-        <v>543328425</v>
+        <v>373359683</v>
       </c>
       <c r="BE7" t="inlineStr">
         <is>
@@ -3342,7 +3342,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>-25.83</t>
+          <t>-27.50</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
@@ -3387,7 +3387,7 @@
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;衝高回落,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
@@ -3397,12 +3397,12 @@
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>3.08</t>
+          <t>3.01</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
         <is>
-          <t>3.01</t>
+          <t>2.99</t>
         </is>
       </c>
       <c r="BU7" t="inlineStr">
@@ -3412,7 +3412,7 @@
       </c>
       <c r="BV7" t="inlineStr">
         <is>
-          <t>26.03</t>
+          <t>26.13</t>
         </is>
       </c>
       <c r="BW7" t="inlineStr">
@@ -3427,12 +3427,12 @@
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>28.89</t>
+          <t>29.15</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
         <is>
-          <t>34195</t>
+          <t>34319</t>
         </is>
       </c>
       <c r="CA7" t="inlineStr">
@@ -3452,22 +3452,22 @@
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>135.0</t>
+          <t>133.0</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>141.5</t>
+          <t>134.5</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>132.5</t>
+          <t>129.5</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>133.5</t>
+          <t>130.5</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
@@ -3499,12 +3499,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>-8.16</t>
+          <t>-2.96</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>5388.546</t>
+          <t>4003.393</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3514,7 +3514,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>137.5</t>
+          <t>133.5</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3524,17 +3524,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>0.72</t>
+          <t>3.96</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-3.38</t>
+          <t>0.32</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>18.56</t>
+          <t>36.89</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3599,7 +3599,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-41.98</t>
+          <t>-43.67</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3609,17 +3609,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>22.28</t>
+          <t>16.56</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>-5.06</t>
+          <t>-5.24</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3630,12 +3630,12 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>12</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>1721</t>
+          <t>1071</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
@@ -3650,57 +3650,57 @@
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>-6.59</t>
+          <t>-7.23</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>-4.57</t>
+          <t>-5.73</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>-6.11</t>
+          <t>-6.6</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>-5.70</t>
+          <t>-5.82</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>147.2</t>
+          <t>143.9</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>154.25</t>
+          <t>152.65</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>164.29</t>
+          <t>163.44</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>174.21</t>
+          <t>173.54</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>-13.45</t>
+          <t>-22.90</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>-6.00</t>
+          <t>-6.89</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>-5.29</t>
+          <t>-5.61</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -3710,7 +3710,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-121.24</t>
+          <t>-122.53</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3720,46 +3720,46 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>1693196887.497848</t>
+          <t>1691092068.840258</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>753939618.0</t>
+          <t>543328425.0</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>239835367.0</t>
+          <t>317370279.0</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>202283159.5</t>
+          <t>231842549.9</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>250790390.86</t>
+          <t>254515985.98</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>37552207</t>
+          <t>85527729</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>-12161789.58854426</t>
+          <t>-3818988.443072045</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>23946656.00574735</t>
+          <t>42066417.85702515</t>
         </is>
       </c>
       <c r="BD8" t="n">
-        <v>753939618</v>
+        <v>543328425</v>
       </c>
       <c r="BE8" t="inlineStr">
         <is>
@@ -3778,7 +3778,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>-23.61</t>
+          <t>-25.83</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
@@ -3823,22 +3823,22 @@
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;衝高回落,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
         <is>
-          <t>價跌量增</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>3.17</t>
+          <t>3.08</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
         <is>
-          <t>3.01</t>
+          <t>2.99</t>
         </is>
       </c>
       <c r="BU8" t="inlineStr">
@@ -3848,7 +3848,7 @@
       </c>
       <c r="BV8" t="inlineStr">
         <is>
-          <t>26.03</t>
+          <t>26.13</t>
         </is>
       </c>
       <c r="BW8" t="inlineStr">
@@ -3863,12 +3863,12 @@
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>28.89</t>
+          <t>29.15</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
         <is>
-          <t>34195</t>
+          <t>34319</t>
         </is>
       </c>
       <c r="CA8" t="inlineStr">
@@ -3888,22 +3888,22 @@
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>147.0</t>
+          <t>135.0</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>147.0</t>
+          <t>141.5</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>135.0</t>
+          <t>132.5</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>137.5</t>
+          <t>133.5</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
@@ -3935,12 +3935,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-8.16</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>617.888</t>
+          <t>5388.546</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3950,7 +3950,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>149.5</t>
+          <t>137.5</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3960,17 +3960,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-7.94</t>
+          <t>1.08</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-3.38</t>
+          <t>0.32</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>-14.19</t>
+          <t>18.56</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -4035,7 +4035,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-36.92</t>
+          <t>-41.98</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4045,17 +4045,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>2.56</t>
+          <t>22.28</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>-1.34</t>
+          <t>-5.06</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4066,12 +4066,12 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>12</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>1721</t>
+          <t>1071</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
@@ -4086,57 +4086,57 @@
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>-0.07</t>
+          <t>-6.59</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>-3.96</t>
+          <t>-4.57</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>-5.65</t>
+          <t>-6.11</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>-5.63</t>
+          <t>-5.70</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>149.6</t>
+          <t>147.2</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>155.78</t>
+          <t>154.25</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>165.1</t>
+          <t>164.29</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>174.95</t>
+          <t>174.21</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>-1.33</t>
+          <t>-13.45</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>-5.18</t>
+          <t>-6.00</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>-5.11</t>
+          <t>-5.29</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -4146,7 +4146,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-120.53</t>
+          <t>-121.24</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4156,46 +4156,46 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>1693196887.497848</t>
+          <t>1691092068.840258</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>92809478.0</t>
+          <t>753939618.0</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>127850905.8</t>
+          <t>239835367.0</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>148995940.1</t>
+          <t>202283159.5</t>
         </is>
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>248204610.78</t>
+          <t>250790390.86</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>-21145034</t>
+          <t>37552207</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>-18726961.5147791</t>
+          <t>-12161789.58854426</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>-25359440.74628332</t>
+          <t>23946656.00574735</t>
         </is>
       </c>
       <c r="BD9" t="n">
-        <v>92809478</v>
+        <v>753939618</v>
       </c>
       <c r="BE9" t="inlineStr">
         <is>
@@ -4214,7 +4214,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>-16.94</t>
+          <t>-23.61</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
@@ -4264,17 +4264,17 @@
       </c>
       <c r="BR9" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價跌量增</t>
         </is>
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>3.44</t>
+          <t>3.17</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
         <is>
-          <t>3.01</t>
+          <t>2.99</t>
         </is>
       </c>
       <c r="BU9" t="inlineStr">
@@ -4284,7 +4284,7 @@
       </c>
       <c r="BV9" t="inlineStr">
         <is>
-          <t>26.03</t>
+          <t>26.13</t>
         </is>
       </c>
       <c r="BW9" t="inlineStr">
@@ -4299,12 +4299,12 @@
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>28.89</t>
+          <t>29.15</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
         <is>
-          <t>34195</t>
+          <t>34319</t>
         </is>
       </c>
       <c r="CA9" t="inlineStr">
@@ -4324,22 +4324,22 @@
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>150.0</t>
+          <t>147.0</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>151.5</t>
+          <t>147.0</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>149.5</t>
+          <t>135.0</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>149.5</t>
+          <t>137.5</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
@@ -4376,7 +4376,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>723.545</t>
+          <t>617.888</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4396,17 +4396,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-7.94</t>
+          <t>-7.55</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-3.38</t>
+          <t>0.32</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>-23.11</t>
+          <t>-14.19</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4481,17 +4481,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>2.99</t>
+          <t>2.56</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>-1.67</t>
+          <t>-1.34</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4502,12 +4502,12 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>12</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>1721</t>
+          <t>1071</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
@@ -4517,62 +4517,62 @@
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>2.22</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>-0.47</t>
+          <t>-0.07</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>-4.07</t>
+          <t>-3.96</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>-5.55</t>
+          <t>-5.65</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>-5.58</t>
+          <t>-5.63</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>150.2</t>
+          <t>149.6</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>156.57</t>
+          <t>155.78</t>
         </is>
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>165.78</t>
+          <t>165.1</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>175.58</t>
+          <t>174.95</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>-3.60</t>
+          <t>-1.33</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>-5.28</t>
+          <t>-5.18</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>-5.09</t>
+          <t>-5.11</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -4582,7 +4582,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-120.46</t>
+          <t>-120.53</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4592,46 +4592,46 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>1693196887.497848</t>
+          <t>1691092068.840258</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>108786918.0</t>
+          <t>92809478.0</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>129166834.4</t>
+          <t>127850905.8</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>167987433.4</t>
+          <t>148995940.1</t>
         </is>
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>261232164.76</t>
+          <t>248204610.78</t>
         </is>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>-38820599</t>
+          <t>-21145034</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>-17521056.19996015</t>
+          <t>-18726961.5147791</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>-24055655.36538848</t>
+          <t>-25359440.74628332</t>
         </is>
       </c>
       <c r="BD10" t="n">
-        <v>108786918</v>
+        <v>92809478</v>
       </c>
       <c r="BE10" t="inlineStr">
         <is>
@@ -4695,7 +4695,7 @@
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
@@ -4710,7 +4710,7 @@
       </c>
       <c r="BT10" t="inlineStr">
         <is>
-          <t>3.01</t>
+          <t>2.99</t>
         </is>
       </c>
       <c r="BU10" t="inlineStr">
@@ -4720,7 +4720,7 @@
       </c>
       <c r="BV10" t="inlineStr">
         <is>
-          <t>26.03</t>
+          <t>26.13</t>
         </is>
       </c>
       <c r="BW10" t="inlineStr">
@@ -4735,12 +4735,12 @@
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>28.89</t>
+          <t>29.15</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
         <is>
-          <t>34195</t>
+          <t>34319</t>
         </is>
       </c>
       <c r="CA10" t="inlineStr">
@@ -4760,17 +4760,17 @@
       </c>
       <c r="CD10" t="inlineStr">
         <is>
+          <t>150.0</t>
+        </is>
+      </c>
+      <c r="CE10" t="inlineStr">
+        <is>
           <t>151.5</t>
         </is>
       </c>
-      <c r="CE10" t="inlineStr">
-        <is>
-          <t>152.5</t>
-        </is>
-      </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>149.0</t>
+          <t>149.5</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
@@ -4807,12 +4807,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>-0.33</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>586.018</t>
+          <t>723.545</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4832,17 +4832,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-7.94</t>
+          <t>-7.55</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-3.38</t>
+          <t>0.32</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>-28.30</t>
+          <t>-23.11</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4917,17 +4917,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>2.42</t>
+          <t>2.99</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>-1.34</t>
+          <t>-1.67</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4938,12 +4938,12 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>12</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>1721</t>
+          <t>1071</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
@@ -4958,57 +4958,57 @@
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>-0.86</t>
+          <t>-0.47</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>-4.25</t>
+          <t>-4.07</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>-5.43</t>
+          <t>-5.55</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>-5.49</t>
+          <t>-5.58</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>150.8</t>
+          <t>150.2</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>157.5</t>
+          <t>156.57</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>166.55</t>
+          <t>165.78</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>176.23</t>
+          <t>175.58</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>-5.51</t>
+          <t>-3.60</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>-5.32</t>
+          <t>-5.28</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>-5.05</t>
+          <t>-5.09</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -5018,7 +5018,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-120.28</t>
+          <t>-120.46</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -5028,46 +5028,46 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>1693196887.497848</t>
+          <t>1691092068.840258</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>87986956.0</t>
+          <t>108786918.0</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>130706959.2</t>
+          <t>129166834.4</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>182292868.5</t>
+          <t>167987433.4</t>
         </is>
       </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>265109106.98</t>
+          <t>261232164.76</t>
         </is>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>-51585909</t>
+          <t>-38820599</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>-16332947.26079137</t>
+          <t>-17521056.19996015</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>-23045842.8439177</t>
+          <t>-24055655.36538848</t>
         </is>
       </c>
       <c r="BD11" t="n">
-        <v>87986956</v>
+        <v>108786918</v>
       </c>
       <c r="BE11" t="inlineStr">
         <is>
@@ -5131,7 +5131,7 @@
       </c>
       <c r="BQ11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR11" t="inlineStr">
@@ -5146,7 +5146,7 @@
       </c>
       <c r="BT11" t="inlineStr">
         <is>
-          <t>3.01</t>
+          <t>2.99</t>
         </is>
       </c>
       <c r="BU11" t="inlineStr">
@@ -5156,7 +5156,7 @@
       </c>
       <c r="BV11" t="inlineStr">
         <is>
-          <t>26.03</t>
+          <t>26.13</t>
         </is>
       </c>
       <c r="BW11" t="inlineStr">
@@ -5171,12 +5171,12 @@
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>28.89</t>
+          <t>29.15</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
         <is>
-          <t>34195</t>
+          <t>34319</t>
         </is>
       </c>
       <c r="CA11" t="inlineStr">
@@ -5201,12 +5201,12 @@
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>151.5</t>
+          <t>152.5</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>149.5</t>
+          <t>149.0</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
@@ -5243,12 +5243,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>0.33</t>
+          <t>-0.33</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>1040.36</t>
+          <t>586.018</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5258,7 +5258,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>150.0</t>
+          <t>149.5</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5268,17 +5268,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-8.3</t>
+          <t>-7.55</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-3.38</t>
+          <t>0.32</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>-24.53</t>
+          <t>-28.30</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5343,7 +5343,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-36.71</t>
+          <t>-36.92</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5353,17 +5353,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>4.30</t>
+          <t>2.42</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>1.39</t>
+          <t>-1.34</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5374,17 +5374,17 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>12</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>1721</t>
+          <t>1071</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>6.67</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
@@ -5394,57 +5394,57 @@
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>-1.12</t>
+          <t>-0.86</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>-4.31</t>
+          <t>-4.25</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>-5.31</t>
+          <t>-5.43</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>-5.34</t>
+          <t>-5.49</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>151.7</t>
+          <t>150.8</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>158.52</t>
+          <t>157.5</t>
         </is>
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>167.41</t>
+          <t>166.55</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>176.86</t>
+          <t>176.23</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>-6.68</t>
+          <t>-5.51</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>-5.31</t>
+          <t>-5.32</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>-4.98</t>
+          <t>-5.05</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
@@ -5454,7 +5454,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-120.00</t>
+          <t>-120.28</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5464,46 +5464,46 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>1693196887.497848</t>
+          <t>1691092068.840258</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>155653865.0</t>
+          <t>87986956.0</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>146314820.8</t>
+          <t>130706959.2</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>193869307.6</t>
+          <t>182292868.5</t>
         </is>
       </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>274342437.92</t>
+          <t>265109106.98</t>
         </is>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>-47554486</t>
+          <t>-51585909</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>-15112420.79113203</t>
+          <t>-16332947.26079137</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>-18551620.35453376</t>
+          <t>-23045842.8439177</t>
         </is>
       </c>
       <c r="BD12" t="n">
-        <v>155653865</v>
+        <v>87986956</v>
       </c>
       <c r="BE12" t="inlineStr">
         <is>
@@ -5522,7 +5522,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>-16.67</t>
+          <t>-16.94</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
@@ -5567,7 +5567,7 @@
       </c>
       <c r="BQ12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;可能出現反轉訊號&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;3&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR12" t="inlineStr">
@@ -5577,12 +5577,12 @@
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>3.46</t>
+          <t>3.44</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
         <is>
-          <t>3.01</t>
+          <t>2.99</t>
         </is>
       </c>
       <c r="BU12" t="inlineStr">
@@ -5592,7 +5592,7 @@
       </c>
       <c r="BV12" t="inlineStr">
         <is>
-          <t>26.03</t>
+          <t>26.13</t>
         </is>
       </c>
       <c r="BW12" t="inlineStr">
@@ -5607,12 +5607,12 @@
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>28.89</t>
+          <t>29.15</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
         <is>
-          <t>34195</t>
+          <t>34319</t>
         </is>
       </c>
       <c r="CA12" t="inlineStr">
@@ -5632,7 +5632,7 @@
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>150.5</t>
+          <t>151.5</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
@@ -5642,12 +5642,12 @@
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>146.5</t>
+          <t>149.5</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
         <is>
-          <t>150.0</t>
+          <t>149.5</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">
@@ -5679,12 +5679,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>0.14</t>
+          <t>3.24</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>6301.223</t>
+          <t>1043.085</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -5694,7 +5694,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>36.9</t>
+          <t>38.1</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -5709,12 +5709,12 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>-1.09</t>
+          <t>0.63</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>29.52</t>
+          <t>41.43</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -5724,7 +5724,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>-95.0</t>
+          <t>-90.0</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -5779,7 +5779,7 @@
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>-14.48</t>
+          <t>-11.70</t>
         </is>
       </c>
       <c r="X13" t="inlineStr">
@@ -5789,17 +5789,17 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>67.14</t>
+          <t>11.11</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>-1.63</t>
+          <t>2.71</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
@@ -5810,77 +5810,77 @@
       <c r="AC13" t="inlineStr"/>
       <c r="AD13" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
-          <t>6301</t>
+          <t>1043</t>
         </is>
       </c>
       <c r="AF13" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG13" t="inlineStr">
         <is>
-          <t>29.75</t>
+          <t>59.17</t>
         </is>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>0.82</t>
+          <t>3.34</t>
         </is>
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>-4.24</t>
+          <t>-3.27</t>
         </is>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>-4.85</t>
+          <t>-4.89</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>-2.68</t>
+          <t>-2.80</t>
         </is>
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>36.60000000000001</t>
+          <t>36.87</t>
         </is>
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>38.22</t>
+          <t>38.11</t>
         </is>
       </c>
       <c r="AN13" t="inlineStr">
         <is>
-          <t>40.17</t>
+          <t>40.07</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>41.28</t>
+          <t>41.23</t>
         </is>
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>-7.24</t>
+          <t>5.10</t>
         </is>
       </c>
       <c r="AQ13" t="inlineStr">
         <is>
-          <t>-1.08</t>
+          <t>-0.95</t>
         </is>
       </c>
       <c r="AR13" t="inlineStr">
         <is>
-          <t>-1.01</t>
+          <t>-1.00</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr">
@@ -5890,56 +5890,56 @@
       </c>
       <c r="AT13" t="inlineStr">
         <is>
-          <t>-137.62</t>
+          <t>-137.15</t>
         </is>
       </c>
       <c r="AU13" t="inlineStr">
         <is>
-          <t>2025/10/23</t>
+          <t>2025/11/25</t>
         </is>
       </c>
       <c r="AV13" t="inlineStr">
         <is>
-          <t>150693340.205165</t>
+          <t>150562465.4441261</t>
         </is>
       </c>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>232650449.0</t>
+          <t>39561838.0</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>74142370.0</t>
+          <t>77102277.8</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>57245793.0</t>
+          <t>54515793.2</t>
         </is>
       </c>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>34130931.06</t>
+          <t>33864219.92</t>
         </is>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
-          <t>16896577</t>
+          <t>22586484</t>
         </is>
       </c>
       <c r="BB13" t="inlineStr">
         <is>
-          <t>3442386.786094812</t>
+          <t>4717477.979434728</t>
         </is>
       </c>
       <c r="BC13" t="inlineStr">
         <is>
-          <t>16400757.27416717</t>
+          <t>11730479.54280426</t>
         </is>
       </c>
       <c r="BD13" t="n">
-        <v>232650449</v>
+        <v>39561838</v>
       </c>
       <c r="BE13" t="inlineStr">
         <is>
@@ -5958,7 +5958,7 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>-11.08</t>
+          <t>-8.19</t>
         </is>
       </c>
       <c r="BI13" t="inlineStr">
@@ -6003,7 +6003,7 @@
       </c>
       <c r="BQ13" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR13" t="inlineStr">
@@ -6013,12 +6013,12 @@
       </c>
       <c r="BS13" t="inlineStr">
         <is>
-          <t>1.02</t>
+          <t>1.05</t>
         </is>
       </c>
       <c r="BT13" t="inlineStr">
         <is>
-          <t>6.78</t>
+          <t>6.56</t>
         </is>
       </c>
       <c r="BU13" t="inlineStr">
@@ -6028,7 +6028,7 @@
       </c>
       <c r="BV13" t="inlineStr">
         <is>
-          <t>15.25</t>
+          <t>15.74</t>
         </is>
       </c>
       <c r="BW13" t="inlineStr">
@@ -6043,12 +6043,12 @@
       </c>
       <c r="BY13" t="inlineStr">
         <is>
-          <t>28.89</t>
+          <t>29.15</t>
         </is>
       </c>
       <c r="BZ13" t="inlineStr">
         <is>
-          <t>11850</t>
+          <t>12236</t>
         </is>
       </c>
       <c r="CA13" t="inlineStr">
@@ -6068,22 +6068,22 @@
       </c>
       <c r="CD13" t="inlineStr">
         <is>
+          <t>37.05</t>
+        </is>
+      </c>
+      <c r="CE13" t="inlineStr">
+        <is>
+          <t>38.2</t>
+        </is>
+      </c>
+      <c r="CF13" t="inlineStr">
+        <is>
           <t>37.0</t>
         </is>
       </c>
-      <c r="CE13" t="inlineStr">
-        <is>
-          <t>37.5</t>
-        </is>
-      </c>
-      <c r="CF13" t="inlineStr">
-        <is>
-          <t>36.9</t>
-        </is>
-      </c>
       <c r="CG13" t="inlineStr">
         <is>
-          <t>36.9</t>
+          <t>38.1</t>
         </is>
       </c>
       <c r="CH13" t="inlineStr">
@@ -6115,12 +6115,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>1.24</t>
+          <t>0.14</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>1128.761</t>
+          <t>6301.223</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -6130,7 +6130,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>36.85</t>
+          <t>36.9</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -6140,17 +6140,17 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>0.14</t>
+          <t>3.15</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>-1.09</t>
+          <t>0.63</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>-1.19</t>
+          <t>29.52</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -6160,7 +6160,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>-95.0</t>
+          <t>-90.0</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -6215,7 +6215,7 @@
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>-14.60</t>
+          <t>-14.48</t>
         </is>
       </c>
       <c r="X14" t="inlineStr">
@@ -6225,17 +6225,17 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>12.03</t>
+          <t>67.14</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2.09</t>
+          <t>-1.63</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
@@ -6246,280 +6246,280 @@
       <c r="AC14" t="inlineStr"/>
       <c r="AD14" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
-          <t>6301</t>
+          <t>1043</t>
         </is>
       </c>
       <c r="AF14" t="inlineStr">
         <is>
+          <t>40.0</t>
+        </is>
+      </c>
+      <c r="AG14" t="inlineStr">
+        <is>
+          <t>29.75</t>
+        </is>
+      </c>
+      <c r="AH14" t="inlineStr">
+        <is>
+          <t>0.82</t>
+        </is>
+      </c>
+      <c r="AI14" t="inlineStr">
+        <is>
+          <t>-4.24</t>
+        </is>
+      </c>
+      <c r="AJ14" t="inlineStr">
+        <is>
+          <t>-4.85</t>
+        </is>
+      </c>
+      <c r="AK14" t="inlineStr">
+        <is>
+          <t>-2.68</t>
+        </is>
+      </c>
+      <c r="AL14" t="inlineStr">
+        <is>
+          <t>36.60000000000001</t>
+        </is>
+      </c>
+      <c r="AM14" t="inlineStr">
+        <is>
+          <t>38.22</t>
+        </is>
+      </c>
+      <c r="AN14" t="inlineStr">
+        <is>
+          <t>40.17</t>
+        </is>
+      </c>
+      <c r="AO14" t="inlineStr">
+        <is>
+          <t>41.28</t>
+        </is>
+      </c>
+      <c r="AP14" t="inlineStr">
+        <is>
+          <t>-7.24</t>
+        </is>
+      </c>
+      <c r="AQ14" t="inlineStr">
+        <is>
+          <t>-1.08</t>
+        </is>
+      </c>
+      <c r="AR14" t="inlineStr">
+        <is>
+          <t>-1.01</t>
+        </is>
+      </c>
+      <c r="AS14" t="inlineStr">
+        <is>
+          <t>2.69</t>
+        </is>
+      </c>
+      <c r="AT14" t="inlineStr">
+        <is>
+          <t>-137.62</t>
+        </is>
+      </c>
+      <c r="AU14" t="inlineStr">
+        <is>
+          <t>2025/11/25</t>
+        </is>
+      </c>
+      <c r="AV14" t="inlineStr">
+        <is>
+          <t>150562465.4441261</t>
+        </is>
+      </c>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>232650449.0</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>74142370.0</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr">
+        <is>
+          <t>57245793.0</t>
+        </is>
+      </c>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>34130931.06</t>
+        </is>
+      </c>
+      <c r="BA14" t="inlineStr">
+        <is>
+          <t>16896577</t>
+        </is>
+      </c>
+      <c r="BB14" t="inlineStr">
+        <is>
+          <t>3442386.786094812</t>
+        </is>
+      </c>
+      <c r="BC14" t="inlineStr">
+        <is>
+          <t>16400757.27416717</t>
+        </is>
+      </c>
+      <c r="BD14" t="n">
+        <v>232650449</v>
+      </c>
+      <c r="BE14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF14" t="inlineStr">
+        <is>
+          <t>41.5</t>
+        </is>
+      </c>
+      <c r="BG14" t="inlineStr">
+        <is>
+          <t>2025/08/07</t>
+        </is>
+      </c>
+      <c r="BH14" t="inlineStr">
+        <is>
+          <t>-11.08</t>
+        </is>
+      </c>
+      <c r="BI14" t="inlineStr">
+        <is>
+          <t>新光鋼</t>
+        </is>
+      </c>
+      <c r="BJ14" t="inlineStr">
+        <is>
+          <t>新光鋼</t>
+        </is>
+      </c>
+      <c r="BK14" t="inlineStr">
+        <is>
+          <t>鋼鐵工業</t>
+        </is>
+      </c>
+      <c r="BL14" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="BM14" t="inlineStr">
+        <is>
+          <t>0.61</t>
+        </is>
+      </c>
+      <c r="BN14" t="inlineStr">
+        <is>
+          <t>-13.67996844119094</t>
+        </is>
+      </c>
+      <c r="BO14" t="inlineStr">
+        <is>
+          <t>-10.11024290164889</t>
+        </is>
+      </c>
+      <c r="BP14" t="inlineStr">
+        <is>
+          <t>24.12947661306339</t>
+        </is>
+      </c>
+      <c r="BQ14" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BR14" t="inlineStr">
+        <is>
+          <t>價-量增</t>
+        </is>
+      </c>
+      <c r="BS14" t="inlineStr">
+        <is>
+          <t>1.02</t>
+        </is>
+      </c>
+      <c r="BT14" t="inlineStr">
+        <is>
+          <t>6.56</t>
+        </is>
+      </c>
+      <c r="BU14" t="inlineStr">
+        <is>
+          <t>11.90</t>
+        </is>
+      </c>
+      <c r="BV14" t="inlineStr">
+        <is>
+          <t>15.74</t>
+        </is>
+      </c>
+      <c r="BW14" t="inlineStr">
+        <is>
+          <t>8.69%</t>
+        </is>
+      </c>
+      <c r="BX14" t="inlineStr">
+        <is>
+          <t>5.19%</t>
+        </is>
+      </c>
+      <c r="BY14" t="inlineStr">
+        <is>
+          <t>29.15</t>
+        </is>
+      </c>
+      <c r="BZ14" t="inlineStr">
+        <is>
+          <t>12236</t>
+        </is>
+      </c>
+      <c r="CA14" t="inlineStr">
+        <is>
+          <t>鋼板38.80%、熱軋及鍍鋅鋼板33.80%、不�袗�板12.60%、特殊鋼板7.00%、加工及其他6.90%、型鋼0.90% (2024年)</t>
+        </is>
+      </c>
+      <c r="CB14" t="inlineStr">
+        <is>
+          <t>新光鋼-鋼鐵工業-上市</t>
+        </is>
+      </c>
+      <c r="CC14" t="inlineStr">
+        <is>
+          <t>鋼鐵工業右下上市</t>
+        </is>
+      </c>
+      <c r="CD14" t="inlineStr">
+        <is>
+          <t>37.0</t>
+        </is>
+      </c>
+      <c r="CE14" t="inlineStr">
+        <is>
           <t>37.5</t>
         </is>
       </c>
-      <c r="AG14" t="inlineStr">
-        <is>
-          <t>16.42</t>
-        </is>
-      </c>
-      <c r="AH14" t="inlineStr">
-        <is>
-          <t>0.66</t>
-        </is>
-      </c>
-      <c r="AI14" t="inlineStr">
-        <is>
-          <t>-4.68</t>
-        </is>
-      </c>
-      <c r="AJ14" t="inlineStr">
-        <is>
-          <t>-4.69</t>
-        </is>
-      </c>
-      <c r="AK14" t="inlineStr">
-        <is>
-          <t>-2.48</t>
-        </is>
-      </c>
-      <c r="AL14" t="inlineStr">
-        <is>
-          <t>36.61</t>
-        </is>
-      </c>
-      <c r="AM14" t="inlineStr">
-        <is>
-          <t>38.41</t>
-        </is>
-      </c>
-      <c r="AN14" t="inlineStr">
-        <is>
-          <t>40.3</t>
-        </is>
-      </c>
-      <c r="AO14" t="inlineStr">
-        <is>
-          <t>41.32</t>
-        </is>
-      </c>
-      <c r="AP14" t="inlineStr">
-        <is>
-          <t>-12.91</t>
-        </is>
-      </c>
-      <c r="AQ14" t="inlineStr">
-        <is>
-          <t>-1.12</t>
-        </is>
-      </c>
-      <c r="AR14" t="inlineStr">
-        <is>
-          <t>-0.99</t>
-        </is>
-      </c>
-      <c r="AS14" t="inlineStr">
-        <is>
-          <t>2.69</t>
-        </is>
-      </c>
-      <c r="AT14" t="inlineStr">
-        <is>
-          <t>-136.94</t>
-        </is>
-      </c>
-      <c r="AU14" t="inlineStr">
-        <is>
-          <t>2025/10/23</t>
-        </is>
-      </c>
-      <c r="AV14" t="inlineStr">
-        <is>
-          <t>150693340.205165</t>
-        </is>
-      </c>
-      <c r="AW14" t="inlineStr">
-        <is>
-          <t>41298962.0</t>
-        </is>
-      </c>
-      <c r="AX14" t="inlineStr">
-        <is>
-          <t>35487232.0</t>
-        </is>
-      </c>
-      <c r="AY14" t="inlineStr">
-        <is>
-          <t>35914543.8</t>
-        </is>
-      </c>
-      <c r="AZ14" t="inlineStr">
-        <is>
-          <t>29950115.64</t>
-        </is>
-      </c>
-      <c r="BA14" t="inlineStr">
-        <is>
-          <t>-427311</t>
-        </is>
-      </c>
-      <c r="BB14" t="inlineStr">
-        <is>
-          <t>1086319.424627111</t>
-        </is>
-      </c>
-      <c r="BC14" t="inlineStr">
-        <is>
-          <t>1798775.809179619</t>
-        </is>
-      </c>
-      <c r="BD14" t="n">
-        <v>41298962</v>
-      </c>
-      <c r="BE14" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BF14" t="inlineStr">
-        <is>
-          <t>41.5</t>
-        </is>
-      </c>
-      <c r="BG14" t="inlineStr">
-        <is>
-          <t>2025/08/07</t>
-        </is>
-      </c>
-      <c r="BH14" t="inlineStr">
-        <is>
-          <t>-11.20</t>
-        </is>
-      </c>
-      <c r="BI14" t="inlineStr">
-        <is>
-          <t>新光鋼</t>
-        </is>
-      </c>
-      <c r="BJ14" t="inlineStr">
-        <is>
-          <t>新光鋼</t>
-        </is>
-      </c>
-      <c r="BK14" t="inlineStr">
-        <is>
-          <t>鋼鐵工業</t>
-        </is>
-      </c>
-      <c r="BL14" t="inlineStr">
-        <is>
-          <t>上市</t>
-        </is>
-      </c>
-      <c r="BM14" t="inlineStr">
-        <is>
-          <t>0.61</t>
-        </is>
-      </c>
-      <c r="BN14" t="inlineStr">
-        <is>
-          <t>-13.67996844119094</t>
-        </is>
-      </c>
-      <c r="BO14" t="inlineStr">
-        <is>
-          <t>-10.11024290164889</t>
-        </is>
-      </c>
-      <c r="BP14" t="inlineStr">
-        <is>
-          <t>24.12947661306339</t>
-        </is>
-      </c>
-      <c r="BQ14" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;可能出現反轉訊號&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;3&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="BR14" t="inlineStr">
-        <is>
-          <t>價-量增</t>
-        </is>
-      </c>
-      <c r="BS14" t="inlineStr">
-        <is>
-          <t>1.01</t>
-        </is>
-      </c>
-      <c r="BT14" t="inlineStr">
-        <is>
-          <t>6.78</t>
-        </is>
-      </c>
-      <c r="BU14" t="inlineStr">
-        <is>
-          <t>11.90</t>
-        </is>
-      </c>
-      <c r="BV14" t="inlineStr">
-        <is>
-          <t>15.25</t>
-        </is>
-      </c>
-      <c r="BW14" t="inlineStr">
-        <is>
-          <t>8.69%</t>
-        </is>
-      </c>
-      <c r="BX14" t="inlineStr">
-        <is>
-          <t>5.19%</t>
-        </is>
-      </c>
-      <c r="BY14" t="inlineStr">
-        <is>
-          <t>28.89</t>
-        </is>
-      </c>
-      <c r="BZ14" t="inlineStr">
-        <is>
-          <t>11850</t>
-        </is>
-      </c>
-      <c r="CA14" t="inlineStr">
-        <is>
-          <t>鋼板38.80%、熱軋及鍍鋅鋼板33.80%、不�袗�板12.60%、特殊鋼板7.00%、加工及其他6.90%、型鋼0.90% (2024年)</t>
-        </is>
-      </c>
-      <c r="CB14" t="inlineStr">
-        <is>
-          <t>新光鋼-鋼鐵工業-上市</t>
-        </is>
-      </c>
-      <c r="CC14" t="inlineStr">
-        <is>
-          <t>鋼鐵工業右下上市</t>
-        </is>
-      </c>
-      <c r="CD14" t="inlineStr">
-        <is>
-          <t>36.4</t>
-        </is>
-      </c>
-      <c r="CE14" t="inlineStr">
-        <is>
-          <t>36.95</t>
-        </is>
-      </c>
       <c r="CF14" t="inlineStr">
         <is>
-          <t>36.0</t>
+          <t>36.9</t>
         </is>
       </c>
       <c r="CG14" t="inlineStr">
         <is>
-          <t>36.85</t>
+          <t>36.9</t>
         </is>
       </c>
       <c r="CH14" t="inlineStr">
@@ -6551,12 +6551,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>0.83</t>
+          <t>1.24</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>776.396</t>
+          <t>1128.761</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -6566,7 +6566,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>36.4</t>
+          <t>36.85</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -6576,17 +6576,17 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>1.36</t>
+          <t>3.28</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>-1.09</t>
+          <t>0.63</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>9.74</t>
+          <t>-1.19</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -6596,7 +6596,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>-95.0</t>
+          <t>-90.0</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -6651,7 +6651,7 @@
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>-15.64</t>
+          <t>-14.60</t>
         </is>
       </c>
       <c r="X15" t="inlineStr">
@@ -6661,17 +6661,17 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>8.27</t>
+          <t>12.03</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>0.70</t>
+          <t>2.09</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
@@ -6682,77 +6682,77 @@
       <c r="AC15" t="inlineStr"/>
       <c r="AD15" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
-          <t>6301</t>
+          <t>1043</t>
         </is>
       </c>
       <c r="AF15" t="inlineStr">
         <is>
-          <t>11.76</t>
+          <t>37.5</t>
         </is>
       </c>
       <c r="AG15" t="inlineStr">
         <is>
-          <t>3.92</t>
+          <t>16.42</t>
         </is>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>-0.90</t>
+          <t>0.66</t>
         </is>
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>-4.83</t>
+          <t>-4.68</t>
         </is>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>-4.54</t>
+          <t>-4.69</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>-2.31</t>
+          <t>-2.48</t>
         </is>
       </c>
       <c r="AL15" t="inlineStr">
         <is>
-          <t>36.73</t>
+          <t>36.61</t>
         </is>
       </c>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>38.6</t>
+          <t>38.41</t>
         </is>
       </c>
       <c r="AN15" t="inlineStr">
         <is>
-          <t>40.43</t>
+          <t>40.3</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>41.39</t>
+          <t>41.32</t>
         </is>
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>-19.31</t>
+          <t>-12.91</t>
         </is>
       </c>
       <c r="AQ15" t="inlineStr">
         <is>
-          <t>-1.15</t>
+          <t>-1.12</t>
         </is>
       </c>
       <c r="AR15" t="inlineStr">
         <is>
-          <t>-0.96</t>
+          <t>-0.99</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr">
@@ -6762,56 +6762,56 @@
       </c>
       <c r="AT15" t="inlineStr">
         <is>
-          <t>-135.75</t>
+          <t>-136.94</t>
         </is>
       </c>
       <c r="AU15" t="inlineStr">
         <is>
-          <t>2025/10/23</t>
+          <t>2025/11/25</t>
         </is>
       </c>
       <c r="AV15" t="inlineStr">
         <is>
-          <t>150693340.205165</t>
+          <t>150562465.4441261</t>
         </is>
       </c>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>28176624.0</t>
+          <t>41298962.0</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>37871124.0</t>
+          <t>35487232.0</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>34509118.0</t>
+          <t>35914543.8</t>
         </is>
       </c>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>29545425.32</t>
+          <t>29950115.64</t>
         </is>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
-          <t>3362006</t>
+          <t>-427311</t>
         </is>
       </c>
       <c r="BB15" t="inlineStr">
         <is>
-          <t>956781.9001630185</t>
+          <t>1086319.424627111</t>
         </is>
       </c>
       <c r="BC15" t="inlineStr">
         <is>
-          <t>1376505.330298137</t>
+          <t>1798775.809179619</t>
         </is>
       </c>
       <c r="BD15" t="n">
-        <v>28176624</v>
+        <v>41298962</v>
       </c>
       <c r="BE15" t="inlineStr">
         <is>
@@ -6830,7 +6830,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>-12.29</t>
+          <t>-11.20</t>
         </is>
       </c>
       <c r="BI15" t="inlineStr">
@@ -6875,22 +6875,22 @@
       </c>
       <c r="BQ15" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;可能出現反轉訊號&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;3&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR15" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS15" t="inlineStr">
         <is>
-          <t>1.00</t>
+          <t>1.01</t>
         </is>
       </c>
       <c r="BT15" t="inlineStr">
         <is>
-          <t>6.78</t>
+          <t>6.56</t>
         </is>
       </c>
       <c r="BU15" t="inlineStr">
@@ -6900,7 +6900,7 @@
       </c>
       <c r="BV15" t="inlineStr">
         <is>
-          <t>15.25</t>
+          <t>15.74</t>
         </is>
       </c>
       <c r="BW15" t="inlineStr">
@@ -6915,12 +6915,12 @@
       </c>
       <c r="BY15" t="inlineStr">
         <is>
-          <t>28.89</t>
+          <t>29.15</t>
         </is>
       </c>
       <c r="BZ15" t="inlineStr">
         <is>
-          <t>11850</t>
+          <t>12236</t>
         </is>
       </c>
       <c r="CA15" t="inlineStr">
@@ -6940,12 +6940,12 @@
       </c>
       <c r="CD15" t="inlineStr">
         <is>
-          <t>36.3</t>
+          <t>36.4</t>
         </is>
       </c>
       <c r="CE15" t="inlineStr">
         <is>
-          <t>36.55</t>
+          <t>36.95</t>
         </is>
       </c>
       <c r="CF15" t="inlineStr">
@@ -6955,7 +6955,7 @@
       </c>
       <c r="CG15" t="inlineStr">
         <is>
-          <t>36.4</t>
+          <t>36.85</t>
         </is>
       </c>
       <c r="CH15" t="inlineStr">
@@ -6987,12 +6987,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>-1.76</t>
+          <t>0.83</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>1212.053</t>
+          <t>776.396</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -7002,7 +7002,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>36.1</t>
+          <t>36.4</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -7012,17 +7012,17 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>2.17</t>
+          <t>4.46</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>-1.09</t>
+          <t>0.63</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>3.03</t>
+          <t>9.74</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -7032,7 +7032,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>-95.0</t>
+          <t>-90.0</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -7087,7 +7087,7 @@
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>-16.34</t>
+          <t>-15.64</t>
         </is>
       </c>
       <c r="X16" t="inlineStr">
@@ -7097,17 +7097,17 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>12.91</t>
+          <t>8.27</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>-1.38</t>
+          <t>0.70</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
@@ -7118,77 +7118,77 @@
       <c r="AC16" t="inlineStr"/>
       <c r="AD16" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
-          <t>6301</t>
+          <t>1043</t>
         </is>
       </c>
       <c r="AF16" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>11.76</t>
         </is>
       </c>
       <c r="AG16" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>3.92</t>
         </is>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>-2.62</t>
+          <t>-0.90</t>
         </is>
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>-4.47</t>
+          <t>-4.83</t>
         </is>
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>-4.38</t>
+          <t>-4.54</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>-2.09</t>
+          <t>-2.31</t>
         </is>
       </c>
       <c r="AL16" t="inlineStr">
         <is>
-          <t>37.07000000000001</t>
+          <t>36.73</t>
         </is>
       </c>
       <c r="AM16" t="inlineStr">
         <is>
-          <t>38.8</t>
+          <t>38.6</t>
         </is>
       </c>
       <c r="AN16" t="inlineStr">
         <is>
-          <t>40.58</t>
+          <t>40.43</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>41.45</t>
+          <t>41.39</t>
         </is>
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>-22.07</t>
+          <t>-19.31</t>
         </is>
       </c>
       <c r="AQ16" t="inlineStr">
         <is>
-          <t>-1.12</t>
+          <t>-1.15</t>
         </is>
       </c>
       <c r="AR16" t="inlineStr">
         <is>
-          <t>-0.91</t>
+          <t>-0.96</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr">
@@ -7198,56 +7198,56 @@
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>-134.02</t>
+          <t>-135.75</t>
         </is>
       </c>
       <c r="AU16" t="inlineStr">
         <is>
-          <t>2025/10/23</t>
+          <t>2025/11/25</t>
         </is>
       </c>
       <c r="AV16" t="inlineStr">
         <is>
-          <t>150693340.205165</t>
+          <t>150562465.4441261</t>
         </is>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>43823516.0</t>
+          <t>28176624.0</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>36085517.8</t>
+          <t>37871124.0</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>35025550.9</t>
+          <t>34509118.0</t>
         </is>
       </c>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>29409986.0</t>
+          <t>29545425.32</t>
         </is>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
-          <t>1059966</t>
+          <t>3362006</t>
         </is>
       </c>
       <c r="BB16" t="inlineStr">
         <is>
-          <t>880468.5492293607</t>
+          <t>956781.9001630185</t>
         </is>
       </c>
       <c r="BC16" t="inlineStr">
         <is>
-          <t>2130065.670099653</t>
+          <t>1376505.330298137</t>
         </is>
       </c>
       <c r="BD16" t="n">
-        <v>43823516</v>
+        <v>28176624</v>
       </c>
       <c r="BE16" t="inlineStr">
         <is>
@@ -7266,7 +7266,7 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>-13.01</t>
+          <t>-12.29</t>
         </is>
       </c>
       <c r="BI16" t="inlineStr">
@@ -7311,7 +7311,7 @@
       </c>
       <c r="BQ16" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR16" t="inlineStr">
@@ -7321,12 +7321,12 @@
       </c>
       <c r="BS16" t="inlineStr">
         <is>
-          <t>0.99</t>
+          <t>1.00</t>
         </is>
       </c>
       <c r="BT16" t="inlineStr">
         <is>
-          <t>6.78</t>
+          <t>6.56</t>
         </is>
       </c>
       <c r="BU16" t="inlineStr">
@@ -7336,7 +7336,7 @@
       </c>
       <c r="BV16" t="inlineStr">
         <is>
-          <t>15.25</t>
+          <t>15.74</t>
         </is>
       </c>
       <c r="BW16" t="inlineStr">
@@ -7351,12 +7351,12 @@
       </c>
       <c r="BY16" t="inlineStr">
         <is>
-          <t>28.89</t>
+          <t>29.15</t>
         </is>
       </c>
       <c r="BZ16" t="inlineStr">
         <is>
-          <t>11850</t>
+          <t>12236</t>
         </is>
       </c>
       <c r="CA16" t="inlineStr">
@@ -7376,22 +7376,22 @@
       </c>
       <c r="CD16" t="inlineStr">
         <is>
-          <t>36.85</t>
+          <t>36.3</t>
         </is>
       </c>
       <c r="CE16" t="inlineStr">
         <is>
-          <t>36.85</t>
+          <t>36.55</t>
         </is>
       </c>
       <c r="CF16" t="inlineStr">
         <is>
-          <t>35.85</t>
+          <t>36.0</t>
         </is>
       </c>
       <c r="CG16" t="inlineStr">
         <is>
-          <t>36.1</t>
+          <t>36.4</t>
         </is>
       </c>
       <c r="CH16" t="inlineStr">
@@ -7423,12 +7423,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>-0.54</t>
+          <t>-1.76</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>672.504</t>
+          <t>1212.053</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -7438,7 +7438,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>36.75</t>
+          <t>36.1</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -7448,17 +7448,17 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>0.41</t>
+          <t>5.25</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>-1.09</t>
+          <t>0.63</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>-2.04</t>
+          <t>3.03</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -7468,7 +7468,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>-95.0</t>
+          <t>-90.0</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -7523,7 +7523,7 @@
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>-14.83</t>
+          <t>-16.34</t>
         </is>
       </c>
       <c r="X17" t="inlineStr">
@@ -7533,17 +7533,17 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>7.17</t>
+          <t>12.91</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>-1.09</t>
+          <t>-1.38</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
@@ -7554,12 +7554,12 @@
       <c r="AC17" t="inlineStr"/>
       <c r="AD17" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
-          <t>6301</t>
+          <t>1043</t>
         </is>
       </c>
       <c r="AF17" t="inlineStr">
@@ -7574,57 +7574,57 @@
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>-1.92</t>
+          <t>-2.62</t>
         </is>
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>-3.97</t>
+          <t>-4.47</t>
         </is>
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>-4.25</t>
+          <t>-4.38</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>-1.83</t>
+          <t>-2.09</t>
         </is>
       </c>
       <c r="AL17" t="inlineStr">
         <is>
-          <t>37.47000000000001</t>
+          <t>37.07000000000001</t>
         </is>
       </c>
       <c r="AM17" t="inlineStr">
         <is>
-          <t>39.02</t>
+          <t>38.8</t>
         </is>
       </c>
       <c r="AN17" t="inlineStr">
         <is>
-          <t>40.75</t>
+          <t>40.58</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>41.51</t>
+          <t>41.45</t>
         </is>
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>-19.33</t>
+          <t>-22.07</t>
         </is>
       </c>
       <c r="AQ17" t="inlineStr">
         <is>
-          <t>-1.03</t>
+          <t>-1.12</t>
         </is>
       </c>
       <c r="AR17" t="inlineStr">
         <is>
-          <t>-0.86</t>
+          <t>-0.91</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr">
@@ -7634,56 +7634,56 @@
       </c>
       <c r="AT17" t="inlineStr">
         <is>
-          <t>-132.14</t>
+          <t>-134.02</t>
         </is>
       </c>
       <c r="AU17" t="inlineStr">
         <is>
-          <t>2025/10/23</t>
+          <t>2025/11/25</t>
         </is>
       </c>
       <c r="AV17" t="inlineStr">
         <is>
-          <t>150693340.205165</t>
+          <t>150562465.4441261</t>
         </is>
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>24762299.0</t>
+          <t>43823516.0</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>31929308.6</t>
+          <t>36085517.8</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>32595150.7</t>
+          <t>35025550.9</t>
         </is>
       </c>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>29130934.74</t>
+          <t>29409986.0</t>
         </is>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
-          <t>-665842</t>
+          <t>1059966</t>
         </is>
       </c>
       <c r="BB17" t="inlineStr">
         <is>
-          <t>653269.0727074891</t>
+          <t>880468.5492293607</t>
         </is>
       </c>
       <c r="BC17" t="inlineStr">
         <is>
-          <t>1454053.953026839</t>
+          <t>2130065.670099653</t>
         </is>
       </c>
       <c r="BD17" t="n">
-        <v>24762299</v>
+        <v>43823516</v>
       </c>
       <c r="BE17" t="inlineStr">
         <is>
@@ -7702,7 +7702,7 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>-11.45</t>
+          <t>-13.01</t>
         </is>
       </c>
       <c r="BI17" t="inlineStr">
@@ -7757,12 +7757,12 @@
       </c>
       <c r="BS17" t="inlineStr">
         <is>
-          <t>1.01</t>
+          <t>0.99</t>
         </is>
       </c>
       <c r="BT17" t="inlineStr">
         <is>
-          <t>6.78</t>
+          <t>6.56</t>
         </is>
       </c>
       <c r="BU17" t="inlineStr">
@@ -7772,7 +7772,7 @@
       </c>
       <c r="BV17" t="inlineStr">
         <is>
-          <t>15.25</t>
+          <t>15.74</t>
         </is>
       </c>
       <c r="BW17" t="inlineStr">
@@ -7787,12 +7787,12 @@
       </c>
       <c r="BY17" t="inlineStr">
         <is>
-          <t>28.89</t>
+          <t>29.15</t>
         </is>
       </c>
       <c r="BZ17" t="inlineStr">
         <is>
-          <t>11850</t>
+          <t>12236</t>
         </is>
       </c>
       <c r="CA17" t="inlineStr">
@@ -7812,22 +7812,22 @@
       </c>
       <c r="CD17" t="inlineStr">
         <is>
-          <t>36.95</t>
+          <t>36.85</t>
         </is>
       </c>
       <c r="CE17" t="inlineStr">
         <is>
-          <t>37.3</t>
+          <t>36.85</t>
         </is>
       </c>
       <c r="CF17" t="inlineStr">
         <is>
-          <t>36.6</t>
+          <t>35.85</t>
         </is>
       </c>
       <c r="CG17" t="inlineStr">
         <is>
-          <t>36.75</t>
+          <t>36.1</t>
         </is>
       </c>
       <c r="CH17" t="inlineStr">
@@ -7859,12 +7859,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>-1.34</t>
+          <t>-0.54</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>1065.248</t>
+          <t>672.504</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -7874,7 +7874,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>36.95</t>
+          <t>36.75</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -7884,102 +7884,102 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>-0.14</t>
+          <t>3.54</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
+          <t>0.63</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>-2.04</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>-90.0</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>2025-08-15 00:00:00</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>2025-08-26 00:00:00</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>2025-03-10 00:00:00</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>2025-03-12 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
+          <t>44.3</t>
+        </is>
+      </c>
+      <c r="R18" t="inlineStr">
+        <is>
+          <t>43.15</t>
+        </is>
+      </c>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>54.0</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>52.5</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>-14.83</t>
+        </is>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>-15.62</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2025-11-18</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>7.17</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
           <t>-1.09</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>28.28</t>
-        </is>
-      </c>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L18" t="inlineStr">
-        <is>
-          <t>-95.0</t>
-        </is>
-      </c>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>2025-08-15 00:00:00</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr">
-        <is>
-          <t>2025-08-26 00:00:00</t>
-        </is>
-      </c>
-      <c r="O18" t="inlineStr">
-        <is>
-          <t>2025-03-10 00:00:00</t>
-        </is>
-      </c>
-      <c r="P18" t="inlineStr">
-        <is>
-          <t>2025-03-12 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q18" t="inlineStr">
-        <is>
-          <t>44.3</t>
-        </is>
-      </c>
-      <c r="R18" t="inlineStr">
-        <is>
-          <t>43.15</t>
-        </is>
-      </c>
-      <c r="S18" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T18" t="inlineStr">
-        <is>
-          <t>54.0</t>
-        </is>
-      </c>
-      <c r="U18" t="inlineStr">
-        <is>
-          <t>52.5</t>
-        </is>
-      </c>
-      <c r="V18" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="W18" t="inlineStr">
-        <is>
-          <t>-14.37</t>
-        </is>
-      </c>
-      <c r="X18" t="inlineStr">
-        <is>
-          <t>-15.62</t>
-        </is>
-      </c>
-      <c r="Y18" t="inlineStr">
-        <is>
-          <t>2025-11-17</t>
-        </is>
-      </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>11.35</t>
-        </is>
-      </c>
-      <c r="AA18" t="inlineStr">
-        <is>
-          <t>-0.81</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
@@ -7990,12 +7990,12 @@
       <c r="AC18" t="inlineStr"/>
       <c r="AD18" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
-          <t>6301</t>
+          <t>1043</t>
         </is>
       </c>
       <c r="AF18" t="inlineStr">
@@ -8005,62 +8005,62 @@
       </c>
       <c r="AG18" t="inlineStr">
         <is>
-          <t>9.38</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>-1.86</t>
+          <t>-1.92</t>
         </is>
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>-4.02</t>
+          <t>-3.97</t>
         </is>
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>-4.09</t>
+          <t>-4.25</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>-1.60</t>
+          <t>-1.83</t>
         </is>
       </c>
       <c r="AL18" t="inlineStr">
         <is>
-          <t>37.65000000000001</t>
+          <t>37.47000000000001</t>
         </is>
       </c>
       <c r="AM18" t="inlineStr">
         <is>
-          <t>39.23</t>
+          <t>39.02</t>
         </is>
       </c>
       <c r="AN18" t="inlineStr">
         <is>
-          <t>40.9</t>
+          <t>40.75</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>41.57</t>
+          <t>41.51</t>
         </is>
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>-18.37</t>
+          <t>-19.33</t>
         </is>
       </c>
       <c r="AQ18" t="inlineStr">
         <is>
-          <t>-0.97</t>
+          <t>-1.03</t>
         </is>
       </c>
       <c r="AR18" t="inlineStr">
         <is>
-          <t>-0.82</t>
+          <t>-0.86</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr">
@@ -8070,56 +8070,56 @@
       </c>
       <c r="AT18" t="inlineStr">
         <is>
-          <t>-130.59</t>
+          <t>-132.14</t>
         </is>
       </c>
       <c r="AU18" t="inlineStr">
         <is>
-          <t>2025/10/23</t>
+          <t>2025/11/25</t>
         </is>
       </c>
       <c r="AV18" t="inlineStr">
         <is>
-          <t>150693340.205165</t>
+          <t>150562465.4441261</t>
         </is>
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>39374759.0</t>
+          <t>24762299.0</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>40349216.0</t>
+          <t>31929308.6</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>31454761.9</t>
+          <t>32595150.7</t>
         </is>
       </c>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>29061426.18</t>
+          <t>29130934.74</t>
         </is>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
-          <t>8894454</t>
+          <t>-665842</t>
         </is>
       </c>
       <c r="BB18" t="inlineStr">
         <is>
-          <t>507671.8217403347</t>
+          <t>653269.0727074891</t>
         </is>
       </c>
       <c r="BC18" t="inlineStr">
         <is>
-          <t>2478665.680314712</t>
+          <t>1454053.953026839</t>
         </is>
       </c>
       <c r="BD18" t="n">
-        <v>39374759</v>
+        <v>24762299</v>
       </c>
       <c r="BE18" t="inlineStr">
         <is>
@@ -8138,7 +8138,7 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>-10.96</t>
+          <t>-11.45</t>
         </is>
       </c>
       <c r="BI18" t="inlineStr">
@@ -8183,22 +8183,22 @@
       </c>
       <c r="BQ18" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR18" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS18" t="inlineStr">
         <is>
-          <t>1.02</t>
+          <t>1.01</t>
         </is>
       </c>
       <c r="BT18" t="inlineStr">
         <is>
-          <t>6.78</t>
+          <t>6.56</t>
         </is>
       </c>
       <c r="BU18" t="inlineStr">
@@ -8208,7 +8208,7 @@
       </c>
       <c r="BV18" t="inlineStr">
         <is>
-          <t>15.25</t>
+          <t>15.74</t>
         </is>
       </c>
       <c r="BW18" t="inlineStr">
@@ -8223,12 +8223,12 @@
       </c>
       <c r="BY18" t="inlineStr">
         <is>
-          <t>28.89</t>
+          <t>29.15</t>
         </is>
       </c>
       <c r="BZ18" t="inlineStr">
         <is>
-          <t>11850</t>
+          <t>12236</t>
         </is>
       </c>
       <c r="CA18" t="inlineStr">
@@ -8248,22 +8248,22 @@
       </c>
       <c r="CD18" t="inlineStr">
         <is>
+          <t>36.95</t>
+        </is>
+      </c>
+      <c r="CE18" t="inlineStr">
+        <is>
           <t>37.3</t>
         </is>
       </c>
-      <c r="CE18" t="inlineStr">
-        <is>
-          <t>37.5</t>
-        </is>
-      </c>
       <c r="CF18" t="inlineStr">
         <is>
-          <t>36.7</t>
+          <t>36.6</t>
         </is>
       </c>
       <c r="CG18" t="inlineStr">
         <is>
-          <t>36.95</t>
+          <t>36.75</t>
         </is>
       </c>
       <c r="CH18" t="inlineStr">
@@ -8295,12 +8295,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>-1.71</t>
+          <t>-1.34</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>1408.733</t>
+          <t>1065.248</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -8310,7 +8310,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>37.45</t>
+          <t>36.95</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -8320,17 +8320,17 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>-1.49</t>
+          <t>3.02</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>-1.09</t>
+          <t>0.63</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>22.93</t>
+          <t>28.28</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -8340,7 +8340,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>-95.0</t>
+          <t>-90.0</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -8395,7 +8395,7 @@
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>-13.21</t>
+          <t>-14.37</t>
         </is>
       </c>
       <c r="X19" t="inlineStr">
@@ -8405,17 +8405,17 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>15.01</t>
+          <t>11.35</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>-2.94</t>
+          <t>-0.81</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
@@ -8426,12 +8426,12 @@
       <c r="AC19" t="inlineStr"/>
       <c r="AD19" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
-          <t>6301</t>
+          <t>1043</t>
         </is>
       </c>
       <c r="AF19" t="inlineStr">
@@ -8441,62 +8441,62 @@
       </c>
       <c r="AG19" t="inlineStr">
         <is>
-          <t>16.69</t>
+          <t>9.38</t>
         </is>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
-          <t>-1.42</t>
+          <t>-1.86</t>
         </is>
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>-3.63</t>
+          <t>-4.02</t>
         </is>
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>-3.96</t>
+          <t>-4.09</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>-1.34</t>
+          <t>-1.60</t>
         </is>
       </c>
       <c r="AL19" t="inlineStr">
         <is>
-          <t>37.99</t>
+          <t>37.65000000000001</t>
         </is>
       </c>
       <c r="AM19" t="inlineStr">
         <is>
-          <t>39.42</t>
+          <t>39.23</t>
         </is>
       </c>
       <c r="AN19" t="inlineStr">
         <is>
-          <t>41.05</t>
+          <t>40.9</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>41.6</t>
+          <t>41.57</t>
         </is>
       </c>
       <c r="AP19" t="inlineStr">
         <is>
-          <t>-15.49</t>
+          <t>-18.37</t>
         </is>
       </c>
       <c r="AQ19" t="inlineStr">
         <is>
-          <t>-0.91</t>
+          <t>-0.97</t>
         </is>
       </c>
       <c r="AR19" t="inlineStr">
         <is>
-          <t>-0.78</t>
+          <t>-0.82</t>
         </is>
       </c>
       <c r="AS19" t="inlineStr">
@@ -8506,56 +8506,56 @@
       </c>
       <c r="AT19" t="inlineStr">
         <is>
-          <t>-129.19</t>
+          <t>-130.59</t>
         </is>
       </c>
       <c r="AU19" t="inlineStr">
         <is>
-          <t>2025/10/23</t>
+          <t>2025/11/25</t>
         </is>
       </c>
       <c r="AV19" t="inlineStr">
         <is>
-          <t>150693340.205165</t>
+          <t>150562465.4441261</t>
         </is>
       </c>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>53218422.0</t>
+          <t>39374759.0</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>36341855.6</t>
+          <t>40349216.0</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
-          <t>29562657.9</t>
+          <t>31454761.9</t>
         </is>
       </c>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>28846965.04</t>
+          <t>29061426.18</t>
         </is>
       </c>
       <c r="BA19" t="inlineStr">
         <is>
-          <t>6779197</t>
+          <t>8894454</t>
         </is>
       </c>
       <c r="BB19" t="inlineStr">
         <is>
-          <t>149309.3019995387</t>
+          <t>507671.8217403347</t>
         </is>
       </c>
       <c r="BC19" t="inlineStr">
         <is>
-          <t>2288252.230714723</t>
+          <t>2478665.680314712</t>
         </is>
       </c>
       <c r="BD19" t="n">
-        <v>53218422</v>
+        <v>39374759</v>
       </c>
       <c r="BE19" t="inlineStr">
         <is>
@@ -8574,7 +8574,7 @@
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>-9.76</t>
+          <t>-10.96</t>
         </is>
       </c>
       <c r="BI19" t="inlineStr">
@@ -8619,22 +8619,22 @@
       </c>
       <c r="BQ19" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR19" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS19" t="inlineStr">
         <is>
-          <t>1.03</t>
+          <t>1.02</t>
         </is>
       </c>
       <c r="BT19" t="inlineStr">
         <is>
-          <t>6.78</t>
+          <t>6.56</t>
         </is>
       </c>
       <c r="BU19" t="inlineStr">
@@ -8644,7 +8644,7 @@
       </c>
       <c r="BV19" t="inlineStr">
         <is>
-          <t>15.25</t>
+          <t>15.74</t>
         </is>
       </c>
       <c r="BW19" t="inlineStr">
@@ -8659,12 +8659,12 @@
       </c>
       <c r="BY19" t="inlineStr">
         <is>
-          <t>28.89</t>
+          <t>29.15</t>
         </is>
       </c>
       <c r="BZ19" t="inlineStr">
         <is>
-          <t>11850</t>
+          <t>12236</t>
         </is>
       </c>
       <c r="CA19" t="inlineStr">
@@ -8684,22 +8684,22 @@
       </c>
       <c r="CD19" t="inlineStr">
         <is>
-          <t>38.1</t>
+          <t>37.3</t>
         </is>
       </c>
       <c r="CE19" t="inlineStr">
         <is>
-          <t>38.7</t>
+          <t>37.5</t>
         </is>
       </c>
       <c r="CF19" t="inlineStr">
         <is>
-          <t>37.3</t>
+          <t>36.7</t>
         </is>
       </c>
       <c r="CG19" t="inlineStr">
         <is>
-          <t>37.45</t>
+          <t>36.95</t>
         </is>
       </c>
       <c r="CH19" t="inlineStr">
@@ -8731,12 +8731,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-1.71</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>504.317</t>
+          <t>1408.733</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -8746,7 +8746,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>38.1</t>
+          <t>37.45</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -8756,17 +8756,17 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>-3.25</t>
+          <t>1.71</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>-1.09</t>
+          <t>0.63</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>20.39</t>
+          <t>22.93</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -8776,7 +8776,7 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>-95.0</t>
+          <t>-90.0</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
@@ -8831,7 +8831,7 @@
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>-11.70</t>
+          <t>-13.21</t>
         </is>
       </c>
       <c r="X20" t="inlineStr">
@@ -8841,17 +8841,17 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>5.37</t>
+          <t>15.01</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>-0.39</t>
+          <t>-2.94</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
@@ -8862,17 +8862,17 @@
       <c r="AC20" t="inlineStr"/>
       <c r="AD20" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
-          <t>6301</t>
+          <t>1043</t>
         </is>
       </c>
       <c r="AF20" t="inlineStr">
         <is>
-          <t>28.13</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG20" t="inlineStr">
@@ -8882,57 +8882,57 @@
       </c>
       <c r="AH20" t="inlineStr">
         <is>
-          <t>-0.55</t>
+          <t>-1.42</t>
         </is>
       </c>
       <c r="AI20" t="inlineStr">
         <is>
-          <t>-3.22</t>
+          <t>-3.63</t>
         </is>
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>-3.86</t>
+          <t>-3.96</t>
         </is>
       </c>
       <c r="AK20" t="inlineStr">
         <is>
-          <t>-1.12</t>
+          <t>-1.34</t>
         </is>
       </c>
       <c r="AL20" t="inlineStr">
         <is>
-          <t>38.31</t>
+          <t>37.99</t>
         </is>
       </c>
       <c r="AM20" t="inlineStr">
         <is>
-          <t>39.58</t>
+          <t>39.42</t>
         </is>
       </c>
       <c r="AN20" t="inlineStr">
         <is>
-          <t>41.17</t>
+          <t>41.05</t>
         </is>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>41.64</t>
+          <t>41.6</t>
         </is>
       </c>
       <c r="AP20" t="inlineStr">
         <is>
-          <t>-13.76</t>
+          <t>-15.49</t>
         </is>
       </c>
       <c r="AQ20" t="inlineStr">
         <is>
-          <t>-0.86</t>
+          <t>-0.91</t>
         </is>
       </c>
       <c r="AR20" t="inlineStr">
         <is>
-          <t>-0.75</t>
+          <t>-0.78</t>
         </is>
       </c>
       <c r="AS20" t="inlineStr">
@@ -8942,56 +8942,56 @@
       </c>
       <c r="AT20" t="inlineStr">
         <is>
-          <t>-128.06</t>
+          <t>-129.19</t>
         </is>
       </c>
       <c r="AU20" t="inlineStr">
         <is>
-          <t>2025/10/23</t>
+          <t>2025/11/25</t>
         </is>
       </c>
       <c r="AV20" t="inlineStr">
         <is>
-          <t>150693340.205165</t>
+          <t>150562465.4441261</t>
         </is>
       </c>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>19248593.0</t>
+          <t>53218422.0</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>31147112.0</t>
+          <t>36341855.6</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
-          <t>25871081.1</t>
+          <t>29562657.9</t>
         </is>
       </c>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>28091032.78</t>
+          <t>28846965.04</t>
         </is>
       </c>
       <c r="BA20" t="inlineStr">
         <is>
-          <t>5276030</t>
+          <t>6779197</t>
         </is>
       </c>
       <c r="BB20" t="inlineStr">
         <is>
-          <t>-239589.4123123131</t>
+          <t>149309.3019995387</t>
         </is>
       </c>
       <c r="BC20" t="inlineStr">
         <is>
-          <t>451260.1159035005</t>
+          <t>2288252.230714723</t>
         </is>
       </c>
       <c r="BD20" t="n">
-        <v>19248593</v>
+        <v>53218422</v>
       </c>
       <c r="BE20" t="inlineStr">
         <is>
@@ -9010,7 +9010,7 @@
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>-8.19</t>
+          <t>-9.76</t>
         </is>
       </c>
       <c r="BI20" t="inlineStr">
@@ -9055,7 +9055,7 @@
       </c>
       <c r="BQ20" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR20" t="inlineStr">
@@ -9065,12 +9065,12 @@
       </c>
       <c r="BS20" t="inlineStr">
         <is>
-          <t>1.05</t>
+          <t>1.03</t>
         </is>
       </c>
       <c r="BT20" t="inlineStr">
         <is>
-          <t>6.78</t>
+          <t>6.56</t>
         </is>
       </c>
       <c r="BU20" t="inlineStr">
@@ -9080,7 +9080,7 @@
       </c>
       <c r="BV20" t="inlineStr">
         <is>
-          <t>15.25</t>
+          <t>15.74</t>
         </is>
       </c>
       <c r="BW20" t="inlineStr">
@@ -9095,12 +9095,12 @@
       </c>
       <c r="BY20" t="inlineStr">
         <is>
-          <t>28.89</t>
+          <t>29.15</t>
         </is>
       </c>
       <c r="BZ20" t="inlineStr">
         <is>
-          <t>11850</t>
+          <t>12236</t>
         </is>
       </c>
       <c r="CA20" t="inlineStr">
@@ -9120,22 +9120,22 @@
       </c>
       <c r="CD20" t="inlineStr">
         <is>
-          <t>38.2</t>
+          <t>38.1</t>
         </is>
       </c>
       <c r="CE20" t="inlineStr">
         <is>
-          <t>38.4</t>
+          <t>38.7</t>
         </is>
       </c>
       <c r="CF20" t="inlineStr">
         <is>
-          <t>37.95</t>
+          <t>37.3</t>
         </is>
       </c>
       <c r="CG20" t="inlineStr">
         <is>
-          <t>38.1</t>
+          <t>37.45</t>
         </is>
       </c>
       <c r="CH20" t="inlineStr">
@@ -9167,12 +9167,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>1.18</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>605.721</t>
+          <t>504.317</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -9192,17 +9192,17 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>-3.25</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>-1.09</t>
+          <t>0.63</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>29.75</t>
+          <t>20.39</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -9212,7 +9212,7 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>-95.0</t>
+          <t>-90.0</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
@@ -9277,17 +9277,17 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>6.45</t>
+          <t>5.37</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>0.40</t>
+          <t>-0.39</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
@@ -9298,77 +9298,77 @@
       <c r="AC21" t="inlineStr"/>
       <c r="AD21" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
-          <t>6301</t>
+          <t>1043</t>
         </is>
       </c>
       <c r="AF21" t="inlineStr">
         <is>
-          <t>21.95</t>
+          <t>28.13</t>
         </is>
       </c>
       <c r="AG21" t="inlineStr">
         <is>
-          <t>7.32</t>
+          <t>16.69</t>
         </is>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
-          <t>-0.94</t>
+          <t>-0.55</t>
         </is>
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>-3.10</t>
+          <t>-3.22</t>
         </is>
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>-3.87</t>
+          <t>-3.86</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
         <is>
-          <t>-0.91</t>
+          <t>-1.12</t>
         </is>
       </c>
       <c r="AL21" t="inlineStr">
         <is>
-          <t>38.46</t>
+          <t>38.31</t>
         </is>
       </c>
       <c r="AM21" t="inlineStr">
         <is>
-          <t>39.69</t>
+          <t>39.58</t>
         </is>
       </c>
       <c r="AN21" t="inlineStr">
         <is>
-          <t>41.29</t>
+          <t>41.17</t>
         </is>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>41.67</t>
+          <t>41.64</t>
         </is>
       </c>
       <c r="AP21" t="inlineStr">
         <is>
-          <t>-16.76</t>
+          <t>-13.76</t>
         </is>
       </c>
       <c r="AQ21" t="inlineStr">
         <is>
-          <t>-0.85</t>
+          <t>-0.86</t>
         </is>
       </c>
       <c r="AR21" t="inlineStr">
         <is>
-          <t>-0.73</t>
+          <t>-0.75</t>
         </is>
       </c>
       <c r="AS21" t="inlineStr">
@@ -9378,56 +9378,56 @@
       </c>
       <c r="AT21" t="inlineStr">
         <is>
-          <t>-127.09</t>
+          <t>-128.06</t>
         </is>
       </c>
       <c r="AU21" t="inlineStr">
         <is>
-          <t>2025/10/23</t>
+          <t>2025/11/25</t>
         </is>
       </c>
       <c r="AV21" t="inlineStr">
         <is>
-          <t>150693340.205165</t>
+          <t>150562465.4441261</t>
         </is>
       </c>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>23042470.0</t>
+          <t>19248593.0</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>33965584.0</t>
+          <t>31147112.0</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
-          <t>26178217.9</t>
+          <t>25871081.1</t>
         </is>
       </c>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>28206383.42</t>
+          <t>28091032.78</t>
         </is>
       </c>
       <c r="BA21" t="inlineStr">
         <is>
-          <t>7787366</t>
+          <t>5276030</t>
         </is>
       </c>
       <c r="BB21" t="inlineStr">
         <is>
-          <t>-365198.417442461</t>
+          <t>-239589.4123123131</t>
         </is>
       </c>
       <c r="BC21" t="inlineStr">
         <is>
-          <t>1450493.769176625</t>
+          <t>451260.1159035005</t>
         </is>
       </c>
       <c r="BD21" t="n">
-        <v>23042470</v>
+        <v>19248593</v>
       </c>
       <c r="BE21" t="inlineStr">
         <is>
@@ -9491,7 +9491,7 @@
       </c>
       <c r="BQ21" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;可能出現反轉訊號&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;3&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR21" t="inlineStr">
@@ -9506,7 +9506,7 @@
       </c>
       <c r="BT21" t="inlineStr">
         <is>
-          <t>6.78</t>
+          <t>6.56</t>
         </is>
       </c>
       <c r="BU21" t="inlineStr">
@@ -9516,7 +9516,7 @@
       </c>
       <c r="BV21" t="inlineStr">
         <is>
-          <t>15.25</t>
+          <t>15.74</t>
         </is>
       </c>
       <c r="BW21" t="inlineStr">
@@ -9531,12 +9531,12 @@
       </c>
       <c r="BY21" t="inlineStr">
         <is>
-          <t>28.89</t>
+          <t>29.15</t>
         </is>
       </c>
       <c r="BZ21" t="inlineStr">
         <is>
-          <t>11850</t>
+          <t>12236</t>
         </is>
       </c>
       <c r="CA21" t="inlineStr">
@@ -9556,17 +9556,17 @@
       </c>
       <c r="CD21" t="inlineStr">
         <is>
-          <t>38.0</t>
+          <t>38.2</t>
         </is>
       </c>
       <c r="CE21" t="inlineStr">
         <is>
-          <t>38.3</t>
+          <t>38.4</t>
         </is>
       </c>
       <c r="CF21" t="inlineStr">
         <is>
-          <t>37.75</t>
+          <t>37.95</t>
         </is>
       </c>
       <c r="CG21" t="inlineStr">
@@ -9603,12 +9603,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>-2.6</t>
+          <t>1.18</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>1764.112</t>
+          <t>605.721</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -9618,7 +9618,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>37.65</t>
+          <t>38.1</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -9628,17 +9628,17 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>-2.03</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>-1.09</t>
+          <t>0.63</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>21.53</t>
+          <t>29.75</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -9648,7 +9648,7 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>-95.0</t>
+          <t>-90.0</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
@@ -9703,7 +9703,7 @@
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>-12.75</t>
+          <t>-11.70</t>
         </is>
       </c>
       <c r="X22" t="inlineStr">
@@ -9713,17 +9713,17 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>18.80</t>
+          <t>6.45</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>-2.12</t>
+          <t>0.40</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
@@ -9734,77 +9734,77 @@
       <c r="AC22" t="inlineStr"/>
       <c r="AD22" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AE22" t="inlineStr">
         <is>
-          <t>6301</t>
+          <t>1043</t>
         </is>
       </c>
       <c r="AF22" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>21.95</t>
         </is>
       </c>
       <c r="AG22" t="inlineStr">
         <is>
-          <t>6.67</t>
+          <t>7.32</t>
         </is>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
-          <t>-2.44</t>
+          <t>-0.94</t>
         </is>
       </c>
       <c r="AI22" t="inlineStr">
         <is>
-          <t>-3.03</t>
+          <t>-3.10</t>
         </is>
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>-3.91</t>
+          <t>-3.87</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
         <is>
-          <t>-0.66</t>
+          <t>-0.91</t>
         </is>
       </c>
       <c r="AL22" t="inlineStr">
         <is>
-          <t>38.59</t>
+          <t>38.46</t>
         </is>
       </c>
       <c r="AM22" t="inlineStr">
         <is>
-          <t>39.8</t>
+          <t>39.69</t>
         </is>
       </c>
       <c r="AN22" t="inlineStr">
         <is>
-          <t>41.42</t>
+          <t>41.29</t>
         </is>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>41.69</t>
+          <t>41.67</t>
         </is>
       </c>
       <c r="AP22" t="inlineStr">
         <is>
-          <t>-18.69</t>
+          <t>-16.76</t>
         </is>
       </c>
       <c r="AQ22" t="inlineStr">
         <is>
-          <t>-0.83</t>
+          <t>-0.85</t>
         </is>
       </c>
       <c r="AR22" t="inlineStr">
         <is>
-          <t>-0.70</t>
+          <t>-0.73</t>
         </is>
       </c>
       <c r="AS22" t="inlineStr">
@@ -9814,56 +9814,56 @@
       </c>
       <c r="AT22" t="inlineStr">
         <is>
-          <t>-125.95</t>
+          <t>-127.09</t>
         </is>
       </c>
       <c r="AU22" t="inlineStr">
         <is>
-          <t>2025/10/23</t>
+          <t>2025/11/25</t>
         </is>
       </c>
       <c r="AV22" t="inlineStr">
         <is>
-          <t>150693340.205165</t>
+          <t>150562465.4441261</t>
         </is>
       </c>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>66861836.0</t>
+          <t>23042470.0</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>33260992.8</t>
+          <t>33965584.0</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr">
         <is>
-          <t>27368625.9</t>
+          <t>26178217.9</t>
         </is>
       </c>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>28716017.48</t>
+          <t>28206383.42</t>
         </is>
       </c>
       <c r="BA22" t="inlineStr">
         <is>
-          <t>5892366</t>
+          <t>7787366</t>
         </is>
       </c>
       <c r="BB22" t="inlineStr">
         <is>
-          <t>-695324.269555022</t>
+          <t>-365198.417442461</t>
         </is>
       </c>
       <c r="BC22" t="inlineStr">
         <is>
-          <t>2419680.246381927</t>
+          <t>1450493.769176625</t>
         </is>
       </c>
       <c r="BD22" t="n">
-        <v>66861836</v>
+        <v>23042470</v>
       </c>
       <c r="BE22" t="inlineStr">
         <is>
@@ -9882,7 +9882,7 @@
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>-9.28</t>
+          <t>-8.19</t>
         </is>
       </c>
       <c r="BI22" t="inlineStr">
@@ -9927,7 +9927,7 @@
       </c>
       <c r="BQ22" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;可能出現反轉訊號&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;3&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR22" t="inlineStr">
@@ -9937,12 +9937,12 @@
       </c>
       <c r="BS22" t="inlineStr">
         <is>
-          <t>1.04</t>
+          <t>1.05</t>
         </is>
       </c>
       <c r="BT22" t="inlineStr">
         <is>
-          <t>6.78</t>
+          <t>6.56</t>
         </is>
       </c>
       <c r="BU22" t="inlineStr">
@@ -9952,7 +9952,7 @@
       </c>
       <c r="BV22" t="inlineStr">
         <is>
-          <t>15.25</t>
+          <t>15.74</t>
         </is>
       </c>
       <c r="BW22" t="inlineStr">
@@ -9967,12 +9967,12 @@
       </c>
       <c r="BY22" t="inlineStr">
         <is>
-          <t>28.89</t>
+          <t>29.15</t>
         </is>
       </c>
       <c r="BZ22" t="inlineStr">
         <is>
-          <t>11850</t>
+          <t>12236</t>
         </is>
       </c>
       <c r="CA22" t="inlineStr">
@@ -9992,22 +9992,22 @@
       </c>
       <c r="CD22" t="inlineStr">
         <is>
-          <t>38.45</t>
+          <t>38.0</t>
         </is>
       </c>
       <c r="CE22" t="inlineStr">
         <is>
-          <t>38.75</t>
+          <t>38.3</t>
         </is>
       </c>
       <c r="CF22" t="inlineStr">
         <is>
-          <t>37.35</t>
+          <t>37.75</t>
         </is>
       </c>
       <c r="CG22" t="inlineStr">
         <is>
-          <t>37.65</t>
+          <t>38.1</t>
         </is>
       </c>
       <c r="CH22" t="inlineStr">
@@ -10039,12 +10039,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>-1.03</t>
+          <t>-2.6</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>499.552</t>
+          <t>1764.112</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -10054,7 +10054,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>38.65</t>
+          <t>37.65</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -10064,17 +10064,17 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>-4.74</t>
+          <t>1.18</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>-1.09</t>
+          <t>0.63</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>0.16</t>
+          <t>21.53</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -10084,7 +10084,7 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>-95.0</t>
+          <t>-90.0</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
@@ -10139,7 +10139,7 @@
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>-10.43</t>
+          <t>-12.75</t>
         </is>
       </c>
       <c r="X23" t="inlineStr">
@@ -10149,17 +10149,17 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>5.32</t>
+          <t>18.80</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>-1.42</t>
+          <t>-2.12</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
@@ -10170,12 +10170,12 @@
       <c r="AC23" t="inlineStr"/>
       <c r="AD23" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AE23" t="inlineStr">
         <is>
-          <t>6301</t>
+          <t>1043</t>
         </is>
       </c>
       <c r="AF23" t="inlineStr">
@@ -10185,17 +10185,17 @@
       </c>
       <c r="AG23" t="inlineStr">
         <is>
-          <t>8.47</t>
+          <t>6.67</t>
         </is>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
-          <t>-0.57</t>
+          <t>-2.44</t>
         </is>
       </c>
       <c r="AI23" t="inlineStr">
         <is>
-          <t>-2.61</t>
+          <t>-3.03</t>
         </is>
       </c>
       <c r="AJ23" t="inlineStr">
@@ -10205,42 +10205,42 @@
       </c>
       <c r="AK23" t="inlineStr">
         <is>
-          <t>-0.43</t>
+          <t>-0.66</t>
         </is>
       </c>
       <c r="AL23" t="inlineStr">
         <is>
-          <t>38.87</t>
+          <t>38.59</t>
         </is>
       </c>
       <c r="AM23" t="inlineStr">
         <is>
-          <t>39.91</t>
+          <t>39.8</t>
         </is>
       </c>
       <c r="AN23" t="inlineStr">
         <is>
-          <t>41.54</t>
+          <t>41.42</t>
         </is>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>41.72</t>
+          <t>41.69</t>
         </is>
       </c>
       <c r="AP23" t="inlineStr">
         <is>
-          <t>-11.54</t>
+          <t>-18.69</t>
         </is>
       </c>
       <c r="AQ23" t="inlineStr">
         <is>
-          <t>-0.74</t>
+          <t>-0.83</t>
         </is>
       </c>
       <c r="AR23" t="inlineStr">
         <is>
-          <t>-0.66</t>
+          <t>-0.70</t>
         </is>
       </c>
       <c r="AS23" t="inlineStr">
@@ -10250,56 +10250,56 @@
       </c>
       <c r="AT23" t="inlineStr">
         <is>
-          <t>-124.74</t>
+          <t>-125.95</t>
         </is>
       </c>
       <c r="AU23" t="inlineStr">
         <is>
-          <t>2025/10/23</t>
+          <t>2025/11/25</t>
         </is>
       </c>
       <c r="AV23" t="inlineStr">
         <is>
-          <t>150693340.205165</t>
+          <t>150562465.4441261</t>
         </is>
       </c>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>19337957.0</t>
+          <t>66861836.0</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>22560307.8</t>
+          <t>33260992.8</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr">
         <is>
-          <t>22524902.5</t>
+          <t>27368625.9</t>
         </is>
       </c>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>28140249.02</t>
+          <t>28716017.48</t>
         </is>
       </c>
       <c r="BA23" t="inlineStr">
         <is>
-          <t>35405</t>
+          <t>5892366</t>
         </is>
       </c>
       <c r="BB23" t="inlineStr">
         <is>
-          <t>-1261688.726998104</t>
+          <t>-695324.269555022</t>
         </is>
       </c>
       <c r="BC23" t="inlineStr">
         <is>
-          <t>-977116.8664098568</t>
+          <t>2419680.246381927</t>
         </is>
       </c>
       <c r="BD23" t="n">
-        <v>19337957</v>
+        <v>66861836</v>
       </c>
       <c r="BE23" t="inlineStr">
         <is>
@@ -10318,7 +10318,7 @@
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>-6.87</t>
+          <t>-9.28</t>
         </is>
       </c>
       <c r="BI23" t="inlineStr">
@@ -10363,7 +10363,7 @@
       </c>
       <c r="BQ23" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR23" t="inlineStr">
@@ -10373,12 +10373,12 @@
       </c>
       <c r="BS23" t="inlineStr">
         <is>
-          <t>1.06</t>
+          <t>1.04</t>
         </is>
       </c>
       <c r="BT23" t="inlineStr">
         <is>
-          <t>6.78</t>
+          <t>6.56</t>
         </is>
       </c>
       <c r="BU23" t="inlineStr">
@@ -10388,7 +10388,7 @@
       </c>
       <c r="BV23" t="inlineStr">
         <is>
-          <t>15.25</t>
+          <t>15.74</t>
         </is>
       </c>
       <c r="BW23" t="inlineStr">
@@ -10403,12 +10403,12 @@
       </c>
       <c r="BY23" t="inlineStr">
         <is>
-          <t>28.89</t>
+          <t>29.15</t>
         </is>
       </c>
       <c r="BZ23" t="inlineStr">
         <is>
-          <t>11850</t>
+          <t>12236</t>
         </is>
       </c>
       <c r="CA23" t="inlineStr">
@@ -10428,22 +10428,22 @@
       </c>
       <c r="CD23" t="inlineStr">
         <is>
-          <t>38.95</t>
+          <t>38.45</t>
         </is>
       </c>
       <c r="CE23" t="inlineStr">
         <is>
-          <t>39.3</t>
+          <t>38.75</t>
         </is>
       </c>
       <c r="CF23" t="inlineStr">
         <is>
-          <t>38.55</t>
+          <t>37.35</t>
         </is>
       </c>
       <c r="CG23" t="inlineStr">
         <is>
-          <t>38.65</t>
+          <t>37.65</t>
         </is>
       </c>
       <c r="CH23" t="inlineStr">

--- a/Result/checksun_type/塔架.xlsx
+++ b/Result/checksun_type/塔架.xlsx
@@ -883,127 +883,127 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
+          <t>2.48</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>885.355</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>142.5</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>-2.05</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>-37.74</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>-65.0</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>2025-06-04 00:00:00</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>2025-06-30 00:00:00</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>2025-05-09 00:00:00</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>2025-05-23 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>199.0</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>237.0</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>181.0</t>
+        </is>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>178.0</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>-39.87</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>11.80</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>2025-11-26</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>3.66</t>
+        </is>
+      </c>
+      <c r="AA2" t="inlineStr">
+        <is>
           <t>0.36</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>1070.548</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>139.0</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>0.32</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>-30.56</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>-65.0</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>2025-06-04 00:00:00</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>2025-06-30 00:00:00</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>2025-05-09 00:00:00</t>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr">
-        <is>
-          <t>2025-05-23 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q2" t="inlineStr">
-        <is>
-          <t>199.0</t>
-        </is>
-      </c>
-      <c r="R2" t="inlineStr">
-        <is>
-          <t>237.0</t>
-        </is>
-      </c>
-      <c r="S2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T2" t="inlineStr">
-        <is>
-          <t>181.0</t>
-        </is>
-      </c>
-      <c r="U2" t="inlineStr">
-        <is>
-          <t>178.0</t>
-        </is>
-      </c>
-      <c r="V2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>-41.35</t>
-        </is>
-      </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>11.80</t>
-        </is>
-      </c>
-      <c r="Y2" t="inlineStr">
-        <is>
-          <t>2025-11-25</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>4.43</t>
-        </is>
-      </c>
-      <c r="AA2" t="inlineStr">
-        <is>
-          <t>-0.71</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1014,37 +1014,37 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>1071</t>
+          <t>885</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>44.74</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>36.84</t>
+          <t>62.28</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>2.51</t>
+          <t>3.26</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>-6.71</t>
+          <t>-4.63</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>-8.49</t>
+          <t>-8.6</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
@@ -1054,37 +1054,37 @@
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>135.6</t>
+          <t>138.0</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>145.35</t>
+          <t>144.7</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>158.83</t>
+          <t>158.31</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>169.32</t>
+          <t>168.75</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>-0.61</t>
+          <t>7.75</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>-7.33</t>
+          <t>-6.60</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>-7.29</t>
+          <t>-7.15</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -1094,56 +1094,56 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-129.29</t>
+          <t>-128.73</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
         <is>
-          <t>2025/09/19</t>
+          <t>2025/11/26</t>
         </is>
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>1691092068.840258</t>
+          <t>1688943454.118026</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>149355643.0</t>
+          <t>126140252.0</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>199168061.0</t>
+          <t>179646773.6</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>286806442.7</t>
+          <t>288541776.1</t>
         </is>
       </c>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>252995092.08</t>
+          <t>249860076.6</t>
         </is>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>-87638381</t>
+          <t>-108895002</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>5491459.465344865</t>
+          <t>2645308.141590643</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>-5288395.852468729</t>
+          <t>-13008524.13905758</t>
         </is>
       </c>
       <c r="BD2" t="n">
-        <v>149355643</v>
+        <v>126140252</v>
       </c>
       <c r="BE2" t="inlineStr">
         <is>
@@ -1162,7 +1162,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>-22.78</t>
+          <t>-20.83</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
@@ -1207,22 +1207,22 @@
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>3.20</t>
+          <t>3.28</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
         <is>
-          <t>2.99</t>
+          <t>2.92</t>
         </is>
       </c>
       <c r="BU2" t="inlineStr">
@@ -1232,7 +1232,7 @@
       </c>
       <c r="BV2" t="inlineStr">
         <is>
-          <t>26.13</t>
+          <t>26.79</t>
         </is>
       </c>
       <c r="BW2" t="inlineStr">
@@ -1247,12 +1247,12 @@
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>29.15</t>
+          <t>29.71</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>34319</t>
+          <t>35183</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
@@ -1272,22 +1272,22 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>139.5</t>
+          <t>141.0</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
+          <t>143.5</t>
+        </is>
+      </c>
+      <c r="CF2" t="inlineStr">
+        <is>
           <t>141.0</t>
         </is>
       </c>
-      <c r="CF2" t="inlineStr">
-        <is>
-          <t>138.0</t>
-        </is>
-      </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>139.0</t>
+          <t>142.5</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
@@ -1302,7 +1302,7 @@
       </c>
       <c r="CJ2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1319,12 +1319,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2.56</t>
+          <t>0.36</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1721.237</t>
+          <t>1070.548</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1334,7 +1334,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>138.5</t>
+          <t>139.0</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1344,17 +1344,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>0.36</t>
+          <t>2.46</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>0.32</t>
+          <t>-2.05</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>-13.08</t>
+          <t>-30.56</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1419,7 +1419,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-41.56</t>
+          <t>-41.35</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1429,17 +1429,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>7.12</t>
+          <t>4.43</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>1.87</t>
+          <t>-0.71</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1450,77 +1450,77 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>1071</t>
+          <t>885</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>42.11</t>
+          <t>44.74</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>29.62</t>
+          <t>36.84</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>3.44</t>
+          <t>2.51</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>-8.46</t>
+          <t>-6.71</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-8.28</t>
+          <t>-8.49</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>-6.17</t>
+          <t>-6.19</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>133.9</t>
+          <t>135.6</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>146.28</t>
+          <t>145.35</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>159.48</t>
+          <t>158.83</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>169.96</t>
+          <t>169.32</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>-7.31</t>
+          <t>-0.61</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>-7.81</t>
+          <t>-7.33</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>-7.28</t>
+          <t>-7.29</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1530,56 +1530,56 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-129.24</t>
+          <t>-129.29</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
         <is>
-          <t>2025/09/19</t>
+          <t>2025/11/26</t>
         </is>
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>1691092068.840258</t>
+          <t>1688943454.118026</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>236429825.0</t>
+          <t>149355643.0</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>243968869.0</t>
+          <t>199168061.0</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>280669574.0</t>
+          <t>286806442.7</t>
         </is>
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>255272113.08</t>
+          <t>252995092.08</t>
         </is>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>-36700705</t>
+          <t>-87638381</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>7451433.159492791</t>
+          <t>5491459.465344865</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>3441866.801674962</t>
+          <t>-5288395.852468729</t>
         </is>
       </c>
       <c r="BD3" t="n">
-        <v>236429825</v>
+        <v>149355643</v>
       </c>
       <c r="BE3" t="inlineStr">
         <is>
@@ -1598,7 +1598,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>-23.06</t>
+          <t>-22.78</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
@@ -1643,7 +1643,7 @@
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;可能出現反轉訊號&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;3&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
@@ -1653,12 +1653,12 @@
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>3.19</t>
+          <t>3.20</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
         <is>
-          <t>2.99</t>
+          <t>2.92</t>
         </is>
       </c>
       <c r="BU3" t="inlineStr">
@@ -1668,7 +1668,7 @@
       </c>
       <c r="BV3" t="inlineStr">
         <is>
-          <t>26.13</t>
+          <t>26.79</t>
         </is>
       </c>
       <c r="BW3" t="inlineStr">
@@ -1683,12 +1683,12 @@
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>29.15</t>
+          <t>29.71</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
-          <t>34319</t>
+          <t>35183</t>
         </is>
       </c>
       <c r="CA3" t="inlineStr">
@@ -1708,22 +1708,22 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>136.5</t>
+          <t>139.5</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>139.5</t>
+          <t>141.0</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>135.0</t>
+          <t>138.0</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>138.5</t>
+          <t>139.0</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
@@ -1738,7 +1738,7 @@
       </c>
       <c r="CJ3" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1755,12 +1755,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>2.56</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>1302.953</t>
+          <t>1721.237</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1770,7 +1770,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>135.0</t>
+          <t>138.5</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1780,17 +1780,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2.88</t>
+          <t>2.81</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>0.32</t>
+          <t>-2.05</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>12.02</t>
+          <t>-13.08</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1855,7 +1855,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-43.04</t>
+          <t>-41.56</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1865,17 +1865,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>5.39</t>
+          <t>7.12</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>3.05</t>
+          <t>1.87</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1886,77 +1886,77 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>1071</t>
+          <t>885</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>23.68</t>
+          <t>42.11</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>15.59</t>
+          <t>29.62</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>1.58</t>
+          <t>3.44</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>-9.76</t>
+          <t>-8.46</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>-8.05</t>
+          <t>-8.28</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>-6.11</t>
+          <t>-6.17</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>132.9</t>
+          <t>133.9</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>147.28</t>
+          <t>146.28</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>160.17</t>
+          <t>159.48</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>170.59</t>
+          <t>169.96</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>-15.53</t>
+          <t>-7.31</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>-8.25</t>
+          <t>-7.81</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>-7.14</t>
+          <t>-7.28</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1966,56 +1966,56 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-128.71</t>
+          <t>-129.24</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
         <is>
-          <t>2025/09/19</t>
+          <t>2025/11/26</t>
         </is>
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>1691092068.840258</t>
+          <t>1688943454.118026</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>173429988.0</t>
+          <t>236429825.0</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>305348589.0</t>
+          <t>243968869.0</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>272591978.0</t>
+          <t>280669574.0</t>
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>254388028.92</t>
+          <t>255272113.08</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>32756611</t>
+          <t>-36700705</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>8180445.224550578</t>
+          <t>7451433.159492791</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>6461370.136106104</t>
+          <t>3441866.801674962</t>
         </is>
       </c>
       <c r="BD4" t="n">
-        <v>173429988</v>
+        <v>236429825</v>
       </c>
       <c r="BE4" t="inlineStr">
         <is>
@@ -2034,7 +2034,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>-25.00</t>
+          <t>-23.06</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
@@ -2079,7 +2079,7 @@
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;可能出現反轉訊號&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;3&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
@@ -2089,12 +2089,12 @@
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>3.11</t>
+          <t>3.19</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
         <is>
-          <t>2.99</t>
+          <t>2.92</t>
         </is>
       </c>
       <c r="BU4" t="inlineStr">
@@ -2104,7 +2104,7 @@
       </c>
       <c r="BV4" t="inlineStr">
         <is>
-          <t>26.13</t>
+          <t>26.79</t>
         </is>
       </c>
       <c r="BW4" t="inlineStr">
@@ -2119,12 +2119,12 @@
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>29.15</t>
+          <t>29.71</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
-          <t>34319</t>
+          <t>35183</t>
         </is>
       </c>
       <c r="CA4" t="inlineStr">
@@ -2144,22 +2144,22 @@
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>132.5</t>
+          <t>136.5</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
+          <t>139.5</t>
+        </is>
+      </c>
+      <c r="CF4" t="inlineStr">
+        <is>
           <t>135.0</t>
         </is>
       </c>
-      <c r="CF4" t="inlineStr">
-        <is>
-          <t>131.0</t>
-        </is>
-      </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>135.0</t>
+          <t>138.5</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
@@ -2174,7 +2174,7 @@
       </c>
       <c r="CJ4" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -2191,12 +2191,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>3.41</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>1595.31</t>
+          <t>1302.953</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2216,17 +2216,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2.88</t>
+          <t>5.26</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>0.32</t>
+          <t>-2.05</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>53.45</t>
+          <t>12.02</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2301,17 +2301,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>6.60</t>
+          <t>5.39</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>1.92</t>
+          <t>3.05</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2322,77 +2322,77 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>1071</t>
+          <t>885</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>23.08</t>
+          <t>23.68</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>7.69</t>
+          <t>15.59</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>1.20</t>
+          <t>1.58</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>-10.06</t>
+          <t>-9.76</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>-7.84</t>
+          <t>-8.05</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>-6.04</t>
+          <t>-6.11</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>133.4</t>
+          <t>132.9</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>148.32</t>
+          <t>147.28</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>160.95</t>
+          <t>160.17</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>171.29</t>
+          <t>170.59</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>-21.52</t>
+          <t>-15.53</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>-8.35</t>
+          <t>-8.25</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>-6.87</t>
+          <t>-7.14</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -2402,56 +2402,56 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-127.59</t>
+          <t>-128.71</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
         <is>
-          <t>2025/09/19</t>
+          <t>2025/11/26</t>
         </is>
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>1691092068.840258</t>
+          <t>1688943454.118026</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>212878160.0</t>
+          <t>173429988.0</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>421450515.0</t>
+          <t>305348589.0</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>274650710.4</t>
+          <t>272591978.0</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>254522728.7</t>
+          <t>254388028.92</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>146799804</t>
+          <t>32756611</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>8493004.331540482</t>
+          <t>8180445.224550578</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>17294165.64471823</t>
+          <t>6461370.136106104</t>
         </is>
       </c>
       <c r="BD5" t="n">
-        <v>212878160</v>
+        <v>173429988</v>
       </c>
       <c r="BE5" t="inlineStr">
         <is>
@@ -2515,12 +2515,12 @@
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;可能出現反轉訊號&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;3&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS5" t="inlineStr">
@@ -2530,7 +2530,7 @@
       </c>
       <c r="BT5" t="inlineStr">
         <is>
-          <t>2.99</t>
+          <t>2.92</t>
         </is>
       </c>
       <c r="BU5" t="inlineStr">
@@ -2540,7 +2540,7 @@
       </c>
       <c r="BV5" t="inlineStr">
         <is>
-          <t>26.13</t>
+          <t>26.79</t>
         </is>
       </c>
       <c r="BW5" t="inlineStr">
@@ -2555,12 +2555,12 @@
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>29.15</t>
+          <t>29.71</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
-          <t>34319</t>
+          <t>35183</t>
         </is>
       </c>
       <c r="CA5" t="inlineStr">
@@ -2580,17 +2580,17 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>132.0</t>
+          <t>132.5</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>136.0</t>
+          <t>135.0</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>131.5</t>
+          <t>131.0</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
@@ -2610,7 +2610,7 @@
       </c>
       <c r="CJ5" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -2627,12 +2627,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>3.41</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>1712.06</t>
+          <t>1595.31</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2642,7 +2642,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>130.5</t>
+          <t>135.0</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2652,17 +2652,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>6.12</t>
+          <t>5.26</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>0.32</t>
+          <t>-2.05</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>50.94</t>
+          <t>53.45</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2727,7 +2727,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-44.94</t>
+          <t>-43.04</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2737,17 +2737,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>7.08</t>
+          <t>6.60</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>-1.14</t>
+          <t>1.92</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2758,77 +2758,77 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>1071</t>
+          <t>885</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>23.08</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>7.69</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>-4.26</t>
+          <t>1.20</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>-8.89</t>
+          <t>-10.06</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>-7.5</t>
+          <t>-7.84</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>-5.97</t>
+          <t>-6.04</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>136.3</t>
+          <t>133.4</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>149.6</t>
+          <t>148.32</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>161.73</t>
+          <t>160.95</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>171.99</t>
+          <t>171.29</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>-28.35</t>
+          <t>-21.52</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>-8.34</t>
+          <t>-8.35</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>-6.50</t>
+          <t>-6.87</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -2838,56 +2838,56 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-126.11</t>
+          <t>-127.59</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
         <is>
-          <t>2025/09/19</t>
+          <t>2025/11/26</t>
         </is>
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>1691092068.840258</t>
+          <t>1688943454.118026</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>223746689.0</t>
+          <t>212878160.0</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>397436778.6</t>
+          <t>421450515.0</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>263301806.5</t>
+          <t>274650710.4</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>254911229.58</t>
+          <t>254522728.7</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>134134972</t>
+          <t>146799804</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>6892793.183689982</t>
+          <t>8493004.331540482</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>27925349.16970986</t>
+          <t>17294165.64471823</t>
         </is>
       </c>
       <c r="BD6" t="n">
-        <v>223746689</v>
+        <v>212878160</v>
       </c>
       <c r="BE6" t="inlineStr">
         <is>
@@ -2906,7 +2906,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>-27.50</t>
+          <t>-25.00</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
@@ -2951,22 +2951,22 @@
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;可能出現反轉訊號&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;3&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
         <is>
-          <t>價漲量縮</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>3.01</t>
+          <t>3.11</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
         <is>
-          <t>2.99</t>
+          <t>2.92</t>
         </is>
       </c>
       <c r="BU6" t="inlineStr">
@@ -2976,7 +2976,7 @@
       </c>
       <c r="BV6" t="inlineStr">
         <is>
-          <t>26.13</t>
+          <t>26.79</t>
         </is>
       </c>
       <c r="BW6" t="inlineStr">
@@ -2991,12 +2991,12 @@
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>29.15</t>
+          <t>29.71</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
         <is>
-          <t>34319</t>
+          <t>35183</t>
         </is>
       </c>
       <c r="CA6" t="inlineStr">
@@ -3016,22 +3016,22 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>131.0</t>
+          <t>132.0</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>133.5</t>
+          <t>136.0</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>129.0</t>
+          <t>131.5</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>130.5</t>
+          <t>135.0</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
@@ -3046,7 +3046,7 @@
       </c>
       <c r="CJ6" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -3063,12 +3063,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>-2.26</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2844.986</t>
+          <t>1712.06</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3088,17 +3088,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>6.12</t>
+          <t>8.42</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>0.32</t>
+          <t>-2.05</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>48.25</t>
+          <t>50.94</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3173,17 +3173,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>11.77</t>
+          <t>7.08</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>-2.29</t>
+          <t>-1.14</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3194,12 +3194,12 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>1071</t>
+          <t>885</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
@@ -3214,57 +3214,57 @@
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>-6.85</t>
+          <t>-4.26</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>-7.30</t>
+          <t>-8.89</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>-7.05</t>
+          <t>-7.5</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>-5.89</t>
+          <t>-5.97</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>140.1</t>
+          <t>136.3</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>151.12</t>
+          <t>149.6</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>162.59</t>
+          <t>161.73</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>172.77</t>
+          <t>171.99</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>-28.43</t>
+          <t>-28.35</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>-7.75</t>
+          <t>-8.34</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>-6.04</t>
+          <t>-6.50</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -3274,56 +3274,56 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-124.26</t>
+          <t>-126.11</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
         <is>
-          <t>2025/09/19</t>
+          <t>2025/11/26</t>
         </is>
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>1691092068.840258</t>
+          <t>1688943454.118026</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>373359683.0</t>
+          <t>223746689.0</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>374444824.4</t>
+          <t>397436778.6</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>252575891.8</t>
+          <t>263301806.5</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>255257682.72</t>
+          <t>254911229.58</t>
         </is>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>121868932</t>
+          <t>134134972</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>3068692.09532273</t>
+          <t>6892793.183689982</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>40950935.056494</t>
+          <t>27925349.16970986</t>
         </is>
       </c>
       <c r="BD7" t="n">
-        <v>373359683</v>
+        <v>223746689</v>
       </c>
       <c r="BE7" t="inlineStr">
         <is>
@@ -3387,12 +3387,12 @@
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價漲量縮</t>
         </is>
       </c>
       <c r="BS7" t="inlineStr">
@@ -3402,7 +3402,7 @@
       </c>
       <c r="BT7" t="inlineStr">
         <is>
-          <t>2.99</t>
+          <t>2.92</t>
         </is>
       </c>
       <c r="BU7" t="inlineStr">
@@ -3412,7 +3412,7 @@
       </c>
       <c r="BV7" t="inlineStr">
         <is>
-          <t>26.13</t>
+          <t>26.79</t>
         </is>
       </c>
       <c r="BW7" t="inlineStr">
@@ -3427,12 +3427,12 @@
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>29.15</t>
+          <t>29.71</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
         <is>
-          <t>34319</t>
+          <t>35183</t>
         </is>
       </c>
       <c r="CA7" t="inlineStr">
@@ -3452,17 +3452,17 @@
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>133.0</t>
+          <t>131.0</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>134.5</t>
+          <t>133.5</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>129.5</t>
+          <t>129.0</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
@@ -3482,7 +3482,7 @@
       </c>
       <c r="CJ7" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -3499,12 +3499,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>-2.96</t>
+          <t>-2.26</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>4003.393</t>
+          <t>2844.986</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3514,7 +3514,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>133.5</t>
+          <t>130.5</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3524,17 +3524,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>3.96</t>
+          <t>8.42</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>0.32</t>
+          <t>-2.05</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>36.89</t>
+          <t>48.25</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3599,7 +3599,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-43.67</t>
+          <t>-44.94</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3609,17 +3609,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>16.56</t>
+          <t>11.77</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>-5.24</t>
+          <t>-2.29</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3630,12 +3630,12 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>1071</t>
+          <t>885</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
@@ -3650,57 +3650,57 @@
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>-7.23</t>
+          <t>-6.85</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>-5.73</t>
+          <t>-7.30</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>-6.6</t>
+          <t>-7.05</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>-5.82</t>
+          <t>-5.89</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>143.9</t>
+          <t>140.1</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>152.65</t>
+          <t>151.12</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>163.44</t>
+          <t>162.59</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>173.54</t>
+          <t>172.77</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>-22.90</t>
+          <t>-28.43</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>-6.89</t>
+          <t>-7.75</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>-5.61</t>
+          <t>-6.04</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -3710,56 +3710,56 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-122.53</t>
+          <t>-124.26</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
         <is>
-          <t>2025/09/19</t>
+          <t>2025/11/26</t>
         </is>
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>1691092068.840258</t>
+          <t>1688943454.118026</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>543328425.0</t>
+          <t>373359683.0</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>317370279.0</t>
+          <t>374444824.4</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>231842549.9</t>
+          <t>252575891.8</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>254515985.98</t>
+          <t>255257682.72</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>85527729</t>
+          <t>121868932</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>-3818988.443072045</t>
+          <t>3068692.09532273</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>42066417.85702515</t>
+          <t>40950935.056494</t>
         </is>
       </c>
       <c r="BD8" t="n">
-        <v>543328425</v>
+        <v>373359683</v>
       </c>
       <c r="BE8" t="inlineStr">
         <is>
@@ -3778,7 +3778,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>-25.83</t>
+          <t>-27.50</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
@@ -3823,7 +3823,7 @@
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;衝高回落,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
@@ -3833,12 +3833,12 @@
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>3.08</t>
+          <t>3.01</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
         <is>
-          <t>2.99</t>
+          <t>2.92</t>
         </is>
       </c>
       <c r="BU8" t="inlineStr">
@@ -3848,7 +3848,7 @@
       </c>
       <c r="BV8" t="inlineStr">
         <is>
-          <t>26.13</t>
+          <t>26.79</t>
         </is>
       </c>
       <c r="BW8" t="inlineStr">
@@ -3863,12 +3863,12 @@
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>29.15</t>
+          <t>29.71</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
         <is>
-          <t>34319</t>
+          <t>35183</t>
         </is>
       </c>
       <c r="CA8" t="inlineStr">
@@ -3888,22 +3888,22 @@
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>135.0</t>
+          <t>133.0</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>141.5</t>
+          <t>134.5</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>132.5</t>
+          <t>129.5</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>133.5</t>
+          <t>130.5</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
@@ -3918,7 +3918,7 @@
       </c>
       <c r="CJ8" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -3935,12 +3935,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>-8.16</t>
+          <t>-2.96</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>5388.546</t>
+          <t>4003.393</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3950,7 +3950,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>137.5</t>
+          <t>133.5</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3960,17 +3960,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>1.08</t>
+          <t>6.32</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>0.32</t>
+          <t>-2.05</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>18.56</t>
+          <t>36.89</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -4035,7 +4035,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-41.98</t>
+          <t>-43.67</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4045,17 +4045,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>22.28</t>
+          <t>16.56</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>-5.06</t>
+          <t>-5.24</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4066,12 +4066,12 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>1071</t>
+          <t>885</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
@@ -4086,57 +4086,57 @@
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>-6.59</t>
+          <t>-7.23</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>-4.57</t>
+          <t>-5.73</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>-6.11</t>
+          <t>-6.6</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>-5.70</t>
+          <t>-5.82</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>147.2</t>
+          <t>143.9</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>154.25</t>
+          <t>152.65</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>164.29</t>
+          <t>163.44</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>174.21</t>
+          <t>173.54</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>-13.45</t>
+          <t>-22.90</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>-6.00</t>
+          <t>-6.89</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>-5.29</t>
+          <t>-5.61</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -4146,56 +4146,56 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-121.24</t>
+          <t>-122.53</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
         <is>
-          <t>2025/09/19</t>
+          <t>2025/11/26</t>
         </is>
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>1691092068.840258</t>
+          <t>1688943454.118026</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>753939618.0</t>
+          <t>543328425.0</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>239835367.0</t>
+          <t>317370279.0</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>202283159.5</t>
+          <t>231842549.9</t>
         </is>
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>250790390.86</t>
+          <t>254515985.98</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>37552207</t>
+          <t>85527729</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>-12161789.58854426</t>
+          <t>-3818988.443072045</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>23946656.00574735</t>
+          <t>42066417.85702515</t>
         </is>
       </c>
       <c r="BD9" t="n">
-        <v>753939618</v>
+        <v>543328425</v>
       </c>
       <c r="BE9" t="inlineStr">
         <is>
@@ -4214,7 +4214,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>-23.61</t>
+          <t>-25.83</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
@@ -4259,22 +4259,22 @@
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;衝高回落,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
         <is>
-          <t>價跌量增</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>3.17</t>
+          <t>3.08</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
         <is>
-          <t>2.99</t>
+          <t>2.92</t>
         </is>
       </c>
       <c r="BU9" t="inlineStr">
@@ -4284,7 +4284,7 @@
       </c>
       <c r="BV9" t="inlineStr">
         <is>
-          <t>26.13</t>
+          <t>26.79</t>
         </is>
       </c>
       <c r="BW9" t="inlineStr">
@@ -4299,12 +4299,12 @@
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>29.15</t>
+          <t>29.71</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
         <is>
-          <t>34319</t>
+          <t>35183</t>
         </is>
       </c>
       <c r="CA9" t="inlineStr">
@@ -4324,22 +4324,22 @@
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>147.0</t>
+          <t>135.0</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>147.0</t>
+          <t>141.5</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>135.0</t>
+          <t>132.5</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>137.5</t>
+          <t>133.5</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
@@ -4354,7 +4354,7 @@
       </c>
       <c r="CJ9" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -4371,12 +4371,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-8.16</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>617.888</t>
+          <t>5388.546</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4386,7 +4386,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>149.5</t>
+          <t>137.5</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4396,17 +4396,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-7.55</t>
+          <t>3.51</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>0.32</t>
+          <t>-2.05</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>-14.19</t>
+          <t>18.56</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4471,7 +4471,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-36.92</t>
+          <t>-41.98</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4481,17 +4481,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>2.56</t>
+          <t>22.28</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>-1.34</t>
+          <t>-5.06</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4502,12 +4502,12 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>1071</t>
+          <t>885</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
@@ -4522,57 +4522,57 @@
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>-0.07</t>
+          <t>-6.59</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>-3.96</t>
+          <t>-4.57</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>-5.65</t>
+          <t>-6.11</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>-5.63</t>
+          <t>-5.70</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>149.6</t>
+          <t>147.2</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>155.78</t>
+          <t>154.25</t>
         </is>
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>165.1</t>
+          <t>164.29</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>174.95</t>
+          <t>174.21</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>-1.33</t>
+          <t>-13.45</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>-5.18</t>
+          <t>-6.00</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>-5.11</t>
+          <t>-5.29</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -4582,56 +4582,56 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-120.53</t>
+          <t>-121.24</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
         <is>
-          <t>2025/09/19</t>
+          <t>2025/11/26</t>
         </is>
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>1691092068.840258</t>
+          <t>1688943454.118026</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>92809478.0</t>
+          <t>753939618.0</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>127850905.8</t>
+          <t>239835367.0</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>148995940.1</t>
+          <t>202283159.5</t>
         </is>
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>248204610.78</t>
+          <t>250790390.86</t>
         </is>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>-21145034</t>
+          <t>37552207</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>-18726961.5147791</t>
+          <t>-12161789.58854426</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>-25359440.74628332</t>
+          <t>23946656.00574735</t>
         </is>
       </c>
       <c r="BD10" t="n">
-        <v>92809478</v>
+        <v>753939618</v>
       </c>
       <c r="BE10" t="inlineStr">
         <is>
@@ -4650,7 +4650,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>-16.94</t>
+          <t>-23.61</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
@@ -4700,17 +4700,17 @@
       </c>
       <c r="BR10" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價跌量增</t>
         </is>
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>3.44</t>
+          <t>3.17</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
         <is>
-          <t>2.99</t>
+          <t>2.92</t>
         </is>
       </c>
       <c r="BU10" t="inlineStr">
@@ -4720,7 +4720,7 @@
       </c>
       <c r="BV10" t="inlineStr">
         <is>
-          <t>26.13</t>
+          <t>26.79</t>
         </is>
       </c>
       <c r="BW10" t="inlineStr">
@@ -4735,12 +4735,12 @@
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>29.15</t>
+          <t>29.71</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
         <is>
-          <t>34319</t>
+          <t>35183</t>
         </is>
       </c>
       <c r="CA10" t="inlineStr">
@@ -4760,22 +4760,22 @@
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>150.0</t>
+          <t>147.0</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>151.5</t>
+          <t>147.0</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>149.5</t>
+          <t>135.0</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>149.5</t>
+          <t>137.5</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
@@ -4790,7 +4790,7 @@
       </c>
       <c r="CJ10" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -4812,7 +4812,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>723.545</t>
+          <t>617.888</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4832,17 +4832,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-7.55</t>
+          <t>-4.91</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>0.32</t>
+          <t>-2.05</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>-23.11</t>
+          <t>-14.19</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4917,17 +4917,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>2.99</t>
+          <t>2.56</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>-1.67</t>
+          <t>-1.34</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4938,12 +4938,12 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>1071</t>
+          <t>885</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
@@ -4953,62 +4953,62 @@
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>2.22</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>-0.47</t>
+          <t>-0.07</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>-4.07</t>
+          <t>-3.96</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>-5.55</t>
+          <t>-5.65</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>-5.58</t>
+          <t>-5.63</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>150.2</t>
+          <t>149.6</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>156.57</t>
+          <t>155.78</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>165.78</t>
+          <t>165.1</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>175.58</t>
+          <t>174.95</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>-3.60</t>
+          <t>-1.33</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>-5.28</t>
+          <t>-5.18</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>-5.09</t>
+          <t>-5.11</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -5018,56 +5018,56 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-120.46</t>
+          <t>-120.53</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
         <is>
-          <t>2025/09/19</t>
+          <t>2025/11/26</t>
         </is>
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>1691092068.840258</t>
+          <t>1688943454.118026</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>108786918.0</t>
+          <t>92809478.0</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>129166834.4</t>
+          <t>127850905.8</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>167987433.4</t>
+          <t>148995940.1</t>
         </is>
       </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>261232164.76</t>
+          <t>248204610.78</t>
         </is>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>-38820599</t>
+          <t>-21145034</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>-17521056.19996015</t>
+          <t>-18726961.5147791</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>-24055655.36538848</t>
+          <t>-25359440.74628332</t>
         </is>
       </c>
       <c r="BD11" t="n">
-        <v>108786918</v>
+        <v>92809478</v>
       </c>
       <c r="BE11" t="inlineStr">
         <is>
@@ -5131,7 +5131,7 @@
       </c>
       <c r="BQ11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR11" t="inlineStr">
@@ -5146,7 +5146,7 @@
       </c>
       <c r="BT11" t="inlineStr">
         <is>
-          <t>2.99</t>
+          <t>2.92</t>
         </is>
       </c>
       <c r="BU11" t="inlineStr">
@@ -5156,7 +5156,7 @@
       </c>
       <c r="BV11" t="inlineStr">
         <is>
-          <t>26.13</t>
+          <t>26.79</t>
         </is>
       </c>
       <c r="BW11" t="inlineStr">
@@ -5171,12 +5171,12 @@
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>29.15</t>
+          <t>29.71</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
         <is>
-          <t>34319</t>
+          <t>35183</t>
         </is>
       </c>
       <c r="CA11" t="inlineStr">
@@ -5196,17 +5196,17 @@
       </c>
       <c r="CD11" t="inlineStr">
         <is>
+          <t>150.0</t>
+        </is>
+      </c>
+      <c r="CE11" t="inlineStr">
+        <is>
           <t>151.5</t>
         </is>
       </c>
-      <c r="CE11" t="inlineStr">
-        <is>
-          <t>152.5</t>
-        </is>
-      </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>149.0</t>
+          <t>149.5</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
@@ -5226,7 +5226,7 @@
       </c>
       <c r="CJ11" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -5243,12 +5243,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>-0.33</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>586.018</t>
+          <t>723.545</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5268,17 +5268,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-7.55</t>
+          <t>-4.91</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>0.32</t>
+          <t>-2.05</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>-28.30</t>
+          <t>-23.11</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5353,17 +5353,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>2.42</t>
+          <t>2.99</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>-1.34</t>
+          <t>-1.67</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5374,12 +5374,12 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>1071</t>
+          <t>885</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
@@ -5394,57 +5394,57 @@
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>-0.86</t>
+          <t>-0.47</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>-4.25</t>
+          <t>-4.07</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>-5.43</t>
+          <t>-5.55</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>-5.49</t>
+          <t>-5.58</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>150.8</t>
+          <t>150.2</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>157.5</t>
+          <t>156.57</t>
         </is>
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>166.55</t>
+          <t>165.78</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>176.23</t>
+          <t>175.58</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>-5.51</t>
+          <t>-3.60</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>-5.32</t>
+          <t>-5.28</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>-5.05</t>
+          <t>-5.09</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
@@ -5454,56 +5454,56 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-120.28</t>
+          <t>-120.46</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
         <is>
-          <t>2025/09/19</t>
+          <t>2025/11/26</t>
         </is>
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>1691092068.840258</t>
+          <t>1688943454.118026</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>87986956.0</t>
+          <t>108786918.0</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>130706959.2</t>
+          <t>129166834.4</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>182292868.5</t>
+          <t>167987433.4</t>
         </is>
       </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>265109106.98</t>
+          <t>261232164.76</t>
         </is>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>-51585909</t>
+          <t>-38820599</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>-16332947.26079137</t>
+          <t>-17521056.19996015</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>-23045842.8439177</t>
+          <t>-24055655.36538848</t>
         </is>
       </c>
       <c r="BD12" t="n">
-        <v>87986956</v>
+        <v>108786918</v>
       </c>
       <c r="BE12" t="inlineStr">
         <is>
@@ -5567,7 +5567,7 @@
       </c>
       <c r="BQ12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR12" t="inlineStr">
@@ -5582,7 +5582,7 @@
       </c>
       <c r="BT12" t="inlineStr">
         <is>
-          <t>2.99</t>
+          <t>2.92</t>
         </is>
       </c>
       <c r="BU12" t="inlineStr">
@@ -5592,7 +5592,7 @@
       </c>
       <c r="BV12" t="inlineStr">
         <is>
-          <t>26.13</t>
+          <t>26.79</t>
         </is>
       </c>
       <c r="BW12" t="inlineStr">
@@ -5607,12 +5607,12 @@
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>29.15</t>
+          <t>29.71</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
         <is>
-          <t>34319</t>
+          <t>35183</t>
         </is>
       </c>
       <c r="CA12" t="inlineStr">
@@ -5637,19 +5637,19 @@
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>151.5</t>
+          <t>152.5</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
+          <t>149.0</t>
+        </is>
+      </c>
+      <c r="CG12" t="inlineStr">
+        <is>
           <t>149.5</t>
         </is>
       </c>
-      <c r="CG12" t="inlineStr">
-        <is>
-          <t>149.5</t>
-        </is>
-      </c>
       <c r="CH12" t="inlineStr">
         <is>
           <t>43.4</t>
@@ -5662,7 +5662,7 @@
       </c>
       <c r="CJ12" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -5679,12 +5679,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>3.24</t>
+          <t>2.61</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>1043.085</t>
+          <t>914.803</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -5694,7 +5694,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>38.1</t>
+          <t>39.1</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -5709,12 +5709,12 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>0.63</t>
+          <t>0.91</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>41.43</t>
+          <t>35.32</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -5779,7 +5779,7 @@
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>-11.70</t>
+          <t>-9.39</t>
         </is>
       </c>
       <c r="X13" t="inlineStr">
@@ -5789,17 +5789,17 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>11.11</t>
+          <t>9.75</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2.71</t>
+          <t>1.47</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
@@ -5810,12 +5810,12 @@
       <c r="AC13" t="inlineStr"/>
       <c r="AD13" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
-          <t>1043</t>
+          <t>915</t>
         </is>
       </c>
       <c r="AF13" t="inlineStr">
@@ -5825,64 +5825,64 @@
       </c>
       <c r="AG13" t="inlineStr">
         <is>
-          <t>59.17</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>3.34</t>
+          <t>4.35</t>
         </is>
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>-3.27</t>
+          <t>-1.59</t>
         </is>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>-4.89</t>
+          <t>-4.88</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>-2.80</t>
+          <t>-2.87</t>
         </is>
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>36.87</t>
+          <t>37.47</t>
         </is>
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>38.11</t>
+          <t>38.08</t>
         </is>
       </c>
       <c r="AN13" t="inlineStr">
         <is>
-          <t>40.07</t>
+          <t>40.03</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>41.23</t>
+          <t>41.21</t>
         </is>
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>5.10</t>
+          <t>20.99</t>
         </is>
       </c>
       <c r="AQ13" t="inlineStr">
         <is>
+          <t>-0.75</t>
+        </is>
+      </c>
+      <c r="AR13" t="inlineStr">
+        <is>
           <t>-0.95</t>
         </is>
       </c>
-      <c r="AR13" t="inlineStr">
-        <is>
-          <t>-1.00</t>
-        </is>
-      </c>
       <c r="AS13" t="inlineStr">
         <is>
           <t>2.69</t>
@@ -5890,7 +5890,7 @@
       </c>
       <c r="AT13" t="inlineStr">
         <is>
-          <t>-137.15</t>
+          <t>-135.29</t>
         </is>
       </c>
       <c r="AU13" t="inlineStr">
@@ -5900,46 +5900,46 @@
       </c>
       <c r="AV13" t="inlineStr">
         <is>
-          <t>150562465.4441261</t>
+          <t>150423914.0772532</t>
         </is>
       </c>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>39561838.0</t>
+          <t>35810040.0</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>77102277.8</t>
+          <t>75499582.6</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>54515793.2</t>
+          <t>55792550.2</t>
         </is>
       </c>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>33864219.92</t>
+          <t>33454972.78</t>
         </is>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
-          <t>22586484</t>
+          <t>19707032</t>
         </is>
       </c>
       <c r="BB13" t="inlineStr">
         <is>
-          <t>4717477.979434728</t>
+          <t>5205041.104487866</t>
         </is>
       </c>
       <c r="BC13" t="inlineStr">
         <is>
-          <t>11730479.54280426</t>
+          <t>7886638.29228013</t>
         </is>
       </c>
       <c r="BD13" t="n">
-        <v>39561838</v>
+        <v>35810040</v>
       </c>
       <c r="BE13" t="inlineStr">
         <is>
@@ -5958,7 +5958,7 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>-8.19</t>
+          <t>-5.78</t>
         </is>
       </c>
       <c r="BI13" t="inlineStr">
@@ -5983,7 +5983,7 @@
       </c>
       <c r="BM13" t="inlineStr">
         <is>
-          <t>0.61</t>
+          <t>0.62</t>
         </is>
       </c>
       <c r="BN13" t="inlineStr">
@@ -6003,22 +6003,22 @@
       </c>
       <c r="BQ13" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR13" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS13" t="inlineStr">
         <is>
-          <t>1.05</t>
+          <t>1.08</t>
         </is>
       </c>
       <c r="BT13" t="inlineStr">
         <is>
-          <t>6.56</t>
+          <t>6.39</t>
         </is>
       </c>
       <c r="BU13" t="inlineStr">
@@ -6028,7 +6028,7 @@
       </c>
       <c r="BV13" t="inlineStr">
         <is>
-          <t>15.74</t>
+          <t>16.16</t>
         </is>
       </c>
       <c r="BW13" t="inlineStr">
@@ -6043,12 +6043,12 @@
       </c>
       <c r="BY13" t="inlineStr">
         <is>
-          <t>29.15</t>
+          <t>29.71</t>
         </is>
       </c>
       <c r="BZ13" t="inlineStr">
         <is>
-          <t>12236</t>
+          <t>12557</t>
         </is>
       </c>
       <c r="CA13" t="inlineStr">
@@ -6068,22 +6068,22 @@
       </c>
       <c r="CD13" t="inlineStr">
         <is>
-          <t>37.05</t>
+          <t>38.3</t>
         </is>
       </c>
       <c r="CE13" t="inlineStr">
         <is>
-          <t>38.2</t>
+          <t>39.5</t>
         </is>
       </c>
       <c r="CF13" t="inlineStr">
         <is>
-          <t>37.0</t>
+          <t>38.15</t>
         </is>
       </c>
       <c r="CG13" t="inlineStr">
         <is>
-          <t>38.1</t>
+          <t>39.1</t>
         </is>
       </c>
       <c r="CH13" t="inlineStr">
@@ -6115,12 +6115,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>0.14</t>
+          <t>3.24</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>6301.223</t>
+          <t>1043.085</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -6130,7 +6130,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>36.9</t>
+          <t>38.1</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -6140,17 +6140,17 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>3.15</t>
+          <t>2.56</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>0.63</t>
+          <t>0.91</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>29.52</t>
+          <t>41.43</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -6215,7 +6215,7 @@
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>-14.48</t>
+          <t>-11.70</t>
         </is>
       </c>
       <c r="X14" t="inlineStr">
@@ -6225,17 +6225,17 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>67.14</t>
+          <t>11.11</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>-1.63</t>
+          <t>2.71</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
@@ -6246,77 +6246,77 @@
       <c r="AC14" t="inlineStr"/>
       <c r="AD14" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
-          <t>1043</t>
+          <t>915</t>
         </is>
       </c>
       <c r="AF14" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG14" t="inlineStr">
         <is>
-          <t>29.75</t>
+          <t>59.17</t>
         </is>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>0.82</t>
+          <t>3.34</t>
         </is>
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>-4.24</t>
+          <t>-3.27</t>
         </is>
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>-4.85</t>
+          <t>-4.89</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>-2.68</t>
+          <t>-2.80</t>
         </is>
       </c>
       <c r="AL14" t="inlineStr">
         <is>
-          <t>36.60000000000001</t>
+          <t>36.87</t>
         </is>
       </c>
       <c r="AM14" t="inlineStr">
         <is>
-          <t>38.22</t>
+          <t>38.11</t>
         </is>
       </c>
       <c r="AN14" t="inlineStr">
         <is>
-          <t>40.17</t>
+          <t>40.07</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>41.28</t>
+          <t>41.23</t>
         </is>
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>-7.24</t>
+          <t>5.10</t>
         </is>
       </c>
       <c r="AQ14" t="inlineStr">
         <is>
-          <t>-1.08</t>
+          <t>-0.95</t>
         </is>
       </c>
       <c r="AR14" t="inlineStr">
         <is>
-          <t>-1.01</t>
+          <t>-1.00</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr">
@@ -6326,7 +6326,7 @@
       </c>
       <c r="AT14" t="inlineStr">
         <is>
-          <t>-137.62</t>
+          <t>-137.15</t>
         </is>
       </c>
       <c r="AU14" t="inlineStr">
@@ -6336,46 +6336,46 @@
       </c>
       <c r="AV14" t="inlineStr">
         <is>
-          <t>150562465.4441261</t>
+          <t>150423914.0772532</t>
         </is>
       </c>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>232650449.0</t>
+          <t>39561838.0</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>74142370.0</t>
+          <t>77102277.8</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
-          <t>57245793.0</t>
+          <t>54515793.2</t>
         </is>
       </c>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>34130931.06</t>
+          <t>33864219.92</t>
         </is>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
-          <t>16896577</t>
+          <t>22586484</t>
         </is>
       </c>
       <c r="BB14" t="inlineStr">
         <is>
-          <t>3442386.786094812</t>
+          <t>4717477.979434728</t>
         </is>
       </c>
       <c r="BC14" t="inlineStr">
         <is>
-          <t>16400757.27416717</t>
+          <t>11730479.54280426</t>
         </is>
       </c>
       <c r="BD14" t="n">
-        <v>232650449</v>
+        <v>39561838</v>
       </c>
       <c r="BE14" t="inlineStr">
         <is>
@@ -6394,7 +6394,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>-11.08</t>
+          <t>-8.19</t>
         </is>
       </c>
       <c r="BI14" t="inlineStr">
@@ -6419,7 +6419,7 @@
       </c>
       <c r="BM14" t="inlineStr">
         <is>
-          <t>0.61</t>
+          <t>0.62</t>
         </is>
       </c>
       <c r="BN14" t="inlineStr">
@@ -6439,7 +6439,7 @@
       </c>
       <c r="BQ14" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR14" t="inlineStr">
@@ -6449,12 +6449,12 @@
       </c>
       <c r="BS14" t="inlineStr">
         <is>
-          <t>1.02</t>
+          <t>1.05</t>
         </is>
       </c>
       <c r="BT14" t="inlineStr">
         <is>
-          <t>6.56</t>
+          <t>6.39</t>
         </is>
       </c>
       <c r="BU14" t="inlineStr">
@@ -6464,7 +6464,7 @@
       </c>
       <c r="BV14" t="inlineStr">
         <is>
-          <t>15.74</t>
+          <t>16.16</t>
         </is>
       </c>
       <c r="BW14" t="inlineStr">
@@ -6479,12 +6479,12 @@
       </c>
       <c r="BY14" t="inlineStr">
         <is>
-          <t>29.15</t>
+          <t>29.71</t>
         </is>
       </c>
       <c r="BZ14" t="inlineStr">
         <is>
-          <t>12236</t>
+          <t>12557</t>
         </is>
       </c>
       <c r="CA14" t="inlineStr">
@@ -6504,22 +6504,22 @@
       </c>
       <c r="CD14" t="inlineStr">
         <is>
+          <t>37.05</t>
+        </is>
+      </c>
+      <c r="CE14" t="inlineStr">
+        <is>
+          <t>38.2</t>
+        </is>
+      </c>
+      <c r="CF14" t="inlineStr">
+        <is>
           <t>37.0</t>
         </is>
       </c>
-      <c r="CE14" t="inlineStr">
-        <is>
-          <t>37.5</t>
-        </is>
-      </c>
-      <c r="CF14" t="inlineStr">
-        <is>
-          <t>36.9</t>
-        </is>
-      </c>
       <c r="CG14" t="inlineStr">
         <is>
-          <t>36.9</t>
+          <t>38.1</t>
         </is>
       </c>
       <c r="CH14" t="inlineStr">
@@ -6551,12 +6551,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>1.24</t>
+          <t>0.14</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>1128.761</t>
+          <t>6301.223</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -6566,7 +6566,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>36.85</t>
+          <t>36.9</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -6576,17 +6576,17 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>3.28</t>
+          <t>5.63</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>0.63</t>
+          <t>0.91</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>-1.19</t>
+          <t>29.52</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -6651,7 +6651,7 @@
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>-14.60</t>
+          <t>-14.48</t>
         </is>
       </c>
       <c r="X15" t="inlineStr">
@@ -6661,17 +6661,17 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>12.03</t>
+          <t>67.14</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2.09</t>
+          <t>-1.63</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
@@ -6682,280 +6682,280 @@
       <c r="AC15" t="inlineStr"/>
       <c r="AD15" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
-          <t>1043</t>
+          <t>915</t>
         </is>
       </c>
       <c r="AF15" t="inlineStr">
         <is>
+          <t>40.0</t>
+        </is>
+      </c>
+      <c r="AG15" t="inlineStr">
+        <is>
+          <t>29.75</t>
+        </is>
+      </c>
+      <c r="AH15" t="inlineStr">
+        <is>
+          <t>0.82</t>
+        </is>
+      </c>
+      <c r="AI15" t="inlineStr">
+        <is>
+          <t>-4.24</t>
+        </is>
+      </c>
+      <c r="AJ15" t="inlineStr">
+        <is>
+          <t>-4.85</t>
+        </is>
+      </c>
+      <c r="AK15" t="inlineStr">
+        <is>
+          <t>-2.68</t>
+        </is>
+      </c>
+      <c r="AL15" t="inlineStr">
+        <is>
+          <t>36.60000000000001</t>
+        </is>
+      </c>
+      <c r="AM15" t="inlineStr">
+        <is>
+          <t>38.22</t>
+        </is>
+      </c>
+      <c r="AN15" t="inlineStr">
+        <is>
+          <t>40.17</t>
+        </is>
+      </c>
+      <c r="AO15" t="inlineStr">
+        <is>
+          <t>41.28</t>
+        </is>
+      </c>
+      <c r="AP15" t="inlineStr">
+        <is>
+          <t>-7.24</t>
+        </is>
+      </c>
+      <c r="AQ15" t="inlineStr">
+        <is>
+          <t>-1.08</t>
+        </is>
+      </c>
+      <c r="AR15" t="inlineStr">
+        <is>
+          <t>-1.01</t>
+        </is>
+      </c>
+      <c r="AS15" t="inlineStr">
+        <is>
+          <t>2.69</t>
+        </is>
+      </c>
+      <c r="AT15" t="inlineStr">
+        <is>
+          <t>-137.62</t>
+        </is>
+      </c>
+      <c r="AU15" t="inlineStr">
+        <is>
+          <t>2025/11/25</t>
+        </is>
+      </c>
+      <c r="AV15" t="inlineStr">
+        <is>
+          <t>150423914.0772532</t>
+        </is>
+      </c>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>232650449.0</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>74142370.0</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr">
+        <is>
+          <t>57245793.0</t>
+        </is>
+      </c>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>34130931.06</t>
+        </is>
+      </c>
+      <c r="BA15" t="inlineStr">
+        <is>
+          <t>16896577</t>
+        </is>
+      </c>
+      <c r="BB15" t="inlineStr">
+        <is>
+          <t>3442386.786094812</t>
+        </is>
+      </c>
+      <c r="BC15" t="inlineStr">
+        <is>
+          <t>16400757.27416717</t>
+        </is>
+      </c>
+      <c r="BD15" t="n">
+        <v>232650449</v>
+      </c>
+      <c r="BE15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF15" t="inlineStr">
+        <is>
+          <t>41.5</t>
+        </is>
+      </c>
+      <c r="BG15" t="inlineStr">
+        <is>
+          <t>2025/08/07</t>
+        </is>
+      </c>
+      <c r="BH15" t="inlineStr">
+        <is>
+          <t>-11.08</t>
+        </is>
+      </c>
+      <c r="BI15" t="inlineStr">
+        <is>
+          <t>新光鋼</t>
+        </is>
+      </c>
+      <c r="BJ15" t="inlineStr">
+        <is>
+          <t>新光鋼</t>
+        </is>
+      </c>
+      <c r="BK15" t="inlineStr">
+        <is>
+          <t>鋼鐵工業</t>
+        </is>
+      </c>
+      <c r="BL15" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="BM15" t="inlineStr">
+        <is>
+          <t>0.62</t>
+        </is>
+      </c>
+      <c r="BN15" t="inlineStr">
+        <is>
+          <t>-13.67996844119094</t>
+        </is>
+      </c>
+      <c r="BO15" t="inlineStr">
+        <is>
+          <t>-10.11024290164889</t>
+        </is>
+      </c>
+      <c r="BP15" t="inlineStr">
+        <is>
+          <t>24.12947661306339</t>
+        </is>
+      </c>
+      <c r="BQ15" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BR15" t="inlineStr">
+        <is>
+          <t>價-量增</t>
+        </is>
+      </c>
+      <c r="BS15" t="inlineStr">
+        <is>
+          <t>1.02</t>
+        </is>
+      </c>
+      <c r="BT15" t="inlineStr">
+        <is>
+          <t>6.39</t>
+        </is>
+      </c>
+      <c r="BU15" t="inlineStr">
+        <is>
+          <t>11.90</t>
+        </is>
+      </c>
+      <c r="BV15" t="inlineStr">
+        <is>
+          <t>16.16</t>
+        </is>
+      </c>
+      <c r="BW15" t="inlineStr">
+        <is>
+          <t>8.69%</t>
+        </is>
+      </c>
+      <c r="BX15" t="inlineStr">
+        <is>
+          <t>5.19%</t>
+        </is>
+      </c>
+      <c r="BY15" t="inlineStr">
+        <is>
+          <t>29.71</t>
+        </is>
+      </c>
+      <c r="BZ15" t="inlineStr">
+        <is>
+          <t>12557</t>
+        </is>
+      </c>
+      <c r="CA15" t="inlineStr">
+        <is>
+          <t>鋼板38.80%、熱軋及鍍鋅鋼板33.80%、不�袗�板12.60%、特殊鋼板7.00%、加工及其他6.90%、型鋼0.90% (2024年)</t>
+        </is>
+      </c>
+      <c r="CB15" t="inlineStr">
+        <is>
+          <t>新光鋼-鋼鐵工業-上市</t>
+        </is>
+      </c>
+      <c r="CC15" t="inlineStr">
+        <is>
+          <t>鋼鐵工業右下上市</t>
+        </is>
+      </c>
+      <c r="CD15" t="inlineStr">
+        <is>
+          <t>37.0</t>
+        </is>
+      </c>
+      <c r="CE15" t="inlineStr">
+        <is>
           <t>37.5</t>
         </is>
       </c>
-      <c r="AG15" t="inlineStr">
-        <is>
-          <t>16.42</t>
-        </is>
-      </c>
-      <c r="AH15" t="inlineStr">
-        <is>
-          <t>0.66</t>
-        </is>
-      </c>
-      <c r="AI15" t="inlineStr">
-        <is>
-          <t>-4.68</t>
-        </is>
-      </c>
-      <c r="AJ15" t="inlineStr">
-        <is>
-          <t>-4.69</t>
-        </is>
-      </c>
-      <c r="AK15" t="inlineStr">
-        <is>
-          <t>-2.48</t>
-        </is>
-      </c>
-      <c r="AL15" t="inlineStr">
-        <is>
-          <t>36.61</t>
-        </is>
-      </c>
-      <c r="AM15" t="inlineStr">
-        <is>
-          <t>38.41</t>
-        </is>
-      </c>
-      <c r="AN15" t="inlineStr">
-        <is>
-          <t>40.3</t>
-        </is>
-      </c>
-      <c r="AO15" t="inlineStr">
-        <is>
-          <t>41.32</t>
-        </is>
-      </c>
-      <c r="AP15" t="inlineStr">
-        <is>
-          <t>-12.91</t>
-        </is>
-      </c>
-      <c r="AQ15" t="inlineStr">
-        <is>
-          <t>-1.12</t>
-        </is>
-      </c>
-      <c r="AR15" t="inlineStr">
-        <is>
-          <t>-0.99</t>
-        </is>
-      </c>
-      <c r="AS15" t="inlineStr">
-        <is>
-          <t>2.69</t>
-        </is>
-      </c>
-      <c r="AT15" t="inlineStr">
-        <is>
-          <t>-136.94</t>
-        </is>
-      </c>
-      <c r="AU15" t="inlineStr">
-        <is>
-          <t>2025/11/25</t>
-        </is>
-      </c>
-      <c r="AV15" t="inlineStr">
-        <is>
-          <t>150562465.4441261</t>
-        </is>
-      </c>
-      <c r="AW15" t="inlineStr">
-        <is>
-          <t>41298962.0</t>
-        </is>
-      </c>
-      <c r="AX15" t="inlineStr">
-        <is>
-          <t>35487232.0</t>
-        </is>
-      </c>
-      <c r="AY15" t="inlineStr">
-        <is>
-          <t>35914543.8</t>
-        </is>
-      </c>
-      <c r="AZ15" t="inlineStr">
-        <is>
-          <t>29950115.64</t>
-        </is>
-      </c>
-      <c r="BA15" t="inlineStr">
-        <is>
-          <t>-427311</t>
-        </is>
-      </c>
-      <c r="BB15" t="inlineStr">
-        <is>
-          <t>1086319.424627111</t>
-        </is>
-      </c>
-      <c r="BC15" t="inlineStr">
-        <is>
-          <t>1798775.809179619</t>
-        </is>
-      </c>
-      <c r="BD15" t="n">
-        <v>41298962</v>
-      </c>
-      <c r="BE15" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BF15" t="inlineStr">
-        <is>
-          <t>41.5</t>
-        </is>
-      </c>
-      <c r="BG15" t="inlineStr">
-        <is>
-          <t>2025/08/07</t>
-        </is>
-      </c>
-      <c r="BH15" t="inlineStr">
-        <is>
-          <t>-11.20</t>
-        </is>
-      </c>
-      <c r="BI15" t="inlineStr">
-        <is>
-          <t>新光鋼</t>
-        </is>
-      </c>
-      <c r="BJ15" t="inlineStr">
-        <is>
-          <t>新光鋼</t>
-        </is>
-      </c>
-      <c r="BK15" t="inlineStr">
-        <is>
-          <t>鋼鐵工業</t>
-        </is>
-      </c>
-      <c r="BL15" t="inlineStr">
-        <is>
-          <t>上市</t>
-        </is>
-      </c>
-      <c r="BM15" t="inlineStr">
-        <is>
-          <t>0.61</t>
-        </is>
-      </c>
-      <c r="BN15" t="inlineStr">
-        <is>
-          <t>-13.67996844119094</t>
-        </is>
-      </c>
-      <c r="BO15" t="inlineStr">
-        <is>
-          <t>-10.11024290164889</t>
-        </is>
-      </c>
-      <c r="BP15" t="inlineStr">
-        <is>
-          <t>24.12947661306339</t>
-        </is>
-      </c>
-      <c r="BQ15" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;可能出現反轉訊號&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;3&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="BR15" t="inlineStr">
-        <is>
-          <t>價-量增</t>
-        </is>
-      </c>
-      <c r="BS15" t="inlineStr">
-        <is>
-          <t>1.01</t>
-        </is>
-      </c>
-      <c r="BT15" t="inlineStr">
-        <is>
-          <t>6.56</t>
-        </is>
-      </c>
-      <c r="BU15" t="inlineStr">
-        <is>
-          <t>11.90</t>
-        </is>
-      </c>
-      <c r="BV15" t="inlineStr">
-        <is>
-          <t>15.74</t>
-        </is>
-      </c>
-      <c r="BW15" t="inlineStr">
-        <is>
-          <t>8.69%</t>
-        </is>
-      </c>
-      <c r="BX15" t="inlineStr">
-        <is>
-          <t>5.19%</t>
-        </is>
-      </c>
-      <c r="BY15" t="inlineStr">
-        <is>
-          <t>29.15</t>
-        </is>
-      </c>
-      <c r="BZ15" t="inlineStr">
-        <is>
-          <t>12236</t>
-        </is>
-      </c>
-      <c r="CA15" t="inlineStr">
-        <is>
-          <t>鋼板38.80%、熱軋及鍍鋅鋼板33.80%、不�袗�板12.60%、特殊鋼板7.00%、加工及其他6.90%、型鋼0.90% (2024年)</t>
-        </is>
-      </c>
-      <c r="CB15" t="inlineStr">
-        <is>
-          <t>新光鋼-鋼鐵工業-上市</t>
-        </is>
-      </c>
-      <c r="CC15" t="inlineStr">
-        <is>
-          <t>鋼鐵工業右下上市</t>
-        </is>
-      </c>
-      <c r="CD15" t="inlineStr">
-        <is>
-          <t>36.4</t>
-        </is>
-      </c>
-      <c r="CE15" t="inlineStr">
-        <is>
-          <t>36.95</t>
-        </is>
-      </c>
       <c r="CF15" t="inlineStr">
         <is>
-          <t>36.0</t>
+          <t>36.9</t>
         </is>
       </c>
       <c r="CG15" t="inlineStr">
         <is>
-          <t>36.85</t>
+          <t>36.9</t>
         </is>
       </c>
       <c r="CH15" t="inlineStr">
@@ -6987,12 +6987,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>0.83</t>
+          <t>1.24</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>776.396</t>
+          <t>1128.761</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -7002,7 +7002,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>36.4</t>
+          <t>36.85</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -7012,17 +7012,17 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>4.46</t>
+          <t>5.75</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>0.63</t>
+          <t>0.91</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>9.74</t>
+          <t>-1.19</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -7087,7 +7087,7 @@
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>-15.64</t>
+          <t>-14.60</t>
         </is>
       </c>
       <c r="X16" t="inlineStr">
@@ -7097,17 +7097,17 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>8.27</t>
+          <t>12.03</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>0.70</t>
+          <t>2.09</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
@@ -7118,77 +7118,77 @@
       <c r="AC16" t="inlineStr"/>
       <c r="AD16" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
-          <t>1043</t>
+          <t>915</t>
         </is>
       </c>
       <c r="AF16" t="inlineStr">
         <is>
-          <t>11.76</t>
+          <t>37.5</t>
         </is>
       </c>
       <c r="AG16" t="inlineStr">
         <is>
-          <t>3.92</t>
+          <t>16.42</t>
         </is>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>-0.90</t>
+          <t>0.66</t>
         </is>
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>-4.83</t>
+          <t>-4.68</t>
         </is>
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>-4.54</t>
+          <t>-4.69</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>-2.31</t>
+          <t>-2.48</t>
         </is>
       </c>
       <c r="AL16" t="inlineStr">
         <is>
-          <t>36.73</t>
+          <t>36.61</t>
         </is>
       </c>
       <c r="AM16" t="inlineStr">
         <is>
-          <t>38.6</t>
+          <t>38.41</t>
         </is>
       </c>
       <c r="AN16" t="inlineStr">
         <is>
-          <t>40.43</t>
+          <t>40.3</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>41.39</t>
+          <t>41.32</t>
         </is>
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>-19.31</t>
+          <t>-12.91</t>
         </is>
       </c>
       <c r="AQ16" t="inlineStr">
         <is>
-          <t>-1.15</t>
+          <t>-1.12</t>
         </is>
       </c>
       <c r="AR16" t="inlineStr">
         <is>
-          <t>-0.96</t>
+          <t>-0.99</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr">
@@ -7198,7 +7198,7 @@
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>-135.75</t>
+          <t>-136.94</t>
         </is>
       </c>
       <c r="AU16" t="inlineStr">
@@ -7208,46 +7208,46 @@
       </c>
       <c r="AV16" t="inlineStr">
         <is>
-          <t>150562465.4441261</t>
+          <t>150423914.0772532</t>
         </is>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>28176624.0</t>
+          <t>41298962.0</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>37871124.0</t>
+          <t>35487232.0</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>34509118.0</t>
+          <t>35914543.8</t>
         </is>
       </c>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>29545425.32</t>
+          <t>29950115.64</t>
         </is>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
-          <t>3362006</t>
+          <t>-427311</t>
         </is>
       </c>
       <c r="BB16" t="inlineStr">
         <is>
-          <t>956781.9001630185</t>
+          <t>1086319.424627111</t>
         </is>
       </c>
       <c r="BC16" t="inlineStr">
         <is>
-          <t>1376505.330298137</t>
+          <t>1798775.809179619</t>
         </is>
       </c>
       <c r="BD16" t="n">
-        <v>28176624</v>
+        <v>41298962</v>
       </c>
       <c r="BE16" t="inlineStr">
         <is>
@@ -7266,7 +7266,7 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>-12.29</t>
+          <t>-11.20</t>
         </is>
       </c>
       <c r="BI16" t="inlineStr">
@@ -7291,7 +7291,7 @@
       </c>
       <c r="BM16" t="inlineStr">
         <is>
-          <t>0.61</t>
+          <t>0.62</t>
         </is>
       </c>
       <c r="BN16" t="inlineStr">
@@ -7311,22 +7311,22 @@
       </c>
       <c r="BQ16" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;可能出現反轉訊號&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;3&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR16" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS16" t="inlineStr">
         <is>
-          <t>1.00</t>
+          <t>1.01</t>
         </is>
       </c>
       <c r="BT16" t="inlineStr">
         <is>
-          <t>6.56</t>
+          <t>6.39</t>
         </is>
       </c>
       <c r="BU16" t="inlineStr">
@@ -7336,7 +7336,7 @@
       </c>
       <c r="BV16" t="inlineStr">
         <is>
-          <t>15.74</t>
+          <t>16.16</t>
         </is>
       </c>
       <c r="BW16" t="inlineStr">
@@ -7351,12 +7351,12 @@
       </c>
       <c r="BY16" t="inlineStr">
         <is>
-          <t>29.15</t>
+          <t>29.71</t>
         </is>
       </c>
       <c r="BZ16" t="inlineStr">
         <is>
-          <t>12236</t>
+          <t>12557</t>
         </is>
       </c>
       <c r="CA16" t="inlineStr">
@@ -7376,12 +7376,12 @@
       </c>
       <c r="CD16" t="inlineStr">
         <is>
-          <t>36.3</t>
+          <t>36.4</t>
         </is>
       </c>
       <c r="CE16" t="inlineStr">
         <is>
-          <t>36.55</t>
+          <t>36.95</t>
         </is>
       </c>
       <c r="CF16" t="inlineStr">
@@ -7391,7 +7391,7 @@
       </c>
       <c r="CG16" t="inlineStr">
         <is>
-          <t>36.4</t>
+          <t>36.85</t>
         </is>
       </c>
       <c r="CH16" t="inlineStr">
@@ -7423,12 +7423,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>-1.76</t>
+          <t>0.83</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>1212.053</t>
+          <t>776.396</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -7438,7 +7438,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>36.1</t>
+          <t>36.4</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -7448,17 +7448,17 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>5.25</t>
+          <t>6.91</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>0.63</t>
+          <t>0.91</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>3.03</t>
+          <t>9.74</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -7523,7 +7523,7 @@
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>-16.34</t>
+          <t>-15.64</t>
         </is>
       </c>
       <c r="X17" t="inlineStr">
@@ -7533,17 +7533,17 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>12.91</t>
+          <t>8.27</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>-1.38</t>
+          <t>0.70</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
@@ -7554,77 +7554,77 @@
       <c r="AC17" t="inlineStr"/>
       <c r="AD17" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
-          <t>1043</t>
+          <t>915</t>
         </is>
       </c>
       <c r="AF17" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>11.76</t>
         </is>
       </c>
       <c r="AG17" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>3.92</t>
         </is>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>-2.62</t>
+          <t>-0.90</t>
         </is>
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>-4.47</t>
+          <t>-4.83</t>
         </is>
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>-4.38</t>
+          <t>-4.54</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>-2.09</t>
+          <t>-2.31</t>
         </is>
       </c>
       <c r="AL17" t="inlineStr">
         <is>
-          <t>37.07000000000001</t>
+          <t>36.73</t>
         </is>
       </c>
       <c r="AM17" t="inlineStr">
         <is>
-          <t>38.8</t>
+          <t>38.6</t>
         </is>
       </c>
       <c r="AN17" t="inlineStr">
         <is>
-          <t>40.58</t>
+          <t>40.43</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>41.45</t>
+          <t>41.39</t>
         </is>
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>-22.07</t>
+          <t>-19.31</t>
         </is>
       </c>
       <c r="AQ17" t="inlineStr">
         <is>
-          <t>-1.12</t>
+          <t>-1.15</t>
         </is>
       </c>
       <c r="AR17" t="inlineStr">
         <is>
-          <t>-0.91</t>
+          <t>-0.96</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr">
@@ -7634,7 +7634,7 @@
       </c>
       <c r="AT17" t="inlineStr">
         <is>
-          <t>-134.02</t>
+          <t>-135.75</t>
         </is>
       </c>
       <c r="AU17" t="inlineStr">
@@ -7644,46 +7644,46 @@
       </c>
       <c r="AV17" t="inlineStr">
         <is>
-          <t>150562465.4441261</t>
+          <t>150423914.0772532</t>
         </is>
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>43823516.0</t>
+          <t>28176624.0</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>36085517.8</t>
+          <t>37871124.0</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>35025550.9</t>
+          <t>34509118.0</t>
         </is>
       </c>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>29409986.0</t>
+          <t>29545425.32</t>
         </is>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
-          <t>1059966</t>
+          <t>3362006</t>
         </is>
       </c>
       <c r="BB17" t="inlineStr">
         <is>
-          <t>880468.5492293607</t>
+          <t>956781.9001630185</t>
         </is>
       </c>
       <c r="BC17" t="inlineStr">
         <is>
-          <t>2130065.670099653</t>
+          <t>1376505.330298137</t>
         </is>
       </c>
       <c r="BD17" t="n">
-        <v>43823516</v>
+        <v>28176624</v>
       </c>
       <c r="BE17" t="inlineStr">
         <is>
@@ -7702,7 +7702,7 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>-13.01</t>
+          <t>-12.29</t>
         </is>
       </c>
       <c r="BI17" t="inlineStr">
@@ -7727,7 +7727,7 @@
       </c>
       <c r="BM17" t="inlineStr">
         <is>
-          <t>0.61</t>
+          <t>0.62</t>
         </is>
       </c>
       <c r="BN17" t="inlineStr">
@@ -7747,7 +7747,7 @@
       </c>
       <c r="BQ17" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR17" t="inlineStr">
@@ -7757,12 +7757,12 @@
       </c>
       <c r="BS17" t="inlineStr">
         <is>
-          <t>0.99</t>
+          <t>1.00</t>
         </is>
       </c>
       <c r="BT17" t="inlineStr">
         <is>
-          <t>6.56</t>
+          <t>6.39</t>
         </is>
       </c>
       <c r="BU17" t="inlineStr">
@@ -7772,7 +7772,7 @@
       </c>
       <c r="BV17" t="inlineStr">
         <is>
-          <t>15.74</t>
+          <t>16.16</t>
         </is>
       </c>
       <c r="BW17" t="inlineStr">
@@ -7787,12 +7787,12 @@
       </c>
       <c r="BY17" t="inlineStr">
         <is>
-          <t>29.15</t>
+          <t>29.71</t>
         </is>
       </c>
       <c r="BZ17" t="inlineStr">
         <is>
-          <t>12236</t>
+          <t>12557</t>
         </is>
       </c>
       <c r="CA17" t="inlineStr">
@@ -7812,22 +7812,22 @@
       </c>
       <c r="CD17" t="inlineStr">
         <is>
-          <t>36.85</t>
+          <t>36.3</t>
         </is>
       </c>
       <c r="CE17" t="inlineStr">
         <is>
-          <t>36.85</t>
+          <t>36.55</t>
         </is>
       </c>
       <c r="CF17" t="inlineStr">
         <is>
-          <t>35.85</t>
+          <t>36.0</t>
         </is>
       </c>
       <c r="CG17" t="inlineStr">
         <is>
-          <t>36.1</t>
+          <t>36.4</t>
         </is>
       </c>
       <c r="CH17" t="inlineStr">
@@ -7859,12 +7859,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>-0.54</t>
+          <t>-1.76</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>672.504</t>
+          <t>1212.053</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -7874,7 +7874,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>36.75</t>
+          <t>36.1</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -7884,17 +7884,17 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>3.54</t>
+          <t>7.67</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>0.63</t>
+          <t>0.91</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>-2.04</t>
+          <t>3.03</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -7959,7 +7959,7 @@
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>-14.83</t>
+          <t>-16.34</t>
         </is>
       </c>
       <c r="X18" t="inlineStr">
@@ -7969,17 +7969,17 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>7.17</t>
+          <t>12.91</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>-1.09</t>
+          <t>-1.38</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
@@ -7990,12 +7990,12 @@
       <c r="AC18" t="inlineStr"/>
       <c r="AD18" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
-          <t>1043</t>
+          <t>915</t>
         </is>
       </c>
       <c r="AF18" t="inlineStr">
@@ -8010,57 +8010,57 @@
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>-1.92</t>
+          <t>-2.62</t>
         </is>
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>-3.97</t>
+          <t>-4.47</t>
         </is>
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>-4.25</t>
+          <t>-4.38</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>-1.83</t>
+          <t>-2.09</t>
         </is>
       </c>
       <c r="AL18" t="inlineStr">
         <is>
-          <t>37.47000000000001</t>
+          <t>37.07000000000001</t>
         </is>
       </c>
       <c r="AM18" t="inlineStr">
         <is>
-          <t>39.02</t>
+          <t>38.8</t>
         </is>
       </c>
       <c r="AN18" t="inlineStr">
         <is>
-          <t>40.75</t>
+          <t>40.58</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>41.51</t>
+          <t>41.45</t>
         </is>
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>-19.33</t>
+          <t>-22.07</t>
         </is>
       </c>
       <c r="AQ18" t="inlineStr">
         <is>
-          <t>-1.03</t>
+          <t>-1.12</t>
         </is>
       </c>
       <c r="AR18" t="inlineStr">
         <is>
-          <t>-0.86</t>
+          <t>-0.91</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr">
@@ -8070,7 +8070,7 @@
       </c>
       <c r="AT18" t="inlineStr">
         <is>
-          <t>-132.14</t>
+          <t>-134.02</t>
         </is>
       </c>
       <c r="AU18" t="inlineStr">
@@ -8080,46 +8080,46 @@
       </c>
       <c r="AV18" t="inlineStr">
         <is>
-          <t>150562465.4441261</t>
+          <t>150423914.0772532</t>
         </is>
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>24762299.0</t>
+          <t>43823516.0</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>31929308.6</t>
+          <t>36085517.8</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>32595150.7</t>
+          <t>35025550.9</t>
         </is>
       </c>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>29130934.74</t>
+          <t>29409986.0</t>
         </is>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
-          <t>-665842</t>
+          <t>1059966</t>
         </is>
       </c>
       <c r="BB18" t="inlineStr">
         <is>
-          <t>653269.0727074891</t>
+          <t>880468.5492293607</t>
         </is>
       </c>
       <c r="BC18" t="inlineStr">
         <is>
-          <t>1454053.953026839</t>
+          <t>2130065.670099653</t>
         </is>
       </c>
       <c r="BD18" t="n">
-        <v>24762299</v>
+        <v>43823516</v>
       </c>
       <c r="BE18" t="inlineStr">
         <is>
@@ -8138,7 +8138,7 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>-11.45</t>
+          <t>-13.01</t>
         </is>
       </c>
       <c r="BI18" t="inlineStr">
@@ -8163,7 +8163,7 @@
       </c>
       <c r="BM18" t="inlineStr">
         <is>
-          <t>0.61</t>
+          <t>0.62</t>
         </is>
       </c>
       <c r="BN18" t="inlineStr">
@@ -8193,12 +8193,12 @@
       </c>
       <c r="BS18" t="inlineStr">
         <is>
-          <t>1.01</t>
+          <t>0.99</t>
         </is>
       </c>
       <c r="BT18" t="inlineStr">
         <is>
-          <t>6.56</t>
+          <t>6.39</t>
         </is>
       </c>
       <c r="BU18" t="inlineStr">
@@ -8208,7 +8208,7 @@
       </c>
       <c r="BV18" t="inlineStr">
         <is>
-          <t>15.74</t>
+          <t>16.16</t>
         </is>
       </c>
       <c r="BW18" t="inlineStr">
@@ -8223,12 +8223,12 @@
       </c>
       <c r="BY18" t="inlineStr">
         <is>
-          <t>29.15</t>
+          <t>29.71</t>
         </is>
       </c>
       <c r="BZ18" t="inlineStr">
         <is>
-          <t>12236</t>
+          <t>12557</t>
         </is>
       </c>
       <c r="CA18" t="inlineStr">
@@ -8248,22 +8248,22 @@
       </c>
       <c r="CD18" t="inlineStr">
         <is>
-          <t>36.95</t>
+          <t>36.85</t>
         </is>
       </c>
       <c r="CE18" t="inlineStr">
         <is>
-          <t>37.3</t>
+          <t>36.85</t>
         </is>
       </c>
       <c r="CF18" t="inlineStr">
         <is>
-          <t>36.6</t>
+          <t>35.85</t>
         </is>
       </c>
       <c r="CG18" t="inlineStr">
         <is>
-          <t>36.75</t>
+          <t>36.1</t>
         </is>
       </c>
       <c r="CH18" t="inlineStr">
@@ -8295,12 +8295,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>-1.34</t>
+          <t>-0.54</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>1065.248</t>
+          <t>672.504</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -8310,7 +8310,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>36.95</t>
+          <t>36.75</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -8320,17 +8320,17 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>3.02</t>
+          <t>6.01</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>0.63</t>
+          <t>0.91</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>28.28</t>
+          <t>-2.04</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -8395,7 +8395,7 @@
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>-14.37</t>
+          <t>-14.83</t>
         </is>
       </c>
       <c r="X19" t="inlineStr">
@@ -8405,17 +8405,17 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>11.35</t>
+          <t>7.17</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>-0.81</t>
+          <t>-1.09</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
@@ -8426,12 +8426,12 @@
       <c r="AC19" t="inlineStr"/>
       <c r="AD19" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
-          <t>1043</t>
+          <t>915</t>
         </is>
       </c>
       <c r="AF19" t="inlineStr">
@@ -8441,62 +8441,62 @@
       </c>
       <c r="AG19" t="inlineStr">
         <is>
-          <t>9.38</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
-          <t>-1.86</t>
+          <t>-1.92</t>
         </is>
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>-4.02</t>
+          <t>-3.97</t>
         </is>
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>-4.09</t>
+          <t>-4.25</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>-1.60</t>
+          <t>-1.83</t>
         </is>
       </c>
       <c r="AL19" t="inlineStr">
         <is>
-          <t>37.65000000000001</t>
+          <t>37.47000000000001</t>
         </is>
       </c>
       <c r="AM19" t="inlineStr">
         <is>
-          <t>39.23</t>
+          <t>39.02</t>
         </is>
       </c>
       <c r="AN19" t="inlineStr">
         <is>
-          <t>40.9</t>
+          <t>40.75</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>41.57</t>
+          <t>41.51</t>
         </is>
       </c>
       <c r="AP19" t="inlineStr">
         <is>
-          <t>-18.37</t>
+          <t>-19.33</t>
         </is>
       </c>
       <c r="AQ19" t="inlineStr">
         <is>
-          <t>-0.97</t>
+          <t>-1.03</t>
         </is>
       </c>
       <c r="AR19" t="inlineStr">
         <is>
-          <t>-0.82</t>
+          <t>-0.86</t>
         </is>
       </c>
       <c r="AS19" t="inlineStr">
@@ -8506,7 +8506,7 @@
       </c>
       <c r="AT19" t="inlineStr">
         <is>
-          <t>-130.59</t>
+          <t>-132.14</t>
         </is>
       </c>
       <c r="AU19" t="inlineStr">
@@ -8516,46 +8516,46 @@
       </c>
       <c r="AV19" t="inlineStr">
         <is>
-          <t>150562465.4441261</t>
+          <t>150423914.0772532</t>
         </is>
       </c>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>39374759.0</t>
+          <t>24762299.0</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>40349216.0</t>
+          <t>31929308.6</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
-          <t>31454761.9</t>
+          <t>32595150.7</t>
         </is>
       </c>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>29061426.18</t>
+          <t>29130934.74</t>
         </is>
       </c>
       <c r="BA19" t="inlineStr">
         <is>
-          <t>8894454</t>
+          <t>-665842</t>
         </is>
       </c>
       <c r="BB19" t="inlineStr">
         <is>
-          <t>507671.8217403347</t>
+          <t>653269.0727074891</t>
         </is>
       </c>
       <c r="BC19" t="inlineStr">
         <is>
-          <t>2478665.680314712</t>
+          <t>1454053.953026839</t>
         </is>
       </c>
       <c r="BD19" t="n">
-        <v>39374759</v>
+        <v>24762299</v>
       </c>
       <c r="BE19" t="inlineStr">
         <is>
@@ -8574,7 +8574,7 @@
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>-10.96</t>
+          <t>-11.45</t>
         </is>
       </c>
       <c r="BI19" t="inlineStr">
@@ -8599,7 +8599,7 @@
       </c>
       <c r="BM19" t="inlineStr">
         <is>
-          <t>0.61</t>
+          <t>0.62</t>
         </is>
       </c>
       <c r="BN19" t="inlineStr">
@@ -8619,22 +8619,22 @@
       </c>
       <c r="BQ19" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR19" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS19" t="inlineStr">
         <is>
-          <t>1.02</t>
+          <t>1.01</t>
         </is>
       </c>
       <c r="BT19" t="inlineStr">
         <is>
-          <t>6.56</t>
+          <t>6.39</t>
         </is>
       </c>
       <c r="BU19" t="inlineStr">
@@ -8644,7 +8644,7 @@
       </c>
       <c r="BV19" t="inlineStr">
         <is>
-          <t>15.74</t>
+          <t>16.16</t>
         </is>
       </c>
       <c r="BW19" t="inlineStr">
@@ -8659,12 +8659,12 @@
       </c>
       <c r="BY19" t="inlineStr">
         <is>
-          <t>29.15</t>
+          <t>29.71</t>
         </is>
       </c>
       <c r="BZ19" t="inlineStr">
         <is>
-          <t>12236</t>
+          <t>12557</t>
         </is>
       </c>
       <c r="CA19" t="inlineStr">
@@ -8684,22 +8684,22 @@
       </c>
       <c r="CD19" t="inlineStr">
         <is>
+          <t>36.95</t>
+        </is>
+      </c>
+      <c r="CE19" t="inlineStr">
+        <is>
           <t>37.3</t>
         </is>
       </c>
-      <c r="CE19" t="inlineStr">
-        <is>
-          <t>37.5</t>
-        </is>
-      </c>
       <c r="CF19" t="inlineStr">
         <is>
-          <t>36.7</t>
+          <t>36.6</t>
         </is>
       </c>
       <c r="CG19" t="inlineStr">
         <is>
-          <t>36.95</t>
+          <t>36.75</t>
         </is>
       </c>
       <c r="CH19" t="inlineStr">
@@ -8731,12 +8731,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>-1.71</t>
+          <t>-1.34</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>1408.733</t>
+          <t>1065.248</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -8746,7 +8746,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>37.45</t>
+          <t>36.95</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -8756,17 +8756,17 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>1.71</t>
+          <t>5.5</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>0.63</t>
+          <t>0.91</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>22.93</t>
+          <t>28.28</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -8831,7 +8831,7 @@
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>-13.21</t>
+          <t>-14.37</t>
         </is>
       </c>
       <c r="X20" t="inlineStr">
@@ -8841,17 +8841,17 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>15.01</t>
+          <t>11.35</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>-2.94</t>
+          <t>-0.81</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
@@ -8862,12 +8862,12 @@
       <c r="AC20" t="inlineStr"/>
       <c r="AD20" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
-          <t>1043</t>
+          <t>915</t>
         </is>
       </c>
       <c r="AF20" t="inlineStr">
@@ -8877,62 +8877,62 @@
       </c>
       <c r="AG20" t="inlineStr">
         <is>
-          <t>16.69</t>
+          <t>9.38</t>
         </is>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
-          <t>-1.42</t>
+          <t>-1.86</t>
         </is>
       </c>
       <c r="AI20" t="inlineStr">
         <is>
-          <t>-3.63</t>
+          <t>-4.02</t>
         </is>
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>-3.96</t>
+          <t>-4.09</t>
         </is>
       </c>
       <c r="AK20" t="inlineStr">
         <is>
-          <t>-1.34</t>
+          <t>-1.60</t>
         </is>
       </c>
       <c r="AL20" t="inlineStr">
         <is>
-          <t>37.99</t>
+          <t>37.65000000000001</t>
         </is>
       </c>
       <c r="AM20" t="inlineStr">
         <is>
-          <t>39.42</t>
+          <t>39.23</t>
         </is>
       </c>
       <c r="AN20" t="inlineStr">
         <is>
-          <t>41.05</t>
+          <t>40.9</t>
         </is>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>41.6</t>
+          <t>41.57</t>
         </is>
       </c>
       <c r="AP20" t="inlineStr">
         <is>
-          <t>-15.49</t>
+          <t>-18.37</t>
         </is>
       </c>
       <c r="AQ20" t="inlineStr">
         <is>
-          <t>-0.91</t>
+          <t>-0.97</t>
         </is>
       </c>
       <c r="AR20" t="inlineStr">
         <is>
-          <t>-0.78</t>
+          <t>-0.82</t>
         </is>
       </c>
       <c r="AS20" t="inlineStr">
@@ -8942,7 +8942,7 @@
       </c>
       <c r="AT20" t="inlineStr">
         <is>
-          <t>-129.19</t>
+          <t>-130.59</t>
         </is>
       </c>
       <c r="AU20" t="inlineStr">
@@ -8952,46 +8952,46 @@
       </c>
       <c r="AV20" t="inlineStr">
         <is>
-          <t>150562465.4441261</t>
+          <t>150423914.0772532</t>
         </is>
       </c>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>53218422.0</t>
+          <t>39374759.0</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>36341855.6</t>
+          <t>40349216.0</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
-          <t>29562657.9</t>
+          <t>31454761.9</t>
         </is>
       </c>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>28846965.04</t>
+          <t>29061426.18</t>
         </is>
       </c>
       <c r="BA20" t="inlineStr">
         <is>
-          <t>6779197</t>
+          <t>8894454</t>
         </is>
       </c>
       <c r="BB20" t="inlineStr">
         <is>
-          <t>149309.3019995387</t>
+          <t>507671.8217403347</t>
         </is>
       </c>
       <c r="BC20" t="inlineStr">
         <is>
-          <t>2288252.230714723</t>
+          <t>2478665.680314712</t>
         </is>
       </c>
       <c r="BD20" t="n">
-        <v>53218422</v>
+        <v>39374759</v>
       </c>
       <c r="BE20" t="inlineStr">
         <is>
@@ -9010,7 +9010,7 @@
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>-9.76</t>
+          <t>-10.96</t>
         </is>
       </c>
       <c r="BI20" t="inlineStr">
@@ -9035,7 +9035,7 @@
       </c>
       <c r="BM20" t="inlineStr">
         <is>
-          <t>0.61</t>
+          <t>0.62</t>
         </is>
       </c>
       <c r="BN20" t="inlineStr">
@@ -9055,22 +9055,22 @@
       </c>
       <c r="BQ20" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR20" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS20" t="inlineStr">
         <is>
-          <t>1.03</t>
+          <t>1.02</t>
         </is>
       </c>
       <c r="BT20" t="inlineStr">
         <is>
-          <t>6.56</t>
+          <t>6.39</t>
         </is>
       </c>
       <c r="BU20" t="inlineStr">
@@ -9080,7 +9080,7 @@
       </c>
       <c r="BV20" t="inlineStr">
         <is>
-          <t>15.74</t>
+          <t>16.16</t>
         </is>
       </c>
       <c r="BW20" t="inlineStr">
@@ -9095,12 +9095,12 @@
       </c>
       <c r="BY20" t="inlineStr">
         <is>
-          <t>29.15</t>
+          <t>29.71</t>
         </is>
       </c>
       <c r="BZ20" t="inlineStr">
         <is>
-          <t>12236</t>
+          <t>12557</t>
         </is>
       </c>
       <c r="CA20" t="inlineStr">
@@ -9120,22 +9120,22 @@
       </c>
       <c r="CD20" t="inlineStr">
         <is>
-          <t>38.1</t>
+          <t>37.3</t>
         </is>
       </c>
       <c r="CE20" t="inlineStr">
         <is>
-          <t>38.7</t>
+          <t>37.5</t>
         </is>
       </c>
       <c r="CF20" t="inlineStr">
         <is>
-          <t>37.3</t>
+          <t>36.7</t>
         </is>
       </c>
       <c r="CG20" t="inlineStr">
         <is>
-          <t>37.45</t>
+          <t>36.95</t>
         </is>
       </c>
       <c r="CH20" t="inlineStr">
@@ -9167,12 +9167,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-1.71</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>504.317</t>
+          <t>1408.733</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -9182,7 +9182,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>38.1</t>
+          <t>37.45</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -9192,17 +9192,17 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>4.22</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>0.63</t>
+          <t>0.91</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>20.39</t>
+          <t>22.93</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -9267,7 +9267,7 @@
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>-11.70</t>
+          <t>-13.21</t>
         </is>
       </c>
       <c r="X21" t="inlineStr">
@@ -9277,17 +9277,17 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>5.37</t>
+          <t>15.01</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>-0.39</t>
+          <t>-2.94</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
@@ -9298,17 +9298,17 @@
       <c r="AC21" t="inlineStr"/>
       <c r="AD21" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
-          <t>1043</t>
+          <t>915</t>
         </is>
       </c>
       <c r="AF21" t="inlineStr">
         <is>
-          <t>28.13</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG21" t="inlineStr">
@@ -9318,57 +9318,57 @@
       </c>
       <c r="AH21" t="inlineStr">
         <is>
-          <t>-0.55</t>
+          <t>-1.42</t>
         </is>
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>-3.22</t>
+          <t>-3.63</t>
         </is>
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>-3.86</t>
+          <t>-3.96</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
         <is>
-          <t>-1.12</t>
+          <t>-1.34</t>
         </is>
       </c>
       <c r="AL21" t="inlineStr">
         <is>
-          <t>38.31</t>
+          <t>37.99</t>
         </is>
       </c>
       <c r="AM21" t="inlineStr">
         <is>
-          <t>39.58</t>
+          <t>39.42</t>
         </is>
       </c>
       <c r="AN21" t="inlineStr">
         <is>
-          <t>41.17</t>
+          <t>41.05</t>
         </is>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>41.64</t>
+          <t>41.6</t>
         </is>
       </c>
       <c r="AP21" t="inlineStr">
         <is>
-          <t>-13.76</t>
+          <t>-15.49</t>
         </is>
       </c>
       <c r="AQ21" t="inlineStr">
         <is>
-          <t>-0.86</t>
+          <t>-0.91</t>
         </is>
       </c>
       <c r="AR21" t="inlineStr">
         <is>
-          <t>-0.75</t>
+          <t>-0.78</t>
         </is>
       </c>
       <c r="AS21" t="inlineStr">
@@ -9378,7 +9378,7 @@
       </c>
       <c r="AT21" t="inlineStr">
         <is>
-          <t>-128.06</t>
+          <t>-129.19</t>
         </is>
       </c>
       <c r="AU21" t="inlineStr">
@@ -9388,46 +9388,46 @@
       </c>
       <c r="AV21" t="inlineStr">
         <is>
-          <t>150562465.4441261</t>
+          <t>150423914.0772532</t>
         </is>
       </c>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>19248593.0</t>
+          <t>53218422.0</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>31147112.0</t>
+          <t>36341855.6</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
-          <t>25871081.1</t>
+          <t>29562657.9</t>
         </is>
       </c>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>28091032.78</t>
+          <t>28846965.04</t>
         </is>
       </c>
       <c r="BA21" t="inlineStr">
         <is>
-          <t>5276030</t>
+          <t>6779197</t>
         </is>
       </c>
       <c r="BB21" t="inlineStr">
         <is>
-          <t>-239589.4123123131</t>
+          <t>149309.3019995387</t>
         </is>
       </c>
       <c r="BC21" t="inlineStr">
         <is>
-          <t>451260.1159035005</t>
+          <t>2288252.230714723</t>
         </is>
       </c>
       <c r="BD21" t="n">
-        <v>19248593</v>
+        <v>53218422</v>
       </c>
       <c r="BE21" t="inlineStr">
         <is>
@@ -9446,7 +9446,7 @@
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>-8.19</t>
+          <t>-9.76</t>
         </is>
       </c>
       <c r="BI21" t="inlineStr">
@@ -9471,7 +9471,7 @@
       </c>
       <c r="BM21" t="inlineStr">
         <is>
-          <t>0.61</t>
+          <t>0.62</t>
         </is>
       </c>
       <c r="BN21" t="inlineStr">
@@ -9491,7 +9491,7 @@
       </c>
       <c r="BQ21" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR21" t="inlineStr">
@@ -9501,12 +9501,12 @@
       </c>
       <c r="BS21" t="inlineStr">
         <is>
-          <t>1.05</t>
+          <t>1.03</t>
         </is>
       </c>
       <c r="BT21" t="inlineStr">
         <is>
-          <t>6.56</t>
+          <t>6.39</t>
         </is>
       </c>
       <c r="BU21" t="inlineStr">
@@ -9516,7 +9516,7 @@
       </c>
       <c r="BV21" t="inlineStr">
         <is>
-          <t>15.74</t>
+          <t>16.16</t>
         </is>
       </c>
       <c r="BW21" t="inlineStr">
@@ -9531,12 +9531,12 @@
       </c>
       <c r="BY21" t="inlineStr">
         <is>
-          <t>29.15</t>
+          <t>29.71</t>
         </is>
       </c>
       <c r="BZ21" t="inlineStr">
         <is>
-          <t>12236</t>
+          <t>12557</t>
         </is>
       </c>
       <c r="CA21" t="inlineStr">
@@ -9556,22 +9556,22 @@
       </c>
       <c r="CD21" t="inlineStr">
         <is>
-          <t>38.2</t>
+          <t>38.1</t>
         </is>
       </c>
       <c r="CE21" t="inlineStr">
         <is>
-          <t>38.4</t>
+          <t>38.7</t>
         </is>
       </c>
       <c r="CF21" t="inlineStr">
         <is>
-          <t>37.95</t>
+          <t>37.3</t>
         </is>
       </c>
       <c r="CG21" t="inlineStr">
         <is>
-          <t>38.1</t>
+          <t>37.45</t>
         </is>
       </c>
       <c r="CH21" t="inlineStr">
@@ -9603,12 +9603,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>1.18</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>605.721</t>
+          <t>504.317</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -9628,17 +9628,17 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>2.56</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>0.63</t>
+          <t>0.91</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>29.75</t>
+          <t>20.39</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -9713,17 +9713,17 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>6.45</t>
+          <t>5.37</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>0.40</t>
+          <t>-0.39</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
@@ -9734,77 +9734,77 @@
       <c r="AC22" t="inlineStr"/>
       <c r="AD22" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AE22" t="inlineStr">
         <is>
-          <t>1043</t>
+          <t>915</t>
         </is>
       </c>
       <c r="AF22" t="inlineStr">
         <is>
-          <t>21.95</t>
+          <t>28.13</t>
         </is>
       </c>
       <c r="AG22" t="inlineStr">
         <is>
-          <t>7.32</t>
+          <t>16.69</t>
         </is>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
-          <t>-0.94</t>
+          <t>-0.55</t>
         </is>
       </c>
       <c r="AI22" t="inlineStr">
         <is>
-          <t>-3.10</t>
+          <t>-3.22</t>
         </is>
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>-3.87</t>
+          <t>-3.86</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
         <is>
-          <t>-0.91</t>
+          <t>-1.12</t>
         </is>
       </c>
       <c r="AL22" t="inlineStr">
         <is>
-          <t>38.46</t>
+          <t>38.31</t>
         </is>
       </c>
       <c r="AM22" t="inlineStr">
         <is>
-          <t>39.69</t>
+          <t>39.58</t>
         </is>
       </c>
       <c r="AN22" t="inlineStr">
         <is>
-          <t>41.29</t>
+          <t>41.17</t>
         </is>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>41.67</t>
+          <t>41.64</t>
         </is>
       </c>
       <c r="AP22" t="inlineStr">
         <is>
-          <t>-16.76</t>
+          <t>-13.76</t>
         </is>
       </c>
       <c r="AQ22" t="inlineStr">
         <is>
-          <t>-0.85</t>
+          <t>-0.86</t>
         </is>
       </c>
       <c r="AR22" t="inlineStr">
         <is>
-          <t>-0.73</t>
+          <t>-0.75</t>
         </is>
       </c>
       <c r="AS22" t="inlineStr">
@@ -9814,7 +9814,7 @@
       </c>
       <c r="AT22" t="inlineStr">
         <is>
-          <t>-127.09</t>
+          <t>-128.06</t>
         </is>
       </c>
       <c r="AU22" t="inlineStr">
@@ -9824,46 +9824,46 @@
       </c>
       <c r="AV22" t="inlineStr">
         <is>
-          <t>150562465.4441261</t>
+          <t>150423914.0772532</t>
         </is>
       </c>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>23042470.0</t>
+          <t>19248593.0</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>33965584.0</t>
+          <t>31147112.0</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr">
         <is>
-          <t>26178217.9</t>
+          <t>25871081.1</t>
         </is>
       </c>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>28206383.42</t>
+          <t>28091032.78</t>
         </is>
       </c>
       <c r="BA22" t="inlineStr">
         <is>
-          <t>7787366</t>
+          <t>5276030</t>
         </is>
       </c>
       <c r="BB22" t="inlineStr">
         <is>
-          <t>-365198.417442461</t>
+          <t>-239589.4123123131</t>
         </is>
       </c>
       <c r="BC22" t="inlineStr">
         <is>
-          <t>1450493.769176625</t>
+          <t>451260.1159035005</t>
         </is>
       </c>
       <c r="BD22" t="n">
-        <v>23042470</v>
+        <v>19248593</v>
       </c>
       <c r="BE22" t="inlineStr">
         <is>
@@ -9907,7 +9907,7 @@
       </c>
       <c r="BM22" t="inlineStr">
         <is>
-          <t>0.61</t>
+          <t>0.62</t>
         </is>
       </c>
       <c r="BN22" t="inlineStr">
@@ -9927,7 +9927,7 @@
       </c>
       <c r="BQ22" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;可能出現反轉訊號&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;3&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR22" t="inlineStr">
@@ -9942,7 +9942,7 @@
       </c>
       <c r="BT22" t="inlineStr">
         <is>
-          <t>6.56</t>
+          <t>6.39</t>
         </is>
       </c>
       <c r="BU22" t="inlineStr">
@@ -9952,7 +9952,7 @@
       </c>
       <c r="BV22" t="inlineStr">
         <is>
-          <t>15.74</t>
+          <t>16.16</t>
         </is>
       </c>
       <c r="BW22" t="inlineStr">
@@ -9967,12 +9967,12 @@
       </c>
       <c r="BY22" t="inlineStr">
         <is>
-          <t>29.15</t>
+          <t>29.71</t>
         </is>
       </c>
       <c r="BZ22" t="inlineStr">
         <is>
-          <t>12236</t>
+          <t>12557</t>
         </is>
       </c>
       <c r="CA22" t="inlineStr">
@@ -9992,17 +9992,17 @@
       </c>
       <c r="CD22" t="inlineStr">
         <is>
-          <t>38.0</t>
+          <t>38.2</t>
         </is>
       </c>
       <c r="CE22" t="inlineStr">
         <is>
-          <t>38.3</t>
+          <t>38.4</t>
         </is>
       </c>
       <c r="CF22" t="inlineStr">
         <is>
-          <t>37.75</t>
+          <t>37.95</t>
         </is>
       </c>
       <c r="CG22" t="inlineStr">
@@ -10039,12 +10039,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>-2.6</t>
+          <t>1.18</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>1764.112</t>
+          <t>605.721</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -10054,7 +10054,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>37.65</t>
+          <t>38.1</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -10064,17 +10064,17 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>1.18</t>
+          <t>2.56</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>0.63</t>
+          <t>0.91</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>21.53</t>
+          <t>29.75</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -10139,7 +10139,7 @@
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>-12.75</t>
+          <t>-11.70</t>
         </is>
       </c>
       <c r="X23" t="inlineStr">
@@ -10149,17 +10149,17 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>18.80</t>
+          <t>6.45</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>-2.12</t>
+          <t>0.40</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
@@ -10170,77 +10170,77 @@
       <c r="AC23" t="inlineStr"/>
       <c r="AD23" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AE23" t="inlineStr">
         <is>
-          <t>1043</t>
+          <t>915</t>
         </is>
       </c>
       <c r="AF23" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>21.95</t>
         </is>
       </c>
       <c r="AG23" t="inlineStr">
         <is>
-          <t>6.67</t>
+          <t>7.32</t>
         </is>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
-          <t>-2.44</t>
+          <t>-0.94</t>
         </is>
       </c>
       <c r="AI23" t="inlineStr">
         <is>
-          <t>-3.03</t>
+          <t>-3.10</t>
         </is>
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>-3.91</t>
+          <t>-3.87</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
         <is>
-          <t>-0.66</t>
+          <t>-0.91</t>
         </is>
       </c>
       <c r="AL23" t="inlineStr">
         <is>
-          <t>38.59</t>
+          <t>38.46</t>
         </is>
       </c>
       <c r="AM23" t="inlineStr">
         <is>
-          <t>39.8</t>
+          <t>39.69</t>
         </is>
       </c>
       <c r="AN23" t="inlineStr">
         <is>
-          <t>41.42</t>
+          <t>41.29</t>
         </is>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>41.69</t>
+          <t>41.67</t>
         </is>
       </c>
       <c r="AP23" t="inlineStr">
         <is>
-          <t>-18.69</t>
+          <t>-16.76</t>
         </is>
       </c>
       <c r="AQ23" t="inlineStr">
         <is>
-          <t>-0.83</t>
+          <t>-0.85</t>
         </is>
       </c>
       <c r="AR23" t="inlineStr">
         <is>
-          <t>-0.70</t>
+          <t>-0.73</t>
         </is>
       </c>
       <c r="AS23" t="inlineStr">
@@ -10250,7 +10250,7 @@
       </c>
       <c r="AT23" t="inlineStr">
         <is>
-          <t>-125.95</t>
+          <t>-127.09</t>
         </is>
       </c>
       <c r="AU23" t="inlineStr">
@@ -10260,46 +10260,46 @@
       </c>
       <c r="AV23" t="inlineStr">
         <is>
-          <t>150562465.4441261</t>
+          <t>150423914.0772532</t>
         </is>
       </c>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>66861836.0</t>
+          <t>23042470.0</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>33260992.8</t>
+          <t>33965584.0</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr">
         <is>
-          <t>27368625.9</t>
+          <t>26178217.9</t>
         </is>
       </c>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>28716017.48</t>
+          <t>28206383.42</t>
         </is>
       </c>
       <c r="BA23" t="inlineStr">
         <is>
-          <t>5892366</t>
+          <t>7787366</t>
         </is>
       </c>
       <c r="BB23" t="inlineStr">
         <is>
-          <t>-695324.269555022</t>
+          <t>-365198.417442461</t>
         </is>
       </c>
       <c r="BC23" t="inlineStr">
         <is>
-          <t>2419680.246381927</t>
+          <t>1450493.769176625</t>
         </is>
       </c>
       <c r="BD23" t="n">
-        <v>66861836</v>
+        <v>23042470</v>
       </c>
       <c r="BE23" t="inlineStr">
         <is>
@@ -10318,7 +10318,7 @@
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>-9.28</t>
+          <t>-8.19</t>
         </is>
       </c>
       <c r="BI23" t="inlineStr">
@@ -10343,7 +10343,7 @@
       </c>
       <c r="BM23" t="inlineStr">
         <is>
-          <t>0.61</t>
+          <t>0.62</t>
         </is>
       </c>
       <c r="BN23" t="inlineStr">
@@ -10363,7 +10363,7 @@
       </c>
       <c r="BQ23" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;可能出現反轉訊號&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;3&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR23" t="inlineStr">
@@ -10373,12 +10373,12 @@
       </c>
       <c r="BS23" t="inlineStr">
         <is>
-          <t>1.04</t>
+          <t>1.05</t>
         </is>
       </c>
       <c r="BT23" t="inlineStr">
         <is>
-          <t>6.56</t>
+          <t>6.39</t>
         </is>
       </c>
       <c r="BU23" t="inlineStr">
@@ -10388,7 +10388,7 @@
       </c>
       <c r="BV23" t="inlineStr">
         <is>
-          <t>15.74</t>
+          <t>16.16</t>
         </is>
       </c>
       <c r="BW23" t="inlineStr">
@@ -10403,12 +10403,12 @@
       </c>
       <c r="BY23" t="inlineStr">
         <is>
-          <t>29.15</t>
+          <t>29.71</t>
         </is>
       </c>
       <c r="BZ23" t="inlineStr">
         <is>
-          <t>12236</t>
+          <t>12557</t>
         </is>
       </c>
       <c r="CA23" t="inlineStr">
@@ -10428,22 +10428,22 @@
       </c>
       <c r="CD23" t="inlineStr">
         <is>
-          <t>38.45</t>
+          <t>38.0</t>
         </is>
       </c>
       <c r="CE23" t="inlineStr">
         <is>
-          <t>38.75</t>
+          <t>38.3</t>
         </is>
       </c>
       <c r="CF23" t="inlineStr">
         <is>
-          <t>37.35</t>
+          <t>37.75</t>
         </is>
       </c>
       <c r="CG23" t="inlineStr">
         <is>
-          <t>37.65</t>
+          <t>38.1</t>
         </is>
       </c>
       <c r="CH23" t="inlineStr">

--- a/Result/checksun_type/塔架.xlsx
+++ b/Result/checksun_type/塔架.xlsx
@@ -873,7 +873,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1057,15 +1057,11 @@
           <t>138.0</t>
         </is>
       </c>
-      <c r="AM2" t="inlineStr">
-        <is>
-          <t>144.7</t>
-        </is>
-      </c>
-      <c r="AN2" t="inlineStr">
-        <is>
-          <t>158.31</t>
-        </is>
+      <c r="AM2" t="n">
+        <v>144.7</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>158.31</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
@@ -1112,20 +1108,16 @@
           <t>126140252.0</t>
         </is>
       </c>
-      <c r="AX2" t="inlineStr">
-        <is>
-          <t>179646773.6</t>
-        </is>
+      <c r="AX2" t="n">
+        <v>179646773.6</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
           <t>288541776.1</t>
         </is>
       </c>
-      <c r="AZ2" t="inlineStr">
-        <is>
-          <t>249860076.6</t>
-        </is>
+      <c r="AZ2" t="n">
+        <v>249860076.6</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
@@ -1142,8 +1134,10 @@
           <t>-13008524.13905758</t>
         </is>
       </c>
-      <c r="BD2" t="n">
-        <v>126140252</v>
+      <c r="BD2" t="inlineStr">
+        <is>
+          <t>126140252.0</t>
+        </is>
       </c>
       <c r="BE2" t="inlineStr">
         <is>
@@ -1309,7 +1303,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1493,15 +1487,11 @@
           <t>135.6</t>
         </is>
       </c>
-      <c r="AM3" t="inlineStr">
-        <is>
-          <t>145.35</t>
-        </is>
-      </c>
-      <c r="AN3" t="inlineStr">
-        <is>
-          <t>158.83</t>
-        </is>
+      <c r="AM3" t="n">
+        <v>145.35</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>158.83</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
@@ -1548,20 +1538,16 @@
           <t>149355643.0</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr">
-        <is>
-          <t>199168061.0</t>
-        </is>
+      <c r="AX3" t="n">
+        <v>199168061</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
           <t>286806442.7</t>
         </is>
       </c>
-      <c r="AZ3" t="inlineStr">
-        <is>
-          <t>252995092.08</t>
-        </is>
+      <c r="AZ3" t="n">
+        <v>252995092.08</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
@@ -1578,8 +1564,10 @@
           <t>-5288395.852468729</t>
         </is>
       </c>
-      <c r="BD3" t="n">
-        <v>149355643</v>
+      <c r="BD3" t="inlineStr">
+        <is>
+          <t>149355643.0</t>
+        </is>
       </c>
       <c r="BE3" t="inlineStr">
         <is>
@@ -1745,7 +1733,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1929,15 +1917,11 @@
           <t>133.9</t>
         </is>
       </c>
-      <c r="AM4" t="inlineStr">
-        <is>
-          <t>146.28</t>
-        </is>
-      </c>
-      <c r="AN4" t="inlineStr">
-        <is>
-          <t>159.48</t>
-        </is>
+      <c r="AM4" t="n">
+        <v>146.28</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>159.48</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
@@ -1984,20 +1968,16 @@
           <t>236429825.0</t>
         </is>
       </c>
-      <c r="AX4" t="inlineStr">
-        <is>
-          <t>243968869.0</t>
-        </is>
+      <c r="AX4" t="n">
+        <v>243968869</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
           <t>280669574.0</t>
         </is>
       </c>
-      <c r="AZ4" t="inlineStr">
-        <is>
-          <t>255272113.08</t>
-        </is>
+      <c r="AZ4" t="n">
+        <v>255272113.08</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
@@ -2014,8 +1994,10 @@
           <t>3441866.801674962</t>
         </is>
       </c>
-      <c r="BD4" t="n">
-        <v>236429825</v>
+      <c r="BD4" t="inlineStr">
+        <is>
+          <t>236429825.0</t>
+        </is>
       </c>
       <c r="BE4" t="inlineStr">
         <is>
@@ -2181,7 +2163,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -2365,15 +2347,11 @@
           <t>132.9</t>
         </is>
       </c>
-      <c r="AM5" t="inlineStr">
-        <is>
-          <t>147.28</t>
-        </is>
-      </c>
-      <c r="AN5" t="inlineStr">
-        <is>
-          <t>160.17</t>
-        </is>
+      <c r="AM5" t="n">
+        <v>147.28</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>160.17</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
@@ -2420,20 +2398,16 @@
           <t>173429988.0</t>
         </is>
       </c>
-      <c r="AX5" t="inlineStr">
-        <is>
-          <t>305348589.0</t>
-        </is>
+      <c r="AX5" t="n">
+        <v>305348589</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
           <t>272591978.0</t>
         </is>
       </c>
-      <c r="AZ5" t="inlineStr">
-        <is>
-          <t>254388028.92</t>
-        </is>
+      <c r="AZ5" t="n">
+        <v>254388028.92</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
@@ -2450,8 +2424,10 @@
           <t>6461370.136106104</t>
         </is>
       </c>
-      <c r="BD5" t="n">
-        <v>173429988</v>
+      <c r="BD5" t="inlineStr">
+        <is>
+          <t>173429988.0</t>
+        </is>
       </c>
       <c r="BE5" t="inlineStr">
         <is>
@@ -2617,7 +2593,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -2801,15 +2777,11 @@
           <t>133.4</t>
         </is>
       </c>
-      <c r="AM6" t="inlineStr">
-        <is>
-          <t>148.32</t>
-        </is>
-      </c>
-      <c r="AN6" t="inlineStr">
-        <is>
-          <t>160.95</t>
-        </is>
+      <c r="AM6" t="n">
+        <v>148.32</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>160.95</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
@@ -2856,20 +2828,16 @@
           <t>212878160.0</t>
         </is>
       </c>
-      <c r="AX6" t="inlineStr">
-        <is>
-          <t>421450515.0</t>
-        </is>
+      <c r="AX6" t="n">
+        <v>421450515</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
           <t>274650710.4</t>
         </is>
       </c>
-      <c r="AZ6" t="inlineStr">
-        <is>
-          <t>254522728.7</t>
-        </is>
+      <c r="AZ6" t="n">
+        <v>254522728.7</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
@@ -2886,8 +2854,10 @@
           <t>17294165.64471823</t>
         </is>
       </c>
-      <c r="BD6" t="n">
-        <v>212878160</v>
+      <c r="BD6" t="inlineStr">
+        <is>
+          <t>212878160.0</t>
+        </is>
       </c>
       <c r="BE6" t="inlineStr">
         <is>
@@ -3053,7 +3023,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -3237,15 +3207,11 @@
           <t>136.3</t>
         </is>
       </c>
-      <c r="AM7" t="inlineStr">
-        <is>
-          <t>149.6</t>
-        </is>
-      </c>
-      <c r="AN7" t="inlineStr">
-        <is>
-          <t>161.73</t>
-        </is>
+      <c r="AM7" t="n">
+        <v>149.6</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>161.73</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
@@ -3292,20 +3258,16 @@
           <t>223746689.0</t>
         </is>
       </c>
-      <c r="AX7" t="inlineStr">
-        <is>
-          <t>397436778.6</t>
-        </is>
+      <c r="AX7" t="n">
+        <v>397436778.6</v>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
           <t>263301806.5</t>
         </is>
       </c>
-      <c r="AZ7" t="inlineStr">
-        <is>
-          <t>254911229.58</t>
-        </is>
+      <c r="AZ7" t="n">
+        <v>254911229.58</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
@@ -3322,8 +3284,10 @@
           <t>27925349.16970986</t>
         </is>
       </c>
-      <c r="BD7" t="n">
-        <v>223746689</v>
+      <c r="BD7" t="inlineStr">
+        <is>
+          <t>223746689.0</t>
+        </is>
       </c>
       <c r="BE7" t="inlineStr">
         <is>
@@ -3489,7 +3453,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -3673,15 +3637,11 @@
           <t>140.1</t>
         </is>
       </c>
-      <c r="AM8" t="inlineStr">
-        <is>
-          <t>151.12</t>
-        </is>
-      </c>
-      <c r="AN8" t="inlineStr">
-        <is>
-          <t>162.59</t>
-        </is>
+      <c r="AM8" t="n">
+        <v>151.12</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>162.59</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
@@ -3728,20 +3688,16 @@
           <t>373359683.0</t>
         </is>
       </c>
-      <c r="AX8" t="inlineStr">
-        <is>
-          <t>374444824.4</t>
-        </is>
+      <c r="AX8" t="n">
+        <v>374444824.4</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
           <t>252575891.8</t>
         </is>
       </c>
-      <c r="AZ8" t="inlineStr">
-        <is>
-          <t>255257682.72</t>
-        </is>
+      <c r="AZ8" t="n">
+        <v>255257682.72</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
@@ -3758,8 +3714,10 @@
           <t>40950935.056494</t>
         </is>
       </c>
-      <c r="BD8" t="n">
-        <v>373359683</v>
+      <c r="BD8" t="inlineStr">
+        <is>
+          <t>373359683.0</t>
+        </is>
       </c>
       <c r="BE8" t="inlineStr">
         <is>
@@ -3925,7 +3883,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -4109,15 +4067,11 @@
           <t>143.9</t>
         </is>
       </c>
-      <c r="AM9" t="inlineStr">
-        <is>
-          <t>152.65</t>
-        </is>
-      </c>
-      <c r="AN9" t="inlineStr">
-        <is>
-          <t>163.44</t>
-        </is>
+      <c r="AM9" t="n">
+        <v>152.65</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>163.44</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
@@ -4164,20 +4118,16 @@
           <t>543328425.0</t>
         </is>
       </c>
-      <c r="AX9" t="inlineStr">
-        <is>
-          <t>317370279.0</t>
-        </is>
+      <c r="AX9" t="n">
+        <v>317370279</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
           <t>231842549.9</t>
         </is>
       </c>
-      <c r="AZ9" t="inlineStr">
-        <is>
-          <t>254515985.98</t>
-        </is>
+      <c r="AZ9" t="n">
+        <v>254515985.98</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
@@ -4194,8 +4144,10 @@
           <t>42066417.85702515</t>
         </is>
       </c>
-      <c r="BD9" t="n">
-        <v>543328425</v>
+      <c r="BD9" t="inlineStr">
+        <is>
+          <t>543328425.0</t>
+        </is>
       </c>
       <c r="BE9" t="inlineStr">
         <is>
@@ -4361,7 +4313,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -4545,15 +4497,11 @@
           <t>147.2</t>
         </is>
       </c>
-      <c r="AM10" t="inlineStr">
-        <is>
-          <t>154.25</t>
-        </is>
-      </c>
-      <c r="AN10" t="inlineStr">
-        <is>
-          <t>164.29</t>
-        </is>
+      <c r="AM10" t="n">
+        <v>154.25</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>164.29</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
@@ -4600,20 +4548,16 @@
           <t>753939618.0</t>
         </is>
       </c>
-      <c r="AX10" t="inlineStr">
-        <is>
-          <t>239835367.0</t>
-        </is>
+      <c r="AX10" t="n">
+        <v>239835367</v>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
           <t>202283159.5</t>
         </is>
       </c>
-      <c r="AZ10" t="inlineStr">
-        <is>
-          <t>250790390.86</t>
-        </is>
+      <c r="AZ10" t="n">
+        <v>250790390.86</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
@@ -4630,8 +4574,10 @@
           <t>23946656.00574735</t>
         </is>
       </c>
-      <c r="BD10" t="n">
-        <v>753939618</v>
+      <c r="BD10" t="inlineStr">
+        <is>
+          <t>753939618.0</t>
+        </is>
       </c>
       <c r="BE10" t="inlineStr">
         <is>
@@ -4797,7 +4743,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -4981,15 +4927,11 @@
           <t>149.6</t>
         </is>
       </c>
-      <c r="AM11" t="inlineStr">
-        <is>
-          <t>155.78</t>
-        </is>
-      </c>
-      <c r="AN11" t="inlineStr">
-        <is>
-          <t>165.1</t>
-        </is>
+      <c r="AM11" t="n">
+        <v>155.78</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>165.1</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
@@ -5036,20 +4978,16 @@
           <t>92809478.0</t>
         </is>
       </c>
-      <c r="AX11" t="inlineStr">
-        <is>
-          <t>127850905.8</t>
-        </is>
+      <c r="AX11" t="n">
+        <v>127850905.8</v>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
           <t>148995940.1</t>
         </is>
       </c>
-      <c r="AZ11" t="inlineStr">
-        <is>
-          <t>248204610.78</t>
-        </is>
+      <c r="AZ11" t="n">
+        <v>248204610.78</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
@@ -5066,8 +5004,10 @@
           <t>-25359440.74628332</t>
         </is>
       </c>
-      <c r="BD11" t="n">
-        <v>92809478</v>
+      <c r="BD11" t="inlineStr">
+        <is>
+          <t>92809478.0</t>
+        </is>
       </c>
       <c r="BE11" t="inlineStr">
         <is>
@@ -5233,7 +5173,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -5417,15 +5357,11 @@
           <t>150.2</t>
         </is>
       </c>
-      <c r="AM12" t="inlineStr">
-        <is>
-          <t>156.57</t>
-        </is>
-      </c>
-      <c r="AN12" t="inlineStr">
-        <is>
-          <t>165.78</t>
-        </is>
+      <c r="AM12" t="n">
+        <v>156.57</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>165.78</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
@@ -5472,20 +5408,16 @@
           <t>108786918.0</t>
         </is>
       </c>
-      <c r="AX12" t="inlineStr">
-        <is>
-          <t>129166834.4</t>
-        </is>
+      <c r="AX12" t="n">
+        <v>129166834.4</v>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
           <t>167987433.4</t>
         </is>
       </c>
-      <c r="AZ12" t="inlineStr">
-        <is>
-          <t>261232164.76</t>
-        </is>
+      <c r="AZ12" t="n">
+        <v>261232164.76</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
@@ -5502,8 +5434,10 @@
           <t>-24055655.36538848</t>
         </is>
       </c>
-      <c r="BD12" t="n">
-        <v>108786918</v>
+      <c r="BD12" t="inlineStr">
+        <is>
+          <t>108786918.0</t>
+        </is>
       </c>
       <c r="BE12" t="inlineStr">
         <is>
@@ -5669,7 +5603,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -5853,15 +5787,11 @@
           <t>37.47</t>
         </is>
       </c>
-      <c r="AM13" t="inlineStr">
-        <is>
-          <t>38.08</t>
-        </is>
-      </c>
-      <c r="AN13" t="inlineStr">
-        <is>
-          <t>40.03</t>
-        </is>
+      <c r="AM13" t="n">
+        <v>38.08</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>40.03</v>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
@@ -5908,20 +5838,16 @@
           <t>35810040.0</t>
         </is>
       </c>
-      <c r="AX13" t="inlineStr">
-        <is>
-          <t>75499582.6</t>
-        </is>
+      <c r="AX13" t="n">
+        <v>75499582.59999999</v>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
           <t>55792550.2</t>
         </is>
       </c>
-      <c r="AZ13" t="inlineStr">
-        <is>
-          <t>33454972.78</t>
-        </is>
+      <c r="AZ13" t="n">
+        <v>33454972.78</v>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
@@ -5938,8 +5864,10 @@
           <t>7886638.29228013</t>
         </is>
       </c>
-      <c r="BD13" t="n">
-        <v>35810040</v>
+      <c r="BD13" t="inlineStr">
+        <is>
+          <t>35810040.0</t>
+        </is>
       </c>
       <c r="BE13" t="inlineStr">
         <is>
@@ -6105,7 +6033,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -6289,15 +6217,11 @@
           <t>36.87</t>
         </is>
       </c>
-      <c r="AM14" t="inlineStr">
-        <is>
-          <t>38.11</t>
-        </is>
-      </c>
-      <c r="AN14" t="inlineStr">
-        <is>
-          <t>40.07</t>
-        </is>
+      <c r="AM14" t="n">
+        <v>38.11</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>40.07</v>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
@@ -6344,20 +6268,16 @@
           <t>39561838.0</t>
         </is>
       </c>
-      <c r="AX14" t="inlineStr">
-        <is>
-          <t>77102277.8</t>
-        </is>
+      <c r="AX14" t="n">
+        <v>77102277.8</v>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
           <t>54515793.2</t>
         </is>
       </c>
-      <c r="AZ14" t="inlineStr">
-        <is>
-          <t>33864219.92</t>
-        </is>
+      <c r="AZ14" t="n">
+        <v>33864219.92</v>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
@@ -6374,8 +6294,10 @@
           <t>11730479.54280426</t>
         </is>
       </c>
-      <c r="BD14" t="n">
-        <v>39561838</v>
+      <c r="BD14" t="inlineStr">
+        <is>
+          <t>39561838.0</t>
+        </is>
       </c>
       <c r="BE14" t="inlineStr">
         <is>
@@ -6541,7 +6463,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -6725,15 +6647,11 @@
           <t>36.60000000000001</t>
         </is>
       </c>
-      <c r="AM15" t="inlineStr">
-        <is>
-          <t>38.22</t>
-        </is>
-      </c>
-      <c r="AN15" t="inlineStr">
-        <is>
-          <t>40.17</t>
-        </is>
+      <c r="AM15" t="n">
+        <v>38.22</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>40.17</v>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
@@ -6780,20 +6698,16 @@
           <t>232650449.0</t>
         </is>
       </c>
-      <c r="AX15" t="inlineStr">
-        <is>
-          <t>74142370.0</t>
-        </is>
+      <c r="AX15" t="n">
+        <v>74142370</v>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
           <t>57245793.0</t>
         </is>
       </c>
-      <c r="AZ15" t="inlineStr">
-        <is>
-          <t>34130931.06</t>
-        </is>
+      <c r="AZ15" t="n">
+        <v>34130931.06</v>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
@@ -6810,8 +6724,10 @@
           <t>16400757.27416717</t>
         </is>
       </c>
-      <c r="BD15" t="n">
-        <v>232650449</v>
+      <c r="BD15" t="inlineStr">
+        <is>
+          <t>232650449.0</t>
+        </is>
       </c>
       <c r="BE15" t="inlineStr">
         <is>
@@ -6977,7 +6893,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -7161,15 +7077,11 @@
           <t>36.61</t>
         </is>
       </c>
-      <c r="AM16" t="inlineStr">
-        <is>
-          <t>38.41</t>
-        </is>
-      </c>
-      <c r="AN16" t="inlineStr">
-        <is>
-          <t>40.3</t>
-        </is>
+      <c r="AM16" t="n">
+        <v>38.41</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>40.3</v>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
@@ -7216,20 +7128,16 @@
           <t>41298962.0</t>
         </is>
       </c>
-      <c r="AX16" t="inlineStr">
-        <is>
-          <t>35487232.0</t>
-        </is>
+      <c r="AX16" t="n">
+        <v>35487232</v>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
           <t>35914543.8</t>
         </is>
       </c>
-      <c r="AZ16" t="inlineStr">
-        <is>
-          <t>29950115.64</t>
-        </is>
+      <c r="AZ16" t="n">
+        <v>29950115.64</v>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
@@ -7246,8 +7154,10 @@
           <t>1798775.809179619</t>
         </is>
       </c>
-      <c r="BD16" t="n">
-        <v>41298962</v>
+      <c r="BD16" t="inlineStr">
+        <is>
+          <t>41298962.0</t>
+        </is>
       </c>
       <c r="BE16" t="inlineStr">
         <is>
@@ -7413,7 +7323,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -7597,15 +7507,11 @@
           <t>36.73</t>
         </is>
       </c>
-      <c r="AM17" t="inlineStr">
-        <is>
-          <t>38.6</t>
-        </is>
-      </c>
-      <c r="AN17" t="inlineStr">
-        <is>
-          <t>40.43</t>
-        </is>
+      <c r="AM17" t="n">
+        <v>38.6</v>
+      </c>
+      <c r="AN17" t="n">
+        <v>40.43</v>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
@@ -7652,20 +7558,16 @@
           <t>28176624.0</t>
         </is>
       </c>
-      <c r="AX17" t="inlineStr">
-        <is>
-          <t>37871124.0</t>
-        </is>
+      <c r="AX17" t="n">
+        <v>37871124</v>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
           <t>34509118.0</t>
         </is>
       </c>
-      <c r="AZ17" t="inlineStr">
-        <is>
-          <t>29545425.32</t>
-        </is>
+      <c r="AZ17" t="n">
+        <v>29545425.32</v>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
@@ -7682,8 +7584,10 @@
           <t>1376505.330298137</t>
         </is>
       </c>
-      <c r="BD17" t="n">
-        <v>28176624</v>
+      <c r="BD17" t="inlineStr">
+        <is>
+          <t>28176624.0</t>
+        </is>
       </c>
       <c r="BE17" t="inlineStr">
         <is>
@@ -7849,7 +7753,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -8033,15 +7937,11 @@
           <t>37.07000000000001</t>
         </is>
       </c>
-      <c r="AM18" t="inlineStr">
-        <is>
-          <t>38.8</t>
-        </is>
-      </c>
-      <c r="AN18" t="inlineStr">
-        <is>
-          <t>40.58</t>
-        </is>
+      <c r="AM18" t="n">
+        <v>38.8</v>
+      </c>
+      <c r="AN18" t="n">
+        <v>40.58</v>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
@@ -8088,20 +7988,16 @@
           <t>43823516.0</t>
         </is>
       </c>
-      <c r="AX18" t="inlineStr">
-        <is>
-          <t>36085517.8</t>
-        </is>
+      <c r="AX18" t="n">
+        <v>36085517.8</v>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
           <t>35025550.9</t>
         </is>
       </c>
-      <c r="AZ18" t="inlineStr">
-        <is>
-          <t>29409986.0</t>
-        </is>
+      <c r="AZ18" t="n">
+        <v>29409986</v>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
@@ -8118,8 +8014,10 @@
           <t>2130065.670099653</t>
         </is>
       </c>
-      <c r="BD18" t="n">
-        <v>43823516</v>
+      <c r="BD18" t="inlineStr">
+        <is>
+          <t>43823516.0</t>
+        </is>
       </c>
       <c r="BE18" t="inlineStr">
         <is>
@@ -8285,7 +8183,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -8469,15 +8367,11 @@
           <t>37.47000000000001</t>
         </is>
       </c>
-      <c r="AM19" t="inlineStr">
-        <is>
-          <t>39.02</t>
-        </is>
-      </c>
-      <c r="AN19" t="inlineStr">
-        <is>
-          <t>40.75</t>
-        </is>
+      <c r="AM19" t="n">
+        <v>39.02</v>
+      </c>
+      <c r="AN19" t="n">
+        <v>40.75</v>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
@@ -8524,20 +8418,16 @@
           <t>24762299.0</t>
         </is>
       </c>
-      <c r="AX19" t="inlineStr">
-        <is>
-          <t>31929308.6</t>
-        </is>
+      <c r="AX19" t="n">
+        <v>31929308.6</v>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
           <t>32595150.7</t>
         </is>
       </c>
-      <c r="AZ19" t="inlineStr">
-        <is>
-          <t>29130934.74</t>
-        </is>
+      <c r="AZ19" t="n">
+        <v>29130934.74</v>
       </c>
       <c r="BA19" t="inlineStr">
         <is>
@@ -8554,8 +8444,10 @@
           <t>1454053.953026839</t>
         </is>
       </c>
-      <c r="BD19" t="n">
-        <v>24762299</v>
+      <c r="BD19" t="inlineStr">
+        <is>
+          <t>24762299.0</t>
+        </is>
       </c>
       <c r="BE19" t="inlineStr">
         <is>
@@ -8721,7 +8613,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -8905,15 +8797,11 @@
           <t>37.65000000000001</t>
         </is>
       </c>
-      <c r="AM20" t="inlineStr">
-        <is>
-          <t>39.23</t>
-        </is>
-      </c>
-      <c r="AN20" t="inlineStr">
-        <is>
-          <t>40.9</t>
-        </is>
+      <c r="AM20" t="n">
+        <v>39.23</v>
+      </c>
+      <c r="AN20" t="n">
+        <v>40.9</v>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
@@ -8960,20 +8848,16 @@
           <t>39374759.0</t>
         </is>
       </c>
-      <c r="AX20" t="inlineStr">
-        <is>
-          <t>40349216.0</t>
-        </is>
+      <c r="AX20" t="n">
+        <v>40349216</v>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
           <t>31454761.9</t>
         </is>
       </c>
-      <c r="AZ20" t="inlineStr">
-        <is>
-          <t>29061426.18</t>
-        </is>
+      <c r="AZ20" t="n">
+        <v>29061426.18</v>
       </c>
       <c r="BA20" t="inlineStr">
         <is>
@@ -8990,8 +8874,10 @@
           <t>2478665.680314712</t>
         </is>
       </c>
-      <c r="BD20" t="n">
-        <v>39374759</v>
+      <c r="BD20" t="inlineStr">
+        <is>
+          <t>39374759.0</t>
+        </is>
       </c>
       <c r="BE20" t="inlineStr">
         <is>
@@ -9157,7 +9043,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -9341,15 +9227,11 @@
           <t>37.99</t>
         </is>
       </c>
-      <c r="AM21" t="inlineStr">
-        <is>
-          <t>39.42</t>
-        </is>
-      </c>
-      <c r="AN21" t="inlineStr">
-        <is>
-          <t>41.05</t>
-        </is>
+      <c r="AM21" t="n">
+        <v>39.42</v>
+      </c>
+      <c r="AN21" t="n">
+        <v>41.05</v>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
@@ -9396,20 +9278,16 @@
           <t>53218422.0</t>
         </is>
       </c>
-      <c r="AX21" t="inlineStr">
-        <is>
-          <t>36341855.6</t>
-        </is>
+      <c r="AX21" t="n">
+        <v>36341855.6</v>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
           <t>29562657.9</t>
         </is>
       </c>
-      <c r="AZ21" t="inlineStr">
-        <is>
-          <t>28846965.04</t>
-        </is>
+      <c r="AZ21" t="n">
+        <v>28846965.04</v>
       </c>
       <c r="BA21" t="inlineStr">
         <is>
@@ -9426,8 +9304,10 @@
           <t>2288252.230714723</t>
         </is>
       </c>
-      <c r="BD21" t="n">
-        <v>53218422</v>
+      <c r="BD21" t="inlineStr">
+        <is>
+          <t>53218422.0</t>
+        </is>
       </c>
       <c r="BE21" t="inlineStr">
         <is>
@@ -9593,7 +9473,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -9777,15 +9657,11 @@
           <t>38.31</t>
         </is>
       </c>
-      <c r="AM22" t="inlineStr">
-        <is>
-          <t>39.58</t>
-        </is>
-      </c>
-      <c r="AN22" t="inlineStr">
-        <is>
-          <t>41.17</t>
-        </is>
+      <c r="AM22" t="n">
+        <v>39.58</v>
+      </c>
+      <c r="AN22" t="n">
+        <v>41.17</v>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
@@ -9832,20 +9708,16 @@
           <t>19248593.0</t>
         </is>
       </c>
-      <c r="AX22" t="inlineStr">
-        <is>
-          <t>31147112.0</t>
-        </is>
+      <c r="AX22" t="n">
+        <v>31147112</v>
       </c>
       <c r="AY22" t="inlineStr">
         <is>
           <t>25871081.1</t>
         </is>
       </c>
-      <c r="AZ22" t="inlineStr">
-        <is>
-          <t>28091032.78</t>
-        </is>
+      <c r="AZ22" t="n">
+        <v>28091032.78</v>
       </c>
       <c r="BA22" t="inlineStr">
         <is>
@@ -9862,8 +9734,10 @@
           <t>451260.1159035005</t>
         </is>
       </c>
-      <c r="BD22" t="n">
-        <v>19248593</v>
+      <c r="BD22" t="inlineStr">
+        <is>
+          <t>19248593.0</t>
+        </is>
       </c>
       <c r="BE22" t="inlineStr">
         <is>
@@ -10029,7 +9903,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -10213,15 +10087,11 @@
           <t>38.46</t>
         </is>
       </c>
-      <c r="AM23" t="inlineStr">
-        <is>
-          <t>39.69</t>
-        </is>
-      </c>
-      <c r="AN23" t="inlineStr">
-        <is>
-          <t>41.29</t>
-        </is>
+      <c r="AM23" t="n">
+        <v>39.69</v>
+      </c>
+      <c r="AN23" t="n">
+        <v>41.29</v>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
@@ -10268,20 +10138,16 @@
           <t>23042470.0</t>
         </is>
       </c>
-      <c r="AX23" t="inlineStr">
-        <is>
-          <t>33965584.0</t>
-        </is>
+      <c r="AX23" t="n">
+        <v>33965584</v>
       </c>
       <c r="AY23" t="inlineStr">
         <is>
           <t>26178217.9</t>
         </is>
       </c>
-      <c r="AZ23" t="inlineStr">
-        <is>
-          <t>28206383.42</t>
-        </is>
+      <c r="AZ23" t="n">
+        <v>28206383.42</v>
       </c>
       <c r="BA23" t="inlineStr">
         <is>
@@ -10298,8 +10164,10 @@
           <t>1450493.769176625</t>
         </is>
       </c>
-      <c r="BD23" t="n">
-        <v>23042470</v>
+      <c r="BD23" t="inlineStr">
+        <is>
+          <t>23042470.0</t>
+        </is>
       </c>
       <c r="BE23" t="inlineStr">
         <is>

--- a/Result/checksun_type/塔架.xlsx
+++ b/Result/checksun_type/塔架.xlsx
@@ -883,12 +883,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2.48</t>
+          <t>-1.04</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>885.355</t>
+          <t>494.362</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>142.5</t>
+          <t>141.0</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-2.05</t>
+          <t>-1.84</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>-37.74</t>
+          <t>-47.22</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-39.87</t>
+          <t>-40.51</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -993,17 +993,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>3.66</t>
+          <t>2.04</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>0.36</t>
+          <t>-2.13</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1014,73 +1014,73 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>885</t>
+          <t>494</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>87.5</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>62.28</t>
+          <t>77.41</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>3.26</t>
+          <t>1.29</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>-4.63</t>
+          <t>-3.35</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>-8.6</t>
+          <t>-8.68</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>-6.19</t>
+          <t>-6.17</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>138.0</t>
+          <t>139.2</t>
         </is>
       </c>
       <c r="AM2" t="n">
-        <v>144.7</v>
+        <v>144.02</v>
       </c>
       <c r="AN2" t="n">
-        <v>158.31</v>
+        <v>157.72</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>168.75</t>
+          <t>168.09</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>7.75</t>
+          <t>12.54</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>-6.60</t>
+          <t>-6.06</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>-7.15</t>
+          <t>-6.93</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -1090,7 +1090,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-128.73</t>
+          <t>-127.86</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1100,43 +1100,43 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>1688943454.118026</t>
+          <t>1686680961.147857</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>126140252.0</t>
+          <t>70132250.0</t>
         </is>
       </c>
       <c r="AX2" t="n">
-        <v>179646773.6</v>
+        <v>151097591.6</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>288541776.1</t>
+          <t>286274053.3</t>
         </is>
       </c>
       <c r="AZ2" t="n">
-        <v>249860076.6</v>
+        <v>248269560.06</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>-108895002</t>
+          <t>-135176461</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>2645308.141590643</t>
+          <t>-1190585.570376122</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>-13008524.13905758</t>
+          <t>-22288000.98619333</t>
         </is>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
-          <t>126140252.0</t>
+          <t>70132250.0</t>
         </is>
       </c>
       <c r="BE2" t="inlineStr">
@@ -1156,7 +1156,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>-20.83</t>
+          <t>-21.67</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
@@ -1201,22 +1201,22 @@
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價跌量-</t>
         </is>
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>3.28</t>
+          <t>3.25</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
         <is>
-          <t>2.92</t>
+          <t>2.95</t>
         </is>
       </c>
       <c r="BU2" t="inlineStr">
@@ -1226,7 +1226,7 @@
       </c>
       <c r="BV2" t="inlineStr">
         <is>
-          <t>26.79</t>
+          <t>26.5</t>
         </is>
       </c>
       <c r="BW2" t="inlineStr">
@@ -1241,12 +1241,12 @@
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>29.71</t>
+          <t>29.67</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>35183</t>
+          <t>34812</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
@@ -1266,22 +1266,22 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
+          <t>144.0</t>
+        </is>
+      </c>
+      <c r="CE2" t="inlineStr">
+        <is>
+          <t>144.0</t>
+        </is>
+      </c>
+      <c r="CF2" t="inlineStr">
+        <is>
           <t>141.0</t>
         </is>
       </c>
-      <c r="CE2" t="inlineStr">
-        <is>
-          <t>143.5</t>
-        </is>
-      </c>
-      <c r="CF2" t="inlineStr">
+      <c r="CG2" t="inlineStr">
         <is>
           <t>141.0</t>
-        </is>
-      </c>
-      <c r="CG2" t="inlineStr">
-        <is>
-          <t>142.5</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
@@ -1303,7 +1303,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>【e】</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1313,127 +1313,127 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
+          <t>2.48</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>885.355</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>142.5</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>-1.06</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>-1.84</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>-37.74</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>-65.0</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>2025-06-04 00:00:00</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>2025-06-30 00:00:00</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>2025-05-09 00:00:00</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>2025-05-23 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>199.0</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>237.0</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>181.0</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>178.0</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>-39.87</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>11.80</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2025-11-26</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>3.66</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
           <t>0.36</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>1070.548</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>139.0</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>2.46</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>-2.05</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>-30.56</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>-65.0</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>2025-06-04 00:00:00</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>2025-06-30 00:00:00</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>2025-05-09 00:00:00</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>2025-05-23 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>199.0</t>
-        </is>
-      </c>
-      <c r="R3" t="inlineStr">
-        <is>
-          <t>237.0</t>
-        </is>
-      </c>
-      <c r="S3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T3" t="inlineStr">
-        <is>
-          <t>181.0</t>
-        </is>
-      </c>
-      <c r="U3" t="inlineStr">
-        <is>
-          <t>178.0</t>
-        </is>
-      </c>
-      <c r="V3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>-41.35</t>
-        </is>
-      </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>11.80</t>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr">
-        <is>
-          <t>2025-11-25</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>4.43</t>
-        </is>
-      </c>
-      <c r="AA3" t="inlineStr">
-        <is>
-          <t>-0.71</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1444,37 +1444,37 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>885</t>
+          <t>494</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>44.74</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>36.84</t>
+          <t>62.28</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>2.51</t>
+          <t>3.26</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>-6.71</t>
+          <t>-4.63</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-8.49</t>
+          <t>-8.6</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
@@ -1484,33 +1484,33 @@
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>135.6</t>
+          <t>138.0</t>
         </is>
       </c>
       <c r="AM3" t="n">
-        <v>145.35</v>
+        <v>144.7</v>
       </c>
       <c r="AN3" t="n">
-        <v>158.83</v>
+        <v>158.31</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>169.32</t>
+          <t>168.75</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>-0.61</t>
+          <t>7.75</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>-7.33</t>
+          <t>-6.60</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>-7.29</t>
+          <t>-7.15</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1520,7 +1520,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-129.29</t>
+          <t>-128.73</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1530,43 +1530,43 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>1688943454.118026</t>
+          <t>1686680961.147857</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>149355643.0</t>
+          <t>126140252.0</t>
         </is>
       </c>
       <c r="AX3" t="n">
-        <v>199168061</v>
+        <v>179646773.6</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>286806442.7</t>
+          <t>288541776.1</t>
         </is>
       </c>
       <c r="AZ3" t="n">
-        <v>252995092.08</v>
+        <v>249860076.6</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>-87638381</t>
+          <t>-108895002</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>5491459.465344865</t>
+          <t>2645308.141590643</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>-5288395.852468729</t>
+          <t>-13008524.13905758</t>
         </is>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
-          <t>149355643.0</t>
+          <t>126140252.0</t>
         </is>
       </c>
       <c r="BE3" t="inlineStr">
@@ -1586,7 +1586,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>-22.78</t>
+          <t>-20.83</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
@@ -1631,22 +1631,22 @@
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>3.20</t>
+          <t>3.28</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
         <is>
-          <t>2.92</t>
+          <t>2.95</t>
         </is>
       </c>
       <c r="BU3" t="inlineStr">
@@ -1656,7 +1656,7 @@
       </c>
       <c r="BV3" t="inlineStr">
         <is>
-          <t>26.79</t>
+          <t>26.5</t>
         </is>
       </c>
       <c r="BW3" t="inlineStr">
@@ -1671,12 +1671,12 @@
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>29.71</t>
+          <t>29.67</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
-          <t>35183</t>
+          <t>34812</t>
         </is>
       </c>
       <c r="CA3" t="inlineStr">
@@ -1696,22 +1696,22 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>139.5</t>
+          <t>141.0</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
+          <t>143.5</t>
+        </is>
+      </c>
+      <c r="CF3" t="inlineStr">
+        <is>
           <t>141.0</t>
         </is>
       </c>
-      <c r="CF3" t="inlineStr">
-        <is>
-          <t>138.0</t>
-        </is>
-      </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>139.0</t>
+          <t>142.5</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
@@ -1743,12 +1743,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>2.56</t>
+          <t>0.36</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>1721.237</t>
+          <t>1070.548</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1758,7 +1758,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>138.5</t>
+          <t>139.0</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1768,17 +1768,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2.81</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-2.05</t>
+          <t>-1.84</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>-13.08</t>
+          <t>-30.56</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1843,7 +1843,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-41.56</t>
+          <t>-41.35</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1853,17 +1853,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>7.12</t>
+          <t>4.43</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>1.87</t>
+          <t>-0.71</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1874,73 +1874,73 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>885</t>
+          <t>494</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>42.11</t>
+          <t>44.74</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>29.62</t>
+          <t>36.84</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>3.44</t>
+          <t>2.51</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>-8.46</t>
+          <t>-6.71</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>-8.28</t>
+          <t>-8.49</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>-6.17</t>
+          <t>-6.19</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>133.9</t>
+          <t>135.6</t>
         </is>
       </c>
       <c r="AM4" t="n">
-        <v>146.28</v>
+        <v>145.35</v>
       </c>
       <c r="AN4" t="n">
-        <v>159.48</v>
+        <v>158.83</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>169.96</t>
+          <t>169.32</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>-7.31</t>
+          <t>-0.61</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>-7.81</t>
+          <t>-7.33</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>-7.28</t>
+          <t>-7.29</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1950,7 +1950,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-129.24</t>
+          <t>-129.29</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1960,43 +1960,43 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>1688943454.118026</t>
+          <t>1686680961.147857</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>236429825.0</t>
+          <t>149355643.0</t>
         </is>
       </c>
       <c r="AX4" t="n">
-        <v>243968869</v>
+        <v>199168061</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>280669574.0</t>
+          <t>286806442.7</t>
         </is>
       </c>
       <c r="AZ4" t="n">
-        <v>255272113.08</v>
+        <v>252995092.08</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>-36700705</t>
+          <t>-87638381</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>7451433.159492791</t>
+          <t>5491459.465344865</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>3441866.801674962</t>
+          <t>-5288395.852468729</t>
         </is>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
-          <t>236429825.0</t>
+          <t>149355643.0</t>
         </is>
       </c>
       <c r="BE4" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>-23.06</t>
+          <t>-22.78</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;可能出現反轉訊號&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;3&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
@@ -2071,12 +2071,12 @@
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>3.19</t>
+          <t>3.20</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
         <is>
-          <t>2.92</t>
+          <t>2.95</t>
         </is>
       </c>
       <c r="BU4" t="inlineStr">
@@ -2086,7 +2086,7 @@
       </c>
       <c r="BV4" t="inlineStr">
         <is>
-          <t>26.79</t>
+          <t>26.5</t>
         </is>
       </c>
       <c r="BW4" t="inlineStr">
@@ -2101,12 +2101,12 @@
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>29.71</t>
+          <t>29.67</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
-          <t>35183</t>
+          <t>34812</t>
         </is>
       </c>
       <c r="CA4" t="inlineStr">
@@ -2126,22 +2126,22 @@
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>136.5</t>
+          <t>139.5</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>139.5</t>
+          <t>141.0</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>135.0</t>
+          <t>138.0</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>138.5</t>
+          <t>139.0</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
@@ -2173,12 +2173,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>2.56</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>1302.953</t>
+          <t>1721.237</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2188,7 +2188,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>135.0</t>
+          <t>138.5</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2198,17 +2198,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>5.26</t>
+          <t>1.77</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-2.05</t>
+          <t>-1.84</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>12.02</t>
+          <t>-13.08</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2273,7 +2273,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-43.04</t>
+          <t>-41.56</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2283,17 +2283,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>5.39</t>
+          <t>7.12</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>3.05</t>
+          <t>1.87</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2304,73 +2304,73 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>885</t>
+          <t>494</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>23.68</t>
+          <t>42.11</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>15.59</t>
+          <t>29.62</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>1.58</t>
+          <t>3.44</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>-9.76</t>
+          <t>-8.46</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>-8.05</t>
+          <t>-8.28</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>-6.11</t>
+          <t>-6.17</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>132.9</t>
+          <t>133.9</t>
         </is>
       </c>
       <c r="AM5" t="n">
-        <v>147.28</v>
+        <v>146.28</v>
       </c>
       <c r="AN5" t="n">
-        <v>160.17</v>
+        <v>159.48</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>170.59</t>
+          <t>169.96</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>-15.53</t>
+          <t>-7.31</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>-8.25</t>
+          <t>-7.81</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>-7.14</t>
+          <t>-7.28</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -2380,7 +2380,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-128.71</t>
+          <t>-129.24</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2390,43 +2390,43 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>1688943454.118026</t>
+          <t>1686680961.147857</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>173429988.0</t>
+          <t>236429825.0</t>
         </is>
       </c>
       <c r="AX5" t="n">
-        <v>305348589</v>
+        <v>243968869</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>272591978.0</t>
+          <t>280669574.0</t>
         </is>
       </c>
       <c r="AZ5" t="n">
-        <v>254388028.92</v>
+        <v>255272113.08</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>32756611</t>
+          <t>-36700705</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>8180445.224550578</t>
+          <t>7451433.159492791</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>6461370.136106104</t>
+          <t>3441866.801674962</t>
         </is>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
-          <t>173429988.0</t>
+          <t>236429825.0</t>
         </is>
       </c>
       <c r="BE5" t="inlineStr">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>-25.00</t>
+          <t>-23.06</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
@@ -2491,7 +2491,7 @@
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;可能出現反轉訊號&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;3&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
@@ -2501,12 +2501,12 @@
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>3.11</t>
+          <t>3.19</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
         <is>
-          <t>2.92</t>
+          <t>2.95</t>
         </is>
       </c>
       <c r="BU5" t="inlineStr">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="BV5" t="inlineStr">
         <is>
-          <t>26.79</t>
+          <t>26.5</t>
         </is>
       </c>
       <c r="BW5" t="inlineStr">
@@ -2531,12 +2531,12 @@
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>29.71</t>
+          <t>29.67</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
-          <t>35183</t>
+          <t>34812</t>
         </is>
       </c>
       <c r="CA5" t="inlineStr">
@@ -2556,22 +2556,22 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>132.5</t>
+          <t>136.5</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
+          <t>139.5</t>
+        </is>
+      </c>
+      <c r="CF5" t="inlineStr">
+        <is>
           <t>135.0</t>
         </is>
       </c>
-      <c r="CF5" t="inlineStr">
-        <is>
-          <t>131.0</t>
-        </is>
-      </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>135.0</t>
+          <t>138.5</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
@@ -2603,12 +2603,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>3.41</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>1595.31</t>
+          <t>1302.953</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2628,17 +2628,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>5.26</t>
+          <t>4.26</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-2.05</t>
+          <t>-1.84</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>53.45</t>
+          <t>12.02</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2713,17 +2713,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>6.60</t>
+          <t>5.39</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>1.92</t>
+          <t>3.05</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2734,73 +2734,73 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>885</t>
+          <t>494</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>23.08</t>
+          <t>23.68</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>7.69</t>
+          <t>15.59</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>1.20</t>
+          <t>1.58</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>-10.06</t>
+          <t>-9.76</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>-7.84</t>
+          <t>-8.05</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>-6.04</t>
+          <t>-6.11</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>133.4</t>
+          <t>132.9</t>
         </is>
       </c>
       <c r="AM6" t="n">
-        <v>148.32</v>
+        <v>147.28</v>
       </c>
       <c r="AN6" t="n">
-        <v>160.95</v>
+        <v>160.17</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>171.29</t>
+          <t>170.59</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>-21.52</t>
+          <t>-15.53</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>-8.35</t>
+          <t>-8.25</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>-6.87</t>
+          <t>-7.14</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -2810,7 +2810,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-127.59</t>
+          <t>-128.71</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2820,43 +2820,43 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>1688943454.118026</t>
+          <t>1686680961.147857</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>212878160.0</t>
+          <t>173429988.0</t>
         </is>
       </c>
       <c r="AX6" t="n">
-        <v>421450515</v>
+        <v>305348589</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>274650710.4</t>
+          <t>272591978.0</t>
         </is>
       </c>
       <c r="AZ6" t="n">
-        <v>254522728.7</v>
+        <v>254388028.92</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>146799804</t>
+          <t>32756611</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>8493004.331540482</t>
+          <t>8180445.224550578</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>17294165.64471823</t>
+          <t>6461370.136106104</t>
         </is>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
-          <t>212878160.0</t>
+          <t>173429988.0</t>
         </is>
       </c>
       <c r="BE6" t="inlineStr">
@@ -2921,12 +2921,12 @@
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;可能出現反轉訊號&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;3&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS6" t="inlineStr">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="BT6" t="inlineStr">
         <is>
-          <t>2.92</t>
+          <t>2.95</t>
         </is>
       </c>
       <c r="BU6" t="inlineStr">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="BV6" t="inlineStr">
         <is>
-          <t>26.79</t>
+          <t>26.5</t>
         </is>
       </c>
       <c r="BW6" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>29.71</t>
+          <t>29.67</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
         <is>
-          <t>35183</t>
+          <t>34812</t>
         </is>
       </c>
       <c r="CA6" t="inlineStr">
@@ -2986,17 +2986,17 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>132.0</t>
+          <t>132.5</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>136.0</t>
+          <t>135.0</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>131.5</t>
+          <t>131.0</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
@@ -3033,12 +3033,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>3.41</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1712.06</t>
+          <t>1595.31</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3048,7 +3048,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>130.5</t>
+          <t>135.0</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3058,17 +3058,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>8.42</t>
+          <t>4.26</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-2.05</t>
+          <t>-1.84</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>50.94</t>
+          <t>53.45</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3133,7 +3133,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-44.94</t>
+          <t>-43.04</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3143,17 +3143,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>7.08</t>
+          <t>6.60</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>-1.14</t>
+          <t>1.92</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3164,73 +3164,73 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>885</t>
+          <t>494</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>23.08</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>7.69</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>-4.26</t>
+          <t>1.20</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>-8.89</t>
+          <t>-10.06</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>-7.5</t>
+          <t>-7.84</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>-5.97</t>
+          <t>-6.04</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>136.3</t>
+          <t>133.4</t>
         </is>
       </c>
       <c r="AM7" t="n">
-        <v>149.6</v>
+        <v>148.32</v>
       </c>
       <c r="AN7" t="n">
-        <v>161.73</v>
+        <v>160.95</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>171.99</t>
+          <t>171.29</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>-28.35</t>
+          <t>-21.52</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>-8.34</t>
+          <t>-8.35</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>-6.50</t>
+          <t>-6.87</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -3240,7 +3240,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-126.11</t>
+          <t>-127.59</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3250,43 +3250,43 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>1688943454.118026</t>
+          <t>1686680961.147857</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>223746689.0</t>
+          <t>212878160.0</t>
         </is>
       </c>
       <c r="AX7" t="n">
-        <v>397436778.6</v>
+        <v>421450515</v>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>263301806.5</t>
+          <t>274650710.4</t>
         </is>
       </c>
       <c r="AZ7" t="n">
-        <v>254911229.58</v>
+        <v>254522728.7</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>134134972</t>
+          <t>146799804</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>6892793.183689982</t>
+          <t>8493004.331540482</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>27925349.16970986</t>
+          <t>17294165.64471823</t>
         </is>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
-          <t>223746689.0</t>
+          <t>212878160.0</t>
         </is>
       </c>
       <c r="BE7" t="inlineStr">
@@ -3306,7 +3306,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>-27.50</t>
+          <t>-25.00</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
@@ -3351,22 +3351,22 @@
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;可能出現反轉訊號&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;3&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
         <is>
-          <t>價漲量縮</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>3.01</t>
+          <t>3.11</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
         <is>
-          <t>2.92</t>
+          <t>2.95</t>
         </is>
       </c>
       <c r="BU7" t="inlineStr">
@@ -3376,7 +3376,7 @@
       </c>
       <c r="BV7" t="inlineStr">
         <is>
-          <t>26.79</t>
+          <t>26.5</t>
         </is>
       </c>
       <c r="BW7" t="inlineStr">
@@ -3391,12 +3391,12 @@
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>29.71</t>
+          <t>29.67</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
         <is>
-          <t>35183</t>
+          <t>34812</t>
         </is>
       </c>
       <c r="CA7" t="inlineStr">
@@ -3416,22 +3416,22 @@
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>131.0</t>
+          <t>132.0</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>133.5</t>
+          <t>136.0</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>129.0</t>
+          <t>131.5</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>130.5</t>
+          <t>135.0</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
@@ -3463,12 +3463,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>-2.26</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2844.986</t>
+          <t>1712.06</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3488,17 +3488,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>8.42</t>
+          <t>7.45</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-2.05</t>
+          <t>-1.84</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>48.25</t>
+          <t>50.94</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3573,17 +3573,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>11.77</t>
+          <t>7.08</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>-2.29</t>
+          <t>-1.14</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3594,12 +3594,12 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>885</t>
+          <t>494</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
@@ -3614,53 +3614,53 @@
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>-6.85</t>
+          <t>-4.26</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>-7.30</t>
+          <t>-8.89</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>-7.05</t>
+          <t>-7.5</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>-5.89</t>
+          <t>-5.97</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>140.1</t>
+          <t>136.3</t>
         </is>
       </c>
       <c r="AM8" t="n">
-        <v>151.12</v>
+        <v>149.6</v>
       </c>
       <c r="AN8" t="n">
-        <v>162.59</v>
+        <v>161.73</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>172.77</t>
+          <t>171.99</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>-28.43</t>
+          <t>-28.35</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>-7.75</t>
+          <t>-8.34</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>-6.04</t>
+          <t>-6.50</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -3670,7 +3670,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-124.26</t>
+          <t>-126.11</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3680,43 +3680,43 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>1688943454.118026</t>
+          <t>1686680961.147857</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>373359683.0</t>
+          <t>223746689.0</t>
         </is>
       </c>
       <c r="AX8" t="n">
-        <v>374444824.4</v>
+        <v>397436778.6</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>252575891.8</t>
+          <t>263301806.5</t>
         </is>
       </c>
       <c r="AZ8" t="n">
-        <v>255257682.72</v>
+        <v>254911229.58</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>121868932</t>
+          <t>134134972</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>3068692.09532273</t>
+          <t>6892793.183689982</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>40950935.056494</t>
+          <t>27925349.16970986</t>
         </is>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
-          <t>373359683.0</t>
+          <t>223746689.0</t>
         </is>
       </c>
       <c r="BE8" t="inlineStr">
@@ -3781,12 +3781,12 @@
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價漲量縮</t>
         </is>
       </c>
       <c r="BS8" t="inlineStr">
@@ -3796,7 +3796,7 @@
       </c>
       <c r="BT8" t="inlineStr">
         <is>
-          <t>2.92</t>
+          <t>2.95</t>
         </is>
       </c>
       <c r="BU8" t="inlineStr">
@@ -3806,7 +3806,7 @@
       </c>
       <c r="BV8" t="inlineStr">
         <is>
-          <t>26.79</t>
+          <t>26.5</t>
         </is>
       </c>
       <c r="BW8" t="inlineStr">
@@ -3821,12 +3821,12 @@
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>29.71</t>
+          <t>29.67</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
         <is>
-          <t>35183</t>
+          <t>34812</t>
         </is>
       </c>
       <c r="CA8" t="inlineStr">
@@ -3846,17 +3846,17 @@
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>133.0</t>
+          <t>131.0</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>134.5</t>
+          <t>133.5</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>129.5</t>
+          <t>129.0</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
@@ -3893,12 +3893,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>-2.96</t>
+          <t>-2.26</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>4003.393</t>
+          <t>2844.986</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3908,7 +3908,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>133.5</t>
+          <t>130.5</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3918,17 +3918,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>6.32</t>
+          <t>7.45</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-2.05</t>
+          <t>-1.84</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>36.89</t>
+          <t>48.25</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3993,7 +3993,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-43.67</t>
+          <t>-44.94</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4003,17 +4003,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>16.56</t>
+          <t>11.77</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>-5.24</t>
+          <t>-2.29</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4024,12 +4024,12 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>885</t>
+          <t>494</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
@@ -4044,53 +4044,53 @@
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>-7.23</t>
+          <t>-6.85</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>-5.73</t>
+          <t>-7.30</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>-6.6</t>
+          <t>-7.05</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>-5.82</t>
+          <t>-5.89</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>143.9</t>
+          <t>140.1</t>
         </is>
       </c>
       <c r="AM9" t="n">
-        <v>152.65</v>
+        <v>151.12</v>
       </c>
       <c r="AN9" t="n">
-        <v>163.44</v>
+        <v>162.59</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>173.54</t>
+          <t>172.77</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>-22.90</t>
+          <t>-28.43</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>-6.89</t>
+          <t>-7.75</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>-5.61</t>
+          <t>-6.04</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -4100,7 +4100,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-122.53</t>
+          <t>-124.26</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4110,43 +4110,43 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>1688943454.118026</t>
+          <t>1686680961.147857</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>543328425.0</t>
+          <t>373359683.0</t>
         </is>
       </c>
       <c r="AX9" t="n">
-        <v>317370279</v>
+        <v>374444824.4</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>231842549.9</t>
+          <t>252575891.8</t>
         </is>
       </c>
       <c r="AZ9" t="n">
-        <v>254515985.98</v>
+        <v>255257682.72</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>85527729</t>
+          <t>121868932</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>-3818988.443072045</t>
+          <t>3068692.09532273</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>42066417.85702515</t>
+          <t>40950935.056494</t>
         </is>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
-          <t>543328425.0</t>
+          <t>373359683.0</t>
         </is>
       </c>
       <c r="BE9" t="inlineStr">
@@ -4166,7 +4166,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>-25.83</t>
+          <t>-27.50</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
@@ -4211,7 +4211,7 @@
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;衝高回落,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
@@ -4221,12 +4221,12 @@
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>3.08</t>
+          <t>3.01</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
         <is>
-          <t>2.92</t>
+          <t>2.95</t>
         </is>
       </c>
       <c r="BU9" t="inlineStr">
@@ -4236,7 +4236,7 @@
       </c>
       <c r="BV9" t="inlineStr">
         <is>
-          <t>26.79</t>
+          <t>26.5</t>
         </is>
       </c>
       <c r="BW9" t="inlineStr">
@@ -4251,12 +4251,12 @@
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>29.71</t>
+          <t>29.67</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
         <is>
-          <t>35183</t>
+          <t>34812</t>
         </is>
       </c>
       <c r="CA9" t="inlineStr">
@@ -4276,22 +4276,22 @@
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>135.0</t>
+          <t>133.0</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>141.5</t>
+          <t>134.5</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>132.5</t>
+          <t>129.5</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>133.5</t>
+          <t>130.5</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
@@ -4323,12 +4323,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>-8.16</t>
+          <t>-2.96</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>5388.546</t>
+          <t>4003.393</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4338,7 +4338,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>137.5</t>
+          <t>133.5</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4348,17 +4348,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>3.51</t>
+          <t>5.32</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-2.05</t>
+          <t>-1.84</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>18.56</t>
+          <t>36.89</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4423,7 +4423,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-41.98</t>
+          <t>-43.67</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4433,17 +4433,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>22.28</t>
+          <t>16.56</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>-5.06</t>
+          <t>-5.24</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4454,12 +4454,12 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>885</t>
+          <t>494</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
@@ -4474,53 +4474,53 @@
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>-6.59</t>
+          <t>-7.23</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>-4.57</t>
+          <t>-5.73</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>-6.11</t>
+          <t>-6.6</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>-5.70</t>
+          <t>-5.82</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>147.2</t>
+          <t>143.9</t>
         </is>
       </c>
       <c r="AM10" t="n">
-        <v>154.25</v>
+        <v>152.65</v>
       </c>
       <c r="AN10" t="n">
-        <v>164.29</v>
+        <v>163.44</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>174.21</t>
+          <t>173.54</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>-13.45</t>
+          <t>-22.90</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>-6.00</t>
+          <t>-6.89</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>-5.29</t>
+          <t>-5.61</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -4530,7 +4530,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-121.24</t>
+          <t>-122.53</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4540,43 +4540,43 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>1688943454.118026</t>
+          <t>1686680961.147857</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>753939618.0</t>
+          <t>543328425.0</t>
         </is>
       </c>
       <c r="AX10" t="n">
-        <v>239835367</v>
+        <v>317370279</v>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>202283159.5</t>
+          <t>231842549.9</t>
         </is>
       </c>
       <c r="AZ10" t="n">
-        <v>250790390.86</v>
+        <v>254515985.98</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>37552207</t>
+          <t>85527729</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>-12161789.58854426</t>
+          <t>-3818988.443072045</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>23946656.00574735</t>
+          <t>42066417.85702515</t>
         </is>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
-          <t>753939618.0</t>
+          <t>543328425.0</t>
         </is>
       </c>
       <c r="BE10" t="inlineStr">
@@ -4596,7 +4596,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>-23.61</t>
+          <t>-25.83</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
@@ -4641,7 +4641,7 @@
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;衝高回落,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
@@ -4651,12 +4651,12 @@
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>3.17</t>
+          <t>3.08</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
         <is>
-          <t>2.92</t>
+          <t>2.95</t>
         </is>
       </c>
       <c r="BU10" t="inlineStr">
@@ -4666,7 +4666,7 @@
       </c>
       <c r="BV10" t="inlineStr">
         <is>
-          <t>26.79</t>
+          <t>26.5</t>
         </is>
       </c>
       <c r="BW10" t="inlineStr">
@@ -4681,12 +4681,12 @@
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>29.71</t>
+          <t>29.67</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
         <is>
-          <t>35183</t>
+          <t>34812</t>
         </is>
       </c>
       <c r="CA10" t="inlineStr">
@@ -4706,22 +4706,22 @@
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>147.0</t>
+          <t>135.0</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>147.0</t>
+          <t>141.5</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>135.0</t>
+          <t>132.5</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>137.5</t>
+          <t>133.5</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
@@ -4753,12 +4753,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-8.16</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>617.888</t>
+          <t>5388.546</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4768,7 +4768,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>149.5</t>
+          <t>137.5</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4778,17 +4778,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-4.91</t>
+          <t>2.48</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-2.05</t>
+          <t>-1.84</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>-14.19</t>
+          <t>18.56</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4853,7 +4853,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-36.92</t>
+          <t>-41.98</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4863,17 +4863,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>2.56</t>
+          <t>22.28</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>-1.34</t>
+          <t>-5.06</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4884,12 +4884,12 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>885</t>
+          <t>494</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
@@ -4904,53 +4904,53 @@
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>-0.07</t>
+          <t>-6.59</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>-3.96</t>
+          <t>-4.57</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>-5.65</t>
+          <t>-6.11</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>-5.63</t>
+          <t>-5.70</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>149.6</t>
+          <t>147.2</t>
         </is>
       </c>
       <c r="AM11" t="n">
-        <v>155.78</v>
+        <v>154.25</v>
       </c>
       <c r="AN11" t="n">
-        <v>165.1</v>
+        <v>164.29</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>174.95</t>
+          <t>174.21</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>-1.33</t>
+          <t>-13.45</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>-5.18</t>
+          <t>-6.00</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>-5.11</t>
+          <t>-5.29</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -4960,7 +4960,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-120.53</t>
+          <t>-121.24</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -4970,43 +4970,43 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>1688943454.118026</t>
+          <t>1686680961.147857</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>92809478.0</t>
+          <t>753939618.0</t>
         </is>
       </c>
       <c r="AX11" t="n">
-        <v>127850905.8</v>
+        <v>239835367</v>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>148995940.1</t>
+          <t>202283159.5</t>
         </is>
       </c>
       <c r="AZ11" t="n">
-        <v>248204610.78</v>
+        <v>250790390.86</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>-21145034</t>
+          <t>37552207</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>-18726961.5147791</t>
+          <t>-12161789.58854426</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>-25359440.74628332</t>
+          <t>23946656.00574735</t>
         </is>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
-          <t>92809478.0</t>
+          <t>753939618.0</t>
         </is>
       </c>
       <c r="BE11" t="inlineStr">
@@ -5026,7 +5026,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>-16.94</t>
+          <t>-23.61</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
@@ -5081,12 +5081,12 @@
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>3.44</t>
+          <t>3.17</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
         <is>
-          <t>2.92</t>
+          <t>2.95</t>
         </is>
       </c>
       <c r="BU11" t="inlineStr">
@@ -5096,7 +5096,7 @@
       </c>
       <c r="BV11" t="inlineStr">
         <is>
-          <t>26.79</t>
+          <t>26.5</t>
         </is>
       </c>
       <c r="BW11" t="inlineStr">
@@ -5111,12 +5111,12 @@
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>29.71</t>
+          <t>29.67</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
         <is>
-          <t>35183</t>
+          <t>34812</t>
         </is>
       </c>
       <c r="CA11" t="inlineStr">
@@ -5136,22 +5136,22 @@
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>150.0</t>
+          <t>147.0</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>151.5</t>
+          <t>147.0</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>149.5</t>
+          <t>135.0</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>149.5</t>
+          <t>137.5</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
@@ -5188,7 +5188,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>723.545</t>
+          <t>617.888</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5208,17 +5208,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-4.91</t>
+          <t>-6.03</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-2.05</t>
+          <t>-1.84</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>-23.11</t>
+          <t>-14.19</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5293,17 +5293,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>2.99</t>
+          <t>2.56</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>-1.67</t>
+          <t>-1.34</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5314,12 +5314,12 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>885</t>
+          <t>494</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
@@ -5329,58 +5329,58 @@
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>2.22</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>-0.47</t>
+          <t>-0.07</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>-4.07</t>
+          <t>-3.96</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>-5.55</t>
+          <t>-5.65</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>-5.58</t>
+          <t>-5.63</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>150.2</t>
+          <t>149.6</t>
         </is>
       </c>
       <c r="AM12" t="n">
-        <v>156.57</v>
+        <v>155.78</v>
       </c>
       <c r="AN12" t="n">
-        <v>165.78</v>
+        <v>165.1</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>175.58</t>
+          <t>174.95</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>-3.60</t>
+          <t>-1.33</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>-5.28</t>
+          <t>-5.18</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>-5.09</t>
+          <t>-5.11</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
@@ -5390,7 +5390,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-120.46</t>
+          <t>-120.53</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5400,43 +5400,43 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>1688943454.118026</t>
+          <t>1686680961.147857</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>108786918.0</t>
+          <t>92809478.0</t>
         </is>
       </c>
       <c r="AX12" t="n">
-        <v>129166834.4</v>
+        <v>127850905.8</v>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>167987433.4</t>
+          <t>148995940.1</t>
         </is>
       </c>
       <c r="AZ12" t="n">
-        <v>261232164.76</v>
+        <v>248204610.78</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>-38820599</t>
+          <t>-21145034</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>-17521056.19996015</t>
+          <t>-18726961.5147791</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>-24055655.36538848</t>
+          <t>-25359440.74628332</t>
         </is>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
-          <t>108786918.0</t>
+          <t>92809478.0</t>
         </is>
       </c>
       <c r="BE12" t="inlineStr">
@@ -5501,7 +5501,7 @@
       </c>
       <c r="BQ12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR12" t="inlineStr">
@@ -5516,7 +5516,7 @@
       </c>
       <c r="BT12" t="inlineStr">
         <is>
-          <t>2.92</t>
+          <t>2.95</t>
         </is>
       </c>
       <c r="BU12" t="inlineStr">
@@ -5526,7 +5526,7 @@
       </c>
       <c r="BV12" t="inlineStr">
         <is>
-          <t>26.79</t>
+          <t>26.5</t>
         </is>
       </c>
       <c r="BW12" t="inlineStr">
@@ -5541,12 +5541,12 @@
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>29.71</t>
+          <t>29.67</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
         <is>
-          <t>35183</t>
+          <t>34812</t>
         </is>
       </c>
       <c r="CA12" t="inlineStr">
@@ -5566,17 +5566,17 @@
       </c>
       <c r="CD12" t="inlineStr">
         <is>
+          <t>150.0</t>
+        </is>
+      </c>
+      <c r="CE12" t="inlineStr">
+        <is>
           <t>151.5</t>
         </is>
       </c>
-      <c r="CE12" t="inlineStr">
-        <is>
-          <t>152.5</t>
-        </is>
-      </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>149.0</t>
+          <t>149.5</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
@@ -5613,12 +5613,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>2.61</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>914.803</t>
+          <t>510.601</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -5643,12 +5643,12 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>0.91</t>
+          <t>1.07</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>35.32</t>
+          <t>32.21</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -5723,17 +5723,17 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>9.75</t>
+          <t>5.44</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>1.47</t>
+          <t>0.39</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
@@ -5744,12 +5744,12 @@
       <c r="AC13" t="inlineStr"/>
       <c r="AD13" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
-          <t>915</t>
+          <t>511</t>
         </is>
       </c>
       <c r="AF13" t="inlineStr">
@@ -5759,58 +5759,58 @@
       </c>
       <c r="AG13" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>4.35</t>
+          <t>2.87</t>
         </is>
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>-1.59</t>
+          <t>-0.09</t>
         </is>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>-4.88</t>
+          <t>-4.82</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>-2.87</t>
+          <t>-2.98</t>
         </is>
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>37.47</t>
+          <t>38.01000000000001</t>
         </is>
       </c>
       <c r="AM13" t="n">
-        <v>38.08</v>
+        <v>38.04</v>
       </c>
       <c r="AN13" t="n">
-        <v>40.03</v>
+        <v>39.97</v>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>41.21</t>
+          <t>41.2</t>
         </is>
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>20.99</t>
+          <t>33.12</t>
         </is>
       </c>
       <c r="AQ13" t="inlineStr">
         <is>
-          <t>-0.75</t>
+          <t>-0.59</t>
         </is>
       </c>
       <c r="AR13" t="inlineStr">
         <is>
-          <t>-0.95</t>
+          <t>-0.88</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr">
@@ -5820,7 +5820,7 @@
       </c>
       <c r="AT13" t="inlineStr">
         <is>
-          <t>-135.29</t>
+          <t>-132.60</t>
         </is>
       </c>
       <c r="AU13" t="inlineStr">
@@ -5830,43 +5830,43 @@
       </c>
       <c r="AV13" t="inlineStr">
         <is>
-          <t>150423914.0772532</t>
+          <t>150251779.8621429</t>
         </is>
       </c>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>35810040.0</t>
+          <t>19953309.0</t>
         </is>
       </c>
       <c r="AX13" t="n">
-        <v>75499582.59999999</v>
+        <v>73854919.59999999</v>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>55792550.2</t>
+          <t>55863021.8</t>
         </is>
       </c>
       <c r="AZ13" t="n">
-        <v>33454972.78</v>
+        <v>33328621.84</v>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
-          <t>19707032</t>
+          <t>17991897</t>
         </is>
       </c>
       <c r="BB13" t="inlineStr">
         <is>
-          <t>5205041.104487866</t>
+          <t>4990346.878352229</t>
         </is>
       </c>
       <c r="BC13" t="inlineStr">
         <is>
-          <t>7886638.29228013</t>
+          <t>3809528.634606227</t>
         </is>
       </c>
       <c r="BD13" t="inlineStr">
         <is>
-          <t>35810040.0</t>
+          <t>19953309.0</t>
         </is>
       </c>
       <c r="BE13" t="inlineStr">
@@ -5931,12 +5931,12 @@
       </c>
       <c r="BQ13" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR13" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量縮</t>
         </is>
       </c>
       <c r="BS13" t="inlineStr">
@@ -5971,7 +5971,7 @@
       </c>
       <c r="BY13" t="inlineStr">
         <is>
-          <t>29.71</t>
+          <t>29.67</t>
         </is>
       </c>
       <c r="BZ13" t="inlineStr">
@@ -5996,17 +5996,17 @@
       </c>
       <c r="CD13" t="inlineStr">
         <is>
-          <t>38.3</t>
+          <t>39.15</t>
         </is>
       </c>
       <c r="CE13" t="inlineStr">
         <is>
-          <t>39.5</t>
+          <t>39.3</t>
         </is>
       </c>
       <c r="CF13" t="inlineStr">
         <is>
-          <t>38.15</t>
+          <t>38.75</t>
         </is>
       </c>
       <c r="CG13" t="inlineStr">
@@ -6043,12 +6043,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>3.24</t>
+          <t>2.61</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>1043.085</t>
+          <t>914.803</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -6058,7 +6058,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>38.1</t>
+          <t>39.1</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -6068,17 +6068,17 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>2.56</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>0.91</t>
+          <t>1.07</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>41.43</t>
+          <t>35.32</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -6143,7 +6143,7 @@
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>-11.70</t>
+          <t>-9.39</t>
         </is>
       </c>
       <c r="X14" t="inlineStr">
@@ -6153,17 +6153,17 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>11.11</t>
+          <t>9.75</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2.71</t>
+          <t>1.47</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
@@ -6174,12 +6174,12 @@
       <c r="AC14" t="inlineStr"/>
       <c r="AD14" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
-          <t>915</t>
+          <t>511</t>
         </is>
       </c>
       <c r="AF14" t="inlineStr">
@@ -6189,60 +6189,60 @@
       </c>
       <c r="AG14" t="inlineStr">
         <is>
-          <t>59.17</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>3.34</t>
+          <t>4.35</t>
         </is>
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>-3.27</t>
+          <t>-1.59</t>
         </is>
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>-4.89</t>
+          <t>-4.88</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>-2.80</t>
+          <t>-2.87</t>
         </is>
       </c>
       <c r="AL14" t="inlineStr">
         <is>
-          <t>36.87</t>
+          <t>37.47</t>
         </is>
       </c>
       <c r="AM14" t="n">
-        <v>38.11</v>
+        <v>38.08</v>
       </c>
       <c r="AN14" t="n">
-        <v>40.07</v>
+        <v>40.03</v>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>41.23</t>
+          <t>41.21</t>
         </is>
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>5.10</t>
+          <t>20.99</t>
         </is>
       </c>
       <c r="AQ14" t="inlineStr">
         <is>
+          <t>-0.75</t>
+        </is>
+      </c>
+      <c r="AR14" t="inlineStr">
+        <is>
           <t>-0.95</t>
         </is>
       </c>
-      <c r="AR14" t="inlineStr">
-        <is>
-          <t>-1.00</t>
-        </is>
-      </c>
       <c r="AS14" t="inlineStr">
         <is>
           <t>2.69</t>
@@ -6250,7 +6250,7 @@
       </c>
       <c r="AT14" t="inlineStr">
         <is>
-          <t>-137.15</t>
+          <t>-135.29</t>
         </is>
       </c>
       <c r="AU14" t="inlineStr">
@@ -6260,43 +6260,43 @@
       </c>
       <c r="AV14" t="inlineStr">
         <is>
-          <t>150423914.0772532</t>
+          <t>150251779.8621429</t>
         </is>
       </c>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>39561838.0</t>
+          <t>35810040.0</t>
         </is>
       </c>
       <c r="AX14" t="n">
-        <v>77102277.8</v>
+        <v>75499582.59999999</v>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
-          <t>54515793.2</t>
+          <t>55792550.2</t>
         </is>
       </c>
       <c r="AZ14" t="n">
-        <v>33864219.92</v>
+        <v>33454972.78</v>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
-          <t>22586484</t>
+          <t>19707032</t>
         </is>
       </c>
       <c r="BB14" t="inlineStr">
         <is>
-          <t>4717477.979434728</t>
+          <t>5205041.104487866</t>
         </is>
       </c>
       <c r="BC14" t="inlineStr">
         <is>
-          <t>11730479.54280426</t>
+          <t>7886638.29228013</t>
         </is>
       </c>
       <c r="BD14" t="inlineStr">
         <is>
-          <t>39561838.0</t>
+          <t>35810040.0</t>
         </is>
       </c>
       <c r="BE14" t="inlineStr">
@@ -6316,7 +6316,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>-8.19</t>
+          <t>-5.78</t>
         </is>
       </c>
       <c r="BI14" t="inlineStr">
@@ -6361,17 +6361,17 @@
       </c>
       <c r="BQ14" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR14" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS14" t="inlineStr">
         <is>
-          <t>1.05</t>
+          <t>1.08</t>
         </is>
       </c>
       <c r="BT14" t="inlineStr">
@@ -6401,7 +6401,7 @@
       </c>
       <c r="BY14" t="inlineStr">
         <is>
-          <t>29.71</t>
+          <t>29.67</t>
         </is>
       </c>
       <c r="BZ14" t="inlineStr">
@@ -6426,22 +6426,22 @@
       </c>
       <c r="CD14" t="inlineStr">
         <is>
-          <t>37.05</t>
+          <t>38.3</t>
         </is>
       </c>
       <c r="CE14" t="inlineStr">
         <is>
-          <t>38.2</t>
+          <t>39.5</t>
         </is>
       </c>
       <c r="CF14" t="inlineStr">
         <is>
-          <t>37.0</t>
+          <t>38.15</t>
         </is>
       </c>
       <c r="CG14" t="inlineStr">
         <is>
-          <t>38.1</t>
+          <t>39.1</t>
         </is>
       </c>
       <c r="CH14" t="inlineStr">
@@ -6463,7 +6463,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>【e】</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -6473,12 +6473,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>0.14</t>
+          <t>3.24</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>6301.223</t>
+          <t>1043.085</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -6488,7 +6488,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>36.9</t>
+          <t>38.1</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -6498,17 +6498,17 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>5.63</t>
+          <t>2.56</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>0.91</t>
+          <t>1.07</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>29.52</t>
+          <t>41.43</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -6573,7 +6573,7 @@
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>-14.48</t>
+          <t>-11.70</t>
         </is>
       </c>
       <c r="X15" t="inlineStr">
@@ -6583,17 +6583,17 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>67.14</t>
+          <t>11.11</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>-1.63</t>
+          <t>2.71</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
@@ -6604,73 +6604,73 @@
       <c r="AC15" t="inlineStr"/>
       <c r="AD15" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
-          <t>915</t>
+          <t>511</t>
         </is>
       </c>
       <c r="AF15" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG15" t="inlineStr">
         <is>
-          <t>29.75</t>
+          <t>59.17</t>
         </is>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>0.82</t>
+          <t>3.34</t>
         </is>
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>-4.24</t>
+          <t>-3.27</t>
         </is>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>-4.85</t>
+          <t>-4.89</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>-2.68</t>
+          <t>-2.80</t>
         </is>
       </c>
       <c r="AL15" t="inlineStr">
         <is>
-          <t>36.60000000000001</t>
+          <t>36.87</t>
         </is>
       </c>
       <c r="AM15" t="n">
-        <v>38.22</v>
+        <v>38.11</v>
       </c>
       <c r="AN15" t="n">
-        <v>40.17</v>
+        <v>40.07</v>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>41.28</t>
+          <t>41.23</t>
         </is>
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>-7.24</t>
+          <t>5.10</t>
         </is>
       </c>
       <c r="AQ15" t="inlineStr">
         <is>
-          <t>-1.08</t>
+          <t>-0.95</t>
         </is>
       </c>
       <c r="AR15" t="inlineStr">
         <is>
-          <t>-1.01</t>
+          <t>-1.00</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr">
@@ -6680,7 +6680,7 @@
       </c>
       <c r="AT15" t="inlineStr">
         <is>
-          <t>-137.62</t>
+          <t>-137.15</t>
         </is>
       </c>
       <c r="AU15" t="inlineStr">
@@ -6690,43 +6690,43 @@
       </c>
       <c r="AV15" t="inlineStr">
         <is>
-          <t>150423914.0772532</t>
+          <t>150251779.8621429</t>
         </is>
       </c>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>232650449.0</t>
+          <t>39561838.0</t>
         </is>
       </c>
       <c r="AX15" t="n">
-        <v>74142370</v>
+        <v>77102277.8</v>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>57245793.0</t>
+          <t>54515793.2</t>
         </is>
       </c>
       <c r="AZ15" t="n">
-        <v>34130931.06</v>
+        <v>33864219.92</v>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
-          <t>16896577</t>
+          <t>22586484</t>
         </is>
       </c>
       <c r="BB15" t="inlineStr">
         <is>
-          <t>3442386.786094812</t>
+          <t>4717477.979434728</t>
         </is>
       </c>
       <c r="BC15" t="inlineStr">
         <is>
-          <t>16400757.27416717</t>
+          <t>11730479.54280426</t>
         </is>
       </c>
       <c r="BD15" t="inlineStr">
         <is>
-          <t>232650449.0</t>
+          <t>39561838.0</t>
         </is>
       </c>
       <c r="BE15" t="inlineStr">
@@ -6746,7 +6746,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>-11.08</t>
+          <t>-8.19</t>
         </is>
       </c>
       <c r="BI15" t="inlineStr">
@@ -6791,7 +6791,7 @@
       </c>
       <c r="BQ15" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR15" t="inlineStr">
@@ -6801,7 +6801,7 @@
       </c>
       <c r="BS15" t="inlineStr">
         <is>
-          <t>1.02</t>
+          <t>1.05</t>
         </is>
       </c>
       <c r="BT15" t="inlineStr">
@@ -6831,7 +6831,7 @@
       </c>
       <c r="BY15" t="inlineStr">
         <is>
-          <t>29.71</t>
+          <t>29.67</t>
         </is>
       </c>
       <c r="BZ15" t="inlineStr">
@@ -6856,22 +6856,22 @@
       </c>
       <c r="CD15" t="inlineStr">
         <is>
+          <t>37.05</t>
+        </is>
+      </c>
+      <c r="CE15" t="inlineStr">
+        <is>
+          <t>38.2</t>
+        </is>
+      </c>
+      <c r="CF15" t="inlineStr">
+        <is>
           <t>37.0</t>
         </is>
       </c>
-      <c r="CE15" t="inlineStr">
-        <is>
-          <t>37.5</t>
-        </is>
-      </c>
-      <c r="CF15" t="inlineStr">
-        <is>
-          <t>36.9</t>
-        </is>
-      </c>
       <c r="CG15" t="inlineStr">
         <is>
-          <t>36.9</t>
+          <t>38.1</t>
         </is>
       </c>
       <c r="CH15" t="inlineStr">
@@ -6903,12 +6903,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>1.24</t>
+          <t>0.14</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>1128.761</t>
+          <t>6301.223</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -6918,7 +6918,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>36.85</t>
+          <t>36.9</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -6928,17 +6928,17 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>5.75</t>
+          <t>5.63</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>0.91</t>
+          <t>1.07</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>-1.19</t>
+          <t>29.52</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -7003,7 +7003,7 @@
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>-14.60</t>
+          <t>-14.48</t>
         </is>
       </c>
       <c r="X16" t="inlineStr">
@@ -7013,17 +7013,17 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>12.03</t>
+          <t>67.14</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2.09</t>
+          <t>-1.63</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
@@ -7034,274 +7034,274 @@
       <c r="AC16" t="inlineStr"/>
       <c r="AD16" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
-          <t>915</t>
+          <t>511</t>
         </is>
       </c>
       <c r="AF16" t="inlineStr">
         <is>
+          <t>40.0</t>
+        </is>
+      </c>
+      <c r="AG16" t="inlineStr">
+        <is>
+          <t>29.75</t>
+        </is>
+      </c>
+      <c r="AH16" t="inlineStr">
+        <is>
+          <t>0.82</t>
+        </is>
+      </c>
+      <c r="AI16" t="inlineStr">
+        <is>
+          <t>-4.24</t>
+        </is>
+      </c>
+      <c r="AJ16" t="inlineStr">
+        <is>
+          <t>-4.85</t>
+        </is>
+      </c>
+      <c r="AK16" t="inlineStr">
+        <is>
+          <t>-2.68</t>
+        </is>
+      </c>
+      <c r="AL16" t="inlineStr">
+        <is>
+          <t>36.60000000000001</t>
+        </is>
+      </c>
+      <c r="AM16" t="n">
+        <v>38.22</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>40.17</v>
+      </c>
+      <c r="AO16" t="inlineStr">
+        <is>
+          <t>41.28</t>
+        </is>
+      </c>
+      <c r="AP16" t="inlineStr">
+        <is>
+          <t>-7.24</t>
+        </is>
+      </c>
+      <c r="AQ16" t="inlineStr">
+        <is>
+          <t>-1.08</t>
+        </is>
+      </c>
+      <c r="AR16" t="inlineStr">
+        <is>
+          <t>-1.01</t>
+        </is>
+      </c>
+      <c r="AS16" t="inlineStr">
+        <is>
+          <t>2.69</t>
+        </is>
+      </c>
+      <c r="AT16" t="inlineStr">
+        <is>
+          <t>-137.62</t>
+        </is>
+      </c>
+      <c r="AU16" t="inlineStr">
+        <is>
+          <t>2025/11/25</t>
+        </is>
+      </c>
+      <c r="AV16" t="inlineStr">
+        <is>
+          <t>150251779.8621429</t>
+        </is>
+      </c>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>232650449.0</t>
+        </is>
+      </c>
+      <c r="AX16" t="n">
+        <v>74142370</v>
+      </c>
+      <c r="AY16" t="inlineStr">
+        <is>
+          <t>57245793.0</t>
+        </is>
+      </c>
+      <c r="AZ16" t="n">
+        <v>34130931.06</v>
+      </c>
+      <c r="BA16" t="inlineStr">
+        <is>
+          <t>16896577</t>
+        </is>
+      </c>
+      <c r="BB16" t="inlineStr">
+        <is>
+          <t>3442386.786094812</t>
+        </is>
+      </c>
+      <c r="BC16" t="inlineStr">
+        <is>
+          <t>16400757.27416717</t>
+        </is>
+      </c>
+      <c r="BD16" t="inlineStr">
+        <is>
+          <t>232650449.0</t>
+        </is>
+      </c>
+      <c r="BE16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF16" t="inlineStr">
+        <is>
+          <t>41.5</t>
+        </is>
+      </c>
+      <c r="BG16" t="inlineStr">
+        <is>
+          <t>2025/08/07</t>
+        </is>
+      </c>
+      <c r="BH16" t="inlineStr">
+        <is>
+          <t>-11.08</t>
+        </is>
+      </c>
+      <c r="BI16" t="inlineStr">
+        <is>
+          <t>新光鋼</t>
+        </is>
+      </c>
+      <c r="BJ16" t="inlineStr">
+        <is>
+          <t>新光鋼</t>
+        </is>
+      </c>
+      <c r="BK16" t="inlineStr">
+        <is>
+          <t>鋼鐵工業</t>
+        </is>
+      </c>
+      <c r="BL16" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="BM16" t="inlineStr">
+        <is>
+          <t>0.62</t>
+        </is>
+      </c>
+      <c r="BN16" t="inlineStr">
+        <is>
+          <t>-13.67996844119094</t>
+        </is>
+      </c>
+      <c r="BO16" t="inlineStr">
+        <is>
+          <t>-10.11024290164889</t>
+        </is>
+      </c>
+      <c r="BP16" t="inlineStr">
+        <is>
+          <t>24.12947661306339</t>
+        </is>
+      </c>
+      <c r="BQ16" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BR16" t="inlineStr">
+        <is>
+          <t>價-量增</t>
+        </is>
+      </c>
+      <c r="BS16" t="inlineStr">
+        <is>
+          <t>1.02</t>
+        </is>
+      </c>
+      <c r="BT16" t="inlineStr">
+        <is>
+          <t>6.39</t>
+        </is>
+      </c>
+      <c r="BU16" t="inlineStr">
+        <is>
+          <t>11.90</t>
+        </is>
+      </c>
+      <c r="BV16" t="inlineStr">
+        <is>
+          <t>16.16</t>
+        </is>
+      </c>
+      <c r="BW16" t="inlineStr">
+        <is>
+          <t>8.69%</t>
+        </is>
+      </c>
+      <c r="BX16" t="inlineStr">
+        <is>
+          <t>5.19%</t>
+        </is>
+      </c>
+      <c r="BY16" t="inlineStr">
+        <is>
+          <t>29.67</t>
+        </is>
+      </c>
+      <c r="BZ16" t="inlineStr">
+        <is>
+          <t>12557</t>
+        </is>
+      </c>
+      <c r="CA16" t="inlineStr">
+        <is>
+          <t>鋼板38.80%、熱軋及鍍鋅鋼板33.80%、不�袗�板12.60%、特殊鋼板7.00%、加工及其他6.90%、型鋼0.90% (2024年)</t>
+        </is>
+      </c>
+      <c r="CB16" t="inlineStr">
+        <is>
+          <t>新光鋼-鋼鐵工業-上市</t>
+        </is>
+      </c>
+      <c r="CC16" t="inlineStr">
+        <is>
+          <t>鋼鐵工業右下上市</t>
+        </is>
+      </c>
+      <c r="CD16" t="inlineStr">
+        <is>
+          <t>37.0</t>
+        </is>
+      </c>
+      <c r="CE16" t="inlineStr">
+        <is>
           <t>37.5</t>
         </is>
       </c>
-      <c r="AG16" t="inlineStr">
-        <is>
-          <t>16.42</t>
-        </is>
-      </c>
-      <c r="AH16" t="inlineStr">
-        <is>
-          <t>0.66</t>
-        </is>
-      </c>
-      <c r="AI16" t="inlineStr">
-        <is>
-          <t>-4.68</t>
-        </is>
-      </c>
-      <c r="AJ16" t="inlineStr">
-        <is>
-          <t>-4.69</t>
-        </is>
-      </c>
-      <c r="AK16" t="inlineStr">
-        <is>
-          <t>-2.48</t>
-        </is>
-      </c>
-      <c r="AL16" t="inlineStr">
-        <is>
-          <t>36.61</t>
-        </is>
-      </c>
-      <c r="AM16" t="n">
-        <v>38.41</v>
-      </c>
-      <c r="AN16" t="n">
-        <v>40.3</v>
-      </c>
-      <c r="AO16" t="inlineStr">
-        <is>
-          <t>41.32</t>
-        </is>
-      </c>
-      <c r="AP16" t="inlineStr">
-        <is>
-          <t>-12.91</t>
-        </is>
-      </c>
-      <c r="AQ16" t="inlineStr">
-        <is>
-          <t>-1.12</t>
-        </is>
-      </c>
-      <c r="AR16" t="inlineStr">
-        <is>
-          <t>-0.99</t>
-        </is>
-      </c>
-      <c r="AS16" t="inlineStr">
-        <is>
-          <t>2.69</t>
-        </is>
-      </c>
-      <c r="AT16" t="inlineStr">
-        <is>
-          <t>-136.94</t>
-        </is>
-      </c>
-      <c r="AU16" t="inlineStr">
-        <is>
-          <t>2025/11/25</t>
-        </is>
-      </c>
-      <c r="AV16" t="inlineStr">
-        <is>
-          <t>150423914.0772532</t>
-        </is>
-      </c>
-      <c r="AW16" t="inlineStr">
-        <is>
-          <t>41298962.0</t>
-        </is>
-      </c>
-      <c r="AX16" t="n">
-        <v>35487232</v>
-      </c>
-      <c r="AY16" t="inlineStr">
-        <is>
-          <t>35914543.8</t>
-        </is>
-      </c>
-      <c r="AZ16" t="n">
-        <v>29950115.64</v>
-      </c>
-      <c r="BA16" t="inlineStr">
-        <is>
-          <t>-427311</t>
-        </is>
-      </c>
-      <c r="BB16" t="inlineStr">
-        <is>
-          <t>1086319.424627111</t>
-        </is>
-      </c>
-      <c r="BC16" t="inlineStr">
-        <is>
-          <t>1798775.809179619</t>
-        </is>
-      </c>
-      <c r="BD16" t="inlineStr">
-        <is>
-          <t>41298962.0</t>
-        </is>
-      </c>
-      <c r="BE16" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BF16" t="inlineStr">
-        <is>
-          <t>41.5</t>
-        </is>
-      </c>
-      <c r="BG16" t="inlineStr">
-        <is>
-          <t>2025/08/07</t>
-        </is>
-      </c>
-      <c r="BH16" t="inlineStr">
-        <is>
-          <t>-11.20</t>
-        </is>
-      </c>
-      <c r="BI16" t="inlineStr">
-        <is>
-          <t>新光鋼</t>
-        </is>
-      </c>
-      <c r="BJ16" t="inlineStr">
-        <is>
-          <t>新光鋼</t>
-        </is>
-      </c>
-      <c r="BK16" t="inlineStr">
-        <is>
-          <t>鋼鐵工業</t>
-        </is>
-      </c>
-      <c r="BL16" t="inlineStr">
-        <is>
-          <t>上市</t>
-        </is>
-      </c>
-      <c r="BM16" t="inlineStr">
-        <is>
-          <t>0.62</t>
-        </is>
-      </c>
-      <c r="BN16" t="inlineStr">
-        <is>
-          <t>-13.67996844119094</t>
-        </is>
-      </c>
-      <c r="BO16" t="inlineStr">
-        <is>
-          <t>-10.11024290164889</t>
-        </is>
-      </c>
-      <c r="BP16" t="inlineStr">
-        <is>
-          <t>24.12947661306339</t>
-        </is>
-      </c>
-      <c r="BQ16" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;可能出現反轉訊號&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;3&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="BR16" t="inlineStr">
-        <is>
-          <t>價-量增</t>
-        </is>
-      </c>
-      <c r="BS16" t="inlineStr">
-        <is>
-          <t>1.01</t>
-        </is>
-      </c>
-      <c r="BT16" t="inlineStr">
-        <is>
-          <t>6.39</t>
-        </is>
-      </c>
-      <c r="BU16" t="inlineStr">
-        <is>
-          <t>11.90</t>
-        </is>
-      </c>
-      <c r="BV16" t="inlineStr">
-        <is>
-          <t>16.16</t>
-        </is>
-      </c>
-      <c r="BW16" t="inlineStr">
-        <is>
-          <t>8.69%</t>
-        </is>
-      </c>
-      <c r="BX16" t="inlineStr">
-        <is>
-          <t>5.19%</t>
-        </is>
-      </c>
-      <c r="BY16" t="inlineStr">
-        <is>
-          <t>29.71</t>
-        </is>
-      </c>
-      <c r="BZ16" t="inlineStr">
-        <is>
-          <t>12557</t>
-        </is>
-      </c>
-      <c r="CA16" t="inlineStr">
-        <is>
-          <t>鋼板38.80%、熱軋及鍍鋅鋼板33.80%、不�袗�板12.60%、特殊鋼板7.00%、加工及其他6.90%、型鋼0.90% (2024年)</t>
-        </is>
-      </c>
-      <c r="CB16" t="inlineStr">
-        <is>
-          <t>新光鋼-鋼鐵工業-上市</t>
-        </is>
-      </c>
-      <c r="CC16" t="inlineStr">
-        <is>
-          <t>鋼鐵工業右下上市</t>
-        </is>
-      </c>
-      <c r="CD16" t="inlineStr">
-        <is>
-          <t>36.4</t>
-        </is>
-      </c>
-      <c r="CE16" t="inlineStr">
-        <is>
-          <t>36.95</t>
-        </is>
-      </c>
       <c r="CF16" t="inlineStr">
         <is>
-          <t>36.0</t>
+          <t>36.9</t>
         </is>
       </c>
       <c r="CG16" t="inlineStr">
         <is>
-          <t>36.85</t>
+          <t>36.9</t>
         </is>
       </c>
       <c r="CH16" t="inlineStr">
@@ -7333,12 +7333,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>0.83</t>
+          <t>1.24</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>776.396</t>
+          <t>1128.761</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -7348,7 +7348,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>36.4</t>
+          <t>36.85</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -7358,17 +7358,17 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>6.91</t>
+          <t>5.75</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>0.91</t>
+          <t>1.07</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>9.74</t>
+          <t>-1.19</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -7433,7 +7433,7 @@
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>-15.64</t>
+          <t>-14.60</t>
         </is>
       </c>
       <c r="X17" t="inlineStr">
@@ -7443,17 +7443,17 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>8.27</t>
+          <t>12.03</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>0.70</t>
+          <t>2.09</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
@@ -7464,73 +7464,73 @@
       <c r="AC17" t="inlineStr"/>
       <c r="AD17" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
-          <t>915</t>
+          <t>511</t>
         </is>
       </c>
       <c r="AF17" t="inlineStr">
         <is>
-          <t>11.76</t>
+          <t>37.5</t>
         </is>
       </c>
       <c r="AG17" t="inlineStr">
         <is>
-          <t>3.92</t>
+          <t>16.42</t>
         </is>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>-0.90</t>
+          <t>0.66</t>
         </is>
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>-4.83</t>
+          <t>-4.68</t>
         </is>
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>-4.54</t>
+          <t>-4.69</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>-2.31</t>
+          <t>-2.48</t>
         </is>
       </c>
       <c r="AL17" t="inlineStr">
         <is>
-          <t>36.73</t>
+          <t>36.61</t>
         </is>
       </c>
       <c r="AM17" t="n">
-        <v>38.6</v>
+        <v>38.41</v>
       </c>
       <c r="AN17" t="n">
-        <v>40.43</v>
+        <v>40.3</v>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>41.39</t>
+          <t>41.32</t>
         </is>
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>-19.31</t>
+          <t>-12.91</t>
         </is>
       </c>
       <c r="AQ17" t="inlineStr">
         <is>
-          <t>-1.15</t>
+          <t>-1.12</t>
         </is>
       </c>
       <c r="AR17" t="inlineStr">
         <is>
-          <t>-0.96</t>
+          <t>-0.99</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr">
@@ -7540,7 +7540,7 @@
       </c>
       <c r="AT17" t="inlineStr">
         <is>
-          <t>-135.75</t>
+          <t>-136.94</t>
         </is>
       </c>
       <c r="AU17" t="inlineStr">
@@ -7550,43 +7550,43 @@
       </c>
       <c r="AV17" t="inlineStr">
         <is>
-          <t>150423914.0772532</t>
+          <t>150251779.8621429</t>
         </is>
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>28176624.0</t>
+          <t>41298962.0</t>
         </is>
       </c>
       <c r="AX17" t="n">
-        <v>37871124</v>
+        <v>35487232</v>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>34509118.0</t>
+          <t>35914543.8</t>
         </is>
       </c>
       <c r="AZ17" t="n">
-        <v>29545425.32</v>
+        <v>29950115.64</v>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
-          <t>3362006</t>
+          <t>-427311</t>
         </is>
       </c>
       <c r="BB17" t="inlineStr">
         <is>
-          <t>956781.9001630185</t>
+          <t>1086319.424627111</t>
         </is>
       </c>
       <c r="BC17" t="inlineStr">
         <is>
-          <t>1376505.330298137</t>
+          <t>1798775.809179619</t>
         </is>
       </c>
       <c r="BD17" t="inlineStr">
         <is>
-          <t>28176624.0</t>
+          <t>41298962.0</t>
         </is>
       </c>
       <c r="BE17" t="inlineStr">
@@ -7606,7 +7606,7 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>-12.29</t>
+          <t>-11.20</t>
         </is>
       </c>
       <c r="BI17" t="inlineStr">
@@ -7651,17 +7651,17 @@
       </c>
       <c r="BQ17" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;可能出現反轉訊號&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;3&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR17" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS17" t="inlineStr">
         <is>
-          <t>1.00</t>
+          <t>1.01</t>
         </is>
       </c>
       <c r="BT17" t="inlineStr">
@@ -7691,7 +7691,7 @@
       </c>
       <c r="BY17" t="inlineStr">
         <is>
-          <t>29.71</t>
+          <t>29.67</t>
         </is>
       </c>
       <c r="BZ17" t="inlineStr">
@@ -7716,12 +7716,12 @@
       </c>
       <c r="CD17" t="inlineStr">
         <is>
-          <t>36.3</t>
+          <t>36.4</t>
         </is>
       </c>
       <c r="CE17" t="inlineStr">
         <is>
-          <t>36.55</t>
+          <t>36.95</t>
         </is>
       </c>
       <c r="CF17" t="inlineStr">
@@ -7731,7 +7731,7 @@
       </c>
       <c r="CG17" t="inlineStr">
         <is>
-          <t>36.4</t>
+          <t>36.85</t>
         </is>
       </c>
       <c r="CH17" t="inlineStr">
@@ -7763,12 +7763,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>-1.76</t>
+          <t>0.83</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>1212.053</t>
+          <t>776.396</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -7778,7 +7778,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>36.1</t>
+          <t>36.4</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -7788,17 +7788,17 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>7.67</t>
+          <t>6.91</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>0.91</t>
+          <t>1.07</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>3.03</t>
+          <t>9.74</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -7863,7 +7863,7 @@
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>-16.34</t>
+          <t>-15.64</t>
         </is>
       </c>
       <c r="X18" t="inlineStr">
@@ -7873,17 +7873,17 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>12.91</t>
+          <t>8.27</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>-1.38</t>
+          <t>0.70</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
@@ -7894,73 +7894,73 @@
       <c r="AC18" t="inlineStr"/>
       <c r="AD18" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
-          <t>915</t>
+          <t>511</t>
         </is>
       </c>
       <c r="AF18" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>11.76</t>
         </is>
       </c>
       <c r="AG18" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>3.92</t>
         </is>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>-2.62</t>
+          <t>-0.90</t>
         </is>
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>-4.47</t>
+          <t>-4.83</t>
         </is>
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>-4.38</t>
+          <t>-4.54</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>-2.09</t>
+          <t>-2.31</t>
         </is>
       </c>
       <c r="AL18" t="inlineStr">
         <is>
-          <t>37.07000000000001</t>
+          <t>36.73</t>
         </is>
       </c>
       <c r="AM18" t="n">
-        <v>38.8</v>
+        <v>38.6</v>
       </c>
       <c r="AN18" t="n">
-        <v>40.58</v>
+        <v>40.43</v>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>41.45</t>
+          <t>41.39</t>
         </is>
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>-22.07</t>
+          <t>-19.31</t>
         </is>
       </c>
       <c r="AQ18" t="inlineStr">
         <is>
-          <t>-1.12</t>
+          <t>-1.15</t>
         </is>
       </c>
       <c r="AR18" t="inlineStr">
         <is>
-          <t>-0.91</t>
+          <t>-0.96</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr">
@@ -7970,7 +7970,7 @@
       </c>
       <c r="AT18" t="inlineStr">
         <is>
-          <t>-134.02</t>
+          <t>-135.75</t>
         </is>
       </c>
       <c r="AU18" t="inlineStr">
@@ -7980,43 +7980,43 @@
       </c>
       <c r="AV18" t="inlineStr">
         <is>
-          <t>150423914.0772532</t>
+          <t>150251779.8621429</t>
         </is>
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>43823516.0</t>
+          <t>28176624.0</t>
         </is>
       </c>
       <c r="AX18" t="n">
-        <v>36085517.8</v>
+        <v>37871124</v>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>35025550.9</t>
+          <t>34509118.0</t>
         </is>
       </c>
       <c r="AZ18" t="n">
-        <v>29409986</v>
+        <v>29545425.32</v>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
-          <t>1059966</t>
+          <t>3362006</t>
         </is>
       </c>
       <c r="BB18" t="inlineStr">
         <is>
-          <t>880468.5492293607</t>
+          <t>956781.9001630185</t>
         </is>
       </c>
       <c r="BC18" t="inlineStr">
         <is>
-          <t>2130065.670099653</t>
+          <t>1376505.330298137</t>
         </is>
       </c>
       <c r="BD18" t="inlineStr">
         <is>
-          <t>43823516.0</t>
+          <t>28176624.0</t>
         </is>
       </c>
       <c r="BE18" t="inlineStr">
@@ -8036,7 +8036,7 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>-13.01</t>
+          <t>-12.29</t>
         </is>
       </c>
       <c r="BI18" t="inlineStr">
@@ -8081,7 +8081,7 @@
       </c>
       <c r="BQ18" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR18" t="inlineStr">
@@ -8091,7 +8091,7 @@
       </c>
       <c r="BS18" t="inlineStr">
         <is>
-          <t>0.99</t>
+          <t>1.00</t>
         </is>
       </c>
       <c r="BT18" t="inlineStr">
@@ -8121,7 +8121,7 @@
       </c>
       <c r="BY18" t="inlineStr">
         <is>
-          <t>29.71</t>
+          <t>29.67</t>
         </is>
       </c>
       <c r="BZ18" t="inlineStr">
@@ -8146,22 +8146,22 @@
       </c>
       <c r="CD18" t="inlineStr">
         <is>
-          <t>36.85</t>
+          <t>36.3</t>
         </is>
       </c>
       <c r="CE18" t="inlineStr">
         <is>
-          <t>36.85</t>
+          <t>36.55</t>
         </is>
       </c>
       <c r="CF18" t="inlineStr">
         <is>
-          <t>35.85</t>
+          <t>36.0</t>
         </is>
       </c>
       <c r="CG18" t="inlineStr">
         <is>
-          <t>36.1</t>
+          <t>36.4</t>
         </is>
       </c>
       <c r="CH18" t="inlineStr">
@@ -8193,12 +8193,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>-0.54</t>
+          <t>-1.76</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>672.504</t>
+          <t>1212.053</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -8208,7 +8208,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>36.75</t>
+          <t>36.1</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -8218,17 +8218,17 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>6.01</t>
+          <t>7.67</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>0.91</t>
+          <t>1.07</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>-2.04</t>
+          <t>3.03</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -8293,7 +8293,7 @@
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>-14.83</t>
+          <t>-16.34</t>
         </is>
       </c>
       <c r="X19" t="inlineStr">
@@ -8303,17 +8303,17 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>7.17</t>
+          <t>12.91</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>-1.09</t>
+          <t>-1.38</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
@@ -8324,12 +8324,12 @@
       <c r="AC19" t="inlineStr"/>
       <c r="AD19" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
-          <t>915</t>
+          <t>511</t>
         </is>
       </c>
       <c r="AF19" t="inlineStr">
@@ -8344,53 +8344,53 @@
       </c>
       <c r="AH19" t="inlineStr">
         <is>
-          <t>-1.92</t>
+          <t>-2.62</t>
         </is>
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>-3.97</t>
+          <t>-4.47</t>
         </is>
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>-4.25</t>
+          <t>-4.38</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>-1.83</t>
+          <t>-2.09</t>
         </is>
       </c>
       <c r="AL19" t="inlineStr">
         <is>
-          <t>37.47000000000001</t>
+          <t>37.07000000000001</t>
         </is>
       </c>
       <c r="AM19" t="n">
-        <v>39.02</v>
+        <v>38.8</v>
       </c>
       <c r="AN19" t="n">
-        <v>40.75</v>
+        <v>40.58</v>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>41.51</t>
+          <t>41.45</t>
         </is>
       </c>
       <c r="AP19" t="inlineStr">
         <is>
-          <t>-19.33</t>
+          <t>-22.07</t>
         </is>
       </c>
       <c r="AQ19" t="inlineStr">
         <is>
-          <t>-1.03</t>
+          <t>-1.12</t>
         </is>
       </c>
       <c r="AR19" t="inlineStr">
         <is>
-          <t>-0.86</t>
+          <t>-0.91</t>
         </is>
       </c>
       <c r="AS19" t="inlineStr">
@@ -8400,7 +8400,7 @@
       </c>
       <c r="AT19" t="inlineStr">
         <is>
-          <t>-132.14</t>
+          <t>-134.02</t>
         </is>
       </c>
       <c r="AU19" t="inlineStr">
@@ -8410,43 +8410,43 @@
       </c>
       <c r="AV19" t="inlineStr">
         <is>
-          <t>150423914.0772532</t>
+          <t>150251779.8621429</t>
         </is>
       </c>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>24762299.0</t>
+          <t>43823516.0</t>
         </is>
       </c>
       <c r="AX19" t="n">
-        <v>31929308.6</v>
+        <v>36085517.8</v>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
-          <t>32595150.7</t>
+          <t>35025550.9</t>
         </is>
       </c>
       <c r="AZ19" t="n">
-        <v>29130934.74</v>
+        <v>29409986</v>
       </c>
       <c r="BA19" t="inlineStr">
         <is>
-          <t>-665842</t>
+          <t>1059966</t>
         </is>
       </c>
       <c r="BB19" t="inlineStr">
         <is>
-          <t>653269.0727074891</t>
+          <t>880468.5492293607</t>
         </is>
       </c>
       <c r="BC19" t="inlineStr">
         <is>
-          <t>1454053.953026839</t>
+          <t>2130065.670099653</t>
         </is>
       </c>
       <c r="BD19" t="inlineStr">
         <is>
-          <t>24762299.0</t>
+          <t>43823516.0</t>
         </is>
       </c>
       <c r="BE19" t="inlineStr">
@@ -8466,7 +8466,7 @@
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>-11.45</t>
+          <t>-13.01</t>
         </is>
       </c>
       <c r="BI19" t="inlineStr">
@@ -8521,7 +8521,7 @@
       </c>
       <c r="BS19" t="inlineStr">
         <is>
-          <t>1.01</t>
+          <t>0.99</t>
         </is>
       </c>
       <c r="BT19" t="inlineStr">
@@ -8551,7 +8551,7 @@
       </c>
       <c r="BY19" t="inlineStr">
         <is>
-          <t>29.71</t>
+          <t>29.67</t>
         </is>
       </c>
       <c r="BZ19" t="inlineStr">
@@ -8576,22 +8576,22 @@
       </c>
       <c r="CD19" t="inlineStr">
         <is>
-          <t>36.95</t>
+          <t>36.85</t>
         </is>
       </c>
       <c r="CE19" t="inlineStr">
         <is>
-          <t>37.3</t>
+          <t>36.85</t>
         </is>
       </c>
       <c r="CF19" t="inlineStr">
         <is>
-          <t>36.6</t>
+          <t>35.85</t>
         </is>
       </c>
       <c r="CG19" t="inlineStr">
         <is>
-          <t>36.75</t>
+          <t>36.1</t>
         </is>
       </c>
       <c r="CH19" t="inlineStr">
@@ -8623,12 +8623,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>-1.34</t>
+          <t>-0.54</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>1065.248</t>
+          <t>672.504</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -8638,7 +8638,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>36.95</t>
+          <t>36.75</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -8648,17 +8648,17 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>5.5</t>
+          <t>6.01</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>0.91</t>
+          <t>1.07</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>28.28</t>
+          <t>-2.04</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -8723,7 +8723,7 @@
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>-14.37</t>
+          <t>-14.83</t>
         </is>
       </c>
       <c r="X20" t="inlineStr">
@@ -8733,17 +8733,17 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>11.35</t>
+          <t>7.17</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>-0.81</t>
+          <t>-1.09</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
@@ -8754,12 +8754,12 @@
       <c r="AC20" t="inlineStr"/>
       <c r="AD20" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
-          <t>915</t>
+          <t>511</t>
         </is>
       </c>
       <c r="AF20" t="inlineStr">
@@ -8769,58 +8769,58 @@
       </c>
       <c r="AG20" t="inlineStr">
         <is>
-          <t>9.38</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
-          <t>-1.86</t>
+          <t>-1.92</t>
         </is>
       </c>
       <c r="AI20" t="inlineStr">
         <is>
-          <t>-4.02</t>
+          <t>-3.97</t>
         </is>
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>-4.09</t>
+          <t>-4.25</t>
         </is>
       </c>
       <c r="AK20" t="inlineStr">
         <is>
-          <t>-1.60</t>
+          <t>-1.83</t>
         </is>
       </c>
       <c r="AL20" t="inlineStr">
         <is>
-          <t>37.65000000000001</t>
+          <t>37.47000000000001</t>
         </is>
       </c>
       <c r="AM20" t="n">
-        <v>39.23</v>
+        <v>39.02</v>
       </c>
       <c r="AN20" t="n">
-        <v>40.9</v>
+        <v>40.75</v>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>41.57</t>
+          <t>41.51</t>
         </is>
       </c>
       <c r="AP20" t="inlineStr">
         <is>
-          <t>-18.37</t>
+          <t>-19.33</t>
         </is>
       </c>
       <c r="AQ20" t="inlineStr">
         <is>
-          <t>-0.97</t>
+          <t>-1.03</t>
         </is>
       </c>
       <c r="AR20" t="inlineStr">
         <is>
-          <t>-0.82</t>
+          <t>-0.86</t>
         </is>
       </c>
       <c r="AS20" t="inlineStr">
@@ -8830,7 +8830,7 @@
       </c>
       <c r="AT20" t="inlineStr">
         <is>
-          <t>-130.59</t>
+          <t>-132.14</t>
         </is>
       </c>
       <c r="AU20" t="inlineStr">
@@ -8840,43 +8840,43 @@
       </c>
       <c r="AV20" t="inlineStr">
         <is>
-          <t>150423914.0772532</t>
+          <t>150251779.8621429</t>
         </is>
       </c>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>39374759.0</t>
+          <t>24762299.0</t>
         </is>
       </c>
       <c r="AX20" t="n">
-        <v>40349216</v>
+        <v>31929308.6</v>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
-          <t>31454761.9</t>
+          <t>32595150.7</t>
         </is>
       </c>
       <c r="AZ20" t="n">
-        <v>29061426.18</v>
+        <v>29130934.74</v>
       </c>
       <c r="BA20" t="inlineStr">
         <is>
-          <t>8894454</t>
+          <t>-665842</t>
         </is>
       </c>
       <c r="BB20" t="inlineStr">
         <is>
-          <t>507671.8217403347</t>
+          <t>653269.0727074891</t>
         </is>
       </c>
       <c r="BC20" t="inlineStr">
         <is>
-          <t>2478665.680314712</t>
+          <t>1454053.953026839</t>
         </is>
       </c>
       <c r="BD20" t="inlineStr">
         <is>
-          <t>39374759.0</t>
+          <t>24762299.0</t>
         </is>
       </c>
       <c r="BE20" t="inlineStr">
@@ -8896,7 +8896,7 @@
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>-10.96</t>
+          <t>-11.45</t>
         </is>
       </c>
       <c r="BI20" t="inlineStr">
@@ -8941,17 +8941,17 @@
       </c>
       <c r="BQ20" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR20" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS20" t="inlineStr">
         <is>
-          <t>1.02</t>
+          <t>1.01</t>
         </is>
       </c>
       <c r="BT20" t="inlineStr">
@@ -8981,7 +8981,7 @@
       </c>
       <c r="BY20" t="inlineStr">
         <is>
-          <t>29.71</t>
+          <t>29.67</t>
         </is>
       </c>
       <c r="BZ20" t="inlineStr">
@@ -9006,22 +9006,22 @@
       </c>
       <c r="CD20" t="inlineStr">
         <is>
+          <t>36.95</t>
+        </is>
+      </c>
+      <c r="CE20" t="inlineStr">
+        <is>
           <t>37.3</t>
         </is>
       </c>
-      <c r="CE20" t="inlineStr">
-        <is>
-          <t>37.5</t>
-        </is>
-      </c>
       <c r="CF20" t="inlineStr">
         <is>
-          <t>36.7</t>
+          <t>36.6</t>
         </is>
       </c>
       <c r="CG20" t="inlineStr">
         <is>
-          <t>36.95</t>
+          <t>36.75</t>
         </is>
       </c>
       <c r="CH20" t="inlineStr">
@@ -9053,12 +9053,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>-1.71</t>
+          <t>-1.34</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>1408.733</t>
+          <t>1065.248</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -9068,7 +9068,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>37.45</t>
+          <t>36.95</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -9078,17 +9078,17 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>4.22</t>
+          <t>5.5</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>0.91</t>
+          <t>1.07</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>22.93</t>
+          <t>28.28</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -9153,7 +9153,7 @@
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>-13.21</t>
+          <t>-14.37</t>
         </is>
       </c>
       <c r="X21" t="inlineStr">
@@ -9163,17 +9163,17 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>15.01</t>
+          <t>11.35</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>-2.94</t>
+          <t>-0.81</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
@@ -9184,12 +9184,12 @@
       <c r="AC21" t="inlineStr"/>
       <c r="AD21" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
-          <t>915</t>
+          <t>511</t>
         </is>
       </c>
       <c r="AF21" t="inlineStr">
@@ -9199,58 +9199,58 @@
       </c>
       <c r="AG21" t="inlineStr">
         <is>
-          <t>16.69</t>
+          <t>9.38</t>
         </is>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
-          <t>-1.42</t>
+          <t>-1.86</t>
         </is>
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>-3.63</t>
+          <t>-4.02</t>
         </is>
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>-3.96</t>
+          <t>-4.09</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
         <is>
-          <t>-1.34</t>
+          <t>-1.60</t>
         </is>
       </c>
       <c r="AL21" t="inlineStr">
         <is>
-          <t>37.99</t>
+          <t>37.65000000000001</t>
         </is>
       </c>
       <c r="AM21" t="n">
-        <v>39.42</v>
+        <v>39.23</v>
       </c>
       <c r="AN21" t="n">
-        <v>41.05</v>
+        <v>40.9</v>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>41.6</t>
+          <t>41.57</t>
         </is>
       </c>
       <c r="AP21" t="inlineStr">
         <is>
-          <t>-15.49</t>
+          <t>-18.37</t>
         </is>
       </c>
       <c r="AQ21" t="inlineStr">
         <is>
-          <t>-0.91</t>
+          <t>-0.97</t>
         </is>
       </c>
       <c r="AR21" t="inlineStr">
         <is>
-          <t>-0.78</t>
+          <t>-0.82</t>
         </is>
       </c>
       <c r="AS21" t="inlineStr">
@@ -9260,7 +9260,7 @@
       </c>
       <c r="AT21" t="inlineStr">
         <is>
-          <t>-129.19</t>
+          <t>-130.59</t>
         </is>
       </c>
       <c r="AU21" t="inlineStr">
@@ -9270,43 +9270,43 @@
       </c>
       <c r="AV21" t="inlineStr">
         <is>
-          <t>150423914.0772532</t>
+          <t>150251779.8621429</t>
         </is>
       </c>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>53218422.0</t>
+          <t>39374759.0</t>
         </is>
       </c>
       <c r="AX21" t="n">
-        <v>36341855.6</v>
+        <v>40349216</v>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
-          <t>29562657.9</t>
+          <t>31454761.9</t>
         </is>
       </c>
       <c r="AZ21" t="n">
-        <v>28846965.04</v>
+        <v>29061426.18</v>
       </c>
       <c r="BA21" t="inlineStr">
         <is>
-          <t>6779197</t>
+          <t>8894454</t>
         </is>
       </c>
       <c r="BB21" t="inlineStr">
         <is>
-          <t>149309.3019995387</t>
+          <t>507671.8217403347</t>
         </is>
       </c>
       <c r="BC21" t="inlineStr">
         <is>
-          <t>2288252.230714723</t>
+          <t>2478665.680314712</t>
         </is>
       </c>
       <c r="BD21" t="inlineStr">
         <is>
-          <t>53218422.0</t>
+          <t>39374759.0</t>
         </is>
       </c>
       <c r="BE21" t="inlineStr">
@@ -9326,7 +9326,7 @@
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>-9.76</t>
+          <t>-10.96</t>
         </is>
       </c>
       <c r="BI21" t="inlineStr">
@@ -9371,7 +9371,7 @@
       </c>
       <c r="BQ21" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR21" t="inlineStr">
@@ -9381,7 +9381,7 @@
       </c>
       <c r="BS21" t="inlineStr">
         <is>
-          <t>1.03</t>
+          <t>1.02</t>
         </is>
       </c>
       <c r="BT21" t="inlineStr">
@@ -9411,7 +9411,7 @@
       </c>
       <c r="BY21" t="inlineStr">
         <is>
-          <t>29.71</t>
+          <t>29.67</t>
         </is>
       </c>
       <c r="BZ21" t="inlineStr">
@@ -9436,22 +9436,22 @@
       </c>
       <c r="CD21" t="inlineStr">
         <is>
-          <t>38.1</t>
+          <t>37.3</t>
         </is>
       </c>
       <c r="CE21" t="inlineStr">
         <is>
-          <t>38.7</t>
+          <t>37.5</t>
         </is>
       </c>
       <c r="CF21" t="inlineStr">
         <is>
-          <t>37.3</t>
+          <t>36.7</t>
         </is>
       </c>
       <c r="CG21" t="inlineStr">
         <is>
-          <t>37.45</t>
+          <t>36.95</t>
         </is>
       </c>
       <c r="CH21" t="inlineStr">
@@ -9483,12 +9483,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-1.71</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>504.317</t>
+          <t>1408.733</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -9498,7 +9498,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>38.1</t>
+          <t>37.45</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -9508,17 +9508,17 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>2.56</t>
+          <t>4.22</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>0.91</t>
+          <t>1.07</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>20.39</t>
+          <t>22.93</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -9583,7 +9583,7 @@
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>-11.70</t>
+          <t>-13.21</t>
         </is>
       </c>
       <c r="X22" t="inlineStr">
@@ -9593,17 +9593,17 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>5.37</t>
+          <t>15.01</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>-0.39</t>
+          <t>-2.94</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
@@ -9614,17 +9614,17 @@
       <c r="AC22" t="inlineStr"/>
       <c r="AD22" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AE22" t="inlineStr">
         <is>
-          <t>915</t>
+          <t>511</t>
         </is>
       </c>
       <c r="AF22" t="inlineStr">
         <is>
-          <t>28.13</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG22" t="inlineStr">
@@ -9634,53 +9634,53 @@
       </c>
       <c r="AH22" t="inlineStr">
         <is>
-          <t>-0.55</t>
+          <t>-1.42</t>
         </is>
       </c>
       <c r="AI22" t="inlineStr">
         <is>
-          <t>-3.22</t>
+          <t>-3.63</t>
         </is>
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>-3.86</t>
+          <t>-3.96</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
         <is>
-          <t>-1.12</t>
+          <t>-1.34</t>
         </is>
       </c>
       <c r="AL22" t="inlineStr">
         <is>
-          <t>38.31</t>
+          <t>37.99</t>
         </is>
       </c>
       <c r="AM22" t="n">
-        <v>39.58</v>
+        <v>39.42</v>
       </c>
       <c r="AN22" t="n">
-        <v>41.17</v>
+        <v>41.05</v>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>41.64</t>
+          <t>41.6</t>
         </is>
       </c>
       <c r="AP22" t="inlineStr">
         <is>
-          <t>-13.76</t>
+          <t>-15.49</t>
         </is>
       </c>
       <c r="AQ22" t="inlineStr">
         <is>
-          <t>-0.86</t>
+          <t>-0.91</t>
         </is>
       </c>
       <c r="AR22" t="inlineStr">
         <is>
-          <t>-0.75</t>
+          <t>-0.78</t>
         </is>
       </c>
       <c r="AS22" t="inlineStr">
@@ -9690,7 +9690,7 @@
       </c>
       <c r="AT22" t="inlineStr">
         <is>
-          <t>-128.06</t>
+          <t>-129.19</t>
         </is>
       </c>
       <c r="AU22" t="inlineStr">
@@ -9700,43 +9700,43 @@
       </c>
       <c r="AV22" t="inlineStr">
         <is>
-          <t>150423914.0772532</t>
+          <t>150251779.8621429</t>
         </is>
       </c>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>19248593.0</t>
+          <t>53218422.0</t>
         </is>
       </c>
       <c r="AX22" t="n">
-        <v>31147112</v>
+        <v>36341855.6</v>
       </c>
       <c r="AY22" t="inlineStr">
         <is>
-          <t>25871081.1</t>
+          <t>29562657.9</t>
         </is>
       </c>
       <c r="AZ22" t="n">
-        <v>28091032.78</v>
+        <v>28846965.04</v>
       </c>
       <c r="BA22" t="inlineStr">
         <is>
-          <t>5276030</t>
+          <t>6779197</t>
         </is>
       </c>
       <c r="BB22" t="inlineStr">
         <is>
-          <t>-239589.4123123131</t>
+          <t>149309.3019995387</t>
         </is>
       </c>
       <c r="BC22" t="inlineStr">
         <is>
-          <t>451260.1159035005</t>
+          <t>2288252.230714723</t>
         </is>
       </c>
       <c r="BD22" t="inlineStr">
         <is>
-          <t>19248593.0</t>
+          <t>53218422.0</t>
         </is>
       </c>
       <c r="BE22" t="inlineStr">
@@ -9756,7 +9756,7 @@
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>-8.19</t>
+          <t>-9.76</t>
         </is>
       </c>
       <c r="BI22" t="inlineStr">
@@ -9801,7 +9801,7 @@
       </c>
       <c r="BQ22" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR22" t="inlineStr">
@@ -9811,7 +9811,7 @@
       </c>
       <c r="BS22" t="inlineStr">
         <is>
-          <t>1.05</t>
+          <t>1.03</t>
         </is>
       </c>
       <c r="BT22" t="inlineStr">
@@ -9841,7 +9841,7 @@
       </c>
       <c r="BY22" t="inlineStr">
         <is>
-          <t>29.71</t>
+          <t>29.67</t>
         </is>
       </c>
       <c r="BZ22" t="inlineStr">
@@ -9866,22 +9866,22 @@
       </c>
       <c r="CD22" t="inlineStr">
         <is>
-          <t>38.2</t>
+          <t>38.1</t>
         </is>
       </c>
       <c r="CE22" t="inlineStr">
         <is>
-          <t>38.4</t>
+          <t>38.7</t>
         </is>
       </c>
       <c r="CF22" t="inlineStr">
         <is>
-          <t>37.95</t>
+          <t>37.3</t>
         </is>
       </c>
       <c r="CG22" t="inlineStr">
         <is>
-          <t>38.1</t>
+          <t>37.45</t>
         </is>
       </c>
       <c r="CH22" t="inlineStr">
@@ -9913,12 +9913,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>1.18</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>605.721</t>
+          <t>504.317</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -9943,12 +9943,12 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>0.91</t>
+          <t>1.07</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>29.75</t>
+          <t>20.39</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -10023,17 +10023,17 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>6.45</t>
+          <t>5.37</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>0.40</t>
+          <t>-0.39</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
@@ -10044,73 +10044,73 @@
       <c r="AC23" t="inlineStr"/>
       <c r="AD23" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AE23" t="inlineStr">
         <is>
-          <t>915</t>
+          <t>511</t>
         </is>
       </c>
       <c r="AF23" t="inlineStr">
         <is>
-          <t>21.95</t>
+          <t>28.13</t>
         </is>
       </c>
       <c r="AG23" t="inlineStr">
         <is>
-          <t>7.32</t>
+          <t>16.69</t>
         </is>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
-          <t>-0.94</t>
+          <t>-0.55</t>
         </is>
       </c>
       <c r="AI23" t="inlineStr">
         <is>
-          <t>-3.10</t>
+          <t>-3.22</t>
         </is>
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>-3.87</t>
+          <t>-3.86</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
         <is>
-          <t>-0.91</t>
+          <t>-1.12</t>
         </is>
       </c>
       <c r="AL23" t="inlineStr">
         <is>
-          <t>38.46</t>
+          <t>38.31</t>
         </is>
       </c>
       <c r="AM23" t="n">
-        <v>39.69</v>
+        <v>39.58</v>
       </c>
       <c r="AN23" t="n">
-        <v>41.29</v>
+        <v>41.17</v>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>41.67</t>
+          <t>41.64</t>
         </is>
       </c>
       <c r="AP23" t="inlineStr">
         <is>
-          <t>-16.76</t>
+          <t>-13.76</t>
         </is>
       </c>
       <c r="AQ23" t="inlineStr">
         <is>
-          <t>-0.85</t>
+          <t>-0.86</t>
         </is>
       </c>
       <c r="AR23" t="inlineStr">
         <is>
-          <t>-0.73</t>
+          <t>-0.75</t>
         </is>
       </c>
       <c r="AS23" t="inlineStr">
@@ -10120,7 +10120,7 @@
       </c>
       <c r="AT23" t="inlineStr">
         <is>
-          <t>-127.09</t>
+          <t>-128.06</t>
         </is>
       </c>
       <c r="AU23" t="inlineStr">
@@ -10130,43 +10130,43 @@
       </c>
       <c r="AV23" t="inlineStr">
         <is>
-          <t>150423914.0772532</t>
+          <t>150251779.8621429</t>
         </is>
       </c>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>23042470.0</t>
+          <t>19248593.0</t>
         </is>
       </c>
       <c r="AX23" t="n">
-        <v>33965584</v>
+        <v>31147112</v>
       </c>
       <c r="AY23" t="inlineStr">
         <is>
-          <t>26178217.9</t>
+          <t>25871081.1</t>
         </is>
       </c>
       <c r="AZ23" t="n">
-        <v>28206383.42</v>
+        <v>28091032.78</v>
       </c>
       <c r="BA23" t="inlineStr">
         <is>
-          <t>7787366</t>
+          <t>5276030</t>
         </is>
       </c>
       <c r="BB23" t="inlineStr">
         <is>
-          <t>-365198.417442461</t>
+          <t>-239589.4123123131</t>
         </is>
       </c>
       <c r="BC23" t="inlineStr">
         <is>
-          <t>1450493.769176625</t>
+          <t>451260.1159035005</t>
         </is>
       </c>
       <c r="BD23" t="inlineStr">
         <is>
-          <t>23042470.0</t>
+          <t>19248593.0</t>
         </is>
       </c>
       <c r="BE23" t="inlineStr">
@@ -10231,7 +10231,7 @@
       </c>
       <c r="BQ23" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;可能出現反轉訊號&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;3&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR23" t="inlineStr">
@@ -10271,7 +10271,7 @@
       </c>
       <c r="BY23" t="inlineStr">
         <is>
-          <t>29.71</t>
+          <t>29.67</t>
         </is>
       </c>
       <c r="BZ23" t="inlineStr">
@@ -10296,17 +10296,17 @@
       </c>
       <c r="CD23" t="inlineStr">
         <is>
-          <t>38.0</t>
+          <t>38.2</t>
         </is>
       </c>
       <c r="CE23" t="inlineStr">
         <is>
-          <t>38.3</t>
+          <t>38.4</t>
         </is>
       </c>
       <c r="CF23" t="inlineStr">
         <is>
-          <t>37.75</t>
+          <t>37.95</t>
         </is>
       </c>
       <c r="CG23" t="inlineStr">

--- a/Result/checksun_type/塔架.xlsx
+++ b/Result/checksun_type/塔架.xlsx
@@ -883,12 +883,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>-1.04</t>
+          <t>-0.35</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>494.362</t>
+          <t>800.978</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>141.0</t>
+          <t>140.5</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-1.84</t>
+          <t>-1.3</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>-47.22</t>
+          <t>-37.50</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-40.51</t>
+          <t>-40.72</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -993,17 +993,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>2.04</t>
+          <t>3.31</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>-2.13</t>
+          <t>0.37</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1014,73 +1014,73 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>11</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>494</t>
+          <t>801</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>87.5</t>
+          <t>83.33</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>77.41</t>
+          <t>90.28</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>1.29</t>
+          <t>0.14</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>-3.35</t>
+          <t>-2.14</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>-8.68</t>
+          <t>-8.77</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>-6.17</t>
+          <t>-6.13</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>139.2</t>
+          <t>140.3</t>
         </is>
       </c>
       <c r="AM2" t="n">
-        <v>144.02</v>
+        <v>143.38</v>
       </c>
       <c r="AN2" t="n">
-        <v>157.72</v>
+        <v>157.15</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>168.09</t>
+          <t>167.42</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>12.54</t>
+          <t>15.78</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>-6.06</t>
+          <t>-5.62</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>-6.93</t>
+          <t>-6.67</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -1090,7 +1090,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-127.86</t>
+          <t>-126.80</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1100,43 +1100,43 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>1686680961.147857</t>
+          <t>1684514497.82311</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>70132250.0</t>
+          <t>111993447.0</t>
         </is>
       </c>
       <c r="AX2" t="n">
-        <v>151097591.6</v>
+        <v>138810283.4</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>286274053.3</t>
+          <t>222079436.2</t>
         </is>
       </c>
       <c r="AZ2" t="n">
-        <v>248269560.06</v>
+        <v>246079338.72</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>-135176461</t>
+          <t>-83269152</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>-1190585.570376122</t>
+          <t>-4866933.171784954</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>-22288000.98619333</t>
+          <t>-25086844.97953352</t>
         </is>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
-          <t>70132250.0</t>
+          <t>111993447.0</t>
         </is>
       </c>
       <c r="BE2" t="inlineStr">
@@ -1156,7 +1156,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>-21.67</t>
+          <t>-21.94</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
@@ -1201,22 +1201,22 @@
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
         <is>
-          <t>價跌量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>3.25</t>
+          <t>3.24</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
         <is>
-          <t>2.95</t>
+          <t>2.96</t>
         </is>
       </c>
       <c r="BU2" t="inlineStr">
@@ -1226,7 +1226,7 @@
       </c>
       <c r="BV2" t="inlineStr">
         <is>
-          <t>26.5</t>
+          <t>26.41</t>
         </is>
       </c>
       <c r="BW2" t="inlineStr">
@@ -1241,12 +1241,12 @@
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>29.67</t>
+          <t>29.63</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>34812</t>
+          <t>34689</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
@@ -1266,22 +1266,22 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>144.0</t>
+          <t>141.5</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>144.0</t>
+          <t>141.5</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>141.0</t>
+          <t>139.0</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>141.0</t>
+          <t>140.5</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
@@ -1313,12 +1313,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2.48</t>
+          <t>-1.04</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>885.355</t>
+          <t>494.362</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1328,7 +1328,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>142.5</t>
+          <t>141.0</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1338,17 +1338,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-1.06</t>
+          <t>-0.36</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-1.84</t>
+          <t>-1.3</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>-37.74</t>
+          <t>-47.22</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1413,7 +1413,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-39.87</t>
+          <t>-40.51</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1423,17 +1423,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>3.66</t>
+          <t>2.04</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>0.36</t>
+          <t>-2.13</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1444,73 +1444,73 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>11</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>494</t>
+          <t>801</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>87.5</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>62.28</t>
+          <t>77.41</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>3.26</t>
+          <t>1.29</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>-4.63</t>
+          <t>-3.35</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-8.6</t>
+          <t>-8.68</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>-6.19</t>
+          <t>-6.17</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>138.0</t>
+          <t>139.2</t>
         </is>
       </c>
       <c r="AM3" t="n">
-        <v>144.7</v>
+        <v>144.02</v>
       </c>
       <c r="AN3" t="n">
-        <v>158.31</v>
+        <v>157.72</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>168.75</t>
+          <t>168.09</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>7.75</t>
+          <t>12.54</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>-6.60</t>
+          <t>-6.06</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>-7.15</t>
+          <t>-6.93</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1520,7 +1520,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-128.73</t>
+          <t>-127.86</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1530,43 +1530,43 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>1686680961.147857</t>
+          <t>1684514497.82311</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>126140252.0</t>
+          <t>70132250.0</t>
         </is>
       </c>
       <c r="AX3" t="n">
-        <v>179646773.6</v>
+        <v>151097591.6</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>288541776.1</t>
+          <t>286274053.3</t>
         </is>
       </c>
       <c r="AZ3" t="n">
-        <v>249860076.6</v>
+        <v>248269560.06</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>-108895002</t>
+          <t>-135176461</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>2645308.141590643</t>
+          <t>-1190585.570376122</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>-13008524.13905758</t>
+          <t>-22288000.98619333</t>
         </is>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
-          <t>126140252.0</t>
+          <t>70132250.0</t>
         </is>
       </c>
       <c r="BE3" t="inlineStr">
@@ -1586,7 +1586,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>-20.83</t>
+          <t>-21.67</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
@@ -1631,22 +1631,22 @@
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價跌量-</t>
         </is>
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>3.28</t>
+          <t>3.25</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
         <is>
-          <t>2.95</t>
+          <t>2.96</t>
         </is>
       </c>
       <c r="BU3" t="inlineStr">
@@ -1656,7 +1656,7 @@
       </c>
       <c r="BV3" t="inlineStr">
         <is>
-          <t>26.5</t>
+          <t>26.41</t>
         </is>
       </c>
       <c r="BW3" t="inlineStr">
@@ -1671,12 +1671,12 @@
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>29.67</t>
+          <t>29.63</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
-          <t>34812</t>
+          <t>34689</t>
         </is>
       </c>
       <c r="CA3" t="inlineStr">
@@ -1696,22 +1696,22 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
+          <t>144.0</t>
+        </is>
+      </c>
+      <c r="CE3" t="inlineStr">
+        <is>
+          <t>144.0</t>
+        </is>
+      </c>
+      <c r="CF3" t="inlineStr">
+        <is>
           <t>141.0</t>
         </is>
       </c>
-      <c r="CE3" t="inlineStr">
-        <is>
-          <t>143.5</t>
-        </is>
-      </c>
-      <c r="CF3" t="inlineStr">
+      <c r="CG3" t="inlineStr">
         <is>
           <t>141.0</t>
-        </is>
-      </c>
-      <c r="CG3" t="inlineStr">
-        <is>
-          <t>142.5</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
@@ -1733,7 +1733,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>【e】</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1743,127 +1743,127 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
+          <t>2.48</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>885.355</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>142.5</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>-1.42</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>-1.3</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>-37.74</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>-65.0</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>2025-06-04 00:00:00</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>2025-06-30 00:00:00</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>2025-05-09 00:00:00</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>2025-05-23 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>199.0</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>237.0</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>181.0</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>178.0</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>-39.87</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>11.80</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-11-26</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>3.66</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
           <t>0.36</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>1070.548</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>139.0</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>1.42</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>-1.84</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>-30.56</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>-65.0</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>2025-06-04 00:00:00</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>2025-06-30 00:00:00</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>2025-05-09 00:00:00</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>2025-05-23 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t>199.0</t>
-        </is>
-      </c>
-      <c r="R4" t="inlineStr">
-        <is>
-          <t>237.0</t>
-        </is>
-      </c>
-      <c r="S4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T4" t="inlineStr">
-        <is>
-          <t>181.0</t>
-        </is>
-      </c>
-      <c r="U4" t="inlineStr">
-        <is>
-          <t>178.0</t>
-        </is>
-      </c>
-      <c r="V4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>-41.35</t>
-        </is>
-      </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>11.80</t>
-        </is>
-      </c>
-      <c r="Y4" t="inlineStr">
-        <is>
-          <t>2025-11-25</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>4.43</t>
-        </is>
-      </c>
-      <c r="AA4" t="inlineStr">
-        <is>
-          <t>-0.71</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1874,37 +1874,37 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>11</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>494</t>
+          <t>801</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>44.74</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>36.84</t>
+          <t>62.28</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>2.51</t>
+          <t>3.26</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>-6.71</t>
+          <t>-4.63</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>-8.49</t>
+          <t>-8.6</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
@@ -1914,33 +1914,33 @@
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>135.6</t>
+          <t>138.0</t>
         </is>
       </c>
       <c r="AM4" t="n">
-        <v>145.35</v>
+        <v>144.7</v>
       </c>
       <c r="AN4" t="n">
-        <v>158.83</v>
+        <v>158.31</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>169.32</t>
+          <t>168.75</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>-0.61</t>
+          <t>7.75</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>-7.33</t>
+          <t>-6.60</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>-7.29</t>
+          <t>-7.15</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1950,7 +1950,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-129.29</t>
+          <t>-128.73</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1960,43 +1960,43 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>1686680961.147857</t>
+          <t>1684514497.82311</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>149355643.0</t>
+          <t>126140252.0</t>
         </is>
       </c>
       <c r="AX4" t="n">
-        <v>199168061</v>
+        <v>179646773.6</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>286806442.7</t>
+          <t>288541776.1</t>
         </is>
       </c>
       <c r="AZ4" t="n">
-        <v>252995092.08</v>
+        <v>249860076.6</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>-87638381</t>
+          <t>-108895002</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>5491459.465344865</t>
+          <t>2645308.141590643</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>-5288395.852468729</t>
+          <t>-13008524.13905758</t>
         </is>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
-          <t>149355643.0</t>
+          <t>126140252.0</t>
         </is>
       </c>
       <c r="BE4" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>-22.78</t>
+          <t>-20.83</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
@@ -2061,22 +2061,22 @@
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>3.20</t>
+          <t>3.28</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
         <is>
-          <t>2.95</t>
+          <t>2.96</t>
         </is>
       </c>
       <c r="BU4" t="inlineStr">
@@ -2086,7 +2086,7 @@
       </c>
       <c r="BV4" t="inlineStr">
         <is>
-          <t>26.5</t>
+          <t>26.41</t>
         </is>
       </c>
       <c r="BW4" t="inlineStr">
@@ -2101,12 +2101,12 @@
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>29.67</t>
+          <t>29.63</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
-          <t>34812</t>
+          <t>34689</t>
         </is>
       </c>
       <c r="CA4" t="inlineStr">
@@ -2126,22 +2126,22 @@
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>139.5</t>
+          <t>141.0</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
+          <t>143.5</t>
+        </is>
+      </c>
+      <c r="CF4" t="inlineStr">
+        <is>
           <t>141.0</t>
         </is>
       </c>
-      <c r="CF4" t="inlineStr">
-        <is>
-          <t>138.0</t>
-        </is>
-      </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>139.0</t>
+          <t>142.5</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
@@ -2173,12 +2173,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>2.56</t>
+          <t>0.36</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>1721.237</t>
+          <t>1070.548</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2188,7 +2188,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>138.5</t>
+          <t>139.0</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2198,17 +2198,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>1.77</t>
+          <t>1.07</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-1.84</t>
+          <t>-1.3</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>-13.08</t>
+          <t>-30.56</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2273,7 +2273,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-41.56</t>
+          <t>-41.35</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2283,17 +2283,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>7.12</t>
+          <t>4.43</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>1.87</t>
+          <t>-0.71</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2304,73 +2304,73 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>11</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>494</t>
+          <t>801</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>42.11</t>
+          <t>44.74</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>29.62</t>
+          <t>36.84</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>3.44</t>
+          <t>2.51</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>-8.46</t>
+          <t>-6.71</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>-8.28</t>
+          <t>-8.49</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>-6.17</t>
+          <t>-6.19</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>133.9</t>
+          <t>135.6</t>
         </is>
       </c>
       <c r="AM5" t="n">
-        <v>146.28</v>
+        <v>145.35</v>
       </c>
       <c r="AN5" t="n">
-        <v>159.48</v>
+        <v>158.83</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>169.96</t>
+          <t>169.32</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>-7.31</t>
+          <t>-0.61</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>-7.81</t>
+          <t>-7.33</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>-7.28</t>
+          <t>-7.29</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -2380,7 +2380,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-129.24</t>
+          <t>-129.29</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2390,43 +2390,43 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>1686680961.147857</t>
+          <t>1684514497.82311</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>236429825.0</t>
+          <t>149355643.0</t>
         </is>
       </c>
       <c r="AX5" t="n">
-        <v>243968869</v>
+        <v>199168061</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>280669574.0</t>
+          <t>286806442.7</t>
         </is>
       </c>
       <c r="AZ5" t="n">
-        <v>255272113.08</v>
+        <v>252995092.08</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>-36700705</t>
+          <t>-87638381</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>7451433.159492791</t>
+          <t>5491459.465344865</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>3441866.801674962</t>
+          <t>-5288395.852468729</t>
         </is>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
-          <t>236429825.0</t>
+          <t>149355643.0</t>
         </is>
       </c>
       <c r="BE5" t="inlineStr">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>-23.06</t>
+          <t>-22.78</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
@@ -2491,7 +2491,7 @@
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;可能出現反轉訊號&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;3&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
@@ -2501,12 +2501,12 @@
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>3.19</t>
+          <t>3.20</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
         <is>
-          <t>2.95</t>
+          <t>2.96</t>
         </is>
       </c>
       <c r="BU5" t="inlineStr">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="BV5" t="inlineStr">
         <is>
-          <t>26.5</t>
+          <t>26.41</t>
         </is>
       </c>
       <c r="BW5" t="inlineStr">
@@ -2531,12 +2531,12 @@
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>29.67</t>
+          <t>29.63</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
-          <t>34812</t>
+          <t>34689</t>
         </is>
       </c>
       <c r="CA5" t="inlineStr">
@@ -2556,22 +2556,22 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>136.5</t>
+          <t>139.5</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>139.5</t>
+          <t>141.0</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>135.0</t>
+          <t>138.0</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>138.5</t>
+          <t>139.0</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
@@ -2603,12 +2603,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>2.56</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>1302.953</t>
+          <t>1721.237</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2618,7 +2618,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>135.0</t>
+          <t>138.5</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2628,17 +2628,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>4.26</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-1.84</t>
+          <t>-1.3</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>12.02</t>
+          <t>-13.08</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2703,7 +2703,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-43.04</t>
+          <t>-41.56</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2713,17 +2713,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>5.39</t>
+          <t>7.12</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>3.05</t>
+          <t>1.87</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2734,73 +2734,73 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>11</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>494</t>
+          <t>801</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>23.68</t>
+          <t>42.11</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>15.59</t>
+          <t>29.62</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>1.58</t>
+          <t>3.44</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>-9.76</t>
+          <t>-8.46</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>-8.05</t>
+          <t>-8.28</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>-6.11</t>
+          <t>-6.17</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>132.9</t>
+          <t>133.9</t>
         </is>
       </c>
       <c r="AM6" t="n">
-        <v>147.28</v>
+        <v>146.28</v>
       </c>
       <c r="AN6" t="n">
-        <v>160.17</v>
+        <v>159.48</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>170.59</t>
+          <t>169.96</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>-15.53</t>
+          <t>-7.31</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>-8.25</t>
+          <t>-7.81</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>-7.14</t>
+          <t>-7.28</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -2810,7 +2810,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-128.71</t>
+          <t>-129.24</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2820,43 +2820,43 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>1686680961.147857</t>
+          <t>1684514497.82311</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>173429988.0</t>
+          <t>236429825.0</t>
         </is>
       </c>
       <c r="AX6" t="n">
-        <v>305348589</v>
+        <v>243968869</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>272591978.0</t>
+          <t>280669574.0</t>
         </is>
       </c>
       <c r="AZ6" t="n">
-        <v>254388028.92</v>
+        <v>255272113.08</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>32756611</t>
+          <t>-36700705</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>8180445.224550578</t>
+          <t>7451433.159492791</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>6461370.136106104</t>
+          <t>3441866.801674962</t>
         </is>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
-          <t>173429988.0</t>
+          <t>236429825.0</t>
         </is>
       </c>
       <c r="BE6" t="inlineStr">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>-25.00</t>
+          <t>-23.06</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
@@ -2921,7 +2921,7 @@
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;可能出現反轉訊號&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;3&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
@@ -2931,12 +2931,12 @@
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>3.11</t>
+          <t>3.19</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
         <is>
-          <t>2.95</t>
+          <t>2.96</t>
         </is>
       </c>
       <c r="BU6" t="inlineStr">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="BV6" t="inlineStr">
         <is>
-          <t>26.5</t>
+          <t>26.41</t>
         </is>
       </c>
       <c r="BW6" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>29.67</t>
+          <t>29.63</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
         <is>
-          <t>34812</t>
+          <t>34689</t>
         </is>
       </c>
       <c r="CA6" t="inlineStr">
@@ -2986,22 +2986,22 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>132.5</t>
+          <t>136.5</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
+          <t>139.5</t>
+        </is>
+      </c>
+      <c r="CF6" t="inlineStr">
+        <is>
           <t>135.0</t>
         </is>
       </c>
-      <c r="CF6" t="inlineStr">
-        <is>
-          <t>131.0</t>
-        </is>
-      </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>135.0</t>
+          <t>138.5</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
@@ -3033,12 +3033,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>3.41</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1595.31</t>
+          <t>1302.953</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3058,17 +3058,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>4.26</t>
+          <t>3.91</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-1.84</t>
+          <t>-1.3</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>53.45</t>
+          <t>12.02</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3143,17 +3143,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>6.60</t>
+          <t>5.39</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>1.92</t>
+          <t>3.05</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3164,73 +3164,73 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>11</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>494</t>
+          <t>801</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>23.08</t>
+          <t>23.68</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>7.69</t>
+          <t>15.59</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>1.20</t>
+          <t>1.58</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>-10.06</t>
+          <t>-9.76</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>-7.84</t>
+          <t>-8.05</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>-6.04</t>
+          <t>-6.11</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>133.4</t>
+          <t>132.9</t>
         </is>
       </c>
       <c r="AM7" t="n">
-        <v>148.32</v>
+        <v>147.28</v>
       </c>
       <c r="AN7" t="n">
-        <v>160.95</v>
+        <v>160.17</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>171.29</t>
+          <t>170.59</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>-21.52</t>
+          <t>-15.53</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>-8.35</t>
+          <t>-8.25</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>-6.87</t>
+          <t>-7.14</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -3240,7 +3240,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-127.59</t>
+          <t>-128.71</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3250,43 +3250,43 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>1686680961.147857</t>
+          <t>1684514497.82311</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>212878160.0</t>
+          <t>173429988.0</t>
         </is>
       </c>
       <c r="AX7" t="n">
-        <v>421450515</v>
+        <v>305348589</v>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>274650710.4</t>
+          <t>272591978.0</t>
         </is>
       </c>
       <c r="AZ7" t="n">
-        <v>254522728.7</v>
+        <v>254388028.92</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>146799804</t>
+          <t>32756611</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>8493004.331540482</t>
+          <t>8180445.224550578</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>17294165.64471823</t>
+          <t>6461370.136106104</t>
         </is>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
-          <t>212878160.0</t>
+          <t>173429988.0</t>
         </is>
       </c>
       <c r="BE7" t="inlineStr">
@@ -3351,12 +3351,12 @@
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;可能出現反轉訊號&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;3&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS7" t="inlineStr">
@@ -3366,7 +3366,7 @@
       </c>
       <c r="BT7" t="inlineStr">
         <is>
-          <t>2.95</t>
+          <t>2.96</t>
         </is>
       </c>
       <c r="BU7" t="inlineStr">
@@ -3376,7 +3376,7 @@
       </c>
       <c r="BV7" t="inlineStr">
         <is>
-          <t>26.5</t>
+          <t>26.41</t>
         </is>
       </c>
       <c r="BW7" t="inlineStr">
@@ -3391,12 +3391,12 @@
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>29.67</t>
+          <t>29.63</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
         <is>
-          <t>34812</t>
+          <t>34689</t>
         </is>
       </c>
       <c r="CA7" t="inlineStr">
@@ -3416,17 +3416,17 @@
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>132.0</t>
+          <t>132.5</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>136.0</t>
+          <t>135.0</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>131.5</t>
+          <t>131.0</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
@@ -3463,12 +3463,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>3.41</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>1712.06</t>
+          <t>1595.31</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3478,7 +3478,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>130.5</t>
+          <t>135.0</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3488,17 +3488,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>7.45</t>
+          <t>3.91</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-1.84</t>
+          <t>-1.3</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>50.94</t>
+          <t>53.45</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3563,7 +3563,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-44.94</t>
+          <t>-43.04</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3573,17 +3573,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>7.08</t>
+          <t>6.60</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>-1.14</t>
+          <t>1.92</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3594,73 +3594,73 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>11</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>494</t>
+          <t>801</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>23.08</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>7.69</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>-4.26</t>
+          <t>1.20</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>-8.89</t>
+          <t>-10.06</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>-7.5</t>
+          <t>-7.84</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>-5.97</t>
+          <t>-6.04</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>136.3</t>
+          <t>133.4</t>
         </is>
       </c>
       <c r="AM8" t="n">
-        <v>149.6</v>
+        <v>148.32</v>
       </c>
       <c r="AN8" t="n">
-        <v>161.73</v>
+        <v>160.95</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>171.99</t>
+          <t>171.29</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>-28.35</t>
+          <t>-21.52</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>-8.34</t>
+          <t>-8.35</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>-6.50</t>
+          <t>-6.87</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -3670,7 +3670,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-126.11</t>
+          <t>-127.59</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3680,43 +3680,43 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>1686680961.147857</t>
+          <t>1684514497.82311</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>223746689.0</t>
+          <t>212878160.0</t>
         </is>
       </c>
       <c r="AX8" t="n">
-        <v>397436778.6</v>
+        <v>421450515</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>263301806.5</t>
+          <t>274650710.4</t>
         </is>
       </c>
       <c r="AZ8" t="n">
-        <v>254911229.58</v>
+        <v>254522728.7</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>134134972</t>
+          <t>146799804</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>6892793.183689982</t>
+          <t>8493004.331540482</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>27925349.16970986</t>
+          <t>17294165.64471823</t>
         </is>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
-          <t>223746689.0</t>
+          <t>212878160.0</t>
         </is>
       </c>
       <c r="BE8" t="inlineStr">
@@ -3736,7 +3736,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>-27.50</t>
+          <t>-25.00</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
@@ -3781,22 +3781,22 @@
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;可能出現反轉訊號&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;3&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
         <is>
-          <t>價漲量縮</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>3.01</t>
+          <t>3.11</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
         <is>
-          <t>2.95</t>
+          <t>2.96</t>
         </is>
       </c>
       <c r="BU8" t="inlineStr">
@@ -3806,7 +3806,7 @@
       </c>
       <c r="BV8" t="inlineStr">
         <is>
-          <t>26.5</t>
+          <t>26.41</t>
         </is>
       </c>
       <c r="BW8" t="inlineStr">
@@ -3821,12 +3821,12 @@
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>29.67</t>
+          <t>29.63</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
         <is>
-          <t>34812</t>
+          <t>34689</t>
         </is>
       </c>
       <c r="CA8" t="inlineStr">
@@ -3846,22 +3846,22 @@
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>131.0</t>
+          <t>132.0</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>133.5</t>
+          <t>136.0</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>129.0</t>
+          <t>131.5</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>130.5</t>
+          <t>135.0</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
@@ -3893,12 +3893,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>-2.26</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2844.986</t>
+          <t>1712.06</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3918,17 +3918,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>7.45</t>
+          <t>7.12</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-1.84</t>
+          <t>-1.3</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>48.25</t>
+          <t>50.94</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -4003,17 +4003,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>11.77</t>
+          <t>7.08</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>-2.29</t>
+          <t>-1.14</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4024,12 +4024,12 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>11</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>494</t>
+          <t>801</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
@@ -4044,53 +4044,53 @@
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>-6.85</t>
+          <t>-4.26</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>-7.30</t>
+          <t>-8.89</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>-7.05</t>
+          <t>-7.5</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>-5.89</t>
+          <t>-5.97</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>140.1</t>
+          <t>136.3</t>
         </is>
       </c>
       <c r="AM9" t="n">
-        <v>151.12</v>
+        <v>149.6</v>
       </c>
       <c r="AN9" t="n">
-        <v>162.59</v>
+        <v>161.73</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>172.77</t>
+          <t>171.99</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>-28.43</t>
+          <t>-28.35</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>-7.75</t>
+          <t>-8.34</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>-6.04</t>
+          <t>-6.50</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -4100,7 +4100,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-124.26</t>
+          <t>-126.11</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4110,43 +4110,43 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>1686680961.147857</t>
+          <t>1684514497.82311</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>373359683.0</t>
+          <t>223746689.0</t>
         </is>
       </c>
       <c r="AX9" t="n">
-        <v>374444824.4</v>
+        <v>397436778.6</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>252575891.8</t>
+          <t>263301806.5</t>
         </is>
       </c>
       <c r="AZ9" t="n">
-        <v>255257682.72</v>
+        <v>254911229.58</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>121868932</t>
+          <t>134134972</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>3068692.09532273</t>
+          <t>6892793.183689982</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>40950935.056494</t>
+          <t>27925349.16970986</t>
         </is>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
-          <t>373359683.0</t>
+          <t>223746689.0</t>
         </is>
       </c>
       <c r="BE9" t="inlineStr">
@@ -4211,12 +4211,12 @@
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價漲量縮</t>
         </is>
       </c>
       <c r="BS9" t="inlineStr">
@@ -4226,7 +4226,7 @@
       </c>
       <c r="BT9" t="inlineStr">
         <is>
-          <t>2.95</t>
+          <t>2.96</t>
         </is>
       </c>
       <c r="BU9" t="inlineStr">
@@ -4236,7 +4236,7 @@
       </c>
       <c r="BV9" t="inlineStr">
         <is>
-          <t>26.5</t>
+          <t>26.41</t>
         </is>
       </c>
       <c r="BW9" t="inlineStr">
@@ -4251,12 +4251,12 @@
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>29.67</t>
+          <t>29.63</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
         <is>
-          <t>34812</t>
+          <t>34689</t>
         </is>
       </c>
       <c r="CA9" t="inlineStr">
@@ -4276,17 +4276,17 @@
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>133.0</t>
+          <t>131.0</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>134.5</t>
+          <t>133.5</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>129.5</t>
+          <t>129.0</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
@@ -4323,12 +4323,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>-2.96</t>
+          <t>-2.26</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>4003.393</t>
+          <t>2844.986</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4338,7 +4338,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>133.5</t>
+          <t>130.5</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4348,17 +4348,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>5.32</t>
+          <t>7.12</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-1.84</t>
+          <t>-1.3</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>36.89</t>
+          <t>48.25</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4423,7 +4423,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-43.67</t>
+          <t>-44.94</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4433,17 +4433,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>16.56</t>
+          <t>11.77</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>-5.24</t>
+          <t>-2.29</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4454,12 +4454,12 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>11</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>494</t>
+          <t>801</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
@@ -4474,53 +4474,53 @@
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>-7.23</t>
+          <t>-6.85</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>-5.73</t>
+          <t>-7.30</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>-6.6</t>
+          <t>-7.05</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>-5.82</t>
+          <t>-5.89</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>143.9</t>
+          <t>140.1</t>
         </is>
       </c>
       <c r="AM10" t="n">
-        <v>152.65</v>
+        <v>151.12</v>
       </c>
       <c r="AN10" t="n">
-        <v>163.44</v>
+        <v>162.59</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>173.54</t>
+          <t>172.77</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>-22.90</t>
+          <t>-28.43</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>-6.89</t>
+          <t>-7.75</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>-5.61</t>
+          <t>-6.04</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -4530,7 +4530,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-122.53</t>
+          <t>-124.26</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4540,43 +4540,43 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>1686680961.147857</t>
+          <t>1684514497.82311</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>543328425.0</t>
+          <t>373359683.0</t>
         </is>
       </c>
       <c r="AX10" t="n">
-        <v>317370279</v>
+        <v>374444824.4</v>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>231842549.9</t>
+          <t>252575891.8</t>
         </is>
       </c>
       <c r="AZ10" t="n">
-        <v>254515985.98</v>
+        <v>255257682.72</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>85527729</t>
+          <t>121868932</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>-3818988.443072045</t>
+          <t>3068692.09532273</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>42066417.85702515</t>
+          <t>40950935.056494</t>
         </is>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
-          <t>543328425.0</t>
+          <t>373359683.0</t>
         </is>
       </c>
       <c r="BE10" t="inlineStr">
@@ -4596,7 +4596,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>-25.83</t>
+          <t>-27.50</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
@@ -4641,7 +4641,7 @@
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;衝高回落,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
@@ -4651,12 +4651,12 @@
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>3.08</t>
+          <t>3.01</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
         <is>
-          <t>2.95</t>
+          <t>2.96</t>
         </is>
       </c>
       <c r="BU10" t="inlineStr">
@@ -4666,7 +4666,7 @@
       </c>
       <c r="BV10" t="inlineStr">
         <is>
-          <t>26.5</t>
+          <t>26.41</t>
         </is>
       </c>
       <c r="BW10" t="inlineStr">
@@ -4681,12 +4681,12 @@
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>29.67</t>
+          <t>29.63</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
         <is>
-          <t>34812</t>
+          <t>34689</t>
         </is>
       </c>
       <c r="CA10" t="inlineStr">
@@ -4706,22 +4706,22 @@
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>135.0</t>
+          <t>133.0</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>141.5</t>
+          <t>134.5</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>132.5</t>
+          <t>129.5</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>133.5</t>
+          <t>130.5</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
@@ -4753,12 +4753,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>-8.16</t>
+          <t>-2.96</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>5388.546</t>
+          <t>4003.393</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4768,7 +4768,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>137.5</t>
+          <t>133.5</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4778,17 +4778,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>2.48</t>
+          <t>4.98</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-1.84</t>
+          <t>-1.3</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>18.56</t>
+          <t>36.89</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4853,7 +4853,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-41.98</t>
+          <t>-43.67</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4863,17 +4863,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>22.28</t>
+          <t>16.56</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>-5.06</t>
+          <t>-5.24</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4884,12 +4884,12 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>11</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>494</t>
+          <t>801</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
@@ -4904,53 +4904,53 @@
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>-6.59</t>
+          <t>-7.23</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>-4.57</t>
+          <t>-5.73</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>-6.11</t>
+          <t>-6.6</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>-5.70</t>
+          <t>-5.82</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>147.2</t>
+          <t>143.9</t>
         </is>
       </c>
       <c r="AM11" t="n">
-        <v>154.25</v>
+        <v>152.65</v>
       </c>
       <c r="AN11" t="n">
-        <v>164.29</v>
+        <v>163.44</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>174.21</t>
+          <t>173.54</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>-13.45</t>
+          <t>-22.90</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>-6.00</t>
+          <t>-6.89</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>-5.29</t>
+          <t>-5.61</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -4960,7 +4960,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-121.24</t>
+          <t>-122.53</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -4970,43 +4970,43 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>1686680961.147857</t>
+          <t>1684514497.82311</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>753939618.0</t>
+          <t>543328425.0</t>
         </is>
       </c>
       <c r="AX11" t="n">
-        <v>239835367</v>
+        <v>317370279</v>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>202283159.5</t>
+          <t>231842549.9</t>
         </is>
       </c>
       <c r="AZ11" t="n">
-        <v>250790390.86</v>
+        <v>254515985.98</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>37552207</t>
+          <t>85527729</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>-12161789.58854426</t>
+          <t>-3818988.443072045</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>23946656.00574735</t>
+          <t>42066417.85702515</t>
         </is>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
-          <t>753939618.0</t>
+          <t>543328425.0</t>
         </is>
       </c>
       <c r="BE11" t="inlineStr">
@@ -5026,7 +5026,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>-23.61</t>
+          <t>-25.83</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
@@ -5071,7 +5071,7 @@
       </c>
       <c r="BQ11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;衝高回落,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR11" t="inlineStr">
@@ -5081,12 +5081,12 @@
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>3.17</t>
+          <t>3.08</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
         <is>
-          <t>2.95</t>
+          <t>2.96</t>
         </is>
       </c>
       <c r="BU11" t="inlineStr">
@@ -5096,7 +5096,7 @@
       </c>
       <c r="BV11" t="inlineStr">
         <is>
-          <t>26.5</t>
+          <t>26.41</t>
         </is>
       </c>
       <c r="BW11" t="inlineStr">
@@ -5111,12 +5111,12 @@
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>29.67</t>
+          <t>29.63</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
         <is>
-          <t>34812</t>
+          <t>34689</t>
         </is>
       </c>
       <c r="CA11" t="inlineStr">
@@ -5136,22 +5136,22 @@
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>147.0</t>
+          <t>135.0</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>147.0</t>
+          <t>141.5</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>135.0</t>
+          <t>132.5</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>137.5</t>
+          <t>133.5</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
@@ -5183,12 +5183,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-8.16</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>617.888</t>
+          <t>5388.546</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5198,7 +5198,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>149.5</t>
+          <t>137.5</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5208,17 +5208,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-6.03</t>
+          <t>2.14</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-1.84</t>
+          <t>-1.3</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>-14.19</t>
+          <t>18.56</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5283,7 +5283,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-36.92</t>
+          <t>-41.98</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5293,17 +5293,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>2.56</t>
+          <t>22.28</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>-1.34</t>
+          <t>-5.06</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5314,12 +5314,12 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>11</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>494</t>
+          <t>801</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
@@ -5334,53 +5334,53 @@
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>-0.07</t>
+          <t>-6.59</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>-3.96</t>
+          <t>-4.57</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>-5.65</t>
+          <t>-6.11</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>-5.63</t>
+          <t>-5.70</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>149.6</t>
+          <t>147.2</t>
         </is>
       </c>
       <c r="AM12" t="n">
-        <v>155.78</v>
+        <v>154.25</v>
       </c>
       <c r="AN12" t="n">
-        <v>165.1</v>
+        <v>164.29</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>174.95</t>
+          <t>174.21</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>-1.33</t>
+          <t>-13.45</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>-5.18</t>
+          <t>-6.00</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>-5.11</t>
+          <t>-5.29</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
@@ -5390,7 +5390,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-120.53</t>
+          <t>-121.24</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5400,43 +5400,43 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>1686680961.147857</t>
+          <t>1684514497.82311</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>92809478.0</t>
+          <t>753939618.0</t>
         </is>
       </c>
       <c r="AX12" t="n">
-        <v>127850905.8</v>
+        <v>239835367</v>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>148995940.1</t>
+          <t>202283159.5</t>
         </is>
       </c>
       <c r="AZ12" t="n">
-        <v>248204610.78</v>
+        <v>250790390.86</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>-21145034</t>
+          <t>37552207</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>-18726961.5147791</t>
+          <t>-12161789.58854426</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>-25359440.74628332</t>
+          <t>23946656.00574735</t>
         </is>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
-          <t>92809478.0</t>
+          <t>753939618.0</t>
         </is>
       </c>
       <c r="BE12" t="inlineStr">
@@ -5456,7 +5456,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>-16.94</t>
+          <t>-23.61</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>3.44</t>
+          <t>3.17</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
         <is>
-          <t>2.95</t>
+          <t>2.96</t>
         </is>
       </c>
       <c r="BU12" t="inlineStr">
@@ -5526,7 +5526,7 @@
       </c>
       <c r="BV12" t="inlineStr">
         <is>
-          <t>26.5</t>
+          <t>26.41</t>
         </is>
       </c>
       <c r="BW12" t="inlineStr">
@@ -5541,12 +5541,12 @@
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>29.67</t>
+          <t>29.63</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
         <is>
-          <t>34812</t>
+          <t>34689</t>
         </is>
       </c>
       <c r="CA12" t="inlineStr">
@@ -5566,22 +5566,22 @@
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>150.0</t>
+          <t>147.0</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>151.5</t>
+          <t>147.0</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>149.5</t>
+          <t>135.0</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
         <is>
-          <t>149.5</t>
+          <t>137.5</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">
@@ -5613,42 +5613,42 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
+          <t>-0.51</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>492.79</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>38.9</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>510.601</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>39.1</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>1.07</t>
+          <t>1.23</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>32.21</t>
+          <t>32.35</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -5713,7 +5713,7 @@
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>-9.39</t>
+          <t>-9.85</t>
         </is>
       </c>
       <c r="X13" t="inlineStr">
@@ -5723,17 +5723,17 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>5.44</t>
+          <t>5.25</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>0.39</t>
+          <t>-0.12</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
@@ -5744,73 +5744,73 @@
       <c r="AC13" t="inlineStr"/>
       <c r="AD13" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
-          <t>511</t>
+          <t>493</t>
         </is>
       </c>
       <c r="AF13" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>93.33</t>
         </is>
       </c>
       <c r="AG13" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>97.78</t>
         </is>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>2.87</t>
+          <t>1.25</t>
         </is>
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>-0.09</t>
+          <t>1.10</t>
         </is>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>-4.82</t>
+          <t>-4.8</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>-2.98</t>
+          <t>-3.07</t>
         </is>
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>38.01000000000001</t>
+          <t>38.42</t>
         </is>
       </c>
       <c r="AM13" t="n">
-        <v>38.04</v>
+        <v>38</v>
       </c>
       <c r="AN13" t="n">
-        <v>39.97</v>
+        <v>39.92</v>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>41.2</t>
+          <t>41.18</t>
         </is>
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>33.12</t>
+          <t>41.20</t>
         </is>
       </c>
       <c r="AQ13" t="inlineStr">
         <is>
-          <t>-0.59</t>
+          <t>-0.47</t>
         </is>
       </c>
       <c r="AR13" t="inlineStr">
         <is>
-          <t>-0.88</t>
+          <t>-0.79</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr">
@@ -5820,7 +5820,7 @@
       </c>
       <c r="AT13" t="inlineStr">
         <is>
-          <t>-132.60</t>
+          <t>-129.55</t>
         </is>
       </c>
       <c r="AU13" t="inlineStr">
@@ -5830,43 +5830,43 @@
       </c>
       <c r="AV13" t="inlineStr">
         <is>
-          <t>150251779.8621429</t>
+          <t>150078431.9122682</t>
         </is>
       </c>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>19953309.0</t>
+          <t>19156578.0</t>
         </is>
       </c>
       <c r="AX13" t="n">
-        <v>73854919.59999999</v>
+        <v>69426442.8</v>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>55863021.8</t>
+          <t>52456837.4</t>
         </is>
       </c>
       <c r="AZ13" t="n">
-        <v>33328621.84</v>
+        <v>33433682.52</v>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
-          <t>17991897</t>
+          <t>16969605</t>
         </is>
       </c>
       <c r="BB13" t="inlineStr">
         <is>
-          <t>4990346.878352229</t>
+          <t>4345764.102201018</t>
         </is>
       </c>
       <c r="BC13" t="inlineStr">
         <is>
-          <t>3809528.634606227</t>
+          <t>800558.8333693519</t>
         </is>
       </c>
       <c r="BD13" t="inlineStr">
         <is>
-          <t>19953309.0</t>
+          <t>19156578.0</t>
         </is>
       </c>
       <c r="BE13" t="inlineStr">
@@ -5886,7 +5886,7 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>-5.78</t>
+          <t>-6.27</t>
         </is>
       </c>
       <c r="BI13" t="inlineStr">
@@ -5931,22 +5931,22 @@
       </c>
       <c r="BQ13" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR13" t="inlineStr">
         <is>
-          <t>價-量縮</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS13" t="inlineStr">
         <is>
-          <t>1.08</t>
+          <t>1.07</t>
         </is>
       </c>
       <c r="BT13" t="inlineStr">
         <is>
-          <t>6.39</t>
+          <t>6.43</t>
         </is>
       </c>
       <c r="BU13" t="inlineStr">
@@ -5956,7 +5956,7 @@
       </c>
       <c r="BV13" t="inlineStr">
         <is>
-          <t>16.16</t>
+          <t>16.07</t>
         </is>
       </c>
       <c r="BW13" t="inlineStr">
@@ -5971,12 +5971,12 @@
       </c>
       <c r="BY13" t="inlineStr">
         <is>
-          <t>29.67</t>
+          <t>29.63</t>
         </is>
       </c>
       <c r="BZ13" t="inlineStr">
         <is>
-          <t>12557</t>
+          <t>12493</t>
         </is>
       </c>
       <c r="CA13" t="inlineStr">
@@ -5996,22 +5996,22 @@
       </c>
       <c r="CD13" t="inlineStr">
         <is>
-          <t>39.15</t>
+          <t>39.1</t>
         </is>
       </c>
       <c r="CE13" t="inlineStr">
         <is>
-          <t>39.3</t>
+          <t>39.25</t>
         </is>
       </c>
       <c r="CF13" t="inlineStr">
         <is>
-          <t>38.75</t>
+          <t>38.6</t>
         </is>
       </c>
       <c r="CG13" t="inlineStr">
         <is>
-          <t>39.1</t>
+          <t>38.9</t>
         </is>
       </c>
       <c r="CH13" t="inlineStr">
@@ -6043,12 +6043,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>2.61</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>914.803</t>
+          <t>510.601</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -6068,17 +6068,17 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-0.51</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>1.07</t>
+          <t>1.23</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>35.32</t>
+          <t>32.21</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -6153,17 +6153,17 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>9.75</t>
+          <t>5.44</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>1.47</t>
+          <t>0.39</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
@@ -6174,12 +6174,12 @@
       <c r="AC14" t="inlineStr"/>
       <c r="AD14" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
-          <t>511</t>
+          <t>493</t>
         </is>
       </c>
       <c r="AF14" t="inlineStr">
@@ -6189,58 +6189,58 @@
       </c>
       <c r="AG14" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>4.35</t>
+          <t>2.87</t>
         </is>
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>-1.59</t>
+          <t>-0.09</t>
         </is>
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>-4.88</t>
+          <t>-4.82</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>-2.87</t>
+          <t>-2.98</t>
         </is>
       </c>
       <c r="AL14" t="inlineStr">
         <is>
-          <t>37.47</t>
+          <t>38.01000000000001</t>
         </is>
       </c>
       <c r="AM14" t="n">
-        <v>38.08</v>
+        <v>38.04</v>
       </c>
       <c r="AN14" t="n">
-        <v>40.03</v>
+        <v>39.97</v>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>41.21</t>
+          <t>41.2</t>
         </is>
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>20.99</t>
+          <t>33.12</t>
         </is>
       </c>
       <c r="AQ14" t="inlineStr">
         <is>
-          <t>-0.75</t>
+          <t>-0.59</t>
         </is>
       </c>
       <c r="AR14" t="inlineStr">
         <is>
-          <t>-0.95</t>
+          <t>-0.88</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr">
@@ -6250,7 +6250,7 @@
       </c>
       <c r="AT14" t="inlineStr">
         <is>
-          <t>-135.29</t>
+          <t>-132.60</t>
         </is>
       </c>
       <c r="AU14" t="inlineStr">
@@ -6260,43 +6260,43 @@
       </c>
       <c r="AV14" t="inlineStr">
         <is>
-          <t>150251779.8621429</t>
+          <t>150078431.9122682</t>
         </is>
       </c>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>35810040.0</t>
+          <t>19953309.0</t>
         </is>
       </c>
       <c r="AX14" t="n">
-        <v>75499582.59999999</v>
+        <v>73854919.59999999</v>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
-          <t>55792550.2</t>
+          <t>55863021.8</t>
         </is>
       </c>
       <c r="AZ14" t="n">
-        <v>33454972.78</v>
+        <v>33328621.84</v>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
-          <t>19707032</t>
+          <t>17991897</t>
         </is>
       </c>
       <c r="BB14" t="inlineStr">
         <is>
-          <t>5205041.104487866</t>
+          <t>4990346.878352229</t>
         </is>
       </c>
       <c r="BC14" t="inlineStr">
         <is>
-          <t>7886638.29228013</t>
+          <t>3809528.634606227</t>
         </is>
       </c>
       <c r="BD14" t="inlineStr">
         <is>
-          <t>35810040.0</t>
+          <t>19953309.0</t>
         </is>
       </c>
       <c r="BE14" t="inlineStr">
@@ -6361,12 +6361,12 @@
       </c>
       <c r="BQ14" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR14" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量縮</t>
         </is>
       </c>
       <c r="BS14" t="inlineStr">
@@ -6376,7 +6376,7 @@
       </c>
       <c r="BT14" t="inlineStr">
         <is>
-          <t>6.39</t>
+          <t>6.43</t>
         </is>
       </c>
       <c r="BU14" t="inlineStr">
@@ -6386,7 +6386,7 @@
       </c>
       <c r="BV14" t="inlineStr">
         <is>
-          <t>16.16</t>
+          <t>16.07</t>
         </is>
       </c>
       <c r="BW14" t="inlineStr">
@@ -6401,12 +6401,12 @@
       </c>
       <c r="BY14" t="inlineStr">
         <is>
-          <t>29.67</t>
+          <t>29.63</t>
         </is>
       </c>
       <c r="BZ14" t="inlineStr">
         <is>
-          <t>12557</t>
+          <t>12493</t>
         </is>
       </c>
       <c r="CA14" t="inlineStr">
@@ -6426,17 +6426,17 @@
       </c>
       <c r="CD14" t="inlineStr">
         <is>
-          <t>38.3</t>
+          <t>39.15</t>
         </is>
       </c>
       <c r="CE14" t="inlineStr">
         <is>
-          <t>39.5</t>
+          <t>39.3</t>
         </is>
       </c>
       <c r="CF14" t="inlineStr">
         <is>
-          <t>38.15</t>
+          <t>38.75</t>
         </is>
       </c>
       <c r="CG14" t="inlineStr">
@@ -6473,12 +6473,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>3.24</t>
+          <t>2.61</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>1043.085</t>
+          <t>914.803</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -6488,7 +6488,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>38.1</t>
+          <t>39.1</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -6498,17 +6498,17 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>2.56</t>
+          <t>-0.51</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>1.07</t>
+          <t>1.23</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>41.43</t>
+          <t>35.32</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -6573,7 +6573,7 @@
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>-11.70</t>
+          <t>-9.39</t>
         </is>
       </c>
       <c r="X15" t="inlineStr">
@@ -6583,17 +6583,17 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>11.11</t>
+          <t>9.75</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2.71</t>
+          <t>1.47</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
@@ -6604,12 +6604,12 @@
       <c r="AC15" t="inlineStr"/>
       <c r="AD15" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
-          <t>511</t>
+          <t>493</t>
         </is>
       </c>
       <c r="AF15" t="inlineStr">
@@ -6619,60 +6619,60 @@
       </c>
       <c r="AG15" t="inlineStr">
         <is>
-          <t>59.17</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>3.34</t>
+          <t>4.35</t>
         </is>
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>-3.27</t>
+          <t>-1.59</t>
         </is>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>-4.89</t>
+          <t>-4.88</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>-2.80</t>
+          <t>-2.87</t>
         </is>
       </c>
       <c r="AL15" t="inlineStr">
         <is>
-          <t>36.87</t>
+          <t>37.47</t>
         </is>
       </c>
       <c r="AM15" t="n">
-        <v>38.11</v>
+        <v>38.08</v>
       </c>
       <c r="AN15" t="n">
-        <v>40.07</v>
+        <v>40.03</v>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>41.23</t>
+          <t>41.21</t>
         </is>
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>5.10</t>
+          <t>20.99</t>
         </is>
       </c>
       <c r="AQ15" t="inlineStr">
         <is>
+          <t>-0.75</t>
+        </is>
+      </c>
+      <c r="AR15" t="inlineStr">
+        <is>
           <t>-0.95</t>
         </is>
       </c>
-      <c r="AR15" t="inlineStr">
-        <is>
-          <t>-1.00</t>
-        </is>
-      </c>
       <c r="AS15" t="inlineStr">
         <is>
           <t>2.69</t>
@@ -6680,7 +6680,7 @@
       </c>
       <c r="AT15" t="inlineStr">
         <is>
-          <t>-137.15</t>
+          <t>-135.29</t>
         </is>
       </c>
       <c r="AU15" t="inlineStr">
@@ -6690,43 +6690,43 @@
       </c>
       <c r="AV15" t="inlineStr">
         <is>
-          <t>150251779.8621429</t>
+          <t>150078431.9122682</t>
         </is>
       </c>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>39561838.0</t>
+          <t>35810040.0</t>
         </is>
       </c>
       <c r="AX15" t="n">
-        <v>77102277.8</v>
+        <v>75499582.59999999</v>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>54515793.2</t>
+          <t>55792550.2</t>
         </is>
       </c>
       <c r="AZ15" t="n">
-        <v>33864219.92</v>
+        <v>33454972.78</v>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
-          <t>22586484</t>
+          <t>19707032</t>
         </is>
       </c>
       <c r="BB15" t="inlineStr">
         <is>
-          <t>4717477.979434728</t>
+          <t>5205041.104487866</t>
         </is>
       </c>
       <c r="BC15" t="inlineStr">
         <is>
-          <t>11730479.54280426</t>
+          <t>7886638.29228013</t>
         </is>
       </c>
       <c r="BD15" t="inlineStr">
         <is>
-          <t>39561838.0</t>
+          <t>35810040.0</t>
         </is>
       </c>
       <c r="BE15" t="inlineStr">
@@ -6746,7 +6746,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>-8.19</t>
+          <t>-5.78</t>
         </is>
       </c>
       <c r="BI15" t="inlineStr">
@@ -6791,22 +6791,22 @@
       </c>
       <c r="BQ15" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR15" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS15" t="inlineStr">
         <is>
-          <t>1.05</t>
+          <t>1.08</t>
         </is>
       </c>
       <c r="BT15" t="inlineStr">
         <is>
-          <t>6.39</t>
+          <t>6.43</t>
         </is>
       </c>
       <c r="BU15" t="inlineStr">
@@ -6816,7 +6816,7 @@
       </c>
       <c r="BV15" t="inlineStr">
         <is>
-          <t>16.16</t>
+          <t>16.07</t>
         </is>
       </c>
       <c r="BW15" t="inlineStr">
@@ -6831,12 +6831,12 @@
       </c>
       <c r="BY15" t="inlineStr">
         <is>
-          <t>29.67</t>
+          <t>29.63</t>
         </is>
       </c>
       <c r="BZ15" t="inlineStr">
         <is>
-          <t>12557</t>
+          <t>12493</t>
         </is>
       </c>
       <c r="CA15" t="inlineStr">
@@ -6856,22 +6856,22 @@
       </c>
       <c r="CD15" t="inlineStr">
         <is>
-          <t>37.05</t>
+          <t>38.3</t>
         </is>
       </c>
       <c r="CE15" t="inlineStr">
         <is>
-          <t>38.2</t>
+          <t>39.5</t>
         </is>
       </c>
       <c r="CF15" t="inlineStr">
         <is>
-          <t>37.0</t>
+          <t>38.15</t>
         </is>
       </c>
       <c r="CG15" t="inlineStr">
         <is>
-          <t>38.1</t>
+          <t>39.1</t>
         </is>
       </c>
       <c r="CH15" t="inlineStr">
@@ -6893,7 +6893,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>【e】</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -6903,12 +6903,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>0.14</t>
+          <t>3.24</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>6301.223</t>
+          <t>1043.085</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -6918,7 +6918,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>36.9</t>
+          <t>38.1</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -6928,17 +6928,17 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>5.63</t>
+          <t>2.06</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>1.07</t>
+          <t>1.23</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>29.52</t>
+          <t>41.43</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -7003,7 +7003,7 @@
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>-14.48</t>
+          <t>-11.70</t>
         </is>
       </c>
       <c r="X16" t="inlineStr">
@@ -7013,17 +7013,17 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>67.14</t>
+          <t>11.11</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>-1.63</t>
+          <t>2.71</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
@@ -7034,73 +7034,73 @@
       <c r="AC16" t="inlineStr"/>
       <c r="AD16" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
-          <t>511</t>
+          <t>493</t>
         </is>
       </c>
       <c r="AF16" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG16" t="inlineStr">
         <is>
-          <t>29.75</t>
+          <t>59.17</t>
         </is>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>0.82</t>
+          <t>3.34</t>
         </is>
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>-4.24</t>
+          <t>-3.27</t>
         </is>
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>-4.85</t>
+          <t>-4.89</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>-2.68</t>
+          <t>-2.80</t>
         </is>
       </c>
       <c r="AL16" t="inlineStr">
         <is>
-          <t>36.60000000000001</t>
+          <t>36.87</t>
         </is>
       </c>
       <c r="AM16" t="n">
-        <v>38.22</v>
+        <v>38.11</v>
       </c>
       <c r="AN16" t="n">
-        <v>40.17</v>
+        <v>40.07</v>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>41.28</t>
+          <t>41.23</t>
         </is>
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>-7.24</t>
+          <t>5.10</t>
         </is>
       </c>
       <c r="AQ16" t="inlineStr">
         <is>
-          <t>-1.08</t>
+          <t>-0.95</t>
         </is>
       </c>
       <c r="AR16" t="inlineStr">
         <is>
-          <t>-1.01</t>
+          <t>-1.00</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr">
@@ -7110,7 +7110,7 @@
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>-137.62</t>
+          <t>-137.15</t>
         </is>
       </c>
       <c r="AU16" t="inlineStr">
@@ -7120,43 +7120,43 @@
       </c>
       <c r="AV16" t="inlineStr">
         <is>
-          <t>150251779.8621429</t>
+          <t>150078431.9122682</t>
         </is>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>232650449.0</t>
+          <t>39561838.0</t>
         </is>
       </c>
       <c r="AX16" t="n">
-        <v>74142370</v>
+        <v>77102277.8</v>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>57245793.0</t>
+          <t>54515793.2</t>
         </is>
       </c>
       <c r="AZ16" t="n">
-        <v>34130931.06</v>
+        <v>33864219.92</v>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
-          <t>16896577</t>
+          <t>22586484</t>
         </is>
       </c>
       <c r="BB16" t="inlineStr">
         <is>
-          <t>3442386.786094812</t>
+          <t>4717477.979434728</t>
         </is>
       </c>
       <c r="BC16" t="inlineStr">
         <is>
-          <t>16400757.27416717</t>
+          <t>11730479.54280426</t>
         </is>
       </c>
       <c r="BD16" t="inlineStr">
         <is>
-          <t>232650449.0</t>
+          <t>39561838.0</t>
         </is>
       </c>
       <c r="BE16" t="inlineStr">
@@ -7176,7 +7176,7 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>-11.08</t>
+          <t>-8.19</t>
         </is>
       </c>
       <c r="BI16" t="inlineStr">
@@ -7221,7 +7221,7 @@
       </c>
       <c r="BQ16" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR16" t="inlineStr">
@@ -7231,12 +7231,12 @@
       </c>
       <c r="BS16" t="inlineStr">
         <is>
-          <t>1.02</t>
+          <t>1.05</t>
         </is>
       </c>
       <c r="BT16" t="inlineStr">
         <is>
-          <t>6.39</t>
+          <t>6.43</t>
         </is>
       </c>
       <c r="BU16" t="inlineStr">
@@ -7246,7 +7246,7 @@
       </c>
       <c r="BV16" t="inlineStr">
         <is>
-          <t>16.16</t>
+          <t>16.07</t>
         </is>
       </c>
       <c r="BW16" t="inlineStr">
@@ -7261,12 +7261,12 @@
       </c>
       <c r="BY16" t="inlineStr">
         <is>
-          <t>29.67</t>
+          <t>29.63</t>
         </is>
       </c>
       <c r="BZ16" t="inlineStr">
         <is>
-          <t>12557</t>
+          <t>12493</t>
         </is>
       </c>
       <c r="CA16" t="inlineStr">
@@ -7286,22 +7286,22 @@
       </c>
       <c r="CD16" t="inlineStr">
         <is>
+          <t>37.05</t>
+        </is>
+      </c>
+      <c r="CE16" t="inlineStr">
+        <is>
+          <t>38.2</t>
+        </is>
+      </c>
+      <c r="CF16" t="inlineStr">
+        <is>
           <t>37.0</t>
         </is>
       </c>
-      <c r="CE16" t="inlineStr">
-        <is>
-          <t>37.5</t>
-        </is>
-      </c>
-      <c r="CF16" t="inlineStr">
-        <is>
-          <t>36.9</t>
-        </is>
-      </c>
       <c r="CG16" t="inlineStr">
         <is>
-          <t>36.9</t>
+          <t>38.1</t>
         </is>
       </c>
       <c r="CH16" t="inlineStr">
@@ -7333,12 +7333,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>1.24</t>
+          <t>0.14</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>1128.761</t>
+          <t>6301.223</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -7348,7 +7348,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>36.85</t>
+          <t>36.9</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -7358,17 +7358,17 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>5.75</t>
+          <t>5.14</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>1.07</t>
+          <t>1.23</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>-1.19</t>
+          <t>29.52</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -7433,7 +7433,7 @@
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>-14.60</t>
+          <t>-14.48</t>
         </is>
       </c>
       <c r="X17" t="inlineStr">
@@ -7443,17 +7443,17 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>12.03</t>
+          <t>67.14</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2.09</t>
+          <t>-1.63</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
@@ -7464,274 +7464,274 @@
       <c r="AC17" t="inlineStr"/>
       <c r="AD17" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
-          <t>511</t>
+          <t>493</t>
         </is>
       </c>
       <c r="AF17" t="inlineStr">
         <is>
+          <t>40.0</t>
+        </is>
+      </c>
+      <c r="AG17" t="inlineStr">
+        <is>
+          <t>29.75</t>
+        </is>
+      </c>
+      <c r="AH17" t="inlineStr">
+        <is>
+          <t>0.82</t>
+        </is>
+      </c>
+      <c r="AI17" t="inlineStr">
+        <is>
+          <t>-4.24</t>
+        </is>
+      </c>
+      <c r="AJ17" t="inlineStr">
+        <is>
+          <t>-4.85</t>
+        </is>
+      </c>
+      <c r="AK17" t="inlineStr">
+        <is>
+          <t>-2.68</t>
+        </is>
+      </c>
+      <c r="AL17" t="inlineStr">
+        <is>
+          <t>36.60000000000001</t>
+        </is>
+      </c>
+      <c r="AM17" t="n">
+        <v>38.22</v>
+      </c>
+      <c r="AN17" t="n">
+        <v>40.17</v>
+      </c>
+      <c r="AO17" t="inlineStr">
+        <is>
+          <t>41.28</t>
+        </is>
+      </c>
+      <c r="AP17" t="inlineStr">
+        <is>
+          <t>-7.24</t>
+        </is>
+      </c>
+      <c r="AQ17" t="inlineStr">
+        <is>
+          <t>-1.08</t>
+        </is>
+      </c>
+      <c r="AR17" t="inlineStr">
+        <is>
+          <t>-1.01</t>
+        </is>
+      </c>
+      <c r="AS17" t="inlineStr">
+        <is>
+          <t>2.69</t>
+        </is>
+      </c>
+      <c r="AT17" t="inlineStr">
+        <is>
+          <t>-137.62</t>
+        </is>
+      </c>
+      <c r="AU17" t="inlineStr">
+        <is>
+          <t>2025/11/25</t>
+        </is>
+      </c>
+      <c r="AV17" t="inlineStr">
+        <is>
+          <t>150078431.9122682</t>
+        </is>
+      </c>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>232650449.0</t>
+        </is>
+      </c>
+      <c r="AX17" t="n">
+        <v>74142370</v>
+      </c>
+      <c r="AY17" t="inlineStr">
+        <is>
+          <t>57245793.0</t>
+        </is>
+      </c>
+      <c r="AZ17" t="n">
+        <v>34130931.06</v>
+      </c>
+      <c r="BA17" t="inlineStr">
+        <is>
+          <t>16896577</t>
+        </is>
+      </c>
+      <c r="BB17" t="inlineStr">
+        <is>
+          <t>3442386.786094812</t>
+        </is>
+      </c>
+      <c r="BC17" t="inlineStr">
+        <is>
+          <t>16400757.27416717</t>
+        </is>
+      </c>
+      <c r="BD17" t="inlineStr">
+        <is>
+          <t>232650449.0</t>
+        </is>
+      </c>
+      <c r="BE17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF17" t="inlineStr">
+        <is>
+          <t>41.5</t>
+        </is>
+      </c>
+      <c r="BG17" t="inlineStr">
+        <is>
+          <t>2025/08/07</t>
+        </is>
+      </c>
+      <c r="BH17" t="inlineStr">
+        <is>
+          <t>-11.08</t>
+        </is>
+      </c>
+      <c r="BI17" t="inlineStr">
+        <is>
+          <t>新光鋼</t>
+        </is>
+      </c>
+      <c r="BJ17" t="inlineStr">
+        <is>
+          <t>新光鋼</t>
+        </is>
+      </c>
+      <c r="BK17" t="inlineStr">
+        <is>
+          <t>鋼鐵工業</t>
+        </is>
+      </c>
+      <c r="BL17" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="BM17" t="inlineStr">
+        <is>
+          <t>0.62</t>
+        </is>
+      </c>
+      <c r="BN17" t="inlineStr">
+        <is>
+          <t>-13.67996844119094</t>
+        </is>
+      </c>
+      <c r="BO17" t="inlineStr">
+        <is>
+          <t>-10.11024290164889</t>
+        </is>
+      </c>
+      <c r="BP17" t="inlineStr">
+        <is>
+          <t>24.12947661306339</t>
+        </is>
+      </c>
+      <c r="BQ17" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BR17" t="inlineStr">
+        <is>
+          <t>價-量增</t>
+        </is>
+      </c>
+      <c r="BS17" t="inlineStr">
+        <is>
+          <t>1.02</t>
+        </is>
+      </c>
+      <c r="BT17" t="inlineStr">
+        <is>
+          <t>6.43</t>
+        </is>
+      </c>
+      <c r="BU17" t="inlineStr">
+        <is>
+          <t>11.90</t>
+        </is>
+      </c>
+      <c r="BV17" t="inlineStr">
+        <is>
+          <t>16.07</t>
+        </is>
+      </c>
+      <c r="BW17" t="inlineStr">
+        <is>
+          <t>8.69%</t>
+        </is>
+      </c>
+      <c r="BX17" t="inlineStr">
+        <is>
+          <t>5.19%</t>
+        </is>
+      </c>
+      <c r="BY17" t="inlineStr">
+        <is>
+          <t>29.63</t>
+        </is>
+      </c>
+      <c r="BZ17" t="inlineStr">
+        <is>
+          <t>12493</t>
+        </is>
+      </c>
+      <c r="CA17" t="inlineStr">
+        <is>
+          <t>鋼板38.80%、熱軋及鍍鋅鋼板33.80%、不�袗�板12.60%、特殊鋼板7.00%、加工及其他6.90%、型鋼0.90% (2024年)</t>
+        </is>
+      </c>
+      <c r="CB17" t="inlineStr">
+        <is>
+          <t>新光鋼-鋼鐵工業-上市</t>
+        </is>
+      </c>
+      <c r="CC17" t="inlineStr">
+        <is>
+          <t>鋼鐵工業右下上市</t>
+        </is>
+      </c>
+      <c r="CD17" t="inlineStr">
+        <is>
+          <t>37.0</t>
+        </is>
+      </c>
+      <c r="CE17" t="inlineStr">
+        <is>
           <t>37.5</t>
         </is>
       </c>
-      <c r="AG17" t="inlineStr">
-        <is>
-          <t>16.42</t>
-        </is>
-      </c>
-      <c r="AH17" t="inlineStr">
-        <is>
-          <t>0.66</t>
-        </is>
-      </c>
-      <c r="AI17" t="inlineStr">
-        <is>
-          <t>-4.68</t>
-        </is>
-      </c>
-      <c r="AJ17" t="inlineStr">
-        <is>
-          <t>-4.69</t>
-        </is>
-      </c>
-      <c r="AK17" t="inlineStr">
-        <is>
-          <t>-2.48</t>
-        </is>
-      </c>
-      <c r="AL17" t="inlineStr">
-        <is>
-          <t>36.61</t>
-        </is>
-      </c>
-      <c r="AM17" t="n">
-        <v>38.41</v>
-      </c>
-      <c r="AN17" t="n">
-        <v>40.3</v>
-      </c>
-      <c r="AO17" t="inlineStr">
-        <is>
-          <t>41.32</t>
-        </is>
-      </c>
-      <c r="AP17" t="inlineStr">
-        <is>
-          <t>-12.91</t>
-        </is>
-      </c>
-      <c r="AQ17" t="inlineStr">
-        <is>
-          <t>-1.12</t>
-        </is>
-      </c>
-      <c r="AR17" t="inlineStr">
-        <is>
-          <t>-0.99</t>
-        </is>
-      </c>
-      <c r="AS17" t="inlineStr">
-        <is>
-          <t>2.69</t>
-        </is>
-      </c>
-      <c r="AT17" t="inlineStr">
-        <is>
-          <t>-136.94</t>
-        </is>
-      </c>
-      <c r="AU17" t="inlineStr">
-        <is>
-          <t>2025/11/25</t>
-        </is>
-      </c>
-      <c r="AV17" t="inlineStr">
-        <is>
-          <t>150251779.8621429</t>
-        </is>
-      </c>
-      <c r="AW17" t="inlineStr">
-        <is>
-          <t>41298962.0</t>
-        </is>
-      </c>
-      <c r="AX17" t="n">
-        <v>35487232</v>
-      </c>
-      <c r="AY17" t="inlineStr">
-        <is>
-          <t>35914543.8</t>
-        </is>
-      </c>
-      <c r="AZ17" t="n">
-        <v>29950115.64</v>
-      </c>
-      <c r="BA17" t="inlineStr">
-        <is>
-          <t>-427311</t>
-        </is>
-      </c>
-      <c r="BB17" t="inlineStr">
-        <is>
-          <t>1086319.424627111</t>
-        </is>
-      </c>
-      <c r="BC17" t="inlineStr">
-        <is>
-          <t>1798775.809179619</t>
-        </is>
-      </c>
-      <c r="BD17" t="inlineStr">
-        <is>
-          <t>41298962.0</t>
-        </is>
-      </c>
-      <c r="BE17" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BF17" t="inlineStr">
-        <is>
-          <t>41.5</t>
-        </is>
-      </c>
-      <c r="BG17" t="inlineStr">
-        <is>
-          <t>2025/08/07</t>
-        </is>
-      </c>
-      <c r="BH17" t="inlineStr">
-        <is>
-          <t>-11.20</t>
-        </is>
-      </c>
-      <c r="BI17" t="inlineStr">
-        <is>
-          <t>新光鋼</t>
-        </is>
-      </c>
-      <c r="BJ17" t="inlineStr">
-        <is>
-          <t>新光鋼</t>
-        </is>
-      </c>
-      <c r="BK17" t="inlineStr">
-        <is>
-          <t>鋼鐵工業</t>
-        </is>
-      </c>
-      <c r="BL17" t="inlineStr">
-        <is>
-          <t>上市</t>
-        </is>
-      </c>
-      <c r="BM17" t="inlineStr">
-        <is>
-          <t>0.62</t>
-        </is>
-      </c>
-      <c r="BN17" t="inlineStr">
-        <is>
-          <t>-13.67996844119094</t>
-        </is>
-      </c>
-      <c r="BO17" t="inlineStr">
-        <is>
-          <t>-10.11024290164889</t>
-        </is>
-      </c>
-      <c r="BP17" t="inlineStr">
-        <is>
-          <t>24.12947661306339</t>
-        </is>
-      </c>
-      <c r="BQ17" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;可能出現反轉訊號&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;3&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="BR17" t="inlineStr">
-        <is>
-          <t>價-量增</t>
-        </is>
-      </c>
-      <c r="BS17" t="inlineStr">
-        <is>
-          <t>1.01</t>
-        </is>
-      </c>
-      <c r="BT17" t="inlineStr">
-        <is>
-          <t>6.39</t>
-        </is>
-      </c>
-      <c r="BU17" t="inlineStr">
-        <is>
-          <t>11.90</t>
-        </is>
-      </c>
-      <c r="BV17" t="inlineStr">
-        <is>
-          <t>16.16</t>
-        </is>
-      </c>
-      <c r="BW17" t="inlineStr">
-        <is>
-          <t>8.69%</t>
-        </is>
-      </c>
-      <c r="BX17" t="inlineStr">
-        <is>
-          <t>5.19%</t>
-        </is>
-      </c>
-      <c r="BY17" t="inlineStr">
-        <is>
-          <t>29.67</t>
-        </is>
-      </c>
-      <c r="BZ17" t="inlineStr">
-        <is>
-          <t>12557</t>
-        </is>
-      </c>
-      <c r="CA17" t="inlineStr">
-        <is>
-          <t>鋼板38.80%、熱軋及鍍鋅鋼板33.80%、不�袗�板12.60%、特殊鋼板7.00%、加工及其他6.90%、型鋼0.90% (2024年)</t>
-        </is>
-      </c>
-      <c r="CB17" t="inlineStr">
-        <is>
-          <t>新光鋼-鋼鐵工業-上市</t>
-        </is>
-      </c>
-      <c r="CC17" t="inlineStr">
-        <is>
-          <t>鋼鐵工業右下上市</t>
-        </is>
-      </c>
-      <c r="CD17" t="inlineStr">
-        <is>
-          <t>36.4</t>
-        </is>
-      </c>
-      <c r="CE17" t="inlineStr">
-        <is>
-          <t>36.95</t>
-        </is>
-      </c>
       <c r="CF17" t="inlineStr">
         <is>
-          <t>36.0</t>
+          <t>36.9</t>
         </is>
       </c>
       <c r="CG17" t="inlineStr">
         <is>
-          <t>36.85</t>
+          <t>36.9</t>
         </is>
       </c>
       <c r="CH17" t="inlineStr">
@@ -7763,12 +7763,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>0.83</t>
+          <t>1.24</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>776.396</t>
+          <t>1128.761</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -7778,7 +7778,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>36.4</t>
+          <t>36.85</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -7788,17 +7788,17 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>6.91</t>
+          <t>5.27</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>1.07</t>
+          <t>1.23</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>9.74</t>
+          <t>-1.19</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -7863,7 +7863,7 @@
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>-15.64</t>
+          <t>-14.60</t>
         </is>
       </c>
       <c r="X18" t="inlineStr">
@@ -7873,17 +7873,17 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>8.27</t>
+          <t>12.03</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>0.70</t>
+          <t>2.09</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
@@ -7894,73 +7894,73 @@
       <c r="AC18" t="inlineStr"/>
       <c r="AD18" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
-          <t>511</t>
+          <t>493</t>
         </is>
       </c>
       <c r="AF18" t="inlineStr">
         <is>
-          <t>11.76</t>
+          <t>37.5</t>
         </is>
       </c>
       <c r="AG18" t="inlineStr">
         <is>
-          <t>3.92</t>
+          <t>16.42</t>
         </is>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>-0.90</t>
+          <t>0.66</t>
         </is>
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>-4.83</t>
+          <t>-4.68</t>
         </is>
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>-4.54</t>
+          <t>-4.69</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>-2.31</t>
+          <t>-2.48</t>
         </is>
       </c>
       <c r="AL18" t="inlineStr">
         <is>
-          <t>36.73</t>
+          <t>36.61</t>
         </is>
       </c>
       <c r="AM18" t="n">
-        <v>38.6</v>
+        <v>38.41</v>
       </c>
       <c r="AN18" t="n">
-        <v>40.43</v>
+        <v>40.3</v>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>41.39</t>
+          <t>41.32</t>
         </is>
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>-19.31</t>
+          <t>-12.91</t>
         </is>
       </c>
       <c r="AQ18" t="inlineStr">
         <is>
-          <t>-1.15</t>
+          <t>-1.12</t>
         </is>
       </c>
       <c r="AR18" t="inlineStr">
         <is>
-          <t>-0.96</t>
+          <t>-0.99</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr">
@@ -7970,7 +7970,7 @@
       </c>
       <c r="AT18" t="inlineStr">
         <is>
-          <t>-135.75</t>
+          <t>-136.94</t>
         </is>
       </c>
       <c r="AU18" t="inlineStr">
@@ -7980,43 +7980,43 @@
       </c>
       <c r="AV18" t="inlineStr">
         <is>
-          <t>150251779.8621429</t>
+          <t>150078431.9122682</t>
         </is>
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>28176624.0</t>
+          <t>41298962.0</t>
         </is>
       </c>
       <c r="AX18" t="n">
-        <v>37871124</v>
+        <v>35487232</v>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>34509118.0</t>
+          <t>35914543.8</t>
         </is>
       </c>
       <c r="AZ18" t="n">
-        <v>29545425.32</v>
+        <v>29950115.64</v>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
-          <t>3362006</t>
+          <t>-427311</t>
         </is>
       </c>
       <c r="BB18" t="inlineStr">
         <is>
-          <t>956781.9001630185</t>
+          <t>1086319.424627111</t>
         </is>
       </c>
       <c r="BC18" t="inlineStr">
         <is>
-          <t>1376505.330298137</t>
+          <t>1798775.809179619</t>
         </is>
       </c>
       <c r="BD18" t="inlineStr">
         <is>
-          <t>28176624.0</t>
+          <t>41298962.0</t>
         </is>
       </c>
       <c r="BE18" t="inlineStr">
@@ -8036,7 +8036,7 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>-12.29</t>
+          <t>-11.20</t>
         </is>
       </c>
       <c r="BI18" t="inlineStr">
@@ -8081,22 +8081,22 @@
       </c>
       <c r="BQ18" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;可能出現反轉訊號&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;3&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR18" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS18" t="inlineStr">
         <is>
-          <t>1.00</t>
+          <t>1.01</t>
         </is>
       </c>
       <c r="BT18" t="inlineStr">
         <is>
-          <t>6.39</t>
+          <t>6.43</t>
         </is>
       </c>
       <c r="BU18" t="inlineStr">
@@ -8106,7 +8106,7 @@
       </c>
       <c r="BV18" t="inlineStr">
         <is>
-          <t>16.16</t>
+          <t>16.07</t>
         </is>
       </c>
       <c r="BW18" t="inlineStr">
@@ -8121,12 +8121,12 @@
       </c>
       <c r="BY18" t="inlineStr">
         <is>
-          <t>29.67</t>
+          <t>29.63</t>
         </is>
       </c>
       <c r="BZ18" t="inlineStr">
         <is>
-          <t>12557</t>
+          <t>12493</t>
         </is>
       </c>
       <c r="CA18" t="inlineStr">
@@ -8146,12 +8146,12 @@
       </c>
       <c r="CD18" t="inlineStr">
         <is>
-          <t>36.3</t>
+          <t>36.4</t>
         </is>
       </c>
       <c r="CE18" t="inlineStr">
         <is>
-          <t>36.55</t>
+          <t>36.95</t>
         </is>
       </c>
       <c r="CF18" t="inlineStr">
@@ -8161,7 +8161,7 @@
       </c>
       <c r="CG18" t="inlineStr">
         <is>
-          <t>36.4</t>
+          <t>36.85</t>
         </is>
       </c>
       <c r="CH18" t="inlineStr">
@@ -8193,12 +8193,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>-1.76</t>
+          <t>0.83</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>1212.053</t>
+          <t>776.396</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -8208,7 +8208,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>36.1</t>
+          <t>36.4</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -8218,17 +8218,17 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>7.67</t>
+          <t>6.43</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>1.07</t>
+          <t>1.23</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>3.03</t>
+          <t>9.74</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -8293,7 +8293,7 @@
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>-16.34</t>
+          <t>-15.64</t>
         </is>
       </c>
       <c r="X19" t="inlineStr">
@@ -8303,17 +8303,17 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>12.91</t>
+          <t>8.27</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>-1.38</t>
+          <t>0.70</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
@@ -8324,73 +8324,73 @@
       <c r="AC19" t="inlineStr"/>
       <c r="AD19" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
-          <t>511</t>
+          <t>493</t>
         </is>
       </c>
       <c r="AF19" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>11.76</t>
         </is>
       </c>
       <c r="AG19" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>3.92</t>
         </is>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
-          <t>-2.62</t>
+          <t>-0.90</t>
         </is>
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>-4.47</t>
+          <t>-4.83</t>
         </is>
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>-4.38</t>
+          <t>-4.54</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>-2.09</t>
+          <t>-2.31</t>
         </is>
       </c>
       <c r="AL19" t="inlineStr">
         <is>
-          <t>37.07000000000001</t>
+          <t>36.73</t>
         </is>
       </c>
       <c r="AM19" t="n">
-        <v>38.8</v>
+        <v>38.6</v>
       </c>
       <c r="AN19" t="n">
-        <v>40.58</v>
+        <v>40.43</v>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>41.45</t>
+          <t>41.39</t>
         </is>
       </c>
       <c r="AP19" t="inlineStr">
         <is>
-          <t>-22.07</t>
+          <t>-19.31</t>
         </is>
       </c>
       <c r="AQ19" t="inlineStr">
         <is>
-          <t>-1.12</t>
+          <t>-1.15</t>
         </is>
       </c>
       <c r="AR19" t="inlineStr">
         <is>
-          <t>-0.91</t>
+          <t>-0.96</t>
         </is>
       </c>
       <c r="AS19" t="inlineStr">
@@ -8400,7 +8400,7 @@
       </c>
       <c r="AT19" t="inlineStr">
         <is>
-          <t>-134.02</t>
+          <t>-135.75</t>
         </is>
       </c>
       <c r="AU19" t="inlineStr">
@@ -8410,43 +8410,43 @@
       </c>
       <c r="AV19" t="inlineStr">
         <is>
-          <t>150251779.8621429</t>
+          <t>150078431.9122682</t>
         </is>
       </c>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>43823516.0</t>
+          <t>28176624.0</t>
         </is>
       </c>
       <c r="AX19" t="n">
-        <v>36085517.8</v>
+        <v>37871124</v>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
-          <t>35025550.9</t>
+          <t>34509118.0</t>
         </is>
       </c>
       <c r="AZ19" t="n">
-        <v>29409986</v>
+        <v>29545425.32</v>
       </c>
       <c r="BA19" t="inlineStr">
         <is>
-          <t>1059966</t>
+          <t>3362006</t>
         </is>
       </c>
       <c r="BB19" t="inlineStr">
         <is>
-          <t>880468.5492293607</t>
+          <t>956781.9001630185</t>
         </is>
       </c>
       <c r="BC19" t="inlineStr">
         <is>
-          <t>2130065.670099653</t>
+          <t>1376505.330298137</t>
         </is>
       </c>
       <c r="BD19" t="inlineStr">
         <is>
-          <t>43823516.0</t>
+          <t>28176624.0</t>
         </is>
       </c>
       <c r="BE19" t="inlineStr">
@@ -8466,7 +8466,7 @@
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>-13.01</t>
+          <t>-12.29</t>
         </is>
       </c>
       <c r="BI19" t="inlineStr">
@@ -8511,7 +8511,7 @@
       </c>
       <c r="BQ19" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR19" t="inlineStr">
@@ -8521,12 +8521,12 @@
       </c>
       <c r="BS19" t="inlineStr">
         <is>
-          <t>0.99</t>
+          <t>1.00</t>
         </is>
       </c>
       <c r="BT19" t="inlineStr">
         <is>
-          <t>6.39</t>
+          <t>6.43</t>
         </is>
       </c>
       <c r="BU19" t="inlineStr">
@@ -8536,7 +8536,7 @@
       </c>
       <c r="BV19" t="inlineStr">
         <is>
-          <t>16.16</t>
+          <t>16.07</t>
         </is>
       </c>
       <c r="BW19" t="inlineStr">
@@ -8551,12 +8551,12 @@
       </c>
       <c r="BY19" t="inlineStr">
         <is>
-          <t>29.67</t>
+          <t>29.63</t>
         </is>
       </c>
       <c r="BZ19" t="inlineStr">
         <is>
-          <t>12557</t>
+          <t>12493</t>
         </is>
       </c>
       <c r="CA19" t="inlineStr">
@@ -8576,22 +8576,22 @@
       </c>
       <c r="CD19" t="inlineStr">
         <is>
-          <t>36.85</t>
+          <t>36.3</t>
         </is>
       </c>
       <c r="CE19" t="inlineStr">
         <is>
-          <t>36.85</t>
+          <t>36.55</t>
         </is>
       </c>
       <c r="CF19" t="inlineStr">
         <is>
-          <t>35.85</t>
+          <t>36.0</t>
         </is>
       </c>
       <c r="CG19" t="inlineStr">
         <is>
-          <t>36.1</t>
+          <t>36.4</t>
         </is>
       </c>
       <c r="CH19" t="inlineStr">
@@ -8623,12 +8623,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>-0.54</t>
+          <t>-1.76</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>672.504</t>
+          <t>1212.053</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -8638,7 +8638,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>36.75</t>
+          <t>36.1</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -8648,17 +8648,17 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>6.01</t>
+          <t>7.2</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>1.07</t>
+          <t>1.23</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>-2.04</t>
+          <t>3.03</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -8723,7 +8723,7 @@
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>-14.83</t>
+          <t>-16.34</t>
         </is>
       </c>
       <c r="X20" t="inlineStr">
@@ -8733,17 +8733,17 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>7.17</t>
+          <t>12.91</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>-1.09</t>
+          <t>-1.38</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
@@ -8754,12 +8754,12 @@
       <c r="AC20" t="inlineStr"/>
       <c r="AD20" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
-          <t>511</t>
+          <t>493</t>
         </is>
       </c>
       <c r="AF20" t="inlineStr">
@@ -8774,53 +8774,53 @@
       </c>
       <c r="AH20" t="inlineStr">
         <is>
-          <t>-1.92</t>
+          <t>-2.62</t>
         </is>
       </c>
       <c r="AI20" t="inlineStr">
         <is>
-          <t>-3.97</t>
+          <t>-4.47</t>
         </is>
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>-4.25</t>
+          <t>-4.38</t>
         </is>
       </c>
       <c r="AK20" t="inlineStr">
         <is>
-          <t>-1.83</t>
+          <t>-2.09</t>
         </is>
       </c>
       <c r="AL20" t="inlineStr">
         <is>
-          <t>37.47000000000001</t>
+          <t>37.07000000000001</t>
         </is>
       </c>
       <c r="AM20" t="n">
-        <v>39.02</v>
+        <v>38.8</v>
       </c>
       <c r="AN20" t="n">
-        <v>40.75</v>
+        <v>40.58</v>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>41.51</t>
+          <t>41.45</t>
         </is>
       </c>
       <c r="AP20" t="inlineStr">
         <is>
-          <t>-19.33</t>
+          <t>-22.07</t>
         </is>
       </c>
       <c r="AQ20" t="inlineStr">
         <is>
-          <t>-1.03</t>
+          <t>-1.12</t>
         </is>
       </c>
       <c r="AR20" t="inlineStr">
         <is>
-          <t>-0.86</t>
+          <t>-0.91</t>
         </is>
       </c>
       <c r="AS20" t="inlineStr">
@@ -8830,7 +8830,7 @@
       </c>
       <c r="AT20" t="inlineStr">
         <is>
-          <t>-132.14</t>
+          <t>-134.02</t>
         </is>
       </c>
       <c r="AU20" t="inlineStr">
@@ -8840,43 +8840,43 @@
       </c>
       <c r="AV20" t="inlineStr">
         <is>
-          <t>150251779.8621429</t>
+          <t>150078431.9122682</t>
         </is>
       </c>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>24762299.0</t>
+          <t>43823516.0</t>
         </is>
       </c>
       <c r="AX20" t="n">
-        <v>31929308.6</v>
+        <v>36085517.8</v>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
-          <t>32595150.7</t>
+          <t>35025550.9</t>
         </is>
       </c>
       <c r="AZ20" t="n">
-        <v>29130934.74</v>
+        <v>29409986</v>
       </c>
       <c r="BA20" t="inlineStr">
         <is>
-          <t>-665842</t>
+          <t>1059966</t>
         </is>
       </c>
       <c r="BB20" t="inlineStr">
         <is>
-          <t>653269.0727074891</t>
+          <t>880468.5492293607</t>
         </is>
       </c>
       <c r="BC20" t="inlineStr">
         <is>
-          <t>1454053.953026839</t>
+          <t>2130065.670099653</t>
         </is>
       </c>
       <c r="BD20" t="inlineStr">
         <is>
-          <t>24762299.0</t>
+          <t>43823516.0</t>
         </is>
       </c>
       <c r="BE20" t="inlineStr">
@@ -8896,7 +8896,7 @@
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>-11.45</t>
+          <t>-13.01</t>
         </is>
       </c>
       <c r="BI20" t="inlineStr">
@@ -8951,12 +8951,12 @@
       </c>
       <c r="BS20" t="inlineStr">
         <is>
-          <t>1.01</t>
+          <t>0.99</t>
         </is>
       </c>
       <c r="BT20" t="inlineStr">
         <is>
-          <t>6.39</t>
+          <t>6.43</t>
         </is>
       </c>
       <c r="BU20" t="inlineStr">
@@ -8966,7 +8966,7 @@
       </c>
       <c r="BV20" t="inlineStr">
         <is>
-          <t>16.16</t>
+          <t>16.07</t>
         </is>
       </c>
       <c r="BW20" t="inlineStr">
@@ -8981,12 +8981,12 @@
       </c>
       <c r="BY20" t="inlineStr">
         <is>
-          <t>29.67</t>
+          <t>29.63</t>
         </is>
       </c>
       <c r="BZ20" t="inlineStr">
         <is>
-          <t>12557</t>
+          <t>12493</t>
         </is>
       </c>
       <c r="CA20" t="inlineStr">
@@ -9006,22 +9006,22 @@
       </c>
       <c r="CD20" t="inlineStr">
         <is>
-          <t>36.95</t>
+          <t>36.85</t>
         </is>
       </c>
       <c r="CE20" t="inlineStr">
         <is>
-          <t>37.3</t>
+          <t>36.85</t>
         </is>
       </c>
       <c r="CF20" t="inlineStr">
         <is>
-          <t>36.6</t>
+          <t>35.85</t>
         </is>
       </c>
       <c r="CG20" t="inlineStr">
         <is>
-          <t>36.75</t>
+          <t>36.1</t>
         </is>
       </c>
       <c r="CH20" t="inlineStr">
@@ -9053,12 +9053,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>-1.34</t>
+          <t>-0.54</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>1065.248</t>
+          <t>672.504</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -9068,7 +9068,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>36.95</t>
+          <t>36.75</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -9078,17 +9078,17 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>5.5</t>
+          <t>5.53</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>1.07</t>
+          <t>1.23</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>28.28</t>
+          <t>-2.04</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -9153,7 +9153,7 @@
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>-14.37</t>
+          <t>-14.83</t>
         </is>
       </c>
       <c r="X21" t="inlineStr">
@@ -9163,17 +9163,17 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>11.35</t>
+          <t>7.17</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>-0.81</t>
+          <t>-1.09</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
@@ -9184,12 +9184,12 @@
       <c r="AC21" t="inlineStr"/>
       <c r="AD21" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
-          <t>511</t>
+          <t>493</t>
         </is>
       </c>
       <c r="AF21" t="inlineStr">
@@ -9199,58 +9199,58 @@
       </c>
       <c r="AG21" t="inlineStr">
         <is>
-          <t>9.38</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
-          <t>-1.86</t>
+          <t>-1.92</t>
         </is>
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>-4.02</t>
+          <t>-3.97</t>
         </is>
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>-4.09</t>
+          <t>-4.25</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
         <is>
-          <t>-1.60</t>
+          <t>-1.83</t>
         </is>
       </c>
       <c r="AL21" t="inlineStr">
         <is>
-          <t>37.65000000000001</t>
+          <t>37.47000000000001</t>
         </is>
       </c>
       <c r="AM21" t="n">
-        <v>39.23</v>
+        <v>39.02</v>
       </c>
       <c r="AN21" t="n">
-        <v>40.9</v>
+        <v>40.75</v>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>41.57</t>
+          <t>41.51</t>
         </is>
       </c>
       <c r="AP21" t="inlineStr">
         <is>
-          <t>-18.37</t>
+          <t>-19.33</t>
         </is>
       </c>
       <c r="AQ21" t="inlineStr">
         <is>
-          <t>-0.97</t>
+          <t>-1.03</t>
         </is>
       </c>
       <c r="AR21" t="inlineStr">
         <is>
-          <t>-0.82</t>
+          <t>-0.86</t>
         </is>
       </c>
       <c r="AS21" t="inlineStr">
@@ -9260,7 +9260,7 @@
       </c>
       <c r="AT21" t="inlineStr">
         <is>
-          <t>-130.59</t>
+          <t>-132.14</t>
         </is>
       </c>
       <c r="AU21" t="inlineStr">
@@ -9270,43 +9270,43 @@
       </c>
       <c r="AV21" t="inlineStr">
         <is>
-          <t>150251779.8621429</t>
+          <t>150078431.9122682</t>
         </is>
       </c>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>39374759.0</t>
+          <t>24762299.0</t>
         </is>
       </c>
       <c r="AX21" t="n">
-        <v>40349216</v>
+        <v>31929308.6</v>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
-          <t>31454761.9</t>
+          <t>32595150.7</t>
         </is>
       </c>
       <c r="AZ21" t="n">
-        <v>29061426.18</v>
+        <v>29130934.74</v>
       </c>
       <c r="BA21" t="inlineStr">
         <is>
-          <t>8894454</t>
+          <t>-665842</t>
         </is>
       </c>
       <c r="BB21" t="inlineStr">
         <is>
-          <t>507671.8217403347</t>
+          <t>653269.0727074891</t>
         </is>
       </c>
       <c r="BC21" t="inlineStr">
         <is>
-          <t>2478665.680314712</t>
+          <t>1454053.953026839</t>
         </is>
       </c>
       <c r="BD21" t="inlineStr">
         <is>
-          <t>39374759.0</t>
+          <t>24762299.0</t>
         </is>
       </c>
       <c r="BE21" t="inlineStr">
@@ -9326,7 +9326,7 @@
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>-10.96</t>
+          <t>-11.45</t>
         </is>
       </c>
       <c r="BI21" t="inlineStr">
@@ -9371,7 +9371,7 @@
       </c>
       <c r="BQ21" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR21" t="inlineStr">
@@ -9381,12 +9381,12 @@
       </c>
       <c r="BS21" t="inlineStr">
         <is>
-          <t>1.02</t>
+          <t>1.01</t>
         </is>
       </c>
       <c r="BT21" t="inlineStr">
         <is>
-          <t>6.39</t>
+          <t>6.43</t>
         </is>
       </c>
       <c r="BU21" t="inlineStr">
@@ -9396,7 +9396,7 @@
       </c>
       <c r="BV21" t="inlineStr">
         <is>
-          <t>16.16</t>
+          <t>16.07</t>
         </is>
       </c>
       <c r="BW21" t="inlineStr">
@@ -9411,12 +9411,12 @@
       </c>
       <c r="BY21" t="inlineStr">
         <is>
-          <t>29.67</t>
+          <t>29.63</t>
         </is>
       </c>
       <c r="BZ21" t="inlineStr">
         <is>
-          <t>12557</t>
+          <t>12493</t>
         </is>
       </c>
       <c r="CA21" t="inlineStr">
@@ -9436,22 +9436,22 @@
       </c>
       <c r="CD21" t="inlineStr">
         <is>
+          <t>36.95</t>
+        </is>
+      </c>
+      <c r="CE21" t="inlineStr">
+        <is>
           <t>37.3</t>
         </is>
       </c>
-      <c r="CE21" t="inlineStr">
-        <is>
-          <t>37.5</t>
-        </is>
-      </c>
       <c r="CF21" t="inlineStr">
         <is>
-          <t>36.7</t>
+          <t>36.6</t>
         </is>
       </c>
       <c r="CG21" t="inlineStr">
         <is>
-          <t>36.95</t>
+          <t>36.75</t>
         </is>
       </c>
       <c r="CH21" t="inlineStr">
@@ -9483,12 +9483,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>-1.71</t>
+          <t>-1.34</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>1408.733</t>
+          <t>1065.248</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -9498,7 +9498,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>37.45</t>
+          <t>36.95</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -9508,17 +9508,17 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>4.22</t>
+          <t>5.01</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>1.07</t>
+          <t>1.23</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>22.93</t>
+          <t>28.28</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -9583,7 +9583,7 @@
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>-13.21</t>
+          <t>-14.37</t>
         </is>
       </c>
       <c r="X22" t="inlineStr">
@@ -9593,17 +9593,17 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>15.01</t>
+          <t>11.35</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>-2.94</t>
+          <t>-0.81</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
@@ -9614,12 +9614,12 @@
       <c r="AC22" t="inlineStr"/>
       <c r="AD22" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE22" t="inlineStr">
         <is>
-          <t>511</t>
+          <t>493</t>
         </is>
       </c>
       <c r="AF22" t="inlineStr">
@@ -9629,58 +9629,58 @@
       </c>
       <c r="AG22" t="inlineStr">
         <is>
-          <t>16.69</t>
+          <t>9.38</t>
         </is>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
-          <t>-1.42</t>
+          <t>-1.86</t>
         </is>
       </c>
       <c r="AI22" t="inlineStr">
         <is>
-          <t>-3.63</t>
+          <t>-4.02</t>
         </is>
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>-3.96</t>
+          <t>-4.09</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
         <is>
-          <t>-1.34</t>
+          <t>-1.60</t>
         </is>
       </c>
       <c r="AL22" t="inlineStr">
         <is>
-          <t>37.99</t>
+          <t>37.65000000000001</t>
         </is>
       </c>
       <c r="AM22" t="n">
-        <v>39.42</v>
+        <v>39.23</v>
       </c>
       <c r="AN22" t="n">
-        <v>41.05</v>
+        <v>40.9</v>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>41.6</t>
+          <t>41.57</t>
         </is>
       </c>
       <c r="AP22" t="inlineStr">
         <is>
-          <t>-15.49</t>
+          <t>-18.37</t>
         </is>
       </c>
       <c r="AQ22" t="inlineStr">
         <is>
-          <t>-0.91</t>
+          <t>-0.97</t>
         </is>
       </c>
       <c r="AR22" t="inlineStr">
         <is>
-          <t>-0.78</t>
+          <t>-0.82</t>
         </is>
       </c>
       <c r="AS22" t="inlineStr">
@@ -9690,7 +9690,7 @@
       </c>
       <c r="AT22" t="inlineStr">
         <is>
-          <t>-129.19</t>
+          <t>-130.59</t>
         </is>
       </c>
       <c r="AU22" t="inlineStr">
@@ -9700,43 +9700,43 @@
       </c>
       <c r="AV22" t="inlineStr">
         <is>
-          <t>150251779.8621429</t>
+          <t>150078431.9122682</t>
         </is>
       </c>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>53218422.0</t>
+          <t>39374759.0</t>
         </is>
       </c>
       <c r="AX22" t="n">
-        <v>36341855.6</v>
+        <v>40349216</v>
       </c>
       <c r="AY22" t="inlineStr">
         <is>
-          <t>29562657.9</t>
+          <t>31454761.9</t>
         </is>
       </c>
       <c r="AZ22" t="n">
-        <v>28846965.04</v>
+        <v>29061426.18</v>
       </c>
       <c r="BA22" t="inlineStr">
         <is>
-          <t>6779197</t>
+          <t>8894454</t>
         </is>
       </c>
       <c r="BB22" t="inlineStr">
         <is>
-          <t>149309.3019995387</t>
+          <t>507671.8217403347</t>
         </is>
       </c>
       <c r="BC22" t="inlineStr">
         <is>
-          <t>2288252.230714723</t>
+          <t>2478665.680314712</t>
         </is>
       </c>
       <c r="BD22" t="inlineStr">
         <is>
-          <t>53218422.0</t>
+          <t>39374759.0</t>
         </is>
       </c>
       <c r="BE22" t="inlineStr">
@@ -9756,7 +9756,7 @@
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>-9.76</t>
+          <t>-10.96</t>
         </is>
       </c>
       <c r="BI22" t="inlineStr">
@@ -9801,7 +9801,7 @@
       </c>
       <c r="BQ22" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR22" t="inlineStr">
@@ -9811,12 +9811,12 @@
       </c>
       <c r="BS22" t="inlineStr">
         <is>
-          <t>1.03</t>
+          <t>1.02</t>
         </is>
       </c>
       <c r="BT22" t="inlineStr">
         <is>
-          <t>6.39</t>
+          <t>6.43</t>
         </is>
       </c>
       <c r="BU22" t="inlineStr">
@@ -9826,7 +9826,7 @@
       </c>
       <c r="BV22" t="inlineStr">
         <is>
-          <t>16.16</t>
+          <t>16.07</t>
         </is>
       </c>
       <c r="BW22" t="inlineStr">
@@ -9841,12 +9841,12 @@
       </c>
       <c r="BY22" t="inlineStr">
         <is>
-          <t>29.67</t>
+          <t>29.63</t>
         </is>
       </c>
       <c r="BZ22" t="inlineStr">
         <is>
-          <t>12557</t>
+          <t>12493</t>
         </is>
       </c>
       <c r="CA22" t="inlineStr">
@@ -9866,22 +9866,22 @@
       </c>
       <c r="CD22" t="inlineStr">
         <is>
-          <t>38.1</t>
+          <t>37.3</t>
         </is>
       </c>
       <c r="CE22" t="inlineStr">
         <is>
-          <t>38.7</t>
+          <t>37.5</t>
         </is>
       </c>
       <c r="CF22" t="inlineStr">
         <is>
-          <t>37.3</t>
+          <t>36.7</t>
         </is>
       </c>
       <c r="CG22" t="inlineStr">
         <is>
-          <t>37.45</t>
+          <t>36.95</t>
         </is>
       </c>
       <c r="CH22" t="inlineStr">
@@ -9913,12 +9913,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-1.71</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>504.317</t>
+          <t>1408.733</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -9928,7 +9928,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>38.1</t>
+          <t>37.45</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -9938,17 +9938,17 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>2.56</t>
+          <t>3.73</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>1.07</t>
+          <t>1.23</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>20.39</t>
+          <t>22.93</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -10013,7 +10013,7 @@
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>-11.70</t>
+          <t>-13.21</t>
         </is>
       </c>
       <c r="X23" t="inlineStr">
@@ -10023,17 +10023,17 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>5.37</t>
+          <t>15.01</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>-0.39</t>
+          <t>-2.94</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
@@ -10044,17 +10044,17 @@
       <c r="AC23" t="inlineStr"/>
       <c r="AD23" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE23" t="inlineStr">
         <is>
-          <t>511</t>
+          <t>493</t>
         </is>
       </c>
       <c r="AF23" t="inlineStr">
         <is>
-          <t>28.13</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG23" t="inlineStr">
@@ -10064,53 +10064,53 @@
       </c>
       <c r="AH23" t="inlineStr">
         <is>
-          <t>-0.55</t>
+          <t>-1.42</t>
         </is>
       </c>
       <c r="AI23" t="inlineStr">
         <is>
-          <t>-3.22</t>
+          <t>-3.63</t>
         </is>
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>-3.86</t>
+          <t>-3.96</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
         <is>
-          <t>-1.12</t>
+          <t>-1.34</t>
         </is>
       </c>
       <c r="AL23" t="inlineStr">
         <is>
-          <t>38.31</t>
+          <t>37.99</t>
         </is>
       </c>
       <c r="AM23" t="n">
-        <v>39.58</v>
+        <v>39.42</v>
       </c>
       <c r="AN23" t="n">
-        <v>41.17</v>
+        <v>41.05</v>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>41.64</t>
+          <t>41.6</t>
         </is>
       </c>
       <c r="AP23" t="inlineStr">
         <is>
-          <t>-13.76</t>
+          <t>-15.49</t>
         </is>
       </c>
       <c r="AQ23" t="inlineStr">
         <is>
-          <t>-0.86</t>
+          <t>-0.91</t>
         </is>
       </c>
       <c r="AR23" t="inlineStr">
         <is>
-          <t>-0.75</t>
+          <t>-0.78</t>
         </is>
       </c>
       <c r="AS23" t="inlineStr">
@@ -10120,7 +10120,7 @@
       </c>
       <c r="AT23" t="inlineStr">
         <is>
-          <t>-128.06</t>
+          <t>-129.19</t>
         </is>
       </c>
       <c r="AU23" t="inlineStr">
@@ -10130,43 +10130,43 @@
       </c>
       <c r="AV23" t="inlineStr">
         <is>
-          <t>150251779.8621429</t>
+          <t>150078431.9122682</t>
         </is>
       </c>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>19248593.0</t>
+          <t>53218422.0</t>
         </is>
       </c>
       <c r="AX23" t="n">
-        <v>31147112</v>
+        <v>36341855.6</v>
       </c>
       <c r="AY23" t="inlineStr">
         <is>
-          <t>25871081.1</t>
+          <t>29562657.9</t>
         </is>
       </c>
       <c r="AZ23" t="n">
-        <v>28091032.78</v>
+        <v>28846965.04</v>
       </c>
       <c r="BA23" t="inlineStr">
         <is>
-          <t>5276030</t>
+          <t>6779197</t>
         </is>
       </c>
       <c r="BB23" t="inlineStr">
         <is>
-          <t>-239589.4123123131</t>
+          <t>149309.3019995387</t>
         </is>
       </c>
       <c r="BC23" t="inlineStr">
         <is>
-          <t>451260.1159035005</t>
+          <t>2288252.230714723</t>
         </is>
       </c>
       <c r="BD23" t="inlineStr">
         <is>
-          <t>19248593.0</t>
+          <t>53218422.0</t>
         </is>
       </c>
       <c r="BE23" t="inlineStr">
@@ -10186,7 +10186,7 @@
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>-8.19</t>
+          <t>-9.76</t>
         </is>
       </c>
       <c r="BI23" t="inlineStr">
@@ -10231,7 +10231,7 @@
       </c>
       <c r="BQ23" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR23" t="inlineStr">
@@ -10241,12 +10241,12 @@
       </c>
       <c r="BS23" t="inlineStr">
         <is>
-          <t>1.05</t>
+          <t>1.03</t>
         </is>
       </c>
       <c r="BT23" t="inlineStr">
         <is>
-          <t>6.39</t>
+          <t>6.43</t>
         </is>
       </c>
       <c r="BU23" t="inlineStr">
@@ -10256,7 +10256,7 @@
       </c>
       <c r="BV23" t="inlineStr">
         <is>
-          <t>16.16</t>
+          <t>16.07</t>
         </is>
       </c>
       <c r="BW23" t="inlineStr">
@@ -10271,12 +10271,12 @@
       </c>
       <c r="BY23" t="inlineStr">
         <is>
-          <t>29.67</t>
+          <t>29.63</t>
         </is>
       </c>
       <c r="BZ23" t="inlineStr">
         <is>
-          <t>12557</t>
+          <t>12493</t>
         </is>
       </c>
       <c r="CA23" t="inlineStr">
@@ -10296,22 +10296,22 @@
       </c>
       <c r="CD23" t="inlineStr">
         <is>
-          <t>38.2</t>
+          <t>38.1</t>
         </is>
       </c>
       <c r="CE23" t="inlineStr">
         <is>
-          <t>38.4</t>
+          <t>38.7</t>
         </is>
       </c>
       <c r="CF23" t="inlineStr">
         <is>
-          <t>37.95</t>
+          <t>37.3</t>
         </is>
       </c>
       <c r="CG23" t="inlineStr">
         <is>
-          <t>38.1</t>
+          <t>37.45</t>
         </is>
       </c>
       <c r="CH23" t="inlineStr">

--- a/Result/checksun_type/塔架.xlsx
+++ b/Result/checksun_type/塔架.xlsx
@@ -883,12 +883,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>-0.35</t>
+          <t>1.77</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>800.978</t>
+          <t>999.152</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>140.5</t>
+          <t>143.0</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-1.3</t>
+          <t>-1.69</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>-37.50</t>
+          <t>-34.04</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-40.72</t>
+          <t>-39.66</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -993,17 +993,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>3.31</t>
+          <t>4.13</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>0.37</t>
+          <t>0.02</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1014,17 +1014,17 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>801</t>
+          <t>999</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>83.33</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
@@ -1034,53 +1034,53 @@
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>0.14</t>
+          <t>1.27</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>-2.14</t>
+          <t>-1.03</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>-8.77</t>
+          <t>-8.91</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>-6.13</t>
+          <t>-6.08</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>140.3</t>
+          <t>141.2</t>
         </is>
       </c>
       <c r="AM2" t="n">
-        <v>143.38</v>
+        <v>142.68</v>
       </c>
       <c r="AN2" t="n">
-        <v>157.15</v>
+        <v>156.63</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>167.42</t>
+          <t>166.78</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>15.78</t>
+          <t>21.03</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>-5.62</t>
+          <t>-5.00</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>-6.67</t>
+          <t>-6.34</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -1090,7 +1090,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-126.80</t>
+          <t>-125.46</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1100,43 +1100,43 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>1684514497.82311</t>
+          <t>1682419827.202991</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>111993447.0</t>
+          <t>142703815.0</t>
         </is>
       </c>
       <c r="AX2" t="n">
-        <v>138810283.4</v>
+        <v>120065081.4</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>222079436.2</t>
+          <t>182016975.2</t>
         </is>
       </c>
       <c r="AZ2" t="n">
-        <v>246079338.72</v>
+        <v>246778897.84</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>-83269152</t>
+          <t>-61951893</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>-4866933.171784954</t>
+          <t>-7828264.537723166</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>-25086844.97953352</t>
+          <t>-24115587.05038333</t>
         </is>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
-          <t>111993447.0</t>
+          <t>142703815.0</t>
         </is>
       </c>
       <c r="BE2" t="inlineStr">
@@ -1156,7 +1156,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>-21.94</t>
+          <t>-20.56</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
@@ -1181,7 +1181,7 @@
       </c>
       <c r="BM2" t="inlineStr">
         <is>
-          <t>0.97</t>
+          <t>0.96</t>
         </is>
       </c>
       <c r="BN2" t="inlineStr">
@@ -1201,7 +1201,7 @@
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
@@ -1211,12 +1211,12 @@
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>3.24</t>
+          <t>3.29</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
         <is>
-          <t>2.96</t>
+          <t>2.91</t>
         </is>
       </c>
       <c r="BU2" t="inlineStr">
@@ -1226,7 +1226,7 @@
       </c>
       <c r="BV2" t="inlineStr">
         <is>
-          <t>26.41</t>
+          <t>26.88</t>
         </is>
       </c>
       <c r="BW2" t="inlineStr">
@@ -1241,12 +1241,12 @@
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>29.63</t>
+          <t>30.23</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>34689</t>
+          <t>35306</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
@@ -1266,22 +1266,22 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>141.5</t>
+          <t>141.0</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>141.5</t>
+          <t>145.0</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>139.0</t>
+          <t>141.0</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>140.5</t>
+          <t>143.0</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
@@ -1313,12 +1313,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>-1.04</t>
+          <t>-0.35</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>494.362</t>
+          <t>800.978</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1328,7 +1328,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>141.0</t>
+          <t>140.5</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1338,17 +1338,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-0.36</t>
+          <t>1.75</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-1.3</t>
+          <t>-1.69</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>-47.22</t>
+          <t>-37.50</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1413,7 +1413,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-40.51</t>
+          <t>-40.72</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1423,17 +1423,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>2.04</t>
+          <t>3.31</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>-2.13</t>
+          <t>0.37</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1444,73 +1444,73 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>801</t>
+          <t>999</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>87.5</t>
+          <t>83.33</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>77.41</t>
+          <t>90.28</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>1.29</t>
+          <t>0.14</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>-3.35</t>
+          <t>-2.14</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-8.68</t>
+          <t>-8.77</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>-6.17</t>
+          <t>-6.13</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>139.2</t>
+          <t>140.3</t>
         </is>
       </c>
       <c r="AM3" t="n">
-        <v>144.02</v>
+        <v>143.38</v>
       </c>
       <c r="AN3" t="n">
-        <v>157.72</v>
+        <v>157.15</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>168.09</t>
+          <t>167.42</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>12.54</t>
+          <t>15.78</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>-6.06</t>
+          <t>-5.62</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>-6.93</t>
+          <t>-6.67</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1520,7 +1520,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-127.86</t>
+          <t>-126.80</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1530,43 +1530,43 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>1684514497.82311</t>
+          <t>1682419827.202991</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>70132250.0</t>
+          <t>111993447.0</t>
         </is>
       </c>
       <c r="AX3" t="n">
-        <v>151097591.6</v>
+        <v>138810283.4</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>286274053.3</t>
+          <t>222079436.2</t>
         </is>
       </c>
       <c r="AZ3" t="n">
-        <v>248269560.06</v>
+        <v>246079338.72</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>-135176461</t>
+          <t>-83269152</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>-1190585.570376122</t>
+          <t>-4866933.171784954</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>-22288000.98619333</t>
+          <t>-25086844.97953352</t>
         </is>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
-          <t>70132250.0</t>
+          <t>111993447.0</t>
         </is>
       </c>
       <c r="BE3" t="inlineStr">
@@ -1586,7 +1586,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>-21.67</t>
+          <t>-21.94</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
@@ -1611,7 +1611,7 @@
       </c>
       <c r="BM3" t="inlineStr">
         <is>
-          <t>0.97</t>
+          <t>0.96</t>
         </is>
       </c>
       <c r="BN3" t="inlineStr">
@@ -1631,22 +1631,22 @@
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
         <is>
-          <t>價跌量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>3.25</t>
+          <t>3.24</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
         <is>
-          <t>2.96</t>
+          <t>2.91</t>
         </is>
       </c>
       <c r="BU3" t="inlineStr">
@@ -1656,7 +1656,7 @@
       </c>
       <c r="BV3" t="inlineStr">
         <is>
-          <t>26.41</t>
+          <t>26.88</t>
         </is>
       </c>
       <c r="BW3" t="inlineStr">
@@ -1671,12 +1671,12 @@
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>29.63</t>
+          <t>30.23</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
-          <t>34689</t>
+          <t>35306</t>
         </is>
       </c>
       <c r="CA3" t="inlineStr">
@@ -1696,22 +1696,22 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>144.0</t>
+          <t>141.5</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>144.0</t>
+          <t>141.5</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>141.0</t>
+          <t>139.0</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>141.0</t>
+          <t>140.5</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
@@ -1743,12 +1743,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>2.48</t>
+          <t>-1.04</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>885.355</t>
+          <t>494.362</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1758,7 +1758,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>142.5</t>
+          <t>141.0</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1768,17 +1768,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-1.42</t>
+          <t>1.4</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-1.3</t>
+          <t>-1.69</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>-37.74</t>
+          <t>-47.22</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1843,7 +1843,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-39.87</t>
+          <t>-40.51</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1853,17 +1853,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>3.66</t>
+          <t>2.04</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>0.36</t>
+          <t>-2.13</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1874,73 +1874,73 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>801</t>
+          <t>999</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>87.5</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>62.28</t>
+          <t>77.41</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>3.26</t>
+          <t>1.29</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>-4.63</t>
+          <t>-3.35</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>-8.6</t>
+          <t>-8.68</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>-6.19</t>
+          <t>-6.17</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>138.0</t>
+          <t>139.2</t>
         </is>
       </c>
       <c r="AM4" t="n">
-        <v>144.7</v>
+        <v>144.02</v>
       </c>
       <c r="AN4" t="n">
-        <v>158.31</v>
+        <v>157.72</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>168.75</t>
+          <t>168.09</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>7.75</t>
+          <t>12.54</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>-6.60</t>
+          <t>-6.06</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>-7.15</t>
+          <t>-6.93</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1950,7 +1950,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-128.73</t>
+          <t>-127.86</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1960,43 +1960,43 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>1684514497.82311</t>
+          <t>1682419827.202991</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>126140252.0</t>
+          <t>70132250.0</t>
         </is>
       </c>
       <c r="AX4" t="n">
-        <v>179646773.6</v>
+        <v>151097591.6</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>288541776.1</t>
+          <t>286274053.3</t>
         </is>
       </c>
       <c r="AZ4" t="n">
-        <v>249860076.6</v>
+        <v>248269560.06</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>-108895002</t>
+          <t>-135176461</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>2645308.141590643</t>
+          <t>-1190585.570376122</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>-13008524.13905758</t>
+          <t>-22288000.98619333</t>
         </is>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
-          <t>126140252.0</t>
+          <t>70132250.0</t>
         </is>
       </c>
       <c r="BE4" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>-20.83</t>
+          <t>-21.67</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
@@ -2041,7 +2041,7 @@
       </c>
       <c r="BM4" t="inlineStr">
         <is>
-          <t>0.97</t>
+          <t>0.96</t>
         </is>
       </c>
       <c r="BN4" t="inlineStr">
@@ -2061,22 +2061,22 @@
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價跌量-</t>
         </is>
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>3.28</t>
+          <t>3.25</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
         <is>
-          <t>2.96</t>
+          <t>2.91</t>
         </is>
       </c>
       <c r="BU4" t="inlineStr">
@@ -2086,7 +2086,7 @@
       </c>
       <c r="BV4" t="inlineStr">
         <is>
-          <t>26.41</t>
+          <t>26.88</t>
         </is>
       </c>
       <c r="BW4" t="inlineStr">
@@ -2101,12 +2101,12 @@
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>29.63</t>
+          <t>30.23</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
-          <t>34689</t>
+          <t>35306</t>
         </is>
       </c>
       <c r="CA4" t="inlineStr">
@@ -2126,22 +2126,22 @@
       </c>
       <c r="CD4" t="inlineStr">
         <is>
+          <t>144.0</t>
+        </is>
+      </c>
+      <c r="CE4" t="inlineStr">
+        <is>
+          <t>144.0</t>
+        </is>
+      </c>
+      <c r="CF4" t="inlineStr">
+        <is>
           <t>141.0</t>
         </is>
       </c>
-      <c r="CE4" t="inlineStr">
-        <is>
-          <t>143.5</t>
-        </is>
-      </c>
-      <c r="CF4" t="inlineStr">
+      <c r="CG4" t="inlineStr">
         <is>
           <t>141.0</t>
-        </is>
-      </c>
-      <c r="CG4" t="inlineStr">
-        <is>
-          <t>142.5</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
@@ -2163,7 +2163,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>【e】</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -2173,127 +2173,127 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
+          <t>2.48</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>885.355</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>142.5</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>0.35</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>-1.69</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>-37.74</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>-65.0</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>2025-06-04 00:00:00</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>2025-06-30 00:00:00</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>2025-05-09 00:00:00</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>2025-05-23 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>199.0</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>237.0</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>181.0</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>178.0</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>-39.87</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>11.80</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-11-26</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>3.66</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
           <t>0.36</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>1070.548</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>139.0</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>1.07</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>-1.3</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>-30.56</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>-65.0</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>2025-06-04 00:00:00</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>2025-06-30 00:00:00</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>2025-05-09 00:00:00</t>
-        </is>
-      </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>2025-05-23 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q5" t="inlineStr">
-        <is>
-          <t>199.0</t>
-        </is>
-      </c>
-      <c r="R5" t="inlineStr">
-        <is>
-          <t>237.0</t>
-        </is>
-      </c>
-      <c r="S5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T5" t="inlineStr">
-        <is>
-          <t>181.0</t>
-        </is>
-      </c>
-      <c r="U5" t="inlineStr">
-        <is>
-          <t>178.0</t>
-        </is>
-      </c>
-      <c r="V5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>-41.35</t>
-        </is>
-      </c>
-      <c r="X5" t="inlineStr">
-        <is>
-          <t>11.80</t>
-        </is>
-      </c>
-      <c r="Y5" t="inlineStr">
-        <is>
-          <t>2025-11-25</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>4.43</t>
-        </is>
-      </c>
-      <c r="AA5" t="inlineStr">
-        <is>
-          <t>-0.71</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2304,37 +2304,37 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>801</t>
+          <t>999</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>44.74</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>36.84</t>
+          <t>62.28</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>2.51</t>
+          <t>3.26</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>-6.71</t>
+          <t>-4.63</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>-8.49</t>
+          <t>-8.6</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
@@ -2344,33 +2344,33 @@
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>135.6</t>
+          <t>138.0</t>
         </is>
       </c>
       <c r="AM5" t="n">
-        <v>145.35</v>
+        <v>144.7</v>
       </c>
       <c r="AN5" t="n">
-        <v>158.83</v>
+        <v>158.31</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>169.32</t>
+          <t>168.75</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>-0.61</t>
+          <t>7.75</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>-7.33</t>
+          <t>-6.60</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>-7.29</t>
+          <t>-7.15</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -2380,7 +2380,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-129.29</t>
+          <t>-128.73</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2390,43 +2390,43 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>1684514497.82311</t>
+          <t>1682419827.202991</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>149355643.0</t>
+          <t>126140252.0</t>
         </is>
       </c>
       <c r="AX5" t="n">
-        <v>199168061</v>
+        <v>179646773.6</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>286806442.7</t>
+          <t>288541776.1</t>
         </is>
       </c>
       <c r="AZ5" t="n">
-        <v>252995092.08</v>
+        <v>249860076.6</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>-87638381</t>
+          <t>-108895002</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>5491459.465344865</t>
+          <t>2645308.141590643</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>-5288395.852468729</t>
+          <t>-13008524.13905758</t>
         </is>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
-          <t>149355643.0</t>
+          <t>126140252.0</t>
         </is>
       </c>
       <c r="BE5" t="inlineStr">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>-22.78</t>
+          <t>-20.83</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
@@ -2471,7 +2471,7 @@
       </c>
       <c r="BM5" t="inlineStr">
         <is>
-          <t>0.97</t>
+          <t>0.96</t>
         </is>
       </c>
       <c r="BN5" t="inlineStr">
@@ -2491,22 +2491,22 @@
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>3.20</t>
+          <t>3.28</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
         <is>
-          <t>2.96</t>
+          <t>2.91</t>
         </is>
       </c>
       <c r="BU5" t="inlineStr">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="BV5" t="inlineStr">
         <is>
-          <t>26.41</t>
+          <t>26.88</t>
         </is>
       </c>
       <c r="BW5" t="inlineStr">
@@ -2531,12 +2531,12 @@
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>29.63</t>
+          <t>30.23</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
-          <t>34689</t>
+          <t>35306</t>
         </is>
       </c>
       <c r="CA5" t="inlineStr">
@@ -2556,22 +2556,22 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>139.5</t>
+          <t>141.0</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
+          <t>143.5</t>
+        </is>
+      </c>
+      <c r="CF5" t="inlineStr">
+        <is>
           <t>141.0</t>
         </is>
       </c>
-      <c r="CF5" t="inlineStr">
-        <is>
-          <t>138.0</t>
-        </is>
-      </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>139.0</t>
+          <t>142.5</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
@@ -2603,12 +2603,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>2.56</t>
+          <t>0.36</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>1721.237</t>
+          <t>1070.548</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2618,7 +2618,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>138.5</t>
+          <t>139.0</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2628,17 +2628,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>2.8</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-1.3</t>
+          <t>-1.69</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>-13.08</t>
+          <t>-30.56</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2703,7 +2703,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-41.56</t>
+          <t>-41.35</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2713,17 +2713,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>7.12</t>
+          <t>4.43</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>1.87</t>
+          <t>-0.71</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2734,73 +2734,73 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>801</t>
+          <t>999</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>42.11</t>
+          <t>44.74</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>29.62</t>
+          <t>36.84</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>3.44</t>
+          <t>2.51</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>-8.46</t>
+          <t>-6.71</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>-8.28</t>
+          <t>-8.49</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>-6.17</t>
+          <t>-6.19</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>133.9</t>
+          <t>135.6</t>
         </is>
       </c>
       <c r="AM6" t="n">
-        <v>146.28</v>
+        <v>145.35</v>
       </c>
       <c r="AN6" t="n">
-        <v>159.48</v>
+        <v>158.83</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>169.96</t>
+          <t>169.32</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>-7.31</t>
+          <t>-0.61</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>-7.81</t>
+          <t>-7.33</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>-7.28</t>
+          <t>-7.29</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -2810,7 +2810,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-129.24</t>
+          <t>-129.29</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2820,43 +2820,43 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>1684514497.82311</t>
+          <t>1682419827.202991</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>236429825.0</t>
+          <t>149355643.0</t>
         </is>
       </c>
       <c r="AX6" t="n">
-        <v>243968869</v>
+        <v>199168061</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>280669574.0</t>
+          <t>286806442.7</t>
         </is>
       </c>
       <c r="AZ6" t="n">
-        <v>255272113.08</v>
+        <v>252995092.08</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>-36700705</t>
+          <t>-87638381</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>7451433.159492791</t>
+          <t>5491459.465344865</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>3441866.801674962</t>
+          <t>-5288395.852468729</t>
         </is>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
-          <t>236429825.0</t>
+          <t>149355643.0</t>
         </is>
       </c>
       <c r="BE6" t="inlineStr">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>-23.06</t>
+          <t>-22.78</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="BM6" t="inlineStr">
         <is>
-          <t>0.97</t>
+          <t>0.96</t>
         </is>
       </c>
       <c r="BN6" t="inlineStr">
@@ -2921,7 +2921,7 @@
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;可能出現反轉訊號&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;3&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
@@ -2931,12 +2931,12 @@
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>3.19</t>
+          <t>3.20</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
         <is>
-          <t>2.96</t>
+          <t>2.91</t>
         </is>
       </c>
       <c r="BU6" t="inlineStr">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="BV6" t="inlineStr">
         <is>
-          <t>26.41</t>
+          <t>26.88</t>
         </is>
       </c>
       <c r="BW6" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>29.63</t>
+          <t>30.23</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
         <is>
-          <t>34689</t>
+          <t>35306</t>
         </is>
       </c>
       <c r="CA6" t="inlineStr">
@@ -2986,22 +2986,22 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>136.5</t>
+          <t>139.5</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>139.5</t>
+          <t>141.0</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>135.0</t>
+          <t>138.0</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>138.5</t>
+          <t>139.0</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
@@ -3033,12 +3033,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>2.56</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1302.953</t>
+          <t>1721.237</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3048,7 +3048,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>135.0</t>
+          <t>138.5</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3058,17 +3058,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>3.91</t>
+          <t>3.15</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-1.3</t>
+          <t>-1.69</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>12.02</t>
+          <t>-13.08</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3133,7 +3133,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-43.04</t>
+          <t>-41.56</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3143,17 +3143,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>5.39</t>
+          <t>7.12</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>3.05</t>
+          <t>1.87</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3164,73 +3164,73 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>801</t>
+          <t>999</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>23.68</t>
+          <t>42.11</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>15.59</t>
+          <t>29.62</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>1.58</t>
+          <t>3.44</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>-9.76</t>
+          <t>-8.46</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>-8.05</t>
+          <t>-8.28</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>-6.11</t>
+          <t>-6.17</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>132.9</t>
+          <t>133.9</t>
         </is>
       </c>
       <c r="AM7" t="n">
-        <v>147.28</v>
+        <v>146.28</v>
       </c>
       <c r="AN7" t="n">
-        <v>160.17</v>
+        <v>159.48</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>170.59</t>
+          <t>169.96</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>-15.53</t>
+          <t>-7.31</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>-8.25</t>
+          <t>-7.81</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>-7.14</t>
+          <t>-7.28</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -3240,7 +3240,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-128.71</t>
+          <t>-129.24</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3250,43 +3250,43 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>1684514497.82311</t>
+          <t>1682419827.202991</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>173429988.0</t>
+          <t>236429825.0</t>
         </is>
       </c>
       <c r="AX7" t="n">
-        <v>305348589</v>
+        <v>243968869</v>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>272591978.0</t>
+          <t>280669574.0</t>
         </is>
       </c>
       <c r="AZ7" t="n">
-        <v>254388028.92</v>
+        <v>255272113.08</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>32756611</t>
+          <t>-36700705</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>8180445.224550578</t>
+          <t>7451433.159492791</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>6461370.136106104</t>
+          <t>3441866.801674962</t>
         </is>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
-          <t>173429988.0</t>
+          <t>236429825.0</t>
         </is>
       </c>
       <c r="BE7" t="inlineStr">
@@ -3306,7 +3306,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>-25.00</t>
+          <t>-23.06</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
@@ -3331,7 +3331,7 @@
       </c>
       <c r="BM7" t="inlineStr">
         <is>
-          <t>0.97</t>
+          <t>0.96</t>
         </is>
       </c>
       <c r="BN7" t="inlineStr">
@@ -3351,7 +3351,7 @@
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;可能出現反轉訊號&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;3&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
@@ -3361,12 +3361,12 @@
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>3.11</t>
+          <t>3.19</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
         <is>
-          <t>2.96</t>
+          <t>2.91</t>
         </is>
       </c>
       <c r="BU7" t="inlineStr">
@@ -3376,7 +3376,7 @@
       </c>
       <c r="BV7" t="inlineStr">
         <is>
-          <t>26.41</t>
+          <t>26.88</t>
         </is>
       </c>
       <c r="BW7" t="inlineStr">
@@ -3391,12 +3391,12 @@
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>29.63</t>
+          <t>30.23</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
         <is>
-          <t>34689</t>
+          <t>35306</t>
         </is>
       </c>
       <c r="CA7" t="inlineStr">
@@ -3416,22 +3416,22 @@
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>132.5</t>
+          <t>136.5</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
+          <t>139.5</t>
+        </is>
+      </c>
+      <c r="CF7" t="inlineStr">
+        <is>
           <t>135.0</t>
         </is>
       </c>
-      <c r="CF7" t="inlineStr">
-        <is>
-          <t>131.0</t>
-        </is>
-      </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>135.0</t>
+          <t>138.5</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
@@ -3463,12 +3463,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>3.41</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>1595.31</t>
+          <t>1302.953</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3488,17 +3488,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>3.91</t>
+          <t>5.59</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-1.3</t>
+          <t>-1.69</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>53.45</t>
+          <t>12.02</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3573,17 +3573,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>6.60</t>
+          <t>5.39</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>1.92</t>
+          <t>3.05</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3594,73 +3594,73 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>801</t>
+          <t>999</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>23.08</t>
+          <t>23.68</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>7.69</t>
+          <t>15.59</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>1.20</t>
+          <t>1.58</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>-10.06</t>
+          <t>-9.76</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>-7.84</t>
+          <t>-8.05</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>-6.04</t>
+          <t>-6.11</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>133.4</t>
+          <t>132.9</t>
         </is>
       </c>
       <c r="AM8" t="n">
-        <v>148.32</v>
+        <v>147.28</v>
       </c>
       <c r="AN8" t="n">
-        <v>160.95</v>
+        <v>160.17</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>171.29</t>
+          <t>170.59</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>-21.52</t>
+          <t>-15.53</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>-8.35</t>
+          <t>-8.25</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>-6.87</t>
+          <t>-7.14</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -3670,7 +3670,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-127.59</t>
+          <t>-128.71</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3680,43 +3680,43 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>1684514497.82311</t>
+          <t>1682419827.202991</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>212878160.0</t>
+          <t>173429988.0</t>
         </is>
       </c>
       <c r="AX8" t="n">
-        <v>421450515</v>
+        <v>305348589</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>274650710.4</t>
+          <t>272591978.0</t>
         </is>
       </c>
       <c r="AZ8" t="n">
-        <v>254522728.7</v>
+        <v>254388028.92</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>146799804</t>
+          <t>32756611</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>8493004.331540482</t>
+          <t>8180445.224550578</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>17294165.64471823</t>
+          <t>6461370.136106104</t>
         </is>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
-          <t>212878160.0</t>
+          <t>173429988.0</t>
         </is>
       </c>
       <c r="BE8" t="inlineStr">
@@ -3761,7 +3761,7 @@
       </c>
       <c r="BM8" t="inlineStr">
         <is>
-          <t>0.97</t>
+          <t>0.96</t>
         </is>
       </c>
       <c r="BN8" t="inlineStr">
@@ -3781,12 +3781,12 @@
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;可能出現反轉訊號&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;3&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS8" t="inlineStr">
@@ -3796,7 +3796,7 @@
       </c>
       <c r="BT8" t="inlineStr">
         <is>
-          <t>2.96</t>
+          <t>2.91</t>
         </is>
       </c>
       <c r="BU8" t="inlineStr">
@@ -3806,7 +3806,7 @@
       </c>
       <c r="BV8" t="inlineStr">
         <is>
-          <t>26.41</t>
+          <t>26.88</t>
         </is>
       </c>
       <c r="BW8" t="inlineStr">
@@ -3821,12 +3821,12 @@
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>29.63</t>
+          <t>30.23</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
         <is>
-          <t>34689</t>
+          <t>35306</t>
         </is>
       </c>
       <c r="CA8" t="inlineStr">
@@ -3846,17 +3846,17 @@
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>132.0</t>
+          <t>132.5</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>136.0</t>
+          <t>135.0</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>131.5</t>
+          <t>131.0</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
@@ -3893,12 +3893,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>3.41</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>1712.06</t>
+          <t>1595.31</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3908,7 +3908,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>130.5</t>
+          <t>135.0</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3918,17 +3918,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>7.12</t>
+          <t>5.59</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-1.3</t>
+          <t>-1.69</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>50.94</t>
+          <t>53.45</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3993,7 +3993,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-44.94</t>
+          <t>-43.04</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4003,17 +4003,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>7.08</t>
+          <t>6.60</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>-1.14</t>
+          <t>1.92</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4024,73 +4024,73 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>801</t>
+          <t>999</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>23.08</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>7.69</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>-4.26</t>
+          <t>1.20</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>-8.89</t>
+          <t>-10.06</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>-7.5</t>
+          <t>-7.84</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>-5.97</t>
+          <t>-6.04</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>136.3</t>
+          <t>133.4</t>
         </is>
       </c>
       <c r="AM9" t="n">
-        <v>149.6</v>
+        <v>148.32</v>
       </c>
       <c r="AN9" t="n">
-        <v>161.73</v>
+        <v>160.95</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>171.99</t>
+          <t>171.29</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>-28.35</t>
+          <t>-21.52</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>-8.34</t>
+          <t>-8.35</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>-6.50</t>
+          <t>-6.87</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -4100,7 +4100,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-126.11</t>
+          <t>-127.59</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4110,43 +4110,43 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>1684514497.82311</t>
+          <t>1682419827.202991</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>223746689.0</t>
+          <t>212878160.0</t>
         </is>
       </c>
       <c r="AX9" t="n">
-        <v>397436778.6</v>
+        <v>421450515</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>263301806.5</t>
+          <t>274650710.4</t>
         </is>
       </c>
       <c r="AZ9" t="n">
-        <v>254911229.58</v>
+        <v>254522728.7</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>134134972</t>
+          <t>146799804</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>6892793.183689982</t>
+          <t>8493004.331540482</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>27925349.16970986</t>
+          <t>17294165.64471823</t>
         </is>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
-          <t>223746689.0</t>
+          <t>212878160.0</t>
         </is>
       </c>
       <c r="BE9" t="inlineStr">
@@ -4166,7 +4166,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>-27.50</t>
+          <t>-25.00</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
@@ -4191,7 +4191,7 @@
       </c>
       <c r="BM9" t="inlineStr">
         <is>
-          <t>0.97</t>
+          <t>0.96</t>
         </is>
       </c>
       <c r="BN9" t="inlineStr">
@@ -4211,22 +4211,22 @@
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;可能出現反轉訊號&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;3&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
         <is>
-          <t>價漲量縮</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>3.01</t>
+          <t>3.11</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
         <is>
-          <t>2.96</t>
+          <t>2.91</t>
         </is>
       </c>
       <c r="BU9" t="inlineStr">
@@ -4236,7 +4236,7 @@
       </c>
       <c r="BV9" t="inlineStr">
         <is>
-          <t>26.41</t>
+          <t>26.88</t>
         </is>
       </c>
       <c r="BW9" t="inlineStr">
@@ -4251,12 +4251,12 @@
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>29.63</t>
+          <t>30.23</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
         <is>
-          <t>34689</t>
+          <t>35306</t>
         </is>
       </c>
       <c r="CA9" t="inlineStr">
@@ -4276,22 +4276,22 @@
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>131.0</t>
+          <t>132.0</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>133.5</t>
+          <t>136.0</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>129.0</t>
+          <t>131.5</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>130.5</t>
+          <t>135.0</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
@@ -4323,12 +4323,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>-2.26</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2844.986</t>
+          <t>1712.06</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4348,17 +4348,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>7.12</t>
+          <t>8.74</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-1.3</t>
+          <t>-1.69</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>48.25</t>
+          <t>50.94</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4433,17 +4433,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>11.77</t>
+          <t>7.08</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>-2.29</t>
+          <t>-1.14</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4454,12 +4454,12 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>801</t>
+          <t>999</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
@@ -4474,53 +4474,53 @@
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>-6.85</t>
+          <t>-4.26</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>-7.30</t>
+          <t>-8.89</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>-7.05</t>
+          <t>-7.5</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>-5.89</t>
+          <t>-5.97</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>140.1</t>
+          <t>136.3</t>
         </is>
       </c>
       <c r="AM10" t="n">
-        <v>151.12</v>
+        <v>149.6</v>
       </c>
       <c r="AN10" t="n">
-        <v>162.59</v>
+        <v>161.73</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>172.77</t>
+          <t>171.99</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>-28.43</t>
+          <t>-28.35</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>-7.75</t>
+          <t>-8.34</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>-6.04</t>
+          <t>-6.50</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -4530,7 +4530,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-124.26</t>
+          <t>-126.11</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4540,43 +4540,43 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>1684514497.82311</t>
+          <t>1682419827.202991</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>373359683.0</t>
+          <t>223746689.0</t>
         </is>
       </c>
       <c r="AX10" t="n">
-        <v>374444824.4</v>
+        <v>397436778.6</v>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>252575891.8</t>
+          <t>263301806.5</t>
         </is>
       </c>
       <c r="AZ10" t="n">
-        <v>255257682.72</v>
+        <v>254911229.58</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>121868932</t>
+          <t>134134972</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>3068692.09532273</t>
+          <t>6892793.183689982</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>40950935.056494</t>
+          <t>27925349.16970986</t>
         </is>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
-          <t>373359683.0</t>
+          <t>223746689.0</t>
         </is>
       </c>
       <c r="BE10" t="inlineStr">
@@ -4621,7 +4621,7 @@
       </c>
       <c r="BM10" t="inlineStr">
         <is>
-          <t>0.97</t>
+          <t>0.96</t>
         </is>
       </c>
       <c r="BN10" t="inlineStr">
@@ -4641,7 +4641,7 @@
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
@@ -4656,7 +4656,7 @@
       </c>
       <c r="BT10" t="inlineStr">
         <is>
-          <t>2.96</t>
+          <t>2.91</t>
         </is>
       </c>
       <c r="BU10" t="inlineStr">
@@ -4666,7 +4666,7 @@
       </c>
       <c r="BV10" t="inlineStr">
         <is>
-          <t>26.41</t>
+          <t>26.88</t>
         </is>
       </c>
       <c r="BW10" t="inlineStr">
@@ -4681,12 +4681,12 @@
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>29.63</t>
+          <t>30.23</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
         <is>
-          <t>34689</t>
+          <t>35306</t>
         </is>
       </c>
       <c r="CA10" t="inlineStr">
@@ -4706,17 +4706,17 @@
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>133.0</t>
+          <t>131.0</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>134.5</t>
+          <t>133.5</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>129.5</t>
+          <t>129.0</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
@@ -4753,12 +4753,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>-2.96</t>
+          <t>-2.26</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>4003.393</t>
+          <t>2844.986</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4768,7 +4768,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>133.5</t>
+          <t>130.5</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4778,17 +4778,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>4.98</t>
+          <t>8.74</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-1.3</t>
+          <t>-1.69</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>36.89</t>
+          <t>48.25</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4853,7 +4853,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-43.67</t>
+          <t>-44.94</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4863,17 +4863,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>16.56</t>
+          <t>11.77</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>-5.24</t>
+          <t>-2.29</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4884,12 +4884,12 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>801</t>
+          <t>999</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
@@ -4904,53 +4904,53 @@
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>-7.23</t>
+          <t>-6.85</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>-5.73</t>
+          <t>-7.30</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>-6.6</t>
+          <t>-7.05</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>-5.82</t>
+          <t>-5.89</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>143.9</t>
+          <t>140.1</t>
         </is>
       </c>
       <c r="AM11" t="n">
-        <v>152.65</v>
+        <v>151.12</v>
       </c>
       <c r="AN11" t="n">
-        <v>163.44</v>
+        <v>162.59</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>173.54</t>
+          <t>172.77</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>-22.90</t>
+          <t>-28.43</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>-6.89</t>
+          <t>-7.75</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>-5.61</t>
+          <t>-6.04</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -4960,7 +4960,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-122.53</t>
+          <t>-124.26</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -4970,43 +4970,43 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>1684514497.82311</t>
+          <t>1682419827.202991</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>543328425.0</t>
+          <t>373359683.0</t>
         </is>
       </c>
       <c r="AX11" t="n">
-        <v>317370279</v>
+        <v>374444824.4</v>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>231842549.9</t>
+          <t>252575891.8</t>
         </is>
       </c>
       <c r="AZ11" t="n">
-        <v>254515985.98</v>
+        <v>255257682.72</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>85527729</t>
+          <t>121868932</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>-3818988.443072045</t>
+          <t>3068692.09532273</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>42066417.85702515</t>
+          <t>40950935.056494</t>
         </is>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
-          <t>543328425.0</t>
+          <t>373359683.0</t>
         </is>
       </c>
       <c r="BE11" t="inlineStr">
@@ -5026,7 +5026,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>-25.83</t>
+          <t>-27.50</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
@@ -5051,7 +5051,7 @@
       </c>
       <c r="BM11" t="inlineStr">
         <is>
-          <t>0.97</t>
+          <t>0.96</t>
         </is>
       </c>
       <c r="BN11" t="inlineStr">
@@ -5071,7 +5071,7 @@
       </c>
       <c r="BQ11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;衝高回落,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR11" t="inlineStr">
@@ -5081,12 +5081,12 @@
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>3.08</t>
+          <t>3.01</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
         <is>
-          <t>2.96</t>
+          <t>2.91</t>
         </is>
       </c>
       <c r="BU11" t="inlineStr">
@@ -5096,7 +5096,7 @@
       </c>
       <c r="BV11" t="inlineStr">
         <is>
-          <t>26.41</t>
+          <t>26.88</t>
         </is>
       </c>
       <c r="BW11" t="inlineStr">
@@ -5111,12 +5111,12 @@
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>29.63</t>
+          <t>30.23</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
         <is>
-          <t>34689</t>
+          <t>35306</t>
         </is>
       </c>
       <c r="CA11" t="inlineStr">
@@ -5136,22 +5136,22 @@
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>135.0</t>
+          <t>133.0</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>141.5</t>
+          <t>134.5</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>132.5</t>
+          <t>129.5</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>133.5</t>
+          <t>130.5</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
@@ -5183,12 +5183,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>-8.16</t>
+          <t>-2.96</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>5388.546</t>
+          <t>4003.393</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5198,7 +5198,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>137.5</t>
+          <t>133.5</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5208,17 +5208,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>2.14</t>
+          <t>6.64</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-1.3</t>
+          <t>-1.69</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>18.56</t>
+          <t>36.89</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5283,7 +5283,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-41.98</t>
+          <t>-43.67</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5293,17 +5293,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>22.28</t>
+          <t>16.56</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>-5.06</t>
+          <t>-5.24</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5314,12 +5314,12 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>801</t>
+          <t>999</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
@@ -5334,53 +5334,53 @@
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>-6.59</t>
+          <t>-7.23</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>-4.57</t>
+          <t>-5.73</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>-6.11</t>
+          <t>-6.6</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>-5.70</t>
+          <t>-5.82</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>147.2</t>
+          <t>143.9</t>
         </is>
       </c>
       <c r="AM12" t="n">
-        <v>154.25</v>
+        <v>152.65</v>
       </c>
       <c r="AN12" t="n">
-        <v>164.29</v>
+        <v>163.44</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>174.21</t>
+          <t>173.54</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>-13.45</t>
+          <t>-22.90</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>-6.00</t>
+          <t>-6.89</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>-5.29</t>
+          <t>-5.61</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
@@ -5390,7 +5390,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-121.24</t>
+          <t>-122.53</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5400,43 +5400,43 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>1684514497.82311</t>
+          <t>1682419827.202991</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>753939618.0</t>
+          <t>543328425.0</t>
         </is>
       </c>
       <c r="AX12" t="n">
-        <v>239835367</v>
+        <v>317370279</v>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>202283159.5</t>
+          <t>231842549.9</t>
         </is>
       </c>
       <c r="AZ12" t="n">
-        <v>250790390.86</v>
+        <v>254515985.98</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>37552207</t>
+          <t>85527729</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>-12161789.58854426</t>
+          <t>-3818988.443072045</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>23946656.00574735</t>
+          <t>42066417.85702515</t>
         </is>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
-          <t>753939618.0</t>
+          <t>543328425.0</t>
         </is>
       </c>
       <c r="BE12" t="inlineStr">
@@ -5456,7 +5456,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>-23.61</t>
+          <t>-25.83</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
@@ -5481,7 +5481,7 @@
       </c>
       <c r="BM12" t="inlineStr">
         <is>
-          <t>0.97</t>
+          <t>0.96</t>
         </is>
       </c>
       <c r="BN12" t="inlineStr">
@@ -5501,7 +5501,7 @@
       </c>
       <c r="BQ12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;衝高回落,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR12" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>3.17</t>
+          <t>3.08</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
         <is>
-          <t>2.96</t>
+          <t>2.91</t>
         </is>
       </c>
       <c r="BU12" t="inlineStr">
@@ -5526,7 +5526,7 @@
       </c>
       <c r="BV12" t="inlineStr">
         <is>
-          <t>26.41</t>
+          <t>26.88</t>
         </is>
       </c>
       <c r="BW12" t="inlineStr">
@@ -5541,12 +5541,12 @@
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>29.63</t>
+          <t>30.23</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
         <is>
-          <t>34689</t>
+          <t>35306</t>
         </is>
       </c>
       <c r="CA12" t="inlineStr">
@@ -5566,22 +5566,22 @@
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>147.0</t>
+          <t>135.0</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>147.0</t>
+          <t>141.5</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>135.0</t>
+          <t>132.5</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
         <is>
-          <t>137.5</t>
+          <t>133.5</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">
@@ -5613,12 +5613,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>-0.51</t>
+          <t>-0.26</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>492.79</t>
+          <t>455.261</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -5628,7 +5628,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>38.9</t>
+          <t>38.8</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -5643,12 +5643,12 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>1.23</t>
+          <t>1.09</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>32.35</t>
+          <t>-47.41</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -5713,7 +5713,7 @@
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>-9.85</t>
+          <t>-10.08</t>
         </is>
       </c>
       <c r="X13" t="inlineStr">
@@ -5723,17 +5723,17 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>5.25</t>
+          <t>4.85</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>-0.12</t>
+          <t>-1.29</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
@@ -5744,73 +5744,73 @@
       <c r="AC13" t="inlineStr"/>
       <c r="AD13" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
-          <t>493</t>
+          <t>455</t>
         </is>
       </c>
       <c r="AF13" t="inlineStr">
         <is>
-          <t>93.33</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="AG13" t="inlineStr">
         <is>
-          <t>97.78</t>
+          <t>94.44</t>
         </is>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>1.25</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>1.10</t>
+          <t>2.16</t>
         </is>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>-4.8</t>
+          <t>-4.72</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>-3.07</t>
+          <t>-3.16</t>
         </is>
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>38.42</t>
+          <t>38.8</t>
         </is>
       </c>
       <c r="AM13" t="n">
-        <v>38</v>
+        <v>37.98</v>
       </c>
       <c r="AN13" t="n">
-        <v>39.92</v>
+        <v>39.86</v>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>41.18</t>
+          <t>41.16</t>
         </is>
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>41.20</t>
+          <t>47.01</t>
         </is>
       </c>
       <c r="AQ13" t="inlineStr">
         <is>
-          <t>-0.47</t>
+          <t>-0.38</t>
         </is>
       </c>
       <c r="AR13" t="inlineStr">
         <is>
-          <t>-0.79</t>
+          <t>-0.71</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr">
@@ -5820,7 +5820,7 @@
       </c>
       <c r="AT13" t="inlineStr">
         <is>
-          <t>-129.55</t>
+          <t>-126.44</t>
         </is>
       </c>
       <c r="AU13" t="inlineStr">
@@ -5830,43 +5830,43 @@
       </c>
       <c r="AV13" t="inlineStr">
         <is>
-          <t>150078431.9122682</t>
+          <t>149902651.9038461</t>
         </is>
       </c>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>19156578.0</t>
+          <t>17787244.0</t>
         </is>
       </c>
       <c r="AX13" t="n">
-        <v>69426442.8</v>
+        <v>26453801.8</v>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>52456837.4</t>
+          <t>50298085.9</t>
         </is>
       </c>
       <c r="AZ13" t="n">
-        <v>33433682.52</v>
+        <v>33264214.78</v>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
-          <t>16969605</t>
+          <t>-23844284</t>
         </is>
       </c>
       <c r="BB13" t="inlineStr">
         <is>
-          <t>4345764.102201018</t>
+          <t>3457425.925196137</t>
         </is>
       </c>
       <c r="BC13" t="inlineStr">
         <is>
-          <t>800558.8333693519</t>
+          <t>-1428434.048330702</t>
         </is>
       </c>
       <c r="BD13" t="inlineStr">
         <is>
-          <t>19156578.0</t>
+          <t>17787244.0</t>
         </is>
       </c>
       <c r="BE13" t="inlineStr">
@@ -5886,7 +5886,7 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>-6.27</t>
+          <t>-6.51</t>
         </is>
       </c>
       <c r="BI13" t="inlineStr">
@@ -5931,7 +5931,7 @@
       </c>
       <c r="BQ13" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR13" t="inlineStr">
@@ -5946,7 +5946,7 @@
       </c>
       <c r="BT13" t="inlineStr">
         <is>
-          <t>6.43</t>
+          <t>6.44</t>
         </is>
       </c>
       <c r="BU13" t="inlineStr">
@@ -5956,7 +5956,7 @@
       </c>
       <c r="BV13" t="inlineStr">
         <is>
-          <t>16.07</t>
+          <t>16.03</t>
         </is>
       </c>
       <c r="BW13" t="inlineStr">
@@ -5971,12 +5971,12 @@
       </c>
       <c r="BY13" t="inlineStr">
         <is>
-          <t>29.63</t>
+          <t>30.23</t>
         </is>
       </c>
       <c r="BZ13" t="inlineStr">
         <is>
-          <t>12493</t>
+          <t>12460</t>
         </is>
       </c>
       <c r="CA13" t="inlineStr">
@@ -5996,12 +5996,12 @@
       </c>
       <c r="CD13" t="inlineStr">
         <is>
-          <t>39.1</t>
+          <t>38.6</t>
         </is>
       </c>
       <c r="CE13" t="inlineStr">
         <is>
-          <t>39.25</t>
+          <t>39.5</t>
         </is>
       </c>
       <c r="CF13" t="inlineStr">
@@ -6011,7 +6011,7 @@
       </c>
       <c r="CG13" t="inlineStr">
         <is>
-          <t>38.9</t>
+          <t>38.8</t>
         </is>
       </c>
       <c r="CH13" t="inlineStr">
@@ -6043,12 +6043,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-0.51</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>510.601</t>
+          <t>492.79</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -6058,7 +6058,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>39.1</t>
+          <t>38.9</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -6068,17 +6068,17 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>-0.51</t>
+          <t>-0.26</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>1.23</t>
+          <t>1.09</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>32.21</t>
+          <t>32.35</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -6143,7 +6143,7 @@
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>-9.39</t>
+          <t>-9.85</t>
         </is>
       </c>
       <c r="X14" t="inlineStr">
@@ -6153,17 +6153,17 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>5.44</t>
+          <t>5.25</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>0.39</t>
+          <t>-0.12</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
@@ -6174,73 +6174,73 @@
       <c r="AC14" t="inlineStr"/>
       <c r="AD14" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
-          <t>493</t>
+          <t>455</t>
         </is>
       </c>
       <c r="AF14" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>93.33</t>
         </is>
       </c>
       <c r="AG14" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>97.78</t>
         </is>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>2.87</t>
+          <t>1.25</t>
         </is>
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>-0.09</t>
+          <t>1.10</t>
         </is>
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>-4.82</t>
+          <t>-4.8</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>-2.98</t>
+          <t>-3.07</t>
         </is>
       </c>
       <c r="AL14" t="inlineStr">
         <is>
-          <t>38.01000000000001</t>
+          <t>38.42</t>
         </is>
       </c>
       <c r="AM14" t="n">
-        <v>38.04</v>
+        <v>38</v>
       </c>
       <c r="AN14" t="n">
-        <v>39.97</v>
+        <v>39.92</v>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>41.2</t>
+          <t>41.18</t>
         </is>
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>33.12</t>
+          <t>41.20</t>
         </is>
       </c>
       <c r="AQ14" t="inlineStr">
         <is>
-          <t>-0.59</t>
+          <t>-0.47</t>
         </is>
       </c>
       <c r="AR14" t="inlineStr">
         <is>
-          <t>-0.88</t>
+          <t>-0.79</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr">
@@ -6250,7 +6250,7 @@
       </c>
       <c r="AT14" t="inlineStr">
         <is>
-          <t>-132.60</t>
+          <t>-129.55</t>
         </is>
       </c>
       <c r="AU14" t="inlineStr">
@@ -6260,43 +6260,43 @@
       </c>
       <c r="AV14" t="inlineStr">
         <is>
-          <t>150078431.9122682</t>
+          <t>149902651.9038461</t>
         </is>
       </c>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>19953309.0</t>
+          <t>19156578.0</t>
         </is>
       </c>
       <c r="AX14" t="n">
-        <v>73854919.59999999</v>
+        <v>69426442.8</v>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
-          <t>55863021.8</t>
+          <t>52456837.4</t>
         </is>
       </c>
       <c r="AZ14" t="n">
-        <v>33328621.84</v>
+        <v>33433682.52</v>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
-          <t>17991897</t>
+          <t>16969605</t>
         </is>
       </c>
       <c r="BB14" t="inlineStr">
         <is>
-          <t>4990346.878352229</t>
+          <t>4345764.102201018</t>
         </is>
       </c>
       <c r="BC14" t="inlineStr">
         <is>
-          <t>3809528.634606227</t>
+          <t>800558.8333693519</t>
         </is>
       </c>
       <c r="BD14" t="inlineStr">
         <is>
-          <t>19953309.0</t>
+          <t>19156578.0</t>
         </is>
       </c>
       <c r="BE14" t="inlineStr">
@@ -6316,7 +6316,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>-5.78</t>
+          <t>-6.27</t>
         </is>
       </c>
       <c r="BI14" t="inlineStr">
@@ -6361,22 +6361,22 @@
       </c>
       <c r="BQ14" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR14" t="inlineStr">
         <is>
-          <t>價-量縮</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS14" t="inlineStr">
         <is>
-          <t>1.08</t>
+          <t>1.07</t>
         </is>
       </c>
       <c r="BT14" t="inlineStr">
         <is>
-          <t>6.43</t>
+          <t>6.44</t>
         </is>
       </c>
       <c r="BU14" t="inlineStr">
@@ -6386,7 +6386,7 @@
       </c>
       <c r="BV14" t="inlineStr">
         <is>
-          <t>16.07</t>
+          <t>16.03</t>
         </is>
       </c>
       <c r="BW14" t="inlineStr">
@@ -6401,12 +6401,12 @@
       </c>
       <c r="BY14" t="inlineStr">
         <is>
-          <t>29.63</t>
+          <t>30.23</t>
         </is>
       </c>
       <c r="BZ14" t="inlineStr">
         <is>
-          <t>12493</t>
+          <t>12460</t>
         </is>
       </c>
       <c r="CA14" t="inlineStr">
@@ -6426,22 +6426,22 @@
       </c>
       <c r="CD14" t="inlineStr">
         <is>
-          <t>39.15</t>
+          <t>39.1</t>
         </is>
       </c>
       <c r="CE14" t="inlineStr">
         <is>
-          <t>39.3</t>
+          <t>39.25</t>
         </is>
       </c>
       <c r="CF14" t="inlineStr">
         <is>
-          <t>38.75</t>
+          <t>38.6</t>
         </is>
       </c>
       <c r="CG14" t="inlineStr">
         <is>
-          <t>39.1</t>
+          <t>38.9</t>
         </is>
       </c>
       <c r="CH14" t="inlineStr">
@@ -6473,12 +6473,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>2.61</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>914.803</t>
+          <t>510.601</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -6498,17 +6498,17 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>-0.51</t>
+          <t>-0.77</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>1.23</t>
+          <t>1.09</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>35.32</t>
+          <t>32.21</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -6583,17 +6583,17 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>9.75</t>
+          <t>5.44</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>1.47</t>
+          <t>0.39</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
@@ -6604,12 +6604,12 @@
       <c r="AC15" t="inlineStr"/>
       <c r="AD15" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
-          <t>493</t>
+          <t>455</t>
         </is>
       </c>
       <c r="AF15" t="inlineStr">
@@ -6619,58 +6619,58 @@
       </c>
       <c r="AG15" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>4.35</t>
+          <t>2.87</t>
         </is>
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>-1.59</t>
+          <t>-0.09</t>
         </is>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>-4.88</t>
+          <t>-4.82</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>-2.87</t>
+          <t>-2.98</t>
         </is>
       </c>
       <c r="AL15" t="inlineStr">
         <is>
-          <t>37.47</t>
+          <t>38.01000000000001</t>
         </is>
       </c>
       <c r="AM15" t="n">
-        <v>38.08</v>
+        <v>38.04</v>
       </c>
       <c r="AN15" t="n">
-        <v>40.03</v>
+        <v>39.97</v>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>41.21</t>
+          <t>41.2</t>
         </is>
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>20.99</t>
+          <t>33.12</t>
         </is>
       </c>
       <c r="AQ15" t="inlineStr">
         <is>
-          <t>-0.75</t>
+          <t>-0.59</t>
         </is>
       </c>
       <c r="AR15" t="inlineStr">
         <is>
-          <t>-0.95</t>
+          <t>-0.88</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr">
@@ -6680,7 +6680,7 @@
       </c>
       <c r="AT15" t="inlineStr">
         <is>
-          <t>-135.29</t>
+          <t>-132.60</t>
         </is>
       </c>
       <c r="AU15" t="inlineStr">
@@ -6690,43 +6690,43 @@
       </c>
       <c r="AV15" t="inlineStr">
         <is>
-          <t>150078431.9122682</t>
+          <t>149902651.9038461</t>
         </is>
       </c>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>35810040.0</t>
+          <t>19953309.0</t>
         </is>
       </c>
       <c r="AX15" t="n">
-        <v>75499582.59999999</v>
+        <v>73854919.59999999</v>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>55792550.2</t>
+          <t>55863021.8</t>
         </is>
       </c>
       <c r="AZ15" t="n">
-        <v>33454972.78</v>
+        <v>33328621.84</v>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
-          <t>19707032</t>
+          <t>17991897</t>
         </is>
       </c>
       <c r="BB15" t="inlineStr">
         <is>
-          <t>5205041.104487866</t>
+          <t>4990346.878352229</t>
         </is>
       </c>
       <c r="BC15" t="inlineStr">
         <is>
-          <t>7886638.29228013</t>
+          <t>3809528.634606227</t>
         </is>
       </c>
       <c r="BD15" t="inlineStr">
         <is>
-          <t>35810040.0</t>
+          <t>19953309.0</t>
         </is>
       </c>
       <c r="BE15" t="inlineStr">
@@ -6791,12 +6791,12 @@
       </c>
       <c r="BQ15" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR15" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量縮</t>
         </is>
       </c>
       <c r="BS15" t="inlineStr">
@@ -6806,7 +6806,7 @@
       </c>
       <c r="BT15" t="inlineStr">
         <is>
-          <t>6.43</t>
+          <t>6.44</t>
         </is>
       </c>
       <c r="BU15" t="inlineStr">
@@ -6816,7 +6816,7 @@
       </c>
       <c r="BV15" t="inlineStr">
         <is>
-          <t>16.07</t>
+          <t>16.03</t>
         </is>
       </c>
       <c r="BW15" t="inlineStr">
@@ -6831,12 +6831,12 @@
       </c>
       <c r="BY15" t="inlineStr">
         <is>
-          <t>29.63</t>
+          <t>30.23</t>
         </is>
       </c>
       <c r="BZ15" t="inlineStr">
         <is>
-          <t>12493</t>
+          <t>12460</t>
         </is>
       </c>
       <c r="CA15" t="inlineStr">
@@ -6856,17 +6856,17 @@
       </c>
       <c r="CD15" t="inlineStr">
         <is>
-          <t>38.3</t>
+          <t>39.15</t>
         </is>
       </c>
       <c r="CE15" t="inlineStr">
         <is>
-          <t>39.5</t>
+          <t>39.3</t>
         </is>
       </c>
       <c r="CF15" t="inlineStr">
         <is>
-          <t>38.15</t>
+          <t>38.75</t>
         </is>
       </c>
       <c r="CG15" t="inlineStr">
@@ -6903,12 +6903,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>3.24</t>
+          <t>2.61</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>1043.085</t>
+          <t>914.803</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -6918,7 +6918,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>38.1</t>
+          <t>39.1</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -6928,17 +6928,17 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>2.06</t>
+          <t>-0.77</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>1.23</t>
+          <t>1.09</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>41.43</t>
+          <t>35.32</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -7003,7 +7003,7 @@
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>-11.70</t>
+          <t>-9.39</t>
         </is>
       </c>
       <c r="X16" t="inlineStr">
@@ -7013,17 +7013,17 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>11.11</t>
+          <t>9.75</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2.71</t>
+          <t>1.47</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
@@ -7034,12 +7034,12 @@
       <c r="AC16" t="inlineStr"/>
       <c r="AD16" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
-          <t>493</t>
+          <t>455</t>
         </is>
       </c>
       <c r="AF16" t="inlineStr">
@@ -7049,60 +7049,60 @@
       </c>
       <c r="AG16" t="inlineStr">
         <is>
-          <t>59.17</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>3.34</t>
+          <t>4.35</t>
         </is>
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>-3.27</t>
+          <t>-1.59</t>
         </is>
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>-4.89</t>
+          <t>-4.88</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>-2.80</t>
+          <t>-2.87</t>
         </is>
       </c>
       <c r="AL16" t="inlineStr">
         <is>
-          <t>36.87</t>
+          <t>37.47</t>
         </is>
       </c>
       <c r="AM16" t="n">
-        <v>38.11</v>
+        <v>38.08</v>
       </c>
       <c r="AN16" t="n">
-        <v>40.07</v>
+        <v>40.03</v>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>41.23</t>
+          <t>41.21</t>
         </is>
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>5.10</t>
+          <t>20.99</t>
         </is>
       </c>
       <c r="AQ16" t="inlineStr">
         <is>
+          <t>-0.75</t>
+        </is>
+      </c>
+      <c r="AR16" t="inlineStr">
+        <is>
           <t>-0.95</t>
         </is>
       </c>
-      <c r="AR16" t="inlineStr">
-        <is>
-          <t>-1.00</t>
-        </is>
-      </c>
       <c r="AS16" t="inlineStr">
         <is>
           <t>2.69</t>
@@ -7110,7 +7110,7 @@
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>-137.15</t>
+          <t>-135.29</t>
         </is>
       </c>
       <c r="AU16" t="inlineStr">
@@ -7120,43 +7120,43 @@
       </c>
       <c r="AV16" t="inlineStr">
         <is>
-          <t>150078431.9122682</t>
+          <t>149902651.9038461</t>
         </is>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>39561838.0</t>
+          <t>35810040.0</t>
         </is>
       </c>
       <c r="AX16" t="n">
-        <v>77102277.8</v>
+        <v>75499582.59999999</v>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>54515793.2</t>
+          <t>55792550.2</t>
         </is>
       </c>
       <c r="AZ16" t="n">
-        <v>33864219.92</v>
+        <v>33454972.78</v>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
-          <t>22586484</t>
+          <t>19707032</t>
         </is>
       </c>
       <c r="BB16" t="inlineStr">
         <is>
-          <t>4717477.979434728</t>
+          <t>5205041.104487866</t>
         </is>
       </c>
       <c r="BC16" t="inlineStr">
         <is>
-          <t>11730479.54280426</t>
+          <t>7886638.29228013</t>
         </is>
       </c>
       <c r="BD16" t="inlineStr">
         <is>
-          <t>39561838.0</t>
+          <t>35810040.0</t>
         </is>
       </c>
       <c r="BE16" t="inlineStr">
@@ -7176,7 +7176,7 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>-8.19</t>
+          <t>-5.78</t>
         </is>
       </c>
       <c r="BI16" t="inlineStr">
@@ -7221,22 +7221,22 @@
       </c>
       <c r="BQ16" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR16" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS16" t="inlineStr">
         <is>
-          <t>1.05</t>
+          <t>1.08</t>
         </is>
       </c>
       <c r="BT16" t="inlineStr">
         <is>
-          <t>6.43</t>
+          <t>6.44</t>
         </is>
       </c>
       <c r="BU16" t="inlineStr">
@@ -7246,7 +7246,7 @@
       </c>
       <c r="BV16" t="inlineStr">
         <is>
-          <t>16.07</t>
+          <t>16.03</t>
         </is>
       </c>
       <c r="BW16" t="inlineStr">
@@ -7261,12 +7261,12 @@
       </c>
       <c r="BY16" t="inlineStr">
         <is>
-          <t>29.63</t>
+          <t>30.23</t>
         </is>
       </c>
       <c r="BZ16" t="inlineStr">
         <is>
-          <t>12493</t>
+          <t>12460</t>
         </is>
       </c>
       <c r="CA16" t="inlineStr">
@@ -7286,22 +7286,22 @@
       </c>
       <c r="CD16" t="inlineStr">
         <is>
-          <t>37.05</t>
+          <t>38.3</t>
         </is>
       </c>
       <c r="CE16" t="inlineStr">
         <is>
-          <t>38.2</t>
+          <t>39.5</t>
         </is>
       </c>
       <c r="CF16" t="inlineStr">
         <is>
-          <t>37.0</t>
+          <t>38.15</t>
         </is>
       </c>
       <c r="CG16" t="inlineStr">
         <is>
-          <t>38.1</t>
+          <t>39.1</t>
         </is>
       </c>
       <c r="CH16" t="inlineStr">
@@ -7323,7 +7323,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>【e】</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -7333,12 +7333,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>0.14</t>
+          <t>3.24</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>6301.223</t>
+          <t>1043.085</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -7348,7 +7348,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>36.9</t>
+          <t>38.1</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -7358,17 +7358,17 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>5.14</t>
+          <t>1.8</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>1.23</t>
+          <t>1.09</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>29.52</t>
+          <t>41.43</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -7433,7 +7433,7 @@
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>-14.48</t>
+          <t>-11.70</t>
         </is>
       </c>
       <c r="X17" t="inlineStr">
@@ -7443,17 +7443,17 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>67.14</t>
+          <t>11.11</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>-1.63</t>
+          <t>2.71</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
@@ -7464,73 +7464,73 @@
       <c r="AC17" t="inlineStr"/>
       <c r="AD17" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
-          <t>493</t>
+          <t>455</t>
         </is>
       </c>
       <c r="AF17" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG17" t="inlineStr">
         <is>
-          <t>29.75</t>
+          <t>59.17</t>
         </is>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>0.82</t>
+          <t>3.34</t>
         </is>
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>-4.24</t>
+          <t>-3.27</t>
         </is>
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>-4.85</t>
+          <t>-4.89</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>-2.68</t>
+          <t>-2.80</t>
         </is>
       </c>
       <c r="AL17" t="inlineStr">
         <is>
-          <t>36.60000000000001</t>
+          <t>36.87</t>
         </is>
       </c>
       <c r="AM17" t="n">
-        <v>38.22</v>
+        <v>38.11</v>
       </c>
       <c r="AN17" t="n">
-        <v>40.17</v>
+        <v>40.07</v>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>41.28</t>
+          <t>41.23</t>
         </is>
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>-7.24</t>
+          <t>5.10</t>
         </is>
       </c>
       <c r="AQ17" t="inlineStr">
         <is>
-          <t>-1.08</t>
+          <t>-0.95</t>
         </is>
       </c>
       <c r="AR17" t="inlineStr">
         <is>
-          <t>-1.01</t>
+          <t>-1.00</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr">
@@ -7540,7 +7540,7 @@
       </c>
       <c r="AT17" t="inlineStr">
         <is>
-          <t>-137.62</t>
+          <t>-137.15</t>
         </is>
       </c>
       <c r="AU17" t="inlineStr">
@@ -7550,43 +7550,43 @@
       </c>
       <c r="AV17" t="inlineStr">
         <is>
-          <t>150078431.9122682</t>
+          <t>149902651.9038461</t>
         </is>
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>232650449.0</t>
+          <t>39561838.0</t>
         </is>
       </c>
       <c r="AX17" t="n">
-        <v>74142370</v>
+        <v>77102277.8</v>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>57245793.0</t>
+          <t>54515793.2</t>
         </is>
       </c>
       <c r="AZ17" t="n">
-        <v>34130931.06</v>
+        <v>33864219.92</v>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
-          <t>16896577</t>
+          <t>22586484</t>
         </is>
       </c>
       <c r="BB17" t="inlineStr">
         <is>
-          <t>3442386.786094812</t>
+          <t>4717477.979434728</t>
         </is>
       </c>
       <c r="BC17" t="inlineStr">
         <is>
-          <t>16400757.27416717</t>
+          <t>11730479.54280426</t>
         </is>
       </c>
       <c r="BD17" t="inlineStr">
         <is>
-          <t>232650449.0</t>
+          <t>39561838.0</t>
         </is>
       </c>
       <c r="BE17" t="inlineStr">
@@ -7606,7 +7606,7 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>-11.08</t>
+          <t>-8.19</t>
         </is>
       </c>
       <c r="BI17" t="inlineStr">
@@ -7651,7 +7651,7 @@
       </c>
       <c r="BQ17" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR17" t="inlineStr">
@@ -7661,12 +7661,12 @@
       </c>
       <c r="BS17" t="inlineStr">
         <is>
-          <t>1.02</t>
+          <t>1.05</t>
         </is>
       </c>
       <c r="BT17" t="inlineStr">
         <is>
-          <t>6.43</t>
+          <t>6.44</t>
         </is>
       </c>
       <c r="BU17" t="inlineStr">
@@ -7676,7 +7676,7 @@
       </c>
       <c r="BV17" t="inlineStr">
         <is>
-          <t>16.07</t>
+          <t>16.03</t>
         </is>
       </c>
       <c r="BW17" t="inlineStr">
@@ -7691,12 +7691,12 @@
       </c>
       <c r="BY17" t="inlineStr">
         <is>
-          <t>29.63</t>
+          <t>30.23</t>
         </is>
       </c>
       <c r="BZ17" t="inlineStr">
         <is>
-          <t>12493</t>
+          <t>12460</t>
         </is>
       </c>
       <c r="CA17" t="inlineStr">
@@ -7716,22 +7716,22 @@
       </c>
       <c r="CD17" t="inlineStr">
         <is>
+          <t>37.05</t>
+        </is>
+      </c>
+      <c r="CE17" t="inlineStr">
+        <is>
+          <t>38.2</t>
+        </is>
+      </c>
+      <c r="CF17" t="inlineStr">
+        <is>
           <t>37.0</t>
         </is>
       </c>
-      <c r="CE17" t="inlineStr">
-        <is>
-          <t>37.5</t>
-        </is>
-      </c>
-      <c r="CF17" t="inlineStr">
-        <is>
-          <t>36.9</t>
-        </is>
-      </c>
       <c r="CG17" t="inlineStr">
         <is>
-          <t>36.9</t>
+          <t>38.1</t>
         </is>
       </c>
       <c r="CH17" t="inlineStr">
@@ -7763,12 +7763,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>1.24</t>
+          <t>0.14</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>1128.761</t>
+          <t>6301.223</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -7778,7 +7778,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>36.85</t>
+          <t>36.9</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -7788,17 +7788,17 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>5.27</t>
+          <t>4.9</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>1.23</t>
+          <t>1.09</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>-1.19</t>
+          <t>29.52</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -7863,7 +7863,7 @@
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>-14.60</t>
+          <t>-14.48</t>
         </is>
       </c>
       <c r="X18" t="inlineStr">
@@ -7873,17 +7873,17 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>12.03</t>
+          <t>67.14</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2.09</t>
+          <t>-1.63</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
@@ -7894,274 +7894,274 @@
       <c r="AC18" t="inlineStr"/>
       <c r="AD18" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
-          <t>493</t>
+          <t>455</t>
         </is>
       </c>
       <c r="AF18" t="inlineStr">
         <is>
+          <t>40.0</t>
+        </is>
+      </c>
+      <c r="AG18" t="inlineStr">
+        <is>
+          <t>29.75</t>
+        </is>
+      </c>
+      <c r="AH18" t="inlineStr">
+        <is>
+          <t>0.82</t>
+        </is>
+      </c>
+      <c r="AI18" t="inlineStr">
+        <is>
+          <t>-4.24</t>
+        </is>
+      </c>
+      <c r="AJ18" t="inlineStr">
+        <is>
+          <t>-4.85</t>
+        </is>
+      </c>
+      <c r="AK18" t="inlineStr">
+        <is>
+          <t>-2.68</t>
+        </is>
+      </c>
+      <c r="AL18" t="inlineStr">
+        <is>
+          <t>36.60000000000001</t>
+        </is>
+      </c>
+      <c r="AM18" t="n">
+        <v>38.22</v>
+      </c>
+      <c r="AN18" t="n">
+        <v>40.17</v>
+      </c>
+      <c r="AO18" t="inlineStr">
+        <is>
+          <t>41.28</t>
+        </is>
+      </c>
+      <c r="AP18" t="inlineStr">
+        <is>
+          <t>-7.24</t>
+        </is>
+      </c>
+      <c r="AQ18" t="inlineStr">
+        <is>
+          <t>-1.08</t>
+        </is>
+      </c>
+      <c r="AR18" t="inlineStr">
+        <is>
+          <t>-1.01</t>
+        </is>
+      </c>
+      <c r="AS18" t="inlineStr">
+        <is>
+          <t>2.69</t>
+        </is>
+      </c>
+      <c r="AT18" t="inlineStr">
+        <is>
+          <t>-137.62</t>
+        </is>
+      </c>
+      <c r="AU18" t="inlineStr">
+        <is>
+          <t>2025/11/25</t>
+        </is>
+      </c>
+      <c r="AV18" t="inlineStr">
+        <is>
+          <t>149902651.9038461</t>
+        </is>
+      </c>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>232650449.0</t>
+        </is>
+      </c>
+      <c r="AX18" t="n">
+        <v>74142370</v>
+      </c>
+      <c r="AY18" t="inlineStr">
+        <is>
+          <t>57245793.0</t>
+        </is>
+      </c>
+      <c r="AZ18" t="n">
+        <v>34130931.06</v>
+      </c>
+      <c r="BA18" t="inlineStr">
+        <is>
+          <t>16896577</t>
+        </is>
+      </c>
+      <c r="BB18" t="inlineStr">
+        <is>
+          <t>3442386.786094812</t>
+        </is>
+      </c>
+      <c r="BC18" t="inlineStr">
+        <is>
+          <t>16400757.27416717</t>
+        </is>
+      </c>
+      <c r="BD18" t="inlineStr">
+        <is>
+          <t>232650449.0</t>
+        </is>
+      </c>
+      <c r="BE18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF18" t="inlineStr">
+        <is>
+          <t>41.5</t>
+        </is>
+      </c>
+      <c r="BG18" t="inlineStr">
+        <is>
+          <t>2025/08/07</t>
+        </is>
+      </c>
+      <c r="BH18" t="inlineStr">
+        <is>
+          <t>-11.08</t>
+        </is>
+      </c>
+      <c r="BI18" t="inlineStr">
+        <is>
+          <t>新光鋼</t>
+        </is>
+      </c>
+      <c r="BJ18" t="inlineStr">
+        <is>
+          <t>新光鋼</t>
+        </is>
+      </c>
+      <c r="BK18" t="inlineStr">
+        <is>
+          <t>鋼鐵工業</t>
+        </is>
+      </c>
+      <c r="BL18" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="BM18" t="inlineStr">
+        <is>
+          <t>0.62</t>
+        </is>
+      </c>
+      <c r="BN18" t="inlineStr">
+        <is>
+          <t>-13.67996844119094</t>
+        </is>
+      </c>
+      <c r="BO18" t="inlineStr">
+        <is>
+          <t>-10.11024290164889</t>
+        </is>
+      </c>
+      <c r="BP18" t="inlineStr">
+        <is>
+          <t>24.12947661306339</t>
+        </is>
+      </c>
+      <c r="BQ18" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BR18" t="inlineStr">
+        <is>
+          <t>價-量增</t>
+        </is>
+      </c>
+      <c r="BS18" t="inlineStr">
+        <is>
+          <t>1.02</t>
+        </is>
+      </c>
+      <c r="BT18" t="inlineStr">
+        <is>
+          <t>6.44</t>
+        </is>
+      </c>
+      <c r="BU18" t="inlineStr">
+        <is>
+          <t>11.90</t>
+        </is>
+      </c>
+      <c r="BV18" t="inlineStr">
+        <is>
+          <t>16.03</t>
+        </is>
+      </c>
+      <c r="BW18" t="inlineStr">
+        <is>
+          <t>8.69%</t>
+        </is>
+      </c>
+      <c r="BX18" t="inlineStr">
+        <is>
+          <t>5.19%</t>
+        </is>
+      </c>
+      <c r="BY18" t="inlineStr">
+        <is>
+          <t>30.23</t>
+        </is>
+      </c>
+      <c r="BZ18" t="inlineStr">
+        <is>
+          <t>12460</t>
+        </is>
+      </c>
+      <c r="CA18" t="inlineStr">
+        <is>
+          <t>鋼板38.80%、熱軋及鍍鋅鋼板33.80%、不�袗�板12.60%、特殊鋼板7.00%、加工及其他6.90%、型鋼0.90% (2024年)</t>
+        </is>
+      </c>
+      <c r="CB18" t="inlineStr">
+        <is>
+          <t>新光鋼-鋼鐵工業-上市</t>
+        </is>
+      </c>
+      <c r="CC18" t="inlineStr">
+        <is>
+          <t>鋼鐵工業右下上市</t>
+        </is>
+      </c>
+      <c r="CD18" t="inlineStr">
+        <is>
+          <t>37.0</t>
+        </is>
+      </c>
+      <c r="CE18" t="inlineStr">
+        <is>
           <t>37.5</t>
         </is>
       </c>
-      <c r="AG18" t="inlineStr">
-        <is>
-          <t>16.42</t>
-        </is>
-      </c>
-      <c r="AH18" t="inlineStr">
-        <is>
-          <t>0.66</t>
-        </is>
-      </c>
-      <c r="AI18" t="inlineStr">
-        <is>
-          <t>-4.68</t>
-        </is>
-      </c>
-      <c r="AJ18" t="inlineStr">
-        <is>
-          <t>-4.69</t>
-        </is>
-      </c>
-      <c r="AK18" t="inlineStr">
-        <is>
-          <t>-2.48</t>
-        </is>
-      </c>
-      <c r="AL18" t="inlineStr">
-        <is>
-          <t>36.61</t>
-        </is>
-      </c>
-      <c r="AM18" t="n">
-        <v>38.41</v>
-      </c>
-      <c r="AN18" t="n">
-        <v>40.3</v>
-      </c>
-      <c r="AO18" t="inlineStr">
-        <is>
-          <t>41.32</t>
-        </is>
-      </c>
-      <c r="AP18" t="inlineStr">
-        <is>
-          <t>-12.91</t>
-        </is>
-      </c>
-      <c r="AQ18" t="inlineStr">
-        <is>
-          <t>-1.12</t>
-        </is>
-      </c>
-      <c r="AR18" t="inlineStr">
-        <is>
-          <t>-0.99</t>
-        </is>
-      </c>
-      <c r="AS18" t="inlineStr">
-        <is>
-          <t>2.69</t>
-        </is>
-      </c>
-      <c r="AT18" t="inlineStr">
-        <is>
-          <t>-136.94</t>
-        </is>
-      </c>
-      <c r="AU18" t="inlineStr">
-        <is>
-          <t>2025/11/25</t>
-        </is>
-      </c>
-      <c r="AV18" t="inlineStr">
-        <is>
-          <t>150078431.9122682</t>
-        </is>
-      </c>
-      <c r="AW18" t="inlineStr">
-        <is>
-          <t>41298962.0</t>
-        </is>
-      </c>
-      <c r="AX18" t="n">
-        <v>35487232</v>
-      </c>
-      <c r="AY18" t="inlineStr">
-        <is>
-          <t>35914543.8</t>
-        </is>
-      </c>
-      <c r="AZ18" t="n">
-        <v>29950115.64</v>
-      </c>
-      <c r="BA18" t="inlineStr">
-        <is>
-          <t>-427311</t>
-        </is>
-      </c>
-      <c r="BB18" t="inlineStr">
-        <is>
-          <t>1086319.424627111</t>
-        </is>
-      </c>
-      <c r="BC18" t="inlineStr">
-        <is>
-          <t>1798775.809179619</t>
-        </is>
-      </c>
-      <c r="BD18" t="inlineStr">
-        <is>
-          <t>41298962.0</t>
-        </is>
-      </c>
-      <c r="BE18" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BF18" t="inlineStr">
-        <is>
-          <t>41.5</t>
-        </is>
-      </c>
-      <c r="BG18" t="inlineStr">
-        <is>
-          <t>2025/08/07</t>
-        </is>
-      </c>
-      <c r="BH18" t="inlineStr">
-        <is>
-          <t>-11.20</t>
-        </is>
-      </c>
-      <c r="BI18" t="inlineStr">
-        <is>
-          <t>新光鋼</t>
-        </is>
-      </c>
-      <c r="BJ18" t="inlineStr">
-        <is>
-          <t>新光鋼</t>
-        </is>
-      </c>
-      <c r="BK18" t="inlineStr">
-        <is>
-          <t>鋼鐵工業</t>
-        </is>
-      </c>
-      <c r="BL18" t="inlineStr">
-        <is>
-          <t>上市</t>
-        </is>
-      </c>
-      <c r="BM18" t="inlineStr">
-        <is>
-          <t>0.62</t>
-        </is>
-      </c>
-      <c r="BN18" t="inlineStr">
-        <is>
-          <t>-13.67996844119094</t>
-        </is>
-      </c>
-      <c r="BO18" t="inlineStr">
-        <is>
-          <t>-10.11024290164889</t>
-        </is>
-      </c>
-      <c r="BP18" t="inlineStr">
-        <is>
-          <t>24.12947661306339</t>
-        </is>
-      </c>
-      <c r="BQ18" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;可能出現反轉訊號&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;3&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="BR18" t="inlineStr">
-        <is>
-          <t>價-量增</t>
-        </is>
-      </c>
-      <c r="BS18" t="inlineStr">
-        <is>
-          <t>1.01</t>
-        </is>
-      </c>
-      <c r="BT18" t="inlineStr">
-        <is>
-          <t>6.43</t>
-        </is>
-      </c>
-      <c r="BU18" t="inlineStr">
-        <is>
-          <t>11.90</t>
-        </is>
-      </c>
-      <c r="BV18" t="inlineStr">
-        <is>
-          <t>16.07</t>
-        </is>
-      </c>
-      <c r="BW18" t="inlineStr">
-        <is>
-          <t>8.69%</t>
-        </is>
-      </c>
-      <c r="BX18" t="inlineStr">
-        <is>
-          <t>5.19%</t>
-        </is>
-      </c>
-      <c r="BY18" t="inlineStr">
-        <is>
-          <t>29.63</t>
-        </is>
-      </c>
-      <c r="BZ18" t="inlineStr">
-        <is>
-          <t>12493</t>
-        </is>
-      </c>
-      <c r="CA18" t="inlineStr">
-        <is>
-          <t>鋼板38.80%、熱軋及鍍鋅鋼板33.80%、不�袗�板12.60%、特殊鋼板7.00%、加工及其他6.90%、型鋼0.90% (2024年)</t>
-        </is>
-      </c>
-      <c r="CB18" t="inlineStr">
-        <is>
-          <t>新光鋼-鋼鐵工業-上市</t>
-        </is>
-      </c>
-      <c r="CC18" t="inlineStr">
-        <is>
-          <t>鋼鐵工業右下上市</t>
-        </is>
-      </c>
-      <c r="CD18" t="inlineStr">
-        <is>
-          <t>36.4</t>
-        </is>
-      </c>
-      <c r="CE18" t="inlineStr">
-        <is>
-          <t>36.95</t>
-        </is>
-      </c>
       <c r="CF18" t="inlineStr">
         <is>
-          <t>36.0</t>
+          <t>36.9</t>
         </is>
       </c>
       <c r="CG18" t="inlineStr">
         <is>
-          <t>36.85</t>
+          <t>36.9</t>
         </is>
       </c>
       <c r="CH18" t="inlineStr">
@@ -8193,12 +8193,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>0.83</t>
+          <t>1.24</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>776.396</t>
+          <t>1128.761</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -8208,7 +8208,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>36.4</t>
+          <t>36.85</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -8218,17 +8218,17 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>6.43</t>
+          <t>5.03</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>1.23</t>
+          <t>1.09</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>9.74</t>
+          <t>-1.19</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -8293,7 +8293,7 @@
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>-15.64</t>
+          <t>-14.60</t>
         </is>
       </c>
       <c r="X19" t="inlineStr">
@@ -8303,17 +8303,17 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>8.27</t>
+          <t>12.03</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>0.70</t>
+          <t>2.09</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
@@ -8324,73 +8324,73 @@
       <c r="AC19" t="inlineStr"/>
       <c r="AD19" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
-          <t>493</t>
+          <t>455</t>
         </is>
       </c>
       <c r="AF19" t="inlineStr">
         <is>
-          <t>11.76</t>
+          <t>37.5</t>
         </is>
       </c>
       <c r="AG19" t="inlineStr">
         <is>
-          <t>3.92</t>
+          <t>16.42</t>
         </is>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
-          <t>-0.90</t>
+          <t>0.66</t>
         </is>
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>-4.83</t>
+          <t>-4.68</t>
         </is>
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>-4.54</t>
+          <t>-4.69</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>-2.31</t>
+          <t>-2.48</t>
         </is>
       </c>
       <c r="AL19" t="inlineStr">
         <is>
-          <t>36.73</t>
+          <t>36.61</t>
         </is>
       </c>
       <c r="AM19" t="n">
-        <v>38.6</v>
+        <v>38.41</v>
       </c>
       <c r="AN19" t="n">
-        <v>40.43</v>
+        <v>40.3</v>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>41.39</t>
+          <t>41.32</t>
         </is>
       </c>
       <c r="AP19" t="inlineStr">
         <is>
-          <t>-19.31</t>
+          <t>-12.91</t>
         </is>
       </c>
       <c r="AQ19" t="inlineStr">
         <is>
-          <t>-1.15</t>
+          <t>-1.12</t>
         </is>
       </c>
       <c r="AR19" t="inlineStr">
         <is>
-          <t>-0.96</t>
+          <t>-0.99</t>
         </is>
       </c>
       <c r="AS19" t="inlineStr">
@@ -8400,7 +8400,7 @@
       </c>
       <c r="AT19" t="inlineStr">
         <is>
-          <t>-135.75</t>
+          <t>-136.94</t>
         </is>
       </c>
       <c r="AU19" t="inlineStr">
@@ -8410,43 +8410,43 @@
       </c>
       <c r="AV19" t="inlineStr">
         <is>
-          <t>150078431.9122682</t>
+          <t>149902651.9038461</t>
         </is>
       </c>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>28176624.0</t>
+          <t>41298962.0</t>
         </is>
       </c>
       <c r="AX19" t="n">
-        <v>37871124</v>
+        <v>35487232</v>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
-          <t>34509118.0</t>
+          <t>35914543.8</t>
         </is>
       </c>
       <c r="AZ19" t="n">
-        <v>29545425.32</v>
+        <v>29950115.64</v>
       </c>
       <c r="BA19" t="inlineStr">
         <is>
-          <t>3362006</t>
+          <t>-427311</t>
         </is>
       </c>
       <c r="BB19" t="inlineStr">
         <is>
-          <t>956781.9001630185</t>
+          <t>1086319.424627111</t>
         </is>
       </c>
       <c r="BC19" t="inlineStr">
         <is>
-          <t>1376505.330298137</t>
+          <t>1798775.809179619</t>
         </is>
       </c>
       <c r="BD19" t="inlineStr">
         <is>
-          <t>28176624.0</t>
+          <t>41298962.0</t>
         </is>
       </c>
       <c r="BE19" t="inlineStr">
@@ -8466,7 +8466,7 @@
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>-12.29</t>
+          <t>-11.20</t>
         </is>
       </c>
       <c r="BI19" t="inlineStr">
@@ -8511,22 +8511,22 @@
       </c>
       <c r="BQ19" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;可能出現反轉訊號&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;3&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR19" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS19" t="inlineStr">
         <is>
-          <t>1.00</t>
+          <t>1.01</t>
         </is>
       </c>
       <c r="BT19" t="inlineStr">
         <is>
-          <t>6.43</t>
+          <t>6.44</t>
         </is>
       </c>
       <c r="BU19" t="inlineStr">
@@ -8536,7 +8536,7 @@
       </c>
       <c r="BV19" t="inlineStr">
         <is>
-          <t>16.07</t>
+          <t>16.03</t>
         </is>
       </c>
       <c r="BW19" t="inlineStr">
@@ -8551,12 +8551,12 @@
       </c>
       <c r="BY19" t="inlineStr">
         <is>
-          <t>29.63</t>
+          <t>30.23</t>
         </is>
       </c>
       <c r="BZ19" t="inlineStr">
         <is>
-          <t>12493</t>
+          <t>12460</t>
         </is>
       </c>
       <c r="CA19" t="inlineStr">
@@ -8576,12 +8576,12 @@
       </c>
       <c r="CD19" t="inlineStr">
         <is>
-          <t>36.3</t>
+          <t>36.4</t>
         </is>
       </c>
       <c r="CE19" t="inlineStr">
         <is>
-          <t>36.55</t>
+          <t>36.95</t>
         </is>
       </c>
       <c r="CF19" t="inlineStr">
@@ -8591,7 +8591,7 @@
       </c>
       <c r="CG19" t="inlineStr">
         <is>
-          <t>36.4</t>
+          <t>36.85</t>
         </is>
       </c>
       <c r="CH19" t="inlineStr">
@@ -8623,12 +8623,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>-1.76</t>
+          <t>0.83</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>1212.053</t>
+          <t>776.396</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -8638,7 +8638,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>36.1</t>
+          <t>36.4</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -8648,17 +8648,17 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>7.2</t>
+          <t>6.19</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>1.23</t>
+          <t>1.09</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>3.03</t>
+          <t>9.74</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -8723,7 +8723,7 @@
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>-16.34</t>
+          <t>-15.64</t>
         </is>
       </c>
       <c r="X20" t="inlineStr">
@@ -8733,17 +8733,17 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>12.91</t>
+          <t>8.27</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>-1.38</t>
+          <t>0.70</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
@@ -8754,73 +8754,73 @@
       <c r="AC20" t="inlineStr"/>
       <c r="AD20" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
-          <t>493</t>
+          <t>455</t>
         </is>
       </c>
       <c r="AF20" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>11.76</t>
         </is>
       </c>
       <c r="AG20" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>3.92</t>
         </is>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
-          <t>-2.62</t>
+          <t>-0.90</t>
         </is>
       </c>
       <c r="AI20" t="inlineStr">
         <is>
-          <t>-4.47</t>
+          <t>-4.83</t>
         </is>
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>-4.38</t>
+          <t>-4.54</t>
         </is>
       </c>
       <c r="AK20" t="inlineStr">
         <is>
-          <t>-2.09</t>
+          <t>-2.31</t>
         </is>
       </c>
       <c r="AL20" t="inlineStr">
         <is>
-          <t>37.07000000000001</t>
+          <t>36.73</t>
         </is>
       </c>
       <c r="AM20" t="n">
-        <v>38.8</v>
+        <v>38.6</v>
       </c>
       <c r="AN20" t="n">
-        <v>40.58</v>
+        <v>40.43</v>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>41.45</t>
+          <t>41.39</t>
         </is>
       </c>
       <c r="AP20" t="inlineStr">
         <is>
-          <t>-22.07</t>
+          <t>-19.31</t>
         </is>
       </c>
       <c r="AQ20" t="inlineStr">
         <is>
-          <t>-1.12</t>
+          <t>-1.15</t>
         </is>
       </c>
       <c r="AR20" t="inlineStr">
         <is>
-          <t>-0.91</t>
+          <t>-0.96</t>
         </is>
       </c>
       <c r="AS20" t="inlineStr">
@@ -8830,7 +8830,7 @@
       </c>
       <c r="AT20" t="inlineStr">
         <is>
-          <t>-134.02</t>
+          <t>-135.75</t>
         </is>
       </c>
       <c r="AU20" t="inlineStr">
@@ -8840,43 +8840,43 @@
       </c>
       <c r="AV20" t="inlineStr">
         <is>
-          <t>150078431.9122682</t>
+          <t>149902651.9038461</t>
         </is>
       </c>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>43823516.0</t>
+          <t>28176624.0</t>
         </is>
       </c>
       <c r="AX20" t="n">
-        <v>36085517.8</v>
+        <v>37871124</v>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
-          <t>35025550.9</t>
+          <t>34509118.0</t>
         </is>
       </c>
       <c r="AZ20" t="n">
-        <v>29409986</v>
+        <v>29545425.32</v>
       </c>
       <c r="BA20" t="inlineStr">
         <is>
-          <t>1059966</t>
+          <t>3362006</t>
         </is>
       </c>
       <c r="BB20" t="inlineStr">
         <is>
-          <t>880468.5492293607</t>
+          <t>956781.9001630185</t>
         </is>
       </c>
       <c r="BC20" t="inlineStr">
         <is>
-          <t>2130065.670099653</t>
+          <t>1376505.330298137</t>
         </is>
       </c>
       <c r="BD20" t="inlineStr">
         <is>
-          <t>43823516.0</t>
+          <t>28176624.0</t>
         </is>
       </c>
       <c r="BE20" t="inlineStr">
@@ -8896,7 +8896,7 @@
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>-13.01</t>
+          <t>-12.29</t>
         </is>
       </c>
       <c r="BI20" t="inlineStr">
@@ -8941,7 +8941,7 @@
       </c>
       <c r="BQ20" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR20" t="inlineStr">
@@ -8951,12 +8951,12 @@
       </c>
       <c r="BS20" t="inlineStr">
         <is>
-          <t>0.99</t>
+          <t>1.00</t>
         </is>
       </c>
       <c r="BT20" t="inlineStr">
         <is>
-          <t>6.43</t>
+          <t>6.44</t>
         </is>
       </c>
       <c r="BU20" t="inlineStr">
@@ -8966,7 +8966,7 @@
       </c>
       <c r="BV20" t="inlineStr">
         <is>
-          <t>16.07</t>
+          <t>16.03</t>
         </is>
       </c>
       <c r="BW20" t="inlineStr">
@@ -8981,12 +8981,12 @@
       </c>
       <c r="BY20" t="inlineStr">
         <is>
-          <t>29.63</t>
+          <t>30.23</t>
         </is>
       </c>
       <c r="BZ20" t="inlineStr">
         <is>
-          <t>12493</t>
+          <t>12460</t>
         </is>
       </c>
       <c r="CA20" t="inlineStr">
@@ -9006,22 +9006,22 @@
       </c>
       <c r="CD20" t="inlineStr">
         <is>
-          <t>36.85</t>
+          <t>36.3</t>
         </is>
       </c>
       <c r="CE20" t="inlineStr">
         <is>
-          <t>36.85</t>
+          <t>36.55</t>
         </is>
       </c>
       <c r="CF20" t="inlineStr">
         <is>
-          <t>35.85</t>
+          <t>36.0</t>
         </is>
       </c>
       <c r="CG20" t="inlineStr">
         <is>
-          <t>36.1</t>
+          <t>36.4</t>
         </is>
       </c>
       <c r="CH20" t="inlineStr">
@@ -9053,12 +9053,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>-0.54</t>
+          <t>-1.76</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>672.504</t>
+          <t>1212.053</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -9068,7 +9068,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>36.75</t>
+          <t>36.1</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -9078,17 +9078,17 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>5.53</t>
+          <t>6.96</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>1.23</t>
+          <t>1.09</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>-2.04</t>
+          <t>3.03</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -9153,7 +9153,7 @@
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>-14.83</t>
+          <t>-16.34</t>
         </is>
       </c>
       <c r="X21" t="inlineStr">
@@ -9163,17 +9163,17 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>7.17</t>
+          <t>12.91</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>-1.09</t>
+          <t>-1.38</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
@@ -9184,12 +9184,12 @@
       <c r="AC21" t="inlineStr"/>
       <c r="AD21" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
-          <t>493</t>
+          <t>455</t>
         </is>
       </c>
       <c r="AF21" t="inlineStr">
@@ -9204,53 +9204,53 @@
       </c>
       <c r="AH21" t="inlineStr">
         <is>
-          <t>-1.92</t>
+          <t>-2.62</t>
         </is>
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>-3.97</t>
+          <t>-4.47</t>
         </is>
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>-4.25</t>
+          <t>-4.38</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
         <is>
-          <t>-1.83</t>
+          <t>-2.09</t>
         </is>
       </c>
       <c r="AL21" t="inlineStr">
         <is>
-          <t>37.47000000000001</t>
+          <t>37.07000000000001</t>
         </is>
       </c>
       <c r="AM21" t="n">
-        <v>39.02</v>
+        <v>38.8</v>
       </c>
       <c r="AN21" t="n">
-        <v>40.75</v>
+        <v>40.58</v>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>41.51</t>
+          <t>41.45</t>
         </is>
       </c>
       <c r="AP21" t="inlineStr">
         <is>
-          <t>-19.33</t>
+          <t>-22.07</t>
         </is>
       </c>
       <c r="AQ21" t="inlineStr">
         <is>
-          <t>-1.03</t>
+          <t>-1.12</t>
         </is>
       </c>
       <c r="AR21" t="inlineStr">
         <is>
-          <t>-0.86</t>
+          <t>-0.91</t>
         </is>
       </c>
       <c r="AS21" t="inlineStr">
@@ -9260,7 +9260,7 @@
       </c>
       <c r="AT21" t="inlineStr">
         <is>
-          <t>-132.14</t>
+          <t>-134.02</t>
         </is>
       </c>
       <c r="AU21" t="inlineStr">
@@ -9270,43 +9270,43 @@
       </c>
       <c r="AV21" t="inlineStr">
         <is>
-          <t>150078431.9122682</t>
+          <t>149902651.9038461</t>
         </is>
       </c>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>24762299.0</t>
+          <t>43823516.0</t>
         </is>
       </c>
       <c r="AX21" t="n">
-        <v>31929308.6</v>
+        <v>36085517.8</v>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
-          <t>32595150.7</t>
+          <t>35025550.9</t>
         </is>
       </c>
       <c r="AZ21" t="n">
-        <v>29130934.74</v>
+        <v>29409986</v>
       </c>
       <c r="BA21" t="inlineStr">
         <is>
-          <t>-665842</t>
+          <t>1059966</t>
         </is>
       </c>
       <c r="BB21" t="inlineStr">
         <is>
-          <t>653269.0727074891</t>
+          <t>880468.5492293607</t>
         </is>
       </c>
       <c r="BC21" t="inlineStr">
         <is>
-          <t>1454053.953026839</t>
+          <t>2130065.670099653</t>
         </is>
       </c>
       <c r="BD21" t="inlineStr">
         <is>
-          <t>24762299.0</t>
+          <t>43823516.0</t>
         </is>
       </c>
       <c r="BE21" t="inlineStr">
@@ -9326,7 +9326,7 @@
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>-11.45</t>
+          <t>-13.01</t>
         </is>
       </c>
       <c r="BI21" t="inlineStr">
@@ -9381,12 +9381,12 @@
       </c>
       <c r="BS21" t="inlineStr">
         <is>
-          <t>1.01</t>
+          <t>0.99</t>
         </is>
       </c>
       <c r="BT21" t="inlineStr">
         <is>
-          <t>6.43</t>
+          <t>6.44</t>
         </is>
       </c>
       <c r="BU21" t="inlineStr">
@@ -9396,7 +9396,7 @@
       </c>
       <c r="BV21" t="inlineStr">
         <is>
-          <t>16.07</t>
+          <t>16.03</t>
         </is>
       </c>
       <c r="BW21" t="inlineStr">
@@ -9411,12 +9411,12 @@
       </c>
       <c r="BY21" t="inlineStr">
         <is>
-          <t>29.63</t>
+          <t>30.23</t>
         </is>
       </c>
       <c r="BZ21" t="inlineStr">
         <is>
-          <t>12493</t>
+          <t>12460</t>
         </is>
       </c>
       <c r="CA21" t="inlineStr">
@@ -9436,22 +9436,22 @@
       </c>
       <c r="CD21" t="inlineStr">
         <is>
-          <t>36.95</t>
+          <t>36.85</t>
         </is>
       </c>
       <c r="CE21" t="inlineStr">
         <is>
-          <t>37.3</t>
+          <t>36.85</t>
         </is>
       </c>
       <c r="CF21" t="inlineStr">
         <is>
-          <t>36.6</t>
+          <t>35.85</t>
         </is>
       </c>
       <c r="CG21" t="inlineStr">
         <is>
-          <t>36.75</t>
+          <t>36.1</t>
         </is>
       </c>
       <c r="CH21" t="inlineStr">
@@ -9483,12 +9483,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>-1.34</t>
+          <t>-0.54</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>1065.248</t>
+          <t>672.504</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -9498,7 +9498,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>36.95</t>
+          <t>36.75</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -9508,17 +9508,17 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>5.01</t>
+          <t>5.28</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>1.23</t>
+          <t>1.09</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>28.28</t>
+          <t>-2.04</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -9583,7 +9583,7 @@
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>-14.37</t>
+          <t>-14.83</t>
         </is>
       </c>
       <c r="X22" t="inlineStr">
@@ -9593,17 +9593,17 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>11.35</t>
+          <t>7.17</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>-0.81</t>
+          <t>-1.09</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
@@ -9614,12 +9614,12 @@
       <c r="AC22" t="inlineStr"/>
       <c r="AD22" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE22" t="inlineStr">
         <is>
-          <t>493</t>
+          <t>455</t>
         </is>
       </c>
       <c r="AF22" t="inlineStr">
@@ -9629,58 +9629,58 @@
       </c>
       <c r="AG22" t="inlineStr">
         <is>
-          <t>9.38</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
-          <t>-1.86</t>
+          <t>-1.92</t>
         </is>
       </c>
       <c r="AI22" t="inlineStr">
         <is>
-          <t>-4.02</t>
+          <t>-3.97</t>
         </is>
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>-4.09</t>
+          <t>-4.25</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
         <is>
-          <t>-1.60</t>
+          <t>-1.83</t>
         </is>
       </c>
       <c r="AL22" t="inlineStr">
         <is>
-          <t>37.65000000000001</t>
+          <t>37.47000000000001</t>
         </is>
       </c>
       <c r="AM22" t="n">
-        <v>39.23</v>
+        <v>39.02</v>
       </c>
       <c r="AN22" t="n">
-        <v>40.9</v>
+        <v>40.75</v>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>41.57</t>
+          <t>41.51</t>
         </is>
       </c>
       <c r="AP22" t="inlineStr">
         <is>
-          <t>-18.37</t>
+          <t>-19.33</t>
         </is>
       </c>
       <c r="AQ22" t="inlineStr">
         <is>
-          <t>-0.97</t>
+          <t>-1.03</t>
         </is>
       </c>
       <c r="AR22" t="inlineStr">
         <is>
-          <t>-0.82</t>
+          <t>-0.86</t>
         </is>
       </c>
       <c r="AS22" t="inlineStr">
@@ -9690,7 +9690,7 @@
       </c>
       <c r="AT22" t="inlineStr">
         <is>
-          <t>-130.59</t>
+          <t>-132.14</t>
         </is>
       </c>
       <c r="AU22" t="inlineStr">
@@ -9700,43 +9700,43 @@
       </c>
       <c r="AV22" t="inlineStr">
         <is>
-          <t>150078431.9122682</t>
+          <t>149902651.9038461</t>
         </is>
       </c>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>39374759.0</t>
+          <t>24762299.0</t>
         </is>
       </c>
       <c r="AX22" t="n">
-        <v>40349216</v>
+        <v>31929308.6</v>
       </c>
       <c r="AY22" t="inlineStr">
         <is>
-          <t>31454761.9</t>
+          <t>32595150.7</t>
         </is>
       </c>
       <c r="AZ22" t="n">
-        <v>29061426.18</v>
+        <v>29130934.74</v>
       </c>
       <c r="BA22" t="inlineStr">
         <is>
-          <t>8894454</t>
+          <t>-665842</t>
         </is>
       </c>
       <c r="BB22" t="inlineStr">
         <is>
-          <t>507671.8217403347</t>
+          <t>653269.0727074891</t>
         </is>
       </c>
       <c r="BC22" t="inlineStr">
         <is>
-          <t>2478665.680314712</t>
+          <t>1454053.953026839</t>
         </is>
       </c>
       <c r="BD22" t="inlineStr">
         <is>
-          <t>39374759.0</t>
+          <t>24762299.0</t>
         </is>
       </c>
       <c r="BE22" t="inlineStr">
@@ -9756,7 +9756,7 @@
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>-10.96</t>
+          <t>-11.45</t>
         </is>
       </c>
       <c r="BI22" t="inlineStr">
@@ -9801,7 +9801,7 @@
       </c>
       <c r="BQ22" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR22" t="inlineStr">
@@ -9811,12 +9811,12 @@
       </c>
       <c r="BS22" t="inlineStr">
         <is>
-          <t>1.02</t>
+          <t>1.01</t>
         </is>
       </c>
       <c r="BT22" t="inlineStr">
         <is>
-          <t>6.43</t>
+          <t>6.44</t>
         </is>
       </c>
       <c r="BU22" t="inlineStr">
@@ -9826,7 +9826,7 @@
       </c>
       <c r="BV22" t="inlineStr">
         <is>
-          <t>16.07</t>
+          <t>16.03</t>
         </is>
       </c>
       <c r="BW22" t="inlineStr">
@@ -9841,12 +9841,12 @@
       </c>
       <c r="BY22" t="inlineStr">
         <is>
-          <t>29.63</t>
+          <t>30.23</t>
         </is>
       </c>
       <c r="BZ22" t="inlineStr">
         <is>
-          <t>12493</t>
+          <t>12460</t>
         </is>
       </c>
       <c r="CA22" t="inlineStr">
@@ -9866,22 +9866,22 @@
       </c>
       <c r="CD22" t="inlineStr">
         <is>
+          <t>36.95</t>
+        </is>
+      </c>
+      <c r="CE22" t="inlineStr">
+        <is>
           <t>37.3</t>
         </is>
       </c>
-      <c r="CE22" t="inlineStr">
-        <is>
-          <t>37.5</t>
-        </is>
-      </c>
       <c r="CF22" t="inlineStr">
         <is>
-          <t>36.7</t>
+          <t>36.6</t>
         </is>
       </c>
       <c r="CG22" t="inlineStr">
         <is>
-          <t>36.95</t>
+          <t>36.75</t>
         </is>
       </c>
       <c r="CH22" t="inlineStr">
@@ -9913,12 +9913,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>-1.71</t>
+          <t>-1.34</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>1408.733</t>
+          <t>1065.248</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -9928,7 +9928,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>37.45</t>
+          <t>36.95</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -9938,17 +9938,17 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>3.73</t>
+          <t>4.77</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>1.23</t>
+          <t>1.09</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>22.93</t>
+          <t>28.28</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -10013,7 +10013,7 @@
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>-13.21</t>
+          <t>-14.37</t>
         </is>
       </c>
       <c r="X23" t="inlineStr">
@@ -10023,17 +10023,17 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>15.01</t>
+          <t>11.35</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>-2.94</t>
+          <t>-0.81</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
@@ -10044,12 +10044,12 @@
       <c r="AC23" t="inlineStr"/>
       <c r="AD23" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE23" t="inlineStr">
         <is>
-          <t>493</t>
+          <t>455</t>
         </is>
       </c>
       <c r="AF23" t="inlineStr">
@@ -10059,58 +10059,58 @@
       </c>
       <c r="AG23" t="inlineStr">
         <is>
-          <t>16.69</t>
+          <t>9.38</t>
         </is>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
-          <t>-1.42</t>
+          <t>-1.86</t>
         </is>
       </c>
       <c r="AI23" t="inlineStr">
         <is>
-          <t>-3.63</t>
+          <t>-4.02</t>
         </is>
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>-3.96</t>
+          <t>-4.09</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
         <is>
-          <t>-1.34</t>
+          <t>-1.60</t>
         </is>
       </c>
       <c r="AL23" t="inlineStr">
         <is>
-          <t>37.99</t>
+          <t>37.65000000000001</t>
         </is>
       </c>
       <c r="AM23" t="n">
-        <v>39.42</v>
+        <v>39.23</v>
       </c>
       <c r="AN23" t="n">
-        <v>41.05</v>
+        <v>40.9</v>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>41.6</t>
+          <t>41.57</t>
         </is>
       </c>
       <c r="AP23" t="inlineStr">
         <is>
-          <t>-15.49</t>
+          <t>-18.37</t>
         </is>
       </c>
       <c r="AQ23" t="inlineStr">
         <is>
-          <t>-0.91</t>
+          <t>-0.97</t>
         </is>
       </c>
       <c r="AR23" t="inlineStr">
         <is>
-          <t>-0.78</t>
+          <t>-0.82</t>
         </is>
       </c>
       <c r="AS23" t="inlineStr">
@@ -10120,7 +10120,7 @@
       </c>
       <c r="AT23" t="inlineStr">
         <is>
-          <t>-129.19</t>
+          <t>-130.59</t>
         </is>
       </c>
       <c r="AU23" t="inlineStr">
@@ -10130,43 +10130,43 @@
       </c>
       <c r="AV23" t="inlineStr">
         <is>
-          <t>150078431.9122682</t>
+          <t>149902651.9038461</t>
         </is>
       </c>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>53218422.0</t>
+          <t>39374759.0</t>
         </is>
       </c>
       <c r="AX23" t="n">
-        <v>36341855.6</v>
+        <v>40349216</v>
       </c>
       <c r="AY23" t="inlineStr">
         <is>
-          <t>29562657.9</t>
+          <t>31454761.9</t>
         </is>
       </c>
       <c r="AZ23" t="n">
-        <v>28846965.04</v>
+        <v>29061426.18</v>
       </c>
       <c r="BA23" t="inlineStr">
         <is>
-          <t>6779197</t>
+          <t>8894454</t>
         </is>
       </c>
       <c r="BB23" t="inlineStr">
         <is>
-          <t>149309.3019995387</t>
+          <t>507671.8217403347</t>
         </is>
       </c>
       <c r="BC23" t="inlineStr">
         <is>
-          <t>2288252.230714723</t>
+          <t>2478665.680314712</t>
         </is>
       </c>
       <c r="BD23" t="inlineStr">
         <is>
-          <t>53218422.0</t>
+          <t>39374759.0</t>
         </is>
       </c>
       <c r="BE23" t="inlineStr">
@@ -10186,7 +10186,7 @@
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>-9.76</t>
+          <t>-10.96</t>
         </is>
       </c>
       <c r="BI23" t="inlineStr">
@@ -10231,7 +10231,7 @@
       </c>
       <c r="BQ23" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR23" t="inlineStr">
@@ -10241,12 +10241,12 @@
       </c>
       <c r="BS23" t="inlineStr">
         <is>
-          <t>1.03</t>
+          <t>1.02</t>
         </is>
       </c>
       <c r="BT23" t="inlineStr">
         <is>
-          <t>6.43</t>
+          <t>6.44</t>
         </is>
       </c>
       <c r="BU23" t="inlineStr">
@@ -10256,7 +10256,7 @@
       </c>
       <c r="BV23" t="inlineStr">
         <is>
-          <t>16.07</t>
+          <t>16.03</t>
         </is>
       </c>
       <c r="BW23" t="inlineStr">
@@ -10271,12 +10271,12 @@
       </c>
       <c r="BY23" t="inlineStr">
         <is>
-          <t>29.63</t>
+          <t>30.23</t>
         </is>
       </c>
       <c r="BZ23" t="inlineStr">
         <is>
-          <t>12493</t>
+          <t>12460</t>
         </is>
       </c>
       <c r="CA23" t="inlineStr">
@@ -10296,22 +10296,22 @@
       </c>
       <c r="CD23" t="inlineStr">
         <is>
-          <t>38.1</t>
+          <t>37.3</t>
         </is>
       </c>
       <c r="CE23" t="inlineStr">
         <is>
-          <t>38.7</t>
+          <t>37.5</t>
         </is>
       </c>
       <c r="CF23" t="inlineStr">
         <is>
-          <t>37.3</t>
+          <t>36.7</t>
         </is>
       </c>
       <c r="CG23" t="inlineStr">
         <is>
-          <t>37.45</t>
+          <t>36.95</t>
         </is>
       </c>
       <c r="CH23" t="inlineStr">

--- a/Result/checksun_type/塔架.xlsx
+++ b/Result/checksun_type/塔架.xlsx
@@ -883,12 +883,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>1.77</t>
+          <t>-1.05</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>999.152</t>
+          <t>798.983</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>143.0</t>
+          <t>141.5</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-1.69</t>
+          <t>0.18</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>-34.04</t>
+          <t>-27.70</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-39.66</t>
+          <t>-40.30</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -993,17 +993,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>4.13</t>
+          <t>3.30</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>0.73</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1014,73 +1014,73 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>999</t>
+          <t>799</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>81.25</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>90.28</t>
+          <t>88.19</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>1.27</t>
+          <t>-0.14</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>-1.03</t>
+          <t>-0.25</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>-8.91</t>
+          <t>-9.02</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>-6.08</t>
+          <t>-6.02</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>141.2</t>
+          <t>141.7</t>
         </is>
       </c>
       <c r="AM2" t="n">
-        <v>142.68</v>
+        <v>142.05</v>
       </c>
       <c r="AN2" t="n">
-        <v>156.63</v>
+        <v>156.13</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>166.78</t>
+          <t>166.12</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>21.03</t>
+          <t>23.39</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>-5.00</t>
+          <t>-4.59</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>-6.34</t>
+          <t>-5.99</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -1090,7 +1090,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-125.46</t>
+          <t>-124.06</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1100,43 +1100,43 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>1682419827.202991</t>
+          <t>1680267492.872689</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>142703815.0</t>
+          <t>112885862.0</t>
         </is>
       </c>
       <c r="AX2" t="n">
-        <v>120065081.4</v>
+        <v>112771125.2</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>182016975.2</t>
+          <t>155969593.1</t>
         </is>
       </c>
       <c r="AZ2" t="n">
-        <v>246778897.84</v>
+        <v>243086486.76</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>-61951893</t>
+          <t>-43198467</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>-7828264.537723166</t>
+          <t>-10480710.50095323</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>-24115587.05038333</t>
+          <t>-25069163.2987186</t>
         </is>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
-          <t>142703815.0</t>
+          <t>112885862.0</t>
         </is>
       </c>
       <c r="BE2" t="inlineStr">
@@ -1156,7 +1156,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>-20.56</t>
+          <t>-21.39</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
@@ -1201,7 +1201,7 @@
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
@@ -1211,12 +1211,12 @@
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>3.29</t>
+          <t>3.26</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
         <is>
-          <t>2.91</t>
+          <t>2.94</t>
         </is>
       </c>
       <c r="BU2" t="inlineStr">
@@ -1226,7 +1226,7 @@
       </c>
       <c r="BV2" t="inlineStr">
         <is>
-          <t>26.88</t>
+          <t>26.6</t>
         </is>
       </c>
       <c r="BW2" t="inlineStr">
@@ -1246,7 +1246,7 @@
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>35306</t>
+          <t>34936</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
@@ -1266,22 +1266,22 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>141.0</t>
+          <t>142.5</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>145.0</t>
+          <t>142.5</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>141.0</t>
+          <t>139.5</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>143.0</t>
+          <t>141.5</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
@@ -1313,12 +1313,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>-0.35</t>
+          <t>1.77</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>800.978</t>
+          <t>999.152</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1328,7 +1328,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>140.5</t>
+          <t>143.0</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1338,17 +1338,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>1.75</t>
+          <t>-1.06</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-1.69</t>
+          <t>0.18</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>-37.50</t>
+          <t>-34.04</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1413,7 +1413,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-40.72</t>
+          <t>-39.66</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1423,17 +1423,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>3.31</t>
+          <t>4.13</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>0.37</t>
+          <t>0.02</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1444,17 +1444,17 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>999</t>
+          <t>799</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>83.33</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
@@ -1464,53 +1464,53 @@
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>0.14</t>
+          <t>1.27</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>-2.14</t>
+          <t>-1.03</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-8.77</t>
+          <t>-8.91</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>-6.13</t>
+          <t>-6.08</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>140.3</t>
+          <t>141.2</t>
         </is>
       </c>
       <c r="AM3" t="n">
-        <v>143.38</v>
+        <v>142.68</v>
       </c>
       <c r="AN3" t="n">
-        <v>157.15</v>
+        <v>156.63</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>167.42</t>
+          <t>166.78</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>15.78</t>
+          <t>21.03</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>-5.62</t>
+          <t>-5.00</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>-6.67</t>
+          <t>-6.34</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1520,7 +1520,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-126.80</t>
+          <t>-125.46</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1530,43 +1530,43 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>1682419827.202991</t>
+          <t>1680267492.872689</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>111993447.0</t>
+          <t>142703815.0</t>
         </is>
       </c>
       <c r="AX3" t="n">
-        <v>138810283.4</v>
+        <v>120065081.4</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>222079436.2</t>
+          <t>182016975.2</t>
         </is>
       </c>
       <c r="AZ3" t="n">
-        <v>246079338.72</v>
+        <v>246778897.84</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>-83269152</t>
+          <t>-61951893</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>-4866933.171784954</t>
+          <t>-7828264.537723166</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>-25086844.97953352</t>
+          <t>-24115587.05038333</t>
         </is>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
-          <t>111993447.0</t>
+          <t>142703815.0</t>
         </is>
       </c>
       <c r="BE3" t="inlineStr">
@@ -1586,7 +1586,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>-21.94</t>
+          <t>-20.56</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
@@ -1631,7 +1631,7 @@
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
@@ -1641,12 +1641,12 @@
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>3.24</t>
+          <t>3.29</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
         <is>
-          <t>2.91</t>
+          <t>2.94</t>
         </is>
       </c>
       <c r="BU3" t="inlineStr">
@@ -1656,7 +1656,7 @@
       </c>
       <c r="BV3" t="inlineStr">
         <is>
-          <t>26.88</t>
+          <t>26.6</t>
         </is>
       </c>
       <c r="BW3" t="inlineStr">
@@ -1676,7 +1676,7 @@
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
-          <t>35306</t>
+          <t>34936</t>
         </is>
       </c>
       <c r="CA3" t="inlineStr">
@@ -1696,22 +1696,22 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>141.5</t>
+          <t>141.0</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>141.5</t>
+          <t>145.0</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>139.0</t>
+          <t>141.0</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>140.5</t>
+          <t>143.0</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
@@ -1743,12 +1743,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>-1.04</t>
+          <t>-0.35</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>494.362</t>
+          <t>800.978</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1758,7 +1758,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>141.0</t>
+          <t>140.5</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1768,17 +1768,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>1.4</t>
+          <t>0.71</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-1.69</t>
+          <t>0.18</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>-47.22</t>
+          <t>-37.50</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1843,7 +1843,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-40.51</t>
+          <t>-40.72</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1853,17 +1853,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>2.04</t>
+          <t>3.31</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>-2.13</t>
+          <t>0.37</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1874,73 +1874,73 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>999</t>
+          <t>799</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>87.5</t>
+          <t>83.33</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>77.41</t>
+          <t>90.28</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>1.29</t>
+          <t>0.14</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>-3.35</t>
+          <t>-2.14</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>-8.68</t>
+          <t>-8.77</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>-6.17</t>
+          <t>-6.13</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>139.2</t>
+          <t>140.3</t>
         </is>
       </c>
       <c r="AM4" t="n">
-        <v>144.02</v>
+        <v>143.38</v>
       </c>
       <c r="AN4" t="n">
-        <v>157.72</v>
+        <v>157.15</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>168.09</t>
+          <t>167.42</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>12.54</t>
+          <t>15.78</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>-6.06</t>
+          <t>-5.62</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>-6.93</t>
+          <t>-6.67</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1950,7 +1950,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-127.86</t>
+          <t>-126.80</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1960,43 +1960,43 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>1682419827.202991</t>
+          <t>1680267492.872689</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>70132250.0</t>
+          <t>111993447.0</t>
         </is>
       </c>
       <c r="AX4" t="n">
-        <v>151097591.6</v>
+        <v>138810283.4</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>286274053.3</t>
+          <t>222079436.2</t>
         </is>
       </c>
       <c r="AZ4" t="n">
-        <v>248269560.06</v>
+        <v>246079338.72</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>-135176461</t>
+          <t>-83269152</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>-1190585.570376122</t>
+          <t>-4866933.171784954</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>-22288000.98619333</t>
+          <t>-25086844.97953352</t>
         </is>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
-          <t>70132250.0</t>
+          <t>111993447.0</t>
         </is>
       </c>
       <c r="BE4" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>-21.67</t>
+          <t>-21.94</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
@@ -2061,22 +2061,22 @@
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
         <is>
-          <t>價跌量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>3.25</t>
+          <t>3.24</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
         <is>
-          <t>2.91</t>
+          <t>2.94</t>
         </is>
       </c>
       <c r="BU4" t="inlineStr">
@@ -2086,7 +2086,7 @@
       </c>
       <c r="BV4" t="inlineStr">
         <is>
-          <t>26.88</t>
+          <t>26.6</t>
         </is>
       </c>
       <c r="BW4" t="inlineStr">
@@ -2106,7 +2106,7 @@
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
-          <t>35306</t>
+          <t>34936</t>
         </is>
       </c>
       <c r="CA4" t="inlineStr">
@@ -2126,22 +2126,22 @@
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>144.0</t>
+          <t>141.5</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>144.0</t>
+          <t>141.5</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>141.0</t>
+          <t>139.0</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>141.0</t>
+          <t>140.5</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
@@ -2173,12 +2173,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>2.48</t>
+          <t>-1.04</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>885.355</t>
+          <t>494.362</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2188,7 +2188,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>142.5</t>
+          <t>141.0</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2203,12 +2203,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-1.69</t>
+          <t>0.18</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>-37.74</t>
+          <t>-47.22</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2273,7 +2273,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-39.87</t>
+          <t>-40.51</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2283,17 +2283,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>3.66</t>
+          <t>2.04</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>0.36</t>
+          <t>-2.13</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2304,73 +2304,73 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>999</t>
+          <t>799</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>87.5</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>62.28</t>
+          <t>77.41</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>3.26</t>
+          <t>1.29</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>-4.63</t>
+          <t>-3.35</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>-8.6</t>
+          <t>-8.68</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>-6.19</t>
+          <t>-6.17</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>138.0</t>
+          <t>139.2</t>
         </is>
       </c>
       <c r="AM5" t="n">
-        <v>144.7</v>
+        <v>144.02</v>
       </c>
       <c r="AN5" t="n">
-        <v>158.31</v>
+        <v>157.72</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>168.75</t>
+          <t>168.09</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>7.75</t>
+          <t>12.54</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>-6.60</t>
+          <t>-6.06</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>-7.15</t>
+          <t>-6.93</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -2380,7 +2380,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-128.73</t>
+          <t>-127.86</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2390,43 +2390,43 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>1682419827.202991</t>
+          <t>1680267492.872689</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>126140252.0</t>
+          <t>70132250.0</t>
         </is>
       </c>
       <c r="AX5" t="n">
-        <v>179646773.6</v>
+        <v>151097591.6</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>288541776.1</t>
+          <t>286274053.3</t>
         </is>
       </c>
       <c r="AZ5" t="n">
-        <v>249860076.6</v>
+        <v>248269560.06</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>-108895002</t>
+          <t>-135176461</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>2645308.141590643</t>
+          <t>-1190585.570376122</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>-13008524.13905758</t>
+          <t>-22288000.98619333</t>
         </is>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
-          <t>126140252.0</t>
+          <t>70132250.0</t>
         </is>
       </c>
       <c r="BE5" t="inlineStr">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>-20.83</t>
+          <t>-21.67</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
@@ -2491,22 +2491,22 @@
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價跌量-</t>
         </is>
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>3.28</t>
+          <t>3.25</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
         <is>
-          <t>2.91</t>
+          <t>2.94</t>
         </is>
       </c>
       <c r="BU5" t="inlineStr">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="BV5" t="inlineStr">
         <is>
-          <t>26.88</t>
+          <t>26.6</t>
         </is>
       </c>
       <c r="BW5" t="inlineStr">
@@ -2536,7 +2536,7 @@
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
-          <t>35306</t>
+          <t>34936</t>
         </is>
       </c>
       <c r="CA5" t="inlineStr">
@@ -2556,22 +2556,22 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
+          <t>144.0</t>
+        </is>
+      </c>
+      <c r="CE5" t="inlineStr">
+        <is>
+          <t>144.0</t>
+        </is>
+      </c>
+      <c r="CF5" t="inlineStr">
+        <is>
           <t>141.0</t>
         </is>
       </c>
-      <c r="CE5" t="inlineStr">
-        <is>
-          <t>143.5</t>
-        </is>
-      </c>
-      <c r="CF5" t="inlineStr">
+      <c r="CG5" t="inlineStr">
         <is>
           <t>141.0</t>
-        </is>
-      </c>
-      <c r="CG5" t="inlineStr">
-        <is>
-          <t>142.5</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
@@ -2593,7 +2593,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>【e】</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -2603,127 +2603,127 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
+          <t>2.48</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>885.355</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>142.5</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>-0.71</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>0.18</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>-37.74</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>-65.0</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>2025-06-04 00:00:00</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>2025-06-30 00:00:00</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>2025-05-09 00:00:00</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>2025-05-23 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>199.0</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>237.0</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>181.0</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>178.0</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>-39.87</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>11.80</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-11-26</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>3.66</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
           <t>0.36</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>1070.548</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>139.0</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>2.8</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>-1.69</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>-30.56</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>-65.0</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>2025-06-04 00:00:00</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>2025-06-30 00:00:00</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>2025-05-09 00:00:00</t>
-        </is>
-      </c>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>2025-05-23 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q6" t="inlineStr">
-        <is>
-          <t>199.0</t>
-        </is>
-      </c>
-      <c r="R6" t="inlineStr">
-        <is>
-          <t>237.0</t>
-        </is>
-      </c>
-      <c r="S6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T6" t="inlineStr">
-        <is>
-          <t>181.0</t>
-        </is>
-      </c>
-      <c r="U6" t="inlineStr">
-        <is>
-          <t>178.0</t>
-        </is>
-      </c>
-      <c r="V6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>-41.35</t>
-        </is>
-      </c>
-      <c r="X6" t="inlineStr">
-        <is>
-          <t>11.80</t>
-        </is>
-      </c>
-      <c r="Y6" t="inlineStr">
-        <is>
-          <t>2025-11-25</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>4.43</t>
-        </is>
-      </c>
-      <c r="AA6" t="inlineStr">
-        <is>
-          <t>-0.71</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2734,37 +2734,37 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>999</t>
+          <t>799</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>44.74</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>36.84</t>
+          <t>62.28</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>2.51</t>
+          <t>3.26</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>-6.71</t>
+          <t>-4.63</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>-8.49</t>
+          <t>-8.6</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
@@ -2774,33 +2774,33 @@
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>135.6</t>
+          <t>138.0</t>
         </is>
       </c>
       <c r="AM6" t="n">
-        <v>145.35</v>
+        <v>144.7</v>
       </c>
       <c r="AN6" t="n">
-        <v>158.83</v>
+        <v>158.31</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>169.32</t>
+          <t>168.75</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>-0.61</t>
+          <t>7.75</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>-7.33</t>
+          <t>-6.60</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>-7.29</t>
+          <t>-7.15</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -2810,7 +2810,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-129.29</t>
+          <t>-128.73</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2820,43 +2820,43 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>1682419827.202991</t>
+          <t>1680267492.872689</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>149355643.0</t>
+          <t>126140252.0</t>
         </is>
       </c>
       <c r="AX6" t="n">
-        <v>199168061</v>
+        <v>179646773.6</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>286806442.7</t>
+          <t>288541776.1</t>
         </is>
       </c>
       <c r="AZ6" t="n">
-        <v>252995092.08</v>
+        <v>249860076.6</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>-87638381</t>
+          <t>-108895002</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>5491459.465344865</t>
+          <t>2645308.141590643</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>-5288395.852468729</t>
+          <t>-13008524.13905758</t>
         </is>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
-          <t>149355643.0</t>
+          <t>126140252.0</t>
         </is>
       </c>
       <c r="BE6" t="inlineStr">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>-22.78</t>
+          <t>-20.83</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
@@ -2921,22 +2921,22 @@
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>3.20</t>
+          <t>3.28</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
         <is>
-          <t>2.91</t>
+          <t>2.94</t>
         </is>
       </c>
       <c r="BU6" t="inlineStr">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="BV6" t="inlineStr">
         <is>
-          <t>26.88</t>
+          <t>26.6</t>
         </is>
       </c>
       <c r="BW6" t="inlineStr">
@@ -2966,7 +2966,7 @@
       </c>
       <c r="BZ6" t="inlineStr">
         <is>
-          <t>35306</t>
+          <t>34936</t>
         </is>
       </c>
       <c r="CA6" t="inlineStr">
@@ -2986,22 +2986,22 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>139.5</t>
+          <t>141.0</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
+          <t>143.5</t>
+        </is>
+      </c>
+      <c r="CF6" t="inlineStr">
+        <is>
           <t>141.0</t>
         </is>
       </c>
-      <c r="CF6" t="inlineStr">
-        <is>
-          <t>138.0</t>
-        </is>
-      </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>139.0</t>
+          <t>142.5</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
@@ -3033,12 +3033,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>2.56</t>
+          <t>0.36</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1721.237</t>
+          <t>1070.548</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3048,7 +3048,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>138.5</t>
+          <t>139.0</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3058,17 +3058,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>3.15</t>
+          <t>1.77</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-1.69</t>
+          <t>0.18</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>-13.08</t>
+          <t>-30.56</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3133,7 +3133,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-41.56</t>
+          <t>-41.35</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3143,17 +3143,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>7.12</t>
+          <t>4.43</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>1.87</t>
+          <t>-0.71</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3164,73 +3164,73 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>999</t>
+          <t>799</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>42.11</t>
+          <t>44.74</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>29.62</t>
+          <t>36.84</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>3.44</t>
+          <t>2.51</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>-8.46</t>
+          <t>-6.71</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>-8.28</t>
+          <t>-8.49</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>-6.17</t>
+          <t>-6.19</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>133.9</t>
+          <t>135.6</t>
         </is>
       </c>
       <c r="AM7" t="n">
-        <v>146.28</v>
+        <v>145.35</v>
       </c>
       <c r="AN7" t="n">
-        <v>159.48</v>
+        <v>158.83</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>169.96</t>
+          <t>169.32</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>-7.31</t>
+          <t>-0.61</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>-7.81</t>
+          <t>-7.33</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>-7.28</t>
+          <t>-7.29</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -3240,7 +3240,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-129.24</t>
+          <t>-129.29</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3250,43 +3250,43 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>1682419827.202991</t>
+          <t>1680267492.872689</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>236429825.0</t>
+          <t>149355643.0</t>
         </is>
       </c>
       <c r="AX7" t="n">
-        <v>243968869</v>
+        <v>199168061</v>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>280669574.0</t>
+          <t>286806442.7</t>
         </is>
       </c>
       <c r="AZ7" t="n">
-        <v>255272113.08</v>
+        <v>252995092.08</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>-36700705</t>
+          <t>-87638381</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>7451433.159492791</t>
+          <t>5491459.465344865</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>3441866.801674962</t>
+          <t>-5288395.852468729</t>
         </is>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
-          <t>236429825.0</t>
+          <t>149355643.0</t>
         </is>
       </c>
       <c r="BE7" t="inlineStr">
@@ -3306,7 +3306,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>-23.06</t>
+          <t>-22.78</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
@@ -3351,7 +3351,7 @@
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;可能出現反轉訊號&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;3&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
@@ -3361,12 +3361,12 @@
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>3.19</t>
+          <t>3.20</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
         <is>
-          <t>2.91</t>
+          <t>2.94</t>
         </is>
       </c>
       <c r="BU7" t="inlineStr">
@@ -3376,7 +3376,7 @@
       </c>
       <c r="BV7" t="inlineStr">
         <is>
-          <t>26.88</t>
+          <t>26.6</t>
         </is>
       </c>
       <c r="BW7" t="inlineStr">
@@ -3396,7 +3396,7 @@
       </c>
       <c r="BZ7" t="inlineStr">
         <is>
-          <t>35306</t>
+          <t>34936</t>
         </is>
       </c>
       <c r="CA7" t="inlineStr">
@@ -3416,22 +3416,22 @@
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>136.5</t>
+          <t>139.5</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>139.5</t>
+          <t>141.0</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>135.0</t>
+          <t>138.0</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>138.5</t>
+          <t>139.0</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
@@ -3463,12 +3463,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>2.56</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>1302.953</t>
+          <t>1721.237</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3478,7 +3478,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>135.0</t>
+          <t>138.5</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3488,17 +3488,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>5.59</t>
+          <t>2.12</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-1.69</t>
+          <t>0.18</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>12.02</t>
+          <t>-13.08</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3563,7 +3563,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-43.04</t>
+          <t>-41.56</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3573,17 +3573,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>5.39</t>
+          <t>7.12</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>3.05</t>
+          <t>1.87</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3594,73 +3594,73 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>999</t>
+          <t>799</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>23.68</t>
+          <t>42.11</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>15.59</t>
+          <t>29.62</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>1.58</t>
+          <t>3.44</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>-9.76</t>
+          <t>-8.46</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>-8.05</t>
+          <t>-8.28</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>-6.11</t>
+          <t>-6.17</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>132.9</t>
+          <t>133.9</t>
         </is>
       </c>
       <c r="AM8" t="n">
-        <v>147.28</v>
+        <v>146.28</v>
       </c>
       <c r="AN8" t="n">
-        <v>160.17</v>
+        <v>159.48</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>170.59</t>
+          <t>169.96</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>-15.53</t>
+          <t>-7.31</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>-8.25</t>
+          <t>-7.81</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>-7.14</t>
+          <t>-7.28</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -3670,7 +3670,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-128.71</t>
+          <t>-129.24</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3680,43 +3680,43 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>1682419827.202991</t>
+          <t>1680267492.872689</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>173429988.0</t>
+          <t>236429825.0</t>
         </is>
       </c>
       <c r="AX8" t="n">
-        <v>305348589</v>
+        <v>243968869</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>272591978.0</t>
+          <t>280669574.0</t>
         </is>
       </c>
       <c r="AZ8" t="n">
-        <v>254388028.92</v>
+        <v>255272113.08</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>32756611</t>
+          <t>-36700705</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>8180445.224550578</t>
+          <t>7451433.159492791</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>6461370.136106104</t>
+          <t>3441866.801674962</t>
         </is>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
-          <t>173429988.0</t>
+          <t>236429825.0</t>
         </is>
       </c>
       <c r="BE8" t="inlineStr">
@@ -3736,7 +3736,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>-25.00</t>
+          <t>-23.06</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
@@ -3781,7 +3781,7 @@
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;可能出現反轉訊號&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;3&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
@@ -3791,12 +3791,12 @@
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>3.11</t>
+          <t>3.19</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
         <is>
-          <t>2.91</t>
+          <t>2.94</t>
         </is>
       </c>
       <c r="BU8" t="inlineStr">
@@ -3806,7 +3806,7 @@
       </c>
       <c r="BV8" t="inlineStr">
         <is>
-          <t>26.88</t>
+          <t>26.6</t>
         </is>
       </c>
       <c r="BW8" t="inlineStr">
@@ -3826,7 +3826,7 @@
       </c>
       <c r="BZ8" t="inlineStr">
         <is>
-          <t>35306</t>
+          <t>34936</t>
         </is>
       </c>
       <c r="CA8" t="inlineStr">
@@ -3846,22 +3846,22 @@
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>132.5</t>
+          <t>136.5</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
+          <t>139.5</t>
+        </is>
+      </c>
+      <c r="CF8" t="inlineStr">
+        <is>
           <t>135.0</t>
         </is>
       </c>
-      <c r="CF8" t="inlineStr">
-        <is>
-          <t>131.0</t>
-        </is>
-      </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>135.0</t>
+          <t>138.5</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
@@ -3893,12 +3893,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>3.41</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>1595.31</t>
+          <t>1302.953</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3918,17 +3918,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>5.59</t>
+          <t>4.59</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-1.69</t>
+          <t>0.18</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>53.45</t>
+          <t>12.02</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -4003,17 +4003,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>6.60</t>
+          <t>5.39</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>1.92</t>
+          <t>3.05</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4024,73 +4024,73 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>999</t>
+          <t>799</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>23.08</t>
+          <t>23.68</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>7.69</t>
+          <t>15.59</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>1.20</t>
+          <t>1.58</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>-10.06</t>
+          <t>-9.76</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>-7.84</t>
+          <t>-8.05</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>-6.04</t>
+          <t>-6.11</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>133.4</t>
+          <t>132.9</t>
         </is>
       </c>
       <c r="AM9" t="n">
-        <v>148.32</v>
+        <v>147.28</v>
       </c>
       <c r="AN9" t="n">
-        <v>160.95</v>
+        <v>160.17</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>171.29</t>
+          <t>170.59</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>-21.52</t>
+          <t>-15.53</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>-8.35</t>
+          <t>-8.25</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>-6.87</t>
+          <t>-7.14</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -4100,7 +4100,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-127.59</t>
+          <t>-128.71</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4110,43 +4110,43 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>1682419827.202991</t>
+          <t>1680267492.872689</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>212878160.0</t>
+          <t>173429988.0</t>
         </is>
       </c>
       <c r="AX9" t="n">
-        <v>421450515</v>
+        <v>305348589</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>274650710.4</t>
+          <t>272591978.0</t>
         </is>
       </c>
       <c r="AZ9" t="n">
-        <v>254522728.7</v>
+        <v>254388028.92</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>146799804</t>
+          <t>32756611</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>8493004.331540482</t>
+          <t>8180445.224550578</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>17294165.64471823</t>
+          <t>6461370.136106104</t>
         </is>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
-          <t>212878160.0</t>
+          <t>173429988.0</t>
         </is>
       </c>
       <c r="BE9" t="inlineStr">
@@ -4211,12 +4211,12 @@
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;可能出現反轉訊號&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;3&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS9" t="inlineStr">
@@ -4226,7 +4226,7 @@
       </c>
       <c r="BT9" t="inlineStr">
         <is>
-          <t>2.91</t>
+          <t>2.94</t>
         </is>
       </c>
       <c r="BU9" t="inlineStr">
@@ -4236,7 +4236,7 @@
       </c>
       <c r="BV9" t="inlineStr">
         <is>
-          <t>26.88</t>
+          <t>26.6</t>
         </is>
       </c>
       <c r="BW9" t="inlineStr">
@@ -4256,7 +4256,7 @@
       </c>
       <c r="BZ9" t="inlineStr">
         <is>
-          <t>35306</t>
+          <t>34936</t>
         </is>
       </c>
       <c r="CA9" t="inlineStr">
@@ -4276,17 +4276,17 @@
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>132.0</t>
+          <t>132.5</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>136.0</t>
+          <t>135.0</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>131.5</t>
+          <t>131.0</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
@@ -4323,12 +4323,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>3.41</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>1712.06</t>
+          <t>1595.31</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4338,7 +4338,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>130.5</t>
+          <t>135.0</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4348,17 +4348,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>8.74</t>
+          <t>4.59</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-1.69</t>
+          <t>0.18</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>50.94</t>
+          <t>53.45</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4423,7 +4423,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-44.94</t>
+          <t>-43.04</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4433,17 +4433,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>7.08</t>
+          <t>6.60</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>-1.14</t>
+          <t>1.92</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4454,73 +4454,73 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>999</t>
+          <t>799</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>23.08</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>7.69</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>-4.26</t>
+          <t>1.20</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>-8.89</t>
+          <t>-10.06</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>-7.5</t>
+          <t>-7.84</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>-5.97</t>
+          <t>-6.04</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>136.3</t>
+          <t>133.4</t>
         </is>
       </c>
       <c r="AM10" t="n">
-        <v>149.6</v>
+        <v>148.32</v>
       </c>
       <c r="AN10" t="n">
-        <v>161.73</v>
+        <v>160.95</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>171.99</t>
+          <t>171.29</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>-28.35</t>
+          <t>-21.52</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>-8.34</t>
+          <t>-8.35</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>-6.50</t>
+          <t>-6.87</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -4530,7 +4530,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-126.11</t>
+          <t>-127.59</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4540,43 +4540,43 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>1682419827.202991</t>
+          <t>1680267492.872689</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>223746689.0</t>
+          <t>212878160.0</t>
         </is>
       </c>
       <c r="AX10" t="n">
-        <v>397436778.6</v>
+        <v>421450515</v>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>263301806.5</t>
+          <t>274650710.4</t>
         </is>
       </c>
       <c r="AZ10" t="n">
-        <v>254911229.58</v>
+        <v>254522728.7</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>134134972</t>
+          <t>146799804</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>6892793.183689982</t>
+          <t>8493004.331540482</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>27925349.16970986</t>
+          <t>17294165.64471823</t>
         </is>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
-          <t>223746689.0</t>
+          <t>212878160.0</t>
         </is>
       </c>
       <c r="BE10" t="inlineStr">
@@ -4596,7 +4596,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>-27.50</t>
+          <t>-25.00</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
@@ -4641,22 +4641,22 @@
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;可能出現反轉訊號&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;3&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
         <is>
-          <t>價跌量增</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>3.01</t>
+          <t>3.11</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
         <is>
-          <t>2.91</t>
+          <t>2.94</t>
         </is>
       </c>
       <c r="BU10" t="inlineStr">
@@ -4666,7 +4666,7 @@
       </c>
       <c r="BV10" t="inlineStr">
         <is>
-          <t>26.88</t>
+          <t>26.6</t>
         </is>
       </c>
       <c r="BW10" t="inlineStr">
@@ -4686,7 +4686,7 @@
       </c>
       <c r="BZ10" t="inlineStr">
         <is>
-          <t>35306</t>
+          <t>34936</t>
         </is>
       </c>
       <c r="CA10" t="inlineStr">
@@ -4706,22 +4706,22 @@
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>131.0</t>
+          <t>132.0</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>133.5</t>
+          <t>136.0</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>129.0</t>
+          <t>131.5</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>130.5</t>
+          <t>135.0</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
@@ -4753,12 +4753,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>-2.26</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2844.986</t>
+          <t>1712.06</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4778,17 +4778,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>8.74</t>
+          <t>7.77</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-1.69</t>
+          <t>0.18</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>48.25</t>
+          <t>50.94</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4863,17 +4863,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>11.77</t>
+          <t>7.08</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>-2.29</t>
+          <t>-1.14</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4884,12 +4884,12 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>999</t>
+          <t>799</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
@@ -4904,53 +4904,53 @@
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>-6.85</t>
+          <t>-4.26</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>-7.30</t>
+          <t>-8.89</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>-7.05</t>
+          <t>-7.5</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>-5.89</t>
+          <t>-5.97</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>140.1</t>
+          <t>136.3</t>
         </is>
       </c>
       <c r="AM11" t="n">
-        <v>151.12</v>
+        <v>149.6</v>
       </c>
       <c r="AN11" t="n">
-        <v>162.59</v>
+        <v>161.73</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>172.77</t>
+          <t>171.99</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>-28.43</t>
+          <t>-28.35</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>-7.75</t>
+          <t>-8.34</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>-6.04</t>
+          <t>-6.50</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -4960,7 +4960,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-124.26</t>
+          <t>-126.11</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -4970,43 +4970,43 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>1682419827.202991</t>
+          <t>1680267492.872689</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>373359683.0</t>
+          <t>223746689.0</t>
         </is>
       </c>
       <c r="AX11" t="n">
-        <v>374444824.4</v>
+        <v>397436778.6</v>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>252575891.8</t>
+          <t>263301806.5</t>
         </is>
       </c>
       <c r="AZ11" t="n">
-        <v>255257682.72</v>
+        <v>254911229.58</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>121868932</t>
+          <t>134134972</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>3068692.09532273</t>
+          <t>6892793.183689982</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>40950935.056494</t>
+          <t>27925349.16970986</t>
         </is>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
-          <t>373359683.0</t>
+          <t>223746689.0</t>
         </is>
       </c>
       <c r="BE11" t="inlineStr">
@@ -5071,7 +5071,7 @@
       </c>
       <c r="BQ11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR11" t="inlineStr">
@@ -5086,7 +5086,7 @@
       </c>
       <c r="BT11" t="inlineStr">
         <is>
-          <t>2.91</t>
+          <t>2.94</t>
         </is>
       </c>
       <c r="BU11" t="inlineStr">
@@ -5096,7 +5096,7 @@
       </c>
       <c r="BV11" t="inlineStr">
         <is>
-          <t>26.88</t>
+          <t>26.6</t>
         </is>
       </c>
       <c r="BW11" t="inlineStr">
@@ -5116,7 +5116,7 @@
       </c>
       <c r="BZ11" t="inlineStr">
         <is>
-          <t>35306</t>
+          <t>34936</t>
         </is>
       </c>
       <c r="CA11" t="inlineStr">
@@ -5136,17 +5136,17 @@
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>133.0</t>
+          <t>131.0</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>134.5</t>
+          <t>133.5</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>129.5</t>
+          <t>129.0</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
@@ -5183,12 +5183,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>-2.96</t>
+          <t>-2.26</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>4003.393</t>
+          <t>2844.986</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5198,7 +5198,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>133.5</t>
+          <t>130.5</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5208,17 +5208,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>6.64</t>
+          <t>7.77</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-1.69</t>
+          <t>0.18</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>36.89</t>
+          <t>48.25</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5283,7 +5283,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-43.67</t>
+          <t>-44.94</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5293,17 +5293,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>16.56</t>
+          <t>11.77</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>-5.24</t>
+          <t>-2.29</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5314,12 +5314,12 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>999</t>
+          <t>799</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
@@ -5334,53 +5334,53 @@
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>-7.23</t>
+          <t>-6.85</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>-5.73</t>
+          <t>-7.30</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>-6.6</t>
+          <t>-7.05</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>-5.82</t>
+          <t>-5.89</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>143.9</t>
+          <t>140.1</t>
         </is>
       </c>
       <c r="AM12" t="n">
-        <v>152.65</v>
+        <v>151.12</v>
       </c>
       <c r="AN12" t="n">
-        <v>163.44</v>
+        <v>162.59</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>173.54</t>
+          <t>172.77</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>-22.90</t>
+          <t>-28.43</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>-6.89</t>
+          <t>-7.75</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>-5.61</t>
+          <t>-6.04</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
@@ -5390,7 +5390,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-122.53</t>
+          <t>-124.26</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5400,43 +5400,43 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>1682419827.202991</t>
+          <t>1680267492.872689</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>543328425.0</t>
+          <t>373359683.0</t>
         </is>
       </c>
       <c r="AX12" t="n">
-        <v>317370279</v>
+        <v>374444824.4</v>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>231842549.9</t>
+          <t>252575891.8</t>
         </is>
       </c>
       <c r="AZ12" t="n">
-        <v>254515985.98</v>
+        <v>255257682.72</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>85527729</t>
+          <t>121868932</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>-3818988.443072045</t>
+          <t>3068692.09532273</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>42066417.85702515</t>
+          <t>40950935.056494</t>
         </is>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
-          <t>543328425.0</t>
+          <t>373359683.0</t>
         </is>
       </c>
       <c r="BE12" t="inlineStr">
@@ -5456,7 +5456,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>-25.83</t>
+          <t>-27.50</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
@@ -5501,7 +5501,7 @@
       </c>
       <c r="BQ12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;衝高回落,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR12" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>3.08</t>
+          <t>3.01</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
         <is>
-          <t>2.91</t>
+          <t>2.94</t>
         </is>
       </c>
       <c r="BU12" t="inlineStr">
@@ -5526,7 +5526,7 @@
       </c>
       <c r="BV12" t="inlineStr">
         <is>
-          <t>26.88</t>
+          <t>26.6</t>
         </is>
       </c>
       <c r="BW12" t="inlineStr">
@@ -5546,7 +5546,7 @@
       </c>
       <c r="BZ12" t="inlineStr">
         <is>
-          <t>35306</t>
+          <t>34936</t>
         </is>
       </c>
       <c r="CA12" t="inlineStr">
@@ -5566,22 +5566,22 @@
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>135.0</t>
+          <t>133.0</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>141.5</t>
+          <t>134.5</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>132.5</t>
+          <t>129.5</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
         <is>
-          <t>133.5</t>
+          <t>130.5</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">
@@ -5613,12 +5613,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>-0.26</t>
+          <t>0.13</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>455.261</t>
+          <t>363.213</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -5628,7 +5628,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>38.8</t>
+          <t>38.85</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -5643,12 +5643,12 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>1.09</t>
+          <t>0.37</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>-47.41</t>
+          <t>-56.62</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -5713,7 +5713,7 @@
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>-10.08</t>
+          <t>-9.97</t>
         </is>
       </c>
       <c r="X13" t="inlineStr">
@@ -5723,17 +5723,17 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>4.85</t>
+          <t>3.87</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>-1.29</t>
+          <t>0.39</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
@@ -5744,73 +5744,73 @@
       <c r="AC13" t="inlineStr"/>
       <c r="AD13" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
-          <t>455</t>
+          <t>363</t>
         </is>
       </c>
       <c r="AF13" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>90.74</t>
         </is>
       </c>
       <c r="AG13" t="inlineStr">
         <is>
-          <t>94.44</t>
+          <t>91.36</t>
         </is>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-0.26</t>
         </is>
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>2.16</t>
+          <t>2.58</t>
         </is>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>-4.72</t>
+          <t>-4.56</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>-3.16</t>
+          <t>-3.22</t>
         </is>
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>38.8</t>
+          <t>38.95</t>
         </is>
       </c>
       <c r="AM13" t="n">
-        <v>37.98</v>
+        <v>37.97</v>
       </c>
       <c r="AN13" t="n">
-        <v>39.86</v>
+        <v>39.78</v>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>41.16</t>
+          <t>41.11</t>
         </is>
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>47.01</t>
+          <t>52.64</t>
         </is>
       </c>
       <c r="AQ13" t="inlineStr">
         <is>
-          <t>-0.38</t>
+          <t>-0.30</t>
         </is>
       </c>
       <c r="AR13" t="inlineStr">
         <is>
-          <t>-0.71</t>
+          <t>-0.63</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr">
@@ -5820,7 +5820,7 @@
       </c>
       <c r="AT13" t="inlineStr">
         <is>
-          <t>-126.44</t>
+          <t>-123.37</t>
         </is>
       </c>
       <c r="AU13" t="inlineStr">
@@ -5830,43 +5830,43 @@
       </c>
       <c r="AV13" t="inlineStr">
         <is>
-          <t>149902651.9038461</t>
+          <t>149719452.0704125</t>
         </is>
       </c>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>17787244.0</t>
+          <t>14075446.0</t>
         </is>
       </c>
       <c r="AX13" t="n">
-        <v>26453801.8</v>
+        <v>21356523.4</v>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>50298085.9</t>
+          <t>49229400.6</t>
         </is>
       </c>
       <c r="AZ13" t="n">
-        <v>33264214.78</v>
+        <v>32854915.68</v>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
-          <t>-23844284</t>
+          <t>-27872877</t>
         </is>
       </c>
       <c r="BB13" t="inlineStr">
         <is>
-          <t>3457425.925196137</t>
+          <t>2428375.311425582</t>
         </is>
       </c>
       <c r="BC13" t="inlineStr">
         <is>
-          <t>-1428434.048330702</t>
+          <t>-3231403.064312473</t>
         </is>
       </c>
       <c r="BD13" t="inlineStr">
         <is>
-          <t>17787244.0</t>
+          <t>14075446.0</t>
         </is>
       </c>
       <c r="BE13" t="inlineStr">
@@ -5886,7 +5886,7 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>-6.51</t>
+          <t>-6.39</t>
         </is>
       </c>
       <c r="BI13" t="inlineStr">
@@ -5931,7 +5931,7 @@
       </c>
       <c r="BQ13" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR13" t="inlineStr">
@@ -5956,7 +5956,7 @@
       </c>
       <c r="BV13" t="inlineStr">
         <is>
-          <t>16.03</t>
+          <t>16.05</t>
         </is>
       </c>
       <c r="BW13" t="inlineStr">
@@ -5976,7 +5976,7 @@
       </c>
       <c r="BZ13" t="inlineStr">
         <is>
-          <t>12460</t>
+          <t>12477</t>
         </is>
       </c>
       <c r="CA13" t="inlineStr">
@@ -5996,22 +5996,22 @@
       </c>
       <c r="CD13" t="inlineStr">
         <is>
+          <t>38.9</t>
+        </is>
+      </c>
+      <c r="CE13" t="inlineStr">
+        <is>
+          <t>38.95</t>
+        </is>
+      </c>
+      <c r="CF13" t="inlineStr">
+        <is>
           <t>38.6</t>
         </is>
       </c>
-      <c r="CE13" t="inlineStr">
-        <is>
-          <t>39.5</t>
-        </is>
-      </c>
-      <c r="CF13" t="inlineStr">
-        <is>
-          <t>38.6</t>
-        </is>
-      </c>
       <c r="CG13" t="inlineStr">
         <is>
-          <t>38.8</t>
+          <t>38.85</t>
         </is>
       </c>
       <c r="CH13" t="inlineStr">
@@ -6043,12 +6043,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>-0.51</t>
+          <t>-0.26</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>492.79</t>
+          <t>455.261</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -6058,7 +6058,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>38.9</t>
+          <t>38.8</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -6068,17 +6068,17 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>-0.26</t>
+          <t>0.13</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>1.09</t>
+          <t>0.37</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>32.35</t>
+          <t>-47.41</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -6143,7 +6143,7 @@
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>-9.85</t>
+          <t>-10.08</t>
         </is>
       </c>
       <c r="X14" t="inlineStr">
@@ -6153,17 +6153,17 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>5.25</t>
+          <t>4.85</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>-0.12</t>
+          <t>-1.29</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
@@ -6174,73 +6174,73 @@
       <c r="AC14" t="inlineStr"/>
       <c r="AD14" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
-          <t>455</t>
+          <t>363</t>
         </is>
       </c>
       <c r="AF14" t="inlineStr">
         <is>
-          <t>93.33</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="AG14" t="inlineStr">
         <is>
-          <t>97.78</t>
+          <t>94.44</t>
         </is>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>1.25</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>1.10</t>
+          <t>2.16</t>
         </is>
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>-4.8</t>
+          <t>-4.72</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>-3.07</t>
+          <t>-3.16</t>
         </is>
       </c>
       <c r="AL14" t="inlineStr">
         <is>
-          <t>38.42</t>
+          <t>38.8</t>
         </is>
       </c>
       <c r="AM14" t="n">
-        <v>38</v>
+        <v>37.98</v>
       </c>
       <c r="AN14" t="n">
-        <v>39.92</v>
+        <v>39.86</v>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>41.18</t>
+          <t>41.16</t>
         </is>
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>41.20</t>
+          <t>47.01</t>
         </is>
       </c>
       <c r="AQ14" t="inlineStr">
         <is>
-          <t>-0.47</t>
+          <t>-0.38</t>
         </is>
       </c>
       <c r="AR14" t="inlineStr">
         <is>
-          <t>-0.79</t>
+          <t>-0.71</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr">
@@ -6250,7 +6250,7 @@
       </c>
       <c r="AT14" t="inlineStr">
         <is>
-          <t>-129.55</t>
+          <t>-126.44</t>
         </is>
       </c>
       <c r="AU14" t="inlineStr">
@@ -6260,43 +6260,43 @@
       </c>
       <c r="AV14" t="inlineStr">
         <is>
-          <t>149902651.9038461</t>
+          <t>149719452.0704125</t>
         </is>
       </c>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>19156578.0</t>
+          <t>17787244.0</t>
         </is>
       </c>
       <c r="AX14" t="n">
-        <v>69426442.8</v>
+        <v>26453801.8</v>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
-          <t>52456837.4</t>
+          <t>50298085.9</t>
         </is>
       </c>
       <c r="AZ14" t="n">
-        <v>33433682.52</v>
+        <v>33264214.78</v>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
-          <t>16969605</t>
+          <t>-23844284</t>
         </is>
       </c>
       <c r="BB14" t="inlineStr">
         <is>
-          <t>4345764.102201018</t>
+          <t>3457425.925196137</t>
         </is>
       </c>
       <c r="BC14" t="inlineStr">
         <is>
-          <t>800558.8333693519</t>
+          <t>-1428434.048330702</t>
         </is>
       </c>
       <c r="BD14" t="inlineStr">
         <is>
-          <t>19156578.0</t>
+          <t>17787244.0</t>
         </is>
       </c>
       <c r="BE14" t="inlineStr">
@@ -6316,7 +6316,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>-6.27</t>
+          <t>-6.51</t>
         </is>
       </c>
       <c r="BI14" t="inlineStr">
@@ -6361,7 +6361,7 @@
       </c>
       <c r="BQ14" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR14" t="inlineStr">
@@ -6386,7 +6386,7 @@
       </c>
       <c r="BV14" t="inlineStr">
         <is>
-          <t>16.03</t>
+          <t>16.05</t>
         </is>
       </c>
       <c r="BW14" t="inlineStr">
@@ -6406,7 +6406,7 @@
       </c>
       <c r="BZ14" t="inlineStr">
         <is>
-          <t>12460</t>
+          <t>12477</t>
         </is>
       </c>
       <c r="CA14" t="inlineStr">
@@ -6426,12 +6426,12 @@
       </c>
       <c r="CD14" t="inlineStr">
         <is>
-          <t>39.1</t>
+          <t>38.6</t>
         </is>
       </c>
       <c r="CE14" t="inlineStr">
         <is>
-          <t>39.25</t>
+          <t>39.5</t>
         </is>
       </c>
       <c r="CF14" t="inlineStr">
@@ -6441,7 +6441,7 @@
       </c>
       <c r="CG14" t="inlineStr">
         <is>
-          <t>38.9</t>
+          <t>38.8</t>
         </is>
       </c>
       <c r="CH14" t="inlineStr">
@@ -6473,12 +6473,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-0.51</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>510.601</t>
+          <t>492.79</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -6488,7 +6488,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>39.1</t>
+          <t>38.9</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -6498,17 +6498,17 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>-0.77</t>
+          <t>-0.13</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>1.09</t>
+          <t>0.37</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>32.21</t>
+          <t>32.35</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -6573,7 +6573,7 @@
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>-9.39</t>
+          <t>-9.85</t>
         </is>
       </c>
       <c r="X15" t="inlineStr">
@@ -6583,17 +6583,17 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>5.44</t>
+          <t>5.25</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>0.39</t>
+          <t>-0.12</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
@@ -6604,73 +6604,73 @@
       <c r="AC15" t="inlineStr"/>
       <c r="AD15" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
-          <t>455</t>
+          <t>363</t>
         </is>
       </c>
       <c r="AF15" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>93.33</t>
         </is>
       </c>
       <c r="AG15" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>97.78</t>
         </is>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>2.87</t>
+          <t>1.25</t>
         </is>
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>-0.09</t>
+          <t>1.10</t>
         </is>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>-4.82</t>
+          <t>-4.8</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>-2.98</t>
+          <t>-3.07</t>
         </is>
       </c>
       <c r="AL15" t="inlineStr">
         <is>
-          <t>38.01000000000001</t>
+          <t>38.42</t>
         </is>
       </c>
       <c r="AM15" t="n">
-        <v>38.04</v>
+        <v>38</v>
       </c>
       <c r="AN15" t="n">
-        <v>39.97</v>
+        <v>39.92</v>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>41.2</t>
+          <t>41.18</t>
         </is>
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>33.12</t>
+          <t>41.20</t>
         </is>
       </c>
       <c r="AQ15" t="inlineStr">
         <is>
-          <t>-0.59</t>
+          <t>-0.47</t>
         </is>
       </c>
       <c r="AR15" t="inlineStr">
         <is>
-          <t>-0.88</t>
+          <t>-0.79</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr">
@@ -6680,7 +6680,7 @@
       </c>
       <c r="AT15" t="inlineStr">
         <is>
-          <t>-132.60</t>
+          <t>-129.55</t>
         </is>
       </c>
       <c r="AU15" t="inlineStr">
@@ -6690,43 +6690,43 @@
       </c>
       <c r="AV15" t="inlineStr">
         <is>
-          <t>149902651.9038461</t>
+          <t>149719452.0704125</t>
         </is>
       </c>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>19953309.0</t>
+          <t>19156578.0</t>
         </is>
       </c>
       <c r="AX15" t="n">
-        <v>73854919.59999999</v>
+        <v>69426442.8</v>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>55863021.8</t>
+          <t>52456837.4</t>
         </is>
       </c>
       <c r="AZ15" t="n">
-        <v>33328621.84</v>
+        <v>33433682.52</v>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
-          <t>17991897</t>
+          <t>16969605</t>
         </is>
       </c>
       <c r="BB15" t="inlineStr">
         <is>
-          <t>4990346.878352229</t>
+          <t>4345764.102201018</t>
         </is>
       </c>
       <c r="BC15" t="inlineStr">
         <is>
-          <t>3809528.634606227</t>
+          <t>800558.8333693519</t>
         </is>
       </c>
       <c r="BD15" t="inlineStr">
         <is>
-          <t>19953309.0</t>
+          <t>19156578.0</t>
         </is>
       </c>
       <c r="BE15" t="inlineStr">
@@ -6746,7 +6746,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>-5.78</t>
+          <t>-6.27</t>
         </is>
       </c>
       <c r="BI15" t="inlineStr">
@@ -6791,17 +6791,17 @@
       </c>
       <c r="BQ15" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR15" t="inlineStr">
         <is>
-          <t>價-量縮</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS15" t="inlineStr">
         <is>
-          <t>1.08</t>
+          <t>1.07</t>
         </is>
       </c>
       <c r="BT15" t="inlineStr">
@@ -6816,7 +6816,7 @@
       </c>
       <c r="BV15" t="inlineStr">
         <is>
-          <t>16.03</t>
+          <t>16.05</t>
         </is>
       </c>
       <c r="BW15" t="inlineStr">
@@ -6836,7 +6836,7 @@
       </c>
       <c r="BZ15" t="inlineStr">
         <is>
-          <t>12460</t>
+          <t>12477</t>
         </is>
       </c>
       <c r="CA15" t="inlineStr">
@@ -6856,22 +6856,22 @@
       </c>
       <c r="CD15" t="inlineStr">
         <is>
-          <t>39.15</t>
+          <t>39.1</t>
         </is>
       </c>
       <c r="CE15" t="inlineStr">
         <is>
-          <t>39.3</t>
+          <t>39.25</t>
         </is>
       </c>
       <c r="CF15" t="inlineStr">
         <is>
-          <t>38.75</t>
+          <t>38.6</t>
         </is>
       </c>
       <c r="CG15" t="inlineStr">
         <is>
-          <t>39.1</t>
+          <t>38.9</t>
         </is>
       </c>
       <c r="CH15" t="inlineStr">
@@ -6903,12 +6903,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>2.61</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>914.803</t>
+          <t>510.601</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -6928,17 +6928,17 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>-0.77</t>
+          <t>-0.64</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>1.09</t>
+          <t>0.37</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>35.32</t>
+          <t>32.21</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -7013,17 +7013,17 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>9.75</t>
+          <t>5.44</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>1.47</t>
+          <t>0.39</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
@@ -7034,12 +7034,12 @@
       <c r="AC16" t="inlineStr"/>
       <c r="AD16" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
-          <t>455</t>
+          <t>363</t>
         </is>
       </c>
       <c r="AF16" t="inlineStr">
@@ -7049,58 +7049,58 @@
       </c>
       <c r="AG16" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>4.35</t>
+          <t>2.87</t>
         </is>
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>-1.59</t>
+          <t>-0.09</t>
         </is>
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>-4.88</t>
+          <t>-4.82</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>-2.87</t>
+          <t>-2.98</t>
         </is>
       </c>
       <c r="AL16" t="inlineStr">
         <is>
-          <t>37.47</t>
+          <t>38.01000000000001</t>
         </is>
       </c>
       <c r="AM16" t="n">
-        <v>38.08</v>
+        <v>38.04</v>
       </c>
       <c r="AN16" t="n">
-        <v>40.03</v>
+        <v>39.97</v>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>41.21</t>
+          <t>41.2</t>
         </is>
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>20.99</t>
+          <t>33.12</t>
         </is>
       </c>
       <c r="AQ16" t="inlineStr">
         <is>
-          <t>-0.75</t>
+          <t>-0.59</t>
         </is>
       </c>
       <c r="AR16" t="inlineStr">
         <is>
-          <t>-0.95</t>
+          <t>-0.88</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr">
@@ -7110,7 +7110,7 @@
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>-135.29</t>
+          <t>-132.60</t>
         </is>
       </c>
       <c r="AU16" t="inlineStr">
@@ -7120,43 +7120,43 @@
       </c>
       <c r="AV16" t="inlineStr">
         <is>
-          <t>149902651.9038461</t>
+          <t>149719452.0704125</t>
         </is>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>35810040.0</t>
+          <t>19953309.0</t>
         </is>
       </c>
       <c r="AX16" t="n">
-        <v>75499582.59999999</v>
+        <v>73854919.59999999</v>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>55792550.2</t>
+          <t>55863021.8</t>
         </is>
       </c>
       <c r="AZ16" t="n">
-        <v>33454972.78</v>
+        <v>33328621.84</v>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
-          <t>19707032</t>
+          <t>17991897</t>
         </is>
       </c>
       <c r="BB16" t="inlineStr">
         <is>
-          <t>5205041.104487866</t>
+          <t>4990346.878352229</t>
         </is>
       </c>
       <c r="BC16" t="inlineStr">
         <is>
-          <t>7886638.29228013</t>
+          <t>3809528.634606227</t>
         </is>
       </c>
       <c r="BD16" t="inlineStr">
         <is>
-          <t>35810040.0</t>
+          <t>19953309.0</t>
         </is>
       </c>
       <c r="BE16" t="inlineStr">
@@ -7221,12 +7221,12 @@
       </c>
       <c r="BQ16" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR16" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量縮</t>
         </is>
       </c>
       <c r="BS16" t="inlineStr">
@@ -7246,7 +7246,7 @@
       </c>
       <c r="BV16" t="inlineStr">
         <is>
-          <t>16.03</t>
+          <t>16.05</t>
         </is>
       </c>
       <c r="BW16" t="inlineStr">
@@ -7266,7 +7266,7 @@
       </c>
       <c r="BZ16" t="inlineStr">
         <is>
-          <t>12460</t>
+          <t>12477</t>
         </is>
       </c>
       <c r="CA16" t="inlineStr">
@@ -7286,17 +7286,17 @@
       </c>
       <c r="CD16" t="inlineStr">
         <is>
-          <t>38.3</t>
+          <t>39.15</t>
         </is>
       </c>
       <c r="CE16" t="inlineStr">
         <is>
-          <t>39.5</t>
+          <t>39.3</t>
         </is>
       </c>
       <c r="CF16" t="inlineStr">
         <is>
-          <t>38.15</t>
+          <t>38.75</t>
         </is>
       </c>
       <c r="CG16" t="inlineStr">
@@ -7333,12 +7333,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>3.24</t>
+          <t>2.61</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>1043.085</t>
+          <t>914.803</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -7348,7 +7348,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>38.1</t>
+          <t>39.1</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -7358,17 +7358,17 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>1.8</t>
+          <t>-0.64</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>1.09</t>
+          <t>0.37</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>41.43</t>
+          <t>35.32</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -7433,7 +7433,7 @@
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>-11.70</t>
+          <t>-9.39</t>
         </is>
       </c>
       <c r="X17" t="inlineStr">
@@ -7443,17 +7443,17 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>11.11</t>
+          <t>9.75</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2.71</t>
+          <t>1.47</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
@@ -7464,12 +7464,12 @@
       <c r="AC17" t="inlineStr"/>
       <c r="AD17" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
-          <t>455</t>
+          <t>363</t>
         </is>
       </c>
       <c r="AF17" t="inlineStr">
@@ -7479,60 +7479,60 @@
       </c>
       <c r="AG17" t="inlineStr">
         <is>
-          <t>59.17</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>3.34</t>
+          <t>4.35</t>
         </is>
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>-3.27</t>
+          <t>-1.59</t>
         </is>
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>-4.89</t>
+          <t>-4.88</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>-2.80</t>
+          <t>-2.87</t>
         </is>
       </c>
       <c r="AL17" t="inlineStr">
         <is>
-          <t>36.87</t>
+          <t>37.47</t>
         </is>
       </c>
       <c r="AM17" t="n">
-        <v>38.11</v>
+        <v>38.08</v>
       </c>
       <c r="AN17" t="n">
-        <v>40.07</v>
+        <v>40.03</v>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>41.23</t>
+          <t>41.21</t>
         </is>
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>5.10</t>
+          <t>20.99</t>
         </is>
       </c>
       <c r="AQ17" t="inlineStr">
         <is>
+          <t>-0.75</t>
+        </is>
+      </c>
+      <c r="AR17" t="inlineStr">
+        <is>
           <t>-0.95</t>
         </is>
       </c>
-      <c r="AR17" t="inlineStr">
-        <is>
-          <t>-1.00</t>
-        </is>
-      </c>
       <c r="AS17" t="inlineStr">
         <is>
           <t>2.69</t>
@@ -7540,7 +7540,7 @@
       </c>
       <c r="AT17" t="inlineStr">
         <is>
-          <t>-137.15</t>
+          <t>-135.29</t>
         </is>
       </c>
       <c r="AU17" t="inlineStr">
@@ -7550,43 +7550,43 @@
       </c>
       <c r="AV17" t="inlineStr">
         <is>
-          <t>149902651.9038461</t>
+          <t>149719452.0704125</t>
         </is>
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>39561838.0</t>
+          <t>35810040.0</t>
         </is>
       </c>
       <c r="AX17" t="n">
-        <v>77102277.8</v>
+        <v>75499582.59999999</v>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>54515793.2</t>
+          <t>55792550.2</t>
         </is>
       </c>
       <c r="AZ17" t="n">
-        <v>33864219.92</v>
+        <v>33454972.78</v>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
-          <t>22586484</t>
+          <t>19707032</t>
         </is>
       </c>
       <c r="BB17" t="inlineStr">
         <is>
-          <t>4717477.979434728</t>
+          <t>5205041.104487866</t>
         </is>
       </c>
       <c r="BC17" t="inlineStr">
         <is>
-          <t>11730479.54280426</t>
+          <t>7886638.29228013</t>
         </is>
       </c>
       <c r="BD17" t="inlineStr">
         <is>
-          <t>39561838.0</t>
+          <t>35810040.0</t>
         </is>
       </c>
       <c r="BE17" t="inlineStr">
@@ -7606,7 +7606,7 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>-8.19</t>
+          <t>-5.78</t>
         </is>
       </c>
       <c r="BI17" t="inlineStr">
@@ -7651,17 +7651,17 @@
       </c>
       <c r="BQ17" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR17" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS17" t="inlineStr">
         <is>
-          <t>1.05</t>
+          <t>1.08</t>
         </is>
       </c>
       <c r="BT17" t="inlineStr">
@@ -7676,7 +7676,7 @@
       </c>
       <c r="BV17" t="inlineStr">
         <is>
-          <t>16.03</t>
+          <t>16.05</t>
         </is>
       </c>
       <c r="BW17" t="inlineStr">
@@ -7696,7 +7696,7 @@
       </c>
       <c r="BZ17" t="inlineStr">
         <is>
-          <t>12460</t>
+          <t>12477</t>
         </is>
       </c>
       <c r="CA17" t="inlineStr">
@@ -7716,22 +7716,22 @@
       </c>
       <c r="CD17" t="inlineStr">
         <is>
-          <t>37.05</t>
+          <t>38.3</t>
         </is>
       </c>
       <c r="CE17" t="inlineStr">
         <is>
-          <t>38.2</t>
+          <t>39.5</t>
         </is>
       </c>
       <c r="CF17" t="inlineStr">
         <is>
-          <t>37.0</t>
+          <t>38.15</t>
         </is>
       </c>
       <c r="CG17" t="inlineStr">
         <is>
-          <t>38.1</t>
+          <t>39.1</t>
         </is>
       </c>
       <c r="CH17" t="inlineStr">
@@ -7753,7 +7753,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>【e】</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -7763,12 +7763,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>0.14</t>
+          <t>3.24</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>6301.223</t>
+          <t>1043.085</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -7778,7 +7778,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>36.9</t>
+          <t>38.1</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -7788,17 +7788,17 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>4.9</t>
+          <t>1.93</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>1.09</t>
+          <t>0.37</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>29.52</t>
+          <t>41.43</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -7863,7 +7863,7 @@
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>-14.48</t>
+          <t>-11.70</t>
         </is>
       </c>
       <c r="X18" t="inlineStr">
@@ -7873,17 +7873,17 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>67.14</t>
+          <t>11.11</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>-1.63</t>
+          <t>2.71</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
@@ -7894,73 +7894,73 @@
       <c r="AC18" t="inlineStr"/>
       <c r="AD18" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
-          <t>455</t>
+          <t>363</t>
         </is>
       </c>
       <c r="AF18" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG18" t="inlineStr">
         <is>
-          <t>29.75</t>
+          <t>59.17</t>
         </is>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>0.82</t>
+          <t>3.34</t>
         </is>
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>-4.24</t>
+          <t>-3.27</t>
         </is>
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>-4.85</t>
+          <t>-4.89</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>-2.68</t>
+          <t>-2.80</t>
         </is>
       </c>
       <c r="AL18" t="inlineStr">
         <is>
-          <t>36.60000000000001</t>
+          <t>36.87</t>
         </is>
       </c>
       <c r="AM18" t="n">
-        <v>38.22</v>
+        <v>38.11</v>
       </c>
       <c r="AN18" t="n">
-        <v>40.17</v>
+        <v>40.07</v>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>41.28</t>
+          <t>41.23</t>
         </is>
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>-7.24</t>
+          <t>5.10</t>
         </is>
       </c>
       <c r="AQ18" t="inlineStr">
         <is>
-          <t>-1.08</t>
+          <t>-0.95</t>
         </is>
       </c>
       <c r="AR18" t="inlineStr">
         <is>
-          <t>-1.01</t>
+          <t>-1.00</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr">
@@ -7970,7 +7970,7 @@
       </c>
       <c r="AT18" t="inlineStr">
         <is>
-          <t>-137.62</t>
+          <t>-137.15</t>
         </is>
       </c>
       <c r="AU18" t="inlineStr">
@@ -7980,43 +7980,43 @@
       </c>
       <c r="AV18" t="inlineStr">
         <is>
-          <t>149902651.9038461</t>
+          <t>149719452.0704125</t>
         </is>
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>232650449.0</t>
+          <t>39561838.0</t>
         </is>
       </c>
       <c r="AX18" t="n">
-        <v>74142370</v>
+        <v>77102277.8</v>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>57245793.0</t>
+          <t>54515793.2</t>
         </is>
       </c>
       <c r="AZ18" t="n">
-        <v>34130931.06</v>
+        <v>33864219.92</v>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
-          <t>16896577</t>
+          <t>22586484</t>
         </is>
       </c>
       <c r="BB18" t="inlineStr">
         <is>
-          <t>3442386.786094812</t>
+          <t>4717477.979434728</t>
         </is>
       </c>
       <c r="BC18" t="inlineStr">
         <is>
-          <t>16400757.27416717</t>
+          <t>11730479.54280426</t>
         </is>
       </c>
       <c r="BD18" t="inlineStr">
         <is>
-          <t>232650449.0</t>
+          <t>39561838.0</t>
         </is>
       </c>
       <c r="BE18" t="inlineStr">
@@ -8036,7 +8036,7 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>-11.08</t>
+          <t>-8.19</t>
         </is>
       </c>
       <c r="BI18" t="inlineStr">
@@ -8081,7 +8081,7 @@
       </c>
       <c r="BQ18" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR18" t="inlineStr">
@@ -8091,7 +8091,7 @@
       </c>
       <c r="BS18" t="inlineStr">
         <is>
-          <t>1.02</t>
+          <t>1.05</t>
         </is>
       </c>
       <c r="BT18" t="inlineStr">
@@ -8106,7 +8106,7 @@
       </c>
       <c r="BV18" t="inlineStr">
         <is>
-          <t>16.03</t>
+          <t>16.05</t>
         </is>
       </c>
       <c r="BW18" t="inlineStr">
@@ -8126,7 +8126,7 @@
       </c>
       <c r="BZ18" t="inlineStr">
         <is>
-          <t>12460</t>
+          <t>12477</t>
         </is>
       </c>
       <c r="CA18" t="inlineStr">
@@ -8146,22 +8146,22 @@
       </c>
       <c r="CD18" t="inlineStr">
         <is>
+          <t>37.05</t>
+        </is>
+      </c>
+      <c r="CE18" t="inlineStr">
+        <is>
+          <t>38.2</t>
+        </is>
+      </c>
+      <c r="CF18" t="inlineStr">
+        <is>
           <t>37.0</t>
         </is>
       </c>
-      <c r="CE18" t="inlineStr">
-        <is>
-          <t>37.5</t>
-        </is>
-      </c>
-      <c r="CF18" t="inlineStr">
-        <is>
-          <t>36.9</t>
-        </is>
-      </c>
       <c r="CG18" t="inlineStr">
         <is>
-          <t>36.9</t>
+          <t>38.1</t>
         </is>
       </c>
       <c r="CH18" t="inlineStr">
@@ -8193,12 +8193,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>1.24</t>
+          <t>0.14</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>1128.761</t>
+          <t>6301.223</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -8208,7 +8208,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>36.85</t>
+          <t>36.9</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -8218,17 +8218,17 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>5.03</t>
+          <t>5.02</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>1.09</t>
+          <t>0.37</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>-1.19</t>
+          <t>29.52</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -8293,7 +8293,7 @@
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>-14.60</t>
+          <t>-14.48</t>
         </is>
       </c>
       <c r="X19" t="inlineStr">
@@ -8303,17 +8303,17 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>12.03</t>
+          <t>67.14</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2.09</t>
+          <t>-1.63</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
@@ -8324,274 +8324,274 @@
       <c r="AC19" t="inlineStr"/>
       <c r="AD19" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
-          <t>455</t>
+          <t>363</t>
         </is>
       </c>
       <c r="AF19" t="inlineStr">
         <is>
+          <t>40.0</t>
+        </is>
+      </c>
+      <c r="AG19" t="inlineStr">
+        <is>
+          <t>29.75</t>
+        </is>
+      </c>
+      <c r="AH19" t="inlineStr">
+        <is>
+          <t>0.82</t>
+        </is>
+      </c>
+      <c r="AI19" t="inlineStr">
+        <is>
+          <t>-4.24</t>
+        </is>
+      </c>
+      <c r="AJ19" t="inlineStr">
+        <is>
+          <t>-4.85</t>
+        </is>
+      </c>
+      <c r="AK19" t="inlineStr">
+        <is>
+          <t>-2.68</t>
+        </is>
+      </c>
+      <c r="AL19" t="inlineStr">
+        <is>
+          <t>36.60000000000001</t>
+        </is>
+      </c>
+      <c r="AM19" t="n">
+        <v>38.22</v>
+      </c>
+      <c r="AN19" t="n">
+        <v>40.17</v>
+      </c>
+      <c r="AO19" t="inlineStr">
+        <is>
+          <t>41.28</t>
+        </is>
+      </c>
+      <c r="AP19" t="inlineStr">
+        <is>
+          <t>-7.24</t>
+        </is>
+      </c>
+      <c r="AQ19" t="inlineStr">
+        <is>
+          <t>-1.08</t>
+        </is>
+      </c>
+      <c r="AR19" t="inlineStr">
+        <is>
+          <t>-1.01</t>
+        </is>
+      </c>
+      <c r="AS19" t="inlineStr">
+        <is>
+          <t>2.69</t>
+        </is>
+      </c>
+      <c r="AT19" t="inlineStr">
+        <is>
+          <t>-137.62</t>
+        </is>
+      </c>
+      <c r="AU19" t="inlineStr">
+        <is>
+          <t>2025/11/25</t>
+        </is>
+      </c>
+      <c r="AV19" t="inlineStr">
+        <is>
+          <t>149719452.0704125</t>
+        </is>
+      </c>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>232650449.0</t>
+        </is>
+      </c>
+      <c r="AX19" t="n">
+        <v>74142370</v>
+      </c>
+      <c r="AY19" t="inlineStr">
+        <is>
+          <t>57245793.0</t>
+        </is>
+      </c>
+      <c r="AZ19" t="n">
+        <v>34130931.06</v>
+      </c>
+      <c r="BA19" t="inlineStr">
+        <is>
+          <t>16896577</t>
+        </is>
+      </c>
+      <c r="BB19" t="inlineStr">
+        <is>
+          <t>3442386.786094812</t>
+        </is>
+      </c>
+      <c r="BC19" t="inlineStr">
+        <is>
+          <t>16400757.27416717</t>
+        </is>
+      </c>
+      <c r="BD19" t="inlineStr">
+        <is>
+          <t>232650449.0</t>
+        </is>
+      </c>
+      <c r="BE19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF19" t="inlineStr">
+        <is>
+          <t>41.5</t>
+        </is>
+      </c>
+      <c r="BG19" t="inlineStr">
+        <is>
+          <t>2025/08/07</t>
+        </is>
+      </c>
+      <c r="BH19" t="inlineStr">
+        <is>
+          <t>-11.08</t>
+        </is>
+      </c>
+      <c r="BI19" t="inlineStr">
+        <is>
+          <t>新光鋼</t>
+        </is>
+      </c>
+      <c r="BJ19" t="inlineStr">
+        <is>
+          <t>新光鋼</t>
+        </is>
+      </c>
+      <c r="BK19" t="inlineStr">
+        <is>
+          <t>鋼鐵工業</t>
+        </is>
+      </c>
+      <c r="BL19" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="BM19" t="inlineStr">
+        <is>
+          <t>0.62</t>
+        </is>
+      </c>
+      <c r="BN19" t="inlineStr">
+        <is>
+          <t>-13.67996844119094</t>
+        </is>
+      </c>
+      <c r="BO19" t="inlineStr">
+        <is>
+          <t>-10.11024290164889</t>
+        </is>
+      </c>
+      <c r="BP19" t="inlineStr">
+        <is>
+          <t>24.12947661306339</t>
+        </is>
+      </c>
+      <c r="BQ19" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BR19" t="inlineStr">
+        <is>
+          <t>價-量增</t>
+        </is>
+      </c>
+      <c r="BS19" t="inlineStr">
+        <is>
+          <t>1.02</t>
+        </is>
+      </c>
+      <c r="BT19" t="inlineStr">
+        <is>
+          <t>6.44</t>
+        </is>
+      </c>
+      <c r="BU19" t="inlineStr">
+        <is>
+          <t>11.90</t>
+        </is>
+      </c>
+      <c r="BV19" t="inlineStr">
+        <is>
+          <t>16.05</t>
+        </is>
+      </c>
+      <c r="BW19" t="inlineStr">
+        <is>
+          <t>8.69%</t>
+        </is>
+      </c>
+      <c r="BX19" t="inlineStr">
+        <is>
+          <t>5.19%</t>
+        </is>
+      </c>
+      <c r="BY19" t="inlineStr">
+        <is>
+          <t>30.23</t>
+        </is>
+      </c>
+      <c r="BZ19" t="inlineStr">
+        <is>
+          <t>12477</t>
+        </is>
+      </c>
+      <c r="CA19" t="inlineStr">
+        <is>
+          <t>鋼板38.80%、熱軋及鍍鋅鋼板33.80%、不�袗�板12.60%、特殊鋼板7.00%、加工及其他6.90%、型鋼0.90% (2024年)</t>
+        </is>
+      </c>
+      <c r="CB19" t="inlineStr">
+        <is>
+          <t>新光鋼-鋼鐵工業-上市</t>
+        </is>
+      </c>
+      <c r="CC19" t="inlineStr">
+        <is>
+          <t>鋼鐵工業右下上市</t>
+        </is>
+      </c>
+      <c r="CD19" t="inlineStr">
+        <is>
+          <t>37.0</t>
+        </is>
+      </c>
+      <c r="CE19" t="inlineStr">
+        <is>
           <t>37.5</t>
         </is>
       </c>
-      <c r="AG19" t="inlineStr">
-        <is>
-          <t>16.42</t>
-        </is>
-      </c>
-      <c r="AH19" t="inlineStr">
-        <is>
-          <t>0.66</t>
-        </is>
-      </c>
-      <c r="AI19" t="inlineStr">
-        <is>
-          <t>-4.68</t>
-        </is>
-      </c>
-      <c r="AJ19" t="inlineStr">
-        <is>
-          <t>-4.69</t>
-        </is>
-      </c>
-      <c r="AK19" t="inlineStr">
-        <is>
-          <t>-2.48</t>
-        </is>
-      </c>
-      <c r="AL19" t="inlineStr">
-        <is>
-          <t>36.61</t>
-        </is>
-      </c>
-      <c r="AM19" t="n">
-        <v>38.41</v>
-      </c>
-      <c r="AN19" t="n">
-        <v>40.3</v>
-      </c>
-      <c r="AO19" t="inlineStr">
-        <is>
-          <t>41.32</t>
-        </is>
-      </c>
-      <c r="AP19" t="inlineStr">
-        <is>
-          <t>-12.91</t>
-        </is>
-      </c>
-      <c r="AQ19" t="inlineStr">
-        <is>
-          <t>-1.12</t>
-        </is>
-      </c>
-      <c r="AR19" t="inlineStr">
-        <is>
-          <t>-0.99</t>
-        </is>
-      </c>
-      <c r="AS19" t="inlineStr">
-        <is>
-          <t>2.69</t>
-        </is>
-      </c>
-      <c r="AT19" t="inlineStr">
-        <is>
-          <t>-136.94</t>
-        </is>
-      </c>
-      <c r="AU19" t="inlineStr">
-        <is>
-          <t>2025/11/25</t>
-        </is>
-      </c>
-      <c r="AV19" t="inlineStr">
-        <is>
-          <t>149902651.9038461</t>
-        </is>
-      </c>
-      <c r="AW19" t="inlineStr">
-        <is>
-          <t>41298962.0</t>
-        </is>
-      </c>
-      <c r="AX19" t="n">
-        <v>35487232</v>
-      </c>
-      <c r="AY19" t="inlineStr">
-        <is>
-          <t>35914543.8</t>
-        </is>
-      </c>
-      <c r="AZ19" t="n">
-        <v>29950115.64</v>
-      </c>
-      <c r="BA19" t="inlineStr">
-        <is>
-          <t>-427311</t>
-        </is>
-      </c>
-      <c r="BB19" t="inlineStr">
-        <is>
-          <t>1086319.424627111</t>
-        </is>
-      </c>
-      <c r="BC19" t="inlineStr">
-        <is>
-          <t>1798775.809179619</t>
-        </is>
-      </c>
-      <c r="BD19" t="inlineStr">
-        <is>
-          <t>41298962.0</t>
-        </is>
-      </c>
-      <c r="BE19" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BF19" t="inlineStr">
-        <is>
-          <t>41.5</t>
-        </is>
-      </c>
-      <c r="BG19" t="inlineStr">
-        <is>
-          <t>2025/08/07</t>
-        </is>
-      </c>
-      <c r="BH19" t="inlineStr">
-        <is>
-          <t>-11.20</t>
-        </is>
-      </c>
-      <c r="BI19" t="inlineStr">
-        <is>
-          <t>新光鋼</t>
-        </is>
-      </c>
-      <c r="BJ19" t="inlineStr">
-        <is>
-          <t>新光鋼</t>
-        </is>
-      </c>
-      <c r="BK19" t="inlineStr">
-        <is>
-          <t>鋼鐵工業</t>
-        </is>
-      </c>
-      <c r="BL19" t="inlineStr">
-        <is>
-          <t>上市</t>
-        </is>
-      </c>
-      <c r="BM19" t="inlineStr">
-        <is>
-          <t>0.62</t>
-        </is>
-      </c>
-      <c r="BN19" t="inlineStr">
-        <is>
-          <t>-13.67996844119094</t>
-        </is>
-      </c>
-      <c r="BO19" t="inlineStr">
-        <is>
-          <t>-10.11024290164889</t>
-        </is>
-      </c>
-      <c r="BP19" t="inlineStr">
-        <is>
-          <t>24.12947661306339</t>
-        </is>
-      </c>
-      <c r="BQ19" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;可能出現反轉訊號&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;3&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="BR19" t="inlineStr">
-        <is>
-          <t>價-量增</t>
-        </is>
-      </c>
-      <c r="BS19" t="inlineStr">
-        <is>
-          <t>1.01</t>
-        </is>
-      </c>
-      <c r="BT19" t="inlineStr">
-        <is>
-          <t>6.44</t>
-        </is>
-      </c>
-      <c r="BU19" t="inlineStr">
-        <is>
-          <t>11.90</t>
-        </is>
-      </c>
-      <c r="BV19" t="inlineStr">
-        <is>
-          <t>16.03</t>
-        </is>
-      </c>
-      <c r="BW19" t="inlineStr">
-        <is>
-          <t>8.69%</t>
-        </is>
-      </c>
-      <c r="BX19" t="inlineStr">
-        <is>
-          <t>5.19%</t>
-        </is>
-      </c>
-      <c r="BY19" t="inlineStr">
-        <is>
-          <t>30.23</t>
-        </is>
-      </c>
-      <c r="BZ19" t="inlineStr">
-        <is>
-          <t>12460</t>
-        </is>
-      </c>
-      <c r="CA19" t="inlineStr">
-        <is>
-          <t>鋼板38.80%、熱軋及鍍鋅鋼板33.80%、不�袗�板12.60%、特殊鋼板7.00%、加工及其他6.90%、型鋼0.90% (2024年)</t>
-        </is>
-      </c>
-      <c r="CB19" t="inlineStr">
-        <is>
-          <t>新光鋼-鋼鐵工業-上市</t>
-        </is>
-      </c>
-      <c r="CC19" t="inlineStr">
-        <is>
-          <t>鋼鐵工業右下上市</t>
-        </is>
-      </c>
-      <c r="CD19" t="inlineStr">
-        <is>
-          <t>36.4</t>
-        </is>
-      </c>
-      <c r="CE19" t="inlineStr">
-        <is>
-          <t>36.95</t>
-        </is>
-      </c>
       <c r="CF19" t="inlineStr">
         <is>
-          <t>36.0</t>
+          <t>36.9</t>
         </is>
       </c>
       <c r="CG19" t="inlineStr">
         <is>
-          <t>36.85</t>
+          <t>36.9</t>
         </is>
       </c>
       <c r="CH19" t="inlineStr">
@@ -8623,12 +8623,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>0.83</t>
+          <t>1.24</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>776.396</t>
+          <t>1128.761</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -8638,7 +8638,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>36.4</t>
+          <t>36.85</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -8648,17 +8648,17 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>6.19</t>
+          <t>5.15</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>1.09</t>
+          <t>0.37</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>9.74</t>
+          <t>-1.19</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -8723,7 +8723,7 @@
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>-15.64</t>
+          <t>-14.60</t>
         </is>
       </c>
       <c r="X20" t="inlineStr">
@@ -8733,17 +8733,17 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>8.27</t>
+          <t>12.03</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>0.70</t>
+          <t>2.09</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
@@ -8754,73 +8754,73 @@
       <c r="AC20" t="inlineStr"/>
       <c r="AD20" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
-          <t>455</t>
+          <t>363</t>
         </is>
       </c>
       <c r="AF20" t="inlineStr">
         <is>
-          <t>11.76</t>
+          <t>37.5</t>
         </is>
       </c>
       <c r="AG20" t="inlineStr">
         <is>
-          <t>3.92</t>
+          <t>16.42</t>
         </is>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
-          <t>-0.90</t>
+          <t>0.66</t>
         </is>
       </c>
       <c r="AI20" t="inlineStr">
         <is>
-          <t>-4.83</t>
+          <t>-4.68</t>
         </is>
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>-4.54</t>
+          <t>-4.69</t>
         </is>
       </c>
       <c r="AK20" t="inlineStr">
         <is>
-          <t>-2.31</t>
+          <t>-2.48</t>
         </is>
       </c>
       <c r="AL20" t="inlineStr">
         <is>
-          <t>36.73</t>
+          <t>36.61</t>
         </is>
       </c>
       <c r="AM20" t="n">
-        <v>38.6</v>
+        <v>38.41</v>
       </c>
       <c r="AN20" t="n">
-        <v>40.43</v>
+        <v>40.3</v>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>41.39</t>
+          <t>41.32</t>
         </is>
       </c>
       <c r="AP20" t="inlineStr">
         <is>
-          <t>-19.31</t>
+          <t>-12.91</t>
         </is>
       </c>
       <c r="AQ20" t="inlineStr">
         <is>
-          <t>-1.15</t>
+          <t>-1.12</t>
         </is>
       </c>
       <c r="AR20" t="inlineStr">
         <is>
-          <t>-0.96</t>
+          <t>-0.99</t>
         </is>
       </c>
       <c r="AS20" t="inlineStr">
@@ -8830,7 +8830,7 @@
       </c>
       <c r="AT20" t="inlineStr">
         <is>
-          <t>-135.75</t>
+          <t>-136.94</t>
         </is>
       </c>
       <c r="AU20" t="inlineStr">
@@ -8840,43 +8840,43 @@
       </c>
       <c r="AV20" t="inlineStr">
         <is>
-          <t>149902651.9038461</t>
+          <t>149719452.0704125</t>
         </is>
       </c>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>28176624.0</t>
+          <t>41298962.0</t>
         </is>
       </c>
       <c r="AX20" t="n">
-        <v>37871124</v>
+        <v>35487232</v>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
-          <t>34509118.0</t>
+          <t>35914543.8</t>
         </is>
       </c>
       <c r="AZ20" t="n">
-        <v>29545425.32</v>
+        <v>29950115.64</v>
       </c>
       <c r="BA20" t="inlineStr">
         <is>
-          <t>3362006</t>
+          <t>-427311</t>
         </is>
       </c>
       <c r="BB20" t="inlineStr">
         <is>
-          <t>956781.9001630185</t>
+          <t>1086319.424627111</t>
         </is>
       </c>
       <c r="BC20" t="inlineStr">
         <is>
-          <t>1376505.330298137</t>
+          <t>1798775.809179619</t>
         </is>
       </c>
       <c r="BD20" t="inlineStr">
         <is>
-          <t>28176624.0</t>
+          <t>41298962.0</t>
         </is>
       </c>
       <c r="BE20" t="inlineStr">
@@ -8896,7 +8896,7 @@
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>-12.29</t>
+          <t>-11.20</t>
         </is>
       </c>
       <c r="BI20" t="inlineStr">
@@ -8941,17 +8941,17 @@
       </c>
       <c r="BQ20" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;可能出現反轉訊號&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;3&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR20" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS20" t="inlineStr">
         <is>
-          <t>1.00</t>
+          <t>1.01</t>
         </is>
       </c>
       <c r="BT20" t="inlineStr">
@@ -8966,7 +8966,7 @@
       </c>
       <c r="BV20" t="inlineStr">
         <is>
-          <t>16.03</t>
+          <t>16.05</t>
         </is>
       </c>
       <c r="BW20" t="inlineStr">
@@ -8986,7 +8986,7 @@
       </c>
       <c r="BZ20" t="inlineStr">
         <is>
-          <t>12460</t>
+          <t>12477</t>
         </is>
       </c>
       <c r="CA20" t="inlineStr">
@@ -9006,12 +9006,12 @@
       </c>
       <c r="CD20" t="inlineStr">
         <is>
-          <t>36.3</t>
+          <t>36.4</t>
         </is>
       </c>
       <c r="CE20" t="inlineStr">
         <is>
-          <t>36.55</t>
+          <t>36.95</t>
         </is>
       </c>
       <c r="CF20" t="inlineStr">
@@ -9021,7 +9021,7 @@
       </c>
       <c r="CG20" t="inlineStr">
         <is>
-          <t>36.4</t>
+          <t>36.85</t>
         </is>
       </c>
       <c r="CH20" t="inlineStr">
@@ -9053,12 +9053,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>-1.76</t>
+          <t>0.83</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>1212.053</t>
+          <t>776.396</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -9068,7 +9068,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>36.1</t>
+          <t>36.4</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -9078,17 +9078,17 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>6.96</t>
+          <t>6.31</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>1.09</t>
+          <t>0.37</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>3.03</t>
+          <t>9.74</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -9153,7 +9153,7 @@
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>-16.34</t>
+          <t>-15.64</t>
         </is>
       </c>
       <c r="X21" t="inlineStr">
@@ -9163,17 +9163,17 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>12.91</t>
+          <t>8.27</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>-1.38</t>
+          <t>0.70</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
@@ -9184,73 +9184,73 @@
       <c r="AC21" t="inlineStr"/>
       <c r="AD21" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
-          <t>455</t>
+          <t>363</t>
         </is>
       </c>
       <c r="AF21" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>11.76</t>
         </is>
       </c>
       <c r="AG21" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>3.92</t>
         </is>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
-          <t>-2.62</t>
+          <t>-0.90</t>
         </is>
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>-4.47</t>
+          <t>-4.83</t>
         </is>
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>-4.38</t>
+          <t>-4.54</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
         <is>
-          <t>-2.09</t>
+          <t>-2.31</t>
         </is>
       </c>
       <c r="AL21" t="inlineStr">
         <is>
-          <t>37.07000000000001</t>
+          <t>36.73</t>
         </is>
       </c>
       <c r="AM21" t="n">
-        <v>38.8</v>
+        <v>38.6</v>
       </c>
       <c r="AN21" t="n">
-        <v>40.58</v>
+        <v>40.43</v>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>41.45</t>
+          <t>41.39</t>
         </is>
       </c>
       <c r="AP21" t="inlineStr">
         <is>
-          <t>-22.07</t>
+          <t>-19.31</t>
         </is>
       </c>
       <c r="AQ21" t="inlineStr">
         <is>
-          <t>-1.12</t>
+          <t>-1.15</t>
         </is>
       </c>
       <c r="AR21" t="inlineStr">
         <is>
-          <t>-0.91</t>
+          <t>-0.96</t>
         </is>
       </c>
       <c r="AS21" t="inlineStr">
@@ -9260,7 +9260,7 @@
       </c>
       <c r="AT21" t="inlineStr">
         <is>
-          <t>-134.02</t>
+          <t>-135.75</t>
         </is>
       </c>
       <c r="AU21" t="inlineStr">
@@ -9270,43 +9270,43 @@
       </c>
       <c r="AV21" t="inlineStr">
         <is>
-          <t>149902651.9038461</t>
+          <t>149719452.0704125</t>
         </is>
       </c>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>43823516.0</t>
+          <t>28176624.0</t>
         </is>
       </c>
       <c r="AX21" t="n">
-        <v>36085517.8</v>
+        <v>37871124</v>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
-          <t>35025550.9</t>
+          <t>34509118.0</t>
         </is>
       </c>
       <c r="AZ21" t="n">
-        <v>29409986</v>
+        <v>29545425.32</v>
       </c>
       <c r="BA21" t="inlineStr">
         <is>
-          <t>1059966</t>
+          <t>3362006</t>
         </is>
       </c>
       <c r="BB21" t="inlineStr">
         <is>
-          <t>880468.5492293607</t>
+          <t>956781.9001630185</t>
         </is>
       </c>
       <c r="BC21" t="inlineStr">
         <is>
-          <t>2130065.670099653</t>
+          <t>1376505.330298137</t>
         </is>
       </c>
       <c r="BD21" t="inlineStr">
         <is>
-          <t>43823516.0</t>
+          <t>28176624.0</t>
         </is>
       </c>
       <c r="BE21" t="inlineStr">
@@ -9326,7 +9326,7 @@
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>-13.01</t>
+          <t>-12.29</t>
         </is>
       </c>
       <c r="BI21" t="inlineStr">
@@ -9371,7 +9371,7 @@
       </c>
       <c r="BQ21" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR21" t="inlineStr">
@@ -9381,7 +9381,7 @@
       </c>
       <c r="BS21" t="inlineStr">
         <is>
-          <t>0.99</t>
+          <t>1.00</t>
         </is>
       </c>
       <c r="BT21" t="inlineStr">
@@ -9396,7 +9396,7 @@
       </c>
       <c r="BV21" t="inlineStr">
         <is>
-          <t>16.03</t>
+          <t>16.05</t>
         </is>
       </c>
       <c r="BW21" t="inlineStr">
@@ -9416,7 +9416,7 @@
       </c>
       <c r="BZ21" t="inlineStr">
         <is>
-          <t>12460</t>
+          <t>12477</t>
         </is>
       </c>
       <c r="CA21" t="inlineStr">
@@ -9436,22 +9436,22 @@
       </c>
       <c r="CD21" t="inlineStr">
         <is>
-          <t>36.85</t>
+          <t>36.3</t>
         </is>
       </c>
       <c r="CE21" t="inlineStr">
         <is>
-          <t>36.85</t>
+          <t>36.55</t>
         </is>
       </c>
       <c r="CF21" t="inlineStr">
         <is>
-          <t>35.85</t>
+          <t>36.0</t>
         </is>
       </c>
       <c r="CG21" t="inlineStr">
         <is>
-          <t>36.1</t>
+          <t>36.4</t>
         </is>
       </c>
       <c r="CH21" t="inlineStr">
@@ -9483,12 +9483,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>-0.54</t>
+          <t>-1.76</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>672.504</t>
+          <t>1212.053</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -9498,7 +9498,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>36.75</t>
+          <t>36.1</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -9508,17 +9508,17 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>5.28</t>
+          <t>7.08</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>1.09</t>
+          <t>0.37</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>-2.04</t>
+          <t>3.03</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -9583,7 +9583,7 @@
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>-14.83</t>
+          <t>-16.34</t>
         </is>
       </c>
       <c r="X22" t="inlineStr">
@@ -9593,17 +9593,17 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>7.17</t>
+          <t>12.91</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>-1.09</t>
+          <t>-1.38</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
@@ -9614,12 +9614,12 @@
       <c r="AC22" t="inlineStr"/>
       <c r="AD22" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE22" t="inlineStr">
         <is>
-          <t>455</t>
+          <t>363</t>
         </is>
       </c>
       <c r="AF22" t="inlineStr">
@@ -9634,53 +9634,53 @@
       </c>
       <c r="AH22" t="inlineStr">
         <is>
-          <t>-1.92</t>
+          <t>-2.62</t>
         </is>
       </c>
       <c r="AI22" t="inlineStr">
         <is>
-          <t>-3.97</t>
+          <t>-4.47</t>
         </is>
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>-4.25</t>
+          <t>-4.38</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
         <is>
-          <t>-1.83</t>
+          <t>-2.09</t>
         </is>
       </c>
       <c r="AL22" t="inlineStr">
         <is>
-          <t>37.47000000000001</t>
+          <t>37.07000000000001</t>
         </is>
       </c>
       <c r="AM22" t="n">
-        <v>39.02</v>
+        <v>38.8</v>
       </c>
       <c r="AN22" t="n">
-        <v>40.75</v>
+        <v>40.58</v>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>41.51</t>
+          <t>41.45</t>
         </is>
       </c>
       <c r="AP22" t="inlineStr">
         <is>
-          <t>-19.33</t>
+          <t>-22.07</t>
         </is>
       </c>
       <c r="AQ22" t="inlineStr">
         <is>
-          <t>-1.03</t>
+          <t>-1.12</t>
         </is>
       </c>
       <c r="AR22" t="inlineStr">
         <is>
-          <t>-0.86</t>
+          <t>-0.91</t>
         </is>
       </c>
       <c r="AS22" t="inlineStr">
@@ -9690,7 +9690,7 @@
       </c>
       <c r="AT22" t="inlineStr">
         <is>
-          <t>-132.14</t>
+          <t>-134.02</t>
         </is>
       </c>
       <c r="AU22" t="inlineStr">
@@ -9700,43 +9700,43 @@
       </c>
       <c r="AV22" t="inlineStr">
         <is>
-          <t>149902651.9038461</t>
+          <t>149719452.0704125</t>
         </is>
       </c>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>24762299.0</t>
+          <t>43823516.0</t>
         </is>
       </c>
       <c r="AX22" t="n">
-        <v>31929308.6</v>
+        <v>36085517.8</v>
       </c>
       <c r="AY22" t="inlineStr">
         <is>
-          <t>32595150.7</t>
+          <t>35025550.9</t>
         </is>
       </c>
       <c r="AZ22" t="n">
-        <v>29130934.74</v>
+        <v>29409986</v>
       </c>
       <c r="BA22" t="inlineStr">
         <is>
-          <t>-665842</t>
+          <t>1059966</t>
         </is>
       </c>
       <c r="BB22" t="inlineStr">
         <is>
-          <t>653269.0727074891</t>
+          <t>880468.5492293607</t>
         </is>
       </c>
       <c r="BC22" t="inlineStr">
         <is>
-          <t>1454053.953026839</t>
+          <t>2130065.670099653</t>
         </is>
       </c>
       <c r="BD22" t="inlineStr">
         <is>
-          <t>24762299.0</t>
+          <t>43823516.0</t>
         </is>
       </c>
       <c r="BE22" t="inlineStr">
@@ -9756,7 +9756,7 @@
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>-11.45</t>
+          <t>-13.01</t>
         </is>
       </c>
       <c r="BI22" t="inlineStr">
@@ -9811,7 +9811,7 @@
       </c>
       <c r="BS22" t="inlineStr">
         <is>
-          <t>1.01</t>
+          <t>0.99</t>
         </is>
       </c>
       <c r="BT22" t="inlineStr">
@@ -9826,7 +9826,7 @@
       </c>
       <c r="BV22" t="inlineStr">
         <is>
-          <t>16.03</t>
+          <t>16.05</t>
         </is>
       </c>
       <c r="BW22" t="inlineStr">
@@ -9846,7 +9846,7 @@
       </c>
       <c r="BZ22" t="inlineStr">
         <is>
-          <t>12460</t>
+          <t>12477</t>
         </is>
       </c>
       <c r="CA22" t="inlineStr">
@@ -9866,22 +9866,22 @@
       </c>
       <c r="CD22" t="inlineStr">
         <is>
-          <t>36.95</t>
+          <t>36.85</t>
         </is>
       </c>
       <c r="CE22" t="inlineStr">
         <is>
-          <t>37.3</t>
+          <t>36.85</t>
         </is>
       </c>
       <c r="CF22" t="inlineStr">
         <is>
-          <t>36.6</t>
+          <t>35.85</t>
         </is>
       </c>
       <c r="CG22" t="inlineStr">
         <is>
-          <t>36.75</t>
+          <t>36.1</t>
         </is>
       </c>
       <c r="CH22" t="inlineStr">
@@ -9913,12 +9913,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>-1.34</t>
+          <t>-0.54</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>1065.248</t>
+          <t>672.504</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -9928,7 +9928,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>36.95</t>
+          <t>36.75</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -9938,17 +9938,17 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>4.77</t>
+          <t>5.41</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>1.09</t>
+          <t>0.37</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>28.28</t>
+          <t>-2.04</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -10013,7 +10013,7 @@
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>-14.37</t>
+          <t>-14.83</t>
         </is>
       </c>
       <c r="X23" t="inlineStr">
@@ -10023,17 +10023,17 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>11.35</t>
+          <t>7.17</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>-0.81</t>
+          <t>-1.09</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
@@ -10044,12 +10044,12 @@
       <c r="AC23" t="inlineStr"/>
       <c r="AD23" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE23" t="inlineStr">
         <is>
-          <t>455</t>
+          <t>363</t>
         </is>
       </c>
       <c r="AF23" t="inlineStr">
@@ -10059,58 +10059,58 @@
       </c>
       <c r="AG23" t="inlineStr">
         <is>
-          <t>9.38</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
-          <t>-1.86</t>
+          <t>-1.92</t>
         </is>
       </c>
       <c r="AI23" t="inlineStr">
         <is>
-          <t>-4.02</t>
+          <t>-3.97</t>
         </is>
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>-4.09</t>
+          <t>-4.25</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
         <is>
-          <t>-1.60</t>
+          <t>-1.83</t>
         </is>
       </c>
       <c r="AL23" t="inlineStr">
         <is>
-          <t>37.65000000000001</t>
+          <t>37.47000000000001</t>
         </is>
       </c>
       <c r="AM23" t="n">
-        <v>39.23</v>
+        <v>39.02</v>
       </c>
       <c r="AN23" t="n">
-        <v>40.9</v>
+        <v>40.75</v>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>41.57</t>
+          <t>41.51</t>
         </is>
       </c>
       <c r="AP23" t="inlineStr">
         <is>
-          <t>-18.37</t>
+          <t>-19.33</t>
         </is>
       </c>
       <c r="AQ23" t="inlineStr">
         <is>
-          <t>-0.97</t>
+          <t>-1.03</t>
         </is>
       </c>
       <c r="AR23" t="inlineStr">
         <is>
-          <t>-0.82</t>
+          <t>-0.86</t>
         </is>
       </c>
       <c r="AS23" t="inlineStr">
@@ -10120,7 +10120,7 @@
       </c>
       <c r="AT23" t="inlineStr">
         <is>
-          <t>-130.59</t>
+          <t>-132.14</t>
         </is>
       </c>
       <c r="AU23" t="inlineStr">
@@ -10130,43 +10130,43 @@
       </c>
       <c r="AV23" t="inlineStr">
         <is>
-          <t>149902651.9038461</t>
+          <t>149719452.0704125</t>
         </is>
       </c>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>39374759.0</t>
+          <t>24762299.0</t>
         </is>
       </c>
       <c r="AX23" t="n">
-        <v>40349216</v>
+        <v>31929308.6</v>
       </c>
       <c r="AY23" t="inlineStr">
         <is>
-          <t>31454761.9</t>
+          <t>32595150.7</t>
         </is>
       </c>
       <c r="AZ23" t="n">
-        <v>29061426.18</v>
+        <v>29130934.74</v>
       </c>
       <c r="BA23" t="inlineStr">
         <is>
-          <t>8894454</t>
+          <t>-665842</t>
         </is>
       </c>
       <c r="BB23" t="inlineStr">
         <is>
-          <t>507671.8217403347</t>
+          <t>653269.0727074891</t>
         </is>
       </c>
       <c r="BC23" t="inlineStr">
         <is>
-          <t>2478665.680314712</t>
+          <t>1454053.953026839</t>
         </is>
       </c>
       <c r="BD23" t="inlineStr">
         <is>
-          <t>39374759.0</t>
+          <t>24762299.0</t>
         </is>
       </c>
       <c r="BE23" t="inlineStr">
@@ -10186,7 +10186,7 @@
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>-10.96</t>
+          <t>-11.45</t>
         </is>
       </c>
       <c r="BI23" t="inlineStr">
@@ -10231,7 +10231,7 @@
       </c>
       <c r="BQ23" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR23" t="inlineStr">
@@ -10241,7 +10241,7 @@
       </c>
       <c r="BS23" t="inlineStr">
         <is>
-          <t>1.02</t>
+          <t>1.01</t>
         </is>
       </c>
       <c r="BT23" t="inlineStr">
@@ -10256,7 +10256,7 @@
       </c>
       <c r="BV23" t="inlineStr">
         <is>
-          <t>16.03</t>
+          <t>16.05</t>
         </is>
       </c>
       <c r="BW23" t="inlineStr">
@@ -10276,7 +10276,7 @@
       </c>
       <c r="BZ23" t="inlineStr">
         <is>
-          <t>12460</t>
+          <t>12477</t>
         </is>
       </c>
       <c r="CA23" t="inlineStr">
@@ -10296,22 +10296,22 @@
       </c>
       <c r="CD23" t="inlineStr">
         <is>
+          <t>36.95</t>
+        </is>
+      </c>
+      <c r="CE23" t="inlineStr">
+        <is>
           <t>37.3</t>
         </is>
       </c>
-      <c r="CE23" t="inlineStr">
-        <is>
-          <t>37.5</t>
-        </is>
-      </c>
       <c r="CF23" t="inlineStr">
         <is>
-          <t>36.7</t>
+          <t>36.6</t>
         </is>
       </c>
       <c r="CG23" t="inlineStr">
         <is>
-          <t>36.95</t>
+          <t>36.75</t>
         </is>
       </c>
       <c r="CH23" t="inlineStr">

--- a/Result/checksun_type/塔架.xlsx
+++ b/Result/checksun_type/塔架.xlsx
@@ -883,12 +883,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>-1.05</t>
+          <t>-0.7</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>798.983</t>
+          <t>458.513</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>141.5</t>
+          <t>140.5</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>0.18</t>
+          <t>0.92</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>-27.70</t>
+          <t>-28.31</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-40.30</t>
+          <t>-40.72</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -993,17 +993,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>3.30</t>
+          <t>1.90</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>0.73</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1014,73 +1014,73 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>799</t>
+          <t>459</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>81.25</t>
+          <t>68.75</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>88.19</t>
+          <t>83.33</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>-0.14</t>
+          <t>-0.57</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>-0.25</t>
+          <t>-0.11</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>-9.02</t>
+          <t>-9.06</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>-6.02</t>
+          <t>-6.00</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>141.7</t>
+          <t>141.3</t>
         </is>
       </c>
       <c r="AM2" t="n">
-        <v>142.05</v>
+        <v>141.45</v>
       </c>
       <c r="AN2" t="n">
-        <v>156.13</v>
+        <v>155.54</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>166.12</t>
+          <t>165.47</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>23.39</t>
+          <t>24.09</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>-4.59</t>
+          <t>-4.29</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>-5.99</t>
+          <t>-5.65</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -1090,7 +1090,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-124.06</t>
+          <t>-122.69</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1100,43 +1100,43 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>1680267492.872689</t>
+          <t>1678017533.0625</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>112885862.0</t>
+          <t>64197191.0</t>
         </is>
       </c>
       <c r="AX2" t="n">
-        <v>112771125.2</v>
+        <v>100382513</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>155969593.1</t>
+          <t>140014643.3</t>
         </is>
       </c>
       <c r="AZ2" t="n">
-        <v>243086486.76</v>
+        <v>239975244.58</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>-43198467</t>
+          <t>-39632130</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>-10480710.50095323</t>
+          <t>-13293153.18005048</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>-25069163.2987186</t>
+          <t>-28761587.91508535</t>
         </is>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
-          <t>112885862.0</t>
+          <t>64197191.0</t>
         </is>
       </c>
       <c r="BE2" t="inlineStr">
@@ -1156,7 +1156,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>-21.39</t>
+          <t>-21.94</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
@@ -1201,7 +1201,7 @@
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
@@ -1211,12 +1211,12 @@
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>3.26</t>
+          <t>3.24</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
         <is>
-          <t>2.94</t>
+          <t>2.96</t>
         </is>
       </c>
       <c r="BU2" t="inlineStr">
@@ -1226,7 +1226,7 @@
       </c>
       <c r="BV2" t="inlineStr">
         <is>
-          <t>26.6</t>
+          <t>26.41</t>
         </is>
       </c>
       <c r="BW2" t="inlineStr">
@@ -1241,12 +1241,12 @@
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>30.23</t>
+          <t>30.48</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>34936</t>
+          <t>34689</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
@@ -1266,22 +1266,22 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>142.5</t>
+          <t>142.0</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>142.5</t>
+          <t>142.0</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>139.5</t>
+          <t>139.0</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>141.5</t>
+          <t>140.5</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
@@ -1313,12 +1313,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>1.77</t>
+          <t>-1.05</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>999.152</t>
+          <t>798.983</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1328,7 +1328,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>143.0</t>
+          <t>141.5</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1338,17 +1338,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-1.06</t>
+          <t>-0.71</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>0.18</t>
+          <t>0.92</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>-34.04</t>
+          <t>-27.70</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1413,7 +1413,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-39.66</t>
+          <t>-40.30</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1423,17 +1423,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>4.13</t>
+          <t>3.30</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>0.73</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1444,73 +1444,73 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>799</t>
+          <t>459</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>81.25</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>90.28</t>
+          <t>88.19</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>1.27</t>
+          <t>-0.14</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>-1.03</t>
+          <t>-0.25</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-8.91</t>
+          <t>-9.02</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>-6.08</t>
+          <t>-6.02</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>141.2</t>
+          <t>141.7</t>
         </is>
       </c>
       <c r="AM3" t="n">
-        <v>142.68</v>
+        <v>142.05</v>
       </c>
       <c r="AN3" t="n">
-        <v>156.63</v>
+        <v>156.13</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>166.78</t>
+          <t>166.12</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>21.03</t>
+          <t>23.39</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>-5.00</t>
+          <t>-4.59</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>-6.34</t>
+          <t>-5.99</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1520,7 +1520,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-125.46</t>
+          <t>-124.06</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1530,43 +1530,43 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>1680267492.872689</t>
+          <t>1678017533.0625</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>142703815.0</t>
+          <t>112885862.0</t>
         </is>
       </c>
       <c r="AX3" t="n">
-        <v>120065081.4</v>
+        <v>112771125.2</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>182016975.2</t>
+          <t>155969593.1</t>
         </is>
       </c>
       <c r="AZ3" t="n">
-        <v>246778897.84</v>
+        <v>243086486.76</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>-61951893</t>
+          <t>-43198467</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>-7828264.537723166</t>
+          <t>-10480710.50095323</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>-24115587.05038333</t>
+          <t>-25069163.2987186</t>
         </is>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
-          <t>142703815.0</t>
+          <t>112885862.0</t>
         </is>
       </c>
       <c r="BE3" t="inlineStr">
@@ -1586,7 +1586,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>-20.56</t>
+          <t>-21.39</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
@@ -1631,7 +1631,7 @@
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
@@ -1641,12 +1641,12 @@
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>3.29</t>
+          <t>3.26</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
         <is>
-          <t>2.94</t>
+          <t>2.96</t>
         </is>
       </c>
       <c r="BU3" t="inlineStr">
@@ -1656,7 +1656,7 @@
       </c>
       <c r="BV3" t="inlineStr">
         <is>
-          <t>26.6</t>
+          <t>26.41</t>
         </is>
       </c>
       <c r="BW3" t="inlineStr">
@@ -1671,12 +1671,12 @@
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>30.23</t>
+          <t>30.48</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
-          <t>34936</t>
+          <t>34689</t>
         </is>
       </c>
       <c r="CA3" t="inlineStr">
@@ -1696,22 +1696,22 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>141.0</t>
+          <t>142.5</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>145.0</t>
+          <t>142.5</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>141.0</t>
+          <t>139.5</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>143.0</t>
+          <t>141.5</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
@@ -1743,12 +1743,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>-0.35</t>
+          <t>1.77</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>800.978</t>
+          <t>999.152</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1758,7 +1758,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>140.5</t>
+          <t>143.0</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1768,17 +1768,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>0.71</t>
+          <t>-1.78</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>0.18</t>
+          <t>0.92</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>-37.50</t>
+          <t>-34.04</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1843,7 +1843,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-40.72</t>
+          <t>-39.66</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1853,17 +1853,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>3.31</t>
+          <t>4.13</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>0.37</t>
+          <t>0.02</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1874,17 +1874,17 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>799</t>
+          <t>459</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>83.33</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
@@ -1894,53 +1894,53 @@
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>0.14</t>
+          <t>1.27</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>-2.14</t>
+          <t>-1.03</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>-8.77</t>
+          <t>-8.91</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>-6.13</t>
+          <t>-6.08</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>140.3</t>
+          <t>141.2</t>
         </is>
       </c>
       <c r="AM4" t="n">
-        <v>143.38</v>
+        <v>142.68</v>
       </c>
       <c r="AN4" t="n">
-        <v>157.15</v>
+        <v>156.63</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>167.42</t>
+          <t>166.78</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>15.78</t>
+          <t>21.03</t>
